--- a/data/base/goias.xlsx
+++ b/data/base/goias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4221" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4252" uniqueCount="295">
   <si>
     <t>CodCliente</t>
   </si>
@@ -780,6 +780,10 @@
 Estamos encontrando algumas dificuldades nas validações da folha complementar de intermitentes. Como os cálculos são realizados individualmente, o processo exige uma conferência mais detalhada. Após a conclusão das validações, finalizaremos o fechamento. - Data Comentário: 10/09/2026 17:34</t>
   </si>
   <si>
+    <t>Controladoria, Erro de baixa, Chamado Nº Nº DO CHAMADO = 83866  
+Fechamento com erro de relatório no evento S5012 - intermitentes. As informações constam no portal porém o único não considera o lançamento. Chamado foi aberto para a baixa. - Data Comentário: 11/09/2026 16:46</t>
+  </si>
+  <si>
     <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 10/09/2026 
 Em processamento. - Data Comentário: 04/09/2026 08:41</t>
   </si>
@@ -787,6 +791,9 @@
     <t>1. Folha em Processamento  Previsão para conclusão dia 10/09/2026 - Data Comentário: 08/09/2026 15:22</t>
   </si>
   <si>
+    <t>Imposto enviado via SCI Report - Data Comentário: 14/09/2026 09:15</t>
+  </si>
+  <si>
     <t>Imposto enviado via SCI Report - Data Comentário: 11/09/2026 13:44</t>
   </si>
   <si>
@@ -911,6 +918,9 @@
   </si>
   <si>
     <t>2 Semana</t>
+  </si>
+  <si>
+    <t>3 Semana</t>
   </si>
 </sst>
 </file>
@@ -1246,7 +1256,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AI297"/>
+  <dimension ref="A1:AI299"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:35">
@@ -1427,10 +1437,10 @@
         <v>139</v>
       </c>
       <c r="AH2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="3" spans="1:35">
@@ -1504,10 +1514,10 @@
         <v>140</v>
       </c>
       <c r="AH3" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI3" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="4" spans="1:35">
@@ -1581,10 +1591,10 @@
         <v>139</v>
       </c>
       <c r="AH4" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI4" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="5" spans="1:35">
@@ -1655,10 +1665,10 @@
         <v>139</v>
       </c>
       <c r="AH5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI5" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="6" spans="1:35">
@@ -1729,10 +1739,10 @@
         <v>140</v>
       </c>
       <c r="AH6" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="7" spans="1:35">
@@ -1803,10 +1813,10 @@
         <v>140</v>
       </c>
       <c r="AH7" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI7" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="8" spans="1:35">
@@ -1877,10 +1887,10 @@
         <v>141</v>
       </c>
       <c r="AH8" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI8" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9" spans="1:35">
@@ -1951,10 +1961,10 @@
         <v>139</v>
       </c>
       <c r="AH9" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI9" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10" spans="1:35">
@@ -2025,10 +2035,10 @@
         <v>142</v>
       </c>
       <c r="AH10" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI10" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="11" spans="1:35">
@@ -2099,10 +2109,10 @@
         <v>142</v>
       </c>
       <c r="AH11" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI11" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="12" spans="1:35">
@@ -2173,10 +2183,10 @@
         <v>143</v>
       </c>
       <c r="AH12" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI12" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="13" spans="1:35">
@@ -2244,13 +2254,13 @@
         <v>0</v>
       </c>
       <c r="AC13" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AH13" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI13" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="14" spans="1:35">
@@ -2318,13 +2328,13 @@
         <v>0</v>
       </c>
       <c r="AC14" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AH14" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI14" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="15" spans="1:35">
@@ -2392,10 +2402,10 @@
         <v>0</v>
       </c>
       <c r="AH15" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI15" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="16" spans="1:35">
@@ -2457,10 +2467,10 @@
         <v>0</v>
       </c>
       <c r="AH16" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI16" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="17" spans="1:35">
@@ -2528,10 +2538,10 @@
         <v>0</v>
       </c>
       <c r="AH17" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI17" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="18" spans="1:35">
@@ -2605,10 +2615,10 @@
         <v>145</v>
       </c>
       <c r="AH18" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI18" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="19" spans="1:35">
@@ -2682,10 +2692,10 @@
         <v>144</v>
       </c>
       <c r="AH19" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI19" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="20" spans="1:35">
@@ -2759,10 +2769,10 @@
         <v>145</v>
       </c>
       <c r="AH20" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI20" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="21" spans="1:35">
@@ -2836,10 +2846,10 @@
         <v>143</v>
       </c>
       <c r="AH21" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI21" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="22" spans="1:35">
@@ -2910,10 +2920,10 @@
         <v>146</v>
       </c>
       <c r="AH22" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI22" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="23" spans="1:35">
@@ -2984,10 +2994,10 @@
         <v>143</v>
       </c>
       <c r="AH23" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI23" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="24" spans="1:35">
@@ -3058,10 +3068,10 @@
         <v>143</v>
       </c>
       <c r="AH24" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI24" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="25" spans="1:35">
@@ -3132,10 +3142,10 @@
         <v>143</v>
       </c>
       <c r="AH25" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI25" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="26" spans="1:35">
@@ -3206,10 +3216,10 @@
         <v>144</v>
       </c>
       <c r="AH26" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI26" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:35">
@@ -3280,10 +3290,10 @@
         <v>143</v>
       </c>
       <c r="AH27" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI27" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:35">
@@ -3354,10 +3364,10 @@
         <v>143</v>
       </c>
       <c r="AH28" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI28" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:35">
@@ -3428,10 +3438,10 @@
         <v>143</v>
       </c>
       <c r="AH29" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI29" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:35">
@@ -3502,10 +3512,10 @@
         <v>147</v>
       </c>
       <c r="AH30" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI30" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31" spans="1:35">
@@ -3582,10 +3592,10 @@
         <v>148</v>
       </c>
       <c r="AH31" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI31" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="32" spans="1:35">
@@ -3656,10 +3666,10 @@
         <v>149</v>
       </c>
       <c r="AH32" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI32" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="33" spans="1:35">
@@ -3736,10 +3746,10 @@
         <v>150</v>
       </c>
       <c r="AH33" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI33" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="34" spans="1:35">
@@ -3813,10 +3823,10 @@
         <v>151</v>
       </c>
       <c r="AH34" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI34" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="35" spans="1:35">
@@ -3890,13 +3900,13 @@
         <v>0</v>
       </c>
       <c r="AC35" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AH35" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI35" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="36" spans="1:35">
@@ -3973,10 +3983,10 @@
         <v>153</v>
       </c>
       <c r="AH36" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI36" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="37" spans="1:35">
@@ -4053,10 +4063,10 @@
         <v>147</v>
       </c>
       <c r="AH37" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI37" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="38" spans="1:35">
@@ -4130,10 +4140,10 @@
         <v>169</v>
       </c>
       <c r="AH38" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI38" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="39" spans="1:35">
@@ -4210,10 +4220,10 @@
         <v>148</v>
       </c>
       <c r="AH39" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI39" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="40" spans="1:35">
@@ -4290,10 +4300,10 @@
         <v>148</v>
       </c>
       <c r="AH40" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI40" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="41" spans="1:35">
@@ -4370,10 +4380,10 @@
         <v>148</v>
       </c>
       <c r="AH41" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI41" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="42" spans="1:35">
@@ -4450,10 +4460,10 @@
         <v>147</v>
       </c>
       <c r="AH42" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI42" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="43" spans="1:35">
@@ -4530,10 +4540,10 @@
         <v>154</v>
       </c>
       <c r="AH43" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI43" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="44" spans="1:35">
@@ -4610,10 +4620,10 @@
         <v>149</v>
       </c>
       <c r="AH44" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI44" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="45" spans="1:35">
@@ -4690,10 +4700,10 @@
         <v>150</v>
       </c>
       <c r="AH45" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI45" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="46" spans="1:35">
@@ -4761,10 +4771,10 @@
         <v>151</v>
       </c>
       <c r="AH46" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI46" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="47" spans="1:35">
@@ -4835,10 +4845,10 @@
         <v>148</v>
       </c>
       <c r="AH47" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI47" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="48" spans="1:35">
@@ -4909,10 +4919,10 @@
         <v>148</v>
       </c>
       <c r="AH48" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI48" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="49" spans="1:35">
@@ -4983,10 +4993,10 @@
         <v>148</v>
       </c>
       <c r="AH49" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI49" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="50" spans="1:35">
@@ -5057,10 +5067,10 @@
         <v>147</v>
       </c>
       <c r="AH50" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI50" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="51" spans="1:35">
@@ -5131,10 +5141,10 @@
         <v>154</v>
       </c>
       <c r="AH51" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI51" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="52" spans="1:35">
@@ -5211,10 +5221,10 @@
         <v>149</v>
       </c>
       <c r="AH52" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI52" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="53" spans="1:35">
@@ -5285,10 +5295,10 @@
         <v>150</v>
       </c>
       <c r="AH53" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI53" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="54" spans="1:35">
@@ -5365,10 +5375,10 @@
         <v>148</v>
       </c>
       <c r="AH54" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI54" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="55" spans="1:35">
@@ -5445,10 +5455,10 @@
         <v>148</v>
       </c>
       <c r="AH55" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI55" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="56" spans="1:35">
@@ -5525,10 +5535,10 @@
         <v>148</v>
       </c>
       <c r="AH56" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI56" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="57" spans="1:35">
@@ -5605,10 +5615,10 @@
         <v>147</v>
       </c>
       <c r="AH57" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI57" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="58" spans="1:35">
@@ -5682,10 +5692,10 @@
         <v>151</v>
       </c>
       <c r="AH58" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI58" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="59" spans="1:35">
@@ -5759,13 +5769,13 @@
         <v>0</v>
       </c>
       <c r="AC59" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AH59" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI59" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="60" spans="1:35">
@@ -5842,10 +5852,10 @@
         <v>148</v>
       </c>
       <c r="AH60" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI60" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="61" spans="1:35">
@@ -5922,10 +5932,10 @@
         <v>148</v>
       </c>
       <c r="AH61" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI61" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="62" spans="1:35">
@@ -6002,10 +6012,10 @@
         <v>148</v>
       </c>
       <c r="AH62" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI62" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="63" spans="1:35">
@@ -6082,10 +6092,10 @@
         <v>147</v>
       </c>
       <c r="AH63" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI63" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="64" spans="1:35">
@@ -6162,10 +6172,10 @@
         <v>154</v>
       </c>
       <c r="AH64" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI64" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="65" spans="1:35">
@@ -6242,10 +6252,10 @@
         <v>149</v>
       </c>
       <c r="AH65" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI65" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="66" spans="1:35">
@@ -6322,10 +6332,10 @@
         <v>150</v>
       </c>
       <c r="AH66" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI66" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="67" spans="1:35">
@@ -6402,10 +6412,10 @@
         <v>148</v>
       </c>
       <c r="AH67" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI67" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="68" spans="1:35">
@@ -6473,10 +6483,10 @@
         <v>151</v>
       </c>
       <c r="AH68" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI68" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="69" spans="1:35">
@@ -6544,13 +6554,13 @@
         <v>0</v>
       </c>
       <c r="AC69" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AH69" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI69" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="70" spans="1:35">
@@ -6621,10 +6631,10 @@
         <v>148</v>
       </c>
       <c r="AH70" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI70" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="71" spans="1:35">
@@ -6695,10 +6705,10 @@
         <v>148</v>
       </c>
       <c r="AH71" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI71" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="72" spans="1:35">
@@ -6769,10 +6779,10 @@
         <v>148</v>
       </c>
       <c r="AH72" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI72" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="73" spans="1:35">
@@ -6843,10 +6853,10 @@
         <v>147</v>
       </c>
       <c r="AH73" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI73" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="74" spans="1:35">
@@ -6917,10 +6927,10 @@
         <v>154</v>
       </c>
       <c r="AH74" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI74" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="75" spans="1:35">
@@ -6991,10 +7001,10 @@
         <v>149</v>
       </c>
       <c r="AH75" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI75" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="76" spans="1:35">
@@ -7065,10 +7075,10 @@
         <v>150</v>
       </c>
       <c r="AH76" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI76" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="77" spans="1:35">
@@ -7139,10 +7149,10 @@
         <v>150</v>
       </c>
       <c r="AH77" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI77" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="78" spans="1:35">
@@ -7213,10 +7223,10 @@
         <v>150</v>
       </c>
       <c r="AH78" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI78" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="79" spans="1:35">
@@ -7287,10 +7297,10 @@
         <v>150</v>
       </c>
       <c r="AH79" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI79" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="80" spans="1:35">
@@ -7361,10 +7371,10 @@
         <v>156</v>
       </c>
       <c r="AH80" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI80" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="81" spans="1:35">
@@ -7435,10 +7445,10 @@
         <v>156</v>
       </c>
       <c r="AH81" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI81" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="82" spans="1:35">
@@ -7509,10 +7519,10 @@
         <v>157</v>
       </c>
       <c r="AH82" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI82" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="83" spans="1:35">
@@ -7583,10 +7593,10 @@
         <v>156</v>
       </c>
       <c r="AH83" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI83" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="84" spans="1:35">
@@ -7657,10 +7667,10 @@
         <v>156</v>
       </c>
       <c r="AH84" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI84" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="85" spans="1:35">
@@ -7731,10 +7741,10 @@
         <v>156</v>
       </c>
       <c r="AH85" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI85" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="86" spans="1:35">
@@ -7799,10 +7809,10 @@
         <v>157</v>
       </c>
       <c r="AH86" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI86" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="87" spans="1:35">
@@ -7873,10 +7883,10 @@
         <v>156</v>
       </c>
       <c r="AH87" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI87" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="88" spans="1:35">
@@ -7947,10 +7957,10 @@
         <v>156</v>
       </c>
       <c r="AH88" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI88" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="89" spans="1:35">
@@ -8021,10 +8031,10 @@
         <v>156</v>
       </c>
       <c r="AH89" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI89" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="90" spans="1:35">
@@ -8089,10 +8099,10 @@
         <v>156</v>
       </c>
       <c r="AH90" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI90" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="91" spans="1:35">
@@ -8157,10 +8167,10 @@
         <v>157</v>
       </c>
       <c r="AH91" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI91" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="92" spans="1:35">
@@ -8231,10 +8241,10 @@
         <v>156</v>
       </c>
       <c r="AH92" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI92" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="93" spans="1:35">
@@ -8305,10 +8315,10 @@
         <v>156</v>
       </c>
       <c r="AH93" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI93" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="94" spans="1:35">
@@ -8379,10 +8389,10 @@
         <v>156</v>
       </c>
       <c r="AH94" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI94" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="95" spans="1:35">
@@ -8447,10 +8457,10 @@
         <v>156</v>
       </c>
       <c r="AH95" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI95" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="96" spans="1:35">
@@ -8515,10 +8525,10 @@
         <v>157</v>
       </c>
       <c r="AH96" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI96" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="97" spans="1:35">
@@ -8589,10 +8599,10 @@
         <v>156</v>
       </c>
       <c r="AH97" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI97" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="98" spans="1:35">
@@ -8663,10 +8673,10 @@
         <v>156</v>
       </c>
       <c r="AH98" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI98" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="99" spans="1:35">
@@ -8737,10 +8747,10 @@
         <v>157</v>
       </c>
       <c r="AH99" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI99" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="100" spans="1:35">
@@ -8817,10 +8827,10 @@
         <v>156</v>
       </c>
       <c r="AH100" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI100" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="101" spans="1:35">
@@ -8888,10 +8898,10 @@
         <v>156</v>
       </c>
       <c r="AH101" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI101" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="102" spans="1:35">
@@ -8962,10 +8972,10 @@
         <v>156</v>
       </c>
       <c r="AH102" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI102" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="103" spans="1:35">
@@ -9036,10 +9046,10 @@
         <v>156</v>
       </c>
       <c r="AH103" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI103" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="104" spans="1:35">
@@ -9110,10 +9120,10 @@
         <v>156</v>
       </c>
       <c r="AH104" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI104" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="105" spans="1:35">
@@ -9178,10 +9188,10 @@
         <v>156</v>
       </c>
       <c r="AH105" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI105" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="106" spans="1:35">
@@ -9246,10 +9256,10 @@
         <v>157</v>
       </c>
       <c r="AH106" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI106" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="107" spans="1:35">
@@ -9320,10 +9330,10 @@
         <v>156</v>
       </c>
       <c r="AH107" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI107" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="108" spans="1:35">
@@ -9394,10 +9404,10 @@
         <v>156</v>
       </c>
       <c r="AH108" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI108" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="109" spans="1:35">
@@ -9465,10 +9475,10 @@
         <v>156</v>
       </c>
       <c r="AH109" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI109" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="110" spans="1:35">
@@ -9539,10 +9549,10 @@
         <v>157</v>
       </c>
       <c r="AH110" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI110" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="111" spans="1:35">
@@ -9610,10 +9620,10 @@
         <v>159</v>
       </c>
       <c r="AH111" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI111" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="112" spans="1:35">
@@ -9684,10 +9694,10 @@
         <v>157</v>
       </c>
       <c r="AH112" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI112" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="113" spans="1:35">
@@ -9758,10 +9768,10 @@
         <v>155</v>
       </c>
       <c r="AH113" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI113" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="114" spans="1:35">
@@ -9829,10 +9839,10 @@
         <v>159</v>
       </c>
       <c r="AH114" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI114" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="115" spans="1:35">
@@ -9903,10 +9913,10 @@
         <v>157</v>
       </c>
       <c r="AH115" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI115" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="116" spans="1:35">
@@ -9977,10 +9987,10 @@
         <v>156</v>
       </c>
       <c r="AH116" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI116" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="117" spans="1:35">
@@ -10051,10 +10061,10 @@
         <v>156</v>
       </c>
       <c r="AH117" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI117" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="118" spans="1:35">
@@ -10125,10 +10135,10 @@
         <v>156</v>
       </c>
       <c r="AH118" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI118" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="119" spans="1:35">
@@ -10193,10 +10203,10 @@
         <v>156</v>
       </c>
       <c r="AH119" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI119" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="120" spans="1:35">
@@ -10261,10 +10271,10 @@
         <v>157</v>
       </c>
       <c r="AH120" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI120" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="121" spans="1:35">
@@ -10335,10 +10345,10 @@
         <v>156</v>
       </c>
       <c r="AH121" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI121" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="122" spans="1:35">
@@ -10409,10 +10419,10 @@
         <v>156</v>
       </c>
       <c r="AH122" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI122" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="123" spans="1:35">
@@ -10483,10 +10493,10 @@
         <v>156</v>
       </c>
       <c r="AH123" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI123" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="124" spans="1:35">
@@ -10551,10 +10561,10 @@
         <v>156</v>
       </c>
       <c r="AH124" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI124" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="125" spans="1:35">
@@ -10619,10 +10629,10 @@
         <v>157</v>
       </c>
       <c r="AH125" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI125" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="126" spans="1:35">
@@ -10699,10 +10709,10 @@
         <v>157</v>
       </c>
       <c r="AH126" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI126" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="127" spans="1:35">
@@ -10779,10 +10789,10 @@
         <v>157</v>
       </c>
       <c r="AH127" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI127" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="128" spans="1:35">
@@ -10853,10 +10863,10 @@
         <v>160</v>
       </c>
       <c r="AH128" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI128" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="129" spans="1:35">
@@ -10927,10 +10937,10 @@
         <v>160</v>
       </c>
       <c r="AH129" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI129" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="130" spans="1:35">
@@ -11007,10 +11017,10 @@
         <v>160</v>
       </c>
       <c r="AH130" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI130" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="131" spans="1:35">
@@ -11081,10 +11091,10 @@
         <v>160</v>
       </c>
       <c r="AH131" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI131" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="132" spans="1:35">
@@ -11155,10 +11165,10 @@
         <v>160</v>
       </c>
       <c r="AH132" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI132" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="133" spans="1:35">
@@ -11229,10 +11239,10 @@
         <v>160</v>
       </c>
       <c r="AH133" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI133" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="134" spans="1:35">
@@ -11303,10 +11313,10 @@
         <v>160</v>
       </c>
       <c r="AH134" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI134" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="135" spans="1:35">
@@ -11383,10 +11393,10 @@
         <v>160</v>
       </c>
       <c r="AH135" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI135" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="136" spans="1:35">
@@ -11457,10 +11467,10 @@
         <v>160</v>
       </c>
       <c r="AH136" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI136" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="137" spans="1:35">
@@ -11531,10 +11541,10 @@
         <v>160</v>
       </c>
       <c r="AH137" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI137" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="138" spans="1:35">
@@ -11605,10 +11615,10 @@
         <v>160</v>
       </c>
       <c r="AH138" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI138" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="139" spans="1:35">
@@ -11685,10 +11695,10 @@
         <v>160</v>
       </c>
       <c r="AH139" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI139" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="140" spans="1:35">
@@ -11759,10 +11769,10 @@
         <v>160</v>
       </c>
       <c r="AH140" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI140" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="141" spans="1:35">
@@ -11833,10 +11843,10 @@
         <v>160</v>
       </c>
       <c r="AH141" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI141" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="142" spans="1:35">
@@ -11907,10 +11917,10 @@
         <v>160</v>
       </c>
       <c r="AH142" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI142" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="143" spans="1:35">
@@ -11981,10 +11991,10 @@
         <v>160</v>
       </c>
       <c r="AH143" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI143" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="144" spans="1:35">
@@ -12055,10 +12065,10 @@
         <v>160</v>
       </c>
       <c r="AH144" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI144" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="145" spans="1:35">
@@ -12129,10 +12139,10 @@
         <v>160</v>
       </c>
       <c r="AH145" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI145" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="146" spans="1:35">
@@ -12203,10 +12213,10 @@
         <v>160</v>
       </c>
       <c r="AH146" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI146" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="147" spans="1:35">
@@ -12277,10 +12287,10 @@
         <v>160</v>
       </c>
       <c r="AH147" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI147" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="148" spans="1:35">
@@ -12351,10 +12361,10 @@
         <v>160</v>
       </c>
       <c r="AH148" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI148" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="149" spans="1:35">
@@ -12425,10 +12435,10 @@
         <v>160</v>
       </c>
       <c r="AH149" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI149" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="150" spans="1:35">
@@ -12505,10 +12515,10 @@
         <v>160</v>
       </c>
       <c r="AH150" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI150" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="151" spans="1:35">
@@ -12579,10 +12589,10 @@
         <v>160</v>
       </c>
       <c r="AH151" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI151" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="152" spans="1:35">
@@ -12653,10 +12663,10 @@
         <v>160</v>
       </c>
       <c r="AH152" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI152" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="153" spans="1:35">
@@ -12727,10 +12737,10 @@
         <v>160</v>
       </c>
       <c r="AH153" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI153" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="154" spans="1:35">
@@ -12801,10 +12811,10 @@
         <v>161</v>
       </c>
       <c r="AH154" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI154" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="155" spans="1:35">
@@ -12875,10 +12885,10 @@
         <v>161</v>
       </c>
       <c r="AH155" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI155" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="156" spans="1:35">
@@ -12949,10 +12959,10 @@
         <v>161</v>
       </c>
       <c r="AH156" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI156" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="157" spans="1:35">
@@ -13023,10 +13033,10 @@
         <v>161</v>
       </c>
       <c r="AH157" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI157" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="158" spans="1:35">
@@ -13097,10 +13107,10 @@
         <v>161</v>
       </c>
       <c r="AH158" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI158" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="159" spans="1:35">
@@ -13171,10 +13181,10 @@
         <v>161</v>
       </c>
       <c r="AH159" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI159" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="160" spans="1:35">
@@ -13245,10 +13255,10 @@
         <v>161</v>
       </c>
       <c r="AH160" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI160" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="161" spans="1:35">
@@ -13319,10 +13329,10 @@
         <v>161</v>
       </c>
       <c r="AH161" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI161" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="162" spans="1:35">
@@ -13393,10 +13403,10 @@
         <v>161</v>
       </c>
       <c r="AH162" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI162" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="163" spans="1:35">
@@ -13467,10 +13477,10 @@
         <v>161</v>
       </c>
       <c r="AH163" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI163" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="164" spans="1:35">
@@ -13541,10 +13551,10 @@
         <v>161</v>
       </c>
       <c r="AH164" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI164" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="165" spans="1:35">
@@ -13615,10 +13625,10 @@
         <v>161</v>
       </c>
       <c r="AH165" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI165" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="166" spans="1:35">
@@ -13689,10 +13699,10 @@
         <v>161</v>
       </c>
       <c r="AH166" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI166" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="167" spans="1:35">
@@ -13763,10 +13773,10 @@
         <v>161</v>
       </c>
       <c r="AH167" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI167" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="168" spans="1:35">
@@ -13837,10 +13847,10 @@
         <v>161</v>
       </c>
       <c r="AH168" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI168" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="169" spans="1:35">
@@ -13914,10 +13924,10 @@
         <v>161</v>
       </c>
       <c r="AH169" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI169" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="170" spans="1:35">
@@ -13991,10 +14001,10 @@
         <v>161</v>
       </c>
       <c r="AH170" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI170" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="171" spans="1:35">
@@ -14068,10 +14078,10 @@
         <v>161</v>
       </c>
       <c r="AH171" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI171" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="172" spans="1:35">
@@ -14145,10 +14155,10 @@
         <v>161</v>
       </c>
       <c r="AH172" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI172" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="173" spans="1:35">
@@ -14222,10 +14232,10 @@
         <v>161</v>
       </c>
       <c r="AH173" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI173" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="174" spans="1:35">
@@ -14299,10 +14309,10 @@
         <v>161</v>
       </c>
       <c r="AH174" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI174" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="175" spans="1:35">
@@ -14376,10 +14386,10 @@
         <v>161</v>
       </c>
       <c r="AH175" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI175" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="176" spans="1:35">
@@ -14453,10 +14463,10 @@
         <v>161</v>
       </c>
       <c r="AH176" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI176" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="177" spans="1:35">
@@ -14530,10 +14540,10 @@
         <v>161</v>
       </c>
       <c r="AH177" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI177" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="178" spans="1:35">
@@ -14607,10 +14617,10 @@
         <v>161</v>
       </c>
       <c r="AH178" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI178" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="179" spans="1:35">
@@ -14684,10 +14694,10 @@
         <v>161</v>
       </c>
       <c r="AH179" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI179" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="180" spans="1:35">
@@ -14761,10 +14771,10 @@
         <v>161</v>
       </c>
       <c r="AH180" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI180" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="181" spans="1:35">
@@ -14838,10 +14848,10 @@
         <v>161</v>
       </c>
       <c r="AH181" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI181" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="182" spans="1:35">
@@ -14915,10 +14925,10 @@
         <v>161</v>
       </c>
       <c r="AH182" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI182" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="183" spans="1:35">
@@ -14986,10 +14996,10 @@
         <v>161</v>
       </c>
       <c r="AH183" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI183" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="184" spans="1:35">
@@ -15057,10 +15067,10 @@
         <v>161</v>
       </c>
       <c r="AH184" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI184" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="185" spans="1:35">
@@ -15128,10 +15138,10 @@
         <v>161</v>
       </c>
       <c r="AH185" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI185" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="186" spans="1:35">
@@ -15199,10 +15209,10 @@
         <v>161</v>
       </c>
       <c r="AH186" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI186" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="187" spans="1:35">
@@ -15270,10 +15280,10 @@
         <v>161</v>
       </c>
       <c r="AH187" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI187" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="188" spans="1:35">
@@ -15341,10 +15351,10 @@
         <v>161</v>
       </c>
       <c r="AH188" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI188" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="189" spans="1:35">
@@ -15412,10 +15422,10 @@
         <v>54</v>
       </c>
       <c r="AH189" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI189" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="190" spans="1:35">
@@ -15483,10 +15493,10 @@
         <v>54</v>
       </c>
       <c r="AH190" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI190" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="191" spans="1:35">
@@ -15554,10 +15564,10 @@
         <v>54</v>
       </c>
       <c r="AH191" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI191" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="192" spans="1:35">
@@ -15625,10 +15635,10 @@
         <v>54</v>
       </c>
       <c r="AH192" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI192" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="193" spans="1:35">
@@ -15696,10 +15706,10 @@
         <v>162</v>
       </c>
       <c r="AH193" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI193" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="194" spans="1:35">
@@ -15767,10 +15777,10 @@
         <v>55</v>
       </c>
       <c r="AH194" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI194" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="195" spans="1:35">
@@ -15838,10 +15848,10 @@
         <v>54</v>
       </c>
       <c r="AH195" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI195" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="196" spans="1:35">
@@ -15909,10 +15919,10 @@
         <v>54</v>
       </c>
       <c r="AH196" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI196" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="197" spans="1:35">
@@ -15980,10 +15990,10 @@
         <v>54</v>
       </c>
       <c r="AH197" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI197" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="198" spans="1:35">
@@ -16051,10 +16061,10 @@
         <v>162</v>
       </c>
       <c r="AH198" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI198" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="199" spans="1:35">
@@ -16122,10 +16132,10 @@
         <v>54</v>
       </c>
       <c r="AH199" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI199" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="200" spans="1:35">
@@ -16193,10 +16203,10 @@
         <v>162</v>
       </c>
       <c r="AH200" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI200" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="201" spans="1:35">
@@ -16264,10 +16274,10 @@
         <v>54</v>
       </c>
       <c r="AH201" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI201" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="202" spans="1:35">
@@ -16335,10 +16345,10 @@
         <v>54</v>
       </c>
       <c r="AH202" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI202" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="203" spans="1:35">
@@ -16406,10 +16416,10 @@
         <v>54</v>
       </c>
       <c r="AH203" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI203" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="204" spans="1:35">
@@ -16477,10 +16487,10 @@
         <v>54</v>
       </c>
       <c r="AH204" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI204" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="205" spans="1:35">
@@ -16548,10 +16558,10 @@
         <v>54</v>
       </c>
       <c r="AH205" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI205" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="206" spans="1:35">
@@ -16619,10 +16629,10 @@
         <v>54</v>
       </c>
       <c r="AH206" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI206" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="207" spans="1:35">
@@ -16690,10 +16700,10 @@
         <v>162</v>
       </c>
       <c r="AH207" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI207" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="208" spans="1:35">
@@ -16761,10 +16771,10 @@
         <v>55</v>
       </c>
       <c r="AH208" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI208" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="209" spans="1:35">
@@ -16835,10 +16845,10 @@
         <v>54</v>
       </c>
       <c r="AH209" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI209" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="210" spans="1:35">
@@ -16909,10 +16919,10 @@
         <v>54</v>
       </c>
       <c r="AH210" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI210" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="211" spans="1:35">
@@ -16983,10 +16993,10 @@
         <v>54</v>
       </c>
       <c r="AH211" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI211" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="212" spans="1:35">
@@ -17057,10 +17067,10 @@
         <v>54</v>
       </c>
       <c r="AH212" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI212" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="213" spans="1:35">
@@ -17128,10 +17138,10 @@
         <v>54</v>
       </c>
       <c r="AH213" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI213" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="214" spans="1:35">
@@ -17199,10 +17209,10 @@
         <v>54</v>
       </c>
       <c r="AH214" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI214" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="215" spans="1:35">
@@ -17267,10 +17277,10 @@
         <v>0</v>
       </c>
       <c r="AH215" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI215" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="216" spans="1:35">
@@ -17332,10 +17342,10 @@
         <v>0</v>
       </c>
       <c r="AH216" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI216" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="217" spans="1:35">
@@ -17403,13 +17413,13 @@
         <v>0</v>
       </c>
       <c r="AC217" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AH217" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI217" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="218" spans="1:35">
@@ -17483,10 +17493,10 @@
         <v>151</v>
       </c>
       <c r="AH218" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI218" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="219" spans="1:35">
@@ -17563,10 +17573,10 @@
         <v>148</v>
       </c>
       <c r="AH219" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI219" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="220" spans="1:35">
@@ -17643,18 +17653,18 @@
         <v>148</v>
       </c>
       <c r="AH220" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI220" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="221" spans="1:35">
       <c r="A221">
-        <v>6779</v>
+        <v>6628</v>
       </c>
       <c r="B221" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C221" t="s">
         <v>50</v>
@@ -17663,7 +17673,7 @@
         <v>52</v>
       </c>
       <c r="E221" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F221" t="s">
         <v>56</v>
@@ -17684,7 +17694,7 @@
         <v>46275</v>
       </c>
       <c r="O221" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="P221">
         <v>8</v>
@@ -17693,25 +17703,25 @@
         <v>2026</v>
       </c>
       <c r="R221">
-        <v>18090250</v>
+        <v>18052530</v>
       </c>
       <c r="S221" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="T221" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="U221" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V221" s="1">
-        <v>46274.48792050926</v>
+        <v>46279.38429019676</v>
       </c>
       <c r="W221">
         <v>4</v>
       </c>
       <c r="X221" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="Y221" t="s">
         <v>249</v>
@@ -17720,21 +17730,21 @@
         <v>0</v>
       </c>
       <c r="AC221" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="AH221" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI221" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="222" spans="1:35">
       <c r="A222">
-        <v>6945</v>
+        <v>6779</v>
       </c>
       <c r="B222" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C222" t="s">
         <v>50</v>
@@ -17746,7 +17756,7 @@
         <v>54</v>
       </c>
       <c r="F222" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G222">
         <v>9746</v>
@@ -17773,25 +17783,25 @@
         <v>2026</v>
       </c>
       <c r="R222">
-        <v>18179154</v>
+        <v>18090250</v>
       </c>
       <c r="S222" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="T222" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="U222" t="s">
         <v>172</v>
       </c>
       <c r="V222" s="1">
-        <v>46274.588374375</v>
+        <v>46274.48792050926</v>
       </c>
       <c r="W222">
         <v>4</v>
       </c>
       <c r="X222" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Y222" t="s">
         <v>250</v>
@@ -17800,27 +17810,27 @@
         <v>0</v>
       </c>
       <c r="AC222" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="AH222" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI222" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="223" spans="1:35">
       <c r="A223">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B223" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C223" t="s">
         <v>50</v>
       </c>
       <c r="D223" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E223" t="s">
         <v>54</v>
@@ -17843,6 +17853,9 @@
       <c r="N223" s="1">
         <v>46275</v>
       </c>
+      <c r="O223" t="s">
+        <v>134</v>
+      </c>
       <c r="P223">
         <v>8</v>
       </c>
@@ -17850,10 +17863,10 @@
         <v>2026</v>
       </c>
       <c r="R223">
-        <v>18190457</v>
+        <v>18179154</v>
       </c>
       <c r="S223" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="T223" t="s">
         <v>168</v>
@@ -17862,60 +17875,63 @@
         <v>172</v>
       </c>
       <c r="V223" s="1">
-        <v>46274.34198912037</v>
+        <v>46274.588374375</v>
       </c>
       <c r="W223">
         <v>4</v>
       </c>
       <c r="X223" t="s">
-        <v>176</v>
+        <v>177</v>
+      </c>
+      <c r="Y223" t="s">
+        <v>251</v>
       </c>
       <c r="AB223">
         <v>0</v>
       </c>
       <c r="AC223" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AH223" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI223" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="224" spans="1:35">
       <c r="A224">
-        <v>6779</v>
+        <v>6949</v>
       </c>
       <c r="B224" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="C224" t="s">
         <v>50</v>
       </c>
       <c r="D224" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E224" t="s">
         <v>54</v>
       </c>
       <c r="F224" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G224">
-        <v>5867</v>
+        <v>9746</v>
       </c>
       <c r="H224">
-        <v>5786</v>
+        <v>0</v>
       </c>
       <c r="I224" t="s">
         <v>61</v>
       </c>
       <c r="J224" t="s">
-        <v>123</v>
+        <v>80</v>
       </c>
       <c r="N224" s="1">
-        <v>46280</v>
+        <v>46275</v>
       </c>
       <c r="P224">
         <v>8</v>
@@ -17924,48 +17940,45 @@
         <v>2026</v>
       </c>
       <c r="R224">
-        <v>18090178</v>
+        <v>18190457</v>
       </c>
       <c r="S224" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="T224" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="U224" t="s">
         <v>172</v>
       </c>
       <c r="V224" s="1">
-        <v>46276.63187557871</v>
+        <v>46274.34198912037</v>
       </c>
       <c r="W224">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="X224" t="s">
-        <v>179</v>
-      </c>
-      <c r="Y224" t="s">
-        <v>251</v>
+        <v>176</v>
       </c>
       <c r="AB224">
         <v>0</v>
       </c>
       <c r="AC224" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="AH224" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AI224" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="225" spans="1:35">
       <c r="A225">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B225" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C225" t="s">
         <v>50</v>
@@ -17974,49 +17987,52 @@
         <v>51</v>
       </c>
       <c r="E225" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F225" t="s">
         <v>56</v>
       </c>
       <c r="G225">
-        <v>6348</v>
+        <v>5867</v>
       </c>
       <c r="H225">
-        <v>0</v>
+        <v>5786</v>
       </c>
       <c r="I225" t="s">
         <v>61</v>
       </c>
       <c r="J225" t="s">
-        <v>87</v>
+        <v>123</v>
       </c>
       <c r="N225" s="1">
-        <v>46275</v>
-      </c>
-      <c r="O225" t="s">
-        <v>134</v>
+        <v>46280</v>
       </c>
       <c r="P225">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q225">
         <v>2026</v>
       </c>
       <c r="R225">
-        <v>18261361</v>
+        <v>17222618</v>
+      </c>
+      <c r="S225" t="s">
+        <v>153</v>
+      </c>
+      <c r="T225" t="s">
+        <v>167</v>
       </c>
       <c r="U225" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="V225" s="1">
-        <v>46275.39631951389</v>
+        <v>46279.40189383102</v>
       </c>
       <c r="W225">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="X225" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Y225" t="s">
         <v>252</v>
@@ -18025,21 +18041,21 @@
         <v>0</v>
       </c>
       <c r="AC225" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="AH225" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI225" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="226" spans="1:35">
       <c r="A226">
-        <v>6628</v>
+        <v>6779</v>
       </c>
       <c r="B226" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C226" t="s">
         <v>50</v>
@@ -18048,238 +18064,238 @@
         <v>52</v>
       </c>
       <c r="E226" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F226" t="s">
         <v>56</v>
       </c>
       <c r="G226">
-        <v>6348</v>
+        <v>5867</v>
       </c>
       <c r="H226">
-        <v>0</v>
+        <v>5786</v>
       </c>
       <c r="I226" t="s">
         <v>61</v>
       </c>
       <c r="J226" t="s">
-        <v>87</v>
+        <v>123</v>
       </c>
       <c r="N226" s="1">
-        <v>46275</v>
-      </c>
-      <c r="O226" t="s">
-        <v>134</v>
+        <v>46280</v>
       </c>
       <c r="P226">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q226">
         <v>2026</v>
       </c>
       <c r="R226">
-        <v>18261362</v>
+        <v>18090178</v>
+      </c>
+      <c r="S226" t="s">
+        <v>154</v>
+      </c>
+      <c r="T226" t="s">
+        <v>169</v>
       </c>
       <c r="U226" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="V226" s="1">
-        <v>46275.39631994213</v>
+        <v>46276.63187557871</v>
       </c>
       <c r="W226">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="X226" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Y226" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AB226">
         <v>0</v>
       </c>
       <c r="AC226" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="AH226" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI226" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="227" spans="1:35">
       <c r="A227">
-        <v>6945</v>
+        <v>6627</v>
       </c>
       <c r="B227" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C227" t="s">
         <v>50</v>
       </c>
       <c r="D227" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E227" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F227" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G227">
-        <v>1862</v>
+        <v>6348</v>
       </c>
       <c r="H227">
         <v>0</v>
       </c>
       <c r="I227" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J227" t="s">
-        <v>124</v>
+        <v>87</v>
       </c>
       <c r="N227" s="1">
-        <v>46281</v>
+        <v>46275</v>
+      </c>
+      <c r="O227" t="s">
+        <v>134</v>
       </c>
       <c r="P227">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q227">
         <v>2026</v>
       </c>
       <c r="R227">
-        <v>18220176</v>
-      </c>
-      <c r="S227" t="s">
-        <v>159</v>
+        <v>18261361</v>
       </c>
       <c r="U227" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="V227" s="1">
-        <v>46276.37795540509</v>
+        <v>46275.39631951389</v>
       </c>
       <c r="W227">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="X227" t="s">
-        <v>177</v>
+        <v>175</v>
+      </c>
+      <c r="Y227" t="s">
+        <v>254</v>
       </c>
       <c r="AB227">
         <v>0</v>
       </c>
       <c r="AC227" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="AH227" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="AI227" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="228" spans="1:35">
       <c r="A228">
-        <v>6548</v>
+        <v>6628</v>
       </c>
       <c r="B228" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C228" t="s">
         <v>50</v>
       </c>
       <c r="D228" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E228" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F228" t="s">
         <v>56</v>
       </c>
       <c r="G228">
-        <v>6805</v>
+        <v>6348</v>
       </c>
       <c r="H228">
         <v>0</v>
       </c>
       <c r="I228" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J228" t="s">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="N228" s="1">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="O228" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="P228">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q228">
         <v>2026</v>
       </c>
       <c r="R228">
-        <v>17222743</v>
-      </c>
-      <c r="S228" t="s">
-        <v>155</v>
-      </c>
-      <c r="T228" t="s">
-        <v>156</v>
+        <v>18261362</v>
       </c>
       <c r="U228" t="s">
         <v>173</v>
       </c>
       <c r="V228" s="1">
-        <v>46276.66923222222</v>
+        <v>46275.39631994213</v>
       </c>
       <c r="W228">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X228" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y228" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AB228">
         <v>0</v>
       </c>
       <c r="AC228" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="AH228" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI228" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="229" spans="1:35">
       <c r="A229">
-        <v>6627</v>
+        <v>6945</v>
       </c>
       <c r="B229" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C229" t="s">
         <v>50</v>
       </c>
       <c r="D229" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E229" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F229" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G229">
-        <v>6805</v>
+        <v>1862</v>
       </c>
       <c r="H229">
         <v>0</v>
@@ -18288,10 +18304,10 @@
         <v>62</v>
       </c>
       <c r="J229" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N229" s="1">
-        <v>46276</v>
+        <v>46281</v>
       </c>
       <c r="P229">
         <v>8</v>
@@ -18300,54 +18316,51 @@
         <v>2026</v>
       </c>
       <c r="R229">
-        <v>18085519</v>
+        <v>18220176</v>
       </c>
       <c r="S229" t="s">
-        <v>156</v>
-      </c>
-      <c r="T229" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="U229" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="V229" s="1">
-        <v>46276.40669469907</v>
+        <v>46276.37795540509</v>
       </c>
       <c r="W229">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="X229" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AB229">
         <v>0</v>
       </c>
       <c r="AC229" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="AH229" t="s">
         <v>289</v>
       </c>
       <c r="AI229" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="230" spans="1:35">
       <c r="A230">
-        <v>6628</v>
+        <v>6548</v>
       </c>
       <c r="B230" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C230" t="s">
         <v>50</v>
       </c>
       <c r="D230" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E230" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F230" t="s">
         <v>56</v>
@@ -18377,10 +18390,10 @@
         <v>2026</v>
       </c>
       <c r="R230">
-        <v>17988709</v>
+        <v>17222743</v>
       </c>
       <c r="S230" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="T230" t="s">
         <v>156</v>
@@ -18389,48 +18402,48 @@
         <v>173</v>
       </c>
       <c r="V230" s="1">
-        <v>46276.64773491898</v>
+        <v>46276.66923222222</v>
       </c>
       <c r="W230">
         <v>3</v>
       </c>
       <c r="X230" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Y230" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AB230">
         <v>0</v>
       </c>
       <c r="AC230" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AH230" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI230" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="231" spans="1:35">
       <c r="A231">
-        <v>6945</v>
+        <v>6627</v>
       </c>
       <c r="B231" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C231" t="s">
         <v>50</v>
       </c>
       <c r="D231" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E231" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F231" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G231">
         <v>6805</v>
@@ -18447,9 +18460,6 @@
       <c r="N231" s="1">
         <v>46276</v>
       </c>
-      <c r="O231" t="s">
-        <v>137</v>
-      </c>
       <c r="P231">
         <v>8</v>
       </c>
@@ -18457,57 +18467,57 @@
         <v>2026</v>
       </c>
       <c r="R231">
-        <v>18220221</v>
+        <v>18085519</v>
       </c>
       <c r="S231" t="s">
-        <v>159</v>
+        <v>156</v>
+      </c>
+      <c r="T231" t="s">
+        <v>156</v>
       </c>
       <c r="U231" t="s">
         <v>173</v>
       </c>
       <c r="V231" s="1">
-        <v>46276.39101108797</v>
+        <v>46276.40669469907</v>
       </c>
       <c r="W231">
         <v>3</v>
       </c>
       <c r="X231" t="s">
-        <v>177</v>
-      </c>
-      <c r="Y231" t="s">
-        <v>255</v>
+        <v>175</v>
       </c>
       <c r="AB231">
         <v>0</v>
       </c>
       <c r="AC231" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="AH231" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI231" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="232" spans="1:35">
       <c r="A232">
-        <v>6963</v>
+        <v>6628</v>
       </c>
       <c r="B232" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C232" t="s">
         <v>50</v>
       </c>
       <c r="D232" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E232" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F232" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G232">
         <v>6805</v>
@@ -18534,10 +18544,10 @@
         <v>2026</v>
       </c>
       <c r="R232">
-        <v>18187261</v>
+        <v>17988709</v>
       </c>
       <c r="S232" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="T232" t="s">
         <v>156</v>
@@ -18546,13 +18556,13 @@
         <v>173</v>
       </c>
       <c r="V232" s="1">
-        <v>46276.66651596065</v>
+        <v>46276.64773491898</v>
       </c>
       <c r="W232">
         <v>3</v>
       </c>
       <c r="X232" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="Y232" t="s">
         <v>256</v>
@@ -18561,36 +18571,36 @@
         <v>0</v>
       </c>
       <c r="AC232" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AH232" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI232" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="233" spans="1:35">
       <c r="A233">
-        <v>6627</v>
+        <v>6945</v>
       </c>
       <c r="B233" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C233" t="s">
         <v>50</v>
       </c>
       <c r="D233" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E233" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F233" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G233">
-        <v>1866</v>
+        <v>6805</v>
       </c>
       <c r="H233">
         <v>0</v>
@@ -18599,10 +18609,13 @@
         <v>62</v>
       </c>
       <c r="J233" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="N233" s="1">
-        <v>46274</v>
+        <v>46276</v>
+      </c>
+      <c r="O233" t="s">
+        <v>137</v>
       </c>
       <c r="P233">
         <v>8</v>
@@ -18611,25 +18624,22 @@
         <v>2026</v>
       </c>
       <c r="R233">
-        <v>17968368</v>
+        <v>18220221</v>
       </c>
       <c r="S233" t="s">
-        <v>156</v>
-      </c>
-      <c r="T233" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="U233" t="s">
         <v>173</v>
       </c>
       <c r="V233" s="1">
-        <v>46274.36843923611</v>
+        <v>46276.39101108797</v>
       </c>
       <c r="W233">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X233" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Y233" t="s">
         <v>257</v>
@@ -18638,21 +18648,21 @@
         <v>0</v>
       </c>
       <c r="AC233" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="AH233" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AI233" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="234" spans="1:35">
       <c r="A234">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B234" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C234" t="s">
         <v>50</v>
@@ -18667,7 +18677,7 @@
         <v>57</v>
       </c>
       <c r="G234">
-        <v>1866</v>
+        <v>6805</v>
       </c>
       <c r="H234">
         <v>0</v>
@@ -18676,10 +18686,13 @@
         <v>62</v>
       </c>
       <c r="J234" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="N234" s="1">
-        <v>46274</v>
+        <v>46276</v>
+      </c>
+      <c r="O234" t="s">
+        <v>137</v>
       </c>
       <c r="P234">
         <v>8</v>
@@ -18688,7 +18701,7 @@
         <v>2026</v>
       </c>
       <c r="R234">
-        <v>18186946</v>
+        <v>18187261</v>
       </c>
       <c r="S234" t="s">
         <v>158</v>
@@ -18700,10 +18713,10 @@
         <v>173</v>
       </c>
       <c r="V234" s="1">
-        <v>46274.66470667824</v>
+        <v>46276.66651596065</v>
       </c>
       <c r="W234">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X234" t="s">
         <v>178</v>
@@ -18718,30 +18731,30 @@
         <v>158</v>
       </c>
       <c r="AH234" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AI234" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="235" spans="1:35">
       <c r="A235">
-        <v>6963</v>
+        <v>6627</v>
       </c>
       <c r="B235" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C235" t="s">
         <v>50</v>
       </c>
       <c r="D235" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E235" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F235" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G235">
         <v>1866</v>
@@ -18765,10 +18778,10 @@
         <v>2026</v>
       </c>
       <c r="R235">
-        <v>18187212</v>
+        <v>17968368</v>
       </c>
       <c r="S235" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="T235" t="s">
         <v>156</v>
@@ -18777,13 +18790,13 @@
         <v>173</v>
       </c>
       <c r="V235" s="1">
-        <v>46274.74452168981</v>
+        <v>46274.36843923611</v>
       </c>
       <c r="W235">
         <v>5</v>
       </c>
       <c r="X235" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="Y235" t="s">
         <v>259</v>
@@ -18792,36 +18805,36 @@
         <v>0</v>
       </c>
       <c r="AC235" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AH235" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI235" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="236" spans="1:35">
       <c r="A236">
-        <v>6548</v>
+        <v>6962</v>
       </c>
       <c r="B236" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C236" t="s">
         <v>50</v>
       </c>
       <c r="D236" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E236" t="s">
         <v>54</v>
       </c>
       <c r="F236" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G236">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="H236">
         <v>0</v>
@@ -18830,14 +18843,11 @@
         <v>62</v>
       </c>
       <c r="J236" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N236" s="1">
         <v>46274</v>
       </c>
-      <c r="O236" t="s">
-        <v>136</v>
-      </c>
       <c r="P236">
         <v>8</v>
       </c>
@@ -18845,10 +18855,10 @@
         <v>2026</v>
       </c>
       <c r="R236">
-        <v>17988543</v>
+        <v>18186946</v>
       </c>
       <c r="S236" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="T236" t="s">
         <v>156</v>
@@ -18857,13 +18867,13 @@
         <v>173</v>
       </c>
       <c r="V236" s="1">
-        <v>46274.64801501157</v>
+        <v>46274.66470667824</v>
       </c>
       <c r="W236">
         <v>5</v>
       </c>
       <c r="X236" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="Y236" t="s">
         <v>260</v>
@@ -18872,36 +18882,36 @@
         <v>0</v>
       </c>
       <c r="AC236" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="AH236" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI236" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="237" spans="1:35">
       <c r="A237">
-        <v>6627</v>
+        <v>6963</v>
       </c>
       <c r="B237" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C237" t="s">
         <v>50</v>
       </c>
       <c r="D237" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E237" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F237" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G237">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="H237">
         <v>0</v>
@@ -18910,7 +18920,7 @@
         <v>62</v>
       </c>
       <c r="J237" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N237" s="1">
         <v>46274</v>
@@ -18922,10 +18932,10 @@
         <v>2026</v>
       </c>
       <c r="R237">
-        <v>17968379</v>
+        <v>18187212</v>
       </c>
       <c r="S237" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="T237" t="s">
         <v>156</v>
@@ -18934,45 +18944,48 @@
         <v>173</v>
       </c>
       <c r="V237" s="1">
-        <v>46274.36695243056</v>
+        <v>46274.74452168981</v>
       </c>
       <c r="W237">
         <v>5</v>
       </c>
       <c r="X237" t="s">
-        <v>175</v>
+        <v>178</v>
+      </c>
+      <c r="Y237" t="s">
+        <v>261</v>
       </c>
       <c r="AB237">
         <v>0</v>
       </c>
       <c r="AC237" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AH237" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI237" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="238" spans="1:35">
       <c r="A238">
-        <v>6945</v>
+        <v>6548</v>
       </c>
       <c r="B238" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C238" t="s">
         <v>50</v>
       </c>
       <c r="D238" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E238" t="s">
         <v>54</v>
       </c>
       <c r="F238" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G238">
         <v>1867</v>
@@ -18990,7 +19003,7 @@
         <v>46274</v>
       </c>
       <c r="O238" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="P238">
         <v>8</v>
@@ -18999,57 +19012,60 @@
         <v>2026</v>
       </c>
       <c r="R238">
-        <v>18220182</v>
+        <v>17988543</v>
       </c>
       <c r="S238" t="s">
-        <v>159</v>
+        <v>155</v>
+      </c>
+      <c r="T238" t="s">
+        <v>156</v>
       </c>
       <c r="U238" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="V238" s="1">
-        <v>46276.4084265625</v>
+        <v>46274.64801501157</v>
       </c>
       <c r="W238">
         <v>5</v>
       </c>
       <c r="X238" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="Y238" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AB238">
         <v>0</v>
       </c>
       <c r="AC238" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="AH238" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI238" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="239" spans="1:35">
       <c r="A239">
-        <v>6962</v>
+        <v>6627</v>
       </c>
       <c r="B239" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C239" t="s">
         <v>50</v>
       </c>
       <c r="D239" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E239" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F239" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G239">
         <v>1867</v>
@@ -19073,10 +19089,10 @@
         <v>2026</v>
       </c>
       <c r="R239">
-        <v>18186953</v>
+        <v>17968379</v>
       </c>
       <c r="S239" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="T239" t="s">
         <v>156</v>
@@ -19085,39 +19101,39 @@
         <v>173</v>
       </c>
       <c r="V239" s="1">
-        <v>46274.7274781713</v>
+        <v>46274.36695243056</v>
       </c>
       <c r="W239">
         <v>5</v>
       </c>
       <c r="X239" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="AB239">
         <v>0</v>
       </c>
       <c r="AC239" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AH239" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI239" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="240" spans="1:35">
       <c r="A240">
-        <v>6963</v>
+        <v>6945</v>
       </c>
       <c r="B240" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C240" t="s">
         <v>50</v>
       </c>
       <c r="D240" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E240" t="s">
         <v>54</v>
@@ -19140,6 +19156,9 @@
       <c r="N240" s="1">
         <v>46274</v>
       </c>
+      <c r="O240" t="s">
+        <v>137</v>
+      </c>
       <c r="P240">
         <v>8</v>
       </c>
@@ -19147,51 +19166,51 @@
         <v>2026</v>
       </c>
       <c r="R240">
-        <v>18187219</v>
+        <v>18220182</v>
       </c>
       <c r="S240" t="s">
-        <v>158</v>
-      </c>
-      <c r="T240" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="U240" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="V240" s="1">
-        <v>46274.74558746528</v>
+        <v>46276.4084265625</v>
       </c>
       <c r="W240">
         <v>5</v>
       </c>
       <c r="X240" t="s">
-        <v>178</v>
+        <v>177</v>
+      </c>
+      <c r="Y240" t="s">
+        <v>263</v>
       </c>
       <c r="AB240">
         <v>0</v>
       </c>
       <c r="AC240" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AH240" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI240" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="241" spans="1:35">
       <c r="A241">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B241" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C241" t="s">
         <v>50</v>
       </c>
       <c r="D241" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E241" t="s">
         <v>54</v>
@@ -19200,19 +19219,19 @@
         <v>57</v>
       </c>
       <c r="G241">
-        <v>6886</v>
+        <v>1867</v>
       </c>
       <c r="H241">
-        <v>1862</v>
+        <v>0</v>
       </c>
       <c r="I241" t="s">
         <v>62</v>
       </c>
       <c r="J241" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="N241" s="1">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="P241">
         <v>8</v>
@@ -19221,10 +19240,10 @@
         <v>2026</v>
       </c>
       <c r="R241">
-        <v>18214907</v>
+        <v>18186953</v>
       </c>
       <c r="S241" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="T241" t="s">
         <v>156</v>
@@ -19233,60 +19252,60 @@
         <v>173</v>
       </c>
       <c r="V241" s="1">
-        <v>46275.79245582176</v>
+        <v>46274.7274781713</v>
       </c>
       <c r="W241">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X241" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AB241">
         <v>0</v>
       </c>
       <c r="AC241" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AH241" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="AI241" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="242" spans="1:35">
       <c r="A242">
-        <v>5417</v>
+        <v>6963</v>
       </c>
       <c r="B242" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C242" t="s">
         <v>50</v>
       </c>
       <c r="D242" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E242" t="s">
         <v>54</v>
       </c>
       <c r="F242" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G242">
-        <v>6806</v>
+        <v>1867</v>
       </c>
       <c r="H242">
         <v>0</v>
       </c>
       <c r="I242" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J242" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="N242" s="1">
-        <v>46276</v>
+        <v>46274</v>
       </c>
       <c r="P242">
         <v>8</v>
@@ -19295,72 +19314,72 @@
         <v>2026</v>
       </c>
       <c r="R242">
-        <v>17399230</v>
+        <v>18187219</v>
       </c>
       <c r="S242" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="T242" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="U242" t="s">
         <v>173</v>
       </c>
       <c r="V242" s="1">
-        <v>46276.49596842592</v>
+        <v>46274.74558746528</v>
       </c>
       <c r="W242">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X242" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AB242">
         <v>0</v>
       </c>
       <c r="AC242" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="AH242" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI242" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="243" spans="1:35">
       <c r="A243">
-        <v>6404</v>
+        <v>6949</v>
       </c>
       <c r="B243" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C243" t="s">
         <v>50</v>
       </c>
       <c r="D243" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E243" t="s">
         <v>54</v>
       </c>
       <c r="F243" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G243">
-        <v>6806</v>
+        <v>6886</v>
       </c>
       <c r="H243">
-        <v>0</v>
+        <v>1862</v>
       </c>
       <c r="I243" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J243" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="N243" s="1">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="P243">
         <v>8</v>
@@ -19369,45 +19388,45 @@
         <v>2026</v>
       </c>
       <c r="R243">
-        <v>16962308</v>
+        <v>18214907</v>
       </c>
       <c r="S243" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="T243" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="U243" t="s">
         <v>173</v>
       </c>
       <c r="V243" s="1">
-        <v>46276.53874935185</v>
+        <v>46275.79245582176</v>
       </c>
       <c r="W243">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X243" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="AB243">
         <v>0</v>
       </c>
       <c r="AC243" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="AH243" t="s">
         <v>289</v>
       </c>
       <c r="AI243" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="244" spans="1:35">
       <c r="A244">
-        <v>6486</v>
+        <v>5417</v>
       </c>
       <c r="B244" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C244" t="s">
         <v>50</v>
@@ -19443,7 +19462,7 @@
         <v>2026</v>
       </c>
       <c r="R244">
-        <v>16976187</v>
+        <v>17399230</v>
       </c>
       <c r="S244" t="s">
         <v>160</v>
@@ -19455,13 +19474,13 @@
         <v>173</v>
       </c>
       <c r="V244" s="1">
-        <v>46276.49597027778</v>
+        <v>46276.49596842592</v>
       </c>
       <c r="W244">
         <v>3</v>
       </c>
       <c r="X244" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AB244">
         <v>0</v>
@@ -19470,18 +19489,18 @@
         <v>160</v>
       </c>
       <c r="AH244" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI244" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="245" spans="1:35">
       <c r="A245">
-        <v>6703</v>
+        <v>6404</v>
       </c>
       <c r="B245" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C245" t="s">
         <v>50</v>
@@ -19517,7 +19536,7 @@
         <v>2026</v>
       </c>
       <c r="R245">
-        <v>17948858</v>
+        <v>16962308</v>
       </c>
       <c r="S245" t="s">
         <v>160</v>
@@ -19529,13 +19548,13 @@
         <v>173</v>
       </c>
       <c r="V245" s="1">
-        <v>46276.62604146991</v>
+        <v>46276.53874935185</v>
       </c>
       <c r="W245">
         <v>3</v>
       </c>
       <c r="X245" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AB245">
         <v>0</v>
@@ -19544,18 +19563,18 @@
         <v>160</v>
       </c>
       <c r="AH245" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI245" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="246" spans="1:35">
       <c r="A246">
-        <v>6704</v>
+        <v>6486</v>
       </c>
       <c r="B246" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C246" t="s">
         <v>50</v>
@@ -19591,7 +19610,7 @@
         <v>2026</v>
       </c>
       <c r="R246">
-        <v>18085297</v>
+        <v>16976187</v>
       </c>
       <c r="S246" t="s">
         <v>160</v>
@@ -19603,13 +19622,13 @@
         <v>173</v>
       </c>
       <c r="V246" s="1">
-        <v>46276.68231165509</v>
+        <v>46276.49597027778</v>
       </c>
       <c r="W246">
         <v>3</v>
       </c>
       <c r="X246" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AB246">
         <v>0</v>
@@ -19618,24 +19637,24 @@
         <v>160</v>
       </c>
       <c r="AH246" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI246" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="247" spans="1:35">
       <c r="A247">
-        <v>6705</v>
+        <v>6703</v>
       </c>
       <c r="B247" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C247" t="s">
         <v>50</v>
       </c>
       <c r="D247" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E247" t="s">
         <v>54</v>
@@ -19658,9 +19677,6 @@
       <c r="N247" s="1">
         <v>46276</v>
       </c>
-      <c r="O247" t="s">
-        <v>138</v>
-      </c>
       <c r="P247">
         <v>8</v>
       </c>
@@ -19668,7 +19684,7 @@
         <v>2026</v>
       </c>
       <c r="R247">
-        <v>17949029</v>
+        <v>17948858</v>
       </c>
       <c r="S247" t="s">
         <v>160</v>
@@ -19680,16 +19696,13 @@
         <v>173</v>
       </c>
       <c r="V247" s="1">
-        <v>46276.7163278588</v>
+        <v>46276.62604146991</v>
       </c>
       <c r="W247">
         <v>3</v>
       </c>
       <c r="X247" t="s">
-        <v>179</v>
-      </c>
-      <c r="Y247" t="s">
-        <v>262</v>
+        <v>183</v>
       </c>
       <c r="AB247">
         <v>0</v>
@@ -19698,24 +19711,24 @@
         <v>160</v>
       </c>
       <c r="AH247" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI247" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="248" spans="1:35">
       <c r="A248">
-        <v>6779</v>
+        <v>6704</v>
       </c>
       <c r="B248" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C248" t="s">
         <v>50</v>
       </c>
       <c r="D248" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E248" t="s">
         <v>54</v>
@@ -19745,7 +19758,7 @@
         <v>2026</v>
       </c>
       <c r="R248">
-        <v>18085066</v>
+        <v>18085297</v>
       </c>
       <c r="S248" t="s">
         <v>160</v>
@@ -19757,7 +19770,7 @@
         <v>173</v>
       </c>
       <c r="V248" s="1">
-        <v>46276.6823121412</v>
+        <v>46276.68231165509</v>
       </c>
       <c r="W248">
         <v>3</v>
@@ -19772,24 +19785,24 @@
         <v>160</v>
       </c>
       <c r="AH248" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI248" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="249" spans="1:35">
       <c r="A249">
-        <v>6404</v>
+        <v>6705</v>
       </c>
       <c r="B249" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C249" t="s">
         <v>50</v>
       </c>
       <c r="D249" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E249" t="s">
         <v>54</v>
@@ -19798,7 +19811,7 @@
         <v>56</v>
       </c>
       <c r="G249">
-        <v>1792</v>
+        <v>6806</v>
       </c>
       <c r="H249">
         <v>0</v>
@@ -19807,10 +19820,13 @@
         <v>63</v>
       </c>
       <c r="J249" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="N249" s="1">
-        <v>46275</v>
+        <v>46276</v>
+      </c>
+      <c r="O249" t="s">
+        <v>138</v>
       </c>
       <c r="P249">
         <v>8</v>
@@ -19819,7 +19835,7 @@
         <v>2026</v>
       </c>
       <c r="R249">
-        <v>16962151</v>
+        <v>17949029</v>
       </c>
       <c r="S249" t="s">
         <v>160</v>
@@ -19828,16 +19844,19 @@
         <v>170</v>
       </c>
       <c r="U249" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="V249" s="1">
-        <v>46274.70622837963</v>
+        <v>46276.7163278588</v>
       </c>
       <c r="W249">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X249" t="s">
-        <v>184</v>
+        <v>179</v>
+      </c>
+      <c r="Y249" t="s">
+        <v>264</v>
       </c>
       <c r="AB249">
         <v>0</v>
@@ -19846,24 +19865,24 @@
         <v>160</v>
       </c>
       <c r="AH249" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AI249" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="250" spans="1:35">
       <c r="A250">
-        <v>6703</v>
+        <v>6779</v>
       </c>
       <c r="B250" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C250" t="s">
         <v>50</v>
       </c>
       <c r="D250" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E250" t="s">
         <v>54</v>
@@ -19872,7 +19891,7 @@
         <v>56</v>
       </c>
       <c r="G250">
-        <v>1792</v>
+        <v>6806</v>
       </c>
       <c r="H250">
         <v>0</v>
@@ -19881,10 +19900,10 @@
         <v>63</v>
       </c>
       <c r="J250" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="N250" s="1">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="P250">
         <v>8</v>
@@ -19893,7 +19912,7 @@
         <v>2026</v>
       </c>
       <c r="R250">
-        <v>17948756</v>
+        <v>18085066</v>
       </c>
       <c r="S250" t="s">
         <v>160</v>
@@ -19905,13 +19924,13 @@
         <v>173</v>
       </c>
       <c r="V250" s="1">
-        <v>46275.71996309028</v>
+        <v>46276.6823121412</v>
       </c>
       <c r="W250">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X250" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="AB250">
         <v>0</v>
@@ -19920,24 +19939,24 @@
         <v>160</v>
       </c>
       <c r="AH250" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AI250" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="251" spans="1:35">
       <c r="A251">
-        <v>6704</v>
+        <v>6404</v>
       </c>
       <c r="B251" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C251" t="s">
         <v>50</v>
       </c>
       <c r="D251" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E251" t="s">
         <v>54</v>
@@ -19967,7 +19986,7 @@
         <v>2026</v>
       </c>
       <c r="R251">
-        <v>18085143</v>
+        <v>16962151</v>
       </c>
       <c r="S251" t="s">
         <v>160</v>
@@ -19976,16 +19995,16 @@
         <v>170</v>
       </c>
       <c r="U251" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="V251" s="1">
-        <v>46275.54278886574</v>
+        <v>46274.70622837963</v>
       </c>
       <c r="W251">
         <v>4</v>
       </c>
       <c r="X251" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="AB251">
         <v>0</v>
@@ -19994,18 +20013,18 @@
         <v>160</v>
       </c>
       <c r="AH251" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI251" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="252" spans="1:35">
       <c r="A252">
-        <v>6404</v>
+        <v>6703</v>
       </c>
       <c r="B252" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C252" t="s">
         <v>50</v>
@@ -20020,7 +20039,7 @@
         <v>56</v>
       </c>
       <c r="G252">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="H252">
         <v>0</v>
@@ -20029,7 +20048,7 @@
         <v>63</v>
       </c>
       <c r="J252" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N252" s="1">
         <v>46275</v>
@@ -20041,7 +20060,7 @@
         <v>2026</v>
       </c>
       <c r="R252">
-        <v>16962161</v>
+        <v>17948756</v>
       </c>
       <c r="S252" t="s">
         <v>160</v>
@@ -20053,13 +20072,13 @@
         <v>173</v>
       </c>
       <c r="V252" s="1">
-        <v>46275.7000328588</v>
+        <v>46275.71996309028</v>
       </c>
       <c r="W252">
         <v>4</v>
       </c>
       <c r="X252" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AB252">
         <v>0</v>
@@ -20068,18 +20087,18 @@
         <v>160</v>
       </c>
       <c r="AH252" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI252" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="253" spans="1:35">
       <c r="A253">
-        <v>6486</v>
+        <v>6704</v>
       </c>
       <c r="B253" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C253" t="s">
         <v>50</v>
@@ -20094,7 +20113,7 @@
         <v>56</v>
       </c>
       <c r="G253">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="H253">
         <v>0</v>
@@ -20103,7 +20122,7 @@
         <v>63</v>
       </c>
       <c r="J253" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N253" s="1">
         <v>46275</v>
@@ -20115,7 +20134,7 @@
         <v>2026</v>
       </c>
       <c r="R253">
-        <v>16975952</v>
+        <v>18085143</v>
       </c>
       <c r="S253" t="s">
         <v>160</v>
@@ -20127,13 +20146,13 @@
         <v>173</v>
       </c>
       <c r="V253" s="1">
-        <v>46275.72031699074</v>
+        <v>46275.54278886574</v>
       </c>
       <c r="W253">
         <v>4</v>
       </c>
       <c r="X253" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AB253">
         <v>0</v>
@@ -20142,18 +20161,18 @@
         <v>160</v>
       </c>
       <c r="AH253" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI253" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="254" spans="1:35">
       <c r="A254">
-        <v>6703</v>
+        <v>6404</v>
       </c>
       <c r="B254" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C254" t="s">
         <v>50</v>
@@ -20189,7 +20208,7 @@
         <v>2026</v>
       </c>
       <c r="R254">
-        <v>17948766</v>
+        <v>16962161</v>
       </c>
       <c r="S254" t="s">
         <v>160</v>
@@ -20201,13 +20220,13 @@
         <v>173</v>
       </c>
       <c r="V254" s="1">
-        <v>46275.54095912037</v>
+        <v>46275.7000328588</v>
       </c>
       <c r="W254">
         <v>4</v>
       </c>
       <c r="X254" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AB254">
         <v>0</v>
@@ -20216,18 +20235,18 @@
         <v>160</v>
       </c>
       <c r="AH254" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI254" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="255" spans="1:35">
       <c r="A255">
-        <v>6704</v>
+        <v>6486</v>
       </c>
       <c r="B255" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C255" t="s">
         <v>50</v>
@@ -20263,7 +20282,7 @@
         <v>2026</v>
       </c>
       <c r="R255">
-        <v>18085154</v>
+        <v>16975952</v>
       </c>
       <c r="S255" t="s">
         <v>160</v>
@@ -20275,13 +20294,13 @@
         <v>173</v>
       </c>
       <c r="V255" s="1">
-        <v>46275.72225363426</v>
+        <v>46275.72031699074</v>
       </c>
       <c r="W255">
         <v>4</v>
       </c>
       <c r="X255" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AB255">
         <v>0</v>
@@ -20290,24 +20309,24 @@
         <v>160</v>
       </c>
       <c r="AH255" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI255" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="256" spans="1:35">
       <c r="A256">
-        <v>6705</v>
+        <v>6703</v>
       </c>
       <c r="B256" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C256" t="s">
         <v>50</v>
       </c>
       <c r="D256" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E256" t="s">
         <v>54</v>
@@ -20337,7 +20356,7 @@
         <v>2026</v>
       </c>
       <c r="R256">
-        <v>17948928</v>
+        <v>17948766</v>
       </c>
       <c r="S256" t="s">
         <v>160</v>
@@ -20349,13 +20368,13 @@
         <v>173</v>
       </c>
       <c r="V256" s="1">
-        <v>46275.7222629051</v>
+        <v>46275.54095912037</v>
       </c>
       <c r="W256">
         <v>4</v>
       </c>
       <c r="X256" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="AB256">
         <v>0</v>
@@ -20364,24 +20383,24 @@
         <v>160</v>
       </c>
       <c r="AH256" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI256" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="257" spans="1:35">
       <c r="A257">
-        <v>6779</v>
+        <v>6704</v>
       </c>
       <c r="B257" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C257" t="s">
         <v>50</v>
       </c>
       <c r="D257" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E257" t="s">
         <v>54</v>
@@ -20411,7 +20430,7 @@
         <v>2026</v>
       </c>
       <c r="R257">
-        <v>18084955</v>
+        <v>18085154</v>
       </c>
       <c r="S257" t="s">
         <v>160</v>
@@ -20423,7 +20442,7 @@
         <v>173</v>
       </c>
       <c r="V257" s="1">
-        <v>46275.7222709838</v>
+        <v>46275.72225363426</v>
       </c>
       <c r="W257">
         <v>4</v>
@@ -20438,24 +20457,24 @@
         <v>160</v>
       </c>
       <c r="AH257" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI257" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="258" spans="1:35">
       <c r="A258">
-        <v>5417</v>
+        <v>6705</v>
       </c>
       <c r="B258" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C258" t="s">
         <v>50</v>
       </c>
       <c r="D258" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E258" t="s">
         <v>54</v>
@@ -20464,7 +20483,7 @@
         <v>56</v>
       </c>
       <c r="G258">
-        <v>1796</v>
+        <v>1793</v>
       </c>
       <c r="H258">
         <v>0</v>
@@ -20473,13 +20492,10 @@
         <v>63</v>
       </c>
       <c r="J258" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="N258" s="1">
-        <v>46273</v>
-      </c>
-      <c r="O258" t="s">
-        <v>136</v>
+        <v>46275</v>
       </c>
       <c r="P258">
         <v>8</v>
@@ -20488,7 +20504,7 @@
         <v>2026</v>
       </c>
       <c r="R258">
-        <v>17398955</v>
+        <v>17948928</v>
       </c>
       <c r="S258" t="s">
         <v>160</v>
@@ -20497,19 +20513,16 @@
         <v>170</v>
       </c>
       <c r="U258" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="V258" s="1">
-        <v>46274.74837762731</v>
+        <v>46275.7222629051</v>
       </c>
       <c r="W258">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="X258" t="s">
-        <v>180</v>
-      </c>
-      <c r="Y258" t="s">
-        <v>263</v>
+        <v>179</v>
       </c>
       <c r="AB258">
         <v>0</v>
@@ -20518,24 +20531,24 @@
         <v>160</v>
       </c>
       <c r="AH258" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="AI258" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="259" spans="1:35">
       <c r="A259">
-        <v>6703</v>
+        <v>6779</v>
       </c>
       <c r="B259" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C259" t="s">
         <v>50</v>
       </c>
       <c r="D259" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E259" t="s">
         <v>54</v>
@@ -20544,7 +20557,7 @@
         <v>56</v>
       </c>
       <c r="G259">
-        <v>1796</v>
+        <v>1793</v>
       </c>
       <c r="H259">
         <v>0</v>
@@ -20553,13 +20566,10 @@
         <v>63</v>
       </c>
       <c r="J259" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="N259" s="1">
-        <v>46273</v>
-      </c>
-      <c r="O259" t="s">
-        <v>136</v>
+        <v>46275</v>
       </c>
       <c r="P259">
         <v>8</v>
@@ -20568,7 +20578,7 @@
         <v>2026</v>
       </c>
       <c r="R259">
-        <v>18073098</v>
+        <v>18084955</v>
       </c>
       <c r="S259" t="s">
         <v>160</v>
@@ -20577,19 +20587,16 @@
         <v>170</v>
       </c>
       <c r="U259" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="V259" s="1">
-        <v>46274.74838096065</v>
+        <v>46275.7222709838</v>
       </c>
       <c r="W259">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="X259" t="s">
-        <v>183</v>
-      </c>
-      <c r="Y259" t="s">
-        <v>263</v>
+        <v>179</v>
       </c>
       <c r="AB259">
         <v>0</v>
@@ -20598,10 +20605,10 @@
         <v>160</v>
       </c>
       <c r="AH259" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="AI259" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="260" spans="1:35">
@@ -20624,7 +20631,7 @@
         <v>56</v>
       </c>
       <c r="G260">
-        <v>11303</v>
+        <v>1796</v>
       </c>
       <c r="H260">
         <v>0</v>
@@ -20633,10 +20640,13 @@
         <v>63</v>
       </c>
       <c r="J260" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="N260" s="1">
-        <v>46279</v>
+        <v>46273</v>
+      </c>
+      <c r="O260" t="s">
+        <v>136</v>
       </c>
       <c r="P260">
         <v>8</v>
@@ -20645,7 +20655,7 @@
         <v>2026</v>
       </c>
       <c r="R260">
-        <v>17399454</v>
+        <v>17398955</v>
       </c>
       <c r="S260" t="s">
         <v>160</v>
@@ -20654,19 +20664,19 @@
         <v>170</v>
       </c>
       <c r="U260" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V260" s="1">
-        <v>46274.42878043981</v>
+        <v>46274.74837762731</v>
       </c>
       <c r="W260">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X260" t="s">
         <v>180</v>
       </c>
       <c r="Y260" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AB260">
         <v>0</v>
@@ -20675,24 +20685,24 @@
         <v>160</v>
       </c>
       <c r="AH260" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI260" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="261" spans="1:35">
       <c r="A261">
-        <v>6486</v>
+        <v>6703</v>
       </c>
       <c r="B261" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C261" t="s">
         <v>50</v>
       </c>
       <c r="D261" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E261" t="s">
         <v>54</v>
@@ -20701,7 +20711,7 @@
         <v>56</v>
       </c>
       <c r="G261">
-        <v>11303</v>
+        <v>1796</v>
       </c>
       <c r="H261">
         <v>0</v>
@@ -20710,10 +20720,13 @@
         <v>63</v>
       </c>
       <c r="J261" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="N261" s="1">
-        <v>46279</v>
+        <v>46273</v>
+      </c>
+      <c r="O261" t="s">
+        <v>136</v>
       </c>
       <c r="P261">
         <v>8</v>
@@ -20722,7 +20735,7 @@
         <v>2026</v>
       </c>
       <c r="R261">
-        <v>16976351</v>
+        <v>18073098</v>
       </c>
       <c r="S261" t="s">
         <v>160</v>
@@ -20731,16 +20744,16 @@
         <v>170</v>
       </c>
       <c r="U261" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V261" s="1">
-        <v>46275.40196778935</v>
+        <v>46274.74838096065</v>
       </c>
       <c r="W261">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X261" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Y261" t="s">
         <v>265</v>
@@ -20752,24 +20765,24 @@
         <v>160</v>
       </c>
       <c r="AH261" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI261" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="262" spans="1:35">
       <c r="A262">
-        <v>6703</v>
+        <v>5417</v>
       </c>
       <c r="B262" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C262" t="s">
         <v>50</v>
       </c>
       <c r="D262" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E262" t="s">
         <v>54</v>
@@ -20778,22 +20791,19 @@
         <v>56</v>
       </c>
       <c r="G262">
-        <v>950</v>
+        <v>11303</v>
       </c>
       <c r="H262">
         <v>0</v>
       </c>
       <c r="I262" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J262" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="N262" s="1">
-        <v>46275</v>
-      </c>
-      <c r="O262" t="s">
-        <v>137</v>
+        <v>46279</v>
       </c>
       <c r="P262">
         <v>8</v>
@@ -20802,22 +20812,25 @@
         <v>2026</v>
       </c>
       <c r="R262">
-        <v>17941146</v>
+        <v>17399454</v>
       </c>
       <c r="S262" t="s">
-        <v>161</v>
+        <v>160</v>
+      </c>
+      <c r="T262" t="s">
+        <v>170</v>
       </c>
       <c r="U262" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="V262" s="1">
-        <v>46276.52399603009</v>
+        <v>46274.42878043981</v>
       </c>
       <c r="W262">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X262" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="Y262" t="s">
         <v>266</v>
@@ -20826,21 +20839,21 @@
         <v>0</v>
       </c>
       <c r="AC262" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AH262" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AI262" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="263" spans="1:35">
       <c r="A263">
-        <v>6704</v>
+        <v>6486</v>
       </c>
       <c r="B263" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C263" t="s">
         <v>50</v>
@@ -20855,22 +20868,19 @@
         <v>56</v>
       </c>
       <c r="G263">
-        <v>950</v>
+        <v>11303</v>
       </c>
       <c r="H263">
         <v>0</v>
       </c>
       <c r="I263" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J263" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="N263" s="1">
-        <v>46275</v>
-      </c>
-      <c r="O263" t="s">
-        <v>137</v>
+        <v>46279</v>
       </c>
       <c r="P263">
         <v>8</v>
@@ -20879,22 +20889,25 @@
         <v>2026</v>
       </c>
       <c r="R263">
-        <v>17952340</v>
+        <v>16976351</v>
       </c>
       <c r="S263" t="s">
-        <v>161</v>
+        <v>160</v>
+      </c>
+      <c r="T263" t="s">
+        <v>170</v>
       </c>
       <c r="U263" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="V263" s="1">
-        <v>46276.5240703125</v>
+        <v>46275.40196778935</v>
       </c>
       <c r="W263">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X263" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Y263" t="s">
         <v>267</v>
@@ -20903,33 +20916,33 @@
         <v>0</v>
       </c>
       <c r="AC263" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AH263" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AI263" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="264" spans="1:35">
       <c r="A264">
-        <v>6949</v>
+        <v>6703</v>
       </c>
       <c r="B264" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C264" t="s">
         <v>50</v>
       </c>
       <c r="D264" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E264" t="s">
         <v>54</v>
       </c>
       <c r="F264" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G264">
         <v>950</v>
@@ -20946,6 +20959,9 @@
       <c r="N264" s="1">
         <v>46275</v>
       </c>
+      <c r="O264" t="s">
+        <v>137</v>
+      </c>
       <c r="P264">
         <v>8</v>
       </c>
@@ -20953,22 +20969,22 @@
         <v>2026</v>
       </c>
       <c r="R264">
-        <v>18178132</v>
+        <v>17941146</v>
       </c>
       <c r="S264" t="s">
         <v>161</v>
       </c>
       <c r="U264" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="V264" s="1">
-        <v>46275.4100730787</v>
+        <v>46276.52399603009</v>
       </c>
       <c r="W264">
         <v>4</v>
       </c>
       <c r="X264" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="Y264" t="s">
         <v>268</v>
@@ -20980,30 +20996,30 @@
         <v>161</v>
       </c>
       <c r="AH264" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI264" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="265" spans="1:35">
       <c r="A265">
-        <v>6962</v>
+        <v>6704</v>
       </c>
       <c r="B265" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C265" t="s">
         <v>50</v>
       </c>
       <c r="D265" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E265" t="s">
         <v>54</v>
       </c>
       <c r="F265" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G265">
         <v>950</v>
@@ -21020,6 +21036,9 @@
       <c r="N265" s="1">
         <v>46275</v>
       </c>
+      <c r="O265" t="s">
+        <v>137</v>
+      </c>
       <c r="P265">
         <v>8</v>
       </c>
@@ -21027,22 +21046,22 @@
         <v>2026</v>
       </c>
       <c r="R265">
-        <v>18188717</v>
+        <v>17952340</v>
       </c>
       <c r="S265" t="s">
         <v>161</v>
       </c>
       <c r="U265" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="V265" s="1">
-        <v>46275.40964188657</v>
+        <v>46276.5240703125</v>
       </c>
       <c r="W265">
         <v>4</v>
       </c>
       <c r="X265" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Y265" t="s">
         <v>269</v>
@@ -21054,24 +21073,24 @@
         <v>161</v>
       </c>
       <c r="AH265" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI265" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="266" spans="1:35">
       <c r="A266">
-        <v>6963</v>
+        <v>6949</v>
       </c>
       <c r="B266" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C266" t="s">
         <v>50</v>
       </c>
       <c r="D266" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E266" t="s">
         <v>54</v>
@@ -21101,7 +21120,7 @@
         <v>2026</v>
       </c>
       <c r="R266">
-        <v>18188623</v>
+        <v>18178132</v>
       </c>
       <c r="S266" t="s">
         <v>161</v>
@@ -21110,13 +21129,13 @@
         <v>173</v>
       </c>
       <c r="V266" s="1">
-        <v>46275.40964245371</v>
+        <v>46275.4100730787</v>
       </c>
       <c r="W266">
         <v>4</v>
       </c>
       <c r="X266" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="Y266" t="s">
         <v>270</v>
@@ -21128,33 +21147,33 @@
         <v>161</v>
       </c>
       <c r="AH266" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI266" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="267" spans="1:35">
       <c r="A267">
-        <v>6548</v>
+        <v>6962</v>
       </c>
       <c r="B267" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C267" t="s">
         <v>50</v>
       </c>
       <c r="D267" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E267" t="s">
         <v>54</v>
       </c>
       <c r="F267" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G267">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H267">
         <v>0</v>
@@ -21163,7 +21182,7 @@
         <v>64</v>
       </c>
       <c r="J267" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N267" s="1">
         <v>46275</v>
@@ -21175,7 +21194,7 @@
         <v>2026</v>
       </c>
       <c r="R267">
-        <v>17222405</v>
+        <v>18188717</v>
       </c>
       <c r="S267" t="s">
         <v>161</v>
@@ -21184,13 +21203,13 @@
         <v>173</v>
       </c>
       <c r="V267" s="1">
-        <v>46275.45011145833</v>
+        <v>46275.40964188657</v>
       </c>
       <c r="W267">
         <v>4</v>
       </c>
       <c r="X267" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="Y267" t="s">
         <v>271</v>
@@ -21202,33 +21221,33 @@
         <v>161</v>
       </c>
       <c r="AH267" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI267" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="268" spans="1:35">
       <c r="A268">
-        <v>6628</v>
+        <v>6963</v>
       </c>
       <c r="B268" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C268" t="s">
         <v>50</v>
       </c>
       <c r="D268" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E268" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F268" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G268">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H268">
         <v>0</v>
@@ -21237,7 +21256,7 @@
         <v>64</v>
       </c>
       <c r="J268" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N268" s="1">
         <v>46275</v>
@@ -21249,7 +21268,7 @@
         <v>2026</v>
       </c>
       <c r="R268">
-        <v>16959950</v>
+        <v>18188623</v>
       </c>
       <c r="S268" t="s">
         <v>161</v>
@@ -21258,13 +21277,16 @@
         <v>173</v>
       </c>
       <c r="V268" s="1">
-        <v>46275.44901016204</v>
+        <v>46275.40964245371</v>
       </c>
       <c r="W268">
         <v>4</v>
       </c>
       <c r="X268" t="s">
-        <v>175</v>
+        <v>178</v>
+      </c>
+      <c r="Y268" t="s">
+        <v>272</v>
       </c>
       <c r="AB268">
         <v>0</v>
@@ -21273,24 +21295,24 @@
         <v>161</v>
       </c>
       <c r="AH268" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI268" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="269" spans="1:35">
       <c r="A269">
-        <v>6703</v>
+        <v>6548</v>
       </c>
       <c r="B269" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="C269" t="s">
         <v>50</v>
       </c>
       <c r="D269" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E269" t="s">
         <v>54</v>
@@ -21313,9 +21335,6 @@
       <c r="N269" s="1">
         <v>46275</v>
       </c>
-      <c r="O269" t="s">
-        <v>138</v>
-      </c>
       <c r="P269">
         <v>8</v>
       </c>
@@ -21323,25 +21342,25 @@
         <v>2026</v>
       </c>
       <c r="R269">
-        <v>17941156</v>
+        <v>17222405</v>
       </c>
       <c r="S269" t="s">
         <v>161</v>
       </c>
       <c r="U269" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="V269" s="1">
-        <v>46276.71732053241</v>
+        <v>46275.45011145833</v>
       </c>
       <c r="W269">
         <v>4</v>
       </c>
       <c r="X269" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="Y269" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AB269">
         <v>0</v>
@@ -21350,27 +21369,27 @@
         <v>161</v>
       </c>
       <c r="AH269" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI269" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="270" spans="1:35">
       <c r="A270">
-        <v>6704</v>
+        <v>6628</v>
       </c>
       <c r="B270" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C270" t="s">
         <v>50</v>
       </c>
       <c r="D270" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E270" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F270" t="s">
         <v>56</v>
@@ -21390,9 +21409,6 @@
       <c r="N270" s="1">
         <v>46275</v>
       </c>
-      <c r="O270" t="s">
-        <v>138</v>
-      </c>
       <c r="P270">
         <v>8</v>
       </c>
@@ -21400,25 +21416,22 @@
         <v>2026</v>
       </c>
       <c r="R270">
-        <v>17952351</v>
+        <v>16959950</v>
       </c>
       <c r="S270" t="s">
         <v>161</v>
       </c>
       <c r="U270" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="V270" s="1">
-        <v>46276.71697232639</v>
+        <v>46275.44901016204</v>
       </c>
       <c r="W270">
         <v>4</v>
       </c>
       <c r="X270" t="s">
-        <v>179</v>
-      </c>
-      <c r="Y270" t="s">
-        <v>273</v>
+        <v>175</v>
       </c>
       <c r="AB270">
         <v>0</v>
@@ -21427,24 +21440,24 @@
         <v>161</v>
       </c>
       <c r="AH270" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI270" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="271" spans="1:35">
       <c r="A271">
-        <v>6705</v>
+        <v>6703</v>
       </c>
       <c r="B271" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C271" t="s">
         <v>50</v>
       </c>
       <c r="D271" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E271" t="s">
         <v>54</v>
@@ -21477,7 +21490,7 @@
         <v>2026</v>
       </c>
       <c r="R271">
-        <v>17952535</v>
+        <v>17941156</v>
       </c>
       <c r="S271" t="s">
         <v>161</v>
@@ -21486,13 +21499,13 @@
         <v>171</v>
       </c>
       <c r="V271" s="1">
-        <v>46276.7175884838</v>
+        <v>46276.71732053241</v>
       </c>
       <c r="W271">
         <v>4</v>
       </c>
       <c r="X271" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="Y271" t="s">
         <v>274</v>
@@ -21504,24 +21517,24 @@
         <v>161</v>
       </c>
       <c r="AH271" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI271" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="272" spans="1:35">
       <c r="A272">
-        <v>6779</v>
+        <v>6704</v>
       </c>
       <c r="B272" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C272" t="s">
         <v>50</v>
       </c>
       <c r="D272" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E272" t="s">
         <v>54</v>
@@ -21554,7 +21567,7 @@
         <v>2026</v>
       </c>
       <c r="R272">
-        <v>18056705</v>
+        <v>17952351</v>
       </c>
       <c r="S272" t="s">
         <v>161</v>
@@ -21563,7 +21576,7 @@
         <v>171</v>
       </c>
       <c r="V272" s="1">
-        <v>46276.7175895949</v>
+        <v>46276.71697232639</v>
       </c>
       <c r="W272">
         <v>4</v>
@@ -21581,18 +21594,18 @@
         <v>161</v>
       </c>
       <c r="AH272" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI272" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="273" spans="1:35">
       <c r="A273">
-        <v>6945</v>
+        <v>6705</v>
       </c>
       <c r="B273" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C273" t="s">
         <v>50</v>
@@ -21604,7 +21617,7 @@
         <v>54</v>
       </c>
       <c r="F273" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G273">
         <v>951</v>
@@ -21631,7 +21644,7 @@
         <v>2026</v>
       </c>
       <c r="R273">
-        <v>18164501</v>
+        <v>17952535</v>
       </c>
       <c r="S273" t="s">
         <v>161</v>
@@ -21640,13 +21653,13 @@
         <v>171</v>
       </c>
       <c r="V273" s="1">
-        <v>46276.71759461806</v>
+        <v>46276.7175884838</v>
       </c>
       <c r="W273">
         <v>4</v>
       </c>
       <c r="X273" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Y273" t="s">
         <v>276</v>
@@ -21658,30 +21671,30 @@
         <v>161</v>
       </c>
       <c r="AH273" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI273" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="274" spans="1:35">
       <c r="A274">
-        <v>6949</v>
+        <v>6779</v>
       </c>
       <c r="B274" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C274" t="s">
         <v>50</v>
       </c>
       <c r="D274" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E274" t="s">
         <v>54</v>
       </c>
       <c r="F274" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G274">
         <v>951</v>
@@ -21698,6 +21711,9 @@
       <c r="N274" s="1">
         <v>46275</v>
       </c>
+      <c r="O274" t="s">
+        <v>138</v>
+      </c>
       <c r="P274">
         <v>8</v>
       </c>
@@ -21705,22 +21721,22 @@
         <v>2026</v>
       </c>
       <c r="R274">
-        <v>18178138</v>
+        <v>18056705</v>
       </c>
       <c r="S274" t="s">
         <v>161</v>
       </c>
       <c r="U274" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="V274" s="1">
-        <v>46275.44975668981</v>
+        <v>46276.7175895949</v>
       </c>
       <c r="W274">
         <v>4</v>
       </c>
       <c r="X274" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Y274" t="s">
         <v>277</v>
@@ -21732,24 +21748,24 @@
         <v>161</v>
       </c>
       <c r="AH274" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI274" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="275" spans="1:35">
       <c r="A275">
-        <v>6962</v>
+        <v>6945</v>
       </c>
       <c r="B275" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C275" t="s">
         <v>50</v>
       </c>
       <c r="D275" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E275" t="s">
         <v>54</v>
@@ -21772,6 +21788,9 @@
       <c r="N275" s="1">
         <v>46275</v>
       </c>
+      <c r="O275" t="s">
+        <v>138</v>
+      </c>
       <c r="P275">
         <v>8</v>
       </c>
@@ -21779,22 +21798,22 @@
         <v>2026</v>
       </c>
       <c r="R275">
-        <v>18188724</v>
+        <v>18164501</v>
       </c>
       <c r="S275" t="s">
         <v>161</v>
       </c>
       <c r="U275" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="V275" s="1">
-        <v>46275.44933692129</v>
+        <v>46276.71759461806</v>
       </c>
       <c r="W275">
         <v>4</v>
       </c>
       <c r="X275" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y275" t="s">
         <v>278</v>
@@ -21806,24 +21825,24 @@
         <v>161</v>
       </c>
       <c r="AH275" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI275" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="276" spans="1:35">
       <c r="A276">
-        <v>6963</v>
+        <v>6949</v>
       </c>
       <c r="B276" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C276" t="s">
         <v>50</v>
       </c>
       <c r="D276" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E276" t="s">
         <v>54</v>
@@ -21853,7 +21872,7 @@
         <v>2026</v>
       </c>
       <c r="R276">
-        <v>18188630</v>
+        <v>18178138</v>
       </c>
       <c r="S276" t="s">
         <v>161</v>
@@ -21862,13 +21881,13 @@
         <v>173</v>
       </c>
       <c r="V276" s="1">
-        <v>46275.44933814815</v>
+        <v>46275.44975668981</v>
       </c>
       <c r="W276">
         <v>4</v>
       </c>
       <c r="X276" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="Y276" t="s">
         <v>279</v>
@@ -21880,18 +21899,18 @@
         <v>161</v>
       </c>
       <c r="AH276" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AI276" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="277" spans="1:35">
       <c r="A277">
-        <v>6703</v>
+        <v>6962</v>
       </c>
       <c r="B277" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C277" t="s">
         <v>50</v>
@@ -21903,10 +21922,10 @@
         <v>54</v>
       </c>
       <c r="F277" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G277">
-        <v>5989</v>
+        <v>951</v>
       </c>
       <c r="H277">
         <v>0</v>
@@ -21915,34 +21934,37 @@
         <v>64</v>
       </c>
       <c r="J277" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="N277" s="1">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="P277">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q277">
         <v>2026</v>
       </c>
       <c r="R277">
-        <v>17941177</v>
+        <v>18188724</v>
       </c>
       <c r="S277" t="s">
         <v>161</v>
       </c>
       <c r="U277" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="V277" s="1">
-        <v>46274.41771849537</v>
+        <v>46275.44933692129</v>
       </c>
       <c r="W277">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="X277" t="s">
-        <v>183</v>
+        <v>178</v>
+      </c>
+      <c r="Y277" t="s">
+        <v>280</v>
       </c>
       <c r="AB277">
         <v>0</v>
@@ -21951,33 +21973,33 @@
         <v>161</v>
       </c>
       <c r="AH277" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI277" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="278" spans="1:35">
       <c r="A278">
-        <v>6704</v>
+        <v>6963</v>
       </c>
       <c r="B278" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C278" t="s">
         <v>50</v>
       </c>
       <c r="D278" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E278" t="s">
         <v>54</v>
       </c>
       <c r="F278" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G278">
-        <v>5989</v>
+        <v>951</v>
       </c>
       <c r="H278">
         <v>0</v>
@@ -21986,34 +22008,37 @@
         <v>64</v>
       </c>
       <c r="J278" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="N278" s="1">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="P278">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q278">
         <v>2026</v>
       </c>
       <c r="R278">
-        <v>17952385</v>
+        <v>18188630</v>
       </c>
       <c r="S278" t="s">
         <v>161</v>
       </c>
       <c r="U278" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="V278" s="1">
-        <v>46274.41775447917</v>
+        <v>46275.44933814815</v>
       </c>
       <c r="W278">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="X278" t="s">
-        <v>179</v>
+        <v>178</v>
+      </c>
+      <c r="Y278" t="s">
+        <v>281</v>
       </c>
       <c r="AB278">
         <v>0</v>
@@ -22022,24 +22047,24 @@
         <v>161</v>
       </c>
       <c r="AH278" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI278" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="279" spans="1:35">
       <c r="A279">
-        <v>6705</v>
+        <v>6703</v>
       </c>
       <c r="B279" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C279" t="s">
         <v>50</v>
       </c>
       <c r="D279" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E279" t="s">
         <v>54</v>
@@ -22069,7 +22094,7 @@
         <v>2026</v>
       </c>
       <c r="R279">
-        <v>17952569</v>
+        <v>17941177</v>
       </c>
       <c r="S279" t="s">
         <v>161</v>
@@ -22078,13 +22103,13 @@
         <v>171</v>
       </c>
       <c r="V279" s="1">
-        <v>46274.41777533565</v>
+        <v>46274.41771849537</v>
       </c>
       <c r="W279">
         <v>6</v>
       </c>
       <c r="X279" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="AB279">
         <v>0</v>
@@ -22093,30 +22118,30 @@
         <v>161</v>
       </c>
       <c r="AH279" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI279" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="280" spans="1:35">
       <c r="A280">
-        <v>6945</v>
+        <v>6704</v>
       </c>
       <c r="B280" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C280" t="s">
         <v>50</v>
       </c>
       <c r="D280" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E280" t="s">
         <v>54</v>
       </c>
       <c r="F280" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G280">
         <v>5989</v>
@@ -22140,7 +22165,7 @@
         <v>2026</v>
       </c>
       <c r="R280">
-        <v>18164516</v>
+        <v>17952385</v>
       </c>
       <c r="S280" t="s">
         <v>161</v>
@@ -22149,13 +22174,13 @@
         <v>171</v>
       </c>
       <c r="V280" s="1">
-        <v>46274.41799166667</v>
+        <v>46274.41775447917</v>
       </c>
       <c r="W280">
         <v>6</v>
       </c>
       <c r="X280" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AB280">
         <v>0</v>
@@ -22164,30 +22189,30 @@
         <v>161</v>
       </c>
       <c r="AH280" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI280" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="281" spans="1:35">
       <c r="A281">
-        <v>6949</v>
+        <v>6705</v>
       </c>
       <c r="B281" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C281" t="s">
         <v>50</v>
       </c>
       <c r="D281" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E281" t="s">
         <v>54</v>
       </c>
       <c r="F281" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G281">
         <v>5989</v>
@@ -22211,7 +22236,7 @@
         <v>2026</v>
       </c>
       <c r="R281">
-        <v>18178157</v>
+        <v>17952569</v>
       </c>
       <c r="S281" t="s">
         <v>161</v>
@@ -22220,13 +22245,13 @@
         <v>171</v>
       </c>
       <c r="V281" s="1">
-        <v>46274.41800114583</v>
+        <v>46274.41777533565</v>
       </c>
       <c r="W281">
         <v>6</v>
       </c>
       <c r="X281" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="AB281">
         <v>0</v>
@@ -22235,45 +22260,45 @@
         <v>161</v>
       </c>
       <c r="AH281" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI281" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="282" spans="1:35">
       <c r="A282">
-        <v>6703</v>
+        <v>6945</v>
       </c>
       <c r="B282" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C282" t="s">
         <v>50</v>
       </c>
       <c r="D282" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E282" t="s">
         <v>54</v>
       </c>
       <c r="F282" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G282">
-        <v>6215</v>
+        <v>5989</v>
       </c>
       <c r="H282">
         <v>0</v>
       </c>
       <c r="I282" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J282" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="N282" s="1">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="P282">
         <v>9</v>
@@ -22282,42 +22307,42 @@
         <v>2026</v>
       </c>
       <c r="R282">
-        <v>17941187</v>
+        <v>18164516</v>
       </c>
       <c r="S282" t="s">
-        <v>54</v>
+        <v>161</v>
       </c>
       <c r="U282" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="V282" s="1">
-        <v>46274.41772148148</v>
+        <v>46274.41799166667</v>
       </c>
       <c r="W282">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X282" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="AB282">
         <v>0</v>
       </c>
       <c r="AC282" t="s">
-        <v>54</v>
+        <v>161</v>
       </c>
       <c r="AH282" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI282" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="283" spans="1:35">
       <c r="A283">
-        <v>6704</v>
+        <v>6949</v>
       </c>
       <c r="B283" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C283" t="s">
         <v>50</v>
@@ -22329,22 +22354,22 @@
         <v>54</v>
       </c>
       <c r="F283" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G283">
-        <v>6215</v>
+        <v>5989</v>
       </c>
       <c r="H283">
         <v>0</v>
       </c>
       <c r="I283" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J283" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="N283" s="1">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="P283">
         <v>9</v>
@@ -22353,48 +22378,48 @@
         <v>2026</v>
       </c>
       <c r="R283">
-        <v>17952400</v>
+        <v>18178157</v>
       </c>
       <c r="S283" t="s">
-        <v>54</v>
+        <v>161</v>
       </c>
       <c r="U283" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="V283" s="1">
-        <v>46274.41773631945</v>
+        <v>46274.41800114583</v>
       </c>
       <c r="W283">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X283" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="AB283">
         <v>0</v>
       </c>
       <c r="AC283" t="s">
-        <v>54</v>
+        <v>161</v>
       </c>
       <c r="AH283" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI283" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="284" spans="1:35">
       <c r="A284">
-        <v>6705</v>
+        <v>6703</v>
       </c>
       <c r="B284" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C284" t="s">
         <v>50</v>
       </c>
       <c r="D284" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E284" t="s">
         <v>54</v>
@@ -22424,7 +22449,7 @@
         <v>2026</v>
       </c>
       <c r="R284">
-        <v>17952580</v>
+        <v>17941187</v>
       </c>
       <c r="S284" t="s">
         <v>54</v>
@@ -22433,13 +22458,13 @@
         <v>173</v>
       </c>
       <c r="V284" s="1">
-        <v>46274.41777481481</v>
+        <v>46274.41772148148</v>
       </c>
       <c r="W284">
         <v>5</v>
       </c>
       <c r="X284" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="AB284">
         <v>0</v>
@@ -22448,30 +22473,30 @@
         <v>54</v>
       </c>
       <c r="AH284" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI284" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="285" spans="1:35">
       <c r="A285">
-        <v>6945</v>
+        <v>6704</v>
       </c>
       <c r="B285" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C285" t="s">
         <v>50</v>
       </c>
       <c r="D285" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E285" t="s">
         <v>54</v>
       </c>
       <c r="F285" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G285">
         <v>6215</v>
@@ -22495,7 +22520,7 @@
         <v>2026</v>
       </c>
       <c r="R285">
-        <v>18164523</v>
+        <v>17952400</v>
       </c>
       <c r="S285" t="s">
         <v>54</v>
@@ -22504,13 +22529,13 @@
         <v>173</v>
       </c>
       <c r="V285" s="1">
-        <v>46274.41799332176</v>
+        <v>46274.41773631945</v>
       </c>
       <c r="W285">
         <v>5</v>
       </c>
       <c r="X285" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AB285">
         <v>0</v>
@@ -22519,30 +22544,30 @@
         <v>54</v>
       </c>
       <c r="AH285" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI285" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="286" spans="1:35">
       <c r="A286">
-        <v>6949</v>
+        <v>6705</v>
       </c>
       <c r="B286" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C286" t="s">
         <v>50</v>
       </c>
       <c r="D286" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E286" t="s">
         <v>54</v>
       </c>
       <c r="F286" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G286">
         <v>6215</v>
@@ -22566,57 +22591,57 @@
         <v>2026</v>
       </c>
       <c r="R286">
-        <v>18178163</v>
+        <v>17952580</v>
       </c>
       <c r="S286" t="s">
-        <v>162</v>
+        <v>54</v>
       </c>
       <c r="U286" t="s">
         <v>173</v>
       </c>
       <c r="V286" s="1">
-        <v>46274.41800085648</v>
+        <v>46274.41777481481</v>
       </c>
       <c r="W286">
         <v>5</v>
       </c>
       <c r="X286" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="AB286">
         <v>0</v>
       </c>
       <c r="AC286" t="s">
-        <v>162</v>
+        <v>54</v>
       </c>
       <c r="AH286" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI286" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="287" spans="1:35">
       <c r="A287">
-        <v>5417</v>
+        <v>6945</v>
       </c>
       <c r="B287" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C287" t="s">
         <v>50</v>
       </c>
       <c r="D287" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E287" t="s">
         <v>54</v>
       </c>
       <c r="F287" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G287">
-        <v>11746</v>
+        <v>6215</v>
       </c>
       <c r="H287">
         <v>0</v>
@@ -22625,19 +22650,19 @@
         <v>65</v>
       </c>
       <c r="J287" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="N287" s="1">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="P287">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q287">
         <v>2026</v>
       </c>
       <c r="R287">
-        <v>17994311</v>
+        <v>18164523</v>
       </c>
       <c r="S287" t="s">
         <v>54</v>
@@ -22646,48 +22671,48 @@
         <v>173</v>
       </c>
       <c r="V287" s="1">
-        <v>46275.31737530093</v>
+        <v>46274.41799332176</v>
       </c>
       <c r="W287">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X287" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="AB287">
         <v>0</v>
       </c>
       <c r="AC287" t="s">
-        <v>162</v>
+        <v>54</v>
       </c>
       <c r="AH287" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="AI287" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="288" spans="1:35">
       <c r="A288">
-        <v>6404</v>
+        <v>6949</v>
       </c>
       <c r="B288" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C288" t="s">
         <v>50</v>
       </c>
       <c r="D288" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E288" t="s">
         <v>54</v>
       </c>
       <c r="F288" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G288">
-        <v>11746</v>
+        <v>6215</v>
       </c>
       <c r="H288">
         <v>0</v>
@@ -22696,34 +22721,34 @@
         <v>65</v>
       </c>
       <c r="J288" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="N288" s="1">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="P288">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q288">
         <v>2026</v>
       </c>
       <c r="R288">
-        <v>17994675</v>
+        <v>18178163</v>
       </c>
       <c r="S288" t="s">
-        <v>54</v>
+        <v>162</v>
       </c>
       <c r="U288" t="s">
         <v>173</v>
       </c>
       <c r="V288" s="1">
-        <v>46275.31747032407</v>
+        <v>46274.41800085648</v>
       </c>
       <c r="W288">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X288" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="AB288">
         <v>0</v>
@@ -22732,18 +22757,18 @@
         <v>162</v>
       </c>
       <c r="AH288" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="AI288" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="289" spans="1:35">
       <c r="A289">
-        <v>6486</v>
+        <v>5417</v>
       </c>
       <c r="B289" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C289" t="s">
         <v>50</v>
@@ -22779,7 +22804,7 @@
         <v>2026</v>
       </c>
       <c r="R289">
-        <v>17994809</v>
+        <v>17994311</v>
       </c>
       <c r="S289" t="s">
         <v>54</v>
@@ -22788,13 +22813,13 @@
         <v>173</v>
       </c>
       <c r="V289" s="1">
-        <v>46275.31747981482</v>
+        <v>46275.31737530093</v>
       </c>
       <c r="W289">
         <v>4</v>
       </c>
       <c r="X289" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AB289">
         <v>0</v>
@@ -22803,24 +22828,24 @@
         <v>162</v>
       </c>
       <c r="AH289" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI289" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="290" spans="1:35">
       <c r="A290">
-        <v>6548</v>
+        <v>6404</v>
       </c>
       <c r="B290" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="C290" t="s">
         <v>50</v>
       </c>
       <c r="D290" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E290" t="s">
         <v>54</v>
@@ -22850,7 +22875,7 @@
         <v>2026</v>
       </c>
       <c r="R290">
-        <v>18006051</v>
+        <v>17994675</v>
       </c>
       <c r="S290" t="s">
         <v>54</v>
@@ -22859,13 +22884,13 @@
         <v>173</v>
       </c>
       <c r="V290" s="1">
-        <v>46275.31748724537</v>
+        <v>46275.31747032407</v>
       </c>
       <c r="W290">
         <v>4</v>
       </c>
       <c r="X290" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="AB290">
         <v>0</v>
@@ -22874,27 +22899,27 @@
         <v>162</v>
       </c>
       <c r="AH290" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI290" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="291" spans="1:35">
       <c r="A291">
-        <v>6628</v>
+        <v>6486</v>
       </c>
       <c r="B291" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C291" t="s">
         <v>50</v>
       </c>
       <c r="D291" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E291" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F291" t="s">
         <v>56</v>
@@ -22921,22 +22946,22 @@
         <v>2026</v>
       </c>
       <c r="R291">
-        <v>18003256</v>
+        <v>17994809</v>
       </c>
       <c r="S291" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="U291" t="s">
         <v>173</v>
       </c>
       <c r="V291" s="1">
-        <v>46275.31749535879</v>
+        <v>46275.31747981482</v>
       </c>
       <c r="W291">
         <v>4</v>
       </c>
       <c r="X291" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="AB291">
         <v>0</v>
@@ -22945,24 +22970,24 @@
         <v>162</v>
       </c>
       <c r="AH291" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI291" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="292" spans="1:35">
       <c r="A292">
-        <v>6703</v>
+        <v>6548</v>
       </c>
       <c r="B292" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="C292" t="s">
         <v>50</v>
       </c>
       <c r="D292" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E292" t="s">
         <v>54</v>
@@ -22992,7 +23017,7 @@
         <v>2026</v>
       </c>
       <c r="R292">
-        <v>18004017</v>
+        <v>18006051</v>
       </c>
       <c r="S292" t="s">
         <v>54</v>
@@ -23001,13 +23026,13 @@
         <v>173</v>
       </c>
       <c r="V292" s="1">
-        <v>46275.31750491898</v>
+        <v>46275.31748724537</v>
       </c>
       <c r="W292">
         <v>4</v>
       </c>
       <c r="X292" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="AB292">
         <v>0</v>
@@ -23016,27 +23041,27 @@
         <v>162</v>
       </c>
       <c r="AH292" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI292" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="293" spans="1:35">
       <c r="A293">
-        <v>6704</v>
+        <v>6628</v>
       </c>
       <c r="B293" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C293" t="s">
         <v>50</v>
       </c>
       <c r="D293" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E293" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F293" t="s">
         <v>56</v>
@@ -23063,22 +23088,22 @@
         <v>2026</v>
       </c>
       <c r="R293">
-        <v>17995164</v>
+        <v>18003256</v>
       </c>
       <c r="S293" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="U293" t="s">
         <v>173</v>
       </c>
       <c r="V293" s="1">
-        <v>46275.31750555555</v>
+        <v>46275.31749535879</v>
       </c>
       <c r="W293">
         <v>4</v>
       </c>
       <c r="X293" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="AB293">
         <v>0</v>
@@ -23087,24 +23112,24 @@
         <v>162</v>
       </c>
       <c r="AH293" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI293" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="294" spans="1:35">
       <c r="A294">
-        <v>6705</v>
+        <v>6703</v>
       </c>
       <c r="B294" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C294" t="s">
         <v>50</v>
       </c>
       <c r="D294" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E294" t="s">
         <v>54</v>
@@ -23134,7 +23159,7 @@
         <v>2026</v>
       </c>
       <c r="R294">
-        <v>18004028</v>
+        <v>18004017</v>
       </c>
       <c r="S294" t="s">
         <v>54</v>
@@ -23143,13 +23168,13 @@
         <v>173</v>
       </c>
       <c r="V294" s="1">
-        <v>46275.31750599537</v>
+        <v>46275.31750491898</v>
       </c>
       <c r="W294">
         <v>4</v>
       </c>
       <c r="X294" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="AB294">
         <v>0</v>
@@ -23158,18 +23183,18 @@
         <v>162</v>
       </c>
       <c r="AH294" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI294" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="295" spans="1:35">
       <c r="A295">
-        <v>5417</v>
+        <v>6704</v>
       </c>
       <c r="B295" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C295" t="s">
         <v>50</v>
@@ -23184,7 +23209,7 @@
         <v>56</v>
       </c>
       <c r="G295">
-        <v>7877</v>
+        <v>11746</v>
       </c>
       <c r="H295">
         <v>0</v>
@@ -23193,63 +23218,60 @@
         <v>65</v>
       </c>
       <c r="J295" t="s">
-        <v>67</v>
+        <v>129</v>
       </c>
       <c r="N295" s="1">
-        <v>46259</v>
+        <v>46275</v>
       </c>
       <c r="P295">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q295">
         <v>2026</v>
       </c>
       <c r="R295">
-        <v>17399329</v>
+        <v>17995164</v>
       </c>
       <c r="S295" t="s">
         <v>54</v>
       </c>
       <c r="U295" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="V295" s="1">
-        <v>46275.5810894676</v>
+        <v>46275.31750555555</v>
       </c>
       <c r="W295">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="X295" t="s">
-        <v>180</v>
-      </c>
-      <c r="Y295" t="s">
-        <v>280</v>
+        <v>179</v>
       </c>
       <c r="AB295">
         <v>0</v>
       </c>
       <c r="AC295" t="s">
-        <v>54</v>
+        <v>162</v>
       </c>
       <c r="AH295" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI295" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="296" spans="1:35">
       <c r="A296">
-        <v>6486</v>
+        <v>6705</v>
       </c>
       <c r="B296" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C296" t="s">
         <v>50</v>
       </c>
       <c r="D296" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E296" t="s">
         <v>54</v>
@@ -23258,7 +23280,7 @@
         <v>56</v>
       </c>
       <c r="G296">
-        <v>9774</v>
+        <v>11746</v>
       </c>
       <c r="H296">
         <v>0</v>
@@ -23267,57 +23289,54 @@
         <v>65</v>
       </c>
       <c r="J296" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="N296" s="1">
-        <v>46259</v>
+        <v>46275</v>
       </c>
       <c r="P296">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q296">
         <v>2026</v>
       </c>
       <c r="R296">
-        <v>16976320</v>
+        <v>18004028</v>
       </c>
       <c r="S296" t="s">
         <v>54</v>
       </c>
       <c r="U296" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="V296" s="1">
-        <v>46275.58158541666</v>
+        <v>46275.31750599537</v>
       </c>
       <c r="W296">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="X296" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y296" t="s">
-        <v>281</v>
+        <v>179</v>
       </c>
       <c r="AB296">
         <v>0</v>
       </c>
       <c r="AC296" t="s">
-        <v>54</v>
+        <v>162</v>
       </c>
       <c r="AH296" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI296" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="297" spans="1:35">
       <c r="A297">
-        <v>6627</v>
+        <v>5417</v>
       </c>
       <c r="B297" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C297" t="s">
         <v>50</v>
@@ -23326,49 +23345,49 @@
         <v>51</v>
       </c>
       <c r="E297" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F297" t="s">
         <v>56</v>
       </c>
       <c r="G297">
-        <v>11056</v>
+        <v>7877</v>
       </c>
       <c r="H297">
         <v>0</v>
       </c>
       <c r="I297" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J297" t="s">
-        <v>122</v>
+        <v>67</v>
       </c>
       <c r="N297" s="1">
-        <v>46276</v>
-      </c>
-      <c r="O297" t="s">
-        <v>138</v>
+        <v>46259</v>
       </c>
       <c r="P297">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q297">
         <v>2026</v>
       </c>
       <c r="R297">
-        <v>18270269</v>
+        <v>17399329</v>
+      </c>
+      <c r="S297" t="s">
+        <v>54</v>
       </c>
       <c r="U297" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="V297" s="1">
-        <v>46276.41675075232</v>
+        <v>46275.5810894676</v>
       </c>
       <c r="W297">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="X297" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="Y297" t="s">
         <v>282</v>
@@ -23377,13 +23396,161 @@
         <v>0</v>
       </c>
       <c r="AC297" t="s">
-        <v>286</v>
+        <v>54</v>
       </c>
       <c r="AH297" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AI297" t="s">
-        <v>291</v>
+        <v>293</v>
+      </c>
+    </row>
+    <row r="298" spans="1:35">
+      <c r="A298">
+        <v>6486</v>
+      </c>
+      <c r="B298" t="s">
+        <v>44</v>
+      </c>
+      <c r="C298" t="s">
+        <v>50</v>
+      </c>
+      <c r="D298" t="s">
+        <v>51</v>
+      </c>
+      <c r="E298" t="s">
+        <v>54</v>
+      </c>
+      <c r="F298" t="s">
+        <v>56</v>
+      </c>
+      <c r="G298">
+        <v>9774</v>
+      </c>
+      <c r="H298">
+        <v>0</v>
+      </c>
+      <c r="I298" t="s">
+        <v>65</v>
+      </c>
+      <c r="J298" t="s">
+        <v>120</v>
+      </c>
+      <c r="N298" s="1">
+        <v>46259</v>
+      </c>
+      <c r="P298">
+        <v>7</v>
+      </c>
+      <c r="Q298">
+        <v>2026</v>
+      </c>
+      <c r="R298">
+        <v>16976320</v>
+      </c>
+      <c r="S298" t="s">
+        <v>54</v>
+      </c>
+      <c r="U298" t="s">
+        <v>171</v>
+      </c>
+      <c r="V298" s="1">
+        <v>46275.58158541666</v>
+      </c>
+      <c r="W298">
+        <v>20</v>
+      </c>
+      <c r="X298" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y298" t="s">
+        <v>283</v>
+      </c>
+      <c r="AB298">
+        <v>0</v>
+      </c>
+      <c r="AC298" t="s">
+        <v>54</v>
+      </c>
+      <c r="AH298" t="s">
+        <v>289</v>
+      </c>
+      <c r="AI298" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="299" spans="1:35">
+      <c r="A299">
+        <v>6627</v>
+      </c>
+      <c r="B299" t="s">
+        <v>36</v>
+      </c>
+      <c r="C299" t="s">
+        <v>50</v>
+      </c>
+      <c r="D299" t="s">
+        <v>51</v>
+      </c>
+      <c r="E299" t="s">
+        <v>55</v>
+      </c>
+      <c r="F299" t="s">
+        <v>56</v>
+      </c>
+      <c r="G299">
+        <v>11056</v>
+      </c>
+      <c r="H299">
+        <v>0</v>
+      </c>
+      <c r="I299" t="s">
+        <v>66</v>
+      </c>
+      <c r="J299" t="s">
+        <v>122</v>
+      </c>
+      <c r="N299" s="1">
+        <v>46276</v>
+      </c>
+      <c r="O299" t="s">
+        <v>138</v>
+      </c>
+      <c r="P299">
+        <v>8</v>
+      </c>
+      <c r="Q299">
+        <v>2026</v>
+      </c>
+      <c r="R299">
+        <v>18270269</v>
+      </c>
+      <c r="U299" t="s">
+        <v>173</v>
+      </c>
+      <c r="V299" s="1">
+        <v>46276.41675075232</v>
+      </c>
+      <c r="W299">
+        <v>3</v>
+      </c>
+      <c r="X299" t="s">
+        <v>175</v>
+      </c>
+      <c r="Y299" t="s">
+        <v>284</v>
+      </c>
+      <c r="AB299">
+        <v>0</v>
+      </c>
+      <c r="AC299" t="s">
+        <v>288</v>
+      </c>
+      <c r="AH299" t="s">
+        <v>289</v>
+      </c>
+      <c r="AI299" t="s">
+        <v>293</v>
       </c>
     </row>
   </sheetData>

--- a/data/base/goias.xlsx
+++ b/data/base/goias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4252" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4300" uniqueCount="296">
   <si>
     <t>CodCliente</t>
   </si>
@@ -789,6 +789,9 @@
   </si>
   <si>
     <t>1. Folha em Processamento  Previsão para conclusão dia 10/09/2026 - Data Comentário: 08/09/2026 15:22</t>
+  </si>
+  <si>
+    <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 14/09/2026 - Data Comentário: 11/09/2026 16:50</t>
   </si>
   <si>
     <t>Imposto enviado via SCI Report - Data Comentário: 14/09/2026 09:15</t>
@@ -1256,7 +1259,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AI299"/>
+  <dimension ref="A1:AI302"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:35">
@@ -1437,10 +1440,10 @@
         <v>139</v>
       </c>
       <c r="AH2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="3" spans="1:35">
@@ -1514,10 +1517,10 @@
         <v>140</v>
       </c>
       <c r="AH3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="4" spans="1:35">
@@ -1591,10 +1594,10 @@
         <v>139</v>
       </c>
       <c r="AH4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5" spans="1:35">
@@ -1665,10 +1668,10 @@
         <v>139</v>
       </c>
       <c r="AH5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6" spans="1:35">
@@ -1739,10 +1742,10 @@
         <v>140</v>
       </c>
       <c r="AH6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="7" spans="1:35">
@@ -1813,10 +1816,10 @@
         <v>140</v>
       </c>
       <c r="AH7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI7" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="8" spans="1:35">
@@ -1887,10 +1890,10 @@
         <v>141</v>
       </c>
       <c r="AH8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9" spans="1:35">
@@ -1961,10 +1964,10 @@
         <v>139</v>
       </c>
       <c r="AH9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10" spans="1:35">
@@ -2035,10 +2038,10 @@
         <v>142</v>
       </c>
       <c r="AH10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="11" spans="1:35">
@@ -2109,10 +2112,10 @@
         <v>142</v>
       </c>
       <c r="AH11" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI11" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="12" spans="1:35">
@@ -2183,10 +2186,10 @@
         <v>143</v>
       </c>
       <c r="AH12" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI12" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="13" spans="1:35">
@@ -2254,13 +2257,13 @@
         <v>0</v>
       </c>
       <c r="AC13" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AH13" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI13" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="14" spans="1:35">
@@ -2328,13 +2331,13 @@
         <v>0</v>
       </c>
       <c r="AC14" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AH14" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI14" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="15" spans="1:35">
@@ -2402,10 +2405,10 @@
         <v>0</v>
       </c>
       <c r="AH15" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI15" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="16" spans="1:35">
@@ -2467,10 +2470,10 @@
         <v>0</v>
       </c>
       <c r="AH16" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI16" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="17" spans="1:35">
@@ -2538,10 +2541,10 @@
         <v>0</v>
       </c>
       <c r="AH17" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI17" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="18" spans="1:35">
@@ -2615,10 +2618,10 @@
         <v>145</v>
       </c>
       <c r="AH18" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI18" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="19" spans="1:35">
@@ -2692,10 +2695,10 @@
         <v>144</v>
       </c>
       <c r="AH19" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI19" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="20" spans="1:35">
@@ -2769,10 +2772,10 @@
         <v>145</v>
       </c>
       <c r="AH20" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI20" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="21" spans="1:35">
@@ -2846,10 +2849,10 @@
         <v>143</v>
       </c>
       <c r="AH21" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI21" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="22" spans="1:35">
@@ -2920,10 +2923,10 @@
         <v>146</v>
       </c>
       <c r="AH22" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI22" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="23" spans="1:35">
@@ -2994,10 +2997,10 @@
         <v>143</v>
       </c>
       <c r="AH23" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI23" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="24" spans="1:35">
@@ -3068,10 +3071,10 @@
         <v>143</v>
       </c>
       <c r="AH24" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI24" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="25" spans="1:35">
@@ -3142,10 +3145,10 @@
         <v>143</v>
       </c>
       <c r="AH25" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI25" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="26" spans="1:35">
@@ -3216,10 +3219,10 @@
         <v>144</v>
       </c>
       <c r="AH26" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI26" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="27" spans="1:35">
@@ -3290,10 +3293,10 @@
         <v>143</v>
       </c>
       <c r="AH27" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI27" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:35">
@@ -3364,10 +3367,10 @@
         <v>143</v>
       </c>
       <c r="AH28" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI28" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:35">
@@ -3438,10 +3441,10 @@
         <v>143</v>
       </c>
       <c r="AH29" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI29" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" spans="1:35">
@@ -3512,10 +3515,10 @@
         <v>147</v>
       </c>
       <c r="AH30" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI30" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:35">
@@ -3592,10 +3595,10 @@
         <v>148</v>
       </c>
       <c r="AH31" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI31" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="32" spans="1:35">
@@ -3666,10 +3669,10 @@
         <v>149</v>
       </c>
       <c r="AH32" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI32" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="33" spans="1:35">
@@ -3746,10 +3749,10 @@
         <v>150</v>
       </c>
       <c r="AH33" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI33" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="34" spans="1:35">
@@ -3823,10 +3826,10 @@
         <v>151</v>
       </c>
       <c r="AH34" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI34" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="35" spans="1:35">
@@ -3900,13 +3903,13 @@
         <v>0</v>
       </c>
       <c r="AC35" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AH35" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI35" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="36" spans="1:35">
@@ -3983,10 +3986,10 @@
         <v>153</v>
       </c>
       <c r="AH36" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI36" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="37" spans="1:35">
@@ -4063,10 +4066,10 @@
         <v>147</v>
       </c>
       <c r="AH37" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI37" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="38" spans="1:35">
@@ -4140,10 +4143,10 @@
         <v>169</v>
       </c>
       <c r="AH38" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI38" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="39" spans="1:35">
@@ -4220,10 +4223,10 @@
         <v>148</v>
       </c>
       <c r="AH39" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI39" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="40" spans="1:35">
@@ -4300,10 +4303,10 @@
         <v>148</v>
       </c>
       <c r="AH40" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI40" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="41" spans="1:35">
@@ -4380,10 +4383,10 @@
         <v>148</v>
       </c>
       <c r="AH41" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI41" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="42" spans="1:35">
@@ -4460,10 +4463,10 @@
         <v>147</v>
       </c>
       <c r="AH42" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI42" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="43" spans="1:35">
@@ -4540,10 +4543,10 @@
         <v>154</v>
       </c>
       <c r="AH43" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI43" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="44" spans="1:35">
@@ -4620,10 +4623,10 @@
         <v>149</v>
       </c>
       <c r="AH44" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI44" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="45" spans="1:35">
@@ -4700,10 +4703,10 @@
         <v>150</v>
       </c>
       <c r="AH45" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI45" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="46" spans="1:35">
@@ -4771,10 +4774,10 @@
         <v>151</v>
       </c>
       <c r="AH46" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI46" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="47" spans="1:35">
@@ -4845,10 +4848,10 @@
         <v>148</v>
       </c>
       <c r="AH47" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI47" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="48" spans="1:35">
@@ -4919,10 +4922,10 @@
         <v>148</v>
       </c>
       <c r="AH48" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI48" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="49" spans="1:35">
@@ -4993,10 +4996,10 @@
         <v>148</v>
       </c>
       <c r="AH49" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI49" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="50" spans="1:35">
@@ -5067,10 +5070,10 @@
         <v>147</v>
       </c>
       <c r="AH50" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI50" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="51" spans="1:35">
@@ -5141,10 +5144,10 @@
         <v>154</v>
       </c>
       <c r="AH51" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI51" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="52" spans="1:35">
@@ -5221,10 +5224,10 @@
         <v>149</v>
       </c>
       <c r="AH52" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI52" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="53" spans="1:35">
@@ -5295,10 +5298,10 @@
         <v>150</v>
       </c>
       <c r="AH53" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI53" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="54" spans="1:35">
@@ -5375,10 +5378,10 @@
         <v>148</v>
       </c>
       <c r="AH54" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI54" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="55" spans="1:35">
@@ -5455,10 +5458,10 @@
         <v>148</v>
       </c>
       <c r="AH55" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI55" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="56" spans="1:35">
@@ -5535,10 +5538,10 @@
         <v>148</v>
       </c>
       <c r="AH56" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI56" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="57" spans="1:35">
@@ -5615,10 +5618,10 @@
         <v>147</v>
       </c>
       <c r="AH57" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI57" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="58" spans="1:35">
@@ -5692,10 +5695,10 @@
         <v>151</v>
       </c>
       <c r="AH58" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI58" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="59" spans="1:35">
@@ -5769,13 +5772,13 @@
         <v>0</v>
       </c>
       <c r="AC59" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AH59" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI59" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="60" spans="1:35">
@@ -5852,10 +5855,10 @@
         <v>148</v>
       </c>
       <c r="AH60" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI60" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="61" spans="1:35">
@@ -5932,10 +5935,10 @@
         <v>148</v>
       </c>
       <c r="AH61" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI61" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="62" spans="1:35">
@@ -6012,10 +6015,10 @@
         <v>148</v>
       </c>
       <c r="AH62" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI62" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="63" spans="1:35">
@@ -6092,10 +6095,10 @@
         <v>147</v>
       </c>
       <c r="AH63" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI63" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="64" spans="1:35">
@@ -6172,10 +6175,10 @@
         <v>154</v>
       </c>
       <c r="AH64" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI64" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="65" spans="1:35">
@@ -6252,10 +6255,10 @@
         <v>149</v>
       </c>
       <c r="AH65" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI65" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="66" spans="1:35">
@@ -6332,10 +6335,10 @@
         <v>150</v>
       </c>
       <c r="AH66" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI66" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="67" spans="1:35">
@@ -6412,10 +6415,10 @@
         <v>148</v>
       </c>
       <c r="AH67" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI67" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="68" spans="1:35">
@@ -6483,10 +6486,10 @@
         <v>151</v>
       </c>
       <c r="AH68" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI68" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="69" spans="1:35">
@@ -6554,13 +6557,13 @@
         <v>0</v>
       </c>
       <c r="AC69" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AH69" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI69" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="70" spans="1:35">
@@ -6631,10 +6634,10 @@
         <v>148</v>
       </c>
       <c r="AH70" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI70" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="71" spans="1:35">
@@ -6705,10 +6708,10 @@
         <v>148</v>
       </c>
       <c r="AH71" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI71" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="72" spans="1:35">
@@ -6779,10 +6782,10 @@
         <v>148</v>
       </c>
       <c r="AH72" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI72" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="73" spans="1:35">
@@ -6853,10 +6856,10 @@
         <v>147</v>
       </c>
       <c r="AH73" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI73" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="74" spans="1:35">
@@ -6927,10 +6930,10 @@
         <v>154</v>
       </c>
       <c r="AH74" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI74" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="75" spans="1:35">
@@ -7001,10 +7004,10 @@
         <v>149</v>
       </c>
       <c r="AH75" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI75" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="76" spans="1:35">
@@ -7075,10 +7078,10 @@
         <v>150</v>
       </c>
       <c r="AH76" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI76" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="77" spans="1:35">
@@ -7149,10 +7152,10 @@
         <v>150</v>
       </c>
       <c r="AH77" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI77" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="78" spans="1:35">
@@ -7223,10 +7226,10 @@
         <v>150</v>
       </c>
       <c r="AH78" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI78" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="79" spans="1:35">
@@ -7297,10 +7300,10 @@
         <v>150</v>
       </c>
       <c r="AH79" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI79" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="80" spans="1:35">
@@ -7371,10 +7374,10 @@
         <v>156</v>
       </c>
       <c r="AH80" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI80" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="81" spans="1:35">
@@ -7445,10 +7448,10 @@
         <v>156</v>
       </c>
       <c r="AH81" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI81" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="82" spans="1:35">
@@ -7519,10 +7522,10 @@
         <v>157</v>
       </c>
       <c r="AH82" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI82" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="83" spans="1:35">
@@ -7593,10 +7596,10 @@
         <v>156</v>
       </c>
       <c r="AH83" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI83" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="84" spans="1:35">
@@ -7667,10 +7670,10 @@
         <v>156</v>
       </c>
       <c r="AH84" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI84" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="85" spans="1:35">
@@ -7741,10 +7744,10 @@
         <v>156</v>
       </c>
       <c r="AH85" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI85" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="86" spans="1:35">
@@ -7809,10 +7812,10 @@
         <v>157</v>
       </c>
       <c r="AH86" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI86" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="87" spans="1:35">
@@ -7883,10 +7886,10 @@
         <v>156</v>
       </c>
       <c r="AH87" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI87" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="88" spans="1:35">
@@ -7957,10 +7960,10 @@
         <v>156</v>
       </c>
       <c r="AH88" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI88" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="89" spans="1:35">
@@ -8031,10 +8034,10 @@
         <v>156</v>
       </c>
       <c r="AH89" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI89" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="90" spans="1:35">
@@ -8099,10 +8102,10 @@
         <v>156</v>
       </c>
       <c r="AH90" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI90" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="91" spans="1:35">
@@ -8167,10 +8170,10 @@
         <v>157</v>
       </c>
       <c r="AH91" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI91" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="92" spans="1:35">
@@ -8241,10 +8244,10 @@
         <v>156</v>
       </c>
       <c r="AH92" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI92" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="93" spans="1:35">
@@ -8315,10 +8318,10 @@
         <v>156</v>
       </c>
       <c r="AH93" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI93" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="94" spans="1:35">
@@ -8389,10 +8392,10 @@
         <v>156</v>
       </c>
       <c r="AH94" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI94" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="95" spans="1:35">
@@ -8457,10 +8460,10 @@
         <v>156</v>
       </c>
       <c r="AH95" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI95" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="96" spans="1:35">
@@ -8525,10 +8528,10 @@
         <v>157</v>
       </c>
       <c r="AH96" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI96" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="97" spans="1:35">
@@ -8599,10 +8602,10 @@
         <v>156</v>
       </c>
       <c r="AH97" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI97" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="98" spans="1:35">
@@ -8673,10 +8676,10 @@
         <v>156</v>
       </c>
       <c r="AH98" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI98" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="99" spans="1:35">
@@ -8747,10 +8750,10 @@
         <v>157</v>
       </c>
       <c r="AH99" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI99" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="100" spans="1:35">
@@ -8827,10 +8830,10 @@
         <v>156</v>
       </c>
       <c r="AH100" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI100" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="101" spans="1:35">
@@ -8898,10 +8901,10 @@
         <v>156</v>
       </c>
       <c r="AH101" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI101" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="102" spans="1:35">
@@ -8972,10 +8975,10 @@
         <v>156</v>
       </c>
       <c r="AH102" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI102" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="103" spans="1:35">
@@ -9046,10 +9049,10 @@
         <v>156</v>
       </c>
       <c r="AH103" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI103" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="104" spans="1:35">
@@ -9120,10 +9123,10 @@
         <v>156</v>
       </c>
       <c r="AH104" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI104" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="105" spans="1:35">
@@ -9188,10 +9191,10 @@
         <v>156</v>
       </c>
       <c r="AH105" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI105" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="106" spans="1:35">
@@ -9256,10 +9259,10 @@
         <v>157</v>
       </c>
       <c r="AH106" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI106" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="107" spans="1:35">
@@ -9330,10 +9333,10 @@
         <v>156</v>
       </c>
       <c r="AH107" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI107" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="108" spans="1:35">
@@ -9404,10 +9407,10 @@
         <v>156</v>
       </c>
       <c r="AH108" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI108" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="109" spans="1:35">
@@ -9475,10 +9478,10 @@
         <v>156</v>
       </c>
       <c r="AH109" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI109" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="110" spans="1:35">
@@ -9549,10 +9552,10 @@
         <v>157</v>
       </c>
       <c r="AH110" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI110" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="111" spans="1:35">
@@ -9620,10 +9623,10 @@
         <v>159</v>
       </c>
       <c r="AH111" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI111" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="112" spans="1:35">
@@ -9694,10 +9697,10 @@
         <v>157</v>
       </c>
       <c r="AH112" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI112" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="113" spans="1:35">
@@ -9768,10 +9771,10 @@
         <v>155</v>
       </c>
       <c r="AH113" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI113" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="114" spans="1:35">
@@ -9839,10 +9842,10 @@
         <v>159</v>
       </c>
       <c r="AH114" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI114" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="115" spans="1:35">
@@ -9913,10 +9916,10 @@
         <v>157</v>
       </c>
       <c r="AH115" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI115" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="116" spans="1:35">
@@ -9987,10 +9990,10 @@
         <v>156</v>
       </c>
       <c r="AH116" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI116" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="117" spans="1:35">
@@ -10061,10 +10064,10 @@
         <v>156</v>
       </c>
       <c r="AH117" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI117" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="118" spans="1:35">
@@ -10135,10 +10138,10 @@
         <v>156</v>
       </c>
       <c r="AH118" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI118" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="119" spans="1:35">
@@ -10203,10 +10206,10 @@
         <v>156</v>
       </c>
       <c r="AH119" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI119" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="120" spans="1:35">
@@ -10271,10 +10274,10 @@
         <v>157</v>
       </c>
       <c r="AH120" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI120" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="121" spans="1:35">
@@ -10345,10 +10348,10 @@
         <v>156</v>
       </c>
       <c r="AH121" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI121" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="122" spans="1:35">
@@ -10419,10 +10422,10 @@
         <v>156</v>
       </c>
       <c r="AH122" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI122" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="123" spans="1:35">
@@ -10493,10 +10496,10 @@
         <v>156</v>
       </c>
       <c r="AH123" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI123" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="124" spans="1:35">
@@ -10561,10 +10564,10 @@
         <v>156</v>
       </c>
       <c r="AH124" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI124" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="125" spans="1:35">
@@ -10629,10 +10632,10 @@
         <v>157</v>
       </c>
       <c r="AH125" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI125" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="126" spans="1:35">
@@ -10709,10 +10712,10 @@
         <v>157</v>
       </c>
       <c r="AH126" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI126" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="127" spans="1:35">
@@ -10789,10 +10792,10 @@
         <v>157</v>
       </c>
       <c r="AH127" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI127" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="128" spans="1:35">
@@ -10863,10 +10866,10 @@
         <v>160</v>
       </c>
       <c r="AH128" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI128" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="129" spans="1:35">
@@ -10937,10 +10940,10 @@
         <v>160</v>
       </c>
       <c r="AH129" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI129" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="130" spans="1:35">
@@ -11017,10 +11020,10 @@
         <v>160</v>
       </c>
       <c r="AH130" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI130" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="131" spans="1:35">
@@ -11091,10 +11094,10 @@
         <v>160</v>
       </c>
       <c r="AH131" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI131" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="132" spans="1:35">
@@ -11165,10 +11168,10 @@
         <v>160</v>
       </c>
       <c r="AH132" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI132" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="133" spans="1:35">
@@ -11239,10 +11242,10 @@
         <v>160</v>
       </c>
       <c r="AH133" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI133" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="134" spans="1:35">
@@ -11313,10 +11316,10 @@
         <v>160</v>
       </c>
       <c r="AH134" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI134" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="135" spans="1:35">
@@ -11393,10 +11396,10 @@
         <v>160</v>
       </c>
       <c r="AH135" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI135" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="136" spans="1:35">
@@ -11467,10 +11470,10 @@
         <v>160</v>
       </c>
       <c r="AH136" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI136" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="137" spans="1:35">
@@ -11541,10 +11544,10 @@
         <v>160</v>
       </c>
       <c r="AH137" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI137" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="138" spans="1:35">
@@ -11615,10 +11618,10 @@
         <v>160</v>
       </c>
       <c r="AH138" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI138" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="139" spans="1:35">
@@ -11695,10 +11698,10 @@
         <v>160</v>
       </c>
       <c r="AH139" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI139" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="140" spans="1:35">
@@ -11769,10 +11772,10 @@
         <v>160</v>
       </c>
       <c r="AH140" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI140" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="141" spans="1:35">
@@ -11843,10 +11846,10 @@
         <v>160</v>
       </c>
       <c r="AH141" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI141" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="142" spans="1:35">
@@ -11917,10 +11920,10 @@
         <v>160</v>
       </c>
       <c r="AH142" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI142" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="143" spans="1:35">
@@ -11991,10 +11994,10 @@
         <v>160</v>
       </c>
       <c r="AH143" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI143" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="144" spans="1:35">
@@ -12065,10 +12068,10 @@
         <v>160</v>
       </c>
       <c r="AH144" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI144" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="145" spans="1:35">
@@ -12139,10 +12142,10 @@
         <v>160</v>
       </c>
       <c r="AH145" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI145" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="146" spans="1:35">
@@ -12213,10 +12216,10 @@
         <v>160</v>
       </c>
       <c r="AH146" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI146" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="147" spans="1:35">
@@ -12287,10 +12290,10 @@
         <v>160</v>
       </c>
       <c r="AH147" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI147" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="148" spans="1:35">
@@ -12361,10 +12364,10 @@
         <v>160</v>
       </c>
       <c r="AH148" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI148" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="149" spans="1:35">
@@ -12435,10 +12438,10 @@
         <v>160</v>
       </c>
       <c r="AH149" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI149" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="150" spans="1:35">
@@ -12515,10 +12518,10 @@
         <v>160</v>
       </c>
       <c r="AH150" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI150" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="151" spans="1:35">
@@ -12589,10 +12592,10 @@
         <v>160</v>
       </c>
       <c r="AH151" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI151" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="152" spans="1:35">
@@ -12663,10 +12666,10 @@
         <v>160</v>
       </c>
       <c r="AH152" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI152" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="153" spans="1:35">
@@ -12737,10 +12740,10 @@
         <v>160</v>
       </c>
       <c r="AH153" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI153" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="154" spans="1:35">
@@ -12811,10 +12814,10 @@
         <v>161</v>
       </c>
       <c r="AH154" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI154" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="155" spans="1:35">
@@ -12885,10 +12888,10 @@
         <v>161</v>
       </c>
       <c r="AH155" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI155" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="156" spans="1:35">
@@ -12959,10 +12962,10 @@
         <v>161</v>
       </c>
       <c r="AH156" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI156" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="157" spans="1:35">
@@ -13033,10 +13036,10 @@
         <v>161</v>
       </c>
       <c r="AH157" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI157" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="158" spans="1:35">
@@ -13107,10 +13110,10 @@
         <v>161</v>
       </c>
       <c r="AH158" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI158" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="159" spans="1:35">
@@ -13181,10 +13184,10 @@
         <v>161</v>
       </c>
       <c r="AH159" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI159" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="160" spans="1:35">
@@ -13255,10 +13258,10 @@
         <v>161</v>
       </c>
       <c r="AH160" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI160" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="161" spans="1:35">
@@ -13329,10 +13332,10 @@
         <v>161</v>
       </c>
       <c r="AH161" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI161" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="162" spans="1:35">
@@ -13403,10 +13406,10 @@
         <v>161</v>
       </c>
       <c r="AH162" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI162" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="163" spans="1:35">
@@ -13477,10 +13480,10 @@
         <v>161</v>
       </c>
       <c r="AH163" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI163" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="164" spans="1:35">
@@ -13551,10 +13554,10 @@
         <v>161</v>
       </c>
       <c r="AH164" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI164" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="165" spans="1:35">
@@ -13625,10 +13628,10 @@
         <v>161</v>
       </c>
       <c r="AH165" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI165" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="166" spans="1:35">
@@ -13699,10 +13702,10 @@
         <v>161</v>
       </c>
       <c r="AH166" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI166" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="167" spans="1:35">
@@ -13773,10 +13776,10 @@
         <v>161</v>
       </c>
       <c r="AH167" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI167" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="168" spans="1:35">
@@ -13847,10 +13850,10 @@
         <v>161</v>
       </c>
       <c r="AH168" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI168" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="169" spans="1:35">
@@ -13924,10 +13927,10 @@
         <v>161</v>
       </c>
       <c r="AH169" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI169" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="170" spans="1:35">
@@ -14001,10 +14004,10 @@
         <v>161</v>
       </c>
       <c r="AH170" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI170" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="171" spans="1:35">
@@ -14078,10 +14081,10 @@
         <v>161</v>
       </c>
       <c r="AH171" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI171" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="172" spans="1:35">
@@ -14155,10 +14158,10 @@
         <v>161</v>
       </c>
       <c r="AH172" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI172" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="173" spans="1:35">
@@ -14232,10 +14235,10 @@
         <v>161</v>
       </c>
       <c r="AH173" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI173" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="174" spans="1:35">
@@ -14309,10 +14312,10 @@
         <v>161</v>
       </c>
       <c r="AH174" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI174" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="175" spans="1:35">
@@ -14386,10 +14389,10 @@
         <v>161</v>
       </c>
       <c r="AH175" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI175" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="176" spans="1:35">
@@ -14463,10 +14466,10 @@
         <v>161</v>
       </c>
       <c r="AH176" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI176" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="177" spans="1:35">
@@ -14540,10 +14543,10 @@
         <v>161</v>
       </c>
       <c r="AH177" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI177" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="178" spans="1:35">
@@ -14617,10 +14620,10 @@
         <v>161</v>
       </c>
       <c r="AH178" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI178" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="179" spans="1:35">
@@ -14694,10 +14697,10 @@
         <v>161</v>
       </c>
       <c r="AH179" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI179" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="180" spans="1:35">
@@ -14771,10 +14774,10 @@
         <v>161</v>
       </c>
       <c r="AH180" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI180" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="181" spans="1:35">
@@ -14848,10 +14851,10 @@
         <v>161</v>
       </c>
       <c r="AH181" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI181" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="182" spans="1:35">
@@ -14925,10 +14928,10 @@
         <v>161</v>
       </c>
       <c r="AH182" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI182" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="183" spans="1:35">
@@ -14996,10 +14999,10 @@
         <v>161</v>
       </c>
       <c r="AH183" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI183" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="184" spans="1:35">
@@ -15067,10 +15070,10 @@
         <v>161</v>
       </c>
       <c r="AH184" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI184" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="185" spans="1:35">
@@ -15138,10 +15141,10 @@
         <v>161</v>
       </c>
       <c r="AH185" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI185" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="186" spans="1:35">
@@ -15209,10 +15212,10 @@
         <v>161</v>
       </c>
       <c r="AH186" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI186" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="187" spans="1:35">
@@ -15280,10 +15283,10 @@
         <v>161</v>
       </c>
       <c r="AH187" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI187" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="188" spans="1:35">
@@ -15351,10 +15354,10 @@
         <v>161</v>
       </c>
       <c r="AH188" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI188" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="189" spans="1:35">
@@ -15422,10 +15425,10 @@
         <v>54</v>
       </c>
       <c r="AH189" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI189" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="190" spans="1:35">
@@ -15493,10 +15496,10 @@
         <v>54</v>
       </c>
       <c r="AH190" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI190" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="191" spans="1:35">
@@ -15564,10 +15567,10 @@
         <v>54</v>
       </c>
       <c r="AH191" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI191" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="192" spans="1:35">
@@ -15635,10 +15638,10 @@
         <v>54</v>
       </c>
       <c r="AH192" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI192" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="193" spans="1:35">
@@ -15706,10 +15709,10 @@
         <v>162</v>
       </c>
       <c r="AH193" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI193" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="194" spans="1:35">
@@ -15777,10 +15780,10 @@
         <v>55</v>
       </c>
       <c r="AH194" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI194" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="195" spans="1:35">
@@ -15848,10 +15851,10 @@
         <v>54</v>
       </c>
       <c r="AH195" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI195" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="196" spans="1:35">
@@ -15919,10 +15922,10 @@
         <v>54</v>
       </c>
       <c r="AH196" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI196" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="197" spans="1:35">
@@ -15990,10 +15993,10 @@
         <v>54</v>
       </c>
       <c r="AH197" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI197" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="198" spans="1:35">
@@ -16061,10 +16064,10 @@
         <v>162</v>
       </c>
       <c r="AH198" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI198" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="199" spans="1:35">
@@ -16132,10 +16135,10 @@
         <v>54</v>
       </c>
       <c r="AH199" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI199" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="200" spans="1:35">
@@ -16203,10 +16206,10 @@
         <v>162</v>
       </c>
       <c r="AH200" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI200" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="201" spans="1:35">
@@ -16274,10 +16277,10 @@
         <v>54</v>
       </c>
       <c r="AH201" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI201" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="202" spans="1:35">
@@ -16345,10 +16348,10 @@
         <v>54</v>
       </c>
       <c r="AH202" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI202" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="203" spans="1:35">
@@ -16416,10 +16419,10 @@
         <v>54</v>
       </c>
       <c r="AH203" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI203" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="204" spans="1:35">
@@ -16487,10 +16490,10 @@
         <v>54</v>
       </c>
       <c r="AH204" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI204" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="205" spans="1:35">
@@ -16558,10 +16561,10 @@
         <v>54</v>
       </c>
       <c r="AH205" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI205" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="206" spans="1:35">
@@ -16629,10 +16632,10 @@
         <v>54</v>
       </c>
       <c r="AH206" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI206" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="207" spans="1:35">
@@ -16700,10 +16703,10 @@
         <v>162</v>
       </c>
       <c r="AH207" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI207" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="208" spans="1:35">
@@ -16771,10 +16774,10 @@
         <v>55</v>
       </c>
       <c r="AH208" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI208" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="209" spans="1:35">
@@ -16845,10 +16848,10 @@
         <v>54</v>
       </c>
       <c r="AH209" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI209" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="210" spans="1:35">
@@ -16919,10 +16922,10 @@
         <v>54</v>
       </c>
       <c r="AH210" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI210" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="211" spans="1:35">
@@ -16993,10 +16996,10 @@
         <v>54</v>
       </c>
       <c r="AH211" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI211" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="212" spans="1:35">
@@ -17067,10 +17070,10 @@
         <v>54</v>
       </c>
       <c r="AH212" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI212" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="213" spans="1:35">
@@ -17138,10 +17141,10 @@
         <v>54</v>
       </c>
       <c r="AH213" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI213" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="214" spans="1:35">
@@ -17209,10 +17212,10 @@
         <v>54</v>
       </c>
       <c r="AH214" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI214" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="215" spans="1:35">
@@ -17277,10 +17280,10 @@
         <v>0</v>
       </c>
       <c r="AH215" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI215" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="216" spans="1:35">
@@ -17342,10 +17345,10 @@
         <v>0</v>
       </c>
       <c r="AH216" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI216" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="217" spans="1:35">
@@ -17413,13 +17416,13 @@
         <v>0</v>
       </c>
       <c r="AC217" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AH217" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI217" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="218" spans="1:35">
@@ -17493,10 +17496,10 @@
         <v>151</v>
       </c>
       <c r="AH218" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI218" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="219" spans="1:35">
@@ -17573,10 +17576,10 @@
         <v>148</v>
       </c>
       <c r="AH219" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI219" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="220" spans="1:35">
@@ -17653,10 +17656,10 @@
         <v>148</v>
       </c>
       <c r="AH220" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI220" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="221" spans="1:35">
@@ -17733,10 +17736,10 @@
         <v>148</v>
       </c>
       <c r="AH221" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI221" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="222" spans="1:35">
@@ -17813,10 +17816,10 @@
         <v>154</v>
       </c>
       <c r="AH222" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI222" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="223" spans="1:35">
@@ -17893,10 +17896,10 @@
         <v>149</v>
       </c>
       <c r="AH223" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI223" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="224" spans="1:35">
@@ -17967,18 +17970,18 @@
         <v>150</v>
       </c>
       <c r="AH224" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI224" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="225" spans="1:35">
       <c r="A225">
-        <v>6548</v>
+        <v>6486</v>
       </c>
       <c r="B225" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C225" t="s">
         <v>50</v>
@@ -18007,6 +18010,9 @@
       <c r="N225" s="1">
         <v>46280</v>
       </c>
+      <c r="O225" t="s">
+        <v>138</v>
+      </c>
       <c r="P225">
         <v>8</v>
       </c>
@@ -18014,10 +18020,10 @@
         <v>2026</v>
       </c>
       <c r="R225">
-        <v>17222618</v>
+        <v>16976056</v>
       </c>
       <c r="S225" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="T225" t="s">
         <v>167</v>
@@ -18026,13 +18032,13 @@
         <v>172</v>
       </c>
       <c r="V225" s="1">
-        <v>46279.40189383102</v>
+        <v>46279.5886965625</v>
       </c>
       <c r="W225">
         <v>-1</v>
       </c>
       <c r="X225" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="Y225" t="s">
         <v>252</v>
@@ -18041,27 +18047,27 @@
         <v>0</v>
       </c>
       <c r="AC225" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="AH225" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI225" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="226" spans="1:35">
       <c r="A226">
-        <v>6779</v>
+        <v>6548</v>
       </c>
       <c r="B226" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="C226" t="s">
         <v>50</v>
       </c>
       <c r="D226" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E226" t="s">
         <v>54</v>
@@ -18091,25 +18097,25 @@
         <v>2026</v>
       </c>
       <c r="R226">
-        <v>18090178</v>
+        <v>17222618</v>
       </c>
       <c r="S226" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="T226" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="U226" t="s">
         <v>172</v>
       </c>
       <c r="V226" s="1">
-        <v>46276.63187557871</v>
+        <v>46279.40189383102</v>
       </c>
       <c r="W226">
         <v>-1</v>
       </c>
       <c r="X226" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="Y226" t="s">
         <v>253</v>
@@ -18118,13 +18124,13 @@
         <v>0</v>
       </c>
       <c r="AC226" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AH226" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI226" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="227" spans="1:35">
@@ -18147,46 +18153,52 @@
         <v>56</v>
       </c>
       <c r="G227">
-        <v>6348</v>
+        <v>5867</v>
       </c>
       <c r="H227">
-        <v>0</v>
+        <v>5786</v>
       </c>
       <c r="I227" t="s">
         <v>61</v>
       </c>
       <c r="J227" t="s">
-        <v>87</v>
+        <v>123</v>
       </c>
       <c r="N227" s="1">
-        <v>46275</v>
+        <v>46280</v>
       </c>
       <c r="O227" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="P227">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q227">
         <v>2026</v>
       </c>
       <c r="R227">
-        <v>18261361</v>
+        <v>18068532</v>
+      </c>
+      <c r="S227" t="s">
+        <v>148</v>
+      </c>
+      <c r="T227" t="s">
+        <v>167</v>
       </c>
       <c r="U227" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="V227" s="1">
-        <v>46275.39631951389</v>
+        <v>46279.58878520833</v>
       </c>
       <c r="W227">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="X227" t="s">
         <v>175</v>
       </c>
       <c r="Y227" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AB227">
         <v>0</v>
@@ -18195,10 +18207,10 @@
         <v>148</v>
       </c>
       <c r="AH227" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI227" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="228" spans="1:35">
@@ -18221,46 +18233,52 @@
         <v>56</v>
       </c>
       <c r="G228">
-        <v>6348</v>
+        <v>5867</v>
       </c>
       <c r="H228">
-        <v>0</v>
+        <v>5786</v>
       </c>
       <c r="I228" t="s">
         <v>61</v>
       </c>
       <c r="J228" t="s">
-        <v>87</v>
+        <v>123</v>
       </c>
       <c r="N228" s="1">
-        <v>46275</v>
+        <v>46280</v>
       </c>
       <c r="O228" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="P228">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q228">
         <v>2026</v>
       </c>
       <c r="R228">
-        <v>18261362</v>
+        <v>18052451</v>
+      </c>
+      <c r="S228" t="s">
+        <v>148</v>
+      </c>
+      <c r="T228" t="s">
+        <v>167</v>
       </c>
       <c r="U228" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="V228" s="1">
-        <v>46275.39631994213</v>
+        <v>46279.58873577546</v>
       </c>
       <c r="W228">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="X228" t="s">
         <v>175</v>
       </c>
       <c r="Y228" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AB228">
         <v>0</v>
@@ -18269,18 +18287,18 @@
         <v>148</v>
       </c>
       <c r="AH228" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI228" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="229" spans="1:35">
       <c r="A229">
-        <v>6945</v>
+        <v>6779</v>
       </c>
       <c r="B229" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C229" t="s">
         <v>50</v>
@@ -18292,22 +18310,22 @@
         <v>54</v>
       </c>
       <c r="F229" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G229">
-        <v>1862</v>
+        <v>5867</v>
       </c>
       <c r="H229">
-        <v>0</v>
+        <v>5786</v>
       </c>
       <c r="I229" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J229" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="N229" s="1">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="P229">
         <v>8</v>
@@ -18316,42 +18334,48 @@
         <v>2026</v>
       </c>
       <c r="R229">
-        <v>18220176</v>
+        <v>18090178</v>
       </c>
       <c r="S229" t="s">
-        <v>159</v>
+        <v>154</v>
+      </c>
+      <c r="T229" t="s">
+        <v>169</v>
       </c>
       <c r="U229" t="s">
         <v>172</v>
       </c>
       <c r="V229" s="1">
-        <v>46276.37795540509</v>
+        <v>46276.63187557871</v>
       </c>
       <c r="W229">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="X229" t="s">
-        <v>177</v>
+        <v>179</v>
+      </c>
+      <c r="Y229" t="s">
+        <v>254</v>
       </c>
       <c r="AB229">
         <v>0</v>
       </c>
       <c r="AC229" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="AH229" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI229" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="230" spans="1:35">
       <c r="A230">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B230" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C230" t="s">
         <v>50</v>
@@ -18360,55 +18384,49 @@
         <v>51</v>
       </c>
       <c r="E230" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F230" t="s">
         <v>56</v>
       </c>
       <c r="G230">
-        <v>6805</v>
+        <v>6348</v>
       </c>
       <c r="H230">
         <v>0</v>
       </c>
       <c r="I230" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J230" t="s">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="N230" s="1">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="O230" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="P230">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q230">
         <v>2026</v>
       </c>
       <c r="R230">
-        <v>17222743</v>
-      </c>
-      <c r="S230" t="s">
-        <v>155</v>
-      </c>
-      <c r="T230" t="s">
-        <v>156</v>
+        <v>18261361</v>
       </c>
       <c r="U230" t="s">
         <v>173</v>
       </c>
       <c r="V230" s="1">
-        <v>46276.66923222222</v>
+        <v>46275.39631951389</v>
       </c>
       <c r="W230">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X230" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y230" t="s">
         <v>255</v>
@@ -18417,27 +18435,27 @@
         <v>0</v>
       </c>
       <c r="AC230" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="AH230" t="s">
         <v>291</v>
       </c>
       <c r="AI230" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="231" spans="1:35">
       <c r="A231">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B231" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C231" t="s">
         <v>50</v>
       </c>
       <c r="D231" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E231" t="s">
         <v>55</v>
@@ -18446,66 +18464,66 @@
         <v>56</v>
       </c>
       <c r="G231">
-        <v>6805</v>
+        <v>6348</v>
       </c>
       <c r="H231">
         <v>0</v>
       </c>
       <c r="I231" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J231" t="s">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="N231" s="1">
-        <v>46276</v>
+        <v>46275</v>
+      </c>
+      <c r="O231" t="s">
+        <v>134</v>
       </c>
       <c r="P231">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q231">
         <v>2026</v>
       </c>
       <c r="R231">
-        <v>18085519</v>
-      </c>
-      <c r="S231" t="s">
-        <v>156</v>
-      </c>
-      <c r="T231" t="s">
-        <v>156</v>
+        <v>18261362</v>
       </c>
       <c r="U231" t="s">
         <v>173</v>
       </c>
       <c r="V231" s="1">
-        <v>46276.40669469907</v>
+        <v>46275.39631994213</v>
       </c>
       <c r="W231">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X231" t="s">
         <v>175</v>
       </c>
+      <c r="Y231" t="s">
+        <v>255</v>
+      </c>
       <c r="AB231">
         <v>0</v>
       </c>
       <c r="AC231" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="AH231" t="s">
         <v>291</v>
       </c>
       <c r="AI231" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="232" spans="1:35">
       <c r="A232">
-        <v>6628</v>
+        <v>6945</v>
       </c>
       <c r="B232" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C232" t="s">
         <v>50</v>
@@ -18514,13 +18532,13 @@
         <v>52</v>
       </c>
       <c r="E232" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F232" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G232">
-        <v>6805</v>
+        <v>1862</v>
       </c>
       <c r="H232">
         <v>0</v>
@@ -18529,13 +18547,10 @@
         <v>62</v>
       </c>
       <c r="J232" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N232" s="1">
-        <v>46276</v>
-      </c>
-      <c r="O232" t="s">
-        <v>137</v>
+        <v>46281</v>
       </c>
       <c r="P232">
         <v>8</v>
@@ -18544,60 +18559,54 @@
         <v>2026</v>
       </c>
       <c r="R232">
-        <v>17988709</v>
+        <v>18220176</v>
       </c>
       <c r="S232" t="s">
-        <v>156</v>
-      </c>
-      <c r="T232" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="U232" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="V232" s="1">
-        <v>46276.64773491898</v>
+        <v>46276.37795540509</v>
       </c>
       <c r="W232">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="X232" t="s">
-        <v>175</v>
-      </c>
-      <c r="Y232" t="s">
-        <v>256</v>
+        <v>177</v>
       </c>
       <c r="AB232">
         <v>0</v>
       </c>
       <c r="AC232" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="AH232" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AI232" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="233" spans="1:35">
       <c r="A233">
-        <v>6945</v>
+        <v>6548</v>
       </c>
       <c r="B233" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C233" t="s">
         <v>50</v>
       </c>
       <c r="D233" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E233" t="s">
         <v>54</v>
       </c>
       <c r="F233" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G233">
         <v>6805</v>
@@ -18624,57 +18633,60 @@
         <v>2026</v>
       </c>
       <c r="R233">
-        <v>18220221</v>
+        <v>17222743</v>
       </c>
       <c r="S233" t="s">
-        <v>159</v>
+        <v>155</v>
+      </c>
+      <c r="T233" t="s">
+        <v>156</v>
       </c>
       <c r="U233" t="s">
         <v>173</v>
       </c>
       <c r="V233" s="1">
-        <v>46276.39101108797</v>
+        <v>46276.66923222222</v>
       </c>
       <c r="W233">
         <v>3</v>
       </c>
       <c r="X233" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="Y233" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AB233">
         <v>0</v>
       </c>
       <c r="AC233" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="AH233" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI233" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="234" spans="1:35">
       <c r="A234">
-        <v>6963</v>
+        <v>6627</v>
       </c>
       <c r="B234" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C234" t="s">
         <v>50</v>
       </c>
       <c r="D234" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E234" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F234" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G234">
         <v>6805</v>
@@ -18691,9 +18703,6 @@
       <c r="N234" s="1">
         <v>46276</v>
       </c>
-      <c r="O234" t="s">
-        <v>137</v>
-      </c>
       <c r="P234">
         <v>8</v>
       </c>
@@ -18701,10 +18710,10 @@
         <v>2026</v>
       </c>
       <c r="R234">
-        <v>18187261</v>
+        <v>18085519</v>
       </c>
       <c r="S234" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="T234" t="s">
         <v>156</v>
@@ -18713,42 +18722,39 @@
         <v>173</v>
       </c>
       <c r="V234" s="1">
-        <v>46276.66651596065</v>
+        <v>46276.40669469907</v>
       </c>
       <c r="W234">
         <v>3</v>
       </c>
       <c r="X234" t="s">
-        <v>178</v>
-      </c>
-      <c r="Y234" t="s">
-        <v>258</v>
+        <v>175</v>
       </c>
       <c r="AB234">
         <v>0</v>
       </c>
       <c r="AC234" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AH234" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI234" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="235" spans="1:35">
       <c r="A235">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B235" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C235" t="s">
         <v>50</v>
       </c>
       <c r="D235" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E235" t="s">
         <v>55</v>
@@ -18757,7 +18763,7 @@
         <v>56</v>
       </c>
       <c r="G235">
-        <v>1866</v>
+        <v>6805</v>
       </c>
       <c r="H235">
         <v>0</v>
@@ -18766,10 +18772,13 @@
         <v>62</v>
       </c>
       <c r="J235" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="N235" s="1">
-        <v>46274</v>
+        <v>46276</v>
+      </c>
+      <c r="O235" t="s">
+        <v>137</v>
       </c>
       <c r="P235">
         <v>8</v>
@@ -18778,7 +18787,7 @@
         <v>2026</v>
       </c>
       <c r="R235">
-        <v>17968368</v>
+        <v>17988709</v>
       </c>
       <c r="S235" t="s">
         <v>156</v>
@@ -18790,16 +18799,16 @@
         <v>173</v>
       </c>
       <c r="V235" s="1">
-        <v>46274.36843923611</v>
+        <v>46276.64773491898</v>
       </c>
       <c r="W235">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X235" t="s">
         <v>175</v>
       </c>
       <c r="Y235" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AB235">
         <v>0</v>
@@ -18808,24 +18817,24 @@
         <v>156</v>
       </c>
       <c r="AH235" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AI235" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="236" spans="1:35">
       <c r="A236">
-        <v>6962</v>
+        <v>6945</v>
       </c>
       <c r="B236" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C236" t="s">
         <v>50</v>
       </c>
       <c r="D236" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E236" t="s">
         <v>54</v>
@@ -18834,7 +18843,7 @@
         <v>57</v>
       </c>
       <c r="G236">
-        <v>1866</v>
+        <v>6805</v>
       </c>
       <c r="H236">
         <v>0</v>
@@ -18843,10 +18852,13 @@
         <v>62</v>
       </c>
       <c r="J236" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="N236" s="1">
-        <v>46274</v>
+        <v>46276</v>
+      </c>
+      <c r="O236" t="s">
+        <v>137</v>
       </c>
       <c r="P236">
         <v>8</v>
@@ -18855,40 +18867,37 @@
         <v>2026</v>
       </c>
       <c r="R236">
-        <v>18186946</v>
+        <v>18220221</v>
       </c>
       <c r="S236" t="s">
-        <v>158</v>
-      </c>
-      <c r="T236" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="U236" t="s">
         <v>173</v>
       </c>
       <c r="V236" s="1">
-        <v>46274.66470667824</v>
+        <v>46276.39101108797</v>
       </c>
       <c r="W236">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X236" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y236" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="AB236">
         <v>0</v>
       </c>
       <c r="AC236" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AH236" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AI236" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="237" spans="1:35">
@@ -18911,7 +18920,7 @@
         <v>57</v>
       </c>
       <c r="G237">
-        <v>1866</v>
+        <v>6805</v>
       </c>
       <c r="H237">
         <v>0</v>
@@ -18920,10 +18929,13 @@
         <v>62</v>
       </c>
       <c r="J237" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="N237" s="1">
-        <v>46274</v>
+        <v>46276</v>
+      </c>
+      <c r="O237" t="s">
+        <v>137</v>
       </c>
       <c r="P237">
         <v>8</v>
@@ -18932,7 +18944,7 @@
         <v>2026</v>
       </c>
       <c r="R237">
-        <v>18187212</v>
+        <v>18187261</v>
       </c>
       <c r="S237" t="s">
         <v>158</v>
@@ -18944,16 +18956,16 @@
         <v>173</v>
       </c>
       <c r="V237" s="1">
-        <v>46274.74452168981</v>
+        <v>46276.66651596065</v>
       </c>
       <c r="W237">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X237" t="s">
         <v>178</v>
       </c>
       <c r="Y237" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="AB237">
         <v>0</v>
@@ -18962,18 +18974,18 @@
         <v>158</v>
       </c>
       <c r="AH237" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AI237" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="238" spans="1:35">
       <c r="A238">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B238" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C238" t="s">
         <v>50</v>
@@ -18982,13 +18994,13 @@
         <v>51</v>
       </c>
       <c r="E238" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F238" t="s">
         <v>56</v>
       </c>
       <c r="G238">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="H238">
         <v>0</v>
@@ -18997,14 +19009,11 @@
         <v>62</v>
       </c>
       <c r="J238" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N238" s="1">
         <v>46274</v>
       </c>
-      <c r="O238" t="s">
-        <v>136</v>
-      </c>
       <c r="P238">
         <v>8</v>
       </c>
@@ -19012,10 +19021,10 @@
         <v>2026</v>
       </c>
       <c r="R238">
-        <v>17988543</v>
+        <v>17968368</v>
       </c>
       <c r="S238" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="T238" t="s">
         <v>156</v>
@@ -19024,51 +19033,51 @@
         <v>173</v>
       </c>
       <c r="V238" s="1">
-        <v>46274.64801501157</v>
+        <v>46274.36843923611</v>
       </c>
       <c r="W238">
         <v>5</v>
       </c>
       <c r="X238" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y238" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="AB238">
         <v>0</v>
       </c>
       <c r="AC238" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AH238" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI238" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="239" spans="1:35">
       <c r="A239">
-        <v>6627</v>
+        <v>6962</v>
       </c>
       <c r="B239" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C239" t="s">
         <v>50</v>
       </c>
       <c r="D239" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E239" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F239" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G239">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="H239">
         <v>0</v>
@@ -19077,7 +19086,7 @@
         <v>62</v>
       </c>
       <c r="J239" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N239" s="1">
         <v>46274</v>
@@ -19089,10 +19098,10 @@
         <v>2026</v>
       </c>
       <c r="R239">
-        <v>17968379</v>
+        <v>18186946</v>
       </c>
       <c r="S239" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="T239" t="s">
         <v>156</v>
@@ -19101,39 +19110,42 @@
         <v>173</v>
       </c>
       <c r="V239" s="1">
-        <v>46274.36695243056</v>
+        <v>46274.66470667824</v>
       </c>
       <c r="W239">
         <v>5</v>
       </c>
       <c r="X239" t="s">
-        <v>175</v>
+        <v>178</v>
+      </c>
+      <c r="Y239" t="s">
+        <v>261</v>
       </c>
       <c r="AB239">
         <v>0</v>
       </c>
       <c r="AC239" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AH239" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI239" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="240" spans="1:35">
       <c r="A240">
-        <v>6945</v>
+        <v>6963</v>
       </c>
       <c r="B240" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C240" t="s">
         <v>50</v>
       </c>
       <c r="D240" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E240" t="s">
         <v>54</v>
@@ -19142,7 +19154,7 @@
         <v>57</v>
       </c>
       <c r="G240">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="H240">
         <v>0</v>
@@ -19151,14 +19163,11 @@
         <v>62</v>
       </c>
       <c r="J240" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N240" s="1">
         <v>46274</v>
       </c>
-      <c r="O240" t="s">
-        <v>137</v>
-      </c>
       <c r="P240">
         <v>8</v>
       </c>
@@ -19166,57 +19175,60 @@
         <v>2026</v>
       </c>
       <c r="R240">
-        <v>18220182</v>
+        <v>18187212</v>
       </c>
       <c r="S240" t="s">
-        <v>159</v>
+        <v>158</v>
+      </c>
+      <c r="T240" t="s">
+        <v>156</v>
       </c>
       <c r="U240" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="V240" s="1">
-        <v>46276.4084265625</v>
+        <v>46274.74452168981</v>
       </c>
       <c r="W240">
         <v>5</v>
       </c>
       <c r="X240" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Y240" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AB240">
         <v>0</v>
       </c>
       <c r="AC240" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AH240" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI240" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="241" spans="1:35">
       <c r="A241">
-        <v>6962</v>
+        <v>6548</v>
       </c>
       <c r="B241" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C241" t="s">
         <v>50</v>
       </c>
       <c r="D241" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E241" t="s">
         <v>54</v>
       </c>
       <c r="F241" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G241">
         <v>1867</v>
@@ -19233,6 +19245,9 @@
       <c r="N241" s="1">
         <v>46274</v>
       </c>
+      <c r="O241" t="s">
+        <v>136</v>
+      </c>
       <c r="P241">
         <v>8</v>
       </c>
@@ -19240,10 +19255,10 @@
         <v>2026</v>
       </c>
       <c r="R241">
-        <v>18186953</v>
+        <v>17988543</v>
       </c>
       <c r="S241" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="T241" t="s">
         <v>156</v>
@@ -19252,45 +19267,48 @@
         <v>173</v>
       </c>
       <c r="V241" s="1">
-        <v>46274.7274781713</v>
+        <v>46274.64801501157</v>
       </c>
       <c r="W241">
         <v>5</v>
       </c>
       <c r="X241" t="s">
-        <v>178</v>
+        <v>174</v>
+      </c>
+      <c r="Y241" t="s">
+        <v>263</v>
       </c>
       <c r="AB241">
         <v>0</v>
       </c>
       <c r="AC241" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="AH241" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI241" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="242" spans="1:35">
       <c r="A242">
-        <v>6963</v>
+        <v>6627</v>
       </c>
       <c r="B242" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C242" t="s">
         <v>50</v>
       </c>
       <c r="D242" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E242" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F242" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G242">
         <v>1867</v>
@@ -19314,10 +19332,10 @@
         <v>2026</v>
       </c>
       <c r="R242">
-        <v>18187219</v>
+        <v>17968379</v>
       </c>
       <c r="S242" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="T242" t="s">
         <v>156</v>
@@ -19326,39 +19344,39 @@
         <v>173</v>
       </c>
       <c r="V242" s="1">
-        <v>46274.74558746528</v>
+        <v>46274.36695243056</v>
       </c>
       <c r="W242">
         <v>5</v>
       </c>
       <c r="X242" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="AB242">
         <v>0</v>
       </c>
       <c r="AC242" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AH242" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI242" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="243" spans="1:35">
       <c r="A243">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B243" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C243" t="s">
         <v>50</v>
       </c>
       <c r="D243" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E243" t="s">
         <v>54</v>
@@ -19367,19 +19385,22 @@
         <v>57</v>
       </c>
       <c r="G243">
-        <v>6886</v>
+        <v>1867</v>
       </c>
       <c r="H243">
-        <v>1862</v>
+        <v>0</v>
       </c>
       <c r="I243" t="s">
         <v>62</v>
       </c>
       <c r="J243" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="N243" s="1">
-        <v>46275</v>
+        <v>46274</v>
+      </c>
+      <c r="O243" t="s">
+        <v>137</v>
       </c>
       <c r="P243">
         <v>8</v>
@@ -19388,72 +19409,72 @@
         <v>2026</v>
       </c>
       <c r="R243">
-        <v>18214907</v>
+        <v>18220182</v>
       </c>
       <c r="S243" t="s">
-        <v>157</v>
-      </c>
-      <c r="T243" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="U243" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="V243" s="1">
-        <v>46275.79245582176</v>
+        <v>46276.4084265625</v>
       </c>
       <c r="W243">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X243" t="s">
-        <v>176</v>
+        <v>177</v>
+      </c>
+      <c r="Y243" t="s">
+        <v>264</v>
       </c>
       <c r="AB243">
         <v>0</v>
       </c>
       <c r="AC243" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AH243" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI243" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="244" spans="1:35">
       <c r="A244">
-        <v>5417</v>
+        <v>6962</v>
       </c>
       <c r="B244" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C244" t="s">
         <v>50</v>
       </c>
       <c r="D244" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E244" t="s">
         <v>54</v>
       </c>
       <c r="F244" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G244">
-        <v>6806</v>
+        <v>1867</v>
       </c>
       <c r="H244">
         <v>0</v>
       </c>
       <c r="I244" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J244" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="N244" s="1">
-        <v>46276</v>
+        <v>46274</v>
       </c>
       <c r="P244">
         <v>8</v>
@@ -19462,45 +19483,45 @@
         <v>2026</v>
       </c>
       <c r="R244">
-        <v>17399230</v>
+        <v>18186953</v>
       </c>
       <c r="S244" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="T244" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="U244" t="s">
         <v>173</v>
       </c>
       <c r="V244" s="1">
-        <v>46276.49596842592</v>
+        <v>46274.7274781713</v>
       </c>
       <c r="W244">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X244" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AB244">
         <v>0</v>
       </c>
       <c r="AC244" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="AH244" t="s">
         <v>291</v>
       </c>
       <c r="AI244" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="245" spans="1:35">
       <c r="A245">
-        <v>6404</v>
+        <v>6963</v>
       </c>
       <c r="B245" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C245" t="s">
         <v>50</v>
@@ -19512,22 +19533,22 @@
         <v>54</v>
       </c>
       <c r="F245" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G245">
-        <v>6806</v>
+        <v>1867</v>
       </c>
       <c r="H245">
         <v>0</v>
       </c>
       <c r="I245" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J245" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="N245" s="1">
-        <v>46276</v>
+        <v>46274</v>
       </c>
       <c r="P245">
         <v>8</v>
@@ -19536,45 +19557,45 @@
         <v>2026</v>
       </c>
       <c r="R245">
-        <v>16962308</v>
+        <v>18187219</v>
       </c>
       <c r="S245" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="T245" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="U245" t="s">
         <v>173</v>
       </c>
       <c r="V245" s="1">
-        <v>46276.53874935185</v>
+        <v>46274.74558746528</v>
       </c>
       <c r="W245">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X245" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="AB245">
         <v>0</v>
       </c>
       <c r="AC245" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="AH245" t="s">
         <v>291</v>
       </c>
       <c r="AI245" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="246" spans="1:35">
       <c r="A246">
-        <v>6486</v>
+        <v>6949</v>
       </c>
       <c r="B246" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C246" t="s">
         <v>50</v>
@@ -19586,22 +19607,22 @@
         <v>54</v>
       </c>
       <c r="F246" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G246">
-        <v>6806</v>
+        <v>6886</v>
       </c>
       <c r="H246">
-        <v>0</v>
+        <v>1862</v>
       </c>
       <c r="I246" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J246" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="N246" s="1">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="P246">
         <v>8</v>
@@ -19610,51 +19631,51 @@
         <v>2026</v>
       </c>
       <c r="R246">
-        <v>16976187</v>
+        <v>18214907</v>
       </c>
       <c r="S246" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="T246" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="U246" t="s">
         <v>173</v>
       </c>
       <c r="V246" s="1">
-        <v>46276.49597027778</v>
+        <v>46275.79245582176</v>
       </c>
       <c r="W246">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X246" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="AB246">
         <v>0</v>
       </c>
       <c r="AC246" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="AH246" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AI246" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="247" spans="1:35">
       <c r="A247">
-        <v>6703</v>
+        <v>5417</v>
       </c>
       <c r="B247" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C247" t="s">
         <v>50</v>
       </c>
       <c r="D247" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E247" t="s">
         <v>54</v>
@@ -19684,7 +19705,7 @@
         <v>2026</v>
       </c>
       <c r="R247">
-        <v>17948858</v>
+        <v>17399230</v>
       </c>
       <c r="S247" t="s">
         <v>160</v>
@@ -19696,13 +19717,13 @@
         <v>173</v>
       </c>
       <c r="V247" s="1">
-        <v>46276.62604146991</v>
+        <v>46276.49596842592</v>
       </c>
       <c r="W247">
         <v>3</v>
       </c>
       <c r="X247" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="AB247">
         <v>0</v>
@@ -19711,24 +19732,24 @@
         <v>160</v>
       </c>
       <c r="AH247" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI247" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="248" spans="1:35">
       <c r="A248">
-        <v>6704</v>
+        <v>6404</v>
       </c>
       <c r="B248" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C248" t="s">
         <v>50</v>
       </c>
       <c r="D248" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E248" t="s">
         <v>54</v>
@@ -19758,7 +19779,7 @@
         <v>2026</v>
       </c>
       <c r="R248">
-        <v>18085297</v>
+        <v>16962308</v>
       </c>
       <c r="S248" t="s">
         <v>160</v>
@@ -19770,13 +19791,13 @@
         <v>173</v>
       </c>
       <c r="V248" s="1">
-        <v>46276.68231165509</v>
+        <v>46276.53874935185</v>
       </c>
       <c r="W248">
         <v>3</v>
       </c>
       <c r="X248" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="AB248">
         <v>0</v>
@@ -19785,24 +19806,24 @@
         <v>160</v>
       </c>
       <c r="AH248" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI248" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="249" spans="1:35">
       <c r="A249">
-        <v>6705</v>
+        <v>6486</v>
       </c>
       <c r="B249" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C249" t="s">
         <v>50</v>
       </c>
       <c r="D249" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E249" t="s">
         <v>54</v>
@@ -19825,9 +19846,6 @@
       <c r="N249" s="1">
         <v>46276</v>
       </c>
-      <c r="O249" t="s">
-        <v>138</v>
-      </c>
       <c r="P249">
         <v>8</v>
       </c>
@@ -19835,7 +19853,7 @@
         <v>2026</v>
       </c>
       <c r="R249">
-        <v>17949029</v>
+        <v>16976187</v>
       </c>
       <c r="S249" t="s">
         <v>160</v>
@@ -19847,16 +19865,13 @@
         <v>173</v>
       </c>
       <c r="V249" s="1">
-        <v>46276.7163278588</v>
+        <v>46276.49597027778</v>
       </c>
       <c r="W249">
         <v>3</v>
       </c>
       <c r="X249" t="s">
-        <v>179</v>
-      </c>
-      <c r="Y249" t="s">
-        <v>264</v>
+        <v>181</v>
       </c>
       <c r="AB249">
         <v>0</v>
@@ -19865,24 +19880,24 @@
         <v>160</v>
       </c>
       <c r="AH249" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI249" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="250" spans="1:35">
       <c r="A250">
-        <v>6779</v>
+        <v>6703</v>
       </c>
       <c r="B250" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C250" t="s">
         <v>50</v>
       </c>
       <c r="D250" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E250" t="s">
         <v>54</v>
@@ -19912,7 +19927,7 @@
         <v>2026</v>
       </c>
       <c r="R250">
-        <v>18085066</v>
+        <v>17948858</v>
       </c>
       <c r="S250" t="s">
         <v>160</v>
@@ -19924,13 +19939,13 @@
         <v>173</v>
       </c>
       <c r="V250" s="1">
-        <v>46276.6823121412</v>
+        <v>46276.62604146991</v>
       </c>
       <c r="W250">
         <v>3</v>
       </c>
       <c r="X250" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="AB250">
         <v>0</v>
@@ -19939,24 +19954,24 @@
         <v>160</v>
       </c>
       <c r="AH250" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI250" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="251" spans="1:35">
       <c r="A251">
-        <v>6404</v>
+        <v>6704</v>
       </c>
       <c r="B251" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C251" t="s">
         <v>50</v>
       </c>
       <c r="D251" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E251" t="s">
         <v>54</v>
@@ -19965,7 +19980,7 @@
         <v>56</v>
       </c>
       <c r="G251">
-        <v>1792</v>
+        <v>6806</v>
       </c>
       <c r="H251">
         <v>0</v>
@@ -19974,10 +19989,10 @@
         <v>63</v>
       </c>
       <c r="J251" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="N251" s="1">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="P251">
         <v>8</v>
@@ -19986,7 +20001,7 @@
         <v>2026</v>
       </c>
       <c r="R251">
-        <v>16962151</v>
+        <v>18085297</v>
       </c>
       <c r="S251" t="s">
         <v>160</v>
@@ -19995,16 +20010,16 @@
         <v>170</v>
       </c>
       <c r="U251" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="V251" s="1">
-        <v>46274.70622837963</v>
+        <v>46276.68231165509</v>
       </c>
       <c r="W251">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X251" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="AB251">
         <v>0</v>
@@ -20013,24 +20028,24 @@
         <v>160</v>
       </c>
       <c r="AH251" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AI251" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="252" spans="1:35">
       <c r="A252">
-        <v>6703</v>
+        <v>6705</v>
       </c>
       <c r="B252" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C252" t="s">
         <v>50</v>
       </c>
       <c r="D252" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E252" t="s">
         <v>54</v>
@@ -20039,7 +20054,7 @@
         <v>56</v>
       </c>
       <c r="G252">
-        <v>1792</v>
+        <v>6806</v>
       </c>
       <c r="H252">
         <v>0</v>
@@ -20048,10 +20063,13 @@
         <v>63</v>
       </c>
       <c r="J252" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="N252" s="1">
-        <v>46275</v>
+        <v>46276</v>
+      </c>
+      <c r="O252" t="s">
+        <v>138</v>
       </c>
       <c r="P252">
         <v>8</v>
@@ -20060,7 +20078,7 @@
         <v>2026</v>
       </c>
       <c r="R252">
-        <v>17948756</v>
+        <v>17949029</v>
       </c>
       <c r="S252" t="s">
         <v>160</v>
@@ -20072,13 +20090,16 @@
         <v>173</v>
       </c>
       <c r="V252" s="1">
-        <v>46275.71996309028</v>
+        <v>46276.7163278588</v>
       </c>
       <c r="W252">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X252" t="s">
-        <v>183</v>
+        <v>179</v>
+      </c>
+      <c r="Y252" t="s">
+        <v>265</v>
       </c>
       <c r="AB252">
         <v>0</v>
@@ -20087,24 +20108,24 @@
         <v>160</v>
       </c>
       <c r="AH252" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AI252" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="253" spans="1:35">
       <c r="A253">
-        <v>6704</v>
+        <v>6779</v>
       </c>
       <c r="B253" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C253" t="s">
         <v>50</v>
       </c>
       <c r="D253" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E253" t="s">
         <v>54</v>
@@ -20113,7 +20134,7 @@
         <v>56</v>
       </c>
       <c r="G253">
-        <v>1792</v>
+        <v>6806</v>
       </c>
       <c r="H253">
         <v>0</v>
@@ -20122,10 +20143,10 @@
         <v>63</v>
       </c>
       <c r="J253" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="N253" s="1">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="P253">
         <v>8</v>
@@ -20134,7 +20155,7 @@
         <v>2026</v>
       </c>
       <c r="R253">
-        <v>18085143</v>
+        <v>18085066</v>
       </c>
       <c r="S253" t="s">
         <v>160</v>
@@ -20146,10 +20167,10 @@
         <v>173</v>
       </c>
       <c r="V253" s="1">
-        <v>46275.54278886574</v>
+        <v>46276.6823121412</v>
       </c>
       <c r="W253">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X253" t="s">
         <v>179</v>
@@ -20161,10 +20182,10 @@
         <v>160</v>
       </c>
       <c r="AH253" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AI253" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="254" spans="1:35">
@@ -20187,7 +20208,7 @@
         <v>56</v>
       </c>
       <c r="G254">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="H254">
         <v>0</v>
@@ -20196,7 +20217,7 @@
         <v>63</v>
       </c>
       <c r="J254" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N254" s="1">
         <v>46275</v>
@@ -20208,7 +20229,7 @@
         <v>2026</v>
       </c>
       <c r="R254">
-        <v>16962161</v>
+        <v>16962151</v>
       </c>
       <c r="S254" t="s">
         <v>160</v>
@@ -20217,10 +20238,10 @@
         <v>170</v>
       </c>
       <c r="U254" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="V254" s="1">
-        <v>46275.7000328588</v>
+        <v>46274.70622837963</v>
       </c>
       <c r="W254">
         <v>4</v>
@@ -20235,24 +20256,24 @@
         <v>160</v>
       </c>
       <c r="AH254" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI254" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="255" spans="1:35">
       <c r="A255">
-        <v>6486</v>
+        <v>6703</v>
       </c>
       <c r="B255" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C255" t="s">
         <v>50</v>
       </c>
       <c r="D255" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E255" t="s">
         <v>54</v>
@@ -20261,7 +20282,7 @@
         <v>56</v>
       </c>
       <c r="G255">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="H255">
         <v>0</v>
@@ -20270,7 +20291,7 @@
         <v>63</v>
       </c>
       <c r="J255" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N255" s="1">
         <v>46275</v>
@@ -20282,7 +20303,7 @@
         <v>2026</v>
       </c>
       <c r="R255">
-        <v>16975952</v>
+        <v>17948756</v>
       </c>
       <c r="S255" t="s">
         <v>160</v>
@@ -20294,13 +20315,13 @@
         <v>173</v>
       </c>
       <c r="V255" s="1">
-        <v>46275.72031699074</v>
+        <v>46275.71996309028</v>
       </c>
       <c r="W255">
         <v>4</v>
       </c>
       <c r="X255" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AB255">
         <v>0</v>
@@ -20309,24 +20330,24 @@
         <v>160</v>
       </c>
       <c r="AH255" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI255" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="256" spans="1:35">
       <c r="A256">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B256" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C256" t="s">
         <v>50</v>
       </c>
       <c r="D256" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E256" t="s">
         <v>54</v>
@@ -20335,7 +20356,7 @@
         <v>56</v>
       </c>
       <c r="G256">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="H256">
         <v>0</v>
@@ -20344,7 +20365,7 @@
         <v>63</v>
       </c>
       <c r="J256" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N256" s="1">
         <v>46275</v>
@@ -20356,7 +20377,7 @@
         <v>2026</v>
       </c>
       <c r="R256">
-        <v>17948766</v>
+        <v>18085143</v>
       </c>
       <c r="S256" t="s">
         <v>160</v>
@@ -20368,13 +20389,13 @@
         <v>173</v>
       </c>
       <c r="V256" s="1">
-        <v>46275.54095912037</v>
+        <v>46275.54278886574</v>
       </c>
       <c r="W256">
         <v>4</v>
       </c>
       <c r="X256" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="AB256">
         <v>0</v>
@@ -20383,24 +20404,24 @@
         <v>160</v>
       </c>
       <c r="AH256" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI256" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="257" spans="1:35">
       <c r="A257">
-        <v>6704</v>
+        <v>6404</v>
       </c>
       <c r="B257" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C257" t="s">
         <v>50</v>
       </c>
       <c r="D257" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E257" t="s">
         <v>54</v>
@@ -20430,7 +20451,7 @@
         <v>2026</v>
       </c>
       <c r="R257">
-        <v>18085154</v>
+        <v>16962161</v>
       </c>
       <c r="S257" t="s">
         <v>160</v>
@@ -20442,13 +20463,13 @@
         <v>173</v>
       </c>
       <c r="V257" s="1">
-        <v>46275.72225363426</v>
+        <v>46275.7000328588</v>
       </c>
       <c r="W257">
         <v>4</v>
       </c>
       <c r="X257" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="AB257">
         <v>0</v>
@@ -20457,24 +20478,24 @@
         <v>160</v>
       </c>
       <c r="AH257" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI257" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="258" spans="1:35">
       <c r="A258">
-        <v>6705</v>
+        <v>6486</v>
       </c>
       <c r="B258" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C258" t="s">
         <v>50</v>
       </c>
       <c r="D258" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E258" t="s">
         <v>54</v>
@@ -20504,7 +20525,7 @@
         <v>2026</v>
       </c>
       <c r="R258">
-        <v>17948928</v>
+        <v>16975952</v>
       </c>
       <c r="S258" t="s">
         <v>160</v>
@@ -20516,13 +20537,13 @@
         <v>173</v>
       </c>
       <c r="V258" s="1">
-        <v>46275.7222629051</v>
+        <v>46275.72031699074</v>
       </c>
       <c r="W258">
         <v>4</v>
       </c>
       <c r="X258" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AB258">
         <v>0</v>
@@ -20531,24 +20552,24 @@
         <v>160</v>
       </c>
       <c r="AH258" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI258" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="259" spans="1:35">
       <c r="A259">
-        <v>6779</v>
+        <v>6703</v>
       </c>
       <c r="B259" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C259" t="s">
         <v>50</v>
       </c>
       <c r="D259" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E259" t="s">
         <v>54</v>
@@ -20578,7 +20599,7 @@
         <v>2026</v>
       </c>
       <c r="R259">
-        <v>18084955</v>
+        <v>17948766</v>
       </c>
       <c r="S259" t="s">
         <v>160</v>
@@ -20590,13 +20611,13 @@
         <v>173</v>
       </c>
       <c r="V259" s="1">
-        <v>46275.7222709838</v>
+        <v>46275.54095912037</v>
       </c>
       <c r="W259">
         <v>4</v>
       </c>
       <c r="X259" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="AB259">
         <v>0</v>
@@ -20605,18 +20626,18 @@
         <v>160</v>
       </c>
       <c r="AH259" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI259" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="260" spans="1:35">
       <c r="A260">
-        <v>5417</v>
+        <v>6704</v>
       </c>
       <c r="B260" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C260" t="s">
         <v>50</v>
@@ -20631,7 +20652,7 @@
         <v>56</v>
       </c>
       <c r="G260">
-        <v>1796</v>
+        <v>1793</v>
       </c>
       <c r="H260">
         <v>0</v>
@@ -20640,13 +20661,10 @@
         <v>63</v>
       </c>
       <c r="J260" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="N260" s="1">
-        <v>46273</v>
-      </c>
-      <c r="O260" t="s">
-        <v>136</v>
+        <v>46275</v>
       </c>
       <c r="P260">
         <v>8</v>
@@ -20655,7 +20673,7 @@
         <v>2026</v>
       </c>
       <c r="R260">
-        <v>17398955</v>
+        <v>18085154</v>
       </c>
       <c r="S260" t="s">
         <v>160</v>
@@ -20664,19 +20682,16 @@
         <v>170</v>
       </c>
       <c r="U260" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="V260" s="1">
-        <v>46274.74837762731</v>
+        <v>46275.72225363426</v>
       </c>
       <c r="W260">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="X260" t="s">
-        <v>180</v>
-      </c>
-      <c r="Y260" t="s">
-        <v>265</v>
+        <v>179</v>
       </c>
       <c r="AB260">
         <v>0</v>
@@ -20685,24 +20700,24 @@
         <v>160</v>
       </c>
       <c r="AH260" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI260" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="261" spans="1:35">
       <c r="A261">
-        <v>6703</v>
+        <v>6705</v>
       </c>
       <c r="B261" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C261" t="s">
         <v>50</v>
       </c>
       <c r="D261" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E261" t="s">
         <v>54</v>
@@ -20711,7 +20726,7 @@
         <v>56</v>
       </c>
       <c r="G261">
-        <v>1796</v>
+        <v>1793</v>
       </c>
       <c r="H261">
         <v>0</v>
@@ -20720,13 +20735,10 @@
         <v>63</v>
       </c>
       <c r="J261" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="N261" s="1">
-        <v>46273</v>
-      </c>
-      <c r="O261" t="s">
-        <v>136</v>
+        <v>46275</v>
       </c>
       <c r="P261">
         <v>8</v>
@@ -20735,7 +20747,7 @@
         <v>2026</v>
       </c>
       <c r="R261">
-        <v>18073098</v>
+        <v>17948928</v>
       </c>
       <c r="S261" t="s">
         <v>160</v>
@@ -20744,19 +20756,16 @@
         <v>170</v>
       </c>
       <c r="U261" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="V261" s="1">
-        <v>46274.74838096065</v>
+        <v>46275.7222629051</v>
       </c>
       <c r="W261">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="X261" t="s">
-        <v>183</v>
-      </c>
-      <c r="Y261" t="s">
-        <v>265</v>
+        <v>179</v>
       </c>
       <c r="AB261">
         <v>0</v>
@@ -20765,24 +20774,24 @@
         <v>160</v>
       </c>
       <c r="AH261" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI261" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="262" spans="1:35">
       <c r="A262">
-        <v>5417</v>
+        <v>6779</v>
       </c>
       <c r="B262" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C262" t="s">
         <v>50</v>
       </c>
       <c r="D262" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E262" t="s">
         <v>54</v>
@@ -20791,7 +20800,7 @@
         <v>56</v>
       </c>
       <c r="G262">
-        <v>11303</v>
+        <v>1793</v>
       </c>
       <c r="H262">
         <v>0</v>
@@ -20800,10 +20809,10 @@
         <v>63</v>
       </c>
       <c r="J262" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="N262" s="1">
-        <v>46279</v>
+        <v>46275</v>
       </c>
       <c r="P262">
         <v>8</v>
@@ -20812,7 +20821,7 @@
         <v>2026</v>
       </c>
       <c r="R262">
-        <v>17399454</v>
+        <v>18084955</v>
       </c>
       <c r="S262" t="s">
         <v>160</v>
@@ -20821,19 +20830,16 @@
         <v>170</v>
       </c>
       <c r="U262" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="V262" s="1">
-        <v>46274.42878043981</v>
+        <v>46275.7222709838</v>
       </c>
       <c r="W262">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X262" t="s">
-        <v>180</v>
-      </c>
-      <c r="Y262" t="s">
-        <v>266</v>
+        <v>179</v>
       </c>
       <c r="AB262">
         <v>0</v>
@@ -20842,18 +20848,18 @@
         <v>160</v>
       </c>
       <c r="AH262" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AI262" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="263" spans="1:35">
       <c r="A263">
-        <v>6486</v>
+        <v>5417</v>
       </c>
       <c r="B263" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C263" t="s">
         <v>50</v>
@@ -20868,7 +20874,7 @@
         <v>56</v>
       </c>
       <c r="G263">
-        <v>11303</v>
+        <v>1796</v>
       </c>
       <c r="H263">
         <v>0</v>
@@ -20877,10 +20883,13 @@
         <v>63</v>
       </c>
       <c r="J263" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="N263" s="1">
-        <v>46279</v>
+        <v>46273</v>
+      </c>
+      <c r="O263" t="s">
+        <v>136</v>
       </c>
       <c r="P263">
         <v>8</v>
@@ -20889,7 +20898,7 @@
         <v>2026</v>
       </c>
       <c r="R263">
-        <v>16976351</v>
+        <v>17398955</v>
       </c>
       <c r="S263" t="s">
         <v>160</v>
@@ -20898,19 +20907,19 @@
         <v>170</v>
       </c>
       <c r="U263" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="V263" s="1">
-        <v>46275.40196778935</v>
+        <v>46274.74837762731</v>
       </c>
       <c r="W263">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X263" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y263" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AB263">
         <v>0</v>
@@ -20919,10 +20928,10 @@
         <v>160</v>
       </c>
       <c r="AH263" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI263" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="264" spans="1:35">
@@ -20945,22 +20954,22 @@
         <v>56</v>
       </c>
       <c r="G264">
-        <v>950</v>
+        <v>1796</v>
       </c>
       <c r="H264">
         <v>0</v>
       </c>
       <c r="I264" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J264" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N264" s="1">
-        <v>46275</v>
+        <v>46273</v>
       </c>
       <c r="O264" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="P264">
         <v>8</v>
@@ -20969,45 +20978,48 @@
         <v>2026</v>
       </c>
       <c r="R264">
-        <v>17941146</v>
+        <v>18073098</v>
       </c>
       <c r="S264" t="s">
-        <v>161</v>
+        <v>160</v>
+      </c>
+      <c r="T264" t="s">
+        <v>170</v>
       </c>
       <c r="U264" t="s">
         <v>171</v>
       </c>
       <c r="V264" s="1">
-        <v>46276.52399603009</v>
+        <v>46274.74838096065</v>
       </c>
       <c r="W264">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="X264" t="s">
         <v>183</v>
       </c>
       <c r="Y264" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="AB264">
         <v>0</v>
       </c>
       <c r="AC264" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AH264" t="s">
         <v>290</v>
       </c>
       <c r="AI264" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="265" spans="1:35">
       <c r="A265">
-        <v>6704</v>
+        <v>5417</v>
       </c>
       <c r="B265" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C265" t="s">
         <v>50</v>
@@ -21022,22 +21034,19 @@
         <v>56</v>
       </c>
       <c r="G265">
-        <v>950</v>
+        <v>11303</v>
       </c>
       <c r="H265">
         <v>0</v>
       </c>
       <c r="I265" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J265" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="N265" s="1">
-        <v>46275</v>
-      </c>
-      <c r="O265" t="s">
-        <v>137</v>
+        <v>46279</v>
       </c>
       <c r="P265">
         <v>8</v>
@@ -21046,45 +21055,48 @@
         <v>2026</v>
       </c>
       <c r="R265">
-        <v>17952340</v>
+        <v>17399454</v>
       </c>
       <c r="S265" t="s">
-        <v>161</v>
+        <v>160</v>
+      </c>
+      <c r="T265" t="s">
+        <v>170</v>
       </c>
       <c r="U265" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="V265" s="1">
-        <v>46276.5240703125</v>
+        <v>46274.42878043981</v>
       </c>
       <c r="W265">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X265" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y265" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="AB265">
         <v>0</v>
       </c>
       <c r="AC265" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AH265" t="s">
         <v>290</v>
       </c>
       <c r="AI265" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="266" spans="1:35">
       <c r="A266">
-        <v>6949</v>
+        <v>6486</v>
       </c>
       <c r="B266" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C266" t="s">
         <v>50</v>
@@ -21096,22 +21108,22 @@
         <v>54</v>
       </c>
       <c r="F266" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G266">
-        <v>950</v>
+        <v>11303</v>
       </c>
       <c r="H266">
         <v>0</v>
       </c>
       <c r="I266" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J266" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="N266" s="1">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="P266">
         <v>8</v>
@@ -21120,45 +21132,48 @@
         <v>2026</v>
       </c>
       <c r="R266">
-        <v>18178132</v>
+        <v>16976351</v>
       </c>
       <c r="S266" t="s">
-        <v>161</v>
+        <v>160</v>
+      </c>
+      <c r="T266" t="s">
+        <v>170</v>
       </c>
       <c r="U266" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="V266" s="1">
-        <v>46275.4100730787</v>
+        <v>46275.40196778935</v>
       </c>
       <c r="W266">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X266" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="Y266" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="AB266">
         <v>0</v>
       </c>
       <c r="AC266" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AH266" t="s">
         <v>290</v>
       </c>
       <c r="AI266" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="267" spans="1:35">
       <c r="A267">
-        <v>6962</v>
+        <v>6703</v>
       </c>
       <c r="B267" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C267" t="s">
         <v>50</v>
@@ -21170,7 +21185,7 @@
         <v>54</v>
       </c>
       <c r="F267" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G267">
         <v>950</v>
@@ -21187,6 +21202,9 @@
       <c r="N267" s="1">
         <v>46275</v>
       </c>
+      <c r="O267" t="s">
+        <v>137</v>
+      </c>
       <c r="P267">
         <v>8</v>
       </c>
@@ -21194,25 +21212,25 @@
         <v>2026</v>
       </c>
       <c r="R267">
-        <v>18188717</v>
+        <v>17941146</v>
       </c>
       <c r="S267" t="s">
         <v>161</v>
       </c>
       <c r="U267" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="V267" s="1">
-        <v>46275.40964188657</v>
+        <v>46276.52399603009</v>
       </c>
       <c r="W267">
         <v>4</v>
       </c>
       <c r="X267" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="Y267" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AB267">
         <v>0</v>
@@ -21221,30 +21239,30 @@
         <v>161</v>
       </c>
       <c r="AH267" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI267" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="268" spans="1:35">
       <c r="A268">
-        <v>6963</v>
+        <v>6704</v>
       </c>
       <c r="B268" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C268" t="s">
         <v>50</v>
       </c>
       <c r="D268" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E268" t="s">
         <v>54</v>
       </c>
       <c r="F268" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G268">
         <v>950</v>
@@ -21261,6 +21279,9 @@
       <c r="N268" s="1">
         <v>46275</v>
       </c>
+      <c r="O268" t="s">
+        <v>137</v>
+      </c>
       <c r="P268">
         <v>8</v>
       </c>
@@ -21268,25 +21289,25 @@
         <v>2026</v>
       </c>
       <c r="R268">
-        <v>18188623</v>
+        <v>17952340</v>
       </c>
       <c r="S268" t="s">
         <v>161</v>
       </c>
       <c r="U268" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="V268" s="1">
-        <v>46275.40964245371</v>
+        <v>46276.5240703125</v>
       </c>
       <c r="W268">
         <v>4</v>
       </c>
       <c r="X268" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Y268" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="AB268">
         <v>0</v>
@@ -21295,18 +21316,18 @@
         <v>161</v>
       </c>
       <c r="AH268" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI268" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="269" spans="1:35">
       <c r="A269">
-        <v>6548</v>
+        <v>6949</v>
       </c>
       <c r="B269" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C269" t="s">
         <v>50</v>
@@ -21318,10 +21339,10 @@
         <v>54</v>
       </c>
       <c r="F269" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G269">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H269">
         <v>0</v>
@@ -21330,7 +21351,7 @@
         <v>64</v>
       </c>
       <c r="J269" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N269" s="1">
         <v>46275</v>
@@ -21342,7 +21363,7 @@
         <v>2026</v>
       </c>
       <c r="R269">
-        <v>17222405</v>
+        <v>18178132</v>
       </c>
       <c r="S269" t="s">
         <v>161</v>
@@ -21351,16 +21372,16 @@
         <v>173</v>
       </c>
       <c r="V269" s="1">
-        <v>46275.45011145833</v>
+        <v>46275.4100730787</v>
       </c>
       <c r="W269">
         <v>4</v>
       </c>
       <c r="X269" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Y269" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="AB269">
         <v>0</v>
@@ -21369,33 +21390,33 @@
         <v>161</v>
       </c>
       <c r="AH269" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI269" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="270" spans="1:35">
       <c r="A270">
-        <v>6628</v>
+        <v>6962</v>
       </c>
       <c r="B270" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C270" t="s">
         <v>50</v>
       </c>
       <c r="D270" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E270" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F270" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G270">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H270">
         <v>0</v>
@@ -21404,7 +21425,7 @@
         <v>64</v>
       </c>
       <c r="J270" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N270" s="1">
         <v>46275</v>
@@ -21416,7 +21437,7 @@
         <v>2026</v>
       </c>
       <c r="R270">
-        <v>16959950</v>
+        <v>18188717</v>
       </c>
       <c r="S270" t="s">
         <v>161</v>
@@ -21425,13 +21446,16 @@
         <v>173</v>
       </c>
       <c r="V270" s="1">
-        <v>46275.44901016204</v>
+        <v>46275.40964188657</v>
       </c>
       <c r="W270">
         <v>4</v>
       </c>
       <c r="X270" t="s">
-        <v>175</v>
+        <v>178</v>
+      </c>
+      <c r="Y270" t="s">
+        <v>272</v>
       </c>
       <c r="AB270">
         <v>0</v>
@@ -21440,18 +21464,18 @@
         <v>161</v>
       </c>
       <c r="AH270" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI270" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="271" spans="1:35">
       <c r="A271">
-        <v>6703</v>
+        <v>6963</v>
       </c>
       <c r="B271" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C271" t="s">
         <v>50</v>
@@ -21463,10 +21487,10 @@
         <v>54</v>
       </c>
       <c r="F271" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G271">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H271">
         <v>0</v>
@@ -21475,14 +21499,11 @@
         <v>64</v>
       </c>
       <c r="J271" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N271" s="1">
         <v>46275</v>
       </c>
-      <c r="O271" t="s">
-        <v>138</v>
-      </c>
       <c r="P271">
         <v>8</v>
       </c>
@@ -21490,25 +21511,25 @@
         <v>2026</v>
       </c>
       <c r="R271">
-        <v>17941156</v>
+        <v>18188623</v>
       </c>
       <c r="S271" t="s">
         <v>161</v>
       </c>
       <c r="U271" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="V271" s="1">
-        <v>46276.71732053241</v>
+        <v>46275.40964245371</v>
       </c>
       <c r="W271">
         <v>4</v>
       </c>
       <c r="X271" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="Y271" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AB271">
         <v>0</v>
@@ -21517,18 +21538,18 @@
         <v>161</v>
       </c>
       <c r="AH271" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI271" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="272" spans="1:35">
       <c r="A272">
-        <v>6704</v>
+        <v>6548</v>
       </c>
       <c r="B272" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C272" t="s">
         <v>50</v>
@@ -21557,9 +21578,6 @@
       <c r="N272" s="1">
         <v>46275</v>
       </c>
-      <c r="O272" t="s">
-        <v>138</v>
-      </c>
       <c r="P272">
         <v>8</v>
       </c>
@@ -21567,25 +21585,25 @@
         <v>2026</v>
       </c>
       <c r="R272">
-        <v>17952351</v>
+        <v>17222405</v>
       </c>
       <c r="S272" t="s">
         <v>161</v>
       </c>
       <c r="U272" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="V272" s="1">
-        <v>46276.71697232639</v>
+        <v>46275.45011145833</v>
       </c>
       <c r="W272">
         <v>4</v>
       </c>
       <c r="X272" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="Y272" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AB272">
         <v>0</v>
@@ -21594,18 +21612,18 @@
         <v>161</v>
       </c>
       <c r="AH272" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI272" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="273" spans="1:35">
       <c r="A273">
-        <v>6705</v>
+        <v>6628</v>
       </c>
       <c r="B273" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C273" t="s">
         <v>50</v>
@@ -21614,7 +21632,7 @@
         <v>52</v>
       </c>
       <c r="E273" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F273" t="s">
         <v>56</v>
@@ -21634,9 +21652,6 @@
       <c r="N273" s="1">
         <v>46275</v>
       </c>
-      <c r="O273" t="s">
-        <v>138</v>
-      </c>
       <c r="P273">
         <v>8</v>
       </c>
@@ -21644,25 +21659,22 @@
         <v>2026</v>
       </c>
       <c r="R273">
-        <v>17952535</v>
+        <v>16959950</v>
       </c>
       <c r="S273" t="s">
         <v>161</v>
       </c>
       <c r="U273" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="V273" s="1">
-        <v>46276.7175884838</v>
+        <v>46275.44901016204</v>
       </c>
       <c r="W273">
         <v>4</v>
       </c>
       <c r="X273" t="s">
-        <v>179</v>
-      </c>
-      <c r="Y273" t="s">
-        <v>276</v>
+        <v>175</v>
       </c>
       <c r="AB273">
         <v>0</v>
@@ -21671,24 +21683,24 @@
         <v>161</v>
       </c>
       <c r="AH273" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI273" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="274" spans="1:35">
       <c r="A274">
-        <v>6779</v>
+        <v>6703</v>
       </c>
       <c r="B274" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C274" t="s">
         <v>50</v>
       </c>
       <c r="D274" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E274" t="s">
         <v>54</v>
@@ -21721,7 +21733,7 @@
         <v>2026</v>
       </c>
       <c r="R274">
-        <v>18056705</v>
+        <v>17941156</v>
       </c>
       <c r="S274" t="s">
         <v>161</v>
@@ -21730,16 +21742,16 @@
         <v>171</v>
       </c>
       <c r="V274" s="1">
-        <v>46276.7175895949</v>
+        <v>46276.71732053241</v>
       </c>
       <c r="W274">
         <v>4</v>
       </c>
       <c r="X274" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="Y274" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AB274">
         <v>0</v>
@@ -21748,30 +21760,30 @@
         <v>161</v>
       </c>
       <c r="AH274" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI274" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="275" spans="1:35">
       <c r="A275">
-        <v>6945</v>
+        <v>6704</v>
       </c>
       <c r="B275" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C275" t="s">
         <v>50</v>
       </c>
       <c r="D275" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E275" t="s">
         <v>54</v>
       </c>
       <c r="F275" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G275">
         <v>951</v>
@@ -21798,7 +21810,7 @@
         <v>2026</v>
       </c>
       <c r="R275">
-        <v>18164501</v>
+        <v>17952351</v>
       </c>
       <c r="S275" t="s">
         <v>161</v>
@@ -21807,16 +21819,16 @@
         <v>171</v>
       </c>
       <c r="V275" s="1">
-        <v>46276.71759461806</v>
+        <v>46276.71697232639</v>
       </c>
       <c r="W275">
         <v>4</v>
       </c>
       <c r="X275" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Y275" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AB275">
         <v>0</v>
@@ -21825,30 +21837,30 @@
         <v>161</v>
       </c>
       <c r="AH275" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI275" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="276" spans="1:35">
       <c r="A276">
-        <v>6949</v>
+        <v>6705</v>
       </c>
       <c r="B276" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C276" t="s">
         <v>50</v>
       </c>
       <c r="D276" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E276" t="s">
         <v>54</v>
       </c>
       <c r="F276" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G276">
         <v>951</v>
@@ -21865,6 +21877,9 @@
       <c r="N276" s="1">
         <v>46275</v>
       </c>
+      <c r="O276" t="s">
+        <v>138</v>
+      </c>
       <c r="P276">
         <v>8</v>
       </c>
@@ -21872,25 +21887,25 @@
         <v>2026</v>
       </c>
       <c r="R276">
-        <v>18178138</v>
+        <v>17952535</v>
       </c>
       <c r="S276" t="s">
         <v>161</v>
       </c>
       <c r="U276" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="V276" s="1">
-        <v>46275.44975668981</v>
+        <v>46276.7175884838</v>
       </c>
       <c r="W276">
         <v>4</v>
       </c>
       <c r="X276" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="Y276" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="AB276">
         <v>0</v>
@@ -21899,30 +21914,30 @@
         <v>161</v>
       </c>
       <c r="AH276" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI276" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="277" spans="1:35">
       <c r="A277">
-        <v>6962</v>
+        <v>6779</v>
       </c>
       <c r="B277" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C277" t="s">
         <v>50</v>
       </c>
       <c r="D277" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E277" t="s">
         <v>54</v>
       </c>
       <c r="F277" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G277">
         <v>951</v>
@@ -21939,6 +21954,9 @@
       <c r="N277" s="1">
         <v>46275</v>
       </c>
+      <c r="O277" t="s">
+        <v>138</v>
+      </c>
       <c r="P277">
         <v>8</v>
       </c>
@@ -21946,25 +21964,25 @@
         <v>2026</v>
       </c>
       <c r="R277">
-        <v>18188724</v>
+        <v>18056705</v>
       </c>
       <c r="S277" t="s">
         <v>161</v>
       </c>
       <c r="U277" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="V277" s="1">
-        <v>46275.44933692129</v>
+        <v>46276.7175895949</v>
       </c>
       <c r="W277">
         <v>4</v>
       </c>
       <c r="X277" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Y277" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="AB277">
         <v>0</v>
@@ -21973,24 +21991,24 @@
         <v>161</v>
       </c>
       <c r="AH277" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI277" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="278" spans="1:35">
       <c r="A278">
-        <v>6963</v>
+        <v>6945</v>
       </c>
       <c r="B278" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C278" t="s">
         <v>50</v>
       </c>
       <c r="D278" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E278" t="s">
         <v>54</v>
@@ -22013,6 +22031,9 @@
       <c r="N278" s="1">
         <v>46275</v>
       </c>
+      <c r="O278" t="s">
+        <v>138</v>
+      </c>
       <c r="P278">
         <v>8</v>
       </c>
@@ -22020,25 +22041,25 @@
         <v>2026</v>
       </c>
       <c r="R278">
-        <v>18188630</v>
+        <v>18164501</v>
       </c>
       <c r="S278" t="s">
         <v>161</v>
       </c>
       <c r="U278" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="V278" s="1">
-        <v>46275.44933814815</v>
+        <v>46276.71759461806</v>
       </c>
       <c r="W278">
         <v>4</v>
       </c>
       <c r="X278" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y278" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="AB278">
         <v>0</v>
@@ -22047,33 +22068,33 @@
         <v>161</v>
       </c>
       <c r="AH278" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AI278" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="279" spans="1:35">
       <c r="A279">
-        <v>6703</v>
+        <v>6949</v>
       </c>
       <c r="B279" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C279" t="s">
         <v>50</v>
       </c>
       <c r="D279" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E279" t="s">
         <v>54</v>
       </c>
       <c r="F279" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G279">
-        <v>5989</v>
+        <v>951</v>
       </c>
       <c r="H279">
         <v>0</v>
@@ -22082,34 +22103,37 @@
         <v>64</v>
       </c>
       <c r="J279" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="N279" s="1">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="P279">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q279">
         <v>2026</v>
       </c>
       <c r="R279">
-        <v>17941177</v>
+        <v>18178138</v>
       </c>
       <c r="S279" t="s">
         <v>161</v>
       </c>
       <c r="U279" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="V279" s="1">
-        <v>46274.41771849537</v>
+        <v>46275.44975668981</v>
       </c>
       <c r="W279">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="X279" t="s">
-        <v>183</v>
+        <v>176</v>
+      </c>
+      <c r="Y279" t="s">
+        <v>280</v>
       </c>
       <c r="AB279">
         <v>0</v>
@@ -22121,30 +22145,30 @@
         <v>291</v>
       </c>
       <c r="AI279" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="280" spans="1:35">
       <c r="A280">
-        <v>6704</v>
+        <v>6962</v>
       </c>
       <c r="B280" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C280" t="s">
         <v>50</v>
       </c>
       <c r="D280" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E280" t="s">
         <v>54</v>
       </c>
       <c r="F280" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G280">
-        <v>5989</v>
+        <v>951</v>
       </c>
       <c r="H280">
         <v>0</v>
@@ -22153,34 +22177,37 @@
         <v>64</v>
       </c>
       <c r="J280" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="N280" s="1">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="P280">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q280">
         <v>2026</v>
       </c>
       <c r="R280">
-        <v>17952385</v>
+        <v>18188724</v>
       </c>
       <c r="S280" t="s">
         <v>161</v>
       </c>
       <c r="U280" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="V280" s="1">
-        <v>46274.41775447917</v>
+        <v>46275.44933692129</v>
       </c>
       <c r="W280">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="X280" t="s">
-        <v>179</v>
+        <v>178</v>
+      </c>
+      <c r="Y280" t="s">
+        <v>281</v>
       </c>
       <c r="AB280">
         <v>0</v>
@@ -22192,30 +22219,30 @@
         <v>291</v>
       </c>
       <c r="AI280" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="281" spans="1:35">
       <c r="A281">
-        <v>6705</v>
+        <v>6963</v>
       </c>
       <c r="B281" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C281" t="s">
         <v>50</v>
       </c>
       <c r="D281" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E281" t="s">
         <v>54</v>
       </c>
       <c r="F281" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G281">
-        <v>5989</v>
+        <v>951</v>
       </c>
       <c r="H281">
         <v>0</v>
@@ -22224,34 +22251,37 @@
         <v>64</v>
       </c>
       <c r="J281" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="N281" s="1">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="P281">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q281">
         <v>2026</v>
       </c>
       <c r="R281">
-        <v>17952569</v>
+        <v>18188630</v>
       </c>
       <c r="S281" t="s">
         <v>161</v>
       </c>
       <c r="U281" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="V281" s="1">
-        <v>46274.41777533565</v>
+        <v>46275.44933814815</v>
       </c>
       <c r="W281">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="X281" t="s">
-        <v>179</v>
+        <v>178</v>
+      </c>
+      <c r="Y281" t="s">
+        <v>282</v>
       </c>
       <c r="AB281">
         <v>0</v>
@@ -22263,27 +22293,27 @@
         <v>291</v>
       </c>
       <c r="AI281" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="282" spans="1:35">
       <c r="A282">
-        <v>6945</v>
+        <v>6703</v>
       </c>
       <c r="B282" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C282" t="s">
         <v>50</v>
       </c>
       <c r="D282" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E282" t="s">
         <v>54</v>
       </c>
       <c r="F282" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G282">
         <v>5989</v>
@@ -22307,7 +22337,7 @@
         <v>2026</v>
       </c>
       <c r="R282">
-        <v>18164516</v>
+        <v>17941177</v>
       </c>
       <c r="S282" t="s">
         <v>161</v>
@@ -22316,13 +22346,13 @@
         <v>171</v>
       </c>
       <c r="V282" s="1">
-        <v>46274.41799166667</v>
+        <v>46274.41771849537</v>
       </c>
       <c r="W282">
         <v>6</v>
       </c>
       <c r="X282" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="AB282">
         <v>0</v>
@@ -22331,18 +22361,18 @@
         <v>161</v>
       </c>
       <c r="AH282" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI282" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="283" spans="1:35">
       <c r="A283">
-        <v>6949</v>
+        <v>6704</v>
       </c>
       <c r="B283" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C283" t="s">
         <v>50</v>
@@ -22354,7 +22384,7 @@
         <v>54</v>
       </c>
       <c r="F283" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G283">
         <v>5989</v>
@@ -22378,7 +22408,7 @@
         <v>2026</v>
       </c>
       <c r="R283">
-        <v>18178157</v>
+        <v>17952385</v>
       </c>
       <c r="S283" t="s">
         <v>161</v>
@@ -22387,13 +22417,13 @@
         <v>171</v>
       </c>
       <c r="V283" s="1">
-        <v>46274.41800114583</v>
+        <v>46274.41775447917</v>
       </c>
       <c r="W283">
         <v>6</v>
       </c>
       <c r="X283" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="AB283">
         <v>0</v>
@@ -22402,24 +22432,24 @@
         <v>161</v>
       </c>
       <c r="AH283" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI283" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="284" spans="1:35">
       <c r="A284">
-        <v>6703</v>
+        <v>6705</v>
       </c>
       <c r="B284" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C284" t="s">
         <v>50</v>
       </c>
       <c r="D284" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E284" t="s">
         <v>54</v>
@@ -22428,19 +22458,19 @@
         <v>56</v>
       </c>
       <c r="G284">
-        <v>6215</v>
+        <v>5989</v>
       </c>
       <c r="H284">
         <v>0</v>
       </c>
       <c r="I284" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J284" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="N284" s="1">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="P284">
         <v>9</v>
@@ -22449,69 +22479,69 @@
         <v>2026</v>
       </c>
       <c r="R284">
-        <v>17941187</v>
+        <v>17952569</v>
       </c>
       <c r="S284" t="s">
-        <v>54</v>
+        <v>161</v>
       </c>
       <c r="U284" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="V284" s="1">
-        <v>46274.41772148148</v>
+        <v>46274.41777533565</v>
       </c>
       <c r="W284">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X284" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="AB284">
         <v>0</v>
       </c>
       <c r="AC284" t="s">
-        <v>54</v>
+        <v>161</v>
       </c>
       <c r="AH284" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI284" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="285" spans="1:35">
       <c r="A285">
-        <v>6704</v>
+        <v>6945</v>
       </c>
       <c r="B285" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C285" t="s">
         <v>50</v>
       </c>
       <c r="D285" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E285" t="s">
         <v>54</v>
       </c>
       <c r="F285" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G285">
-        <v>6215</v>
+        <v>5989</v>
       </c>
       <c r="H285">
         <v>0</v>
       </c>
       <c r="I285" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J285" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="N285" s="1">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="P285">
         <v>9</v>
@@ -22520,69 +22550,69 @@
         <v>2026</v>
       </c>
       <c r="R285">
-        <v>17952400</v>
+        <v>18164516</v>
       </c>
       <c r="S285" t="s">
-        <v>54</v>
+        <v>161</v>
       </c>
       <c r="U285" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="V285" s="1">
-        <v>46274.41773631945</v>
+        <v>46274.41799166667</v>
       </c>
       <c r="W285">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X285" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="AB285">
         <v>0</v>
       </c>
       <c r="AC285" t="s">
-        <v>54</v>
+        <v>161</v>
       </c>
       <c r="AH285" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI285" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="286" spans="1:35">
       <c r="A286">
-        <v>6705</v>
+        <v>6949</v>
       </c>
       <c r="B286" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="C286" t="s">
         <v>50</v>
       </c>
       <c r="D286" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E286" t="s">
         <v>54</v>
       </c>
       <c r="F286" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G286">
-        <v>6215</v>
+        <v>5989</v>
       </c>
       <c r="H286">
         <v>0</v>
       </c>
       <c r="I286" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J286" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="N286" s="1">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="P286">
         <v>9</v>
@@ -22591,54 +22621,54 @@
         <v>2026</v>
       </c>
       <c r="R286">
-        <v>17952580</v>
+        <v>18178157</v>
       </c>
       <c r="S286" t="s">
-        <v>54</v>
+        <v>161</v>
       </c>
       <c r="U286" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="V286" s="1">
-        <v>46274.41777481481</v>
+        <v>46274.41800114583</v>
       </c>
       <c r="W286">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X286" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="AB286">
         <v>0</v>
       </c>
       <c r="AC286" t="s">
-        <v>54</v>
+        <v>161</v>
       </c>
       <c r="AH286" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI286" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="287" spans="1:35">
       <c r="A287">
-        <v>6945</v>
+        <v>6703</v>
       </c>
       <c r="B287" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C287" t="s">
         <v>50</v>
       </c>
       <c r="D287" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E287" t="s">
         <v>54</v>
       </c>
       <c r="F287" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G287">
         <v>6215</v>
@@ -22662,7 +22692,7 @@
         <v>2026</v>
       </c>
       <c r="R287">
-        <v>18164523</v>
+        <v>17941187</v>
       </c>
       <c r="S287" t="s">
         <v>54</v>
@@ -22671,13 +22701,13 @@
         <v>173</v>
       </c>
       <c r="V287" s="1">
-        <v>46274.41799332176</v>
+        <v>46274.41772148148</v>
       </c>
       <c r="W287">
         <v>5</v>
       </c>
       <c r="X287" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="AB287">
         <v>0</v>
@@ -22686,18 +22716,18 @@
         <v>54</v>
       </c>
       <c r="AH287" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI287" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="288" spans="1:35">
       <c r="A288">
-        <v>6949</v>
+        <v>6704</v>
       </c>
       <c r="B288" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C288" t="s">
         <v>50</v>
@@ -22709,7 +22739,7 @@
         <v>54</v>
       </c>
       <c r="F288" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G288">
         <v>6215</v>
@@ -22733,48 +22763,48 @@
         <v>2026</v>
       </c>
       <c r="R288">
-        <v>18178163</v>
+        <v>17952400</v>
       </c>
       <c r="S288" t="s">
-        <v>162</v>
+        <v>54</v>
       </c>
       <c r="U288" t="s">
         <v>173</v>
       </c>
       <c r="V288" s="1">
-        <v>46274.41800085648</v>
+        <v>46274.41773631945</v>
       </c>
       <c r="W288">
         <v>5</v>
       </c>
       <c r="X288" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="AB288">
         <v>0</v>
       </c>
       <c r="AC288" t="s">
-        <v>162</v>
+        <v>54</v>
       </c>
       <c r="AH288" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AI288" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="289" spans="1:35">
       <c r="A289">
-        <v>5417</v>
+        <v>6705</v>
       </c>
       <c r="B289" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C289" t="s">
         <v>50</v>
       </c>
       <c r="D289" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E289" t="s">
         <v>54</v>
@@ -22783,7 +22813,7 @@
         <v>56</v>
       </c>
       <c r="G289">
-        <v>11746</v>
+        <v>6215</v>
       </c>
       <c r="H289">
         <v>0</v>
@@ -22792,19 +22822,19 @@
         <v>65</v>
       </c>
       <c r="J289" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="N289" s="1">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="P289">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q289">
         <v>2026</v>
       </c>
       <c r="R289">
-        <v>17994311</v>
+        <v>17952580</v>
       </c>
       <c r="S289" t="s">
         <v>54</v>
@@ -22813,48 +22843,48 @@
         <v>173</v>
       </c>
       <c r="V289" s="1">
-        <v>46275.31737530093</v>
+        <v>46274.41777481481</v>
       </c>
       <c r="W289">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X289" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AB289">
         <v>0</v>
       </c>
       <c r="AC289" t="s">
-        <v>162</v>
+        <v>54</v>
       </c>
       <c r="AH289" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="AI289" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="290" spans="1:35">
       <c r="A290">
-        <v>6404</v>
+        <v>6945</v>
       </c>
       <c r="B290" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C290" t="s">
         <v>50</v>
       </c>
       <c r="D290" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E290" t="s">
         <v>54</v>
       </c>
       <c r="F290" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G290">
-        <v>11746</v>
+        <v>6215</v>
       </c>
       <c r="H290">
         <v>0</v>
@@ -22863,19 +22893,19 @@
         <v>65</v>
       </c>
       <c r="J290" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="N290" s="1">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="P290">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q290">
         <v>2026</v>
       </c>
       <c r="R290">
-        <v>17994675</v>
+        <v>18164523</v>
       </c>
       <c r="S290" t="s">
         <v>54</v>
@@ -22884,33 +22914,33 @@
         <v>173</v>
       </c>
       <c r="V290" s="1">
-        <v>46275.31747032407</v>
+        <v>46274.41799332176</v>
       </c>
       <c r="W290">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X290" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="AB290">
         <v>0</v>
       </c>
       <c r="AC290" t="s">
-        <v>162</v>
+        <v>54</v>
       </c>
       <c r="AH290" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="AI290" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="291" spans="1:35">
       <c r="A291">
-        <v>6486</v>
+        <v>6949</v>
       </c>
       <c r="B291" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C291" t="s">
         <v>50</v>
@@ -22922,10 +22952,10 @@
         <v>54</v>
       </c>
       <c r="F291" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G291">
-        <v>11746</v>
+        <v>6215</v>
       </c>
       <c r="H291">
         <v>0</v>
@@ -22934,34 +22964,34 @@
         <v>65</v>
       </c>
       <c r="J291" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="N291" s="1">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="P291">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q291">
         <v>2026</v>
       </c>
       <c r="R291">
-        <v>17994809</v>
+        <v>18178163</v>
       </c>
       <c r="S291" t="s">
-        <v>54</v>
+        <v>162</v>
       </c>
       <c r="U291" t="s">
         <v>173</v>
       </c>
       <c r="V291" s="1">
-        <v>46275.31747981482</v>
+        <v>46274.41800085648</v>
       </c>
       <c r="W291">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X291" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="AB291">
         <v>0</v>
@@ -22970,18 +23000,18 @@
         <v>162</v>
       </c>
       <c r="AH291" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="AI291" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="292" spans="1:35">
       <c r="A292">
-        <v>6548</v>
+        <v>5417</v>
       </c>
       <c r="B292" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C292" t="s">
         <v>50</v>
@@ -23017,7 +23047,7 @@
         <v>2026</v>
       </c>
       <c r="R292">
-        <v>18006051</v>
+        <v>17994311</v>
       </c>
       <c r="S292" t="s">
         <v>54</v>
@@ -23026,13 +23056,13 @@
         <v>173</v>
       </c>
       <c r="V292" s="1">
-        <v>46275.31748724537</v>
+        <v>46275.31737530093</v>
       </c>
       <c r="W292">
         <v>4</v>
       </c>
       <c r="X292" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="AB292">
         <v>0</v>
@@ -23041,27 +23071,27 @@
         <v>162</v>
       </c>
       <c r="AH292" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI292" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="293" spans="1:35">
       <c r="A293">
-        <v>6628</v>
+        <v>6404</v>
       </c>
       <c r="B293" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C293" t="s">
         <v>50</v>
       </c>
       <c r="D293" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E293" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F293" t="s">
         <v>56</v>
@@ -23088,22 +23118,22 @@
         <v>2026</v>
       </c>
       <c r="R293">
-        <v>18003256</v>
+        <v>17994675</v>
       </c>
       <c r="S293" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="U293" t="s">
         <v>173</v>
       </c>
       <c r="V293" s="1">
-        <v>46275.31749535879</v>
+        <v>46275.31747032407</v>
       </c>
       <c r="W293">
         <v>4</v>
       </c>
       <c r="X293" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="AB293">
         <v>0</v>
@@ -23112,24 +23142,24 @@
         <v>162</v>
       </c>
       <c r="AH293" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI293" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="294" spans="1:35">
       <c r="A294">
-        <v>6703</v>
+        <v>6486</v>
       </c>
       <c r="B294" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C294" t="s">
         <v>50</v>
       </c>
       <c r="D294" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E294" t="s">
         <v>54</v>
@@ -23159,7 +23189,7 @@
         <v>2026</v>
       </c>
       <c r="R294">
-        <v>18004017</v>
+        <v>17994809</v>
       </c>
       <c r="S294" t="s">
         <v>54</v>
@@ -23168,13 +23198,13 @@
         <v>173</v>
       </c>
       <c r="V294" s="1">
-        <v>46275.31750491898</v>
+        <v>46275.31747981482</v>
       </c>
       <c r="W294">
         <v>4</v>
       </c>
       <c r="X294" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="AB294">
         <v>0</v>
@@ -23183,18 +23213,18 @@
         <v>162</v>
       </c>
       <c r="AH294" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI294" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="295" spans="1:35">
       <c r="A295">
-        <v>6704</v>
+        <v>6548</v>
       </c>
       <c r="B295" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C295" t="s">
         <v>50</v>
@@ -23230,7 +23260,7 @@
         <v>2026</v>
       </c>
       <c r="R295">
-        <v>17995164</v>
+        <v>18006051</v>
       </c>
       <c r="S295" t="s">
         <v>54</v>
@@ -23239,13 +23269,13 @@
         <v>173</v>
       </c>
       <c r="V295" s="1">
-        <v>46275.31750555555</v>
+        <v>46275.31748724537</v>
       </c>
       <c r="W295">
         <v>4</v>
       </c>
       <c r="X295" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="AB295">
         <v>0</v>
@@ -23254,18 +23284,18 @@
         <v>162</v>
       </c>
       <c r="AH295" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI295" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="296" spans="1:35">
       <c r="A296">
-        <v>6705</v>
+        <v>6628</v>
       </c>
       <c r="B296" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C296" t="s">
         <v>50</v>
@@ -23274,7 +23304,7 @@
         <v>52</v>
       </c>
       <c r="E296" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F296" t="s">
         <v>56</v>
@@ -23301,22 +23331,22 @@
         <v>2026</v>
       </c>
       <c r="R296">
-        <v>18004028</v>
+        <v>18003256</v>
       </c>
       <c r="S296" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="U296" t="s">
         <v>173</v>
       </c>
       <c r="V296" s="1">
-        <v>46275.31750599537</v>
+        <v>46275.31749535879</v>
       </c>
       <c r="W296">
         <v>4</v>
       </c>
       <c r="X296" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="AB296">
         <v>0</v>
@@ -23325,24 +23355,24 @@
         <v>162</v>
       </c>
       <c r="AH296" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI296" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="297" spans="1:35">
       <c r="A297">
-        <v>5417</v>
+        <v>6703</v>
       </c>
       <c r="B297" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C297" t="s">
         <v>50</v>
       </c>
       <c r="D297" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E297" t="s">
         <v>54</v>
@@ -23351,7 +23381,7 @@
         <v>56</v>
       </c>
       <c r="G297">
-        <v>7877</v>
+        <v>11746</v>
       </c>
       <c r="H297">
         <v>0</v>
@@ -23360,57 +23390,54 @@
         <v>65</v>
       </c>
       <c r="J297" t="s">
-        <v>67</v>
+        <v>129</v>
       </c>
       <c r="N297" s="1">
-        <v>46259</v>
+        <v>46275</v>
       </c>
       <c r="P297">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q297">
         <v>2026</v>
       </c>
       <c r="R297">
-        <v>17399329</v>
+        <v>18004017</v>
       </c>
       <c r="S297" t="s">
         <v>54</v>
       </c>
       <c r="U297" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="V297" s="1">
-        <v>46275.5810894676</v>
+        <v>46275.31750491898</v>
       </c>
       <c r="W297">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="X297" t="s">
-        <v>180</v>
-      </c>
-      <c r="Y297" t="s">
-        <v>282</v>
+        <v>183</v>
       </c>
       <c r="AB297">
         <v>0</v>
       </c>
       <c r="AC297" t="s">
-        <v>54</v>
+        <v>162</v>
       </c>
       <c r="AH297" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI297" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="298" spans="1:35">
       <c r="A298">
-        <v>6486</v>
+        <v>6704</v>
       </c>
       <c r="B298" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C298" t="s">
         <v>50</v>
@@ -23425,7 +23452,7 @@
         <v>56</v>
       </c>
       <c r="G298">
-        <v>9774</v>
+        <v>11746</v>
       </c>
       <c r="H298">
         <v>0</v>
@@ -23434,87 +23461,81 @@
         <v>65</v>
       </c>
       <c r="J298" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="N298" s="1">
-        <v>46259</v>
+        <v>46275</v>
       </c>
       <c r="P298">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q298">
         <v>2026</v>
       </c>
       <c r="R298">
-        <v>16976320</v>
+        <v>17995164</v>
       </c>
       <c r="S298" t="s">
         <v>54</v>
       </c>
       <c r="U298" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="V298" s="1">
-        <v>46275.58158541666</v>
+        <v>46275.31750555555</v>
       </c>
       <c r="W298">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="X298" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y298" t="s">
-        <v>283</v>
+        <v>179</v>
       </c>
       <c r="AB298">
         <v>0</v>
       </c>
       <c r="AC298" t="s">
-        <v>54</v>
+        <v>162</v>
       </c>
       <c r="AH298" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AI298" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="299" spans="1:35">
       <c r="A299">
-        <v>6627</v>
+        <v>6705</v>
       </c>
       <c r="B299" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="C299" t="s">
         <v>50</v>
       </c>
       <c r="D299" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E299" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F299" t="s">
         <v>56</v>
       </c>
       <c r="G299">
-        <v>11056</v>
+        <v>11746</v>
       </c>
       <c r="H299">
         <v>0</v>
       </c>
       <c r="I299" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J299" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="N299" s="1">
-        <v>46276</v>
-      </c>
-      <c r="O299" t="s">
-        <v>138</v>
+        <v>46275</v>
       </c>
       <c r="P299">
         <v>8</v>
@@ -23523,34 +23544,256 @@
         <v>2026</v>
       </c>
       <c r="R299">
-        <v>18270269</v>
+        <v>18004028</v>
+      </c>
+      <c r="S299" t="s">
+        <v>54</v>
       </c>
       <c r="U299" t="s">
         <v>173</v>
       </c>
       <c r="V299" s="1">
+        <v>46275.31750599537</v>
+      </c>
+      <c r="W299">
+        <v>4</v>
+      </c>
+      <c r="X299" t="s">
+        <v>179</v>
+      </c>
+      <c r="AB299">
+        <v>0</v>
+      </c>
+      <c r="AC299" t="s">
+        <v>162</v>
+      </c>
+      <c r="AH299" t="s">
+        <v>290</v>
+      </c>
+      <c r="AI299" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="300" spans="1:35">
+      <c r="A300">
+        <v>5417</v>
+      </c>
+      <c r="B300" t="s">
+        <v>43</v>
+      </c>
+      <c r="C300" t="s">
+        <v>50</v>
+      </c>
+      <c r="D300" t="s">
+        <v>51</v>
+      </c>
+      <c r="E300" t="s">
+        <v>54</v>
+      </c>
+      <c r="F300" t="s">
+        <v>56</v>
+      </c>
+      <c r="G300">
+        <v>7877</v>
+      </c>
+      <c r="H300">
+        <v>0</v>
+      </c>
+      <c r="I300" t="s">
+        <v>65</v>
+      </c>
+      <c r="J300" t="s">
+        <v>67</v>
+      </c>
+      <c r="N300" s="1">
+        <v>46259</v>
+      </c>
+      <c r="P300">
+        <v>7</v>
+      </c>
+      <c r="Q300">
+        <v>2026</v>
+      </c>
+      <c r="R300">
+        <v>17399329</v>
+      </c>
+      <c r="S300" t="s">
+        <v>54</v>
+      </c>
+      <c r="U300" t="s">
+        <v>171</v>
+      </c>
+      <c r="V300" s="1">
+        <v>46275.5810894676</v>
+      </c>
+      <c r="W300">
+        <v>20</v>
+      </c>
+      <c r="X300" t="s">
+        <v>180</v>
+      </c>
+      <c r="Y300" t="s">
+        <v>283</v>
+      </c>
+      <c r="AB300">
+        <v>0</v>
+      </c>
+      <c r="AC300" t="s">
+        <v>54</v>
+      </c>
+      <c r="AH300" t="s">
+        <v>290</v>
+      </c>
+      <c r="AI300" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="301" spans="1:35">
+      <c r="A301">
+        <v>6486</v>
+      </c>
+      <c r="B301" t="s">
+        <v>44</v>
+      </c>
+      <c r="C301" t="s">
+        <v>50</v>
+      </c>
+      <c r="D301" t="s">
+        <v>51</v>
+      </c>
+      <c r="E301" t="s">
+        <v>54</v>
+      </c>
+      <c r="F301" t="s">
+        <v>56</v>
+      </c>
+      <c r="G301">
+        <v>9774</v>
+      </c>
+      <c r="H301">
+        <v>0</v>
+      </c>
+      <c r="I301" t="s">
+        <v>65</v>
+      </c>
+      <c r="J301" t="s">
+        <v>120</v>
+      </c>
+      <c r="N301" s="1">
+        <v>46259</v>
+      </c>
+      <c r="P301">
+        <v>7</v>
+      </c>
+      <c r="Q301">
+        <v>2026</v>
+      </c>
+      <c r="R301">
+        <v>16976320</v>
+      </c>
+      <c r="S301" t="s">
+        <v>54</v>
+      </c>
+      <c r="U301" t="s">
+        <v>171</v>
+      </c>
+      <c r="V301" s="1">
+        <v>46275.58158541666</v>
+      </c>
+      <c r="W301">
+        <v>20</v>
+      </c>
+      <c r="X301" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y301" t="s">
+        <v>284</v>
+      </c>
+      <c r="AB301">
+        <v>0</v>
+      </c>
+      <c r="AC301" t="s">
+        <v>54</v>
+      </c>
+      <c r="AH301" t="s">
+        <v>290</v>
+      </c>
+      <c r="AI301" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="302" spans="1:35">
+      <c r="A302">
+        <v>6627</v>
+      </c>
+      <c r="B302" t="s">
+        <v>36</v>
+      </c>
+      <c r="C302" t="s">
+        <v>50</v>
+      </c>
+      <c r="D302" t="s">
+        <v>51</v>
+      </c>
+      <c r="E302" t="s">
+        <v>55</v>
+      </c>
+      <c r="F302" t="s">
+        <v>56</v>
+      </c>
+      <c r="G302">
+        <v>11056</v>
+      </c>
+      <c r="H302">
+        <v>0</v>
+      </c>
+      <c r="I302" t="s">
+        <v>66</v>
+      </c>
+      <c r="J302" t="s">
+        <v>122</v>
+      </c>
+      <c r="N302" s="1">
+        <v>46276</v>
+      </c>
+      <c r="O302" t="s">
+        <v>138</v>
+      </c>
+      <c r="P302">
+        <v>8</v>
+      </c>
+      <c r="Q302">
+        <v>2026</v>
+      </c>
+      <c r="R302">
+        <v>18270269</v>
+      </c>
+      <c r="U302" t="s">
+        <v>173</v>
+      </c>
+      <c r="V302" s="1">
         <v>46276.41675075232</v>
       </c>
-      <c r="W299">
+      <c r="W302">
         <v>3</v>
       </c>
-      <c r="X299" t="s">
+      <c r="X302" t="s">
         <v>175</v>
       </c>
-      <c r="Y299" t="s">
-        <v>284</v>
-      </c>
-      <c r="AB299">
-        <v>0</v>
-      </c>
-      <c r="AC299" t="s">
-        <v>288</v>
-      </c>
-      <c r="AH299" t="s">
+      <c r="Y302" t="s">
+        <v>285</v>
+      </c>
+      <c r="AB302">
+        <v>0</v>
+      </c>
+      <c r="AC302" t="s">
         <v>289</v>
       </c>
-      <c r="AI299" t="s">
-        <v>293</v>
+      <c r="AH302" t="s">
+        <v>290</v>
+      </c>
+      <c r="AI302" t="s">
+        <v>294</v>
       </c>
     </row>
   </sheetData>

--- a/data/base/goias.xlsx
+++ b/data/base/goias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4535" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4550" uniqueCount="312">
   <si>
     <t>CodCliente</t>
   </si>
@@ -854,6 +854,9 @@
   </si>
   <si>
     <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 11/09/2026 - Data Comentário: 04/09/2026 17:02</t>
+  </si>
+  <si>
+    <t>Controladoria, Erro de baixa, Chamado Nº Nº DO CHAMADO = 83973 - Data Comentário: 14/09/2026 17:50</t>
   </si>
   <si>
     <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 11/09/2026 - Data Comentário: 04/09/2026 16:38</t>
@@ -1307,7 +1310,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AI318"/>
+  <dimension ref="A1:AI319"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:35">
@@ -1473,7 +1476,7 @@
         <v>46268.63953865741</v>
       </c>
       <c r="W2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X2" t="s">
         <v>180</v>
@@ -1488,10 +1491,10 @@
         <v>145</v>
       </c>
       <c r="AH2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="3" spans="1:35">
@@ -1550,7 +1553,7 @@
         <v>46266.57730150463</v>
       </c>
       <c r="W3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X3" t="s">
         <v>181</v>
@@ -1565,10 +1568,10 @@
         <v>146</v>
       </c>
       <c r="AH3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="4" spans="1:35">
@@ -1627,7 +1630,7 @@
         <v>46266.41668148148</v>
       </c>
       <c r="W4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X4" t="s">
         <v>182</v>
@@ -1642,10 +1645,10 @@
         <v>145</v>
       </c>
       <c r="AH4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="5" spans="1:35">
@@ -1704,7 +1707,7 @@
         <v>46267.75233784723</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X5" t="s">
         <v>180</v>
@@ -1716,10 +1719,10 @@
         <v>145</v>
       </c>
       <c r="AH5" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="6" spans="1:35">
@@ -1778,7 +1781,7 @@
         <v>46267.75233927083</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X6" t="s">
         <v>181</v>
@@ -1790,10 +1793,10 @@
         <v>146</v>
       </c>
       <c r="AH6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="7" spans="1:35">
@@ -1852,7 +1855,7 @@
         <v>46267.7523394676</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7" t="s">
         <v>181</v>
@@ -1864,10 +1867,10 @@
         <v>146</v>
       </c>
       <c r="AH7" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI7" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="8" spans="1:35">
@@ -1926,7 +1929,7 @@
         <v>46267.75234278935</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8" t="s">
         <v>183</v>
@@ -1938,10 +1941,10 @@
         <v>147</v>
       </c>
       <c r="AH8" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI8" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="9" spans="1:35">
@@ -2000,7 +2003,7 @@
         <v>46267.75234309028</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9" t="s">
         <v>182</v>
@@ -2012,10 +2015,10 @@
         <v>145</v>
       </c>
       <c r="AH9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI9" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10" spans="1:35">
@@ -2074,7 +2077,7 @@
         <v>46267.75234383102</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10" t="s">
         <v>184</v>
@@ -2086,10 +2089,10 @@
         <v>148</v>
       </c>
       <c r="AH10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="11" spans="1:35">
@@ -2148,7 +2151,7 @@
         <v>46267.75234424769</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X11" t="s">
         <v>184</v>
@@ -2160,10 +2163,10 @@
         <v>148</v>
       </c>
       <c r="AH11" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI11" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="12" spans="1:35">
@@ -2222,7 +2225,7 @@
         <v>46267.47365627315</v>
       </c>
       <c r="W12">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="X12" t="s">
         <v>185</v>
@@ -2234,10 +2237,10 @@
         <v>149</v>
       </c>
       <c r="AH12" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI12" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="13" spans="1:35">
@@ -2296,7 +2299,7 @@
         <v>46266.47620831019</v>
       </c>
       <c r="W13">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="X13" t="s">
         <v>186</v>
@@ -2305,13 +2308,13 @@
         <v>0</v>
       </c>
       <c r="AC13" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AH13" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI13" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="14" spans="1:35">
@@ -2370,7 +2373,7 @@
         <v>46267.57586420139</v>
       </c>
       <c r="W14">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="X14" t="s">
         <v>187</v>
@@ -2379,13 +2382,13 @@
         <v>0</v>
       </c>
       <c r="AC14" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AH14" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI14" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="15" spans="1:35">
@@ -2441,7 +2444,7 @@
         <v>46266.44145744213</v>
       </c>
       <c r="W15">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X15" t="s">
         <v>188</v>
@@ -2453,10 +2456,10 @@
         <v>0</v>
       </c>
       <c r="AH15" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI15" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="16" spans="1:35">
@@ -2509,7 +2512,7 @@
         <v>46266.44156952546</v>
       </c>
       <c r="W16">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="X16" t="s">
         <v>188</v>
@@ -2518,10 +2521,10 @@
         <v>0</v>
       </c>
       <c r="AH16" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI16" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="17" spans="1:35">
@@ -2577,7 +2580,7 @@
         <v>46266.44152346065</v>
       </c>
       <c r="W17">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X17" t="s">
         <v>188</v>
@@ -2589,10 +2592,10 @@
         <v>0</v>
       </c>
       <c r="AH17" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI17" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="18" spans="1:35">
@@ -2651,7 +2654,7 @@
         <v>46269.3962034375</v>
       </c>
       <c r="W18">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X18" t="s">
         <v>189</v>
@@ -2666,10 +2669,10 @@
         <v>151</v>
       </c>
       <c r="AH18" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI18" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="19" spans="1:35">
@@ -2728,7 +2731,7 @@
         <v>46268.54759884259</v>
       </c>
       <c r="W19">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X19" t="s">
         <v>186</v>
@@ -2743,10 +2746,10 @@
         <v>150</v>
       </c>
       <c r="AH19" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI19" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="20" spans="1:35">
@@ -2805,7 +2808,7 @@
         <v>46269.38216940972</v>
       </c>
       <c r="W20">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X20" t="s">
         <v>187</v>
@@ -2820,10 +2823,10 @@
         <v>151</v>
       </c>
       <c r="AH20" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI20" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="21" spans="1:35">
@@ -2882,7 +2885,7 @@
         <v>46269.40844942129</v>
       </c>
       <c r="W21">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X21" t="s">
         <v>185</v>
@@ -2897,10 +2900,10 @@
         <v>149</v>
       </c>
       <c r="AH21" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI21" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="22" spans="1:35">
@@ -2959,7 +2962,7 @@
         <v>46266.37634084491</v>
       </c>
       <c r="W22">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="X22" t="s">
         <v>190</v>
@@ -2971,10 +2974,10 @@
         <v>152</v>
       </c>
       <c r="AH22" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI22" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="23" spans="1:35">
@@ -3033,7 +3036,7 @@
         <v>46267.47452163194</v>
       </c>
       <c r="W23">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="X23" t="s">
         <v>185</v>
@@ -3045,10 +3048,10 @@
         <v>149</v>
       </c>
       <c r="AH23" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI23" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="24" spans="1:35">
@@ -3107,7 +3110,7 @@
         <v>46267.4745221412</v>
       </c>
       <c r="W24">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="X24" t="s">
         <v>185</v>
@@ -3119,10 +3122,10 @@
         <v>149</v>
       </c>
       <c r="AH24" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI24" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="25" spans="1:35">
@@ -3181,7 +3184,7 @@
         <v>46267.47452299768</v>
       </c>
       <c r="W25">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="X25" t="s">
         <v>185</v>
@@ -3193,10 +3196,10 @@
         <v>149</v>
       </c>
       <c r="AH25" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI25" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="26" spans="1:35">
@@ -3255,7 +3258,7 @@
         <v>46267.75231010417</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X26" t="s">
         <v>186</v>
@@ -3267,10 +3270,10 @@
         <v>150</v>
       </c>
       <c r="AH26" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI26" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="27" spans="1:35">
@@ -3329,7 +3332,7 @@
         <v>46267.75234059028</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X27" t="s">
         <v>185</v>
@@ -3341,10 +3344,10 @@
         <v>149</v>
       </c>
       <c r="AH27" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI27" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="28" spans="1:35">
@@ -3403,7 +3406,7 @@
         <v>46267.7523409375</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X28" t="s">
         <v>185</v>
@@ -3415,10 +3418,10 @@
         <v>149</v>
       </c>
       <c r="AH28" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI28" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="29" spans="1:35">
@@ -3477,7 +3480,7 @@
         <v>46267.75234170139</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X29" t="s">
         <v>185</v>
@@ -3489,10 +3492,10 @@
         <v>149</v>
       </c>
       <c r="AH29" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI29" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="30" spans="1:35">
@@ -3551,7 +3554,7 @@
         <v>46268.58940019676</v>
       </c>
       <c r="W30">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="X30" t="s">
         <v>189</v>
@@ -3563,10 +3566,10 @@
         <v>153</v>
       </c>
       <c r="AH30" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI30" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="31" spans="1:35">
@@ -3628,7 +3631,7 @@
         <v>46268.37896984954</v>
       </c>
       <c r="W31">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X31" t="s">
         <v>181</v>
@@ -3643,10 +3646,10 @@
         <v>154</v>
       </c>
       <c r="AH31" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI31" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="32" spans="1:35">
@@ -3705,7 +3708,7 @@
         <v>46269.71652982639</v>
       </c>
       <c r="W32">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X32" t="s">
         <v>183</v>
@@ -3717,10 +3720,10 @@
         <v>155</v>
       </c>
       <c r="AH32" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI32" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="33" spans="1:35">
@@ -3782,7 +3785,7 @@
         <v>46269.71069613426</v>
       </c>
       <c r="W33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X33" t="s">
         <v>182</v>
@@ -3797,10 +3800,10 @@
         <v>156</v>
       </c>
       <c r="AH33" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI33" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="34" spans="1:35">
@@ -3859,7 +3862,7 @@
         <v>46267.55838734953</v>
       </c>
       <c r="W34">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X34" t="s">
         <v>186</v>
@@ -3874,10 +3877,10 @@
         <v>157</v>
       </c>
       <c r="AH34" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI34" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="35" spans="1:35">
@@ -3939,7 +3942,7 @@
         <v>46273.59003707176</v>
       </c>
       <c r="W35">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X35" t="s">
         <v>190</v>
@@ -3951,13 +3954,13 @@
         <v>0</v>
       </c>
       <c r="AC35" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AH35" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI35" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="36" spans="1:35">
@@ -4019,7 +4022,7 @@
         <v>46268.74069754629</v>
       </c>
       <c r="W36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X36" t="s">
         <v>180</v>
@@ -4034,10 +4037,10 @@
         <v>159</v>
       </c>
       <c r="AH36" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI36" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="37" spans="1:35">
@@ -4099,7 +4102,7 @@
         <v>46273.45940115741</v>
       </c>
       <c r="W37">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X37" t="s">
         <v>189</v>
@@ -4114,10 +4117,10 @@
         <v>153</v>
       </c>
       <c r="AH37" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI37" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="38" spans="1:35">
@@ -4176,7 +4179,7 @@
         <v>46267.66088636574</v>
       </c>
       <c r="W38">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X38" t="s">
         <v>186</v>
@@ -4191,10 +4194,10 @@
         <v>175</v>
       </c>
       <c r="AH38" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI38" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="39" spans="1:35">
@@ -4256,7 +4259,7 @@
         <v>46268.45922827546</v>
       </c>
       <c r="W39">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X39" t="s">
         <v>187</v>
@@ -4271,10 +4274,10 @@
         <v>154</v>
       </c>
       <c r="AH39" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI39" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="40" spans="1:35">
@@ -4336,7 +4339,7 @@
         <v>46269.59248078704</v>
       </c>
       <c r="W40">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X40" t="s">
         <v>181</v>
@@ -4351,10 +4354,10 @@
         <v>154</v>
       </c>
       <c r="AH40" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI40" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="41" spans="1:35">
@@ -4416,7 +4419,7 @@
         <v>46269.59224453704</v>
       </c>
       <c r="W41">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X41" t="s">
         <v>181</v>
@@ -4431,10 +4434,10 @@
         <v>154</v>
       </c>
       <c r="AH41" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI41" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="42" spans="1:35">
@@ -4496,7 +4499,7 @@
         <v>46268.5891771875</v>
       </c>
       <c r="W42">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X42" t="s">
         <v>189</v>
@@ -4511,10 +4514,10 @@
         <v>153</v>
       </c>
       <c r="AH42" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI42" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="43" spans="1:35">
@@ -4576,7 +4579,7 @@
         <v>46267.64795916666</v>
       </c>
       <c r="W43">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X43" t="s">
         <v>185</v>
@@ -4591,10 +4594,10 @@
         <v>160</v>
       </c>
       <c r="AH43" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI43" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:35">
@@ -4656,7 +4659,7 @@
         <v>46267.4478849537</v>
       </c>
       <c r="W44">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X44" t="s">
         <v>183</v>
@@ -4671,10 +4674,10 @@
         <v>155</v>
       </c>
       <c r="AH44" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI44" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:35">
@@ -4736,7 +4739,7 @@
         <v>46269.59056300926</v>
       </c>
       <c r="W45">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X45" t="s">
         <v>182</v>
@@ -4751,10 +4754,10 @@
         <v>156</v>
       </c>
       <c r="AH45" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI45" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="46" spans="1:35">
@@ -4810,7 +4813,7 @@
         <v>46273.67026252315</v>
       </c>
       <c r="W46">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X46" t="s">
         <v>186</v>
@@ -4822,10 +4825,10 @@
         <v>157</v>
       </c>
       <c r="AH46" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI46" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47" spans="1:35">
@@ -4884,7 +4887,7 @@
         <v>46269.677524375</v>
       </c>
       <c r="W47">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X47" t="s">
         <v>187</v>
@@ -4896,10 +4899,10 @@
         <v>154</v>
       </c>
       <c r="AH47" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI47" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="48" spans="1:35">
@@ -4958,7 +4961,7 @@
         <v>46269.677525</v>
       </c>
       <c r="W48">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X48" t="s">
         <v>181</v>
@@ -4970,10 +4973,10 @@
         <v>154</v>
       </c>
       <c r="AH48" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI48" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="49" spans="1:35">
@@ -5032,7 +5035,7 @@
         <v>46269.677525625</v>
       </c>
       <c r="W49">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X49" t="s">
         <v>181</v>
@@ -5044,10 +5047,10 @@
         <v>154</v>
       </c>
       <c r="AH49" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI49" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="50" spans="1:35">
@@ -5106,7 +5109,7 @@
         <v>46268.58906282407</v>
       </c>
       <c r="W50">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X50" t="s">
         <v>189</v>
@@ -5118,10 +5121,10 @@
         <v>153</v>
       </c>
       <c r="AH50" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI50" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="51" spans="1:35">
@@ -5180,7 +5183,7 @@
         <v>46267.64761306713</v>
       </c>
       <c r="W51">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X51" t="s">
         <v>185</v>
@@ -5192,10 +5195,10 @@
         <v>160</v>
       </c>
       <c r="AH51" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI51" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="52" spans="1:35">
@@ -5257,7 +5260,7 @@
         <v>46273.64957155092</v>
       </c>
       <c r="W52">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X52" t="s">
         <v>183</v>
@@ -5272,10 +5275,10 @@
         <v>155</v>
       </c>
       <c r="AH52" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI52" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="53" spans="1:35">
@@ -5334,7 +5337,7 @@
         <v>46273.39871140046</v>
       </c>
       <c r="W53">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X53" t="s">
         <v>182</v>
@@ -5346,10 +5349,10 @@
         <v>156</v>
       </c>
       <c r="AH53" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI53" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="54" spans="1:35">
@@ -5411,7 +5414,7 @@
         <v>46267.35832805555</v>
       </c>
       <c r="W54">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X54" t="s">
         <v>187</v>
@@ -5426,10 +5429,10 @@
         <v>154</v>
       </c>
       <c r="AH54" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI54" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="55" spans="1:35">
@@ -5491,7 +5494,7 @@
         <v>46268.71229238426</v>
       </c>
       <c r="W55">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X55" t="s">
         <v>181</v>
@@ -5506,10 +5509,10 @@
         <v>154</v>
       </c>
       <c r="AH55" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI55" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="56" spans="1:35">
@@ -5571,7 +5574,7 @@
         <v>46268.71229297454</v>
       </c>
       <c r="W56">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X56" t="s">
         <v>181</v>
@@ -5586,10 +5589,10 @@
         <v>154</v>
       </c>
       <c r="AH56" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI56" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="57" spans="1:35">
@@ -5651,7 +5654,7 @@
         <v>46267.74532275463</v>
       </c>
       <c r="W57">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X57" t="s">
         <v>189</v>
@@ -5666,10 +5669,10 @@
         <v>153</v>
       </c>
       <c r="AH57" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI57" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="58" spans="1:35">
@@ -5728,7 +5731,7 @@
         <v>46269.60160202546</v>
       </c>
       <c r="W58">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X58" t="s">
         <v>186</v>
@@ -5743,10 +5746,10 @@
         <v>157</v>
       </c>
       <c r="AH58" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI58" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="59" spans="1:35">
@@ -5808,7 +5811,7 @@
         <v>46273.64508760416</v>
       </c>
       <c r="W59">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X59" t="s">
         <v>190</v>
@@ -5820,13 +5823,13 @@
         <v>0</v>
       </c>
       <c r="AC59" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AH59" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI59" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="60" spans="1:35">
@@ -5888,7 +5891,7 @@
         <v>46268.45926839121</v>
       </c>
       <c r="W60">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X60" t="s">
         <v>187</v>
@@ -5903,10 +5906,10 @@
         <v>154</v>
       </c>
       <c r="AH60" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI60" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="61" spans="1:35">
@@ -5968,7 +5971,7 @@
         <v>46269.59250902777</v>
       </c>
       <c r="W61">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X61" t="s">
         <v>181</v>
@@ -5983,10 +5986,10 @@
         <v>154</v>
       </c>
       <c r="AH61" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI61" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="62" spans="1:35">
@@ -6048,7 +6051,7 @@
         <v>46269.5922865625</v>
       </c>
       <c r="W62">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X62" t="s">
         <v>181</v>
@@ -6063,10 +6066,10 @@
         <v>154</v>
       </c>
       <c r="AH62" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI62" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="63" spans="1:35">
@@ -6128,7 +6131,7 @@
         <v>46268.58922707176</v>
       </c>
       <c r="W63">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X63" t="s">
         <v>189</v>
@@ -6143,10 +6146,10 @@
         <v>153</v>
       </c>
       <c r="AH63" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI63" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="64" spans="1:35">
@@ -6208,7 +6211,7 @@
         <v>46267.64800344907</v>
       </c>
       <c r="W64">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X64" t="s">
         <v>185</v>
@@ -6223,10 +6226,10 @@
         <v>160</v>
       </c>
       <c r="AH64" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI64" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="65" spans="1:35">
@@ -6288,7 +6291,7 @@
         <v>46267.44799793982</v>
       </c>
       <c r="W65">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X65" t="s">
         <v>183</v>
@@ -6303,10 +6306,10 @@
         <v>155</v>
       </c>
       <c r="AH65" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI65" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="66" spans="1:35">
@@ -6368,7 +6371,7 @@
         <v>46269.59070487269</v>
       </c>
       <c r="W66">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X66" t="s">
         <v>182</v>
@@ -6383,10 +6386,10 @@
         <v>156</v>
       </c>
       <c r="AH66" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI66" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="67" spans="1:35">
@@ -6448,7 +6451,7 @@
         <v>46269.49635894676</v>
       </c>
       <c r="W67">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X67" t="s">
         <v>187</v>
@@ -6463,10 +6466,10 @@
         <v>154</v>
       </c>
       <c r="AH67" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI67" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="68" spans="1:35">
@@ -6522,7 +6525,7 @@
         <v>46269.63659284722</v>
       </c>
       <c r="W68">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X68" t="s">
         <v>186</v>
@@ -6534,10 +6537,10 @@
         <v>157</v>
       </c>
       <c r="AH68" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI68" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="69" spans="1:35">
@@ -6596,7 +6599,7 @@
         <v>46273.64532122685</v>
       </c>
       <c r="W69">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X69" t="s">
         <v>190</v>
@@ -6605,13 +6608,13 @@
         <v>0</v>
       </c>
       <c r="AC69" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AH69" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI69" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="70" spans="1:35">
@@ -6670,7 +6673,7 @@
         <v>46268.45929986111</v>
       </c>
       <c r="W70">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X70" t="s">
         <v>187</v>
@@ -6682,10 +6685,10 @@
         <v>154</v>
       </c>
       <c r="AH70" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI70" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="71" spans="1:35">
@@ -6744,7 +6747,7 @@
         <v>46269.5925421875</v>
       </c>
       <c r="W71">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X71" t="s">
         <v>181</v>
@@ -6756,10 +6759,10 @@
         <v>154</v>
       </c>
       <c r="AH71" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI71" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="72" spans="1:35">
@@ -6818,7 +6821,7 @@
         <v>46269.59231454861</v>
       </c>
       <c r="W72">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X72" t="s">
         <v>181</v>
@@ -6830,10 +6833,10 @@
         <v>154</v>
       </c>
       <c r="AH72" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI72" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="73" spans="1:35">
@@ -6892,7 +6895,7 @@
         <v>46268.58932953704</v>
       </c>
       <c r="W73">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X73" t="s">
         <v>189</v>
@@ -6904,10 +6907,10 @@
         <v>153</v>
       </c>
       <c r="AH73" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI73" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="74" spans="1:35">
@@ -6966,7 +6969,7 @@
         <v>46267.648038125</v>
       </c>
       <c r="W74">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X74" t="s">
         <v>185</v>
@@ -6978,10 +6981,10 @@
         <v>160</v>
       </c>
       <c r="AH74" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI74" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="75" spans="1:35">
@@ -7040,7 +7043,7 @@
         <v>46267.44824061343</v>
       </c>
       <c r="W75">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X75" t="s">
         <v>183</v>
@@ -7052,10 +7055,10 @@
         <v>155</v>
       </c>
       <c r="AH75" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI75" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="76" spans="1:35">
@@ -7114,7 +7117,7 @@
         <v>46269.59082328704</v>
       </c>
       <c r="W76">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X76" t="s">
         <v>182</v>
@@ -7126,10 +7129,10 @@
         <v>156</v>
       </c>
       <c r="AH76" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI76" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="77" spans="1:35">
@@ -7185,7 +7188,7 @@
         <v>46273.63629708334</v>
       </c>
       <c r="W77">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X77" t="s">
         <v>182</v>
@@ -7200,10 +7203,10 @@
         <v>156</v>
       </c>
       <c r="AH77" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI77" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="78" spans="1:35">
@@ -7259,7 +7262,7 @@
         <v>46273.64318633102</v>
       </c>
       <c r="W78">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X78" t="s">
         <v>182</v>
@@ -7274,10 +7277,10 @@
         <v>156</v>
       </c>
       <c r="AH78" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI78" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="79" spans="1:35">
@@ -7333,7 +7336,7 @@
         <v>46273.64880981482</v>
       </c>
       <c r="W79">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X79" t="s">
         <v>182</v>
@@ -7348,10 +7351,10 @@
         <v>156</v>
       </c>
       <c r="AH79" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI79" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="80" spans="1:35">
@@ -7410,7 +7413,7 @@
         <v>46267.72055925926</v>
       </c>
       <c r="W80">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="X80" t="s">
         <v>180</v>
@@ -7422,10 +7425,10 @@
         <v>162</v>
       </c>
       <c r="AH80" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI80" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="81" spans="1:35">
@@ -7484,7 +7487,7 @@
         <v>46267.79441380787</v>
       </c>
       <c r="W81">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="X81" t="s">
         <v>181</v>
@@ -7496,10 +7499,10 @@
         <v>162</v>
       </c>
       <c r="AH81" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI81" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="82" spans="1:35">
@@ -7558,7 +7561,7 @@
         <v>46267.79441215278</v>
       </c>
       <c r="W82">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="X82" t="s">
         <v>182</v>
@@ -7570,10 +7573,10 @@
         <v>163</v>
       </c>
       <c r="AH82" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI82" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="83" spans="1:35">
@@ -7632,7 +7635,7 @@
         <v>46267.7205502662</v>
       </c>
       <c r="W83">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X83" t="s">
         <v>180</v>
@@ -7644,10 +7647,10 @@
         <v>162</v>
       </c>
       <c r="AH83" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI83" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="84" spans="1:35">
@@ -7706,7 +7709,7 @@
         <v>46267.79439748843</v>
       </c>
       <c r="W84">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X84" t="s">
         <v>181</v>
@@ -7718,10 +7721,10 @@
         <v>162</v>
       </c>
       <c r="AH84" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI84" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="85" spans="1:35">
@@ -7777,7 +7780,7 @@
         <v>46267.79440011574</v>
       </c>
       <c r="W85">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X85" t="s">
         <v>183</v>
@@ -7792,10 +7795,10 @@
         <v>162</v>
       </c>
       <c r="AH85" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI85" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="86" spans="1:35">
@@ -7848,7 +7851,7 @@
         <v>46267.79439818287</v>
       </c>
       <c r="W86">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X86" t="s">
         <v>182</v>
@@ -7860,10 +7863,10 @@
         <v>163</v>
       </c>
       <c r="AH86" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI86" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="87" spans="1:35">
@@ -7922,7 +7925,7 @@
         <v>46267.7202693287</v>
       </c>
       <c r="W87">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X87" t="s">
         <v>180</v>
@@ -7934,10 +7937,10 @@
         <v>162</v>
       </c>
       <c r="AH87" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI87" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="88" spans="1:35">
@@ -7996,7 +7999,7 @@
         <v>46267.79409846065</v>
       </c>
       <c r="W88">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X88" t="s">
         <v>181</v>
@@ -8008,10 +8011,10 @@
         <v>162</v>
       </c>
       <c r="AH88" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI88" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="89" spans="1:35">
@@ -8070,7 +8073,7 @@
         <v>46267.79409725694</v>
       </c>
       <c r="W89">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X89" t="s">
         <v>181</v>
@@ -8082,10 +8085,10 @@
         <v>162</v>
       </c>
       <c r="AH89" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI89" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="90" spans="1:35">
@@ -8138,7 +8141,7 @@
         <v>46267.79410239583</v>
       </c>
       <c r="W90">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X90" t="s">
         <v>183</v>
@@ -8150,10 +8153,10 @@
         <v>162</v>
       </c>
       <c r="AH90" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI90" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="91" spans="1:35">
@@ -8206,7 +8209,7 @@
         <v>46267.79409934028</v>
       </c>
       <c r="W91">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X91" t="s">
         <v>182</v>
@@ -8218,10 +8221,10 @@
         <v>163</v>
       </c>
       <c r="AH91" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI91" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="92" spans="1:35">
@@ -8280,7 +8283,7 @@
         <v>46267.72033356482</v>
       </c>
       <c r="W92">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X92" t="s">
         <v>180</v>
@@ -8292,10 +8295,10 @@
         <v>162</v>
       </c>
       <c r="AH92" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI92" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="93" spans="1:35">
@@ -8354,7 +8357,7 @@
         <v>46267.79418105324</v>
       </c>
       <c r="W93">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X93" t="s">
         <v>181</v>
@@ -8366,10 +8369,10 @@
         <v>162</v>
       </c>
       <c r="AH93" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI93" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="94" spans="1:35">
@@ -8428,7 +8431,7 @@
         <v>46267.79418005787</v>
       </c>
       <c r="W94">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X94" t="s">
         <v>181</v>
@@ -8440,10 +8443,10 @@
         <v>162</v>
       </c>
       <c r="AH94" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI94" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="95" spans="1:35">
@@ -8496,7 +8499,7 @@
         <v>46267.79418379629</v>
       </c>
       <c r="W95">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X95" t="s">
         <v>183</v>
@@ -8508,10 +8511,10 @@
         <v>162</v>
       </c>
       <c r="AH95" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI95" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="96" spans="1:35">
@@ -8564,7 +8567,7 @@
         <v>46267.79418283565</v>
       </c>
       <c r="W96">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X96" t="s">
         <v>182</v>
@@ -8576,10 +8579,10 @@
         <v>163</v>
       </c>
       <c r="AH96" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI96" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="97" spans="1:35">
@@ -8638,7 +8641,7 @@
         <v>46267.71937662037</v>
       </c>
       <c r="W97">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X97" t="s">
         <v>180</v>
@@ -8650,10 +8653,10 @@
         <v>162</v>
       </c>
       <c r="AH97" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI97" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="98" spans="1:35">
@@ -8712,7 +8715,7 @@
         <v>46267.79259834491</v>
       </c>
       <c r="W98">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X98" t="s">
         <v>181</v>
@@ -8724,10 +8727,10 @@
         <v>162</v>
       </c>
       <c r="AH98" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI98" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="99" spans="1:35">
@@ -8786,7 +8789,7 @@
         <v>46267.79260170139</v>
       </c>
       <c r="W99">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X99" t="s">
         <v>182</v>
@@ -8798,10 +8801,10 @@
         <v>163</v>
       </c>
       <c r="AH99" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI99" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="100" spans="1:35">
@@ -8863,7 +8866,7 @@
         <v>46268.37621265047</v>
       </c>
       <c r="W100">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X100" t="s">
         <v>184</v>
@@ -8878,10 +8881,10 @@
         <v>162</v>
       </c>
       <c r="AH100" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI100" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="101" spans="1:35">
@@ -8937,7 +8940,7 @@
         <v>46267.79440636574</v>
       </c>
       <c r="W101">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X101" t="s">
         <v>183</v>
@@ -8949,10 +8952,10 @@
         <v>162</v>
       </c>
       <c r="AH101" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI101" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="102" spans="1:35">
@@ -9011,7 +9014,7 @@
         <v>46267.72037954861</v>
       </c>
       <c r="W102">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X102" t="s">
         <v>180</v>
@@ -9023,10 +9026,10 @@
         <v>162</v>
       </c>
       <c r="AH102" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI102" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="103" spans="1:35">
@@ -9085,7 +9088,7 @@
         <v>46267.79424664352</v>
       </c>
       <c r="W103">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X103" t="s">
         <v>181</v>
@@ -9097,10 +9100,10 @@
         <v>162</v>
       </c>
       <c r="AH103" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI103" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="104" spans="1:35">
@@ -9159,7 +9162,7 @@
         <v>46267.79424586806</v>
       </c>
       <c r="W104">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X104" t="s">
         <v>181</v>
@@ -9171,10 +9174,10 @@
         <v>162</v>
       </c>
       <c r="AH104" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI104" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="105" spans="1:35">
@@ -9227,7 +9230,7 @@
         <v>46267.79424864583</v>
       </c>
       <c r="W105">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X105" t="s">
         <v>183</v>
@@ -9239,10 +9242,10 @@
         <v>162</v>
       </c>
       <c r="AH105" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI105" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="106" spans="1:35">
@@ -9295,7 +9298,7 @@
         <v>46267.79424725694</v>
       </c>
       <c r="W106">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X106" t="s">
         <v>182</v>
@@ -9307,10 +9310,10 @@
         <v>163</v>
       </c>
       <c r="AH106" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI106" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="107" spans="1:35">
@@ -9369,7 +9372,7 @@
         <v>46267.79425081018</v>
       </c>
       <c r="W107">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X107" t="s">
         <v>184</v>
@@ -9381,10 +9384,10 @@
         <v>162</v>
       </c>
       <c r="AH107" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI107" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="108" spans="1:35">
@@ -9443,7 +9446,7 @@
         <v>46267.71942916667</v>
       </c>
       <c r="W108">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X108" t="s">
         <v>180</v>
@@ -9455,10 +9458,10 @@
         <v>162</v>
       </c>
       <c r="AH108" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI108" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="109" spans="1:35">
@@ -9514,7 +9517,7 @@
         <v>46267.79268530093</v>
       </c>
       <c r="W109">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X109" t="s">
         <v>183</v>
@@ -9526,10 +9529,10 @@
         <v>162</v>
       </c>
       <c r="AH109" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI109" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="110" spans="1:35">
@@ -9588,7 +9591,7 @@
         <v>46267.79268769676</v>
       </c>
       <c r="W110">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X110" t="s">
         <v>182</v>
@@ -9600,10 +9603,10 @@
         <v>163</v>
       </c>
       <c r="AH110" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI110" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="111" spans="1:35">
@@ -9659,7 +9662,7 @@
         <v>46267.79249748842</v>
       </c>
       <c r="W111">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X111" t="s">
         <v>183</v>
@@ -9671,10 +9674,10 @@
         <v>165</v>
       </c>
       <c r="AH111" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI111" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="112" spans="1:35">
@@ -9733,7 +9736,7 @@
         <v>46267.79249788194</v>
       </c>
       <c r="W112">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X112" t="s">
         <v>182</v>
@@ -9745,10 +9748,10 @@
         <v>163</v>
       </c>
       <c r="AH112" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI112" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="113" spans="1:35">
@@ -9807,7 +9810,7 @@
         <v>46267.71927280092</v>
       </c>
       <c r="W113">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X113" t="s">
         <v>180</v>
@@ -9819,10 +9822,10 @@
         <v>161</v>
       </c>
       <c r="AH113" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI113" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="114" spans="1:35">
@@ -9878,7 +9881,7 @@
         <v>46267.79251079861</v>
       </c>
       <c r="W114">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X114" t="s">
         <v>183</v>
@@ -9890,10 +9893,10 @@
         <v>165</v>
       </c>
       <c r="AH114" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI114" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="115" spans="1:35">
@@ -9952,7 +9955,7 @@
         <v>46267.79251038194</v>
       </c>
       <c r="W115">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X115" t="s">
         <v>182</v>
@@ -9964,10 +9967,10 @@
         <v>163</v>
       </c>
       <c r="AH115" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI115" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="116" spans="1:35">
@@ -10026,7 +10029,7 @@
         <v>46267.72044811342</v>
       </c>
       <c r="W116">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X116" t="s">
         <v>180</v>
@@ -10038,10 +10041,10 @@
         <v>162</v>
       </c>
       <c r="AH116" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI116" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="117" spans="1:35">
@@ -10100,7 +10103,7 @@
         <v>46267.79429737268</v>
       </c>
       <c r="W117">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X117" t="s">
         <v>181</v>
@@ -10112,10 +10115,10 @@
         <v>162</v>
       </c>
       <c r="AH117" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI117" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="118" spans="1:35">
@@ -10174,7 +10177,7 @@
         <v>46267.79429603009</v>
       </c>
       <c r="W118">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X118" t="s">
         <v>181</v>
@@ -10186,10 +10189,10 @@
         <v>162</v>
       </c>
       <c r="AH118" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI118" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="119" spans="1:35">
@@ -10242,7 +10245,7 @@
         <v>46267.79429876158</v>
       </c>
       <c r="W119">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X119" t="s">
         <v>183</v>
@@ -10254,10 +10257,10 @@
         <v>162</v>
       </c>
       <c r="AH119" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI119" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="120" spans="1:35">
@@ -10310,7 +10313,7 @@
         <v>46267.79429826389</v>
       </c>
       <c r="W120">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X120" t="s">
         <v>182</v>
@@ -10322,10 +10325,10 @@
         <v>163</v>
       </c>
       <c r="AH120" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI120" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="121" spans="1:35">
@@ -10384,7 +10387,7 @@
         <v>46267.72050385417</v>
       </c>
       <c r="W121">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X121" t="s">
         <v>180</v>
@@ -10396,10 +10399,10 @@
         <v>162</v>
       </c>
       <c r="AH121" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI121" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="122" spans="1:35">
@@ -10458,7 +10461,7 @@
         <v>46267.79434996528</v>
       </c>
       <c r="W122">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X122" t="s">
         <v>181</v>
@@ -10470,10 +10473,10 @@
         <v>162</v>
       </c>
       <c r="AH122" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI122" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="123" spans="1:35">
@@ -10532,7 +10535,7 @@
         <v>46267.79434864583</v>
       </c>
       <c r="W123">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X123" t="s">
         <v>181</v>
@@ -10544,10 +10547,10 @@
         <v>162</v>
       </c>
       <c r="AH123" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI123" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="124" spans="1:35">
@@ -10600,7 +10603,7 @@
         <v>46267.79435208334</v>
       </c>
       <c r="W124">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X124" t="s">
         <v>183</v>
@@ -10612,10 +10615,10 @@
         <v>162</v>
       </c>
       <c r="AH124" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI124" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="125" spans="1:35">
@@ -10668,7 +10671,7 @@
         <v>46267.79435100695</v>
       </c>
       <c r="W125">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X125" t="s">
         <v>182</v>
@@ -10680,10 +10683,10 @@
         <v>163</v>
       </c>
       <c r="AH125" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI125" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="126" spans="1:35">
@@ -10745,7 +10748,7 @@
         <v>46273.6788224074</v>
       </c>
       <c r="W126">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X126" t="s">
         <v>182</v>
@@ -10760,10 +10763,10 @@
         <v>163</v>
       </c>
       <c r="AH126" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI126" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="127" spans="1:35">
@@ -10825,7 +10828,7 @@
         <v>46273.67943539352</v>
       </c>
       <c r="W127">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X127" t="s">
         <v>182</v>
@@ -10840,10 +10843,10 @@
         <v>163</v>
       </c>
       <c r="AH127" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI127" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="128" spans="1:35">
@@ -10902,7 +10905,7 @@
         <v>46266.37636392361</v>
       </c>
       <c r="W128">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X128" t="s">
         <v>186</v>
@@ -10914,10 +10917,10 @@
         <v>166</v>
       </c>
       <c r="AH128" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI128" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="129" spans="1:35">
@@ -10976,7 +10979,7 @@
         <v>46266.37598834491</v>
       </c>
       <c r="W129">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X129" t="s">
         <v>186</v>
@@ -10988,10 +10991,10 @@
         <v>166</v>
       </c>
       <c r="AH129" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI129" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="130" spans="1:35">
@@ -11053,7 +11056,7 @@
         <v>46268.45899988426</v>
       </c>
       <c r="W130">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X130" t="s">
         <v>187</v>
@@ -11068,10 +11071,10 @@
         <v>166</v>
       </c>
       <c r="AH130" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI130" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="131" spans="1:35">
@@ -11130,7 +11133,7 @@
         <v>46266.45957881944</v>
       </c>
       <c r="W131">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X131" t="s">
         <v>185</v>
@@ -11142,10 +11145,10 @@
         <v>166</v>
       </c>
       <c r="AH131" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI131" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="132" spans="1:35">
@@ -11204,7 +11207,7 @@
         <v>46266.37645462963</v>
       </c>
       <c r="W132">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X132" t="s">
         <v>186</v>
@@ -11216,10 +11219,10 @@
         <v>166</v>
       </c>
       <c r="AH132" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI132" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="133" spans="1:35">
@@ -11278,7 +11281,7 @@
         <v>46266.37649475694</v>
       </c>
       <c r="W133">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X133" t="s">
         <v>186</v>
@@ -11290,10 +11293,10 @@
         <v>166</v>
       </c>
       <c r="AH133" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI133" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="134" spans="1:35">
@@ -11352,7 +11355,7 @@
         <v>46266.37591180555</v>
       </c>
       <c r="W134">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X134" t="s">
         <v>186</v>
@@ -11364,10 +11367,10 @@
         <v>166</v>
       </c>
       <c r="AH134" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI134" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="135" spans="1:35">
@@ -11429,7 +11432,7 @@
         <v>46268.45896508102</v>
       </c>
       <c r="W135">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X135" t="s">
         <v>187</v>
@@ -11444,10 +11447,10 @@
         <v>166</v>
       </c>
       <c r="AH135" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI135" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="136" spans="1:35">
@@ -11506,7 +11509,7 @@
         <v>46266.45946195602</v>
       </c>
       <c r="W136">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X136" t="s">
         <v>185</v>
@@ -11518,10 +11521,10 @@
         <v>166</v>
       </c>
       <c r="AH136" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI136" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="137" spans="1:35">
@@ -11580,7 +11583,7 @@
         <v>46266.37538684028</v>
       </c>
       <c r="W137">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X137" t="s">
         <v>186</v>
@@ -11592,10 +11595,10 @@
         <v>166</v>
       </c>
       <c r="AH137" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI137" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="138" spans="1:35">
@@ -11654,7 +11657,7 @@
         <v>46266.37538506944</v>
       </c>
       <c r="W138">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X138" t="s">
         <v>190</v>
@@ -11666,10 +11669,10 @@
         <v>166</v>
       </c>
       <c r="AH138" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI138" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="139" spans="1:35">
@@ -11731,7 +11734,7 @@
         <v>46268.45881820602</v>
       </c>
       <c r="W139">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X139" t="s">
         <v>187</v>
@@ -11746,10 +11749,10 @@
         <v>166</v>
       </c>
       <c r="AH139" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI139" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="140" spans="1:35">
@@ -11808,7 +11811,7 @@
         <v>46266.45895332176</v>
       </c>
       <c r="W140">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X140" t="s">
         <v>189</v>
@@ -11820,10 +11823,10 @@
         <v>166</v>
       </c>
       <c r="AH140" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI140" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="141" spans="1:35">
@@ -11882,7 +11885,7 @@
         <v>46266.45874105324</v>
       </c>
       <c r="W141">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X141" t="s">
         <v>185</v>
@@ -11894,10 +11897,10 @@
         <v>166</v>
       </c>
       <c r="AH141" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI141" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="142" spans="1:35">
@@ -11956,7 +11959,7 @@
         <v>46266.45873584491</v>
       </c>
       <c r="W142">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X142" t="s">
         <v>185</v>
@@ -11968,10 +11971,10 @@
         <v>166</v>
       </c>
       <c r="AH142" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI142" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="143" spans="1:35">
@@ -12030,7 +12033,7 @@
         <v>46273.6799675</v>
       </c>
       <c r="W143">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X143" t="s">
         <v>185</v>
@@ -12042,10 +12045,10 @@
         <v>166</v>
       </c>
       <c r="AH143" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI143" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="144" spans="1:35">
@@ -12104,7 +12107,7 @@
         <v>46273.55254606481</v>
       </c>
       <c r="W144">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X144" t="s">
         <v>186</v>
@@ -12116,10 +12119,10 @@
         <v>166</v>
       </c>
       <c r="AH144" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI144" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="145" spans="1:35">
@@ -12178,7 +12181,7 @@
         <v>46273.55252126158</v>
       </c>
       <c r="W145">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X145" t="s">
         <v>190</v>
@@ -12190,10 +12193,10 @@
         <v>166</v>
       </c>
       <c r="AH145" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI145" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="146" spans="1:35">
@@ -12252,7 +12255,7 @@
         <v>46273.55254163194</v>
       </c>
       <c r="W146">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X146" t="s">
         <v>187</v>
@@ -12264,10 +12267,10 @@
         <v>166</v>
       </c>
       <c r="AH146" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI146" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="147" spans="1:35">
@@ -12326,7 +12329,7 @@
         <v>46273.5525440162</v>
       </c>
       <c r="W147">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X147" t="s">
         <v>189</v>
@@ -12338,10 +12341,10 @@
         <v>166</v>
       </c>
       <c r="AH147" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI147" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="148" spans="1:35">
@@ -12400,7 +12403,7 @@
         <v>46273.84422141204</v>
       </c>
       <c r="W148">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X148" t="s">
         <v>185</v>
@@ -12412,10 +12415,10 @@
         <v>166</v>
       </c>
       <c r="AH148" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI148" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="149" spans="1:35">
@@ -12474,7 +12477,7 @@
         <v>46273.55254652778</v>
       </c>
       <c r="W149">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X149" t="s">
         <v>185</v>
@@ -12486,10 +12489,10 @@
         <v>166</v>
       </c>
       <c r="AH149" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI149" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="150" spans="1:35">
@@ -12551,7 +12554,7 @@
         <v>46268.45898549769</v>
       </c>
       <c r="W150">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X150" t="s">
         <v>187</v>
@@ -12566,10 +12569,10 @@
         <v>166</v>
       </c>
       <c r="AH150" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI150" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="151" spans="1:35">
@@ -12628,7 +12631,7 @@
         <v>46268.45915543981</v>
       </c>
       <c r="W151">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X151" t="s">
         <v>187</v>
@@ -12640,10 +12643,10 @@
         <v>166</v>
       </c>
       <c r="AH151" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI151" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="152" spans="1:35">
@@ -12702,7 +12705,7 @@
         <v>46273.56305208334</v>
       </c>
       <c r="W152">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X152" t="s">
         <v>185</v>
@@ -12714,10 +12717,10 @@
         <v>166</v>
       </c>
       <c r="AH152" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI152" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="153" spans="1:35">
@@ -12776,7 +12779,7 @@
         <v>46267.44505795139</v>
       </c>
       <c r="W153">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X153" t="s">
         <v>185</v>
@@ -12788,10 +12791,10 @@
         <v>166</v>
       </c>
       <c r="AH153" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI153" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="154" spans="1:35">
@@ -12847,7 +12850,7 @@
         <v>46266.04180934028</v>
       </c>
       <c r="W154">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="X154" t="s">
         <v>181</v>
@@ -12862,10 +12865,10 @@
         <v>167</v>
       </c>
       <c r="AH154" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI154" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="155" spans="1:35">
@@ -12921,7 +12924,7 @@
         <v>46266.08343295139</v>
       </c>
       <c r="W155">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="X155" t="s">
         <v>185</v>
@@ -12936,10 +12939,10 @@
         <v>167</v>
       </c>
       <c r="AH155" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI155" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="156" spans="1:35">
@@ -12995,7 +12998,7 @@
         <v>46266.08344398148</v>
       </c>
       <c r="W156">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="X156" t="s">
         <v>183</v>
@@ -13010,10 +13013,10 @@
         <v>167</v>
       </c>
       <c r="AH156" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI156" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="157" spans="1:35">
@@ -13069,7 +13072,7 @@
         <v>46266.25077376157</v>
       </c>
       <c r="W157">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="X157" t="s">
         <v>186</v>
@@ -13084,10 +13087,10 @@
         <v>167</v>
       </c>
       <c r="AH157" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI157" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="158" spans="1:35">
@@ -13143,7 +13146,7 @@
         <v>46266.25004302083</v>
       </c>
       <c r="W158">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="X158" t="s">
         <v>190</v>
@@ -13158,10 +13161,10 @@
         <v>167</v>
       </c>
       <c r="AH158" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI158" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="159" spans="1:35">
@@ -13217,7 +13220,7 @@
         <v>46266.25135543982</v>
       </c>
       <c r="W159">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="X159" t="s">
         <v>189</v>
@@ -13232,10 +13235,10 @@
         <v>167</v>
       </c>
       <c r="AH159" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI159" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="160" spans="1:35">
@@ -13291,7 +13294,7 @@
         <v>46266.25305</v>
       </c>
       <c r="W160">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="X160" t="s">
         <v>186</v>
@@ -13306,10 +13309,10 @@
         <v>167</v>
       </c>
       <c r="AH160" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI160" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="161" spans="1:35">
@@ -13365,7 +13368,7 @@
         <v>46266.25270034722</v>
       </c>
       <c r="W161">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="X161" t="s">
         <v>190</v>
@@ -13380,10 +13383,10 @@
         <v>167</v>
       </c>
       <c r="AH161" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI161" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="162" spans="1:35">
@@ -13439,7 +13442,7 @@
         <v>46266.25274991898</v>
       </c>
       <c r="W162">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="X162" t="s">
         <v>181</v>
@@ -13454,10 +13457,10 @@
         <v>167</v>
       </c>
       <c r="AH162" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI162" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="163" spans="1:35">
@@ -13513,7 +13516,7 @@
         <v>46266.25364633102</v>
       </c>
       <c r="W163">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="X163" t="s">
         <v>189</v>
@@ -13528,10 +13531,10 @@
         <v>167</v>
       </c>
       <c r="AH163" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI163" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="164" spans="1:35">
@@ -13587,7 +13590,7 @@
         <v>46266.25369826389</v>
       </c>
       <c r="W164">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="X164" t="s">
         <v>182</v>
@@ -13602,10 +13605,10 @@
         <v>167</v>
       </c>
       <c r="AH164" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI164" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="165" spans="1:35">
@@ -13661,7 +13664,7 @@
         <v>46266.25305112269</v>
       </c>
       <c r="W165">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="X165" t="s">
         <v>186</v>
@@ -13676,10 +13679,10 @@
         <v>167</v>
       </c>
       <c r="AH165" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI165" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="166" spans="1:35">
@@ -13735,7 +13738,7 @@
         <v>46266.25275173611</v>
       </c>
       <c r="W166">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="X166" t="s">
         <v>181</v>
@@ -13750,10 +13753,10 @@
         <v>167</v>
       </c>
       <c r="AH166" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI166" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="167" spans="1:35">
@@ -13809,7 +13812,7 @@
         <v>46266.25364869213</v>
       </c>
       <c r="W167">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="X167" t="s">
         <v>185</v>
@@ -13824,10 +13827,10 @@
         <v>167</v>
       </c>
       <c r="AH167" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI167" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="168" spans="1:35">
@@ -13883,7 +13886,7 @@
         <v>46266.25369988426</v>
       </c>
       <c r="W168">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="X168" t="s">
         <v>182</v>
@@ -13898,10 +13901,10 @@
         <v>167</v>
       </c>
       <c r="AH168" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI168" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="169" spans="1:35">
@@ -13960,7 +13963,7 @@
         <v>46268.62318445602</v>
       </c>
       <c r="W169">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X169" t="s">
         <v>186</v>
@@ -13975,10 +13978,10 @@
         <v>167</v>
       </c>
       <c r="AH169" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI169" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="170" spans="1:35">
@@ -14037,7 +14040,7 @@
         <v>46268.62319864584</v>
       </c>
       <c r="W170">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X170" t="s">
         <v>190</v>
@@ -14052,10 +14055,10 @@
         <v>167</v>
       </c>
       <c r="AH170" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI170" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="171" spans="1:35">
@@ -14114,7 +14117,7 @@
         <v>46268.62320026621</v>
       </c>
       <c r="W171">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X171" t="s">
         <v>187</v>
@@ -14129,10 +14132,10 @@
         <v>167</v>
       </c>
       <c r="AH171" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI171" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="172" spans="1:35">
@@ -14191,7 +14194,7 @@
         <v>46268.62320177083</v>
       </c>
       <c r="W172">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X172" t="s">
         <v>180</v>
@@ -14206,10 +14209,10 @@
         <v>167</v>
       </c>
       <c r="AH172" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI172" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="173" spans="1:35">
@@ -14268,7 +14271,7 @@
         <v>46268.62320378472</v>
       </c>
       <c r="W173">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X173" t="s">
         <v>181</v>
@@ -14283,10 +14286,10 @@
         <v>167</v>
       </c>
       <c r="AH173" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI173" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="174" spans="1:35">
@@ -14345,7 +14348,7 @@
         <v>46268.62320393518</v>
       </c>
       <c r="W174">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X174" t="s">
         <v>181</v>
@@ -14360,10 +14363,10 @@
         <v>167</v>
       </c>
       <c r="AH174" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI174" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="175" spans="1:35">
@@ -14422,7 +14425,7 @@
         <v>46268.62320697917</v>
       </c>
       <c r="W175">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X175" t="s">
         <v>189</v>
@@ -14437,10 +14440,10 @@
         <v>167</v>
       </c>
       <c r="AH175" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI175" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="176" spans="1:35">
@@ -14499,7 +14502,7 @@
         <v>46268.62320717592</v>
       </c>
       <c r="W176">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X176" t="s">
         <v>185</v>
@@ -14514,10 +14517,10 @@
         <v>167</v>
       </c>
       <c r="AH176" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI176" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="177" spans="1:35">
@@ -14576,7 +14579,7 @@
         <v>46268.62320732639</v>
       </c>
       <c r="W177">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X177" t="s">
         <v>185</v>
@@ -14591,10 +14594,10 @@
         <v>167</v>
       </c>
       <c r="AH177" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI177" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="178" spans="1:35">
@@ -14653,7 +14656,7 @@
         <v>46268.62320810185</v>
       </c>
       <c r="W178">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X178" t="s">
         <v>185</v>
@@ -14668,10 +14671,10 @@
         <v>167</v>
       </c>
       <c r="AH178" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI178" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="179" spans="1:35">
@@ -14730,7 +14733,7 @@
         <v>46268.6232125</v>
       </c>
       <c r="W179">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X179" t="s">
         <v>183</v>
@@ -14745,10 +14748,10 @@
         <v>167</v>
       </c>
       <c r="AH179" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI179" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="180" spans="1:35">
@@ -14807,7 +14810,7 @@
         <v>46268.62321412037</v>
       </c>
       <c r="W180">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X180" t="s">
         <v>182</v>
@@ -14822,10 +14825,10 @@
         <v>167</v>
       </c>
       <c r="AH180" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI180" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="181" spans="1:35">
@@ -14884,7 +14887,7 @@
         <v>46268.6232128125</v>
       </c>
       <c r="W181">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X181" t="s">
         <v>184</v>
@@ -14899,10 +14902,10 @@
         <v>167</v>
       </c>
       <c r="AH181" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI181" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="182" spans="1:35">
@@ -14961,7 +14964,7 @@
         <v>46268.62321296296</v>
       </c>
       <c r="W182">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X182" t="s">
         <v>184</v>
@@ -14976,10 +14979,10 @@
         <v>167</v>
       </c>
       <c r="AH182" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI182" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="183" spans="1:35">
@@ -15035,7 +15038,7 @@
         <v>46269.41908927084</v>
       </c>
       <c r="W183">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X183" t="s">
         <v>186</v>
@@ -15047,10 +15050,10 @@
         <v>167</v>
       </c>
       <c r="AH183" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI183" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="184" spans="1:35">
@@ -15106,7 +15109,7 @@
         <v>46269.41910457176</v>
       </c>
       <c r="W184">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X184" t="s">
         <v>190</v>
@@ -15118,10 +15121,10 @@
         <v>167</v>
       </c>
       <c r="AH184" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI184" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="185" spans="1:35">
@@ -15177,7 +15180,7 @@
         <v>46269.37885223379</v>
       </c>
       <c r="W185">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X185" t="s">
         <v>187</v>
@@ -15189,10 +15192,10 @@
         <v>167</v>
       </c>
       <c r="AH185" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI185" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="186" spans="1:35">
@@ -15248,7 +15251,7 @@
         <v>46269.3782503125</v>
       </c>
       <c r="W186">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X186" t="s">
         <v>180</v>
@@ -15260,10 +15263,10 @@
         <v>167</v>
       </c>
       <c r="AH186" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI186" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="187" spans="1:35">
@@ -15319,7 +15322,7 @@
         <v>46269.41913152778</v>
       </c>
       <c r="W187">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X187" t="s">
         <v>181</v>
@@ -15331,10 +15334,10 @@
         <v>167</v>
       </c>
       <c r="AH187" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI187" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="188" spans="1:35">
@@ -15390,7 +15393,7 @@
         <v>46269.41913775463</v>
       </c>
       <c r="W188">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X188" t="s">
         <v>181</v>
@@ -15402,10 +15405,10 @@
         <v>167</v>
       </c>
       <c r="AH188" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI188" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="189" spans="1:35">
@@ -15461,7 +15464,7 @@
         <v>46268.7596207176</v>
       </c>
       <c r="W189">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X189" t="s">
         <v>186</v>
@@ -15473,10 +15476,10 @@
         <v>54</v>
       </c>
       <c r="AH189" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI189" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="190" spans="1:35">
@@ -15532,7 +15535,7 @@
         <v>46268.75963109954</v>
       </c>
       <c r="W190">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X190" t="s">
         <v>190</v>
@@ -15544,10 +15547,10 @@
         <v>54</v>
       </c>
       <c r="AH190" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI190" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="191" spans="1:35">
@@ -15603,7 +15606,7 @@
         <v>46268.75963225694</v>
       </c>
       <c r="W191">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X191" t="s">
         <v>187</v>
@@ -15615,10 +15618,10 @@
         <v>54</v>
       </c>
       <c r="AH191" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI191" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="192" spans="1:35">
@@ -15674,7 +15677,7 @@
         <v>46268.75963348379</v>
       </c>
       <c r="W192">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X192" t="s">
         <v>180</v>
@@ -15686,10 +15689,10 @@
         <v>54</v>
       </c>
       <c r="AH192" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI192" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="193" spans="1:35">
@@ -15745,7 +15748,7 @@
         <v>46268.75963414352</v>
       </c>
       <c r="W193">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X193" t="s">
         <v>181</v>
@@ -15757,10 +15760,10 @@
         <v>168</v>
       </c>
       <c r="AH193" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI193" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="194" spans="1:35">
@@ -15816,7 +15819,7 @@
         <v>46268.62326365741</v>
       </c>
       <c r="W194">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X194" t="s">
         <v>181</v>
@@ -15828,10 +15831,10 @@
         <v>55</v>
       </c>
       <c r="AH194" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI194" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="195" spans="1:35">
@@ -15887,7 +15890,7 @@
         <v>46268.75963472222</v>
       </c>
       <c r="W195">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X195" t="s">
         <v>189</v>
@@ -15899,10 +15902,10 @@
         <v>54</v>
       </c>
       <c r="AH195" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI195" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="196" spans="1:35">
@@ -15958,7 +15961,7 @@
         <v>46268.75963475694</v>
       </c>
       <c r="W196">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X196" t="s">
         <v>185</v>
@@ -15970,10 +15973,10 @@
         <v>54</v>
       </c>
       <c r="AH196" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI196" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="197" spans="1:35">
@@ -16029,7 +16032,7 @@
         <v>46268.75963506944</v>
       </c>
       <c r="W197">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X197" t="s">
         <v>185</v>
@@ -16041,10 +16044,10 @@
         <v>54</v>
       </c>
       <c r="AH197" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI197" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="198" spans="1:35">
@@ -16100,7 +16103,7 @@
         <v>46268.7596360301</v>
       </c>
       <c r="W198">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X198" t="s">
         <v>185</v>
@@ -16112,10 +16115,10 @@
         <v>168</v>
       </c>
       <c r="AH198" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI198" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="199" spans="1:35">
@@ -16171,7 +16174,7 @@
         <v>46268.62327121528</v>
       </c>
       <c r="W199">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X199" t="s">
         <v>183</v>
@@ -16183,10 +16186,10 @@
         <v>54</v>
       </c>
       <c r="AH199" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI199" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="200" spans="1:35">
@@ -16242,7 +16245,7 @@
         <v>46268.75963931713</v>
       </c>
       <c r="W200">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X200" t="s">
         <v>182</v>
@@ -16254,10 +16257,10 @@
         <v>168</v>
       </c>
       <c r="AH200" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI200" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="201" spans="1:35">
@@ -16313,7 +16316,7 @@
         <v>46268.75963822917</v>
       </c>
       <c r="W201">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X201" t="s">
         <v>184</v>
@@ -16325,10 +16328,10 @@
         <v>54</v>
       </c>
       <c r="AH201" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI201" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="202" spans="1:35">
@@ -16384,7 +16387,7 @@
         <v>46268.75963857639</v>
       </c>
       <c r="W202">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X202" t="s">
         <v>184</v>
@@ -16396,10 +16399,10 @@
         <v>54</v>
       </c>
       <c r="AH202" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI202" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="203" spans="1:35">
@@ -16455,7 +16458,7 @@
         <v>46269.41908901621</v>
       </c>
       <c r="W203">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X203" t="s">
         <v>186</v>
@@ -16467,10 +16470,10 @@
         <v>54</v>
       </c>
       <c r="AH203" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI203" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="204" spans="1:35">
@@ -16526,7 +16529,7 @@
         <v>46269.41910425926</v>
       </c>
       <c r="W204">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X204" t="s">
         <v>190</v>
@@ -16538,10 +16541,10 @@
         <v>54</v>
       </c>
       <c r="AH204" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI204" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="205" spans="1:35">
@@ -16597,7 +16600,7 @@
         <v>46269.37890997685</v>
       </c>
       <c r="W205">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X205" t="s">
         <v>187</v>
@@ -16609,10 +16612,10 @@
         <v>54</v>
       </c>
       <c r="AH205" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI205" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="206" spans="1:35">
@@ -16668,7 +16671,7 @@
         <v>46269.37833320602</v>
       </c>
       <c r="W206">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X206" t="s">
         <v>180</v>
@@ -16680,10 +16683,10 @@
         <v>54</v>
       </c>
       <c r="AH206" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI206" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="207" spans="1:35">
@@ -16739,7 +16742,7 @@
         <v>46269.41913112268</v>
       </c>
       <c r="W207">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X207" t="s">
         <v>181</v>
@@ -16751,10 +16754,10 @@
         <v>168</v>
       </c>
       <c r="AH207" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI207" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="208" spans="1:35">
@@ -16810,7 +16813,7 @@
         <v>46269.41913740741</v>
       </c>
       <c r="W208">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X208" t="s">
         <v>181</v>
@@ -16822,10 +16825,10 @@
         <v>55</v>
       </c>
       <c r="AH208" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI208" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="209" spans="1:35">
@@ -16881,7 +16884,7 @@
         <v>46267.66131466435</v>
       </c>
       <c r="W209">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X209" t="s">
         <v>190</v>
@@ -16896,10 +16899,10 @@
         <v>54</v>
       </c>
       <c r="AH209" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI209" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="210" spans="1:35">
@@ -16955,7 +16958,7 @@
         <v>46266.21595836805</v>
       </c>
       <c r="W210">
-        <v>-42</v>
+        <v>-41</v>
       </c>
       <c r="X210" t="s">
         <v>190</v>
@@ -16970,10 +16973,10 @@
         <v>54</v>
       </c>
       <c r="AH210" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI210" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="211" spans="1:35">
@@ -17029,7 +17032,7 @@
         <v>46266.21572962963</v>
       </c>
       <c r="W211">
-        <v>-42</v>
+        <v>-41</v>
       </c>
       <c r="X211" t="s">
         <v>186</v>
@@ -17044,10 +17047,10 @@
         <v>54</v>
       </c>
       <c r="AH211" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI211" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="212" spans="1:35">
@@ -17103,7 +17106,7 @@
         <v>46266.21550011574</v>
       </c>
       <c r="W212">
-        <v>-42</v>
+        <v>-41</v>
       </c>
       <c r="X212" t="s">
         <v>187</v>
@@ -17118,10 +17121,10 @@
         <v>54</v>
       </c>
       <c r="AH212" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI212" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="213" spans="1:35">
@@ -17177,7 +17180,7 @@
         <v>46266.00006921296</v>
       </c>
       <c r="W213">
-        <v>-42</v>
+        <v>-41</v>
       </c>
       <c r="X213" t="s">
         <v>186</v>
@@ -17189,10 +17192,10 @@
         <v>54</v>
       </c>
       <c r="AH213" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI213" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="214" spans="1:35">
@@ -17248,7 +17251,7 @@
         <v>46266.00006921296</v>
       </c>
       <c r="W214">
-        <v>-42</v>
+        <v>-41</v>
       </c>
       <c r="X214" t="s">
         <v>190</v>
@@ -17260,10 +17263,10 @@
         <v>54</v>
       </c>
       <c r="AH214" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI214" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="215" spans="1:35">
@@ -17316,7 +17319,7 @@
         <v>46269.57097615741</v>
       </c>
       <c r="W215">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X215" t="s">
         <v>187</v>
@@ -17328,10 +17331,10 @@
         <v>0</v>
       </c>
       <c r="AH215" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI215" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="216" spans="1:35">
@@ -17384,7 +17387,7 @@
         <v>46266.00006921296</v>
       </c>
       <c r="W216">
-        <v>-42</v>
+        <v>-41</v>
       </c>
       <c r="X216" t="s">
         <v>187</v>
@@ -17393,10 +17396,10 @@
         <v>0</v>
       </c>
       <c r="AH216" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI216" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="217" spans="1:35">
@@ -17452,7 +17455,7 @@
         <v>46269.46753030093</v>
       </c>
       <c r="W217">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X217" t="s">
         <v>183</v>
@@ -17464,13 +17467,13 @@
         <v>0</v>
       </c>
       <c r="AC217" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AH217" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI217" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="218" spans="1:35">
@@ -17532,7 +17535,7 @@
         <v>46279.66710767361</v>
       </c>
       <c r="W218">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="X218" t="s">
         <v>185</v>
@@ -17547,10 +17550,10 @@
         <v>160</v>
       </c>
       <c r="AH218" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI218" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="219" spans="1:35">
@@ -17609,7 +17612,7 @@
         <v>46279.62681744213</v>
       </c>
       <c r="W219">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="X219" t="s">
         <v>189</v>
@@ -17621,10 +17624,10 @@
         <v>153</v>
       </c>
       <c r="AH219" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI219" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="220" spans="1:35">
@@ -17683,7 +17686,7 @@
         <v>46279.66707821759</v>
       </c>
       <c r="W220">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="X220" t="s">
         <v>185</v>
@@ -17695,10 +17698,10 @@
         <v>160</v>
       </c>
       <c r="AH220" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI220" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="221" spans="1:35">
@@ -17757,7 +17760,7 @@
         <v>46279.6268503125</v>
       </c>
       <c r="W221">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="X221" t="s">
         <v>189</v>
@@ -17769,10 +17772,10 @@
         <v>153</v>
       </c>
       <c r="AH221" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI221" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="222" spans="1:35">
@@ -17831,7 +17834,7 @@
         <v>46279.66698128472</v>
       </c>
       <c r="W222">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="X222" t="s">
         <v>185</v>
@@ -17843,10 +17846,10 @@
         <v>160</v>
       </c>
       <c r="AH222" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI222" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="223" spans="1:35">
@@ -17902,7 +17905,7 @@
         <v>46279.66929922454</v>
       </c>
       <c r="W223">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="X223" t="s">
         <v>186</v>
@@ -17917,10 +17920,10 @@
         <v>157</v>
       </c>
       <c r="AH223" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI223" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="224" spans="1:35">
@@ -17979,7 +17982,7 @@
         <v>46279.7222346412</v>
       </c>
       <c r="W224">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="X224" t="s">
         <v>187</v>
@@ -17994,10 +17997,10 @@
         <v>154</v>
       </c>
       <c r="AH224" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI224" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="225" spans="1:35">
@@ -18056,7 +18059,7 @@
         <v>46279.63250563657</v>
       </c>
       <c r="W225">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="X225" t="s">
         <v>180</v>
@@ -18071,10 +18074,10 @@
         <v>159</v>
       </c>
       <c r="AH225" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI225" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="226" spans="1:35">
@@ -18133,7 +18136,7 @@
         <v>46279.72223498843</v>
       </c>
       <c r="W226">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="X226" t="s">
         <v>181</v>
@@ -18148,10 +18151,10 @@
         <v>154</v>
       </c>
       <c r="AH226" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI226" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="227" spans="1:35">
@@ -18210,7 +18213,7 @@
         <v>46279.72223515046</v>
       </c>
       <c r="W227">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="X227" t="s">
         <v>181</v>
@@ -18225,10 +18228,10 @@
         <v>154</v>
       </c>
       <c r="AH227" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI227" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="228" spans="1:35">
@@ -18287,7 +18290,7 @@
         <v>46274.60593387731</v>
       </c>
       <c r="W228">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X228" t="s">
         <v>186</v>
@@ -18302,10 +18305,10 @@
         <v>157</v>
       </c>
       <c r="AH228" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI228" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="229" spans="1:35">
@@ -18367,7 +18370,7 @@
         <v>46274.47210818287</v>
       </c>
       <c r="W229">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X229" t="s">
         <v>187</v>
@@ -18382,10 +18385,10 @@
         <v>154</v>
       </c>
       <c r="AH229" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI229" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="230" spans="1:35">
@@ -18447,7 +18450,7 @@
         <v>46276.48975401621</v>
       </c>
       <c r="W230">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X230" t="s">
         <v>181</v>
@@ -18462,10 +18465,10 @@
         <v>154</v>
       </c>
       <c r="AH230" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI230" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="231" spans="1:35">
@@ -18527,7 +18530,7 @@
         <v>46279.38429019676</v>
       </c>
       <c r="W231">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X231" t="s">
         <v>181</v>
@@ -18542,10 +18545,10 @@
         <v>154</v>
       </c>
       <c r="AH231" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI231" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="232" spans="1:35">
@@ -18607,7 +18610,7 @@
         <v>46274.48792050926</v>
       </c>
       <c r="W232">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X232" t="s">
         <v>185</v>
@@ -18622,10 +18625,10 @@
         <v>160</v>
       </c>
       <c r="AH232" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI232" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="233" spans="1:35">
@@ -18687,7 +18690,7 @@
         <v>46274.588374375</v>
       </c>
       <c r="W233">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X233" t="s">
         <v>183</v>
@@ -18702,10 +18705,10 @@
         <v>155</v>
       </c>
       <c r="AH233" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI233" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="234" spans="1:35">
@@ -18764,7 +18767,7 @@
         <v>46274.34198912037</v>
       </c>
       <c r="W234">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X234" t="s">
         <v>182</v>
@@ -18776,10 +18779,10 @@
         <v>156</v>
       </c>
       <c r="AH234" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI234" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="235" spans="1:35">
@@ -18835,7 +18838,7 @@
         <v>46279.6693627662</v>
       </c>
       <c r="W235">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X235" t="s">
         <v>186</v>
@@ -18850,10 +18853,10 @@
         <v>157</v>
       </c>
       <c r="AH235" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI235" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="236" spans="1:35">
@@ -18915,7 +18918,7 @@
         <v>46279.5886965625</v>
       </c>
       <c r="W236">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X236" t="s">
         <v>187</v>
@@ -18930,10 +18933,10 @@
         <v>154</v>
       </c>
       <c r="AH236" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI236" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="237" spans="1:35">
@@ -18992,7 +18995,7 @@
         <v>46279.40189383102</v>
       </c>
       <c r="W237">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X237" t="s">
         <v>180</v>
@@ -19007,10 +19010,10 @@
         <v>159</v>
       </c>
       <c r="AH237" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI237" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="238" spans="1:35">
@@ -19072,7 +19075,7 @@
         <v>46279.58878520833</v>
       </c>
       <c r="W238">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X238" t="s">
         <v>181</v>
@@ -19087,10 +19090,10 @@
         <v>154</v>
       </c>
       <c r="AH238" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI238" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="239" spans="1:35">
@@ -19152,7 +19155,7 @@
         <v>46279.58873577546</v>
       </c>
       <c r="W239">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X239" t="s">
         <v>181</v>
@@ -19167,10 +19170,10 @@
         <v>154</v>
       </c>
       <c r="AH239" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI239" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="240" spans="1:35">
@@ -19229,7 +19232,7 @@
         <v>46279.63255</v>
       </c>
       <c r="W240">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X240" t="s">
         <v>189</v>
@@ -19244,10 +19247,10 @@
         <v>153</v>
       </c>
       <c r="AH240" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI240" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="241" spans="1:35">
@@ -19306,7 +19309,7 @@
         <v>46276.63187557871</v>
       </c>
       <c r="W241">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X241" t="s">
         <v>185</v>
@@ -19321,10 +19324,10 @@
         <v>160</v>
       </c>
       <c r="AH241" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI241" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="242" spans="1:35">
@@ -19383,7 +19386,7 @@
         <v>46279.6265846875</v>
       </c>
       <c r="W242">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X242" t="s">
         <v>183</v>
@@ -19398,10 +19401,10 @@
         <v>155</v>
       </c>
       <c r="AH242" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI242" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="243" spans="1:35">
@@ -19460,7 +19463,7 @@
         <v>46279.63255401621</v>
       </c>
       <c r="W243">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X243" t="s">
         <v>182</v>
@@ -19475,10 +19478,10 @@
         <v>156</v>
       </c>
       <c r="AH243" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI243" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="244" spans="1:35">
@@ -19540,7 +19543,7 @@
         <v>46279.66713805556</v>
       </c>
       <c r="W244">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="X244" t="s">
         <v>185</v>
@@ -19555,10 +19558,10 @@
         <v>160</v>
       </c>
       <c r="AH244" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI244" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="245" spans="1:35">
@@ -19614,7 +19617,7 @@
         <v>46275.39631951389</v>
       </c>
       <c r="W245">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X245" t="s">
         <v>181</v>
@@ -19629,10 +19632,10 @@
         <v>154</v>
       </c>
       <c r="AH245" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI245" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="246" spans="1:35">
@@ -19688,7 +19691,7 @@
         <v>46275.39631994213</v>
       </c>
       <c r="W246">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X246" t="s">
         <v>181</v>
@@ -19703,10 +19706,10 @@
         <v>154</v>
       </c>
       <c r="AH246" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI246" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="247" spans="1:35">
@@ -19762,7 +19765,7 @@
         <v>46276.37795540509</v>
       </c>
       <c r="W247">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="X247" t="s">
         <v>183</v>
@@ -19774,10 +19777,10 @@
         <v>165</v>
       </c>
       <c r="AH247" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI247" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="248" spans="1:35">
@@ -19839,7 +19842,7 @@
         <v>46276.66923222222</v>
       </c>
       <c r="W248">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X248" t="s">
         <v>180</v>
@@ -19854,10 +19857,10 @@
         <v>161</v>
       </c>
       <c r="AH248" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI248" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="249" spans="1:35">
@@ -19916,7 +19919,7 @@
         <v>46276.40669469907</v>
       </c>
       <c r="W249">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X249" t="s">
         <v>181</v>
@@ -19928,10 +19931,10 @@
         <v>162</v>
       </c>
       <c r="AH249" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI249" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="250" spans="1:35">
@@ -19993,7 +19996,7 @@
         <v>46276.64773491898</v>
       </c>
       <c r="W250">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X250" t="s">
         <v>181</v>
@@ -20008,10 +20011,10 @@
         <v>162</v>
       </c>
       <c r="AH250" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI250" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="251" spans="1:35">
@@ -20070,7 +20073,7 @@
         <v>46276.39101108797</v>
       </c>
       <c r="W251">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X251" t="s">
         <v>183</v>
@@ -20085,18 +20088,18 @@
         <v>165</v>
       </c>
       <c r="AH251" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI251" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="252" spans="1:35">
       <c r="A252">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B252" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C252" t="s">
         <v>50</v>
@@ -20125,9 +20128,6 @@
       <c r="N252" s="1">
         <v>46276</v>
       </c>
-      <c r="O252" t="s">
-        <v>143</v>
-      </c>
       <c r="P252">
         <v>8</v>
       </c>
@@ -20135,7 +20135,7 @@
         <v>2026</v>
       </c>
       <c r="R252">
-        <v>18187261</v>
+        <v>18186995</v>
       </c>
       <c r="S252" t="s">
         <v>164</v>
@@ -20144,13 +20144,13 @@
         <v>162</v>
       </c>
       <c r="U252" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="V252" s="1">
-        <v>46276.66651596065</v>
+        <v>46279.74982357639</v>
       </c>
       <c r="W252">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X252" t="s">
         <v>184</v>
@@ -20165,33 +20165,33 @@
         <v>164</v>
       </c>
       <c r="AH252" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI252" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="253" spans="1:35">
       <c r="A253">
-        <v>6627</v>
+        <v>6963</v>
       </c>
       <c r="B253" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C253" t="s">
         <v>50</v>
       </c>
       <c r="D253" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E253" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F253" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G253">
-        <v>1866</v>
+        <v>6805</v>
       </c>
       <c r="H253">
         <v>0</v>
@@ -20200,10 +20200,13 @@
         <v>62</v>
       </c>
       <c r="J253" t="s">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="N253" s="1">
-        <v>46274</v>
+        <v>46276</v>
+      </c>
+      <c r="O253" t="s">
+        <v>143</v>
       </c>
       <c r="P253">
         <v>8</v>
@@ -20212,10 +20215,10 @@
         <v>2026</v>
       </c>
       <c r="R253">
-        <v>17968368</v>
+        <v>18187261</v>
       </c>
       <c r="S253" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="T253" t="s">
         <v>162</v>
@@ -20224,13 +20227,13 @@
         <v>179</v>
       </c>
       <c r="V253" s="1">
-        <v>46274.36843923611</v>
+        <v>46276.66651596065</v>
       </c>
       <c r="W253">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="X253" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="Y253" t="s">
         <v>274</v>
@@ -20239,33 +20242,33 @@
         <v>0</v>
       </c>
       <c r="AC253" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="AH253" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AI253" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="254" spans="1:35">
       <c r="A254">
-        <v>6962</v>
+        <v>6627</v>
       </c>
       <c r="B254" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C254" t="s">
         <v>50</v>
       </c>
       <c r="D254" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E254" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F254" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G254">
         <v>1866</v>
@@ -20289,10 +20292,10 @@
         <v>2026</v>
       </c>
       <c r="R254">
-        <v>18186946</v>
+        <v>17968368</v>
       </c>
       <c r="S254" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="T254" t="s">
         <v>162</v>
@@ -20301,13 +20304,13 @@
         <v>179</v>
       </c>
       <c r="V254" s="1">
-        <v>46274.66470667824</v>
+        <v>46274.36843923611</v>
       </c>
       <c r="W254">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X254" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="Y254" t="s">
         <v>275</v>
@@ -20316,21 +20319,21 @@
         <v>0</v>
       </c>
       <c r="AC254" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AH254" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI254" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="255" spans="1:35">
       <c r="A255">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B255" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C255" t="s">
         <v>50</v>
@@ -20366,7 +20369,7 @@
         <v>2026</v>
       </c>
       <c r="R255">
-        <v>18187212</v>
+        <v>18186946</v>
       </c>
       <c r="S255" t="s">
         <v>164</v>
@@ -20378,10 +20381,10 @@
         <v>179</v>
       </c>
       <c r="V255" s="1">
-        <v>46274.74452168981</v>
+        <v>46274.66470667824</v>
       </c>
       <c r="W255">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X255" t="s">
         <v>184</v>
@@ -20396,33 +20399,33 @@
         <v>164</v>
       </c>
       <c r="AH255" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI255" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="256" spans="1:35">
       <c r="A256">
-        <v>6548</v>
+        <v>6963</v>
       </c>
       <c r="B256" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C256" t="s">
         <v>50</v>
       </c>
       <c r="D256" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E256" t="s">
         <v>54</v>
       </c>
       <c r="F256" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G256">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="H256">
         <v>0</v>
@@ -20431,14 +20434,11 @@
         <v>62</v>
       </c>
       <c r="J256" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N256" s="1">
         <v>46274</v>
       </c>
-      <c r="O256" t="s">
-        <v>141</v>
-      </c>
       <c r="P256">
         <v>8</v>
       </c>
@@ -20446,10 +20446,10 @@
         <v>2026</v>
       </c>
       <c r="R256">
-        <v>17988543</v>
+        <v>18187212</v>
       </c>
       <c r="S256" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="T256" t="s">
         <v>162</v>
@@ -20458,13 +20458,13 @@
         <v>179</v>
       </c>
       <c r="V256" s="1">
-        <v>46274.64801501157</v>
+        <v>46274.74452168981</v>
       </c>
       <c r="W256">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X256" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="Y256" t="s">
         <v>277</v>
@@ -20473,21 +20473,21 @@
         <v>0</v>
       </c>
       <c r="AC256" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="AH256" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI256" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="257" spans="1:35">
       <c r="A257">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B257" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C257" t="s">
         <v>50</v>
@@ -20496,7 +20496,7 @@
         <v>51</v>
       </c>
       <c r="E257" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F257" t="s">
         <v>56</v>
@@ -20516,6 +20516,9 @@
       <c r="N257" s="1">
         <v>46274</v>
       </c>
+      <c r="O257" t="s">
+        <v>141</v>
+      </c>
       <c r="P257">
         <v>8</v>
       </c>
@@ -20523,10 +20526,10 @@
         <v>2026</v>
       </c>
       <c r="R257">
-        <v>17968379</v>
+        <v>17988543</v>
       </c>
       <c r="S257" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="T257" t="s">
         <v>162</v>
@@ -20535,45 +20538,48 @@
         <v>179</v>
       </c>
       <c r="V257" s="1">
-        <v>46274.36695243056</v>
+        <v>46274.64801501157</v>
       </c>
       <c r="W257">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X257" t="s">
-        <v>181</v>
+        <v>180</v>
+      </c>
+      <c r="Y257" t="s">
+        <v>278</v>
       </c>
       <c r="AB257">
         <v>0</v>
       </c>
       <c r="AC257" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AH257" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI257" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="258" spans="1:35">
       <c r="A258">
-        <v>6945</v>
+        <v>6627</v>
       </c>
       <c r="B258" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C258" t="s">
         <v>50</v>
       </c>
       <c r="D258" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E258" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F258" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G258">
         <v>1867</v>
@@ -20590,9 +20596,6 @@
       <c r="N258" s="1">
         <v>46274</v>
       </c>
-      <c r="O258" t="s">
-        <v>143</v>
-      </c>
       <c r="P258">
         <v>8</v>
       </c>
@@ -20600,51 +20603,51 @@
         <v>2026</v>
       </c>
       <c r="R258">
-        <v>18220182</v>
+        <v>17968379</v>
       </c>
       <c r="S258" t="s">
-        <v>165</v>
+        <v>162</v>
+      </c>
+      <c r="T258" t="s">
+        <v>162</v>
       </c>
       <c r="U258" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="V258" s="1">
-        <v>46276.4084265625</v>
+        <v>46274.36695243056</v>
       </c>
       <c r="W258">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X258" t="s">
-        <v>183</v>
-      </c>
-      <c r="Y258" t="s">
-        <v>278</v>
+        <v>181</v>
       </c>
       <c r="AB258">
         <v>0</v>
       </c>
       <c r="AC258" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="AH258" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI258" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="259" spans="1:35">
       <c r="A259">
-        <v>6962</v>
+        <v>6945</v>
       </c>
       <c r="B259" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C259" t="s">
         <v>50</v>
       </c>
       <c r="D259" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E259" t="s">
         <v>54</v>
@@ -20667,6 +20670,9 @@
       <c r="N259" s="1">
         <v>46274</v>
       </c>
+      <c r="O259" t="s">
+        <v>143</v>
+      </c>
       <c r="P259">
         <v>8</v>
       </c>
@@ -20674,45 +20680,45 @@
         <v>2026</v>
       </c>
       <c r="R259">
-        <v>18186953</v>
+        <v>18220182</v>
       </c>
       <c r="S259" t="s">
-        <v>164</v>
-      </c>
-      <c r="T259" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="U259" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="V259" s="1">
-        <v>46274.7274781713</v>
+        <v>46276.4084265625</v>
       </c>
       <c r="W259">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X259" t="s">
-        <v>184</v>
+        <v>183</v>
+      </c>
+      <c r="Y259" t="s">
+        <v>279</v>
       </c>
       <c r="AB259">
         <v>0</v>
       </c>
       <c r="AC259" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AH259" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI259" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="260" spans="1:35">
       <c r="A260">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B260" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C260" t="s">
         <v>50</v>
@@ -20748,7 +20754,7 @@
         <v>2026</v>
       </c>
       <c r="R260">
-        <v>18187219</v>
+        <v>18186953</v>
       </c>
       <c r="S260" t="s">
         <v>164</v>
@@ -20760,10 +20766,10 @@
         <v>179</v>
       </c>
       <c r="V260" s="1">
-        <v>46274.74558746528</v>
+        <v>46274.7274781713</v>
       </c>
       <c r="W260">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X260" t="s">
         <v>184</v>
@@ -20775,24 +20781,24 @@
         <v>164</v>
       </c>
       <c r="AH260" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI260" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="261" spans="1:35">
       <c r="A261">
-        <v>6949</v>
+        <v>6963</v>
       </c>
       <c r="B261" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C261" t="s">
         <v>50</v>
       </c>
       <c r="D261" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E261" t="s">
         <v>54</v>
@@ -20801,19 +20807,19 @@
         <v>57</v>
       </c>
       <c r="G261">
-        <v>6886</v>
+        <v>1867</v>
       </c>
       <c r="H261">
-        <v>1862</v>
+        <v>0</v>
       </c>
       <c r="I261" t="s">
         <v>62</v>
       </c>
       <c r="J261" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="N261" s="1">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="P261">
         <v>8</v>
@@ -20822,10 +20828,10 @@
         <v>2026</v>
       </c>
       <c r="R261">
-        <v>18214907</v>
+        <v>18187219</v>
       </c>
       <c r="S261" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="T261" t="s">
         <v>162</v>
@@ -20834,33 +20840,33 @@
         <v>179</v>
       </c>
       <c r="V261" s="1">
-        <v>46275.79245582176</v>
+        <v>46274.74558746528</v>
       </c>
       <c r="W261">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="X261" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AB261">
         <v>0</v>
       </c>
       <c r="AC261" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AH261" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AI261" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="262" spans="1:35">
       <c r="A262">
-        <v>5417</v>
+        <v>6949</v>
       </c>
       <c r="B262" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C262" t="s">
         <v>50</v>
@@ -20872,22 +20878,22 @@
         <v>54</v>
       </c>
       <c r="F262" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G262">
-        <v>6806</v>
+        <v>6886</v>
       </c>
       <c r="H262">
-        <v>0</v>
+        <v>1862</v>
       </c>
       <c r="I262" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J262" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="N262" s="1">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="P262">
         <v>8</v>
@@ -20896,51 +20902,51 @@
         <v>2026</v>
       </c>
       <c r="R262">
-        <v>17399230</v>
+        <v>18214907</v>
       </c>
       <c r="S262" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="T262" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="U262" t="s">
         <v>179</v>
       </c>
       <c r="V262" s="1">
-        <v>46276.49596842592</v>
+        <v>46275.79245582176</v>
       </c>
       <c r="W262">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X262" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="AB262">
         <v>0</v>
       </c>
       <c r="AC262" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="AH262" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AI262" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="263" spans="1:35">
       <c r="A263">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B263" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C263" t="s">
         <v>50</v>
       </c>
       <c r="D263" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E263" t="s">
         <v>54</v>
@@ -20970,7 +20976,7 @@
         <v>2026</v>
       </c>
       <c r="R263">
-        <v>16962308</v>
+        <v>17399230</v>
       </c>
       <c r="S263" t="s">
         <v>166</v>
@@ -20982,13 +20988,13 @@
         <v>179</v>
       </c>
       <c r="V263" s="1">
-        <v>46276.53874935185</v>
+        <v>46276.49596842592</v>
       </c>
       <c r="W263">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X263" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="AB263">
         <v>0</v>
@@ -20997,24 +21003,24 @@
         <v>166</v>
       </c>
       <c r="AH263" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI263" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="264" spans="1:35">
       <c r="A264">
-        <v>6486</v>
+        <v>6404</v>
       </c>
       <c r="B264" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C264" t="s">
         <v>50</v>
       </c>
       <c r="D264" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E264" t="s">
         <v>54</v>
@@ -21044,7 +21050,7 @@
         <v>2026</v>
       </c>
       <c r="R264">
-        <v>16976187</v>
+        <v>16962308</v>
       </c>
       <c r="S264" t="s">
         <v>166</v>
@@ -21056,13 +21062,13 @@
         <v>179</v>
       </c>
       <c r="V264" s="1">
-        <v>46276.49597027778</v>
+        <v>46276.53874935185</v>
       </c>
       <c r="W264">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X264" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="AB264">
         <v>0</v>
@@ -21071,24 +21077,24 @@
         <v>166</v>
       </c>
       <c r="AH264" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI264" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="265" spans="1:35">
       <c r="A265">
-        <v>6703</v>
+        <v>6486</v>
       </c>
       <c r="B265" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C265" t="s">
         <v>50</v>
       </c>
       <c r="D265" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E265" t="s">
         <v>54</v>
@@ -21118,7 +21124,7 @@
         <v>2026</v>
       </c>
       <c r="R265">
-        <v>17948858</v>
+        <v>16976187</v>
       </c>
       <c r="S265" t="s">
         <v>166</v>
@@ -21130,13 +21136,13 @@
         <v>179</v>
       </c>
       <c r="V265" s="1">
-        <v>46276.62604146991</v>
+        <v>46276.49597027778</v>
       </c>
       <c r="W265">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X265" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AB265">
         <v>0</v>
@@ -21145,24 +21151,24 @@
         <v>166</v>
       </c>
       <c r="AH265" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI265" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="266" spans="1:35">
       <c r="A266">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B266" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C266" t="s">
         <v>50</v>
       </c>
       <c r="D266" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E266" t="s">
         <v>54</v>
@@ -21192,7 +21198,7 @@
         <v>2026</v>
       </c>
       <c r="R266">
-        <v>18085297</v>
+        <v>17948858</v>
       </c>
       <c r="S266" t="s">
         <v>166</v>
@@ -21204,13 +21210,13 @@
         <v>179</v>
       </c>
       <c r="V266" s="1">
-        <v>46276.68231165509</v>
+        <v>46276.62604146991</v>
       </c>
       <c r="W266">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X266" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="AB266">
         <v>0</v>
@@ -21219,24 +21225,24 @@
         <v>166</v>
       </c>
       <c r="AH266" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI266" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="267" spans="1:35">
       <c r="A267">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B267" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C267" t="s">
         <v>50</v>
       </c>
       <c r="D267" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E267" t="s">
         <v>54</v>
@@ -21259,9 +21265,6 @@
       <c r="N267" s="1">
         <v>46276</v>
       </c>
-      <c r="O267" t="s">
-        <v>144</v>
-      </c>
       <c r="P267">
         <v>8</v>
       </c>
@@ -21269,7 +21272,7 @@
         <v>2026</v>
       </c>
       <c r="R267">
-        <v>17949029</v>
+        <v>18085297</v>
       </c>
       <c r="S267" t="s">
         <v>166</v>
@@ -21281,17 +21284,14 @@
         <v>179</v>
       </c>
       <c r="V267" s="1">
-        <v>46276.7163278588</v>
+        <v>46276.68231165509</v>
       </c>
       <c r="W267">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X267" t="s">
         <v>185</v>
       </c>
-      <c r="Y267" t="s">
-        <v>279</v>
-      </c>
       <c r="AB267">
         <v>0</v>
       </c>
@@ -21299,18 +21299,18 @@
         <v>166</v>
       </c>
       <c r="AH267" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI267" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="268" spans="1:35">
       <c r="A268">
-        <v>6779</v>
+        <v>6705</v>
       </c>
       <c r="B268" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C268" t="s">
         <v>50</v>
@@ -21339,6 +21339,9 @@
       <c r="N268" s="1">
         <v>46276</v>
       </c>
+      <c r="O268" t="s">
+        <v>144</v>
+      </c>
       <c r="P268">
         <v>8</v>
       </c>
@@ -21346,7 +21349,7 @@
         <v>2026</v>
       </c>
       <c r="R268">
-        <v>18085066</v>
+        <v>17949029</v>
       </c>
       <c r="S268" t="s">
         <v>166</v>
@@ -21358,14 +21361,17 @@
         <v>179</v>
       </c>
       <c r="V268" s="1">
-        <v>46276.6823121412</v>
+        <v>46276.7163278588</v>
       </c>
       <c r="W268">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X268" t="s">
         <v>185</v>
       </c>
+      <c r="Y268" t="s">
+        <v>280</v>
+      </c>
       <c r="AB268">
         <v>0</v>
       </c>
@@ -21373,24 +21379,24 @@
         <v>166</v>
       </c>
       <c r="AH268" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI268" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="269" spans="1:35">
       <c r="A269">
-        <v>6404</v>
+        <v>6779</v>
       </c>
       <c r="B269" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C269" t="s">
         <v>50</v>
       </c>
       <c r="D269" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E269" t="s">
         <v>54</v>
@@ -21399,7 +21405,7 @@
         <v>56</v>
       </c>
       <c r="G269">
-        <v>1792</v>
+        <v>6806</v>
       </c>
       <c r="H269">
         <v>0</v>
@@ -21408,10 +21414,10 @@
         <v>63</v>
       </c>
       <c r="J269" t="s">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="N269" s="1">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="P269">
         <v>8</v>
@@ -21420,7 +21426,7 @@
         <v>2026</v>
       </c>
       <c r="R269">
-        <v>16962151</v>
+        <v>18085066</v>
       </c>
       <c r="S269" t="s">
         <v>166</v>
@@ -21429,16 +21435,16 @@
         <v>176</v>
       </c>
       <c r="U269" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="V269" s="1">
-        <v>46274.70622837963</v>
+        <v>46276.6823121412</v>
       </c>
       <c r="W269">
         <v>4</v>
       </c>
       <c r="X269" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="AB269">
         <v>0</v>
@@ -21447,18 +21453,18 @@
         <v>166</v>
       </c>
       <c r="AH269" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AI269" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="270" spans="1:35">
       <c r="A270">
-        <v>6703</v>
+        <v>6404</v>
       </c>
       <c r="B270" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C270" t="s">
         <v>50</v>
@@ -21494,7 +21500,7 @@
         <v>2026</v>
       </c>
       <c r="R270">
-        <v>17948756</v>
+        <v>16962151</v>
       </c>
       <c r="S270" t="s">
         <v>166</v>
@@ -21503,16 +21509,16 @@
         <v>176</v>
       </c>
       <c r="U270" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="V270" s="1">
-        <v>46275.71996309028</v>
+        <v>46274.70622837963</v>
       </c>
       <c r="W270">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X270" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AB270">
         <v>0</v>
@@ -21521,24 +21527,24 @@
         <v>166</v>
       </c>
       <c r="AH270" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI270" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="271" spans="1:35">
       <c r="A271">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B271" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C271" t="s">
         <v>50</v>
       </c>
       <c r="D271" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E271" t="s">
         <v>54</v>
@@ -21568,7 +21574,7 @@
         <v>2026</v>
       </c>
       <c r="R271">
-        <v>18085143</v>
+        <v>17948756</v>
       </c>
       <c r="S271" t="s">
         <v>166</v>
@@ -21580,13 +21586,13 @@
         <v>179</v>
       </c>
       <c r="V271" s="1">
-        <v>46275.54278886574</v>
+        <v>46275.71996309028</v>
       </c>
       <c r="W271">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X271" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="AB271">
         <v>0</v>
@@ -21595,24 +21601,24 @@
         <v>166</v>
       </c>
       <c r="AH271" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI271" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="272" spans="1:35">
       <c r="A272">
-        <v>6404</v>
+        <v>6704</v>
       </c>
       <c r="B272" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C272" t="s">
         <v>50</v>
       </c>
       <c r="D272" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E272" t="s">
         <v>54</v>
@@ -21621,7 +21627,7 @@
         <v>56</v>
       </c>
       <c r="G272">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="H272">
         <v>0</v>
@@ -21630,7 +21636,7 @@
         <v>63</v>
       </c>
       <c r="J272" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N272" s="1">
         <v>46275</v>
@@ -21642,7 +21648,7 @@
         <v>2026</v>
       </c>
       <c r="R272">
-        <v>16962161</v>
+        <v>18085143</v>
       </c>
       <c r="S272" t="s">
         <v>166</v>
@@ -21654,13 +21660,13 @@
         <v>179</v>
       </c>
       <c r="V272" s="1">
-        <v>46275.7000328588</v>
+        <v>46275.54278886574</v>
       </c>
       <c r="W272">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X272" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="AB272">
         <v>0</v>
@@ -21669,24 +21675,24 @@
         <v>166</v>
       </c>
       <c r="AH272" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI272" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="273" spans="1:35">
       <c r="A273">
-        <v>6486</v>
+        <v>6404</v>
       </c>
       <c r="B273" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C273" t="s">
         <v>50</v>
       </c>
       <c r="D273" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E273" t="s">
         <v>54</v>
@@ -21716,7 +21722,7 @@
         <v>2026</v>
       </c>
       <c r="R273">
-        <v>16975952</v>
+        <v>16962161</v>
       </c>
       <c r="S273" t="s">
         <v>166</v>
@@ -21728,13 +21734,13 @@
         <v>179</v>
       </c>
       <c r="V273" s="1">
-        <v>46275.72031699074</v>
+        <v>46275.7000328588</v>
       </c>
       <c r="W273">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X273" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="AB273">
         <v>0</v>
@@ -21743,24 +21749,24 @@
         <v>166</v>
       </c>
       <c r="AH273" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI273" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="274" spans="1:35">
       <c r="A274">
-        <v>6703</v>
+        <v>6486</v>
       </c>
       <c r="B274" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C274" t="s">
         <v>50</v>
       </c>
       <c r="D274" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E274" t="s">
         <v>54</v>
@@ -21790,7 +21796,7 @@
         <v>2026</v>
       </c>
       <c r="R274">
-        <v>17948766</v>
+        <v>16975952</v>
       </c>
       <c r="S274" t="s">
         <v>166</v>
@@ -21802,13 +21808,13 @@
         <v>179</v>
       </c>
       <c r="V274" s="1">
-        <v>46275.54095912037</v>
+        <v>46275.72031699074</v>
       </c>
       <c r="W274">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X274" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AB274">
         <v>0</v>
@@ -21817,24 +21823,24 @@
         <v>166</v>
       </c>
       <c r="AH274" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI274" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="275" spans="1:35">
       <c r="A275">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B275" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C275" t="s">
         <v>50</v>
       </c>
       <c r="D275" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E275" t="s">
         <v>54</v>
@@ -21864,7 +21870,7 @@
         <v>2026</v>
       </c>
       <c r="R275">
-        <v>18085154</v>
+        <v>17948766</v>
       </c>
       <c r="S275" t="s">
         <v>166</v>
@@ -21876,13 +21882,13 @@
         <v>179</v>
       </c>
       <c r="V275" s="1">
-        <v>46275.72225363426</v>
+        <v>46275.54095912037</v>
       </c>
       <c r="W275">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X275" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="AB275">
         <v>0</v>
@@ -21891,24 +21897,24 @@
         <v>166</v>
       </c>
       <c r="AH275" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI275" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="276" spans="1:35">
       <c r="A276">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B276" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C276" t="s">
         <v>50</v>
       </c>
       <c r="D276" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E276" t="s">
         <v>54</v>
@@ -21938,7 +21944,7 @@
         <v>2026</v>
       </c>
       <c r="R276">
-        <v>17948928</v>
+        <v>18085154</v>
       </c>
       <c r="S276" t="s">
         <v>166</v>
@@ -21950,10 +21956,10 @@
         <v>179</v>
       </c>
       <c r="V276" s="1">
-        <v>46275.7222629051</v>
+        <v>46275.72225363426</v>
       </c>
       <c r="W276">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X276" t="s">
         <v>185</v>
@@ -21965,18 +21971,18 @@
         <v>166</v>
       </c>
       <c r="AH276" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI276" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="277" spans="1:35">
       <c r="A277">
-        <v>6779</v>
+        <v>6705</v>
       </c>
       <c r="B277" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C277" t="s">
         <v>50</v>
@@ -22012,7 +22018,7 @@
         <v>2026</v>
       </c>
       <c r="R277">
-        <v>18084955</v>
+        <v>17948928</v>
       </c>
       <c r="S277" t="s">
         <v>166</v>
@@ -22024,10 +22030,10 @@
         <v>179</v>
       </c>
       <c r="V277" s="1">
-        <v>46275.7222709838</v>
+        <v>46275.7222629051</v>
       </c>
       <c r="W277">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X277" t="s">
         <v>185</v>
@@ -22039,24 +22045,24 @@
         <v>166</v>
       </c>
       <c r="AH277" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI277" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="278" spans="1:35">
       <c r="A278">
-        <v>5417</v>
+        <v>6779</v>
       </c>
       <c r="B278" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C278" t="s">
         <v>50</v>
       </c>
       <c r="D278" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E278" t="s">
         <v>54</v>
@@ -22065,7 +22071,7 @@
         <v>56</v>
       </c>
       <c r="G278">
-        <v>1796</v>
+        <v>1793</v>
       </c>
       <c r="H278">
         <v>0</v>
@@ -22074,13 +22080,10 @@
         <v>63</v>
       </c>
       <c r="J278" t="s">
-        <v>131</v>
+        <v>101</v>
       </c>
       <c r="N278" s="1">
-        <v>46273</v>
-      </c>
-      <c r="O278" t="s">
-        <v>141</v>
+        <v>46275</v>
       </c>
       <c r="P278">
         <v>8</v>
@@ -22089,7 +22092,7 @@
         <v>2026</v>
       </c>
       <c r="R278">
-        <v>17398955</v>
+        <v>18084955</v>
       </c>
       <c r="S278" t="s">
         <v>166</v>
@@ -22098,19 +22101,16 @@
         <v>176</v>
       </c>
       <c r="U278" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="V278" s="1">
-        <v>46274.74837762731</v>
+        <v>46275.7222709838</v>
       </c>
       <c r="W278">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X278" t="s">
-        <v>186</v>
-      </c>
-      <c r="Y278" t="s">
-        <v>280</v>
+        <v>185</v>
       </c>
       <c r="AB278">
         <v>0</v>
@@ -22119,24 +22119,24 @@
         <v>166</v>
       </c>
       <c r="AH278" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AI278" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="279" spans="1:35">
       <c r="A279">
-        <v>6703</v>
+        <v>5417</v>
       </c>
       <c r="B279" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C279" t="s">
         <v>50</v>
       </c>
       <c r="D279" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E279" t="s">
         <v>54</v>
@@ -22169,7 +22169,7 @@
         <v>2026</v>
       </c>
       <c r="R279">
-        <v>18073098</v>
+        <v>17398955</v>
       </c>
       <c r="S279" t="s">
         <v>166</v>
@@ -22181,16 +22181,16 @@
         <v>177</v>
       </c>
       <c r="V279" s="1">
-        <v>46274.74838096065</v>
+        <v>46274.74837762731</v>
       </c>
       <c r="W279">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X279" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="Y279" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AB279">
         <v>0</v>
@@ -22199,24 +22199,24 @@
         <v>166</v>
       </c>
       <c r="AH279" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI279" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="280" spans="1:35">
       <c r="A280">
-        <v>5417</v>
+        <v>6703</v>
       </c>
       <c r="B280" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C280" t="s">
         <v>50</v>
       </c>
       <c r="D280" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E280" t="s">
         <v>54</v>
@@ -22225,7 +22225,7 @@
         <v>56</v>
       </c>
       <c r="G280">
-        <v>11303</v>
+        <v>1796</v>
       </c>
       <c r="H280">
         <v>0</v>
@@ -22234,10 +22234,13 @@
         <v>63</v>
       </c>
       <c r="J280" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="N280" s="1">
-        <v>46279</v>
+        <v>46273</v>
+      </c>
+      <c r="O280" t="s">
+        <v>141</v>
       </c>
       <c r="P280">
         <v>8</v>
@@ -22246,7 +22249,7 @@
         <v>2026</v>
       </c>
       <c r="R280">
-        <v>17399454</v>
+        <v>18073098</v>
       </c>
       <c r="S280" t="s">
         <v>166</v>
@@ -22255,16 +22258,16 @@
         <v>176</v>
       </c>
       <c r="U280" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="V280" s="1">
-        <v>46274.42878043981</v>
+        <v>46274.74838096065</v>
       </c>
       <c r="W280">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="X280" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="Y280" t="s">
         <v>281</v>
@@ -22276,18 +22279,18 @@
         <v>166</v>
       </c>
       <c r="AH280" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI280" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="281" spans="1:35">
       <c r="A281">
-        <v>6486</v>
+        <v>5417</v>
       </c>
       <c r="B281" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C281" t="s">
         <v>50</v>
@@ -22323,7 +22326,7 @@
         <v>2026</v>
       </c>
       <c r="R281">
-        <v>16976351</v>
+        <v>17399454</v>
       </c>
       <c r="S281" t="s">
         <v>166</v>
@@ -22335,13 +22338,13 @@
         <v>178</v>
       </c>
       <c r="V281" s="1">
-        <v>46275.40196778935</v>
+        <v>46274.42878043981</v>
       </c>
       <c r="W281">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X281" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Y281" t="s">
         <v>282</v>
@@ -22353,24 +22356,24 @@
         <v>166</v>
       </c>
       <c r="AH281" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI281" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="282" spans="1:35">
       <c r="A282">
-        <v>6703</v>
+        <v>6486</v>
       </c>
       <c r="B282" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C282" t="s">
         <v>50</v>
       </c>
       <c r="D282" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E282" t="s">
         <v>54</v>
@@ -22379,22 +22382,19 @@
         <v>56</v>
       </c>
       <c r="G282">
-        <v>950</v>
+        <v>11303</v>
       </c>
       <c r="H282">
         <v>0</v>
       </c>
       <c r="I282" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J282" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="N282" s="1">
-        <v>46275</v>
-      </c>
-      <c r="O282" t="s">
-        <v>143</v>
+        <v>46279</v>
       </c>
       <c r="P282">
         <v>8</v>
@@ -22403,22 +22403,25 @@
         <v>2026</v>
       </c>
       <c r="R282">
-        <v>17941146</v>
+        <v>16976351</v>
       </c>
       <c r="S282" t="s">
-        <v>167</v>
+        <v>166</v>
+      </c>
+      <c r="T282" t="s">
+        <v>176</v>
       </c>
       <c r="U282" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="V282" s="1">
-        <v>46276.52399603009</v>
+        <v>46275.40196778935</v>
       </c>
       <c r="W282">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="X282" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="Y282" t="s">
         <v>283</v>
@@ -22427,27 +22430,27 @@
         <v>0</v>
       </c>
       <c r="AC282" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AH282" t="s">
         <v>306</v>
       </c>
       <c r="AI282" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="283" spans="1:35">
       <c r="A283">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B283" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C283" t="s">
         <v>50</v>
       </c>
       <c r="D283" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E283" t="s">
         <v>54</v>
@@ -22480,7 +22483,7 @@
         <v>2026</v>
       </c>
       <c r="R283">
-        <v>17952340</v>
+        <v>17941146</v>
       </c>
       <c r="S283" t="s">
         <v>167</v>
@@ -22489,13 +22492,13 @@
         <v>177</v>
       </c>
       <c r="V283" s="1">
-        <v>46276.5240703125</v>
+        <v>46276.52399603009</v>
       </c>
       <c r="W283">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X283" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="Y283" t="s">
         <v>284</v>
@@ -22507,18 +22510,18 @@
         <v>167</v>
       </c>
       <c r="AH283" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI283" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="284" spans="1:35">
       <c r="A284">
-        <v>6949</v>
+        <v>6704</v>
       </c>
       <c r="B284" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C284" t="s">
         <v>50</v>
@@ -22530,7 +22533,7 @@
         <v>54</v>
       </c>
       <c r="F284" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G284">
         <v>950</v>
@@ -22547,6 +22550,9 @@
       <c r="N284" s="1">
         <v>46275</v>
       </c>
+      <c r="O284" t="s">
+        <v>143</v>
+      </c>
       <c r="P284">
         <v>8</v>
       </c>
@@ -22554,22 +22560,22 @@
         <v>2026</v>
       </c>
       <c r="R284">
-        <v>18178132</v>
+        <v>17952340</v>
       </c>
       <c r="S284" t="s">
         <v>167</v>
       </c>
       <c r="U284" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="V284" s="1">
-        <v>46275.4100730787</v>
+        <v>46276.5240703125</v>
       </c>
       <c r="W284">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X284" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Y284" t="s">
         <v>285</v>
@@ -22581,24 +22587,24 @@
         <v>167</v>
       </c>
       <c r="AH284" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI284" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="285" spans="1:35">
       <c r="A285">
-        <v>6962</v>
+        <v>6949</v>
       </c>
       <c r="B285" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C285" t="s">
         <v>50</v>
       </c>
       <c r="D285" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E285" t="s">
         <v>54</v>
@@ -22628,7 +22634,7 @@
         <v>2026</v>
       </c>
       <c r="R285">
-        <v>18188717</v>
+        <v>18178132</v>
       </c>
       <c r="S285" t="s">
         <v>167</v>
@@ -22637,13 +22643,13 @@
         <v>179</v>
       </c>
       <c r="V285" s="1">
-        <v>46275.40964188657</v>
+        <v>46275.4100730787</v>
       </c>
       <c r="W285">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X285" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="Y285" t="s">
         <v>286</v>
@@ -22655,18 +22661,18 @@
         <v>167</v>
       </c>
       <c r="AH285" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI285" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="286" spans="1:35">
       <c r="A286">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B286" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C286" t="s">
         <v>50</v>
@@ -22702,7 +22708,7 @@
         <v>2026</v>
       </c>
       <c r="R286">
-        <v>18188623</v>
+        <v>18188717</v>
       </c>
       <c r="S286" t="s">
         <v>167</v>
@@ -22711,10 +22717,10 @@
         <v>179</v>
       </c>
       <c r="V286" s="1">
-        <v>46275.40964245371</v>
+        <v>46275.40964188657</v>
       </c>
       <c r="W286">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X286" t="s">
         <v>184</v>
@@ -22729,33 +22735,33 @@
         <v>167</v>
       </c>
       <c r="AH286" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI286" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="287" spans="1:35">
       <c r="A287">
-        <v>6548</v>
+        <v>6963</v>
       </c>
       <c r="B287" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C287" t="s">
         <v>50</v>
       </c>
       <c r="D287" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E287" t="s">
         <v>54</v>
       </c>
       <c r="F287" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G287">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H287">
         <v>0</v>
@@ -22764,7 +22770,7 @@
         <v>64</v>
       </c>
       <c r="J287" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="N287" s="1">
         <v>46275</v>
@@ -22776,7 +22782,7 @@
         <v>2026</v>
       </c>
       <c r="R287">
-        <v>17222405</v>
+        <v>18188623</v>
       </c>
       <c r="S287" t="s">
         <v>167</v>
@@ -22785,13 +22791,13 @@
         <v>179</v>
       </c>
       <c r="V287" s="1">
-        <v>46275.45011145833</v>
+        <v>46275.40964245371</v>
       </c>
       <c r="W287">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X287" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="Y287" t="s">
         <v>288</v>
@@ -22803,27 +22809,27 @@
         <v>167</v>
       </c>
       <c r="AH287" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI287" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="288" spans="1:35">
       <c r="A288">
-        <v>6628</v>
+        <v>6548</v>
       </c>
       <c r="B288" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C288" t="s">
         <v>50</v>
       </c>
       <c r="D288" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E288" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F288" t="s">
         <v>56</v>
@@ -22850,7 +22856,7 @@
         <v>2026</v>
       </c>
       <c r="R288">
-        <v>16959950</v>
+        <v>17222405</v>
       </c>
       <c r="S288" t="s">
         <v>167</v>
@@ -22859,13 +22865,16 @@
         <v>179</v>
       </c>
       <c r="V288" s="1">
-        <v>46275.44901016204</v>
+        <v>46275.45011145833</v>
       </c>
       <c r="W288">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X288" t="s">
-        <v>181</v>
+        <v>180</v>
+      </c>
+      <c r="Y288" t="s">
+        <v>289</v>
       </c>
       <c r="AB288">
         <v>0</v>
@@ -22874,27 +22883,27 @@
         <v>167</v>
       </c>
       <c r="AH288" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI288" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="289" spans="1:35">
       <c r="A289">
-        <v>6703</v>
+        <v>6628</v>
       </c>
       <c r="B289" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C289" t="s">
         <v>50</v>
       </c>
       <c r="D289" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E289" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F289" t="s">
         <v>56</v>
@@ -22914,9 +22923,6 @@
       <c r="N289" s="1">
         <v>46275</v>
       </c>
-      <c r="O289" t="s">
-        <v>144</v>
-      </c>
       <c r="P289">
         <v>8</v>
       </c>
@@ -22924,25 +22930,22 @@
         <v>2026</v>
       </c>
       <c r="R289">
-        <v>17941156</v>
+        <v>16959950</v>
       </c>
       <c r="S289" t="s">
         <v>167</v>
       </c>
       <c r="U289" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="V289" s="1">
-        <v>46276.71732053241</v>
+        <v>46275.44901016204</v>
       </c>
       <c r="W289">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X289" t="s">
-        <v>189</v>
-      </c>
-      <c r="Y289" t="s">
-        <v>289</v>
+        <v>181</v>
       </c>
       <c r="AB289">
         <v>0</v>
@@ -22951,24 +22954,24 @@
         <v>167</v>
       </c>
       <c r="AH289" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI289" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="290" spans="1:35">
       <c r="A290">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B290" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C290" t="s">
         <v>50</v>
       </c>
       <c r="D290" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E290" t="s">
         <v>54</v>
@@ -23001,7 +23004,7 @@
         <v>2026</v>
       </c>
       <c r="R290">
-        <v>17952351</v>
+        <v>17941156</v>
       </c>
       <c r="S290" t="s">
         <v>167</v>
@@ -23010,13 +23013,13 @@
         <v>177</v>
       </c>
       <c r="V290" s="1">
-        <v>46276.71697232639</v>
+        <v>46276.71732053241</v>
       </c>
       <c r="W290">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X290" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="Y290" t="s">
         <v>290</v>
@@ -23028,24 +23031,24 @@
         <v>167</v>
       </c>
       <c r="AH290" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI290" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="291" spans="1:35">
       <c r="A291">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B291" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C291" t="s">
         <v>50</v>
       </c>
       <c r="D291" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E291" t="s">
         <v>54</v>
@@ -23078,7 +23081,7 @@
         <v>2026</v>
       </c>
       <c r="R291">
-        <v>17952535</v>
+        <v>17952351</v>
       </c>
       <c r="S291" t="s">
         <v>167</v>
@@ -23087,10 +23090,10 @@
         <v>177</v>
       </c>
       <c r="V291" s="1">
-        <v>46276.7175884838</v>
+        <v>46276.71697232639</v>
       </c>
       <c r="W291">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X291" t="s">
         <v>185</v>
@@ -23105,18 +23108,18 @@
         <v>167</v>
       </c>
       <c r="AH291" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI291" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="292" spans="1:35">
       <c r="A292">
-        <v>6779</v>
+        <v>6705</v>
       </c>
       <c r="B292" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C292" t="s">
         <v>50</v>
@@ -23155,7 +23158,7 @@
         <v>2026</v>
       </c>
       <c r="R292">
-        <v>18056705</v>
+        <v>17952535</v>
       </c>
       <c r="S292" t="s">
         <v>167</v>
@@ -23164,10 +23167,10 @@
         <v>177</v>
       </c>
       <c r="V292" s="1">
-        <v>46276.7175895949</v>
+        <v>46276.7175884838</v>
       </c>
       <c r="W292">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X292" t="s">
         <v>185</v>
@@ -23182,18 +23185,18 @@
         <v>167</v>
       </c>
       <c r="AH292" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI292" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="293" spans="1:35">
       <c r="A293">
-        <v>6945</v>
+        <v>6779</v>
       </c>
       <c r="B293" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C293" t="s">
         <v>50</v>
@@ -23205,7 +23208,7 @@
         <v>54</v>
       </c>
       <c r="F293" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G293">
         <v>951</v>
@@ -23232,7 +23235,7 @@
         <v>2026</v>
       </c>
       <c r="R293">
-        <v>18164501</v>
+        <v>18056705</v>
       </c>
       <c r="S293" t="s">
         <v>167</v>
@@ -23241,13 +23244,13 @@
         <v>177</v>
       </c>
       <c r="V293" s="1">
-        <v>46276.71759461806</v>
+        <v>46276.7175895949</v>
       </c>
       <c r="W293">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X293" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Y293" t="s">
         <v>293</v>
@@ -23259,24 +23262,24 @@
         <v>167</v>
       </c>
       <c r="AH293" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI293" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="294" spans="1:35">
       <c r="A294">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B294" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C294" t="s">
         <v>50</v>
       </c>
       <c r="D294" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E294" t="s">
         <v>54</v>
@@ -23299,6 +23302,9 @@
       <c r="N294" s="1">
         <v>46275</v>
       </c>
+      <c r="O294" t="s">
+        <v>144</v>
+      </c>
       <c r="P294">
         <v>8</v>
       </c>
@@ -23306,22 +23312,22 @@
         <v>2026</v>
       </c>
       <c r="R294">
-        <v>18178138</v>
+        <v>18164501</v>
       </c>
       <c r="S294" t="s">
         <v>167</v>
       </c>
       <c r="U294" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="V294" s="1">
-        <v>46275.44975668981</v>
+        <v>46276.71759461806</v>
       </c>
       <c r="W294">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X294" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Y294" t="s">
         <v>294</v>
@@ -23333,24 +23339,24 @@
         <v>167</v>
       </c>
       <c r="AH294" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI294" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="295" spans="1:35">
       <c r="A295">
-        <v>6962</v>
+        <v>6949</v>
       </c>
       <c r="B295" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C295" t="s">
         <v>50</v>
       </c>
       <c r="D295" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E295" t="s">
         <v>54</v>
@@ -23380,7 +23386,7 @@
         <v>2026</v>
       </c>
       <c r="R295">
-        <v>18188724</v>
+        <v>18178138</v>
       </c>
       <c r="S295" t="s">
         <v>167</v>
@@ -23389,13 +23395,13 @@
         <v>179</v>
       </c>
       <c r="V295" s="1">
-        <v>46275.44933692129</v>
+        <v>46275.44975668981</v>
       </c>
       <c r="W295">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X295" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="Y295" t="s">
         <v>295</v>
@@ -23407,18 +23413,18 @@
         <v>167</v>
       </c>
       <c r="AH295" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI295" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="296" spans="1:35">
       <c r="A296">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B296" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C296" t="s">
         <v>50</v>
@@ -23454,7 +23460,7 @@
         <v>2026</v>
       </c>
       <c r="R296">
-        <v>18188630</v>
+        <v>18188724</v>
       </c>
       <c r="S296" t="s">
         <v>167</v>
@@ -23463,10 +23469,10 @@
         <v>179</v>
       </c>
       <c r="V296" s="1">
-        <v>46275.44933814815</v>
+        <v>46275.44933692129</v>
       </c>
       <c r="W296">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X296" t="s">
         <v>184</v>
@@ -23481,18 +23487,18 @@
         <v>167</v>
       </c>
       <c r="AH296" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AI296" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="297" spans="1:35">
       <c r="A297">
-        <v>6703</v>
+        <v>6963</v>
       </c>
       <c r="B297" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C297" t="s">
         <v>50</v>
@@ -23504,10 +23510,10 @@
         <v>54</v>
       </c>
       <c r="F297" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G297">
-        <v>5989</v>
+        <v>951</v>
       </c>
       <c r="H297">
         <v>0</v>
@@ -23516,34 +23522,37 @@
         <v>64</v>
       </c>
       <c r="J297" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="N297" s="1">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="P297">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q297">
         <v>2026</v>
       </c>
       <c r="R297">
-        <v>17941177</v>
+        <v>18188630</v>
       </c>
       <c r="S297" t="s">
         <v>167</v>
       </c>
       <c r="U297" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="V297" s="1">
-        <v>46274.41771849537</v>
+        <v>46275.44933814815</v>
       </c>
       <c r="W297">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X297" t="s">
-        <v>189</v>
+        <v>184</v>
+      </c>
+      <c r="Y297" t="s">
+        <v>297</v>
       </c>
       <c r="AB297">
         <v>0</v>
@@ -23555,21 +23564,21 @@
         <v>307</v>
       </c>
       <c r="AI297" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="298" spans="1:35">
       <c r="A298">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B298" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C298" t="s">
         <v>50</v>
       </c>
       <c r="D298" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E298" t="s">
         <v>54</v>
@@ -23599,7 +23608,7 @@
         <v>2026</v>
       </c>
       <c r="R298">
-        <v>17952385</v>
+        <v>17941177</v>
       </c>
       <c r="S298" t="s">
         <v>167</v>
@@ -23608,13 +23617,13 @@
         <v>177</v>
       </c>
       <c r="V298" s="1">
-        <v>46274.41775447917</v>
+        <v>46274.41771849537</v>
       </c>
       <c r="W298">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X298" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="AB298">
         <v>0</v>
@@ -23623,24 +23632,24 @@
         <v>167</v>
       </c>
       <c r="AH298" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI298" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="299" spans="1:35">
       <c r="A299">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B299" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C299" t="s">
         <v>50</v>
       </c>
       <c r="D299" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E299" t="s">
         <v>54</v>
@@ -23670,7 +23679,7 @@
         <v>2026</v>
       </c>
       <c r="R299">
-        <v>17952569</v>
+        <v>17952385</v>
       </c>
       <c r="S299" t="s">
         <v>167</v>
@@ -23679,10 +23688,10 @@
         <v>177</v>
       </c>
       <c r="V299" s="1">
-        <v>46274.41777533565</v>
+        <v>46274.41775447917</v>
       </c>
       <c r="W299">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X299" t="s">
         <v>185</v>
@@ -23694,18 +23703,18 @@
         <v>167</v>
       </c>
       <c r="AH299" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI299" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="300" spans="1:35">
       <c r="A300">
-        <v>6945</v>
+        <v>6705</v>
       </c>
       <c r="B300" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C300" t="s">
         <v>50</v>
@@ -23717,7 +23726,7 @@
         <v>54</v>
       </c>
       <c r="F300" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G300">
         <v>5989</v>
@@ -23741,7 +23750,7 @@
         <v>2026</v>
       </c>
       <c r="R300">
-        <v>18164516</v>
+        <v>17952569</v>
       </c>
       <c r="S300" t="s">
         <v>167</v>
@@ -23750,13 +23759,13 @@
         <v>177</v>
       </c>
       <c r="V300" s="1">
-        <v>46274.41799166667</v>
+        <v>46274.41777533565</v>
       </c>
       <c r="W300">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X300" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="AB300">
         <v>0</v>
@@ -23765,24 +23774,24 @@
         <v>167</v>
       </c>
       <c r="AH300" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI300" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="301" spans="1:35">
       <c r="A301">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B301" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C301" t="s">
         <v>50</v>
       </c>
       <c r="D301" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E301" t="s">
         <v>54</v>
@@ -23812,7 +23821,7 @@
         <v>2026</v>
       </c>
       <c r="R301">
-        <v>18178157</v>
+        <v>18164516</v>
       </c>
       <c r="S301" t="s">
         <v>167</v>
@@ -23821,13 +23830,13 @@
         <v>177</v>
       </c>
       <c r="V301" s="1">
-        <v>46274.41800114583</v>
+        <v>46274.41799166667</v>
       </c>
       <c r="W301">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X301" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AB301">
         <v>0</v>
@@ -23836,45 +23845,45 @@
         <v>167</v>
       </c>
       <c r="AH301" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI301" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="302" spans="1:35">
       <c r="A302">
-        <v>6703</v>
+        <v>6949</v>
       </c>
       <c r="B302" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C302" t="s">
         <v>50</v>
       </c>
       <c r="D302" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E302" t="s">
         <v>54</v>
       </c>
       <c r="F302" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G302">
-        <v>6215</v>
+        <v>5989</v>
       </c>
       <c r="H302">
         <v>0</v>
       </c>
       <c r="I302" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J302" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="N302" s="1">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="P302">
         <v>9</v>
@@ -23883,48 +23892,48 @@
         <v>2026</v>
       </c>
       <c r="R302">
-        <v>17941187</v>
+        <v>18178157</v>
       </c>
       <c r="S302" t="s">
-        <v>54</v>
+        <v>167</v>
       </c>
       <c r="U302" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="V302" s="1">
-        <v>46274.41772148148</v>
+        <v>46274.41800114583</v>
       </c>
       <c r="W302">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X302" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="AB302">
         <v>0</v>
       </c>
       <c r="AC302" t="s">
-        <v>54</v>
+        <v>167</v>
       </c>
       <c r="AH302" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI302" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="303" spans="1:35">
       <c r="A303">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B303" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C303" t="s">
         <v>50</v>
       </c>
       <c r="D303" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E303" t="s">
         <v>54</v>
@@ -23954,7 +23963,7 @@
         <v>2026</v>
       </c>
       <c r="R303">
-        <v>17952400</v>
+        <v>17941187</v>
       </c>
       <c r="S303" t="s">
         <v>54</v>
@@ -23963,13 +23972,13 @@
         <v>179</v>
       </c>
       <c r="V303" s="1">
-        <v>46274.41773631945</v>
+        <v>46274.41772148148</v>
       </c>
       <c r="W303">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X303" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="AB303">
         <v>0</v>
@@ -23978,24 +23987,24 @@
         <v>54</v>
       </c>
       <c r="AH303" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI303" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="304" spans="1:35">
       <c r="A304">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B304" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C304" t="s">
         <v>50</v>
       </c>
       <c r="D304" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E304" t="s">
         <v>54</v>
@@ -24025,7 +24034,7 @@
         <v>2026</v>
       </c>
       <c r="R304">
-        <v>17952580</v>
+        <v>17952400</v>
       </c>
       <c r="S304" t="s">
         <v>54</v>
@@ -24034,10 +24043,10 @@
         <v>179</v>
       </c>
       <c r="V304" s="1">
-        <v>46274.41777481481</v>
+        <v>46274.41773631945</v>
       </c>
       <c r="W304">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X304" t="s">
         <v>185</v>
@@ -24049,18 +24058,18 @@
         <v>54</v>
       </c>
       <c r="AH304" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI304" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="305" spans="1:35">
       <c r="A305">
-        <v>6945</v>
+        <v>6705</v>
       </c>
       <c r="B305" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C305" t="s">
         <v>50</v>
@@ -24072,7 +24081,7 @@
         <v>54</v>
       </c>
       <c r="F305" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G305">
         <v>6215</v>
@@ -24096,7 +24105,7 @@
         <v>2026</v>
       </c>
       <c r="R305">
-        <v>18164523</v>
+        <v>17952580</v>
       </c>
       <c r="S305" t="s">
         <v>54</v>
@@ -24105,13 +24114,13 @@
         <v>179</v>
       </c>
       <c r="V305" s="1">
-        <v>46274.41799332176</v>
+        <v>46274.41777481481</v>
       </c>
       <c r="W305">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X305" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="AB305">
         <v>0</v>
@@ -24120,24 +24129,24 @@
         <v>54</v>
       </c>
       <c r="AH305" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI305" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="306" spans="1:35">
       <c r="A306">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B306" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C306" t="s">
         <v>50</v>
       </c>
       <c r="D306" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E306" t="s">
         <v>54</v>
@@ -24167,42 +24176,42 @@
         <v>2026</v>
       </c>
       <c r="R306">
-        <v>18178163</v>
+        <v>18164523</v>
       </c>
       <c r="S306" t="s">
-        <v>168</v>
+        <v>54</v>
       </c>
       <c r="U306" t="s">
         <v>179</v>
       </c>
       <c r="V306" s="1">
-        <v>46274.41800085648</v>
+        <v>46274.41799332176</v>
       </c>
       <c r="W306">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X306" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AB306">
         <v>0</v>
       </c>
       <c r="AC306" t="s">
-        <v>168</v>
+        <v>54</v>
       </c>
       <c r="AH306" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AI306" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="307" spans="1:35">
       <c r="A307">
-        <v>5417</v>
+        <v>6949</v>
       </c>
       <c r="B307" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C307" t="s">
         <v>50</v>
@@ -24214,10 +24223,10 @@
         <v>54</v>
       </c>
       <c r="F307" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G307">
-        <v>11746</v>
+        <v>6215</v>
       </c>
       <c r="H307">
         <v>0</v>
@@ -24226,34 +24235,34 @@
         <v>65</v>
       </c>
       <c r="J307" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="N307" s="1">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="P307">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q307">
         <v>2026</v>
       </c>
       <c r="R307">
-        <v>17994311</v>
+        <v>18178163</v>
       </c>
       <c r="S307" t="s">
-        <v>54</v>
+        <v>168</v>
       </c>
       <c r="U307" t="s">
         <v>179</v>
       </c>
       <c r="V307" s="1">
-        <v>46275.31737530093</v>
+        <v>46274.41800085648</v>
       </c>
       <c r="W307">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="X307" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="AB307">
         <v>0</v>
@@ -24262,24 +24271,24 @@
         <v>168</v>
       </c>
       <c r="AH307" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="AI307" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="308" spans="1:35">
       <c r="A308">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B308" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C308" t="s">
         <v>50</v>
       </c>
       <c r="D308" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E308" t="s">
         <v>54</v>
@@ -24309,7 +24318,7 @@
         <v>2026</v>
       </c>
       <c r="R308">
-        <v>17994675</v>
+        <v>17994311</v>
       </c>
       <c r="S308" t="s">
         <v>54</v>
@@ -24318,13 +24327,13 @@
         <v>179</v>
       </c>
       <c r="V308" s="1">
-        <v>46275.31747032407</v>
+        <v>46275.31737530093</v>
       </c>
       <c r="W308">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X308" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="AB308">
         <v>0</v>
@@ -24333,24 +24342,24 @@
         <v>168</v>
       </c>
       <c r="AH308" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI308" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="309" spans="1:35">
       <c r="A309">
-        <v>6486</v>
+        <v>6404</v>
       </c>
       <c r="B309" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C309" t="s">
         <v>50</v>
       </c>
       <c r="D309" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E309" t="s">
         <v>54</v>
@@ -24380,7 +24389,7 @@
         <v>2026</v>
       </c>
       <c r="R309">
-        <v>17994809</v>
+        <v>17994675</v>
       </c>
       <c r="S309" t="s">
         <v>54</v>
@@ -24389,13 +24398,13 @@
         <v>179</v>
       </c>
       <c r="V309" s="1">
-        <v>46275.31747981482</v>
+        <v>46275.31747032407</v>
       </c>
       <c r="W309">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X309" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="AB309">
         <v>0</v>
@@ -24404,18 +24413,18 @@
         <v>168</v>
       </c>
       <c r="AH309" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI309" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="310" spans="1:35">
       <c r="A310">
-        <v>6548</v>
+        <v>6486</v>
       </c>
       <c r="B310" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C310" t="s">
         <v>50</v>
@@ -24451,7 +24460,7 @@
         <v>2026</v>
       </c>
       <c r="R310">
-        <v>18006051</v>
+        <v>17994809</v>
       </c>
       <c r="S310" t="s">
         <v>54</v>
@@ -24460,13 +24469,13 @@
         <v>179</v>
       </c>
       <c r="V310" s="1">
-        <v>46275.31748724537</v>
+        <v>46275.31747981482</v>
       </c>
       <c r="W310">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X310" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="AB310">
         <v>0</v>
@@ -24475,27 +24484,27 @@
         <v>168</v>
       </c>
       <c r="AH310" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI310" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="311" spans="1:35">
       <c r="A311">
-        <v>6628</v>
+        <v>6548</v>
       </c>
       <c r="B311" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C311" t="s">
         <v>50</v>
       </c>
       <c r="D311" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E311" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F311" t="s">
         <v>56</v>
@@ -24522,22 +24531,22 @@
         <v>2026</v>
       </c>
       <c r="R311">
-        <v>18003256</v>
+        <v>18006051</v>
       </c>
       <c r="S311" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="U311" t="s">
         <v>179</v>
       </c>
       <c r="V311" s="1">
-        <v>46275.31749535879</v>
+        <v>46275.31748724537</v>
       </c>
       <c r="W311">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X311" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AB311">
         <v>0</v>
@@ -24546,27 +24555,27 @@
         <v>168</v>
       </c>
       <c r="AH311" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI311" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="312" spans="1:35">
       <c r="A312">
-        <v>6703</v>
+        <v>6628</v>
       </c>
       <c r="B312" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C312" t="s">
         <v>50</v>
       </c>
       <c r="D312" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E312" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F312" t="s">
         <v>56</v>
@@ -24593,22 +24602,22 @@
         <v>2026</v>
       </c>
       <c r="R312">
-        <v>18004017</v>
+        <v>18003256</v>
       </c>
       <c r="S312" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="U312" t="s">
         <v>179</v>
       </c>
       <c r="V312" s="1">
-        <v>46275.31750491898</v>
+        <v>46275.31749535879</v>
       </c>
       <c r="W312">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X312" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="AB312">
         <v>0</v>
@@ -24617,24 +24626,24 @@
         <v>168</v>
       </c>
       <c r="AH312" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI312" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="313" spans="1:35">
       <c r="A313">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B313" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C313" t="s">
         <v>50</v>
       </c>
       <c r="D313" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E313" t="s">
         <v>54</v>
@@ -24664,7 +24673,7 @@
         <v>2026</v>
       </c>
       <c r="R313">
-        <v>17995164</v>
+        <v>18004017</v>
       </c>
       <c r="S313" t="s">
         <v>54</v>
@@ -24673,13 +24682,13 @@
         <v>179</v>
       </c>
       <c r="V313" s="1">
-        <v>46275.31750555555</v>
+        <v>46275.31750491898</v>
       </c>
       <c r="W313">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X313" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="AB313">
         <v>0</v>
@@ -24688,24 +24697,24 @@
         <v>168</v>
       </c>
       <c r="AH313" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI313" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="314" spans="1:35">
       <c r="A314">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B314" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C314" t="s">
         <v>50</v>
       </c>
       <c r="D314" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E314" t="s">
         <v>54</v>
@@ -24735,7 +24744,7 @@
         <v>2026</v>
       </c>
       <c r="R314">
-        <v>18004028</v>
+        <v>17995164</v>
       </c>
       <c r="S314" t="s">
         <v>54</v>
@@ -24744,10 +24753,10 @@
         <v>179</v>
       </c>
       <c r="V314" s="1">
-        <v>46275.31750599537</v>
+        <v>46275.31750555555</v>
       </c>
       <c r="W314">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X314" t="s">
         <v>185</v>
@@ -24759,24 +24768,24 @@
         <v>168</v>
       </c>
       <c r="AH314" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI314" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="315" spans="1:35">
       <c r="A315">
-        <v>5417</v>
+        <v>6705</v>
       </c>
       <c r="B315" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C315" t="s">
         <v>50</v>
       </c>
       <c r="D315" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E315" t="s">
         <v>54</v>
@@ -24785,7 +24794,7 @@
         <v>56</v>
       </c>
       <c r="G315">
-        <v>7877</v>
+        <v>11746</v>
       </c>
       <c r="H315">
         <v>0</v>
@@ -24794,57 +24803,54 @@
         <v>65</v>
       </c>
       <c r="J315" t="s">
-        <v>67</v>
+        <v>134</v>
       </c>
       <c r="N315" s="1">
-        <v>46259</v>
+        <v>46275</v>
       </c>
       <c r="P315">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q315">
         <v>2026</v>
       </c>
       <c r="R315">
-        <v>17399329</v>
+        <v>18004028</v>
       </c>
       <c r="S315" t="s">
         <v>54</v>
       </c>
       <c r="U315" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="V315" s="1">
-        <v>46275.5810894676</v>
+        <v>46275.31750599537</v>
       </c>
       <c r="W315">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="X315" t="s">
-        <v>186</v>
-      </c>
-      <c r="Y315" t="s">
-        <v>297</v>
+        <v>185</v>
       </c>
       <c r="AB315">
         <v>0</v>
       </c>
       <c r="AC315" t="s">
-        <v>54</v>
+        <v>168</v>
       </c>
       <c r="AH315" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI315" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="316" spans="1:35">
       <c r="A316">
-        <v>6486</v>
+        <v>5417</v>
       </c>
       <c r="B316" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C316" t="s">
         <v>50</v>
@@ -24859,7 +24865,7 @@
         <v>56</v>
       </c>
       <c r="G316">
-        <v>9774</v>
+        <v>7877</v>
       </c>
       <c r="H316">
         <v>0</v>
@@ -24868,7 +24874,7 @@
         <v>65</v>
       </c>
       <c r="J316" t="s">
-        <v>120</v>
+        <v>67</v>
       </c>
       <c r="N316" s="1">
         <v>46259</v>
@@ -24880,7 +24886,7 @@
         <v>2026</v>
       </c>
       <c r="R316">
-        <v>16976320</v>
+        <v>17399329</v>
       </c>
       <c r="S316" t="s">
         <v>54</v>
@@ -24889,13 +24895,13 @@
         <v>177</v>
       </c>
       <c r="V316" s="1">
-        <v>46275.58158541666</v>
+        <v>46275.5810894676</v>
       </c>
       <c r="W316">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X316" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Y316" t="s">
         <v>298</v>
@@ -24907,18 +24913,18 @@
         <v>54</v>
       </c>
       <c r="AH316" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI316" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="317" spans="1:35">
       <c r="A317">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B317" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C317" t="s">
         <v>50</v>
@@ -24933,7 +24939,7 @@
         <v>56</v>
       </c>
       <c r="G317">
-        <v>7027</v>
+        <v>9774</v>
       </c>
       <c r="H317">
         <v>0</v>
@@ -24942,34 +24948,34 @@
         <v>65</v>
       </c>
       <c r="J317" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N317" s="1">
-        <v>46289</v>
+        <v>46259</v>
       </c>
       <c r="P317">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q317">
         <v>2026</v>
       </c>
       <c r="R317">
-        <v>17399290</v>
+        <v>16976320</v>
       </c>
       <c r="S317" t="s">
         <v>54</v>
       </c>
       <c r="U317" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="V317" s="1">
-        <v>46279.70955146991</v>
+        <v>46275.58158541666</v>
       </c>
       <c r="W317">
-        <v>-10</v>
+        <v>21</v>
       </c>
       <c r="X317" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Y317" t="s">
         <v>299</v>
@@ -24981,7 +24987,7 @@
         <v>54</v>
       </c>
       <c r="AH317" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AI317" t="s">
         <v>310</v>
@@ -24989,10 +24995,10 @@
     </row>
     <row r="318" spans="1:35">
       <c r="A318">
-        <v>6627</v>
+        <v>5417</v>
       </c>
       <c r="B318" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C318" t="s">
         <v>50</v>
@@ -25001,28 +25007,25 @@
         <v>51</v>
       </c>
       <c r="E318" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F318" t="s">
         <v>56</v>
       </c>
       <c r="G318">
-        <v>11056</v>
+        <v>7027</v>
       </c>
       <c r="H318">
         <v>0</v>
       </c>
       <c r="I318" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J318" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="N318" s="1">
-        <v>46276</v>
-      </c>
-      <c r="O318" t="s">
-        <v>144</v>
+        <v>46289</v>
       </c>
       <c r="P318">
         <v>8</v>
@@ -25031,19 +25034,22 @@
         <v>2026</v>
       </c>
       <c r="R318">
-        <v>18270269</v>
+        <v>17399290</v>
+      </c>
+      <c r="S318" t="s">
+        <v>54</v>
       </c>
       <c r="U318" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="V318" s="1">
-        <v>46276.41675075232</v>
+        <v>46279.70955146991</v>
       </c>
       <c r="W318">
-        <v>3</v>
+        <v>-9</v>
       </c>
       <c r="X318" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="Y318" t="s">
         <v>300</v>
@@ -25052,13 +25058,87 @@
         <v>0</v>
       </c>
       <c r="AC318" t="s">
-        <v>304</v>
+        <v>54</v>
       </c>
       <c r="AH318" t="s">
+        <v>306</v>
+      </c>
+      <c r="AI318" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="319" spans="1:35">
+      <c r="A319">
+        <v>6627</v>
+      </c>
+      <c r="B319" t="s">
+        <v>36</v>
+      </c>
+      <c r="C319" t="s">
+        <v>50</v>
+      </c>
+      <c r="D319" t="s">
+        <v>51</v>
+      </c>
+      <c r="E319" t="s">
+        <v>55</v>
+      </c>
+      <c r="F319" t="s">
+        <v>56</v>
+      </c>
+      <c r="G319">
+        <v>11056</v>
+      </c>
+      <c r="H319">
+        <v>0</v>
+      </c>
+      <c r="I319" t="s">
+        <v>66</v>
+      </c>
+      <c r="J319" t="s">
+        <v>122</v>
+      </c>
+      <c r="N319" s="1">
+        <v>46276</v>
+      </c>
+      <c r="O319" t="s">
+        <v>144</v>
+      </c>
+      <c r="P319">
+        <v>8</v>
+      </c>
+      <c r="Q319">
+        <v>2026</v>
+      </c>
+      <c r="R319">
+        <v>18270269</v>
+      </c>
+      <c r="U319" t="s">
+        <v>179</v>
+      </c>
+      <c r="V319" s="1">
+        <v>46276.41675075232</v>
+      </c>
+      <c r="W319">
+        <v>4</v>
+      </c>
+      <c r="X319" t="s">
+        <v>181</v>
+      </c>
+      <c r="Y319" t="s">
+        <v>301</v>
+      </c>
+      <c r="AB319">
+        <v>0</v>
+      </c>
+      <c r="AC319" t="s">
         <v>305</v>
       </c>
-      <c r="AI318" t="s">
-        <v>309</v>
+      <c r="AH319" t="s">
+        <v>306</v>
+      </c>
+      <c r="AI319" t="s">
+        <v>310</v>
       </c>
     </row>
   </sheetData>

--- a/data/base/goias.xlsx
+++ b/data/base/goias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4584" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4600" uniqueCount="318">
   <si>
     <t>CodCliente</t>
   </si>
@@ -809,6 +809,9 @@
     <t>Imposto enviado via SCI Report - Data Comentário: 14/09/2026 13:54</t>
   </si>
   <si>
+    <t>Imposto enviado via SCI Report - Data Comentário: 15/09/2026 10:07</t>
+  </si>
+  <si>
     <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 10/09/2026 
 em processamento - Data Comentário: 08/09/2026 16:10</t>
   </si>
@@ -863,6 +866,10 @@
   </si>
   <si>
     <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 11/09/2026 - Data Comentário: 04/09/2026 17:02</t>
+  </si>
+  <si>
+    <t>Comentário Colaborador + Previsão De Conclusão   Previsão para conclusão dia 15/09/2026 
+Em elaboração. - Data Comentário: 14/09/2026 17:53</t>
   </si>
   <si>
     <t>Controladoria, Erro de baixa, Chamado Nº Nº DO CHAMADO = 83973 - Data Comentário: 14/09/2026 17:50</t>
@@ -1322,7 +1329,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AI322"/>
+  <dimension ref="A1:AI323"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:35">
@@ -1503,10 +1510,10 @@
         <v>147</v>
       </c>
       <c r="AH2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="3" spans="1:35">
@@ -1580,10 +1587,10 @@
         <v>148</v>
       </c>
       <c r="AH3" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI3" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="4" spans="1:35">
@@ -1657,10 +1664,10 @@
         <v>147</v>
       </c>
       <c r="AH4" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI4" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="5" spans="1:35">
@@ -1731,10 +1738,10 @@
         <v>147</v>
       </c>
       <c r="AH5" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI5" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="6" spans="1:35">
@@ -1805,10 +1812,10 @@
         <v>148</v>
       </c>
       <c r="AH6" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI6" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="7" spans="1:35">
@@ -1879,10 +1886,10 @@
         <v>148</v>
       </c>
       <c r="AH7" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI7" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="8" spans="1:35">
@@ -1953,10 +1960,10 @@
         <v>149</v>
       </c>
       <c r="AH8" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI8" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="9" spans="1:35">
@@ -2027,10 +2034,10 @@
         <v>147</v>
       </c>
       <c r="AH9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10" spans="1:35">
@@ -2101,10 +2108,10 @@
         <v>150</v>
       </c>
       <c r="AH10" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI10" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="11" spans="1:35">
@@ -2175,10 +2182,10 @@
         <v>150</v>
       </c>
       <c r="AH11" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI11" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="12" spans="1:35">
@@ -2249,10 +2256,10 @@
         <v>151</v>
       </c>
       <c r="AH12" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI12" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="13" spans="1:35">
@@ -2320,13 +2327,13 @@
         <v>0</v>
       </c>
       <c r="AC13" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AH13" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI13" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="14" spans="1:35">
@@ -2394,13 +2401,13 @@
         <v>0</v>
       </c>
       <c r="AC14" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AH14" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI14" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="15" spans="1:35">
@@ -2468,10 +2475,10 @@
         <v>0</v>
       </c>
       <c r="AH15" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI15" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="16" spans="1:35">
@@ -2533,10 +2540,10 @@
         <v>0</v>
       </c>
       <c r="AH16" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI16" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="17" spans="1:35">
@@ -2604,10 +2611,10 @@
         <v>0</v>
       </c>
       <c r="AH17" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI17" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="18" spans="1:35">
@@ -2681,10 +2688,10 @@
         <v>153</v>
       </c>
       <c r="AH18" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI18" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="19" spans="1:35">
@@ -2758,10 +2765,10 @@
         <v>152</v>
       </c>
       <c r="AH19" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI19" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="20" spans="1:35">
@@ -2835,10 +2842,10 @@
         <v>153</v>
       </c>
       <c r="AH20" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI20" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="21" spans="1:35">
@@ -2912,10 +2919,10 @@
         <v>151</v>
       </c>
       <c r="AH21" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI21" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="22" spans="1:35">
@@ -2986,10 +2993,10 @@
         <v>154</v>
       </c>
       <c r="AH22" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI22" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="23" spans="1:35">
@@ -3060,10 +3067,10 @@
         <v>151</v>
       </c>
       <c r="AH23" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI23" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="24" spans="1:35">
@@ -3134,10 +3141,10 @@
         <v>151</v>
       </c>
       <c r="AH24" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI24" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="25" spans="1:35">
@@ -3208,10 +3215,10 @@
         <v>151</v>
       </c>
       <c r="AH25" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI25" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="26" spans="1:35">
@@ -3282,10 +3289,10 @@
         <v>152</v>
       </c>
       <c r="AH26" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI26" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="27" spans="1:35">
@@ -3356,10 +3363,10 @@
         <v>151</v>
       </c>
       <c r="AH27" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI27" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="28" spans="1:35">
@@ -3430,10 +3437,10 @@
         <v>151</v>
       </c>
       <c r="AH28" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI28" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="29" spans="1:35">
@@ -3504,10 +3511,10 @@
         <v>151</v>
       </c>
       <c r="AH29" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI29" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="30" spans="1:35">
@@ -3578,10 +3585,10 @@
         <v>155</v>
       </c>
       <c r="AH30" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI30" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="31" spans="1:35">
@@ -3658,10 +3665,10 @@
         <v>156</v>
       </c>
       <c r="AH31" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI31" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="32" spans="1:35">
@@ -3732,10 +3739,10 @@
         <v>157</v>
       </c>
       <c r="AH32" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI32" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="33" spans="1:35">
@@ -3812,10 +3819,10 @@
         <v>158</v>
       </c>
       <c r="AH33" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI33" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="34" spans="1:35">
@@ -3889,10 +3896,10 @@
         <v>159</v>
       </c>
       <c r="AH34" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI34" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="35" spans="1:35">
@@ -3966,13 +3973,13 @@
         <v>0</v>
       </c>
       <c r="AC35" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AH35" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI35" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="36" spans="1:35">
@@ -4049,10 +4056,10 @@
         <v>161</v>
       </c>
       <c r="AH36" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI36" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="37" spans="1:35">
@@ -4129,10 +4136,10 @@
         <v>155</v>
       </c>
       <c r="AH37" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI37" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="38" spans="1:35">
@@ -4206,10 +4213,10 @@
         <v>177</v>
       </c>
       <c r="AH38" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI38" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="39" spans="1:35">
@@ -4286,10 +4293,10 @@
         <v>156</v>
       </c>
       <c r="AH39" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI39" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="40" spans="1:35">
@@ -4366,10 +4373,10 @@
         <v>156</v>
       </c>
       <c r="AH40" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI40" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="41" spans="1:35">
@@ -4446,10 +4453,10 @@
         <v>156</v>
       </c>
       <c r="AH41" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI41" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="42" spans="1:35">
@@ -4526,10 +4533,10 @@
         <v>155</v>
       </c>
       <c r="AH42" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI42" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="43" spans="1:35">
@@ -4606,10 +4613,10 @@
         <v>162</v>
       </c>
       <c r="AH43" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI43" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="44" spans="1:35">
@@ -4686,10 +4693,10 @@
         <v>157</v>
       </c>
       <c r="AH44" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI44" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="45" spans="1:35">
@@ -4766,10 +4773,10 @@
         <v>158</v>
       </c>
       <c r="AH45" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI45" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="46" spans="1:35">
@@ -4837,10 +4844,10 @@
         <v>159</v>
       </c>
       <c r="AH46" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI46" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="47" spans="1:35">
@@ -4911,10 +4918,10 @@
         <v>156</v>
       </c>
       <c r="AH47" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI47" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="48" spans="1:35">
@@ -4985,10 +4992,10 @@
         <v>156</v>
       </c>
       <c r="AH48" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI48" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="49" spans="1:35">
@@ -5059,10 +5066,10 @@
         <v>156</v>
       </c>
       <c r="AH49" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI49" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:35">
@@ -5133,10 +5140,10 @@
         <v>155</v>
       </c>
       <c r="AH50" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI50" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:35">
@@ -5207,10 +5214,10 @@
         <v>162</v>
       </c>
       <c r="AH51" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI51" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" spans="1:35">
@@ -5287,10 +5294,10 @@
         <v>157</v>
       </c>
       <c r="AH52" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI52" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53" spans="1:35">
@@ -5361,10 +5368,10 @@
         <v>158</v>
       </c>
       <c r="AH53" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI53" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:35">
@@ -5441,10 +5448,10 @@
         <v>156</v>
       </c>
       <c r="AH54" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI54" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="55" spans="1:35">
@@ -5521,10 +5528,10 @@
         <v>156</v>
       </c>
       <c r="AH55" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI55" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="56" spans="1:35">
@@ -5601,10 +5608,10 @@
         <v>156</v>
       </c>
       <c r="AH56" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI56" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="57" spans="1:35">
@@ -5681,10 +5688,10 @@
         <v>155</v>
       </c>
       <c r="AH57" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI57" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="58" spans="1:35">
@@ -5758,10 +5765,10 @@
         <v>159</v>
       </c>
       <c r="AH58" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI58" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="59" spans="1:35">
@@ -5835,13 +5842,13 @@
         <v>0</v>
       </c>
       <c r="AC59" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AH59" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI59" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="60" spans="1:35">
@@ -5918,10 +5925,10 @@
         <v>156</v>
       </c>
       <c r="AH60" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI60" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="61" spans="1:35">
@@ -5998,10 +6005,10 @@
         <v>156</v>
       </c>
       <c r="AH61" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI61" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="62" spans="1:35">
@@ -6078,10 +6085,10 @@
         <v>156</v>
       </c>
       <c r="AH62" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI62" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="63" spans="1:35">
@@ -6158,10 +6165,10 @@
         <v>155</v>
       </c>
       <c r="AH63" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI63" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="64" spans="1:35">
@@ -6238,10 +6245,10 @@
         <v>162</v>
       </c>
       <c r="AH64" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI64" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="65" spans="1:35">
@@ -6318,10 +6325,10 @@
         <v>157</v>
       </c>
       <c r="AH65" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI65" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="66" spans="1:35">
@@ -6398,10 +6405,10 @@
         <v>158</v>
       </c>
       <c r="AH66" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI66" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="67" spans="1:35">
@@ -6478,10 +6485,10 @@
         <v>156</v>
       </c>
       <c r="AH67" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI67" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="68" spans="1:35">
@@ -6549,10 +6556,10 @@
         <v>159</v>
       </c>
       <c r="AH68" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI68" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="69" spans="1:35">
@@ -6620,13 +6627,13 @@
         <v>0</v>
       </c>
       <c r="AC69" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AH69" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI69" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="70" spans="1:35">
@@ -6697,10 +6704,10 @@
         <v>156</v>
       </c>
       <c r="AH70" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI70" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="71" spans="1:35">
@@ -6771,10 +6778,10 @@
         <v>156</v>
       </c>
       <c r="AH71" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI71" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="72" spans="1:35">
@@ -6845,10 +6852,10 @@
         <v>156</v>
       </c>
       <c r="AH72" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI72" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="73" spans="1:35">
@@ -6919,10 +6926,10 @@
         <v>155</v>
       </c>
       <c r="AH73" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI73" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="74" spans="1:35">
@@ -6993,10 +7000,10 @@
         <v>162</v>
       </c>
       <c r="AH74" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI74" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="75" spans="1:35">
@@ -7067,10 +7074,10 @@
         <v>157</v>
       </c>
       <c r="AH75" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI75" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="76" spans="1:35">
@@ -7141,10 +7148,10 @@
         <v>158</v>
       </c>
       <c r="AH76" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI76" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="77" spans="1:35">
@@ -7215,10 +7222,10 @@
         <v>158</v>
       </c>
       <c r="AH77" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI77" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="78" spans="1:35">
@@ -7289,10 +7296,10 @@
         <v>158</v>
       </c>
       <c r="AH78" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI78" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="79" spans="1:35">
@@ -7363,10 +7370,10 @@
         <v>158</v>
       </c>
       <c r="AH79" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI79" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="80" spans="1:35">
@@ -7437,10 +7444,10 @@
         <v>178</v>
       </c>
       <c r="AH80" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI80" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="81" spans="1:35">
@@ -7508,10 +7515,10 @@
         <v>178</v>
       </c>
       <c r="AH81" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI81" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="82" spans="1:35">
@@ -7582,10 +7589,10 @@
         <v>165</v>
       </c>
       <c r="AH82" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI82" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="83" spans="1:35">
@@ -7656,10 +7663,10 @@
         <v>178</v>
       </c>
       <c r="AH83" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI83" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="84" spans="1:35">
@@ -7727,10 +7734,10 @@
         <v>178</v>
       </c>
       <c r="AH84" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI84" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="85" spans="1:35">
@@ -7801,10 +7808,10 @@
         <v>178</v>
       </c>
       <c r="AH85" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI85" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="86" spans="1:35">
@@ -7869,10 +7876,10 @@
         <v>165</v>
       </c>
       <c r="AH86" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI86" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="87" spans="1:35">
@@ -7943,10 +7950,10 @@
         <v>178</v>
       </c>
       <c r="AH87" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI87" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="88" spans="1:35">
@@ -8014,10 +8021,10 @@
         <v>178</v>
       </c>
       <c r="AH88" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI88" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="89" spans="1:35">
@@ -8088,10 +8095,10 @@
         <v>178</v>
       </c>
       <c r="AH89" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI89" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="90" spans="1:35">
@@ -8156,10 +8163,10 @@
         <v>178</v>
       </c>
       <c r="AH90" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI90" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="91" spans="1:35">
@@ -8224,10 +8231,10 @@
         <v>165</v>
       </c>
       <c r="AH91" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI91" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="92" spans="1:35">
@@ -8298,10 +8305,10 @@
         <v>178</v>
       </c>
       <c r="AH92" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI92" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="93" spans="1:35">
@@ -8369,10 +8376,10 @@
         <v>178</v>
       </c>
       <c r="AH93" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI93" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="94" spans="1:35">
@@ -8443,10 +8450,10 @@
         <v>178</v>
       </c>
       <c r="AH94" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI94" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="95" spans="1:35">
@@ -8511,10 +8518,10 @@
         <v>178</v>
       </c>
       <c r="AH95" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI95" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="96" spans="1:35">
@@ -8579,10 +8586,10 @@
         <v>165</v>
       </c>
       <c r="AH96" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI96" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="97" spans="1:35">
@@ -8653,10 +8660,10 @@
         <v>178</v>
       </c>
       <c r="AH97" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI97" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="98" spans="1:35">
@@ -8724,10 +8731,10 @@
         <v>178</v>
       </c>
       <c r="AH98" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI98" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="99" spans="1:35">
@@ -8798,10 +8805,10 @@
         <v>165</v>
       </c>
       <c r="AH99" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI99" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="100" spans="1:35">
@@ -8878,10 +8885,10 @@
         <v>178</v>
       </c>
       <c r="AH100" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI100" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="101" spans="1:35">
@@ -8949,10 +8956,10 @@
         <v>178</v>
       </c>
       <c r="AH101" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI101" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="102" spans="1:35">
@@ -9023,10 +9030,10 @@
         <v>178</v>
       </c>
       <c r="AH102" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI102" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="103" spans="1:35">
@@ -9094,10 +9101,10 @@
         <v>178</v>
       </c>
       <c r="AH103" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI103" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="104" spans="1:35">
@@ -9168,10 +9175,10 @@
         <v>178</v>
       </c>
       <c r="AH104" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI104" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="105" spans="1:35">
@@ -9236,10 +9243,10 @@
         <v>178</v>
       </c>
       <c r="AH105" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI105" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="106" spans="1:35">
@@ -9304,10 +9311,10 @@
         <v>165</v>
       </c>
       <c r="AH106" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI106" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="107" spans="1:35">
@@ -9378,10 +9385,10 @@
         <v>178</v>
       </c>
       <c r="AH107" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI107" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="108" spans="1:35">
@@ -9452,10 +9459,10 @@
         <v>178</v>
       </c>
       <c r="AH108" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI108" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="109" spans="1:35">
@@ -9523,10 +9530,10 @@
         <v>178</v>
       </c>
       <c r="AH109" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI109" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="110" spans="1:35">
@@ -9597,10 +9604,10 @@
         <v>165</v>
       </c>
       <c r="AH110" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI110" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="111" spans="1:35">
@@ -9668,10 +9675,10 @@
         <v>164</v>
       </c>
       <c r="AH111" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI111" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="112" spans="1:35">
@@ -9742,10 +9749,10 @@
         <v>165</v>
       </c>
       <c r="AH112" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI112" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="113" spans="1:35">
@@ -9816,10 +9823,10 @@
         <v>163</v>
       </c>
       <c r="AH113" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI113" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="114" spans="1:35">
@@ -9887,10 +9894,10 @@
         <v>164</v>
       </c>
       <c r="AH114" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI114" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="115" spans="1:35">
@@ -9961,10 +9968,10 @@
         <v>165</v>
       </c>
       <c r="AH115" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI115" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="116" spans="1:35">
@@ -10035,10 +10042,10 @@
         <v>178</v>
       </c>
       <c r="AH116" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI116" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="117" spans="1:35">
@@ -10106,10 +10113,10 @@
         <v>178</v>
       </c>
       <c r="AH117" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI117" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="118" spans="1:35">
@@ -10180,10 +10187,10 @@
         <v>178</v>
       </c>
       <c r="AH118" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI118" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="119" spans="1:35">
@@ -10248,10 +10255,10 @@
         <v>178</v>
       </c>
       <c r="AH119" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI119" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="120" spans="1:35">
@@ -10316,10 +10323,10 @@
         <v>165</v>
       </c>
       <c r="AH120" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI120" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="121" spans="1:35">
@@ -10390,10 +10397,10 @@
         <v>178</v>
       </c>
       <c r="AH121" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI121" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="122" spans="1:35">
@@ -10461,10 +10468,10 @@
         <v>178</v>
       </c>
       <c r="AH122" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI122" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="123" spans="1:35">
@@ -10535,10 +10542,10 @@
         <v>178</v>
       </c>
       <c r="AH123" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI123" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="124" spans="1:35">
@@ -10603,10 +10610,10 @@
         <v>178</v>
       </c>
       <c r="AH124" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI124" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="125" spans="1:35">
@@ -10671,10 +10678,10 @@
         <v>165</v>
       </c>
       <c r="AH125" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI125" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="126" spans="1:35">
@@ -10751,10 +10758,10 @@
         <v>165</v>
       </c>
       <c r="AH126" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI126" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="127" spans="1:35">
@@ -10831,10 +10838,10 @@
         <v>165</v>
       </c>
       <c r="AH127" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI127" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="128" spans="1:35">
@@ -10905,10 +10912,10 @@
         <v>168</v>
       </c>
       <c r="AH128" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI128" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="129" spans="1:35">
@@ -10979,10 +10986,10 @@
         <v>168</v>
       </c>
       <c r="AH129" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI129" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="130" spans="1:35">
@@ -11059,10 +11066,10 @@
         <v>168</v>
       </c>
       <c r="AH130" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI130" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="131" spans="1:35">
@@ -11133,10 +11140,10 @@
         <v>168</v>
       </c>
       <c r="AH131" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI131" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="132" spans="1:35">
@@ -11207,10 +11214,10 @@
         <v>168</v>
       </c>
       <c r="AH132" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI132" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="133" spans="1:35">
@@ -11281,10 +11288,10 @@
         <v>168</v>
       </c>
       <c r="AH133" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI133" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="134" spans="1:35">
@@ -11355,10 +11362,10 @@
         <v>168</v>
       </c>
       <c r="AH134" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI134" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="135" spans="1:35">
@@ -11435,10 +11442,10 @@
         <v>168</v>
       </c>
       <c r="AH135" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI135" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="136" spans="1:35">
@@ -11509,10 +11516,10 @@
         <v>168</v>
       </c>
       <c r="AH136" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI136" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="137" spans="1:35">
@@ -11583,10 +11590,10 @@
         <v>168</v>
       </c>
       <c r="AH137" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI137" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="138" spans="1:35">
@@ -11657,10 +11664,10 @@
         <v>168</v>
       </c>
       <c r="AH138" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI138" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="139" spans="1:35">
@@ -11737,10 +11744,10 @@
         <v>168</v>
       </c>
       <c r="AH139" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI139" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="140" spans="1:35">
@@ -11811,10 +11818,10 @@
         <v>168</v>
       </c>
       <c r="AH140" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI140" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="141" spans="1:35">
@@ -11885,10 +11892,10 @@
         <v>168</v>
       </c>
       <c r="AH141" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI141" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="142" spans="1:35">
@@ -11959,10 +11966,10 @@
         <v>168</v>
       </c>
       <c r="AH142" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI142" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="143" spans="1:35">
@@ -12033,10 +12040,10 @@
         <v>168</v>
       </c>
       <c r="AH143" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI143" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="144" spans="1:35">
@@ -12107,10 +12114,10 @@
         <v>168</v>
       </c>
       <c r="AH144" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI144" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="145" spans="1:35">
@@ -12181,10 +12188,10 @@
         <v>168</v>
       </c>
       <c r="AH145" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI145" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="146" spans="1:35">
@@ -12255,10 +12262,10 @@
         <v>168</v>
       </c>
       <c r="AH146" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI146" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="147" spans="1:35">
@@ -12329,10 +12336,10 @@
         <v>168</v>
       </c>
       <c r="AH147" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI147" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="148" spans="1:35">
@@ -12403,10 +12410,10 @@
         <v>168</v>
       </c>
       <c r="AH148" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI148" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="149" spans="1:35">
@@ -12477,10 +12484,10 @@
         <v>168</v>
       </c>
       <c r="AH149" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI149" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="150" spans="1:35">
@@ -12557,10 +12564,10 @@
         <v>168</v>
       </c>
       <c r="AH150" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI150" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="151" spans="1:35">
@@ -12631,10 +12638,10 @@
         <v>168</v>
       </c>
       <c r="AH151" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI151" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="152" spans="1:35">
@@ -12705,10 +12712,10 @@
         <v>168</v>
       </c>
       <c r="AH152" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI152" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="153" spans="1:35">
@@ -12779,10 +12786,10 @@
         <v>168</v>
       </c>
       <c r="AH153" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI153" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="154" spans="1:35">
@@ -12853,10 +12860,10 @@
         <v>169</v>
       </c>
       <c r="AH154" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI154" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="155" spans="1:35">
@@ -12927,10 +12934,10 @@
         <v>169</v>
       </c>
       <c r="AH155" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI155" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="156" spans="1:35">
@@ -13001,10 +13008,10 @@
         <v>169</v>
       </c>
       <c r="AH156" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI156" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="157" spans="1:35">
@@ -13075,10 +13082,10 @@
         <v>169</v>
       </c>
       <c r="AH157" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI157" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="158" spans="1:35">
@@ -13149,10 +13156,10 @@
         <v>169</v>
       </c>
       <c r="AH158" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI158" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="159" spans="1:35">
@@ -13223,10 +13230,10 @@
         <v>169</v>
       </c>
       <c r="AH159" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI159" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="160" spans="1:35">
@@ -13297,10 +13304,10 @@
         <v>169</v>
       </c>
       <c r="AH160" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI160" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="161" spans="1:35">
@@ -13371,10 +13378,10 @@
         <v>169</v>
       </c>
       <c r="AH161" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI161" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="162" spans="1:35">
@@ -13445,10 +13452,10 @@
         <v>169</v>
       </c>
       <c r="AH162" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI162" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="163" spans="1:35">
@@ -13519,10 +13526,10 @@
         <v>169</v>
       </c>
       <c r="AH163" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI163" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="164" spans="1:35">
@@ -13593,10 +13600,10 @@
         <v>169</v>
       </c>
       <c r="AH164" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI164" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="165" spans="1:35">
@@ -13667,10 +13674,10 @@
         <v>169</v>
       </c>
       <c r="AH165" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI165" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="166" spans="1:35">
@@ -13741,10 +13748,10 @@
         <v>169</v>
       </c>
       <c r="AH166" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI166" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="167" spans="1:35">
@@ -13815,10 +13822,10 @@
         <v>169</v>
       </c>
       <c r="AH167" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI167" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="168" spans="1:35">
@@ -13889,10 +13896,10 @@
         <v>169</v>
       </c>
       <c r="AH168" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI168" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="169" spans="1:35">
@@ -13966,10 +13973,10 @@
         <v>169</v>
       </c>
       <c r="AH169" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI169" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="170" spans="1:35">
@@ -14043,10 +14050,10 @@
         <v>169</v>
       </c>
       <c r="AH170" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI170" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="171" spans="1:35">
@@ -14120,10 +14127,10 @@
         <v>169</v>
       </c>
       <c r="AH171" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI171" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="172" spans="1:35">
@@ -14197,10 +14204,10 @@
         <v>169</v>
       </c>
       <c r="AH172" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI172" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="173" spans="1:35">
@@ -14274,10 +14281,10 @@
         <v>169</v>
       </c>
       <c r="AH173" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI173" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="174" spans="1:35">
@@ -14351,10 +14358,10 @@
         <v>169</v>
       </c>
       <c r="AH174" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI174" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="175" spans="1:35">
@@ -14428,10 +14435,10 @@
         <v>169</v>
       </c>
       <c r="AH175" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI175" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="176" spans="1:35">
@@ -14505,10 +14512,10 @@
         <v>169</v>
       </c>
       <c r="AH176" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI176" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="177" spans="1:35">
@@ -14582,10 +14589,10 @@
         <v>169</v>
       </c>
       <c r="AH177" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI177" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="178" spans="1:35">
@@ -14659,10 +14666,10 @@
         <v>169</v>
       </c>
       <c r="AH178" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI178" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="179" spans="1:35">
@@ -14736,10 +14743,10 @@
         <v>169</v>
       </c>
       <c r="AH179" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI179" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="180" spans="1:35">
@@ -14813,10 +14820,10 @@
         <v>169</v>
       </c>
       <c r="AH180" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI180" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="181" spans="1:35">
@@ -14890,10 +14897,10 @@
         <v>169</v>
       </c>
       <c r="AH181" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI181" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="182" spans="1:35">
@@ -14967,10 +14974,10 @@
         <v>169</v>
       </c>
       <c r="AH182" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI182" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="183" spans="1:35">
@@ -15038,10 +15045,10 @@
         <v>169</v>
       </c>
       <c r="AH183" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI183" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="184" spans="1:35">
@@ -15109,10 +15116,10 @@
         <v>169</v>
       </c>
       <c r="AH184" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI184" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="185" spans="1:35">
@@ -15180,10 +15187,10 @@
         <v>169</v>
       </c>
       <c r="AH185" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI185" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="186" spans="1:35">
@@ -15251,10 +15258,10 @@
         <v>169</v>
       </c>
       <c r="AH186" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI186" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="187" spans="1:35">
@@ -15322,10 +15329,10 @@
         <v>169</v>
       </c>
       <c r="AH187" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI187" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="188" spans="1:35">
@@ -15393,10 +15400,10 @@
         <v>169</v>
       </c>
       <c r="AH188" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI188" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="189" spans="1:35">
@@ -15464,10 +15471,10 @@
         <v>54</v>
       </c>
       <c r="AH189" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI189" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="190" spans="1:35">
@@ -15535,10 +15542,10 @@
         <v>54</v>
       </c>
       <c r="AH190" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI190" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="191" spans="1:35">
@@ -15606,10 +15613,10 @@
         <v>54</v>
       </c>
       <c r="AH191" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI191" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="192" spans="1:35">
@@ -15677,10 +15684,10 @@
         <v>54</v>
       </c>
       <c r="AH192" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI192" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="193" spans="1:35">
@@ -15748,10 +15755,10 @@
         <v>170</v>
       </c>
       <c r="AH193" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI193" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="194" spans="1:35">
@@ -15819,10 +15826,10 @@
         <v>55</v>
       </c>
       <c r="AH194" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI194" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="195" spans="1:35">
@@ -15890,10 +15897,10 @@
         <v>54</v>
       </c>
       <c r="AH195" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI195" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="196" spans="1:35">
@@ -15961,10 +15968,10 @@
         <v>54</v>
       </c>
       <c r="AH196" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI196" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="197" spans="1:35">
@@ -16032,10 +16039,10 @@
         <v>54</v>
       </c>
       <c r="AH197" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI197" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="198" spans="1:35">
@@ -16103,10 +16110,10 @@
         <v>170</v>
       </c>
       <c r="AH198" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI198" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="199" spans="1:35">
@@ -16174,10 +16181,10 @@
         <v>54</v>
       </c>
       <c r="AH199" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI199" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="200" spans="1:35">
@@ -16245,10 +16252,10 @@
         <v>170</v>
       </c>
       <c r="AH200" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI200" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="201" spans="1:35">
@@ -16316,10 +16323,10 @@
         <v>54</v>
       </c>
       <c r="AH201" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI201" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="202" spans="1:35">
@@ -16387,10 +16394,10 @@
         <v>54</v>
       </c>
       <c r="AH202" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI202" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="203" spans="1:35">
@@ -16458,10 +16465,10 @@
         <v>54</v>
       </c>
       <c r="AH203" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI203" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="204" spans="1:35">
@@ -16529,10 +16536,10 @@
         <v>54</v>
       </c>
       <c r="AH204" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI204" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="205" spans="1:35">
@@ -16600,10 +16607,10 @@
         <v>54</v>
       </c>
       <c r="AH205" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI205" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="206" spans="1:35">
@@ -16671,10 +16678,10 @@
         <v>54</v>
       </c>
       <c r="AH206" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI206" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="207" spans="1:35">
@@ -16742,10 +16749,10 @@
         <v>170</v>
       </c>
       <c r="AH207" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI207" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="208" spans="1:35">
@@ -16813,10 +16820,10 @@
         <v>55</v>
       </c>
       <c r="AH208" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI208" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="209" spans="1:35">
@@ -16887,10 +16894,10 @@
         <v>54</v>
       </c>
       <c r="AH209" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI209" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="210" spans="1:35">
@@ -16961,10 +16968,10 @@
         <v>54</v>
       </c>
       <c r="AH210" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI210" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="211" spans="1:35">
@@ -17035,10 +17042,10 @@
         <v>54</v>
       </c>
       <c r="AH211" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI211" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="212" spans="1:35">
@@ -17109,10 +17116,10 @@
         <v>54</v>
       </c>
       <c r="AH212" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI212" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="213" spans="1:35">
@@ -17180,10 +17187,10 @@
         <v>54</v>
       </c>
       <c r="AH213" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI213" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="214" spans="1:35">
@@ -17251,10 +17258,10 @@
         <v>54</v>
       </c>
       <c r="AH214" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI214" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="215" spans="1:35">
@@ -17319,10 +17326,10 @@
         <v>0</v>
       </c>
       <c r="AH215" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI215" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="216" spans="1:35">
@@ -17384,10 +17391,10 @@
         <v>0</v>
       </c>
       <c r="AH216" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI216" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="217" spans="1:35">
@@ -17455,13 +17462,13 @@
         <v>0</v>
       </c>
       <c r="AC217" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AH217" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI217" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="218" spans="1:35">
@@ -17532,10 +17539,10 @@
         <v>152</v>
       </c>
       <c r="AH218" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI218" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="219" spans="1:35">
@@ -17612,10 +17619,10 @@
         <v>162</v>
       </c>
       <c r="AH219" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI219" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="220" spans="1:35">
@@ -17686,10 +17693,10 @@
         <v>155</v>
       </c>
       <c r="AH220" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI220" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="221" spans="1:35">
@@ -17760,10 +17767,10 @@
         <v>162</v>
       </c>
       <c r="AH221" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI221" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="222" spans="1:35">
@@ -17834,10 +17841,10 @@
         <v>155</v>
       </c>
       <c r="AH222" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI222" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="223" spans="1:35">
@@ -17908,10 +17915,10 @@
         <v>162</v>
       </c>
       <c r="AH223" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI223" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="224" spans="1:35">
@@ -17982,10 +17989,10 @@
         <v>159</v>
       </c>
       <c r="AH224" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI224" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="225" spans="1:35">
@@ -18059,10 +18066,10 @@
         <v>156</v>
       </c>
       <c r="AH225" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI225" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="226" spans="1:35">
@@ -18136,24 +18143,24 @@
         <v>161</v>
       </c>
       <c r="AH226" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI226" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="227" spans="1:35">
       <c r="A227">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B227" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C227" t="s">
         <v>50</v>
       </c>
       <c r="D227" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E227" t="s">
         <v>55</v>
@@ -18183,7 +18190,7 @@
         <v>2026</v>
       </c>
       <c r="R227">
-        <v>18257668</v>
+        <v>18256366</v>
       </c>
       <c r="S227" t="s">
         <v>156</v>
@@ -18195,7 +18202,7 @@
         <v>181</v>
       </c>
       <c r="V227" s="1">
-        <v>46279.72223498843</v>
+        <v>46279.72223515046</v>
       </c>
       <c r="W227">
         <v>-1</v>
@@ -18213,18 +18220,18 @@
         <v>156</v>
       </c>
       <c r="AH227" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI227" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="228" spans="1:35">
       <c r="A228">
-        <v>6628</v>
+        <v>6945</v>
       </c>
       <c r="B228" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C228" t="s">
         <v>50</v>
@@ -18233,10 +18240,10 @@
         <v>52</v>
       </c>
       <c r="E228" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F228" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G228">
         <v>7012</v>
@@ -18260,40 +18267,40 @@
         <v>2026</v>
       </c>
       <c r="R228">
-        <v>18256366</v>
+        <v>18254903</v>
       </c>
       <c r="S228" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="T228" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="U228" t="s">
         <v>181</v>
       </c>
       <c r="V228" s="1">
-        <v>46279.72223515046</v>
+        <v>46280.43132989584</v>
       </c>
       <c r="W228">
         <v>-1</v>
       </c>
       <c r="X228" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Y228" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AB228">
         <v>0</v>
       </c>
       <c r="AC228" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AH228" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI228" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="229" spans="1:35">
@@ -18358,7 +18365,7 @@
         <v>189</v>
       </c>
       <c r="Y229" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AB229">
         <v>0</v>
@@ -18367,10 +18374,10 @@
         <v>159</v>
       </c>
       <c r="AH229" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI229" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="230" spans="1:35">
@@ -18438,7 +18445,7 @@
         <v>190</v>
       </c>
       <c r="Y230" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AB230">
         <v>0</v>
@@ -18447,10 +18454,10 @@
         <v>156</v>
       </c>
       <c r="AH230" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI230" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="231" spans="1:35">
@@ -18518,7 +18525,7 @@
         <v>184</v>
       </c>
       <c r="Y231" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AB231">
         <v>0</v>
@@ -18527,10 +18534,10 @@
         <v>156</v>
       </c>
       <c r="AH231" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI231" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="232" spans="1:35">
@@ -18598,7 +18605,7 @@
         <v>184</v>
       </c>
       <c r="Y232" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AB232">
         <v>0</v>
@@ -18607,10 +18614,10 @@
         <v>156</v>
       </c>
       <c r="AH232" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI232" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="233" spans="1:35">
@@ -18678,7 +18685,7 @@
         <v>188</v>
       </c>
       <c r="Y233" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AB233">
         <v>0</v>
@@ -18687,10 +18694,10 @@
         <v>162</v>
       </c>
       <c r="AH233" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI233" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="234" spans="1:35">
@@ -18758,7 +18765,7 @@
         <v>186</v>
       </c>
       <c r="Y234" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AB234">
         <v>0</v>
@@ -18767,10 +18774,10 @@
         <v>157</v>
       </c>
       <c r="AH234" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI234" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="235" spans="1:35">
@@ -18841,10 +18848,10 @@
         <v>158</v>
       </c>
       <c r="AH235" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI235" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="236" spans="1:35">
@@ -18906,7 +18913,7 @@
         <v>189</v>
       </c>
       <c r="Y236" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AB236">
         <v>0</v>
@@ -18915,10 +18922,10 @@
         <v>159</v>
       </c>
       <c r="AH236" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI236" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="237" spans="1:35">
@@ -18986,7 +18993,7 @@
         <v>190</v>
       </c>
       <c r="Y237" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AB237">
         <v>0</v>
@@ -18995,10 +19002,10 @@
         <v>156</v>
       </c>
       <c r="AH237" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI237" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="238" spans="1:35">
@@ -19063,7 +19070,7 @@
         <v>183</v>
       </c>
       <c r="Y238" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AB238">
         <v>0</v>
@@ -19072,10 +19079,10 @@
         <v>161</v>
       </c>
       <c r="AH238" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI238" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="239" spans="1:35">
@@ -19143,7 +19150,7 @@
         <v>184</v>
       </c>
       <c r="Y239" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AB239">
         <v>0</v>
@@ -19152,10 +19159,10 @@
         <v>156</v>
       </c>
       <c r="AH239" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI239" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="240" spans="1:35">
@@ -19223,7 +19230,7 @@
         <v>184</v>
       </c>
       <c r="Y240" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AB240">
         <v>0</v>
@@ -19232,10 +19239,10 @@
         <v>156</v>
       </c>
       <c r="AH240" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI240" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="241" spans="1:35">
@@ -19300,7 +19307,7 @@
         <v>192</v>
       </c>
       <c r="Y241" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AB241">
         <v>0</v>
@@ -19309,10 +19316,10 @@
         <v>155</v>
       </c>
       <c r="AH241" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI241" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="242" spans="1:35">
@@ -19377,7 +19384,7 @@
         <v>188</v>
       </c>
       <c r="Y242" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AB242">
         <v>0</v>
@@ -19386,10 +19393,10 @@
         <v>162</v>
       </c>
       <c r="AH242" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI242" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="243" spans="1:35">
@@ -19454,7 +19461,7 @@
         <v>186</v>
       </c>
       <c r="Y243" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AB243">
         <v>0</v>
@@ -19463,10 +19470,10 @@
         <v>157</v>
       </c>
       <c r="AH243" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI243" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="244" spans="1:35">
@@ -19531,7 +19538,7 @@
         <v>185</v>
       </c>
       <c r="Y244" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AB244">
         <v>0</v>
@@ -19540,10 +19547,10 @@
         <v>158</v>
       </c>
       <c r="AH244" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI244" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="245" spans="1:35">
@@ -19620,10 +19627,10 @@
         <v>162</v>
       </c>
       <c r="AH245" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI245" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="246" spans="1:35">
@@ -19685,7 +19692,7 @@
         <v>184</v>
       </c>
       <c r="Y246" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AB246">
         <v>0</v>
@@ -19694,10 +19701,10 @@
         <v>156</v>
       </c>
       <c r="AH246" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI246" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="247" spans="1:35">
@@ -19759,7 +19766,7 @@
         <v>184</v>
       </c>
       <c r="Y247" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AB247">
         <v>0</v>
@@ -19768,10 +19775,10 @@
         <v>156</v>
       </c>
       <c r="AH247" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI247" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="248" spans="1:35">
@@ -19839,10 +19846,10 @@
         <v>164</v>
       </c>
       <c r="AH248" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI248" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="249" spans="1:35">
@@ -19910,7 +19917,7 @@
         <v>183</v>
       </c>
       <c r="Y249" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AB249">
         <v>0</v>
@@ -19919,10 +19926,10 @@
         <v>163</v>
       </c>
       <c r="AH249" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI249" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="250" spans="1:35">
@@ -19990,10 +19997,10 @@
         <v>178</v>
       </c>
       <c r="AH250" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI250" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="251" spans="1:35">
@@ -20061,7 +20068,7 @@
         <v>184</v>
       </c>
       <c r="Y251" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AB251">
         <v>0</v>
@@ -20070,10 +20077,10 @@
         <v>178</v>
       </c>
       <c r="AH251" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI251" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="252" spans="1:35">
@@ -20138,7 +20145,7 @@
         <v>186</v>
       </c>
       <c r="Y252" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AB252">
         <v>0</v>
@@ -20147,24 +20154,24 @@
         <v>164</v>
       </c>
       <c r="AH252" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI252" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="253" spans="1:35">
       <c r="A253">
-        <v>6962</v>
+        <v>6949</v>
       </c>
       <c r="B253" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C253" t="s">
         <v>50</v>
       </c>
       <c r="D253" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E253" t="s">
         <v>54</v>
@@ -20187,6 +20194,9 @@
       <c r="N253" s="1">
         <v>46276</v>
       </c>
+      <c r="O253" t="s">
+        <v>146</v>
+      </c>
       <c r="P253">
         <v>8</v>
       </c>
@@ -20194,10 +20204,10 @@
         <v>2026</v>
       </c>
       <c r="R253">
-        <v>18186995</v>
+        <v>18214901</v>
       </c>
       <c r="S253" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="T253" t="s">
         <v>178</v>
@@ -20206,36 +20216,36 @@
         <v>180</v>
       </c>
       <c r="V253" s="1">
-        <v>46279.74982357639</v>
+        <v>46280.40395534722</v>
       </c>
       <c r="W253">
         <v>4</v>
       </c>
       <c r="X253" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="Y253" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AB253">
         <v>0</v>
       </c>
       <c r="AC253" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="AH253" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI253" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="254" spans="1:35">
       <c r="A254">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B254" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C254" t="s">
         <v>50</v>
@@ -20264,9 +20274,6 @@
       <c r="N254" s="1">
         <v>46276</v>
       </c>
-      <c r="O254" t="s">
-        <v>144</v>
-      </c>
       <c r="P254">
         <v>8</v>
       </c>
@@ -20274,7 +20281,7 @@
         <v>2026</v>
       </c>
       <c r="R254">
-        <v>18187261</v>
+        <v>18186995</v>
       </c>
       <c r="S254" t="s">
         <v>167</v>
@@ -20283,10 +20290,10 @@
         <v>178</v>
       </c>
       <c r="U254" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="V254" s="1">
-        <v>46276.66651596065</v>
+        <v>46279.74982357639</v>
       </c>
       <c r="W254">
         <v>4</v>
@@ -20295,7 +20302,7 @@
         <v>187</v>
       </c>
       <c r="Y254" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AB254">
         <v>0</v>
@@ -20304,33 +20311,33 @@
         <v>167</v>
       </c>
       <c r="AH254" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI254" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="255" spans="1:35">
       <c r="A255">
-        <v>6627</v>
+        <v>6963</v>
       </c>
       <c r="B255" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C255" t="s">
         <v>50</v>
       </c>
       <c r="D255" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E255" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F255" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G255">
-        <v>1866</v>
+        <v>6805</v>
       </c>
       <c r="H255">
         <v>0</v>
@@ -20339,10 +20346,13 @@
         <v>62</v>
       </c>
       <c r="J255" t="s">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="N255" s="1">
-        <v>46274</v>
+        <v>46276</v>
+      </c>
+      <c r="O255" t="s">
+        <v>144</v>
       </c>
       <c r="P255">
         <v>8</v>
@@ -20351,57 +20361,60 @@
         <v>2026</v>
       </c>
       <c r="R255">
-        <v>17968368</v>
+        <v>18187261</v>
       </c>
       <c r="S255" t="s">
-        <v>164</v>
+        <v>167</v>
+      </c>
+      <c r="T255" t="s">
+        <v>178</v>
       </c>
       <c r="U255" t="s">
         <v>182</v>
       </c>
       <c r="V255" s="1">
-        <v>46274.36843923611</v>
+        <v>46276.66651596065</v>
       </c>
       <c r="W255">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="X255" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Y255" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AB255">
         <v>0</v>
       </c>
       <c r="AC255" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="AH255" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="AI255" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="256" spans="1:35">
       <c r="A256">
-        <v>6962</v>
+        <v>6627</v>
       </c>
       <c r="B256" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C256" t="s">
         <v>50</v>
       </c>
       <c r="D256" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E256" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F256" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G256">
         <v>1866</v>
@@ -20425,48 +20438,45 @@
         <v>2026</v>
       </c>
       <c r="R256">
-        <v>18186946</v>
+        <v>17968368</v>
       </c>
       <c r="S256" t="s">
-        <v>167</v>
-      </c>
-      <c r="T256" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="U256" t="s">
         <v>182</v>
       </c>
       <c r="V256" s="1">
-        <v>46274.66470667824</v>
+        <v>46274.36843923611</v>
       </c>
       <c r="W256">
         <v>6</v>
       </c>
       <c r="X256" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="Y256" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AB256">
         <v>0</v>
       </c>
       <c r="AC256" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="AH256" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI256" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="257" spans="1:35">
       <c r="A257">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B257" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C257" t="s">
         <v>50</v>
@@ -20502,7 +20512,7 @@
         <v>2026</v>
       </c>
       <c r="R257">
-        <v>18187212</v>
+        <v>18186946</v>
       </c>
       <c r="S257" t="s">
         <v>167</v>
@@ -20514,7 +20524,7 @@
         <v>182</v>
       </c>
       <c r="V257" s="1">
-        <v>46274.74452168981</v>
+        <v>46274.66470667824</v>
       </c>
       <c r="W257">
         <v>6</v>
@@ -20523,7 +20533,7 @@
         <v>187</v>
       </c>
       <c r="Y257" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AB257">
         <v>0</v>
@@ -20532,33 +20542,33 @@
         <v>167</v>
       </c>
       <c r="AH257" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI257" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="258" spans="1:35">
       <c r="A258">
-        <v>6548</v>
+        <v>6963</v>
       </c>
       <c r="B258" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C258" t="s">
         <v>50</v>
       </c>
       <c r="D258" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E258" t="s">
         <v>54</v>
       </c>
       <c r="F258" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G258">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="H258">
         <v>0</v>
@@ -20567,14 +20577,11 @@
         <v>62</v>
       </c>
       <c r="J258" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N258" s="1">
         <v>46274</v>
       </c>
-      <c r="O258" t="s">
-        <v>142</v>
-      </c>
       <c r="P258">
         <v>8</v>
       </c>
@@ -20582,10 +20589,10 @@
         <v>2026</v>
       </c>
       <c r="R258">
-        <v>17988543</v>
+        <v>18187212</v>
       </c>
       <c r="S258" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="T258" t="s">
         <v>178</v>
@@ -20594,36 +20601,36 @@
         <v>182</v>
       </c>
       <c r="V258" s="1">
-        <v>46274.64801501157</v>
+        <v>46274.74452168981</v>
       </c>
       <c r="W258">
         <v>6</v>
       </c>
       <c r="X258" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="Y258" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AB258">
         <v>0</v>
       </c>
       <c r="AC258" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="AH258" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI258" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="259" spans="1:35">
       <c r="A259">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B259" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C259" t="s">
         <v>50</v>
@@ -20632,7 +20639,7 @@
         <v>51</v>
       </c>
       <c r="E259" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F259" t="s">
         <v>56</v>
@@ -20652,6 +20659,9 @@
       <c r="N259" s="1">
         <v>46274</v>
       </c>
+      <c r="O259" t="s">
+        <v>142</v>
+      </c>
       <c r="P259">
         <v>8</v>
       </c>
@@ -20659,54 +20669,60 @@
         <v>2026</v>
       </c>
       <c r="R259">
-        <v>17968379</v>
+        <v>17988543</v>
       </c>
       <c r="S259" t="s">
-        <v>164</v>
+        <v>163</v>
+      </c>
+      <c r="T259" t="s">
+        <v>178</v>
       </c>
       <c r="U259" t="s">
         <v>182</v>
       </c>
       <c r="V259" s="1">
-        <v>46274.36695243056</v>
+        <v>46274.64801501157</v>
       </c>
       <c r="W259">
         <v>6</v>
       </c>
       <c r="X259" t="s">
-        <v>184</v>
+        <v>183</v>
+      </c>
+      <c r="Y259" t="s">
+        <v>283</v>
       </c>
       <c r="AB259">
         <v>0</v>
       </c>
       <c r="AC259" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="AH259" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI259" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="260" spans="1:35">
       <c r="A260">
-        <v>6945</v>
+        <v>6627</v>
       </c>
       <c r="B260" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C260" t="s">
         <v>50</v>
       </c>
       <c r="D260" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E260" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F260" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G260">
         <v>1867</v>
@@ -20723,9 +20739,6 @@
       <c r="N260" s="1">
         <v>46274</v>
       </c>
-      <c r="O260" t="s">
-        <v>144</v>
-      </c>
       <c r="P260">
         <v>8</v>
       </c>
@@ -20733,51 +20746,48 @@
         <v>2026</v>
       </c>
       <c r="R260">
-        <v>18220182</v>
+        <v>17968379</v>
       </c>
       <c r="S260" t="s">
         <v>164</v>
       </c>
       <c r="U260" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="V260" s="1">
-        <v>46276.4084265625</v>
+        <v>46274.36695243056</v>
       </c>
       <c r="W260">
         <v>6</v>
       </c>
       <c r="X260" t="s">
-        <v>186</v>
-      </c>
-      <c r="Y260" t="s">
-        <v>282</v>
+        <v>184</v>
       </c>
       <c r="AB260">
         <v>0</v>
       </c>
       <c r="AC260" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="AH260" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI260" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="261" spans="1:35">
       <c r="A261">
-        <v>6962</v>
+        <v>6945</v>
       </c>
       <c r="B261" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C261" t="s">
         <v>50</v>
       </c>
       <c r="D261" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E261" t="s">
         <v>54</v>
@@ -20800,6 +20810,9 @@
       <c r="N261" s="1">
         <v>46274</v>
       </c>
+      <c r="O261" t="s">
+        <v>144</v>
+      </c>
       <c r="P261">
         <v>8</v>
       </c>
@@ -20807,45 +20820,45 @@
         <v>2026</v>
       </c>
       <c r="R261">
-        <v>18186953</v>
+        <v>18220182</v>
       </c>
       <c r="S261" t="s">
-        <v>167</v>
-      </c>
-      <c r="T261" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="U261" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="V261" s="1">
-        <v>46274.7274781713</v>
+        <v>46276.4084265625</v>
       </c>
       <c r="W261">
         <v>6</v>
       </c>
       <c r="X261" t="s">
-        <v>187</v>
+        <v>186</v>
+      </c>
+      <c r="Y261" t="s">
+        <v>284</v>
       </c>
       <c r="AB261">
         <v>0</v>
       </c>
       <c r="AC261" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="AH261" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI261" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="262" spans="1:35">
       <c r="A262">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B262" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C262" t="s">
         <v>50</v>
@@ -20881,7 +20894,7 @@
         <v>2026</v>
       </c>
       <c r="R262">
-        <v>18187219</v>
+        <v>18186953</v>
       </c>
       <c r="S262" t="s">
         <v>167</v>
@@ -20893,7 +20906,7 @@
         <v>182</v>
       </c>
       <c r="V262" s="1">
-        <v>46274.74558746528</v>
+        <v>46274.7274781713</v>
       </c>
       <c r="W262">
         <v>6</v>
@@ -20908,24 +20921,24 @@
         <v>167</v>
       </c>
       <c r="AH262" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI262" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="263" spans="1:35">
       <c r="A263">
-        <v>6949</v>
+        <v>6963</v>
       </c>
       <c r="B263" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C263" t="s">
         <v>50</v>
       </c>
       <c r="D263" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E263" t="s">
         <v>54</v>
@@ -20934,19 +20947,19 @@
         <v>57</v>
       </c>
       <c r="G263">
-        <v>6886</v>
+        <v>1867</v>
       </c>
       <c r="H263">
-        <v>1862</v>
+        <v>0</v>
       </c>
       <c r="I263" t="s">
         <v>62</v>
       </c>
       <c r="J263" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="N263" s="1">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="P263">
         <v>8</v>
@@ -20955,10 +20968,10 @@
         <v>2026</v>
       </c>
       <c r="R263">
-        <v>18214907</v>
+        <v>18187219</v>
       </c>
       <c r="S263" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="T263" t="s">
         <v>178</v>
@@ -20967,39 +20980,39 @@
         <v>182</v>
       </c>
       <c r="V263" s="1">
-        <v>46275.79245582176</v>
+        <v>46274.74558746528</v>
       </c>
       <c r="W263">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X263" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="AB263">
         <v>0</v>
       </c>
       <c r="AC263" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="AH263" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="AI263" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="264" spans="1:35">
       <c r="A264">
-        <v>6945</v>
+        <v>6949</v>
       </c>
       <c r="B264" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C264" t="s">
         <v>50</v>
       </c>
       <c r="D264" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E264" t="s">
         <v>54</v>
@@ -21008,22 +21021,19 @@
         <v>57</v>
       </c>
       <c r="G264">
-        <v>10674</v>
+        <v>6886</v>
       </c>
       <c r="H264">
-        <v>0</v>
+        <v>1862</v>
       </c>
       <c r="I264" t="s">
         <v>62</v>
       </c>
       <c r="J264" t="s">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="N264" s="1">
-        <v>46280</v>
-      </c>
-      <c r="O264" t="s">
-        <v>146</v>
+        <v>46275</v>
       </c>
       <c r="P264">
         <v>8</v>
@@ -21032,51 +21042,51 @@
         <v>2026</v>
       </c>
       <c r="R264">
-        <v>18220233</v>
+        <v>18214907</v>
       </c>
       <c r="S264" t="s">
-        <v>164</v>
+        <v>165</v>
+      </c>
+      <c r="T264" t="s">
+        <v>178</v>
       </c>
       <c r="U264" t="s">
         <v>182</v>
       </c>
       <c r="V264" s="1">
-        <v>46280.38311703704</v>
+        <v>46275.79245582176</v>
       </c>
       <c r="W264">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X264" t="s">
-        <v>186</v>
-      </c>
-      <c r="Y264" t="s">
-        <v>283</v>
+        <v>185</v>
       </c>
       <c r="AB264">
         <v>0</v>
       </c>
       <c r="AC264" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AH264" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI264" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="265" spans="1:35">
       <c r="A265">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B265" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C265" t="s">
         <v>50</v>
       </c>
       <c r="D265" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E265" t="s">
         <v>54</v>
@@ -21109,48 +21119,45 @@
         <v>2026</v>
       </c>
       <c r="R265">
-        <v>18214919</v>
+        <v>18220233</v>
       </c>
       <c r="S265" t="s">
-        <v>165</v>
-      </c>
-      <c r="T265" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="U265" t="s">
         <v>182</v>
       </c>
       <c r="V265" s="1">
-        <v>46280.37743127315</v>
+        <v>46280.38311703704</v>
       </c>
       <c r="W265">
         <v>0</v>
       </c>
       <c r="X265" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Y265" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AB265">
         <v>0</v>
       </c>
       <c r="AC265" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AH265" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI265" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="266" spans="1:35">
       <c r="A266">
-        <v>5417</v>
+        <v>6949</v>
       </c>
       <c r="B266" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C266" t="s">
         <v>50</v>
@@ -21162,22 +21169,25 @@
         <v>54</v>
       </c>
       <c r="F266" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G266">
-        <v>6806</v>
+        <v>10674</v>
       </c>
       <c r="H266">
         <v>0</v>
       </c>
       <c r="I266" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J266" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="N266" s="1">
-        <v>46276</v>
+        <v>46280</v>
+      </c>
+      <c r="O266" t="s">
+        <v>146</v>
       </c>
       <c r="P266">
         <v>8</v>
@@ -21186,51 +21196,54 @@
         <v>2026</v>
       </c>
       <c r="R266">
-        <v>17399230</v>
+        <v>18214919</v>
       </c>
       <c r="S266" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="T266" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="U266" t="s">
         <v>182</v>
       </c>
       <c r="V266" s="1">
-        <v>46276.49596842592</v>
+        <v>46280.37743127315</v>
       </c>
       <c r="W266">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X266" t="s">
-        <v>189</v>
+        <v>185</v>
+      </c>
+      <c r="Y266" t="s">
+        <v>285</v>
       </c>
       <c r="AB266">
         <v>0</v>
       </c>
       <c r="AC266" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="AH266" t="s">
         <v>312</v>
       </c>
       <c r="AI266" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="267" spans="1:35">
       <c r="A267">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B267" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C267" t="s">
         <v>50</v>
       </c>
       <c r="D267" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E267" t="s">
         <v>54</v>
@@ -21260,7 +21273,7 @@
         <v>2026</v>
       </c>
       <c r="R267">
-        <v>16962308</v>
+        <v>17399230</v>
       </c>
       <c r="S267" t="s">
         <v>168</v>
@@ -21272,13 +21285,13 @@
         <v>182</v>
       </c>
       <c r="V267" s="1">
-        <v>46276.53874935185</v>
+        <v>46276.49596842592</v>
       </c>
       <c r="W267">
         <v>4</v>
       </c>
       <c r="X267" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="AB267">
         <v>0</v>
@@ -21287,24 +21300,24 @@
         <v>168</v>
       </c>
       <c r="AH267" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI267" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="268" spans="1:35">
       <c r="A268">
-        <v>6486</v>
+        <v>6404</v>
       </c>
       <c r="B268" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C268" t="s">
         <v>50</v>
       </c>
       <c r="D268" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E268" t="s">
         <v>54</v>
@@ -21334,7 +21347,7 @@
         <v>2026</v>
       </c>
       <c r="R268">
-        <v>16976187</v>
+        <v>16962308</v>
       </c>
       <c r="S268" t="s">
         <v>168</v>
@@ -21346,13 +21359,13 @@
         <v>182</v>
       </c>
       <c r="V268" s="1">
-        <v>46276.49597027778</v>
+        <v>46276.53874935185</v>
       </c>
       <c r="W268">
         <v>4</v>
       </c>
       <c r="X268" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="AB268">
         <v>0</v>
@@ -21361,24 +21374,24 @@
         <v>168</v>
       </c>
       <c r="AH268" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI268" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="269" spans="1:35">
       <c r="A269">
-        <v>6703</v>
+        <v>6486</v>
       </c>
       <c r="B269" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C269" t="s">
         <v>50</v>
       </c>
       <c r="D269" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E269" t="s">
         <v>54</v>
@@ -21408,7 +21421,7 @@
         <v>2026</v>
       </c>
       <c r="R269">
-        <v>17948858</v>
+        <v>16976187</v>
       </c>
       <c r="S269" t="s">
         <v>168</v>
@@ -21420,13 +21433,13 @@
         <v>182</v>
       </c>
       <c r="V269" s="1">
-        <v>46276.62604146991</v>
+        <v>46276.49597027778</v>
       </c>
       <c r="W269">
         <v>4</v>
       </c>
       <c r="X269" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="AB269">
         <v>0</v>
@@ -21435,24 +21448,24 @@
         <v>168</v>
       </c>
       <c r="AH269" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI269" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="270" spans="1:35">
       <c r="A270">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B270" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C270" t="s">
         <v>50</v>
       </c>
       <c r="D270" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E270" t="s">
         <v>54</v>
@@ -21482,7 +21495,7 @@
         <v>2026</v>
       </c>
       <c r="R270">
-        <v>18085297</v>
+        <v>17948858</v>
       </c>
       <c r="S270" t="s">
         <v>168</v>
@@ -21494,13 +21507,13 @@
         <v>182</v>
       </c>
       <c r="V270" s="1">
-        <v>46276.68231165509</v>
+        <v>46276.62604146991</v>
       </c>
       <c r="W270">
         <v>4</v>
       </c>
       <c r="X270" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="AB270">
         <v>0</v>
@@ -21509,24 +21522,24 @@
         <v>168</v>
       </c>
       <c r="AH270" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI270" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="271" spans="1:35">
       <c r="A271">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B271" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C271" t="s">
         <v>50</v>
       </c>
       <c r="D271" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E271" t="s">
         <v>54</v>
@@ -21549,9 +21562,6 @@
       <c r="N271" s="1">
         <v>46276</v>
       </c>
-      <c r="O271" t="s">
-        <v>145</v>
-      </c>
       <c r="P271">
         <v>8</v>
       </c>
@@ -21559,7 +21569,7 @@
         <v>2026</v>
       </c>
       <c r="R271">
-        <v>17949029</v>
+        <v>18085297</v>
       </c>
       <c r="S271" t="s">
         <v>168</v>
@@ -21571,7 +21581,7 @@
         <v>182</v>
       </c>
       <c r="V271" s="1">
-        <v>46276.7163278588</v>
+        <v>46276.68231165509</v>
       </c>
       <c r="W271">
         <v>4</v>
@@ -21579,9 +21589,6 @@
       <c r="X271" t="s">
         <v>188</v>
       </c>
-      <c r="Y271" t="s">
-        <v>284</v>
-      </c>
       <c r="AB271">
         <v>0</v>
       </c>
@@ -21589,18 +21596,18 @@
         <v>168</v>
       </c>
       <c r="AH271" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI271" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="272" spans="1:35">
       <c r="A272">
-        <v>6779</v>
+        <v>6705</v>
       </c>
       <c r="B272" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C272" t="s">
         <v>50</v>
@@ -21629,6 +21636,9 @@
       <c r="N272" s="1">
         <v>46276</v>
       </c>
+      <c r="O272" t="s">
+        <v>145</v>
+      </c>
       <c r="P272">
         <v>8</v>
       </c>
@@ -21636,7 +21646,7 @@
         <v>2026</v>
       </c>
       <c r="R272">
-        <v>18085066</v>
+        <v>17949029</v>
       </c>
       <c r="S272" t="s">
         <v>168</v>
@@ -21648,7 +21658,7 @@
         <v>182</v>
       </c>
       <c r="V272" s="1">
-        <v>46276.6823121412</v>
+        <v>46276.7163278588</v>
       </c>
       <c r="W272">
         <v>4</v>
@@ -21656,6 +21666,9 @@
       <c r="X272" t="s">
         <v>188</v>
       </c>
+      <c r="Y272" t="s">
+        <v>286</v>
+      </c>
       <c r="AB272">
         <v>0</v>
       </c>
@@ -21663,24 +21676,24 @@
         <v>168</v>
       </c>
       <c r="AH272" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI272" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="273" spans="1:35">
       <c r="A273">
-        <v>6404</v>
+        <v>6779</v>
       </c>
       <c r="B273" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C273" t="s">
         <v>50</v>
       </c>
       <c r="D273" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E273" t="s">
         <v>54</v>
@@ -21689,7 +21702,7 @@
         <v>56</v>
       </c>
       <c r="G273">
-        <v>1792</v>
+        <v>6806</v>
       </c>
       <c r="H273">
         <v>0</v>
@@ -21698,10 +21711,10 @@
         <v>63</v>
       </c>
       <c r="J273" t="s">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="N273" s="1">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="P273">
         <v>8</v>
@@ -21710,7 +21723,7 @@
         <v>2026</v>
       </c>
       <c r="R273">
-        <v>16962151</v>
+        <v>18085066</v>
       </c>
       <c r="S273" t="s">
         <v>168</v>
@@ -21719,16 +21732,16 @@
         <v>179</v>
       </c>
       <c r="U273" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="V273" s="1">
-        <v>46274.70622837963</v>
+        <v>46276.6823121412</v>
       </c>
       <c r="W273">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="X273" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="AB273">
         <v>0</v>
@@ -21737,18 +21750,18 @@
         <v>168</v>
       </c>
       <c r="AH273" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="AI273" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="274" spans="1:35">
       <c r="A274">
-        <v>6703</v>
+        <v>6404</v>
       </c>
       <c r="B274" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C274" t="s">
         <v>50</v>
@@ -21784,7 +21797,7 @@
         <v>2026</v>
       </c>
       <c r="R274">
-        <v>17948756</v>
+        <v>16962151</v>
       </c>
       <c r="S274" t="s">
         <v>168</v>
@@ -21793,16 +21806,16 @@
         <v>179</v>
       </c>
       <c r="U274" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="V274" s="1">
-        <v>46275.71996309028</v>
+        <v>46274.70622837963</v>
       </c>
       <c r="W274">
         <v>5</v>
       </c>
       <c r="X274" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AB274">
         <v>0</v>
@@ -21811,24 +21824,24 @@
         <v>168</v>
       </c>
       <c r="AH274" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI274" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="275" spans="1:35">
       <c r="A275">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B275" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C275" t="s">
         <v>50</v>
       </c>
       <c r="D275" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E275" t="s">
         <v>54</v>
@@ -21858,7 +21871,7 @@
         <v>2026</v>
       </c>
       <c r="R275">
-        <v>18085143</v>
+        <v>17948756</v>
       </c>
       <c r="S275" t="s">
         <v>168</v>
@@ -21870,13 +21883,13 @@
         <v>182</v>
       </c>
       <c r="V275" s="1">
-        <v>46275.54278886574</v>
+        <v>46275.71996309028</v>
       </c>
       <c r="W275">
         <v>5</v>
       </c>
       <c r="X275" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="AB275">
         <v>0</v>
@@ -21885,24 +21898,24 @@
         <v>168</v>
       </c>
       <c r="AH275" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI275" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="276" spans="1:35">
       <c r="A276">
-        <v>6404</v>
+        <v>6704</v>
       </c>
       <c r="B276" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C276" t="s">
         <v>50</v>
       </c>
       <c r="D276" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E276" t="s">
         <v>54</v>
@@ -21911,7 +21924,7 @@
         <v>56</v>
       </c>
       <c r="G276">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="H276">
         <v>0</v>
@@ -21920,7 +21933,7 @@
         <v>63</v>
       </c>
       <c r="J276" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N276" s="1">
         <v>46275</v>
@@ -21932,7 +21945,7 @@
         <v>2026</v>
       </c>
       <c r="R276">
-        <v>16962161</v>
+        <v>18085143</v>
       </c>
       <c r="S276" t="s">
         <v>168</v>
@@ -21944,13 +21957,13 @@
         <v>182</v>
       </c>
       <c r="V276" s="1">
-        <v>46275.7000328588</v>
+        <v>46275.54278886574</v>
       </c>
       <c r="W276">
         <v>5</v>
       </c>
       <c r="X276" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="AB276">
         <v>0</v>
@@ -21959,24 +21972,24 @@
         <v>168</v>
       </c>
       <c r="AH276" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI276" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="277" spans="1:35">
       <c r="A277">
-        <v>6486</v>
+        <v>6404</v>
       </c>
       <c r="B277" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C277" t="s">
         <v>50</v>
       </c>
       <c r="D277" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E277" t="s">
         <v>54</v>
@@ -22006,7 +22019,7 @@
         <v>2026</v>
       </c>
       <c r="R277">
-        <v>16975952</v>
+        <v>16962161</v>
       </c>
       <c r="S277" t="s">
         <v>168</v>
@@ -22018,13 +22031,13 @@
         <v>182</v>
       </c>
       <c r="V277" s="1">
-        <v>46275.72031699074</v>
+        <v>46275.7000328588</v>
       </c>
       <c r="W277">
         <v>5</v>
       </c>
       <c r="X277" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="AB277">
         <v>0</v>
@@ -22033,24 +22046,24 @@
         <v>168</v>
       </c>
       <c r="AH277" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI277" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="278" spans="1:35">
       <c r="A278">
-        <v>6703</v>
+        <v>6486</v>
       </c>
       <c r="B278" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C278" t="s">
         <v>50</v>
       </c>
       <c r="D278" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E278" t="s">
         <v>54</v>
@@ -22080,7 +22093,7 @@
         <v>2026</v>
       </c>
       <c r="R278">
-        <v>17948766</v>
+        <v>16975952</v>
       </c>
       <c r="S278" t="s">
         <v>168</v>
@@ -22092,13 +22105,13 @@
         <v>182</v>
       </c>
       <c r="V278" s="1">
-        <v>46275.54095912037</v>
+        <v>46275.72031699074</v>
       </c>
       <c r="W278">
         <v>5</v>
       </c>
       <c r="X278" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="AB278">
         <v>0</v>
@@ -22107,24 +22120,24 @@
         <v>168</v>
       </c>
       <c r="AH278" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI278" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="279" spans="1:35">
       <c r="A279">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B279" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C279" t="s">
         <v>50</v>
       </c>
       <c r="D279" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E279" t="s">
         <v>54</v>
@@ -22154,7 +22167,7 @@
         <v>2026</v>
       </c>
       <c r="R279">
-        <v>18085154</v>
+        <v>17948766</v>
       </c>
       <c r="S279" t="s">
         <v>168</v>
@@ -22166,13 +22179,13 @@
         <v>182</v>
       </c>
       <c r="V279" s="1">
-        <v>46275.72225363426</v>
+        <v>46275.54095912037</v>
       </c>
       <c r="W279">
         <v>5</v>
       </c>
       <c r="X279" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="AB279">
         <v>0</v>
@@ -22181,24 +22194,24 @@
         <v>168</v>
       </c>
       <c r="AH279" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI279" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="280" spans="1:35">
       <c r="A280">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B280" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C280" t="s">
         <v>50</v>
       </c>
       <c r="D280" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E280" t="s">
         <v>54</v>
@@ -22228,7 +22241,7 @@
         <v>2026</v>
       </c>
       <c r="R280">
-        <v>17948928</v>
+        <v>18085154</v>
       </c>
       <c r="S280" t="s">
         <v>168</v>
@@ -22240,7 +22253,7 @@
         <v>182</v>
       </c>
       <c r="V280" s="1">
-        <v>46275.7222629051</v>
+        <v>46275.72225363426</v>
       </c>
       <c r="W280">
         <v>5</v>
@@ -22255,18 +22268,18 @@
         <v>168</v>
       </c>
       <c r="AH280" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI280" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="281" spans="1:35">
       <c r="A281">
-        <v>6779</v>
+        <v>6705</v>
       </c>
       <c r="B281" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C281" t="s">
         <v>50</v>
@@ -22302,7 +22315,7 @@
         <v>2026</v>
       </c>
       <c r="R281">
-        <v>18084955</v>
+        <v>17948928</v>
       </c>
       <c r="S281" t="s">
         <v>168</v>
@@ -22314,7 +22327,7 @@
         <v>182</v>
       </c>
       <c r="V281" s="1">
-        <v>46275.7222709838</v>
+        <v>46275.7222629051</v>
       </c>
       <c r="W281">
         <v>5</v>
@@ -22329,24 +22342,24 @@
         <v>168</v>
       </c>
       <c r="AH281" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI281" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="282" spans="1:35">
       <c r="A282">
-        <v>5417</v>
+        <v>6779</v>
       </c>
       <c r="B282" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C282" t="s">
         <v>50</v>
       </c>
       <c r="D282" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E282" t="s">
         <v>54</v>
@@ -22355,7 +22368,7 @@
         <v>56</v>
       </c>
       <c r="G282">
-        <v>1796</v>
+        <v>1793</v>
       </c>
       <c r="H282">
         <v>0</v>
@@ -22364,13 +22377,10 @@
         <v>63</v>
       </c>
       <c r="J282" t="s">
-        <v>132</v>
+        <v>101</v>
       </c>
       <c r="N282" s="1">
-        <v>46273</v>
-      </c>
-      <c r="O282" t="s">
-        <v>142</v>
+        <v>46275</v>
       </c>
       <c r="P282">
         <v>8</v>
@@ -22379,7 +22389,7 @@
         <v>2026</v>
       </c>
       <c r="R282">
-        <v>17398955</v>
+        <v>18084955</v>
       </c>
       <c r="S282" t="s">
         <v>168</v>
@@ -22388,19 +22398,16 @@
         <v>179</v>
       </c>
       <c r="U282" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="V282" s="1">
-        <v>46274.74837762731</v>
+        <v>46275.7222709838</v>
       </c>
       <c r="W282">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X282" t="s">
-        <v>189</v>
-      </c>
-      <c r="Y282" t="s">
-        <v>285</v>
+        <v>188</v>
       </c>
       <c r="AB282">
         <v>0</v>
@@ -22409,24 +22416,24 @@
         <v>168</v>
       </c>
       <c r="AH282" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="AI282" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="283" spans="1:35">
       <c r="A283">
-        <v>6703</v>
+        <v>5417</v>
       </c>
       <c r="B283" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C283" t="s">
         <v>50</v>
       </c>
       <c r="D283" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E283" t="s">
         <v>54</v>
@@ -22459,7 +22466,7 @@
         <v>2026</v>
       </c>
       <c r="R283">
-        <v>18073098</v>
+        <v>17398955</v>
       </c>
       <c r="S283" t="s">
         <v>168</v>
@@ -22471,16 +22478,16 @@
         <v>180</v>
       </c>
       <c r="V283" s="1">
-        <v>46274.74838096065</v>
+        <v>46274.74837762731</v>
       </c>
       <c r="W283">
         <v>7</v>
       </c>
       <c r="X283" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="Y283" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AB283">
         <v>0</v>
@@ -22489,24 +22496,24 @@
         <v>168</v>
       </c>
       <c r="AH283" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI283" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="284" spans="1:35">
       <c r="A284">
-        <v>5417</v>
+        <v>6703</v>
       </c>
       <c r="B284" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C284" t="s">
         <v>50</v>
       </c>
       <c r="D284" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E284" t="s">
         <v>54</v>
@@ -22515,7 +22522,7 @@
         <v>56</v>
       </c>
       <c r="G284">
-        <v>11303</v>
+        <v>1796</v>
       </c>
       <c r="H284">
         <v>0</v>
@@ -22524,10 +22531,13 @@
         <v>63</v>
       </c>
       <c r="J284" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="N284" s="1">
-        <v>46279</v>
+        <v>46273</v>
+      </c>
+      <c r="O284" t="s">
+        <v>142</v>
       </c>
       <c r="P284">
         <v>8</v>
@@ -22536,7 +22546,7 @@
         <v>2026</v>
       </c>
       <c r="R284">
-        <v>17399454</v>
+        <v>18073098</v>
       </c>
       <c r="S284" t="s">
         <v>168</v>
@@ -22545,19 +22555,19 @@
         <v>179</v>
       </c>
       <c r="U284" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="V284" s="1">
-        <v>46274.42878043981</v>
+        <v>46274.74838096065</v>
       </c>
       <c r="W284">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="X284" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Y284" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AB284">
         <v>0</v>
@@ -22566,18 +22576,18 @@
         <v>168</v>
       </c>
       <c r="AH284" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI284" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="285" spans="1:35">
       <c r="A285">
-        <v>6486</v>
+        <v>5417</v>
       </c>
       <c r="B285" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C285" t="s">
         <v>50</v>
@@ -22613,7 +22623,7 @@
         <v>2026</v>
       </c>
       <c r="R285">
-        <v>16976351</v>
+        <v>17399454</v>
       </c>
       <c r="S285" t="s">
         <v>168</v>
@@ -22625,16 +22635,16 @@
         <v>181</v>
       </c>
       <c r="V285" s="1">
-        <v>46275.40196778935</v>
+        <v>46274.42878043981</v>
       </c>
       <c r="W285">
         <v>1</v>
       </c>
       <c r="X285" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Y285" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AB285">
         <v>0</v>
@@ -22643,24 +22653,24 @@
         <v>168</v>
       </c>
       <c r="AH285" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI285" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="286" spans="1:35">
       <c r="A286">
-        <v>6703</v>
+        <v>6486</v>
       </c>
       <c r="B286" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C286" t="s">
         <v>50</v>
       </c>
       <c r="D286" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E286" t="s">
         <v>54</v>
@@ -22669,22 +22679,19 @@
         <v>56</v>
       </c>
       <c r="G286">
-        <v>950</v>
+        <v>11303</v>
       </c>
       <c r="H286">
         <v>0</v>
       </c>
       <c r="I286" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J286" t="s">
-        <v>133</v>
+        <v>111</v>
       </c>
       <c r="N286" s="1">
-        <v>46275</v>
-      </c>
-      <c r="O286" t="s">
-        <v>144</v>
+        <v>46279</v>
       </c>
       <c r="P286">
         <v>8</v>
@@ -22693,51 +22700,54 @@
         <v>2026</v>
       </c>
       <c r="R286">
-        <v>17941146</v>
+        <v>16976351</v>
       </c>
       <c r="S286" t="s">
-        <v>169</v>
+        <v>168</v>
+      </c>
+      <c r="T286" t="s">
+        <v>179</v>
       </c>
       <c r="U286" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="V286" s="1">
-        <v>46276.52399603009</v>
+        <v>46275.40196778935</v>
       </c>
       <c r="W286">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="X286" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="Y286" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AB286">
         <v>0</v>
       </c>
       <c r="AC286" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AH286" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AI286" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="287" spans="1:35">
       <c r="A287">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B287" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C287" t="s">
         <v>50</v>
       </c>
       <c r="D287" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E287" t="s">
         <v>54</v>
@@ -22770,7 +22780,7 @@
         <v>2026</v>
       </c>
       <c r="R287">
-        <v>17952340</v>
+        <v>17941146</v>
       </c>
       <c r="S287" t="s">
         <v>169</v>
@@ -22779,16 +22789,16 @@
         <v>180</v>
       </c>
       <c r="V287" s="1">
-        <v>46276.5240703125</v>
+        <v>46276.52399603009</v>
       </c>
       <c r="W287">
         <v>5</v>
       </c>
       <c r="X287" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="Y287" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AB287">
         <v>0</v>
@@ -22797,18 +22807,18 @@
         <v>169</v>
       </c>
       <c r="AH287" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI287" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="288" spans="1:35">
       <c r="A288">
-        <v>6949</v>
+        <v>6704</v>
       </c>
       <c r="B288" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C288" t="s">
         <v>50</v>
@@ -22820,7 +22830,7 @@
         <v>54</v>
       </c>
       <c r="F288" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G288">
         <v>950</v>
@@ -22837,6 +22847,9 @@
       <c r="N288" s="1">
         <v>46275</v>
       </c>
+      <c r="O288" t="s">
+        <v>144</v>
+      </c>
       <c r="P288">
         <v>8</v>
       </c>
@@ -22844,25 +22857,25 @@
         <v>2026</v>
       </c>
       <c r="R288">
-        <v>18178132</v>
+        <v>17952340</v>
       </c>
       <c r="S288" t="s">
         <v>169</v>
       </c>
       <c r="U288" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="V288" s="1">
-        <v>46275.4100730787</v>
+        <v>46276.5240703125</v>
       </c>
       <c r="W288">
         <v>5</v>
       </c>
       <c r="X288" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Y288" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AB288">
         <v>0</v>
@@ -22871,24 +22884,24 @@
         <v>169</v>
       </c>
       <c r="AH288" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI288" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="289" spans="1:35">
       <c r="A289">
-        <v>6962</v>
+        <v>6949</v>
       </c>
       <c r="B289" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C289" t="s">
         <v>50</v>
       </c>
       <c r="D289" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E289" t="s">
         <v>54</v>
@@ -22918,7 +22931,7 @@
         <v>2026</v>
       </c>
       <c r="R289">
-        <v>18188717</v>
+        <v>18178132</v>
       </c>
       <c r="S289" t="s">
         <v>169</v>
@@ -22927,16 +22940,16 @@
         <v>182</v>
       </c>
       <c r="V289" s="1">
-        <v>46275.40964188657</v>
+        <v>46275.4100730787</v>
       </c>
       <c r="W289">
         <v>5</v>
       </c>
       <c r="X289" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="Y289" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AB289">
         <v>0</v>
@@ -22945,18 +22958,18 @@
         <v>169</v>
       </c>
       <c r="AH289" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI289" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="290" spans="1:35">
       <c r="A290">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B290" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C290" t="s">
         <v>50</v>
@@ -22992,7 +23005,7 @@
         <v>2026</v>
       </c>
       <c r="R290">
-        <v>18188623</v>
+        <v>18188717</v>
       </c>
       <c r="S290" t="s">
         <v>169</v>
@@ -23001,7 +23014,7 @@
         <v>182</v>
       </c>
       <c r="V290" s="1">
-        <v>46275.40964245371</v>
+        <v>46275.40964188657</v>
       </c>
       <c r="W290">
         <v>5</v>
@@ -23010,7 +23023,7 @@
         <v>187</v>
       </c>
       <c r="Y290" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AB290">
         <v>0</v>
@@ -23019,33 +23032,33 @@
         <v>169</v>
       </c>
       <c r="AH290" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI290" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="291" spans="1:35">
       <c r="A291">
-        <v>6548</v>
+        <v>6963</v>
       </c>
       <c r="B291" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C291" t="s">
         <v>50</v>
       </c>
       <c r="D291" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E291" t="s">
         <v>54</v>
       </c>
       <c r="F291" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G291">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H291">
         <v>0</v>
@@ -23054,7 +23067,7 @@
         <v>64</v>
       </c>
       <c r="J291" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="N291" s="1">
         <v>46275</v>
@@ -23066,7 +23079,7 @@
         <v>2026</v>
       </c>
       <c r="R291">
-        <v>17222405</v>
+        <v>18188623</v>
       </c>
       <c r="S291" t="s">
         <v>169</v>
@@ -23075,16 +23088,16 @@
         <v>182</v>
       </c>
       <c r="V291" s="1">
-        <v>46275.45011145833</v>
+        <v>46275.40964245371</v>
       </c>
       <c r="W291">
         <v>5</v>
       </c>
       <c r="X291" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="Y291" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AB291">
         <v>0</v>
@@ -23093,27 +23106,27 @@
         <v>169</v>
       </c>
       <c r="AH291" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI291" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="292" spans="1:35">
       <c r="A292">
-        <v>6628</v>
+        <v>6548</v>
       </c>
       <c r="B292" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C292" t="s">
         <v>50</v>
       </c>
       <c r="D292" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E292" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F292" t="s">
         <v>56</v>
@@ -23140,7 +23153,7 @@
         <v>2026</v>
       </c>
       <c r="R292">
-        <v>16959950</v>
+        <v>17222405</v>
       </c>
       <c r="S292" t="s">
         <v>169</v>
@@ -23149,13 +23162,16 @@
         <v>182</v>
       </c>
       <c r="V292" s="1">
-        <v>46275.44901016204</v>
+        <v>46275.45011145833</v>
       </c>
       <c r="W292">
         <v>5</v>
       </c>
       <c r="X292" t="s">
-        <v>184</v>
+        <v>183</v>
+      </c>
+      <c r="Y292" t="s">
+        <v>295</v>
       </c>
       <c r="AB292">
         <v>0</v>
@@ -23164,27 +23180,27 @@
         <v>169</v>
       </c>
       <c r="AH292" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI292" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="293" spans="1:35">
       <c r="A293">
-        <v>6703</v>
+        <v>6628</v>
       </c>
       <c r="B293" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C293" t="s">
         <v>50</v>
       </c>
       <c r="D293" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E293" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F293" t="s">
         <v>56</v>
@@ -23204,9 +23220,6 @@
       <c r="N293" s="1">
         <v>46275</v>
       </c>
-      <c r="O293" t="s">
-        <v>145</v>
-      </c>
       <c r="P293">
         <v>8</v>
       </c>
@@ -23214,25 +23227,22 @@
         <v>2026</v>
       </c>
       <c r="R293">
-        <v>17941156</v>
+        <v>16959950</v>
       </c>
       <c r="S293" t="s">
         <v>169</v>
       </c>
       <c r="U293" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="V293" s="1">
-        <v>46276.71732053241</v>
+        <v>46275.44901016204</v>
       </c>
       <c r="W293">
         <v>5</v>
       </c>
       <c r="X293" t="s">
-        <v>192</v>
-      </c>
-      <c r="Y293" t="s">
-        <v>294</v>
+        <v>184</v>
       </c>
       <c r="AB293">
         <v>0</v>
@@ -23241,24 +23251,24 @@
         <v>169</v>
       </c>
       <c r="AH293" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI293" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="294" spans="1:35">
       <c r="A294">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B294" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C294" t="s">
         <v>50</v>
       </c>
       <c r="D294" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E294" t="s">
         <v>54</v>
@@ -23291,7 +23301,7 @@
         <v>2026</v>
       </c>
       <c r="R294">
-        <v>17952351</v>
+        <v>17941156</v>
       </c>
       <c r="S294" t="s">
         <v>169</v>
@@ -23300,16 +23310,16 @@
         <v>180</v>
       </c>
       <c r="V294" s="1">
-        <v>46276.71697232639</v>
+        <v>46276.71732053241</v>
       </c>
       <c r="W294">
         <v>5</v>
       </c>
       <c r="X294" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="Y294" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AB294">
         <v>0</v>
@@ -23318,24 +23328,24 @@
         <v>169</v>
       </c>
       <c r="AH294" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI294" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="295" spans="1:35">
       <c r="A295">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B295" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C295" t="s">
         <v>50</v>
       </c>
       <c r="D295" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E295" t="s">
         <v>54</v>
@@ -23368,7 +23378,7 @@
         <v>2026</v>
       </c>
       <c r="R295">
-        <v>17952535</v>
+        <v>17952351</v>
       </c>
       <c r="S295" t="s">
         <v>169</v>
@@ -23377,7 +23387,7 @@
         <v>180</v>
       </c>
       <c r="V295" s="1">
-        <v>46276.7175884838</v>
+        <v>46276.71697232639</v>
       </c>
       <c r="W295">
         <v>5</v>
@@ -23386,7 +23396,7 @@
         <v>188</v>
       </c>
       <c r="Y295" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AB295">
         <v>0</v>
@@ -23395,18 +23405,18 @@
         <v>169</v>
       </c>
       <c r="AH295" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI295" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="296" spans="1:35">
       <c r="A296">
-        <v>6779</v>
+        <v>6705</v>
       </c>
       <c r="B296" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C296" t="s">
         <v>50</v>
@@ -23445,7 +23455,7 @@
         <v>2026</v>
       </c>
       <c r="R296">
-        <v>18056705</v>
+        <v>17952535</v>
       </c>
       <c r="S296" t="s">
         <v>169</v>
@@ -23454,7 +23464,7 @@
         <v>180</v>
       </c>
       <c r="V296" s="1">
-        <v>46276.7175895949</v>
+        <v>46276.7175884838</v>
       </c>
       <c r="W296">
         <v>5</v>
@@ -23463,7 +23473,7 @@
         <v>188</v>
       </c>
       <c r="Y296" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AB296">
         <v>0</v>
@@ -23472,18 +23482,18 @@
         <v>169</v>
       </c>
       <c r="AH296" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI296" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="297" spans="1:35">
       <c r="A297">
-        <v>6945</v>
+        <v>6779</v>
       </c>
       <c r="B297" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C297" t="s">
         <v>50</v>
@@ -23495,7 +23505,7 @@
         <v>54</v>
       </c>
       <c r="F297" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G297">
         <v>951</v>
@@ -23522,7 +23532,7 @@
         <v>2026</v>
       </c>
       <c r="R297">
-        <v>18164501</v>
+        <v>18056705</v>
       </c>
       <c r="S297" t="s">
         <v>169</v>
@@ -23531,16 +23541,16 @@
         <v>180</v>
       </c>
       <c r="V297" s="1">
-        <v>46276.71759461806</v>
+        <v>46276.7175895949</v>
       </c>
       <c r="W297">
         <v>5</v>
       </c>
       <c r="X297" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Y297" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AB297">
         <v>0</v>
@@ -23549,24 +23559,24 @@
         <v>169</v>
       </c>
       <c r="AH297" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI297" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="298" spans="1:35">
       <c r="A298">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B298" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C298" t="s">
         <v>50</v>
       </c>
       <c r="D298" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E298" t="s">
         <v>54</v>
@@ -23589,6 +23599,9 @@
       <c r="N298" s="1">
         <v>46275</v>
       </c>
+      <c r="O298" t="s">
+        <v>145</v>
+      </c>
       <c r="P298">
         <v>8</v>
       </c>
@@ -23596,25 +23609,25 @@
         <v>2026</v>
       </c>
       <c r="R298">
-        <v>18178138</v>
+        <v>18164501</v>
       </c>
       <c r="S298" t="s">
         <v>169</v>
       </c>
       <c r="U298" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="V298" s="1">
-        <v>46275.44975668981</v>
+        <v>46276.71759461806</v>
       </c>
       <c r="W298">
         <v>5</v>
       </c>
       <c r="X298" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Y298" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AB298">
         <v>0</v>
@@ -23623,24 +23636,24 @@
         <v>169</v>
       </c>
       <c r="AH298" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI298" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="299" spans="1:35">
       <c r="A299">
-        <v>6962</v>
+        <v>6949</v>
       </c>
       <c r="B299" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C299" t="s">
         <v>50</v>
       </c>
       <c r="D299" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E299" t="s">
         <v>54</v>
@@ -23670,7 +23683,7 @@
         <v>2026</v>
       </c>
       <c r="R299">
-        <v>18188724</v>
+        <v>18178138</v>
       </c>
       <c r="S299" t="s">
         <v>169</v>
@@ -23679,16 +23692,16 @@
         <v>182</v>
       </c>
       <c r="V299" s="1">
-        <v>46275.44933692129</v>
+        <v>46275.44975668981</v>
       </c>
       <c r="W299">
         <v>5</v>
       </c>
       <c r="X299" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="Y299" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AB299">
         <v>0</v>
@@ -23697,18 +23710,18 @@
         <v>169</v>
       </c>
       <c r="AH299" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI299" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="300" spans="1:35">
       <c r="A300">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B300" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C300" t="s">
         <v>50</v>
@@ -23744,7 +23757,7 @@
         <v>2026</v>
       </c>
       <c r="R300">
-        <v>18188630</v>
+        <v>18188724</v>
       </c>
       <c r="S300" t="s">
         <v>169</v>
@@ -23753,7 +23766,7 @@
         <v>182</v>
       </c>
       <c r="V300" s="1">
-        <v>46275.44933814815</v>
+        <v>46275.44933692129</v>
       </c>
       <c r="W300">
         <v>5</v>
@@ -23762,7 +23775,7 @@
         <v>187</v>
       </c>
       <c r="Y300" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AB300">
         <v>0</v>
@@ -23771,18 +23784,18 @@
         <v>169</v>
       </c>
       <c r="AH300" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AI300" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="301" spans="1:35">
       <c r="A301">
-        <v>6703</v>
+        <v>6963</v>
       </c>
       <c r="B301" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C301" t="s">
         <v>50</v>
@@ -23794,10 +23807,10 @@
         <v>54</v>
       </c>
       <c r="F301" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G301">
-        <v>5989</v>
+        <v>951</v>
       </c>
       <c r="H301">
         <v>0</v>
@@ -23806,34 +23819,37 @@
         <v>64</v>
       </c>
       <c r="J301" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="N301" s="1">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="P301">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q301">
         <v>2026</v>
       </c>
       <c r="R301">
-        <v>17941177</v>
+        <v>18188630</v>
       </c>
       <c r="S301" t="s">
         <v>169</v>
       </c>
       <c r="U301" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="V301" s="1">
-        <v>46274.41771849537</v>
+        <v>46275.44933814815</v>
       </c>
       <c r="W301">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X301" t="s">
-        <v>192</v>
+        <v>187</v>
+      </c>
+      <c r="Y301" t="s">
+        <v>303</v>
       </c>
       <c r="AB301">
         <v>0</v>
@@ -23842,24 +23858,24 @@
         <v>169</v>
       </c>
       <c r="AH301" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AI301" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="302" spans="1:35">
       <c r="A302">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B302" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C302" t="s">
         <v>50</v>
       </c>
       <c r="D302" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E302" t="s">
         <v>54</v>
@@ -23889,7 +23905,7 @@
         <v>2026</v>
       </c>
       <c r="R302">
-        <v>17952385</v>
+        <v>17941177</v>
       </c>
       <c r="S302" t="s">
         <v>169</v>
@@ -23898,13 +23914,13 @@
         <v>180</v>
       </c>
       <c r="V302" s="1">
-        <v>46274.41775447917</v>
+        <v>46274.41771849537</v>
       </c>
       <c r="W302">
         <v>7</v>
       </c>
       <c r="X302" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="AB302">
         <v>0</v>
@@ -23913,24 +23929,24 @@
         <v>169</v>
       </c>
       <c r="AH302" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI302" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="303" spans="1:35">
       <c r="A303">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B303" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C303" t="s">
         <v>50</v>
       </c>
       <c r="D303" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E303" t="s">
         <v>54</v>
@@ -23960,7 +23976,7 @@
         <v>2026</v>
       </c>
       <c r="R303">
-        <v>17952569</v>
+        <v>17952385</v>
       </c>
       <c r="S303" t="s">
         <v>169</v>
@@ -23969,7 +23985,7 @@
         <v>180</v>
       </c>
       <c r="V303" s="1">
-        <v>46274.41777533565</v>
+        <v>46274.41775447917</v>
       </c>
       <c r="W303">
         <v>7</v>
@@ -23984,18 +24000,18 @@
         <v>169</v>
       </c>
       <c r="AH303" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI303" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="304" spans="1:35">
       <c r="A304">
-        <v>6945</v>
+        <v>6705</v>
       </c>
       <c r="B304" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C304" t="s">
         <v>50</v>
@@ -24007,7 +24023,7 @@
         <v>54</v>
       </c>
       <c r="F304" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G304">
         <v>5989</v>
@@ -24031,7 +24047,7 @@
         <v>2026</v>
       </c>
       <c r="R304">
-        <v>18164516</v>
+        <v>17952569</v>
       </c>
       <c r="S304" t="s">
         <v>169</v>
@@ -24040,13 +24056,13 @@
         <v>180</v>
       </c>
       <c r="V304" s="1">
-        <v>46274.41799166667</v>
+        <v>46274.41777533565</v>
       </c>
       <c r="W304">
         <v>7</v>
       </c>
       <c r="X304" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AB304">
         <v>0</v>
@@ -24055,24 +24071,24 @@
         <v>169</v>
       </c>
       <c r="AH304" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI304" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="305" spans="1:35">
       <c r="A305">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B305" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C305" t="s">
         <v>50</v>
       </c>
       <c r="D305" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E305" t="s">
         <v>54</v>
@@ -24102,7 +24118,7 @@
         <v>2026</v>
       </c>
       <c r="R305">
-        <v>18178157</v>
+        <v>18164516</v>
       </c>
       <c r="S305" t="s">
         <v>169</v>
@@ -24111,13 +24127,13 @@
         <v>180</v>
       </c>
       <c r="V305" s="1">
-        <v>46274.41800114583</v>
+        <v>46274.41799166667</v>
       </c>
       <c r="W305">
         <v>7</v>
       </c>
       <c r="X305" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AB305">
         <v>0</v>
@@ -24126,45 +24142,45 @@
         <v>169</v>
       </c>
       <c r="AH305" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI305" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="306" spans="1:35">
       <c r="A306">
-        <v>6703</v>
+        <v>6949</v>
       </c>
       <c r="B306" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C306" t="s">
         <v>50</v>
       </c>
       <c r="D306" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E306" t="s">
         <v>54</v>
       </c>
       <c r="F306" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G306">
-        <v>6215</v>
+        <v>5989</v>
       </c>
       <c r="H306">
         <v>0</v>
       </c>
       <c r="I306" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J306" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="N306" s="1">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="P306">
         <v>9</v>
@@ -24173,48 +24189,48 @@
         <v>2026</v>
       </c>
       <c r="R306">
-        <v>17941187</v>
+        <v>18178157</v>
       </c>
       <c r="S306" t="s">
-        <v>54</v>
+        <v>169</v>
       </c>
       <c r="U306" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="V306" s="1">
-        <v>46274.41772148148</v>
+        <v>46274.41800114583</v>
       </c>
       <c r="W306">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X306" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="AB306">
         <v>0</v>
       </c>
       <c r="AC306" t="s">
-        <v>54</v>
+        <v>169</v>
       </c>
       <c r="AH306" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI306" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="307" spans="1:35">
       <c r="A307">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B307" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C307" t="s">
         <v>50</v>
       </c>
       <c r="D307" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E307" t="s">
         <v>54</v>
@@ -24244,7 +24260,7 @@
         <v>2026</v>
       </c>
       <c r="R307">
-        <v>17952400</v>
+        <v>17941187</v>
       </c>
       <c r="S307" t="s">
         <v>54</v>
@@ -24253,13 +24269,13 @@
         <v>182</v>
       </c>
       <c r="V307" s="1">
-        <v>46274.41773631945</v>
+        <v>46274.41772148148</v>
       </c>
       <c r="W307">
         <v>6</v>
       </c>
       <c r="X307" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="AB307">
         <v>0</v>
@@ -24268,24 +24284,24 @@
         <v>54</v>
       </c>
       <c r="AH307" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI307" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="308" spans="1:35">
       <c r="A308">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B308" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C308" t="s">
         <v>50</v>
       </c>
       <c r="D308" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E308" t="s">
         <v>54</v>
@@ -24315,7 +24331,7 @@
         <v>2026</v>
       </c>
       <c r="R308">
-        <v>17952580</v>
+        <v>17952400</v>
       </c>
       <c r="S308" t="s">
         <v>54</v>
@@ -24324,7 +24340,7 @@
         <v>182</v>
       </c>
       <c r="V308" s="1">
-        <v>46274.41777481481</v>
+        <v>46274.41773631945</v>
       </c>
       <c r="W308">
         <v>6</v>
@@ -24339,18 +24355,18 @@
         <v>54</v>
       </c>
       <c r="AH308" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI308" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="309" spans="1:35">
       <c r="A309">
-        <v>6945</v>
+        <v>6705</v>
       </c>
       <c r="B309" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C309" t="s">
         <v>50</v>
@@ -24362,7 +24378,7 @@
         <v>54</v>
       </c>
       <c r="F309" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G309">
         <v>6215</v>
@@ -24386,7 +24402,7 @@
         <v>2026</v>
       </c>
       <c r="R309">
-        <v>18164523</v>
+        <v>17952580</v>
       </c>
       <c r="S309" t="s">
         <v>54</v>
@@ -24395,13 +24411,13 @@
         <v>182</v>
       </c>
       <c r="V309" s="1">
-        <v>46274.41799332176</v>
+        <v>46274.41777481481</v>
       </c>
       <c r="W309">
         <v>6</v>
       </c>
       <c r="X309" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AB309">
         <v>0</v>
@@ -24410,24 +24426,24 @@
         <v>54</v>
       </c>
       <c r="AH309" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI309" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="310" spans="1:35">
       <c r="A310">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B310" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C310" t="s">
         <v>50</v>
       </c>
       <c r="D310" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E310" t="s">
         <v>54</v>
@@ -24457,42 +24473,42 @@
         <v>2026</v>
       </c>
       <c r="R310">
-        <v>18178163</v>
+        <v>18164523</v>
       </c>
       <c r="S310" t="s">
-        <v>170</v>
+        <v>54</v>
       </c>
       <c r="U310" t="s">
         <v>182</v>
       </c>
       <c r="V310" s="1">
-        <v>46274.41800085648</v>
+        <v>46274.41799332176</v>
       </c>
       <c r="W310">
         <v>6</v>
       </c>
       <c r="X310" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AB310">
         <v>0</v>
       </c>
       <c r="AC310" t="s">
-        <v>170</v>
+        <v>54</v>
       </c>
       <c r="AH310" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AI310" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="311" spans="1:35">
       <c r="A311">
-        <v>5417</v>
+        <v>6949</v>
       </c>
       <c r="B311" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C311" t="s">
         <v>50</v>
@@ -24504,10 +24520,10 @@
         <v>54</v>
       </c>
       <c r="F311" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G311">
-        <v>11746</v>
+        <v>6215</v>
       </c>
       <c r="H311">
         <v>0</v>
@@ -24516,34 +24532,34 @@
         <v>65</v>
       </c>
       <c r="J311" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="N311" s="1">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="P311">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q311">
         <v>2026</v>
       </c>
       <c r="R311">
-        <v>17994311</v>
+        <v>18178163</v>
       </c>
       <c r="S311" t="s">
-        <v>54</v>
+        <v>170</v>
       </c>
       <c r="U311" t="s">
         <v>182</v>
       </c>
       <c r="V311" s="1">
-        <v>46275.31737530093</v>
+        <v>46274.41800085648</v>
       </c>
       <c r="W311">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X311" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="AB311">
         <v>0</v>
@@ -24552,24 +24568,24 @@
         <v>170</v>
       </c>
       <c r="AH311" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="AI311" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="312" spans="1:35">
       <c r="A312">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B312" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C312" t="s">
         <v>50</v>
       </c>
       <c r="D312" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E312" t="s">
         <v>54</v>
@@ -24599,7 +24615,7 @@
         <v>2026</v>
       </c>
       <c r="R312">
-        <v>17994675</v>
+        <v>17994311</v>
       </c>
       <c r="S312" t="s">
         <v>54</v>
@@ -24608,13 +24624,13 @@
         <v>182</v>
       </c>
       <c r="V312" s="1">
-        <v>46275.31747032407</v>
+        <v>46275.31737530093</v>
       </c>
       <c r="W312">
         <v>5</v>
       </c>
       <c r="X312" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="AB312">
         <v>0</v>
@@ -24623,24 +24639,24 @@
         <v>170</v>
       </c>
       <c r="AH312" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI312" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="313" spans="1:35">
       <c r="A313">
-        <v>6486</v>
+        <v>6404</v>
       </c>
       <c r="B313" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C313" t="s">
         <v>50</v>
       </c>
       <c r="D313" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E313" t="s">
         <v>54</v>
@@ -24670,7 +24686,7 @@
         <v>2026</v>
       </c>
       <c r="R313">
-        <v>17994809</v>
+        <v>17994675</v>
       </c>
       <c r="S313" t="s">
         <v>54</v>
@@ -24679,13 +24695,13 @@
         <v>182</v>
       </c>
       <c r="V313" s="1">
-        <v>46275.31747981482</v>
+        <v>46275.31747032407</v>
       </c>
       <c r="W313">
         <v>5</v>
       </c>
       <c r="X313" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="AB313">
         <v>0</v>
@@ -24694,18 +24710,18 @@
         <v>170</v>
       </c>
       <c r="AH313" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI313" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="314" spans="1:35">
       <c r="A314">
-        <v>6548</v>
+        <v>6486</v>
       </c>
       <c r="B314" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C314" t="s">
         <v>50</v>
@@ -24741,7 +24757,7 @@
         <v>2026</v>
       </c>
       <c r="R314">
-        <v>18006051</v>
+        <v>17994809</v>
       </c>
       <c r="S314" t="s">
         <v>54</v>
@@ -24750,13 +24766,13 @@
         <v>182</v>
       </c>
       <c r="V314" s="1">
-        <v>46275.31748724537</v>
+        <v>46275.31747981482</v>
       </c>
       <c r="W314">
         <v>5</v>
       </c>
       <c r="X314" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="AB314">
         <v>0</v>
@@ -24765,27 +24781,27 @@
         <v>170</v>
       </c>
       <c r="AH314" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI314" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="315" spans="1:35">
       <c r="A315">
-        <v>6628</v>
+        <v>6548</v>
       </c>
       <c r="B315" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C315" t="s">
         <v>50</v>
       </c>
       <c r="D315" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E315" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F315" t="s">
         <v>56</v>
@@ -24812,22 +24828,22 @@
         <v>2026</v>
       </c>
       <c r="R315">
-        <v>18003256</v>
+        <v>18006051</v>
       </c>
       <c r="S315" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="U315" t="s">
         <v>182</v>
       </c>
       <c r="V315" s="1">
-        <v>46275.31749535879</v>
+        <v>46275.31748724537</v>
       </c>
       <c r="W315">
         <v>5</v>
       </c>
       <c r="X315" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AB315">
         <v>0</v>
@@ -24836,27 +24852,27 @@
         <v>170</v>
       </c>
       <c r="AH315" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI315" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="316" spans="1:35">
       <c r="A316">
-        <v>6703</v>
+        <v>6628</v>
       </c>
       <c r="B316" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C316" t="s">
         <v>50</v>
       </c>
       <c r="D316" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E316" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F316" t="s">
         <v>56</v>
@@ -24883,22 +24899,22 @@
         <v>2026</v>
       </c>
       <c r="R316">
-        <v>18004017</v>
+        <v>18003256</v>
       </c>
       <c r="S316" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="U316" t="s">
         <v>182</v>
       </c>
       <c r="V316" s="1">
-        <v>46275.31750491898</v>
+        <v>46275.31749535879</v>
       </c>
       <c r="W316">
         <v>5</v>
       </c>
       <c r="X316" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="AB316">
         <v>0</v>
@@ -24907,24 +24923,24 @@
         <v>170</v>
       </c>
       <c r="AH316" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI316" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="317" spans="1:35">
       <c r="A317">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B317" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C317" t="s">
         <v>50</v>
       </c>
       <c r="D317" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E317" t="s">
         <v>54</v>
@@ -24954,7 +24970,7 @@
         <v>2026</v>
       </c>
       <c r="R317">
-        <v>17995164</v>
+        <v>18004017</v>
       </c>
       <c r="S317" t="s">
         <v>54</v>
@@ -24963,13 +24979,13 @@
         <v>182</v>
       </c>
       <c r="V317" s="1">
-        <v>46275.31750555555</v>
+        <v>46275.31750491898</v>
       </c>
       <c r="W317">
         <v>5</v>
       </c>
       <c r="X317" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="AB317">
         <v>0</v>
@@ -24978,24 +24994,24 @@
         <v>170</v>
       </c>
       <c r="AH317" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI317" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="318" spans="1:35">
       <c r="A318">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B318" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C318" t="s">
         <v>50</v>
       </c>
       <c r="D318" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E318" t="s">
         <v>54</v>
@@ -25025,7 +25041,7 @@
         <v>2026</v>
       </c>
       <c r="R318">
-        <v>18004028</v>
+        <v>17995164</v>
       </c>
       <c r="S318" t="s">
         <v>54</v>
@@ -25034,7 +25050,7 @@
         <v>182</v>
       </c>
       <c r="V318" s="1">
-        <v>46275.31750599537</v>
+        <v>46275.31750555555</v>
       </c>
       <c r="W318">
         <v>5</v>
@@ -25049,24 +25065,24 @@
         <v>170</v>
       </c>
       <c r="AH318" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI318" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="319" spans="1:35">
       <c r="A319">
-        <v>5417</v>
+        <v>6705</v>
       </c>
       <c r="B319" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C319" t="s">
         <v>50</v>
       </c>
       <c r="D319" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E319" t="s">
         <v>54</v>
@@ -25075,7 +25091,7 @@
         <v>56</v>
       </c>
       <c r="G319">
-        <v>7877</v>
+        <v>11746</v>
       </c>
       <c r="H319">
         <v>0</v>
@@ -25084,57 +25100,54 @@
         <v>65</v>
       </c>
       <c r="J319" t="s">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="N319" s="1">
-        <v>46259</v>
+        <v>46275</v>
       </c>
       <c r="P319">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q319">
         <v>2026</v>
       </c>
       <c r="R319">
-        <v>17399329</v>
+        <v>18004028</v>
       </c>
       <c r="S319" t="s">
         <v>54</v>
       </c>
       <c r="U319" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="V319" s="1">
-        <v>46275.5810894676</v>
+        <v>46275.31750599537</v>
       </c>
       <c r="W319">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="X319" t="s">
-        <v>189</v>
-      </c>
-      <c r="Y319" t="s">
-        <v>302</v>
+        <v>188</v>
       </c>
       <c r="AB319">
         <v>0</v>
       </c>
       <c r="AC319" t="s">
-        <v>54</v>
+        <v>170</v>
       </c>
       <c r="AH319" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI319" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="320" spans="1:35">
       <c r="A320">
-        <v>6486</v>
+        <v>5417</v>
       </c>
       <c r="B320" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C320" t="s">
         <v>50</v>
@@ -25149,7 +25162,7 @@
         <v>56</v>
       </c>
       <c r="G320">
-        <v>9774</v>
+        <v>7877</v>
       </c>
       <c r="H320">
         <v>0</v>
@@ -25158,7 +25171,7 @@
         <v>65</v>
       </c>
       <c r="J320" t="s">
-        <v>120</v>
+        <v>67</v>
       </c>
       <c r="N320" s="1">
         <v>46259</v>
@@ -25170,7 +25183,7 @@
         <v>2026</v>
       </c>
       <c r="R320">
-        <v>16976320</v>
+        <v>17399329</v>
       </c>
       <c r="S320" t="s">
         <v>54</v>
@@ -25179,16 +25192,16 @@
         <v>180</v>
       </c>
       <c r="V320" s="1">
-        <v>46275.58158541666</v>
+        <v>46275.5810894676</v>
       </c>
       <c r="W320">
         <v>21</v>
       </c>
       <c r="X320" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Y320" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AB320">
         <v>0</v>
@@ -25197,18 +25210,18 @@
         <v>54</v>
       </c>
       <c r="AH320" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI320" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="321" spans="1:35">
       <c r="A321">
-        <v>5417</v>
+        <v>6486</v>
       </c>
       <c r="B321" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C321" t="s">
         <v>50</v>
@@ -25223,7 +25236,7 @@
         <v>56</v>
       </c>
       <c r="G321">
-        <v>7027</v>
+        <v>9774</v>
       </c>
       <c r="H321">
         <v>0</v>
@@ -25232,37 +25245,37 @@
         <v>65</v>
       </c>
       <c r="J321" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N321" s="1">
-        <v>46289</v>
+        <v>46259</v>
       </c>
       <c r="P321">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q321">
         <v>2026</v>
       </c>
       <c r="R321">
-        <v>17399290</v>
+        <v>16976320</v>
       </c>
       <c r="S321" t="s">
         <v>54</v>
       </c>
       <c r="U321" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="V321" s="1">
-        <v>46279.70955146991</v>
+        <v>46275.58158541666</v>
       </c>
       <c r="W321">
-        <v>-9</v>
+        <v>21</v>
       </c>
       <c r="X321" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Y321" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AB321">
         <v>0</v>
@@ -25271,18 +25284,18 @@
         <v>54</v>
       </c>
       <c r="AH321" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AI321" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="322" spans="1:35">
       <c r="A322">
-        <v>6627</v>
+        <v>5417</v>
       </c>
       <c r="B322" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C322" t="s">
         <v>50</v>
@@ -25291,28 +25304,25 @@
         <v>51</v>
       </c>
       <c r="E322" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F322" t="s">
         <v>56</v>
       </c>
       <c r="G322">
-        <v>11056</v>
+        <v>7027</v>
       </c>
       <c r="H322">
         <v>0</v>
       </c>
       <c r="I322" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J322" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="N322" s="1">
-        <v>46276</v>
-      </c>
-      <c r="O322" t="s">
-        <v>145</v>
+        <v>46289</v>
       </c>
       <c r="P322">
         <v>8</v>
@@ -25321,34 +25331,111 @@
         <v>2026</v>
       </c>
       <c r="R322">
+        <v>17399290</v>
+      </c>
+      <c r="S322" t="s">
+        <v>54</v>
+      </c>
+      <c r="U322" t="s">
+        <v>181</v>
+      </c>
+      <c r="V322" s="1">
+        <v>46279.70955146991</v>
+      </c>
+      <c r="W322">
+        <v>-9</v>
+      </c>
+      <c r="X322" t="s">
+        <v>189</v>
+      </c>
+      <c r="Y322" t="s">
+        <v>306</v>
+      </c>
+      <c r="AB322">
+        <v>0</v>
+      </c>
+      <c r="AC322" t="s">
+        <v>54</v>
+      </c>
+      <c r="AH322" t="s">
+        <v>312</v>
+      </c>
+      <c r="AI322" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="323" spans="1:35">
+      <c r="A323">
+        <v>6627</v>
+      </c>
+      <c r="B323" t="s">
+        <v>36</v>
+      </c>
+      <c r="C323" t="s">
+        <v>50</v>
+      </c>
+      <c r="D323" t="s">
+        <v>51</v>
+      </c>
+      <c r="E323" t="s">
+        <v>55</v>
+      </c>
+      <c r="F323" t="s">
+        <v>56</v>
+      </c>
+      <c r="G323">
+        <v>11056</v>
+      </c>
+      <c r="H323">
+        <v>0</v>
+      </c>
+      <c r="I323" t="s">
+        <v>66</v>
+      </c>
+      <c r="J323" t="s">
+        <v>122</v>
+      </c>
+      <c r="N323" s="1">
+        <v>46276</v>
+      </c>
+      <c r="O323" t="s">
+        <v>145</v>
+      </c>
+      <c r="P323">
+        <v>8</v>
+      </c>
+      <c r="Q323">
+        <v>2026</v>
+      </c>
+      <c r="R323">
         <v>18270269</v>
       </c>
-      <c r="U322" t="s">
+      <c r="U323" t="s">
         <v>182</v>
       </c>
-      <c r="V322" s="1">
+      <c r="V323" s="1">
         <v>46276.41675075232</v>
       </c>
-      <c r="W322">
+      <c r="W323">
         <v>4</v>
       </c>
-      <c r="X322" t="s">
+      <c r="X323" t="s">
         <v>184</v>
       </c>
-      <c r="Y322" t="s">
-        <v>305</v>
-      </c>
-      <c r="AB322">
-        <v>0</v>
-      </c>
-      <c r="AC322" t="s">
-        <v>309</v>
-      </c>
-      <c r="AH322" t="s">
-        <v>310</v>
-      </c>
-      <c r="AI322" t="s">
-        <v>314</v>
+      <c r="Y323" t="s">
+        <v>307</v>
+      </c>
+      <c r="AB323">
+        <v>0</v>
+      </c>
+      <c r="AC323" t="s">
+        <v>311</v>
+      </c>
+      <c r="AH323" t="s">
+        <v>312</v>
+      </c>
+      <c r="AI323" t="s">
+        <v>316</v>
       </c>
     </row>
   </sheetData>

--- a/data/base/goias.xlsx
+++ b/data/base/goias.xlsx
@@ -1572,7 +1572,7 @@
         <v>46268.63953865741</v>
       </c>
       <c r="W2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X2" t="s">
         <v>191</v>
@@ -1649,7 +1649,7 @@
         <v>46266.57730150463</v>
       </c>
       <c r="W3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X3" t="s">
         <v>192</v>
@@ -1726,7 +1726,7 @@
         <v>46266.41668148148</v>
       </c>
       <c r="W4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X4" t="s">
         <v>193</v>
@@ -1803,7 +1803,7 @@
         <v>46267.75233784723</v>
       </c>
       <c r="W5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X5" t="s">
         <v>191</v>
@@ -1877,7 +1877,7 @@
         <v>46267.75233927083</v>
       </c>
       <c r="W6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X6" t="s">
         <v>192</v>
@@ -1951,7 +1951,7 @@
         <v>46267.7523394676</v>
       </c>
       <c r="W7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X7" t="s">
         <v>192</v>
@@ -2025,7 +2025,7 @@
         <v>46267.75234278935</v>
       </c>
       <c r="W8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X8" t="s">
         <v>194</v>
@@ -2099,7 +2099,7 @@
         <v>46267.75234309028</v>
       </c>
       <c r="W9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X9" t="s">
         <v>193</v>
@@ -2173,7 +2173,7 @@
         <v>46267.75234383102</v>
       </c>
       <c r="W10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X10" t="s">
         <v>195</v>
@@ -2247,7 +2247,7 @@
         <v>46267.75234424769</v>
       </c>
       <c r="W11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X11" t="s">
         <v>195</v>
@@ -2321,7 +2321,7 @@
         <v>46267.47365627315</v>
       </c>
       <c r="W12">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="X12" t="s">
         <v>196</v>
@@ -2395,7 +2395,7 @@
         <v>46266.47620831019</v>
       </c>
       <c r="W13">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="X13" t="s">
         <v>197</v>
@@ -2469,7 +2469,7 @@
         <v>46267.57586420139</v>
       </c>
       <c r="W14">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="X14" t="s">
         <v>198</v>
@@ -2540,7 +2540,7 @@
         <v>46266.44145744213</v>
       </c>
       <c r="W15">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="X15" t="s">
         <v>199</v>
@@ -2608,7 +2608,7 @@
         <v>46266.44156952546</v>
       </c>
       <c r="W16">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="X16" t="s">
         <v>199</v>
@@ -2676,7 +2676,7 @@
         <v>46266.44152346065</v>
       </c>
       <c r="W17">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X17" t="s">
         <v>199</v>
@@ -2750,7 +2750,7 @@
         <v>46269.3962034375</v>
       </c>
       <c r="W18">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X18" t="s">
         <v>200</v>
@@ -2827,7 +2827,7 @@
         <v>46268.54759884259</v>
       </c>
       <c r="W19">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X19" t="s">
         <v>197</v>
@@ -2904,7 +2904,7 @@
         <v>46269.38216940972</v>
       </c>
       <c r="W20">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X20" t="s">
         <v>198</v>
@@ -2981,7 +2981,7 @@
         <v>46269.40844942129</v>
       </c>
       <c r="W21">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X21" t="s">
         <v>196</v>
@@ -3058,7 +3058,7 @@
         <v>46266.37634084491</v>
       </c>
       <c r="W22">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="X22" t="s">
         <v>201</v>
@@ -3132,7 +3132,7 @@
         <v>46267.47452163194</v>
       </c>
       <c r="W23">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="X23" t="s">
         <v>196</v>
@@ -3206,7 +3206,7 @@
         <v>46267.4745221412</v>
       </c>
       <c r="W24">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="X24" t="s">
         <v>196</v>
@@ -3280,7 +3280,7 @@
         <v>46267.47452299768</v>
       </c>
       <c r="W25">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="X25" t="s">
         <v>196</v>
@@ -3354,7 +3354,7 @@
         <v>46267.75231010417</v>
       </c>
       <c r="W26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X26" t="s">
         <v>197</v>
@@ -3428,7 +3428,7 @@
         <v>46267.75234059028</v>
       </c>
       <c r="W27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X27" t="s">
         <v>196</v>
@@ -3502,7 +3502,7 @@
         <v>46267.7523409375</v>
       </c>
       <c r="W28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X28" t="s">
         <v>196</v>
@@ -3576,7 +3576,7 @@
         <v>46267.75234170139</v>
       </c>
       <c r="W29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X29" t="s">
         <v>196</v>
@@ -3650,7 +3650,7 @@
         <v>46268.58940019676</v>
       </c>
       <c r="W30">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="X30" t="s">
         <v>200</v>
@@ -3727,7 +3727,7 @@
         <v>46268.37896984954</v>
       </c>
       <c r="W31">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X31" t="s">
         <v>192</v>
@@ -3804,7 +3804,7 @@
         <v>46269.71652982639</v>
       </c>
       <c r="W32">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X32" t="s">
         <v>194</v>
@@ -3881,7 +3881,7 @@
         <v>46269.71069613426</v>
       </c>
       <c r="W33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X33" t="s">
         <v>193</v>
@@ -3958,7 +3958,7 @@
         <v>46267.55838734953</v>
       </c>
       <c r="W34">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X34" t="s">
         <v>197</v>
@@ -4038,7 +4038,7 @@
         <v>46273.59003707176</v>
       </c>
       <c r="W35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X35" t="s">
         <v>201</v>
@@ -4118,7 +4118,7 @@
         <v>46268.74069754629</v>
       </c>
       <c r="W36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X36" t="s">
         <v>191</v>
@@ -4198,7 +4198,7 @@
         <v>46273.45940115741</v>
       </c>
       <c r="W37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X37" t="s">
         <v>200</v>
@@ -4275,7 +4275,7 @@
         <v>46267.66088636574</v>
       </c>
       <c r="W38">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X38" t="s">
         <v>197</v>
@@ -4355,7 +4355,7 @@
         <v>46268.45922827546</v>
       </c>
       <c r="W39">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X39" t="s">
         <v>198</v>
@@ -4435,7 +4435,7 @@
         <v>46269.59248078704</v>
       </c>
       <c r="W40">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X40" t="s">
         <v>192</v>
@@ -4515,7 +4515,7 @@
         <v>46269.59224453704</v>
       </c>
       <c r="W41">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X41" t="s">
         <v>192</v>
@@ -4595,7 +4595,7 @@
         <v>46268.5891771875</v>
       </c>
       <c r="W42">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X42" t="s">
         <v>200</v>
@@ -4675,7 +4675,7 @@
         <v>46267.64795916666</v>
       </c>
       <c r="W43">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X43" t="s">
         <v>196</v>
@@ -4755,7 +4755,7 @@
         <v>46267.4478849537</v>
       </c>
       <c r="W44">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X44" t="s">
         <v>194</v>
@@ -4835,7 +4835,7 @@
         <v>46269.59056300926</v>
       </c>
       <c r="W45">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X45" t="s">
         <v>193</v>
@@ -4909,7 +4909,7 @@
         <v>46273.67026252315</v>
       </c>
       <c r="W46">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X46" t="s">
         <v>197</v>
@@ -4983,7 +4983,7 @@
         <v>46269.677524375</v>
       </c>
       <c r="W47">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X47" t="s">
         <v>198</v>
@@ -5057,7 +5057,7 @@
         <v>46269.677525</v>
       </c>
       <c r="W48">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X48" t="s">
         <v>192</v>
@@ -5131,7 +5131,7 @@
         <v>46269.677525625</v>
       </c>
       <c r="W49">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X49" t="s">
         <v>192</v>
@@ -5205,7 +5205,7 @@
         <v>46268.58906282407</v>
       </c>
       <c r="W50">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X50" t="s">
         <v>200</v>
@@ -5279,7 +5279,7 @@
         <v>46267.64761306713</v>
       </c>
       <c r="W51">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X51" t="s">
         <v>196</v>
@@ -5356,7 +5356,7 @@
         <v>46273.64957155092</v>
       </c>
       <c r="W52">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X52" t="s">
         <v>194</v>
@@ -5433,7 +5433,7 @@
         <v>46273.39871140046</v>
       </c>
       <c r="W53">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X53" t="s">
         <v>193</v>
@@ -5510,7 +5510,7 @@
         <v>46267.35832805555</v>
       </c>
       <c r="W54">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X54" t="s">
         <v>198</v>
@@ -5590,7 +5590,7 @@
         <v>46268.71229238426</v>
       </c>
       <c r="W55">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X55" t="s">
         <v>192</v>
@@ -5670,7 +5670,7 @@
         <v>46268.71229297454</v>
       </c>
       <c r="W56">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X56" t="s">
         <v>192</v>
@@ -5750,7 +5750,7 @@
         <v>46267.74532275463</v>
       </c>
       <c r="W57">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X57" t="s">
         <v>200</v>
@@ -5827,7 +5827,7 @@
         <v>46269.60160202546</v>
       </c>
       <c r="W58">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X58" t="s">
         <v>197</v>
@@ -5907,7 +5907,7 @@
         <v>46273.64508760416</v>
       </c>
       <c r="W59">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X59" t="s">
         <v>201</v>
@@ -5987,7 +5987,7 @@
         <v>46268.45926839121</v>
       </c>
       <c r="W60">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X60" t="s">
         <v>198</v>
@@ -6067,7 +6067,7 @@
         <v>46269.59250902777</v>
       </c>
       <c r="W61">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X61" t="s">
         <v>192</v>
@@ -6147,7 +6147,7 @@
         <v>46269.5922865625</v>
       </c>
       <c r="W62">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X62" t="s">
         <v>192</v>
@@ -6227,7 +6227,7 @@
         <v>46268.58922707176</v>
       </c>
       <c r="W63">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X63" t="s">
         <v>200</v>
@@ -6307,7 +6307,7 @@
         <v>46267.64800344907</v>
       </c>
       <c r="W64">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X64" t="s">
         <v>196</v>
@@ -6387,7 +6387,7 @@
         <v>46267.44799793982</v>
       </c>
       <c r="W65">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X65" t="s">
         <v>194</v>
@@ -6467,7 +6467,7 @@
         <v>46269.59070487269</v>
       </c>
       <c r="W66">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X66" t="s">
         <v>193</v>
@@ -6547,7 +6547,7 @@
         <v>46269.49635894676</v>
       </c>
       <c r="W67">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X67" t="s">
         <v>198</v>
@@ -6621,7 +6621,7 @@
         <v>46269.63659284722</v>
       </c>
       <c r="W68">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X68" t="s">
         <v>197</v>
@@ -6695,7 +6695,7 @@
         <v>46273.64532122685</v>
       </c>
       <c r="W69">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X69" t="s">
         <v>201</v>
@@ -6769,7 +6769,7 @@
         <v>46268.45929986111</v>
       </c>
       <c r="W70">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X70" t="s">
         <v>198</v>
@@ -6843,7 +6843,7 @@
         <v>46269.5925421875</v>
       </c>
       <c r="W71">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X71" t="s">
         <v>192</v>
@@ -6917,7 +6917,7 @@
         <v>46269.59231454861</v>
       </c>
       <c r="W72">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X72" t="s">
         <v>192</v>
@@ -6991,7 +6991,7 @@
         <v>46268.58932953704</v>
       </c>
       <c r="W73">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X73" t="s">
         <v>200</v>
@@ -7065,7 +7065,7 @@
         <v>46267.648038125</v>
       </c>
       <c r="W74">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X74" t="s">
         <v>196</v>
@@ -7139,7 +7139,7 @@
         <v>46267.44824061343</v>
       </c>
       <c r="W75">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X75" t="s">
         <v>194</v>
@@ -7213,7 +7213,7 @@
         <v>46269.59082328704</v>
       </c>
       <c r="W76">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X76" t="s">
         <v>193</v>
@@ -7284,7 +7284,7 @@
         <v>46273.63629708334</v>
       </c>
       <c r="W77">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X77" t="s">
         <v>193</v>
@@ -7358,7 +7358,7 @@
         <v>46273.64318633102</v>
       </c>
       <c r="W78">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X78" t="s">
         <v>193</v>
@@ -7432,7 +7432,7 @@
         <v>46273.64880981482</v>
       </c>
       <c r="W79">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X79" t="s">
         <v>193</v>
@@ -7509,7 +7509,7 @@
         <v>46267.72055925926</v>
       </c>
       <c r="W80">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="X80" t="s">
         <v>191</v>
@@ -7580,7 +7580,7 @@
         <v>46267.79441380787</v>
       </c>
       <c r="W81">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="X81" t="s">
         <v>192</v>
@@ -7654,7 +7654,7 @@
         <v>46267.79441215278</v>
       </c>
       <c r="W82">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="X82" t="s">
         <v>193</v>
@@ -7728,7 +7728,7 @@
         <v>46267.7205502662</v>
       </c>
       <c r="W83">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X83" t="s">
         <v>191</v>
@@ -7799,7 +7799,7 @@
         <v>46267.79439748843</v>
       </c>
       <c r="W84">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X84" t="s">
         <v>192</v>
@@ -7870,7 +7870,7 @@
         <v>46267.79440011574</v>
       </c>
       <c r="W85">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X85" t="s">
         <v>194</v>
@@ -7941,7 +7941,7 @@
         <v>46267.79439818287</v>
       </c>
       <c r="W86">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X86" t="s">
         <v>193</v>
@@ -8015,7 +8015,7 @@
         <v>46267.7202693287</v>
       </c>
       <c r="W87">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X87" t="s">
         <v>191</v>
@@ -8086,7 +8086,7 @@
         <v>46267.79409846065</v>
       </c>
       <c r="W88">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X88" t="s">
         <v>192</v>
@@ -8160,7 +8160,7 @@
         <v>46267.79409725694</v>
       </c>
       <c r="W89">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X89" t="s">
         <v>192</v>
@@ -8228,7 +8228,7 @@
         <v>46267.79410239583</v>
       </c>
       <c r="W90">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X90" t="s">
         <v>194</v>
@@ -8296,7 +8296,7 @@
         <v>46267.79409934028</v>
       </c>
       <c r="W91">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X91" t="s">
         <v>193</v>
@@ -8370,7 +8370,7 @@
         <v>46267.72033356482</v>
       </c>
       <c r="W92">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X92" t="s">
         <v>191</v>
@@ -8441,7 +8441,7 @@
         <v>46267.79418105324</v>
       </c>
       <c r="W93">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X93" t="s">
         <v>192</v>
@@ -8515,7 +8515,7 @@
         <v>46267.79418005787</v>
       </c>
       <c r="W94">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X94" t="s">
         <v>192</v>
@@ -8583,7 +8583,7 @@
         <v>46267.79418379629</v>
       </c>
       <c r="W95">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X95" t="s">
         <v>194</v>
@@ -8651,7 +8651,7 @@
         <v>46267.79418283565</v>
       </c>
       <c r="W96">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X96" t="s">
         <v>193</v>
@@ -8725,7 +8725,7 @@
         <v>46267.71937662037</v>
       </c>
       <c r="W97">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X97" t="s">
         <v>191</v>
@@ -8796,7 +8796,7 @@
         <v>46267.79259834491</v>
       </c>
       <c r="W98">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X98" t="s">
         <v>192</v>
@@ -8870,7 +8870,7 @@
         <v>46267.79260170139</v>
       </c>
       <c r="W99">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X99" t="s">
         <v>193</v>
@@ -8947,7 +8947,7 @@
         <v>46268.37621265047</v>
       </c>
       <c r="W100">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X100" t="s">
         <v>195</v>
@@ -9021,7 +9021,7 @@
         <v>46267.79440636574</v>
       </c>
       <c r="W101">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X101" t="s">
         <v>194</v>
@@ -9095,7 +9095,7 @@
         <v>46267.72037954861</v>
       </c>
       <c r="W102">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X102" t="s">
         <v>191</v>
@@ -9166,7 +9166,7 @@
         <v>46267.79424664352</v>
       </c>
       <c r="W103">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X103" t="s">
         <v>192</v>
@@ -9240,7 +9240,7 @@
         <v>46267.79424586806</v>
       </c>
       <c r="W104">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X104" t="s">
         <v>192</v>
@@ -9308,7 +9308,7 @@
         <v>46267.79424864583</v>
       </c>
       <c r="W105">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X105" t="s">
         <v>194</v>
@@ -9376,7 +9376,7 @@
         <v>46267.79424725694</v>
       </c>
       <c r="W106">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X106" t="s">
         <v>193</v>
@@ -9450,7 +9450,7 @@
         <v>46267.79425081018</v>
       </c>
       <c r="W107">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X107" t="s">
         <v>195</v>
@@ -9524,7 +9524,7 @@
         <v>46267.71942916667</v>
       </c>
       <c r="W108">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X108" t="s">
         <v>191</v>
@@ -9595,7 +9595,7 @@
         <v>46267.79268530093</v>
       </c>
       <c r="W109">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X109" t="s">
         <v>194</v>
@@ -9669,7 +9669,7 @@
         <v>46267.79268769676</v>
       </c>
       <c r="W110">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X110" t="s">
         <v>193</v>
@@ -9740,7 +9740,7 @@
         <v>46267.79249748842</v>
       </c>
       <c r="W111">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X111" t="s">
         <v>194</v>
@@ -9814,7 +9814,7 @@
         <v>46267.79249788194</v>
       </c>
       <c r="W112">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X112" t="s">
         <v>193</v>
@@ -9888,7 +9888,7 @@
         <v>46267.71927280092</v>
       </c>
       <c r="W113">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X113" t="s">
         <v>191</v>
@@ -9959,7 +9959,7 @@
         <v>46267.79251079861</v>
       </c>
       <c r="W114">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X114" t="s">
         <v>194</v>
@@ -10033,7 +10033,7 @@
         <v>46267.79251038194</v>
       </c>
       <c r="W115">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X115" t="s">
         <v>193</v>
@@ -10107,7 +10107,7 @@
         <v>46267.72044811342</v>
       </c>
       <c r="W116">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X116" t="s">
         <v>191</v>
@@ -10178,7 +10178,7 @@
         <v>46267.79429737268</v>
       </c>
       <c r="W117">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X117" t="s">
         <v>192</v>
@@ -10252,7 +10252,7 @@
         <v>46267.79429603009</v>
       </c>
       <c r="W118">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X118" t="s">
         <v>192</v>
@@ -10320,7 +10320,7 @@
         <v>46267.79429876158</v>
       </c>
       <c r="W119">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X119" t="s">
         <v>194</v>
@@ -10388,7 +10388,7 @@
         <v>46267.79429826389</v>
       </c>
       <c r="W120">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X120" t="s">
         <v>193</v>
@@ -10462,7 +10462,7 @@
         <v>46267.72050385417</v>
       </c>
       <c r="W121">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X121" t="s">
         <v>191</v>
@@ -10533,7 +10533,7 @@
         <v>46267.79434996528</v>
       </c>
       <c r="W122">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X122" t="s">
         <v>192</v>
@@ -10607,7 +10607,7 @@
         <v>46267.79434864583</v>
       </c>
       <c r="W123">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X123" t="s">
         <v>192</v>
@@ -10675,7 +10675,7 @@
         <v>46267.79435208334</v>
       </c>
       <c r="W124">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X124" t="s">
         <v>194</v>
@@ -10743,7 +10743,7 @@
         <v>46267.79435100695</v>
       </c>
       <c r="W125">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X125" t="s">
         <v>193</v>
@@ -10820,7 +10820,7 @@
         <v>46273.6788224074</v>
       </c>
       <c r="W126">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X126" t="s">
         <v>193</v>
@@ -10900,7 +10900,7 @@
         <v>46273.67943539352</v>
       </c>
       <c r="W127">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X127" t="s">
         <v>193</v>
@@ -10977,7 +10977,7 @@
         <v>46266.37636392361</v>
       </c>
       <c r="W128">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X128" t="s">
         <v>197</v>
@@ -11051,7 +11051,7 @@
         <v>46266.37598834491</v>
       </c>
       <c r="W129">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X129" t="s">
         <v>197</v>
@@ -11128,7 +11128,7 @@
         <v>46268.45899988426</v>
       </c>
       <c r="W130">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X130" t="s">
         <v>198</v>
@@ -11205,7 +11205,7 @@
         <v>46266.45957881944</v>
       </c>
       <c r="W131">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X131" t="s">
         <v>196</v>
@@ -11279,7 +11279,7 @@
         <v>46266.37645462963</v>
       </c>
       <c r="W132">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X132" t="s">
         <v>197</v>
@@ -11353,7 +11353,7 @@
         <v>46266.37649475694</v>
       </c>
       <c r="W133">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X133" t="s">
         <v>197</v>
@@ -11427,7 +11427,7 @@
         <v>46266.37591180555</v>
       </c>
       <c r="W134">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X134" t="s">
         <v>197</v>
@@ -11504,7 +11504,7 @@
         <v>46268.45896508102</v>
       </c>
       <c r="W135">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X135" t="s">
         <v>198</v>
@@ -11581,7 +11581,7 @@
         <v>46266.45946195602</v>
       </c>
       <c r="W136">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X136" t="s">
         <v>196</v>
@@ -11655,7 +11655,7 @@
         <v>46266.37538684028</v>
       </c>
       <c r="W137">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X137" t="s">
         <v>197</v>
@@ -11729,7 +11729,7 @@
         <v>46266.37538506944</v>
       </c>
       <c r="W138">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X138" t="s">
         <v>201</v>
@@ -11806,7 +11806,7 @@
         <v>46268.45881820602</v>
       </c>
       <c r="W139">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X139" t="s">
         <v>198</v>
@@ -11883,7 +11883,7 @@
         <v>46266.45895332176</v>
       </c>
       <c r="W140">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X140" t="s">
         <v>200</v>
@@ -11957,7 +11957,7 @@
         <v>46266.45874105324</v>
       </c>
       <c r="W141">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X141" t="s">
         <v>196</v>
@@ -12031,7 +12031,7 @@
         <v>46266.45873584491</v>
       </c>
       <c r="W142">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X142" t="s">
         <v>196</v>
@@ -12105,7 +12105,7 @@
         <v>46273.6799675</v>
       </c>
       <c r="W143">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X143" t="s">
         <v>196</v>
@@ -12179,7 +12179,7 @@
         <v>46273.55254606481</v>
       </c>
       <c r="W144">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X144" t="s">
         <v>197</v>
@@ -12253,7 +12253,7 @@
         <v>46273.55252126158</v>
       </c>
       <c r="W145">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X145" t="s">
         <v>201</v>
@@ -12327,7 +12327,7 @@
         <v>46273.55254163194</v>
       </c>
       <c r="W146">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X146" t="s">
         <v>198</v>
@@ -12401,7 +12401,7 @@
         <v>46273.5525440162</v>
       </c>
       <c r="W147">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X147" t="s">
         <v>200</v>
@@ -12475,7 +12475,7 @@
         <v>46273.84422141204</v>
       </c>
       <c r="W148">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X148" t="s">
         <v>196</v>
@@ -12549,7 +12549,7 @@
         <v>46273.55254652778</v>
       </c>
       <c r="W149">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X149" t="s">
         <v>196</v>
@@ -12626,7 +12626,7 @@
         <v>46268.45898549769</v>
       </c>
       <c r="W150">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X150" t="s">
         <v>198</v>
@@ -12703,7 +12703,7 @@
         <v>46268.45915543981</v>
       </c>
       <c r="W151">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X151" t="s">
         <v>198</v>
@@ -12777,7 +12777,7 @@
         <v>46273.56305208334</v>
       </c>
       <c r="W152">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X152" t="s">
         <v>196</v>
@@ -12851,7 +12851,7 @@
         <v>46267.44505795139</v>
       </c>
       <c r="W153">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X153" t="s">
         <v>196</v>
@@ -12922,7 +12922,7 @@
         <v>46266.04180934028</v>
       </c>
       <c r="W154">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="X154" t="s">
         <v>192</v>
@@ -12996,7 +12996,7 @@
         <v>46266.08343295139</v>
       </c>
       <c r="W155">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="X155" t="s">
         <v>196</v>
@@ -13070,7 +13070,7 @@
         <v>46266.08344398148</v>
       </c>
       <c r="W156">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="X156" t="s">
         <v>194</v>
@@ -13144,7 +13144,7 @@
         <v>46266.25077376157</v>
       </c>
       <c r="W157">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="X157" t="s">
         <v>197</v>
@@ -13218,7 +13218,7 @@
         <v>46266.25004302083</v>
       </c>
       <c r="W158">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="X158" t="s">
         <v>201</v>
@@ -13292,7 +13292,7 @@
         <v>46266.25135543982</v>
       </c>
       <c r="W159">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="X159" t="s">
         <v>200</v>
@@ -13366,7 +13366,7 @@
         <v>46266.25305</v>
       </c>
       <c r="W160">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="X160" t="s">
         <v>197</v>
@@ -13440,7 +13440,7 @@
         <v>46266.25270034722</v>
       </c>
       <c r="W161">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="X161" t="s">
         <v>201</v>
@@ -13514,7 +13514,7 @@
         <v>46266.25274991898</v>
       </c>
       <c r="W162">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="X162" t="s">
         <v>192</v>
@@ -13588,7 +13588,7 @@
         <v>46266.25364633102</v>
       </c>
       <c r="W163">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="X163" t="s">
         <v>200</v>
@@ -13662,7 +13662,7 @@
         <v>46266.25369826389</v>
       </c>
       <c r="W164">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="X164" t="s">
         <v>193</v>
@@ -13736,7 +13736,7 @@
         <v>46266.25305112269</v>
       </c>
       <c r="W165">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="X165" t="s">
         <v>197</v>
@@ -13810,7 +13810,7 @@
         <v>46266.25275173611</v>
       </c>
       <c r="W166">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="X166" t="s">
         <v>192</v>
@@ -13884,7 +13884,7 @@
         <v>46266.25364869213</v>
       </c>
       <c r="W167">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="X167" t="s">
         <v>196</v>
@@ -13958,7 +13958,7 @@
         <v>46266.25369988426</v>
       </c>
       <c r="W168">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="X168" t="s">
         <v>193</v>
@@ -14035,7 +14035,7 @@
         <v>46268.62318445602</v>
       </c>
       <c r="W169">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X169" t="s">
         <v>197</v>
@@ -14112,7 +14112,7 @@
         <v>46268.62319864584</v>
       </c>
       <c r="W170">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X170" t="s">
         <v>201</v>
@@ -14189,7 +14189,7 @@
         <v>46268.62320026621</v>
       </c>
       <c r="W171">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X171" t="s">
         <v>198</v>
@@ -14266,7 +14266,7 @@
         <v>46268.62320177083</v>
       </c>
       <c r="W172">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X172" t="s">
         <v>191</v>
@@ -14343,7 +14343,7 @@
         <v>46268.62320378472</v>
       </c>
       <c r="W173">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X173" t="s">
         <v>192</v>
@@ -14420,7 +14420,7 @@
         <v>46268.62320393518</v>
       </c>
       <c r="W174">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X174" t="s">
         <v>192</v>
@@ -14497,7 +14497,7 @@
         <v>46268.62320697917</v>
       </c>
       <c r="W175">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X175" t="s">
         <v>200</v>
@@ -14574,7 +14574,7 @@
         <v>46268.62320717592</v>
       </c>
       <c r="W176">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X176" t="s">
         <v>196</v>
@@ -14651,7 +14651,7 @@
         <v>46268.62320732639</v>
       </c>
       <c r="W177">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X177" t="s">
         <v>196</v>
@@ -14728,7 +14728,7 @@
         <v>46268.62320810185</v>
       </c>
       <c r="W178">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X178" t="s">
         <v>196</v>
@@ -14805,7 +14805,7 @@
         <v>46268.6232125</v>
       </c>
       <c r="W179">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X179" t="s">
         <v>194</v>
@@ -14882,7 +14882,7 @@
         <v>46268.62321412037</v>
       </c>
       <c r="W180">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X180" t="s">
         <v>193</v>
@@ -14959,7 +14959,7 @@
         <v>46268.6232128125</v>
       </c>
       <c r="W181">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X181" t="s">
         <v>195</v>
@@ -15036,7 +15036,7 @@
         <v>46268.62321296296</v>
       </c>
       <c r="W182">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X182" t="s">
         <v>195</v>
@@ -15110,7 +15110,7 @@
         <v>46269.41908927084</v>
       </c>
       <c r="W183">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X183" t="s">
         <v>197</v>
@@ -15181,7 +15181,7 @@
         <v>46269.41910457176</v>
       </c>
       <c r="W184">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X184" t="s">
         <v>201</v>
@@ -15252,7 +15252,7 @@
         <v>46269.37885223379</v>
       </c>
       <c r="W185">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X185" t="s">
         <v>198</v>
@@ -15323,7 +15323,7 @@
         <v>46269.3782503125</v>
       </c>
       <c r="W186">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X186" t="s">
         <v>191</v>
@@ -15394,7 +15394,7 @@
         <v>46269.41913152778</v>
       </c>
       <c r="W187">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X187" t="s">
         <v>192</v>
@@ -15465,7 +15465,7 @@
         <v>46269.41913775463</v>
       </c>
       <c r="W188">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X188" t="s">
         <v>192</v>
@@ -15536,7 +15536,7 @@
         <v>46268.7596207176</v>
       </c>
       <c r="W189">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X189" t="s">
         <v>197</v>
@@ -15607,7 +15607,7 @@
         <v>46268.75963109954</v>
       </c>
       <c r="W190">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X190" t="s">
         <v>201</v>
@@ -15678,7 +15678,7 @@
         <v>46268.75963225694</v>
       </c>
       <c r="W191">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X191" t="s">
         <v>198</v>
@@ -15749,7 +15749,7 @@
         <v>46268.75963348379</v>
       </c>
       <c r="W192">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X192" t="s">
         <v>191</v>
@@ -15820,7 +15820,7 @@
         <v>46268.75963414352</v>
       </c>
       <c r="W193">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X193" t="s">
         <v>192</v>
@@ -15891,7 +15891,7 @@
         <v>46268.62326365741</v>
       </c>
       <c r="W194">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X194" t="s">
         <v>192</v>
@@ -15962,7 +15962,7 @@
         <v>46268.75963472222</v>
       </c>
       <c r="W195">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X195" t="s">
         <v>200</v>
@@ -16033,7 +16033,7 @@
         <v>46268.75963475694</v>
       </c>
       <c r="W196">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X196" t="s">
         <v>196</v>
@@ -16104,7 +16104,7 @@
         <v>46268.75963506944</v>
       </c>
       <c r="W197">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X197" t="s">
         <v>196</v>
@@ -16175,7 +16175,7 @@
         <v>46268.7596360301</v>
       </c>
       <c r="W198">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X198" t="s">
         <v>196</v>
@@ -16246,7 +16246,7 @@
         <v>46268.62327121528</v>
       </c>
       <c r="W199">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X199" t="s">
         <v>194</v>
@@ -16317,7 +16317,7 @@
         <v>46268.75963931713</v>
       </c>
       <c r="W200">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X200" t="s">
         <v>193</v>
@@ -16388,7 +16388,7 @@
         <v>46268.75963822917</v>
       </c>
       <c r="W201">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X201" t="s">
         <v>195</v>
@@ -16459,7 +16459,7 @@
         <v>46268.75963857639</v>
       </c>
       <c r="W202">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X202" t="s">
         <v>195</v>
@@ -16530,7 +16530,7 @@
         <v>46269.41908901621</v>
       </c>
       <c r="W203">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X203" t="s">
         <v>197</v>
@@ -16601,7 +16601,7 @@
         <v>46269.41910425926</v>
       </c>
       <c r="W204">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X204" t="s">
         <v>201</v>
@@ -16672,7 +16672,7 @@
         <v>46269.37890997685</v>
       </c>
       <c r="W205">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X205" t="s">
         <v>198</v>
@@ -16743,7 +16743,7 @@
         <v>46269.37833320602</v>
       </c>
       <c r="W206">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X206" t="s">
         <v>191</v>
@@ -16814,7 +16814,7 @@
         <v>46269.41913112268</v>
       </c>
       <c r="W207">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X207" t="s">
         <v>192</v>
@@ -16885,7 +16885,7 @@
         <v>46269.41913740741</v>
       </c>
       <c r="W208">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X208" t="s">
         <v>192</v>
@@ -16956,7 +16956,7 @@
         <v>46267.66131466435</v>
       </c>
       <c r="W209">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X209" t="s">
         <v>201</v>
@@ -17030,7 +17030,7 @@
         <v>46266.21595836805</v>
       </c>
       <c r="W210">
-        <v>-40</v>
+        <v>-39</v>
       </c>
       <c r="X210" t="s">
         <v>201</v>
@@ -17104,7 +17104,7 @@
         <v>46266.21572962963</v>
       </c>
       <c r="W211">
-        <v>-40</v>
+        <v>-39</v>
       </c>
       <c r="X211" t="s">
         <v>197</v>
@@ -17178,7 +17178,7 @@
         <v>46266.21550011574</v>
       </c>
       <c r="W212">
-        <v>-40</v>
+        <v>-39</v>
       </c>
       <c r="X212" t="s">
         <v>198</v>
@@ -17252,7 +17252,7 @@
         <v>46266.00006921296</v>
       </c>
       <c r="W213">
-        <v>-40</v>
+        <v>-39</v>
       </c>
       <c r="X213" t="s">
         <v>197</v>
@@ -17323,7 +17323,7 @@
         <v>46266.00006921296</v>
       </c>
       <c r="W214">
-        <v>-40</v>
+        <v>-39</v>
       </c>
       <c r="X214" t="s">
         <v>201</v>
@@ -17391,7 +17391,7 @@
         <v>46269.57097615741</v>
       </c>
       <c r="W215">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X215" t="s">
         <v>198</v>
@@ -17459,7 +17459,7 @@
         <v>46266.00006921296</v>
       </c>
       <c r="W216">
-        <v>-40</v>
+        <v>-39</v>
       </c>
       <c r="X216" t="s">
         <v>198</v>
@@ -17527,7 +17527,7 @@
         <v>46269.46753030093</v>
       </c>
       <c r="W217">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X217" t="s">
         <v>194</v>
@@ -17604,7 +17604,7 @@
         <v>46280.37528408565</v>
       </c>
       <c r="W218">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="X218" t="s">
         <v>197</v>
@@ -17681,7 +17681,7 @@
         <v>46281.63558861111</v>
       </c>
       <c r="W219">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="X219" t="s">
         <v>192</v>
@@ -17761,7 +17761,7 @@
         <v>46281.6358927662</v>
       </c>
       <c r="W220">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="X220" t="s">
         <v>192</v>
@@ -17841,7 +17841,7 @@
         <v>46281.47564895833</v>
       </c>
       <c r="W221">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="X221" t="s">
         <v>194</v>
@@ -17921,7 +17921,7 @@
         <v>46279.66710767361</v>
       </c>
       <c r="W222">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="X222" t="s">
         <v>196</v>
@@ -18001,7 +18001,7 @@
         <v>46281.68877074074</v>
       </c>
       <c r="W223">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="X223" t="s">
         <v>198</v>
@@ -18081,7 +18081,7 @@
         <v>46280.57958537037</v>
       </c>
       <c r="W224">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="X224" t="s">
         <v>191</v>
@@ -18161,7 +18161,7 @@
         <v>46281.63570936343</v>
       </c>
       <c r="W225">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="X225" t="s">
         <v>192</v>
@@ -18241,7 +18241,7 @@
         <v>46281.63595871528</v>
       </c>
       <c r="W226">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="X226" t="s">
         <v>192</v>
@@ -18318,7 +18318,7 @@
         <v>46279.62681744213</v>
       </c>
       <c r="W227">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="X227" t="s">
         <v>200</v>
@@ -18392,7 +18392,7 @@
         <v>46279.66707821759</v>
       </c>
       <c r="W228">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="X228" t="s">
         <v>196</v>
@@ -18469,7 +18469,7 @@
         <v>46281.68880230324</v>
       </c>
       <c r="W229">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="X229" t="s">
         <v>198</v>
@@ -18549,7 +18549,7 @@
         <v>46280.57972293982</v>
       </c>
       <c r="W230">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="X230" t="s">
         <v>191</v>
@@ -18629,7 +18629,7 @@
         <v>46281.63575075231</v>
       </c>
       <c r="W231">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="X231" t="s">
         <v>192</v>
@@ -18709,7 +18709,7 @@
         <v>46281.63599785879</v>
       </c>
       <c r="W232">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="X232" t="s">
         <v>192</v>
@@ -18786,7 +18786,7 @@
         <v>46279.6268503125</v>
       </c>
       <c r="W233">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="X233" t="s">
         <v>200</v>
@@ -18860,7 +18860,7 @@
         <v>46279.66698128472</v>
       </c>
       <c r="W234">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="X234" t="s">
         <v>196</v>
@@ -18931,7 +18931,7 @@
         <v>46279.66929922454</v>
       </c>
       <c r="W235">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X235" t="s">
         <v>197</v>
@@ -19008,7 +19008,7 @@
         <v>46280.61353684028</v>
       </c>
       <c r="W236">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X236" t="s">
         <v>201</v>
@@ -19085,7 +19085,7 @@
         <v>46280.61353920139</v>
       </c>
       <c r="W237">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X237" t="s">
         <v>198</v>
@@ -19162,7 +19162,7 @@
         <v>46279.63250563657</v>
       </c>
       <c r="W238">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X238" t="s">
         <v>191</v>
@@ -19239,7 +19239,7 @@
         <v>46280.61354019676</v>
       </c>
       <c r="W239">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X239" t="s">
         <v>192</v>
@@ -19316,7 +19316,7 @@
         <v>46280.6135403125</v>
       </c>
       <c r="W240">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X240" t="s">
         <v>192</v>
@@ -19396,7 +19396,7 @@
         <v>46281.71218414352</v>
       </c>
       <c r="W241">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X241" t="s">
         <v>200</v>
@@ -19473,7 +19473,7 @@
         <v>46281.41576883102</v>
       </c>
       <c r="W242">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X242" t="s">
         <v>196</v>
@@ -19550,7 +19550,7 @@
         <v>46280.43132989584</v>
       </c>
       <c r="W243">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X243" t="s">
         <v>194</v>
@@ -19627,7 +19627,7 @@
         <v>46280.61367623843</v>
       </c>
       <c r="W244">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X244" t="s">
         <v>193</v>
@@ -19704,7 +19704,7 @@
         <v>46274.60593387731</v>
       </c>
       <c r="W245">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X245" t="s">
         <v>197</v>
@@ -19784,7 +19784,7 @@
         <v>46274.47210818287</v>
       </c>
       <c r="W246">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X246" t="s">
         <v>198</v>
@@ -19864,7 +19864,7 @@
         <v>46276.48975401621</v>
       </c>
       <c r="W247">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X247" t="s">
         <v>192</v>
@@ -19944,7 +19944,7 @@
         <v>46279.38429019676</v>
       </c>
       <c r="W248">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X248" t="s">
         <v>192</v>
@@ -20024,7 +20024,7 @@
         <v>46274.48792050926</v>
       </c>
       <c r="W249">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X249" t="s">
         <v>196</v>
@@ -20104,7 +20104,7 @@
         <v>46274.588374375</v>
       </c>
       <c r="W250">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X250" t="s">
         <v>194</v>
@@ -20181,7 +20181,7 @@
         <v>46274.34198912037</v>
       </c>
       <c r="W251">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X251" t="s">
         <v>193</v>
@@ -20252,7 +20252,7 @@
         <v>46279.6693627662</v>
       </c>
       <c r="W252">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X252" t="s">
         <v>197</v>
@@ -20332,7 +20332,7 @@
         <v>46279.5886965625</v>
       </c>
       <c r="W253">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X253" t="s">
         <v>198</v>
@@ -20409,7 +20409,7 @@
         <v>46279.40189383102</v>
       </c>
       <c r="W254">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X254" t="s">
         <v>191</v>
@@ -20489,7 +20489,7 @@
         <v>46279.58878520833</v>
       </c>
       <c r="W255">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X255" t="s">
         <v>192</v>
@@ -20569,7 +20569,7 @@
         <v>46279.58873577546</v>
       </c>
       <c r="W256">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X256" t="s">
         <v>192</v>
@@ -20646,7 +20646,7 @@
         <v>46279.63255</v>
       </c>
       <c r="W257">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X257" t="s">
         <v>200</v>
@@ -20723,7 +20723,7 @@
         <v>46276.63187557871</v>
       </c>
       <c r="W258">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X258" t="s">
         <v>196</v>
@@ -20800,7 +20800,7 @@
         <v>46279.6265846875</v>
       </c>
       <c r="W259">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X259" t="s">
         <v>194</v>
@@ -20877,7 +20877,7 @@
         <v>46279.63255401621</v>
       </c>
       <c r="W260">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X260" t="s">
         <v>193</v>
@@ -20957,7 +20957,7 @@
         <v>46279.66713805556</v>
       </c>
       <c r="W261">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="X261" t="s">
         <v>196</v>
@@ -21031,7 +21031,7 @@
         <v>46281.63317659722</v>
       </c>
       <c r="W262">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X262" t="s">
         <v>198</v>
@@ -21105,7 +21105,7 @@
         <v>46275.39631951389</v>
       </c>
       <c r="W263">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X263" t="s">
         <v>192</v>
@@ -21179,7 +21179,7 @@
         <v>46275.39631994213</v>
       </c>
       <c r="W264">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X264" t="s">
         <v>192</v>
@@ -21259,7 +21259,7 @@
         <v>46280.62789608796</v>
       </c>
       <c r="W265">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X265" t="s">
         <v>195</v>
@@ -21339,7 +21339,7 @@
         <v>46280.63189497685</v>
       </c>
       <c r="W266">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X266" t="s">
         <v>195</v>
@@ -21419,7 +21419,7 @@
         <v>46280.72961366898</v>
       </c>
       <c r="W267">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X267" t="s">
         <v>192</v>
@@ -21493,7 +21493,7 @@
         <v>46276.37795540509</v>
       </c>
       <c r="W268">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X268" t="s">
         <v>194</v>
@@ -21570,7 +21570,7 @@
         <v>46276.66923222222</v>
       </c>
       <c r="W269">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X269" t="s">
         <v>191</v>
@@ -21644,7 +21644,7 @@
         <v>46276.40669469907</v>
       </c>
       <c r="W270">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X270" t="s">
         <v>192</v>
@@ -21721,7 +21721,7 @@
         <v>46276.64773491898</v>
       </c>
       <c r="W271">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X271" t="s">
         <v>192</v>
@@ -21798,7 +21798,7 @@
         <v>46276.39101108797</v>
       </c>
       <c r="W272">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X272" t="s">
         <v>194</v>
@@ -21878,7 +21878,7 @@
         <v>46280.40395534722</v>
       </c>
       <c r="W273">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X273" t="s">
         <v>193</v>
@@ -21955,7 +21955,7 @@
         <v>46279.74982357639</v>
       </c>
       <c r="W274">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X274" t="s">
         <v>195</v>
@@ -22035,7 +22035,7 @@
         <v>46276.66651596065</v>
       </c>
       <c r="W275">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X275" t="s">
         <v>195</v>
@@ -22112,7 +22112,7 @@
         <v>46280.66345891204</v>
       </c>
       <c r="W276">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="X276" t="s">
         <v>192</v>
@@ -22186,7 +22186,7 @@
         <v>46274.36843923611</v>
       </c>
       <c r="W277">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X277" t="s">
         <v>192</v>
@@ -22263,7 +22263,7 @@
         <v>46274.66470667824</v>
       </c>
       <c r="W278">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X278" t="s">
         <v>195</v>
@@ -22340,7 +22340,7 @@
         <v>46274.74452168981</v>
       </c>
       <c r="W279">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X279" t="s">
         <v>195</v>
@@ -22420,7 +22420,7 @@
         <v>46274.64801501157</v>
       </c>
       <c r="W280">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X280" t="s">
         <v>191</v>
@@ -22494,7 +22494,7 @@
         <v>46274.36695243056</v>
       </c>
       <c r="W281">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X281" t="s">
         <v>192</v>
@@ -22568,7 +22568,7 @@
         <v>46276.4084265625</v>
       </c>
       <c r="W282">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X282" t="s">
         <v>194</v>
@@ -22645,7 +22645,7 @@
         <v>46274.7274781713</v>
       </c>
       <c r="W283">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X283" t="s">
         <v>195</v>
@@ -22719,7 +22719,7 @@
         <v>46274.74558746528</v>
       </c>
       <c r="W284">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X284" t="s">
         <v>195</v>
@@ -22793,7 +22793,7 @@
         <v>46275.79245582176</v>
       </c>
       <c r="W285">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X285" t="s">
         <v>193</v>
@@ -22867,7 +22867,7 @@
         <v>46280.63707425926</v>
       </c>
       <c r="W286">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X286" t="s">
         <v>192</v>
@@ -22944,7 +22944,7 @@
         <v>46280.38311703704</v>
       </c>
       <c r="W287">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X287" t="s">
         <v>194</v>
@@ -23024,7 +23024,7 @@
         <v>46280.37743127315</v>
       </c>
       <c r="W288">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X288" t="s">
         <v>193</v>
@@ -23104,7 +23104,7 @@
         <v>46280.45035295139</v>
       </c>
       <c r="W289">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X289" t="s">
         <v>198</v>
@@ -23181,7 +23181,7 @@
         <v>46280.59788275463</v>
       </c>
       <c r="W290">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="X290" t="s">
         <v>198</v>
@@ -23261,7 +23261,7 @@
         <v>46280.73313407407</v>
       </c>
       <c r="W291">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X291" t="s">
         <v>196</v>
@@ -23338,7 +23338,7 @@
         <v>46276.49596842592</v>
       </c>
       <c r="W292">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X292" t="s">
         <v>197</v>
@@ -23412,7 +23412,7 @@
         <v>46276.53874935185</v>
       </c>
       <c r="W293">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X293" t="s">
         <v>201</v>
@@ -23486,7 +23486,7 @@
         <v>46276.49597027778</v>
       </c>
       <c r="W294">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X294" t="s">
         <v>198</v>
@@ -23560,7 +23560,7 @@
         <v>46276.62604146991</v>
       </c>
       <c r="W295">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X295" t="s">
         <v>200</v>
@@ -23634,7 +23634,7 @@
         <v>46276.68231165509</v>
       </c>
       <c r="W296">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X296" t="s">
         <v>196</v>
@@ -23711,7 +23711,7 @@
         <v>46276.7163278588</v>
       </c>
       <c r="W297">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X297" t="s">
         <v>196</v>
@@ -23788,7 +23788,7 @@
         <v>46276.6823121412</v>
       </c>
       <c r="W298">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X298" t="s">
         <v>196</v>
@@ -23865,7 +23865,7 @@
         <v>46280.69323744213</v>
       </c>
       <c r="W299">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X299" t="s">
         <v>197</v>
@@ -23942,7 +23942,7 @@
         <v>46274.70622837963</v>
       </c>
       <c r="W300">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X300" t="s">
         <v>201</v>
@@ -24016,7 +24016,7 @@
         <v>46275.71996309028</v>
       </c>
       <c r="W301">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X301" t="s">
         <v>200</v>
@@ -24090,7 +24090,7 @@
         <v>46275.54278886574</v>
       </c>
       <c r="W302">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X302" t="s">
         <v>196</v>
@@ -24167,7 +24167,7 @@
         <v>46280.74859975695</v>
       </c>
       <c r="W303">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="X303" t="s">
         <v>197</v>
@@ -24244,7 +24244,7 @@
         <v>46275.7000328588</v>
       </c>
       <c r="W304">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X304" t="s">
         <v>201</v>
@@ -24318,7 +24318,7 @@
         <v>46275.72031699074</v>
       </c>
       <c r="W305">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X305" t="s">
         <v>198</v>
@@ -24392,7 +24392,7 @@
         <v>46275.54095912037</v>
       </c>
       <c r="W306">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X306" t="s">
         <v>200</v>
@@ -24466,7 +24466,7 @@
         <v>46275.72225363426</v>
       </c>
       <c r="W307">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X307" t="s">
         <v>196</v>
@@ -24540,7 +24540,7 @@
         <v>46275.7222629051</v>
       </c>
       <c r="W308">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X308" t="s">
         <v>196</v>
@@ -24614,7 +24614,7 @@
         <v>46275.7222709838</v>
       </c>
       <c r="W309">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X309" t="s">
         <v>196</v>
@@ -24691,7 +24691,7 @@
         <v>46274.74837762731</v>
       </c>
       <c r="W310">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X310" t="s">
         <v>197</v>
@@ -24771,7 +24771,7 @@
         <v>46274.74838096065</v>
       </c>
       <c r="W311">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X311" t="s">
         <v>200</v>
@@ -24851,7 +24851,7 @@
         <v>46280.56274502315</v>
       </c>
       <c r="W312">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X312" t="s">
         <v>196</v>
@@ -24928,7 +24928,7 @@
         <v>46274.42878043981</v>
       </c>
       <c r="W313">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X313" t="s">
         <v>197</v>
@@ -25005,7 +25005,7 @@
         <v>46275.40196778935</v>
       </c>
       <c r="W314">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X314" t="s">
         <v>198</v>
@@ -25082,7 +25082,7 @@
         <v>46276.52399603009</v>
       </c>
       <c r="W315">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X315" t="s">
         <v>200</v>
@@ -25159,7 +25159,7 @@
         <v>46276.5240703125</v>
       </c>
       <c r="W316">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X316" t="s">
         <v>196</v>
@@ -25233,7 +25233,7 @@
         <v>46275.4100730787</v>
       </c>
       <c r="W317">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X317" t="s">
         <v>193</v>
@@ -25307,7 +25307,7 @@
         <v>46275.40964188657</v>
       </c>
       <c r="W318">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X318" t="s">
         <v>195</v>
@@ -25381,7 +25381,7 @@
         <v>46275.40964245371</v>
       </c>
       <c r="W319">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X319" t="s">
         <v>195</v>
@@ -25455,7 +25455,7 @@
         <v>46275.45011145833</v>
       </c>
       <c r="W320">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X320" t="s">
         <v>191</v>
@@ -25529,7 +25529,7 @@
         <v>46275.44901016204</v>
       </c>
       <c r="W321">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X321" t="s">
         <v>192</v>
@@ -25603,7 +25603,7 @@
         <v>46276.71732053241</v>
       </c>
       <c r="W322">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X322" t="s">
         <v>200</v>
@@ -25680,7 +25680,7 @@
         <v>46276.71697232639</v>
       </c>
       <c r="W323">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X323" t="s">
         <v>196</v>
@@ -25757,7 +25757,7 @@
         <v>46276.7175884838</v>
       </c>
       <c r="W324">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X324" t="s">
         <v>196</v>
@@ -25834,7 +25834,7 @@
         <v>46276.7175895949</v>
       </c>
       <c r="W325">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X325" t="s">
         <v>196</v>
@@ -25911,7 +25911,7 @@
         <v>46276.71759461806</v>
       </c>
       <c r="W326">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X326" t="s">
         <v>194</v>
@@ -25985,7 +25985,7 @@
         <v>46275.44975668981</v>
       </c>
       <c r="W327">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X327" t="s">
         <v>193</v>
@@ -26059,7 +26059,7 @@
         <v>46275.44933692129</v>
       </c>
       <c r="W328">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X328" t="s">
         <v>195</v>
@@ -26133,7 +26133,7 @@
         <v>46275.44933814815</v>
       </c>
       <c r="W329">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X329" t="s">
         <v>195</v>
@@ -26207,7 +26207,7 @@
         <v>46274.41771849537</v>
       </c>
       <c r="W330">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X330" t="s">
         <v>200</v>
@@ -26278,7 +26278,7 @@
         <v>46274.41775447917</v>
       </c>
       <c r="W331">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X331" t="s">
         <v>196</v>
@@ -26349,7 +26349,7 @@
         <v>46274.41777533565</v>
       </c>
       <c r="W332">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X332" t="s">
         <v>196</v>
@@ -26420,7 +26420,7 @@
         <v>46274.41799166667</v>
       </c>
       <c r="W333">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X333" t="s">
         <v>194</v>
@@ -26491,7 +26491,7 @@
         <v>46274.41800114583</v>
       </c>
       <c r="W334">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X334" t="s">
         <v>193</v>
@@ -26562,7 +26562,7 @@
         <v>46274.41772148148</v>
       </c>
       <c r="W335">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X335" t="s">
         <v>200</v>
@@ -26633,7 +26633,7 @@
         <v>46274.41773631945</v>
       </c>
       <c r="W336">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X336" t="s">
         <v>196</v>
@@ -26704,7 +26704,7 @@
         <v>46274.41777481481</v>
       </c>
       <c r="W337">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X337" t="s">
         <v>196</v>
@@ -26775,7 +26775,7 @@
         <v>46274.41799332176</v>
       </c>
       <c r="W338">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X338" t="s">
         <v>194</v>
@@ -26846,7 +26846,7 @@
         <v>46274.41800085648</v>
       </c>
       <c r="W339">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X339" t="s">
         <v>193</v>
@@ -26917,7 +26917,7 @@
         <v>46275.31737530093</v>
       </c>
       <c r="W340">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X340" t="s">
         <v>197</v>
@@ -26988,7 +26988,7 @@
         <v>46275.31747032407</v>
       </c>
       <c r="W341">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X341" t="s">
         <v>201</v>
@@ -27059,7 +27059,7 @@
         <v>46275.31747981482</v>
       </c>
       <c r="W342">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X342" t="s">
         <v>198</v>
@@ -27130,7 +27130,7 @@
         <v>46275.31748724537</v>
       </c>
       <c r="W343">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X343" t="s">
         <v>191</v>
@@ -27201,7 +27201,7 @@
         <v>46275.31749535879</v>
       </c>
       <c r="W344">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X344" t="s">
         <v>192</v>
@@ -27272,7 +27272,7 @@
         <v>46275.31750491898</v>
       </c>
       <c r="W345">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X345" t="s">
         <v>200</v>
@@ -27343,7 +27343,7 @@
         <v>46275.31750555555</v>
       </c>
       <c r="W346">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X346" t="s">
         <v>196</v>
@@ -27414,7 +27414,7 @@
         <v>46275.31750599537</v>
       </c>
       <c r="W347">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X347" t="s">
         <v>196</v>
@@ -27485,7 +27485,7 @@
         <v>46275.5810894676</v>
       </c>
       <c r="W348">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X348" t="s">
         <v>197</v>
@@ -27559,7 +27559,7 @@
         <v>46275.58158541666</v>
       </c>
       <c r="W349">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X349" t="s">
         <v>198</v>
@@ -27633,7 +27633,7 @@
         <v>46279.70955146991</v>
       </c>
       <c r="W350">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="X350" t="s">
         <v>197</v>
@@ -27707,7 +27707,7 @@
         <v>46276.41675075232</v>
       </c>
       <c r="W351">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X351" t="s">
         <v>192</v>

--- a/data/base/goias.xlsx
+++ b/data/base/goias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5544" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5558" uniqueCount="353">
   <si>
     <t>CodCliente</t>
   </si>
@@ -1437,7 +1437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AI385"/>
+  <dimension ref="A1:AI386"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:35">
@@ -27761,16 +27761,16 @@
     </row>
     <row r="352" spans="1:35">
       <c r="A352">
-        <v>6703</v>
+        <v>6548</v>
       </c>
       <c r="B352" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="C352" t="s">
         <v>50</v>
       </c>
       <c r="D352" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E352" t="s">
         <v>54</v>
@@ -27779,13 +27779,13 @@
         <v>56</v>
       </c>
       <c r="G352">
-        <v>1628</v>
+        <v>1697</v>
       </c>
       <c r="H352">
-        <v>1581</v>
+        <v>1650</v>
       </c>
       <c r="I352" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J352" t="s">
         <v>75</v>
@@ -27800,31 +27800,31 @@
         <v>2026</v>
       </c>
       <c r="R352">
-        <v>17955176</v>
+        <v>17968001</v>
       </c>
       <c r="S352" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="T352" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="U352" t="s">
         <v>193</v>
       </c>
       <c r="V352" s="1">
-        <v>46282.42251184028</v>
+        <v>46282.62254486111</v>
       </c>
       <c r="W352">
         <v>-4</v>
       </c>
       <c r="X352" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="AB352">
         <v>0</v>
       </c>
       <c r="AC352" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="AH352" t="s">
         <v>347</v>
@@ -27835,16 +27835,16 @@
     </row>
     <row r="353" spans="1:35">
       <c r="A353">
-        <v>5417</v>
+        <v>6703</v>
       </c>
       <c r="B353" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C353" t="s">
         <v>50</v>
       </c>
       <c r="D353" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E353" t="s">
         <v>54</v>
@@ -27853,49 +27853,52 @@
         <v>56</v>
       </c>
       <c r="G353">
-        <v>5883</v>
+        <v>1628</v>
       </c>
       <c r="H353">
-        <v>5792</v>
+        <v>1581</v>
       </c>
       <c r="I353" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J353" t="s">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="N353" s="1">
         <v>46286</v>
       </c>
       <c r="P353">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q353">
         <v>2026</v>
       </c>
       <c r="R353">
-        <v>17399067</v>
+        <v>17955176</v>
       </c>
       <c r="S353" t="s">
-        <v>171</v>
+        <v>165</v>
+      </c>
+      <c r="T353" t="s">
+        <v>186</v>
       </c>
       <c r="U353" t="s">
         <v>193</v>
       </c>
       <c r="V353" s="1">
-        <v>46282.47420876157</v>
+        <v>46282.42251184028</v>
       </c>
       <c r="W353">
         <v>-4</v>
       </c>
       <c r="X353" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="AB353">
         <v>0</v>
       </c>
       <c r="AC353" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="AH353" t="s">
         <v>347</v>
@@ -27924,7 +27927,7 @@
         <v>56</v>
       </c>
       <c r="G354">
-        <v>5884</v>
+        <v>5883</v>
       </c>
       <c r="H354">
         <v>5792</v>
@@ -27933,7 +27936,7 @@
         <v>61</v>
       </c>
       <c r="J354" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N354" s="1">
         <v>46286</v>
@@ -27945,7 +27948,7 @@
         <v>2026</v>
       </c>
       <c r="R354">
-        <v>17399077</v>
+        <v>17399067</v>
       </c>
       <c r="S354" t="s">
         <v>171</v>
@@ -27954,7 +27957,7 @@
         <v>193</v>
       </c>
       <c r="V354" s="1">
-        <v>46282.47437324074</v>
+        <v>46282.47420876157</v>
       </c>
       <c r="W354">
         <v>-4</v>
@@ -27977,16 +27980,16 @@
     </row>
     <row r="355" spans="1:35">
       <c r="A355">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B355" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C355" t="s">
         <v>50</v>
       </c>
       <c r="D355" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E355" t="s">
         <v>54</v>
@@ -27995,23 +27998,20 @@
         <v>56</v>
       </c>
       <c r="G355">
-        <v>5903</v>
+        <v>5884</v>
       </c>
       <c r="H355">
-        <v>5830</v>
+        <v>5792</v>
       </c>
       <c r="I355" t="s">
         <v>61</v>
       </c>
       <c r="J355" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="N355" s="1">
         <v>46286</v>
       </c>
-      <c r="O355" t="s">
-        <v>154</v>
-      </c>
       <c r="P355">
         <v>9</v>
       </c>
@@ -28019,34 +28019,28 @@
         <v>2026</v>
       </c>
       <c r="R355">
-        <v>16962221</v>
+        <v>17399077</v>
       </c>
       <c r="S355" t="s">
-        <v>172</v>
-      </c>
-      <c r="T355" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="U355" t="s">
         <v>193</v>
       </c>
       <c r="V355" s="1">
-        <v>46282.42048836806</v>
+        <v>46282.47437324074</v>
       </c>
       <c r="W355">
         <v>-4</v>
       </c>
       <c r="X355" t="s">
-        <v>205</v>
-      </c>
-      <c r="Y355" t="s">
-        <v>337</v>
+        <v>201</v>
       </c>
       <c r="AB355">
         <v>0</v>
       </c>
       <c r="AC355" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AH355" t="s">
         <v>347</v>
@@ -28075,20 +28069,23 @@
         <v>56</v>
       </c>
       <c r="G356">
+        <v>5903</v>
+      </c>
+      <c r="H356">
         <v>5830</v>
-      </c>
-      <c r="H356">
-        <v>5784</v>
       </c>
       <c r="I356" t="s">
         <v>61</v>
       </c>
       <c r="J356" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="N356" s="1">
         <v>46286</v>
       </c>
+      <c r="O356" t="s">
+        <v>154</v>
+      </c>
       <c r="P356">
         <v>9</v>
       </c>
@@ -28096,7 +28093,7 @@
         <v>2026</v>
       </c>
       <c r="R356">
-        <v>16962211</v>
+        <v>16962221</v>
       </c>
       <c r="S356" t="s">
         <v>172</v>
@@ -28108,13 +28105,16 @@
         <v>193</v>
       </c>
       <c r="V356" s="1">
-        <v>46282.42138976852</v>
+        <v>46282.42048836806</v>
       </c>
       <c r="W356">
         <v>-4</v>
       </c>
       <c r="X356" t="s">
         <v>205</v>
+      </c>
+      <c r="Y356" t="s">
+        <v>337</v>
       </c>
       <c r="AB356">
         <v>0</v>
@@ -28149,55 +28149,52 @@
         <v>56</v>
       </c>
       <c r="G357">
-        <v>7025</v>
+        <v>5830</v>
       </c>
       <c r="H357">
-        <v>0</v>
+        <v>5784</v>
       </c>
       <c r="I357" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J357" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="N357" s="1">
-        <v>46288</v>
+        <v>46286</v>
       </c>
       <c r="P357">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q357">
         <v>2026</v>
       </c>
       <c r="R357">
-        <v>16962338</v>
+        <v>16962211</v>
       </c>
       <c r="S357" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="T357" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="U357" t="s">
         <v>193</v>
       </c>
       <c r="V357" s="1">
-        <v>46282.54038741898</v>
+        <v>46282.42138976852</v>
       </c>
       <c r="W357">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="X357" t="s">
         <v>205</v>
       </c>
-      <c r="Y357" t="s">
-        <v>338</v>
-      </c>
       <c r="AB357">
         <v>0</v>
       </c>
       <c r="AC357" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="AH357" t="s">
         <v>347</v>
@@ -28208,16 +28205,16 @@
     </row>
     <row r="358" spans="1:35">
       <c r="A358">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B358" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C358" t="s">
         <v>50</v>
       </c>
       <c r="D358" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E358" t="s">
         <v>54</v>
@@ -28226,58 +28223,58 @@
         <v>56</v>
       </c>
       <c r="G358">
-        <v>9086</v>
+        <v>7025</v>
       </c>
       <c r="H358">
         <v>0</v>
       </c>
       <c r="I358" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J358" t="s">
-        <v>144</v>
+        <v>121</v>
       </c>
       <c r="N358" s="1">
-        <v>46282</v>
-      </c>
-      <c r="O358" t="s">
-        <v>155</v>
+        <v>46288</v>
       </c>
       <c r="P358">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q358">
         <v>2026</v>
       </c>
       <c r="R358">
-        <v>17399363</v>
+        <v>16962338</v>
       </c>
       <c r="S358" t="s">
-        <v>181</v>
+        <v>180</v>
+      </c>
+      <c r="T358" t="s">
+        <v>191</v>
       </c>
       <c r="U358" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="V358" s="1">
-        <v>46282.36440621527</v>
+        <v>46282.54038741898</v>
       </c>
       <c r="W358">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="X358" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="Y358" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AB358">
         <v>0</v>
       </c>
       <c r="AC358" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AH358" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="AI358" t="s">
         <v>352</v>
@@ -28285,16 +28282,16 @@
     </row>
     <row r="359" spans="1:35">
       <c r="A359">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B359" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C359" t="s">
         <v>50</v>
       </c>
       <c r="D359" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E359" t="s">
         <v>54</v>
@@ -28327,7 +28324,7 @@
         <v>2026</v>
       </c>
       <c r="R359">
-        <v>16962380</v>
+        <v>17399363</v>
       </c>
       <c r="S359" t="s">
         <v>181</v>
@@ -28336,13 +28333,13 @@
         <v>194</v>
       </c>
       <c r="V359" s="1">
-        <v>46282.36462596065</v>
+        <v>46282.36440621527</v>
       </c>
       <c r="W359">
         <v>0</v>
       </c>
       <c r="X359" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="Y359" t="s">
         <v>339</v>
@@ -28362,16 +28359,16 @@
     </row>
     <row r="360" spans="1:35">
       <c r="A360">
-        <v>6486</v>
+        <v>6404</v>
       </c>
       <c r="B360" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C360" t="s">
         <v>50</v>
       </c>
       <c r="D360" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E360" t="s">
         <v>54</v>
@@ -28404,7 +28401,7 @@
         <v>2026</v>
       </c>
       <c r="R360">
-        <v>16976270</v>
+        <v>16962380</v>
       </c>
       <c r="S360" t="s">
         <v>181</v>
@@ -28413,13 +28410,13 @@
         <v>194</v>
       </c>
       <c r="V360" s="1">
-        <v>46282.36464421296</v>
+        <v>46282.36462596065</v>
       </c>
       <c r="W360">
         <v>0</v>
       </c>
       <c r="X360" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Y360" t="s">
         <v>339</v>
@@ -28439,10 +28436,10 @@
     </row>
     <row r="361" spans="1:35">
       <c r="A361">
-        <v>6548</v>
+        <v>6486</v>
       </c>
       <c r="B361" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C361" t="s">
         <v>50</v>
@@ -28481,7 +28478,7 @@
         <v>2026</v>
       </c>
       <c r="R361">
-        <v>17222865</v>
+        <v>16976270</v>
       </c>
       <c r="S361" t="s">
         <v>181</v>
@@ -28490,13 +28487,13 @@
         <v>194</v>
       </c>
       <c r="V361" s="1">
-        <v>46282.36467337963</v>
+        <v>46282.36464421296</v>
       </c>
       <c r="W361">
         <v>0</v>
       </c>
       <c r="X361" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="Y361" t="s">
         <v>339</v>
@@ -28516,10 +28513,10 @@
     </row>
     <row r="362" spans="1:35">
       <c r="A362">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B362" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C362" t="s">
         <v>50</v>
@@ -28528,7 +28525,7 @@
         <v>51</v>
       </c>
       <c r="E362" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F362" t="s">
         <v>56</v>
@@ -28558,7 +28555,7 @@
         <v>2026</v>
       </c>
       <c r="R362">
-        <v>17042587</v>
+        <v>17222865</v>
       </c>
       <c r="S362" t="s">
         <v>181</v>
@@ -28567,13 +28564,13 @@
         <v>194</v>
       </c>
       <c r="V362" s="1">
-        <v>46282.36469679398</v>
+        <v>46282.36467337963</v>
       </c>
       <c r="W362">
         <v>0</v>
       </c>
       <c r="X362" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Y362" t="s">
         <v>339</v>
@@ -28593,16 +28590,16 @@
     </row>
     <row r="363" spans="1:35">
       <c r="A363">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B363" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C363" t="s">
         <v>50</v>
       </c>
       <c r="D363" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E363" t="s">
         <v>55</v>
@@ -28635,7 +28632,7 @@
         <v>2026</v>
       </c>
       <c r="R363">
-        <v>16960074</v>
+        <v>17042587</v>
       </c>
       <c r="S363" t="s">
         <v>181</v>
@@ -28644,7 +28641,7 @@
         <v>194</v>
       </c>
       <c r="V363" s="1">
-        <v>46282.36469869213</v>
+        <v>46282.36469679398</v>
       </c>
       <c r="W363">
         <v>0</v>
@@ -28670,19 +28667,19 @@
     </row>
     <row r="364" spans="1:35">
       <c r="A364">
-        <v>6703</v>
+        <v>6628</v>
       </c>
       <c r="B364" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C364" t="s">
         <v>50</v>
       </c>
       <c r="D364" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E364" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F364" t="s">
         <v>56</v>
@@ -28712,7 +28709,7 @@
         <v>2026</v>
       </c>
       <c r="R364">
-        <v>17941217</v>
+        <v>16960074</v>
       </c>
       <c r="S364" t="s">
         <v>181</v>
@@ -28721,13 +28718,13 @@
         <v>194</v>
       </c>
       <c r="V364" s="1">
-        <v>46282.36473159722</v>
+        <v>46282.36469869213</v>
       </c>
       <c r="W364">
         <v>0</v>
       </c>
       <c r="X364" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="Y364" t="s">
         <v>339</v>
@@ -28747,16 +28744,16 @@
     </row>
     <row r="365" spans="1:35">
       <c r="A365">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B365" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C365" t="s">
         <v>50</v>
       </c>
       <c r="D365" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E365" t="s">
         <v>54</v>
@@ -28789,7 +28786,7 @@
         <v>2026</v>
       </c>
       <c r="R365">
-        <v>17952444</v>
+        <v>17941217</v>
       </c>
       <c r="S365" t="s">
         <v>181</v>
@@ -28798,13 +28795,13 @@
         <v>194</v>
       </c>
       <c r="V365" s="1">
-        <v>46282.36473394676</v>
+        <v>46282.36473159722</v>
       </c>
       <c r="W365">
         <v>0</v>
       </c>
       <c r="X365" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="Y365" t="s">
         <v>339</v>
@@ -28824,16 +28821,16 @@
     </row>
     <row r="366" spans="1:35">
       <c r="A366">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B366" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C366" t="s">
         <v>50</v>
       </c>
       <c r="D366" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E366" t="s">
         <v>54</v>
@@ -28866,7 +28863,7 @@
         <v>2026</v>
       </c>
       <c r="R366">
-        <v>17952624</v>
+        <v>17952444</v>
       </c>
       <c r="S366" t="s">
         <v>181</v>
@@ -28875,7 +28872,7 @@
         <v>194</v>
       </c>
       <c r="V366" s="1">
-        <v>46282.36473579861</v>
+        <v>46282.36473394676</v>
       </c>
       <c r="W366">
         <v>0</v>
@@ -28901,10 +28898,10 @@
     </row>
     <row r="367" spans="1:35">
       <c r="A367">
-        <v>6779</v>
+        <v>6705</v>
       </c>
       <c r="B367" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C367" t="s">
         <v>50</v>
@@ -28943,7 +28940,7 @@
         <v>2026</v>
       </c>
       <c r="R367">
-        <v>18056801</v>
+        <v>17952624</v>
       </c>
       <c r="S367" t="s">
         <v>181</v>
@@ -28952,7 +28949,7 @@
         <v>194</v>
       </c>
       <c r="V367" s="1">
-        <v>46282.36475297454</v>
+        <v>46282.36473579861</v>
       </c>
       <c r="W367">
         <v>0</v>
@@ -28978,10 +28975,10 @@
     </row>
     <row r="368" spans="1:35">
       <c r="A368">
-        <v>6945</v>
+        <v>6779</v>
       </c>
       <c r="B368" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C368" t="s">
         <v>50</v>
@@ -28993,7 +28990,7 @@
         <v>54</v>
       </c>
       <c r="F368" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G368">
         <v>9086</v>
@@ -29020,7 +29017,7 @@
         <v>2026</v>
       </c>
       <c r="R368">
-        <v>18164551</v>
+        <v>18056801</v>
       </c>
       <c r="S368" t="s">
         <v>181</v>
@@ -29029,13 +29026,13 @@
         <v>194</v>
       </c>
       <c r="V368" s="1">
-        <v>46282.36486408565</v>
+        <v>46282.36475297454</v>
       </c>
       <c r="W368">
         <v>0</v>
       </c>
       <c r="X368" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Y368" t="s">
         <v>339</v>
@@ -29055,16 +29052,16 @@
     </row>
     <row r="369" spans="1:35">
       <c r="A369">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B369" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C369" t="s">
         <v>50</v>
       </c>
       <c r="D369" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E369" t="s">
         <v>54</v>
@@ -29097,7 +29094,7 @@
         <v>2026</v>
       </c>
       <c r="R369">
-        <v>18178187</v>
+        <v>18164551</v>
       </c>
       <c r="S369" t="s">
         <v>181</v>
@@ -29106,16 +29103,16 @@
         <v>194</v>
       </c>
       <c r="V369" s="1">
-        <v>46282.36487561343</v>
+        <v>46282.36486408565</v>
       </c>
       <c r="W369">
         <v>0</v>
       </c>
       <c r="X369" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Y369" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AB369">
         <v>0</v>
@@ -29132,16 +29129,16 @@
     </row>
     <row r="370" spans="1:35">
       <c r="A370">
-        <v>6962</v>
+        <v>6949</v>
       </c>
       <c r="B370" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C370" t="s">
         <v>50</v>
       </c>
       <c r="D370" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E370" t="s">
         <v>54</v>
@@ -29174,7 +29171,7 @@
         <v>2026</v>
       </c>
       <c r="R370">
-        <v>18188774</v>
+        <v>18178187</v>
       </c>
       <c r="S370" t="s">
         <v>181</v>
@@ -29183,16 +29180,16 @@
         <v>194</v>
       </c>
       <c r="V370" s="1">
-        <v>46282.36486778935</v>
+        <v>46282.36487561343</v>
       </c>
       <c r="W370">
         <v>0</v>
       </c>
       <c r="X370" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="Y370" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AB370">
         <v>0</v>
@@ -29209,10 +29206,10 @@
     </row>
     <row r="371" spans="1:35">
       <c r="A371">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B371" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C371" t="s">
         <v>50</v>
@@ -29251,7 +29248,7 @@
         <v>2026</v>
       </c>
       <c r="R371">
-        <v>18188680</v>
+        <v>18188774</v>
       </c>
       <c r="S371" t="s">
         <v>181</v>
@@ -29260,7 +29257,7 @@
         <v>194</v>
       </c>
       <c r="V371" s="1">
-        <v>46282.36486851852</v>
+        <v>46282.36486778935</v>
       </c>
       <c r="W371">
         <v>0</v>
@@ -29286,40 +29283,40 @@
     </row>
     <row r="372" spans="1:35">
       <c r="A372">
-        <v>5417</v>
+        <v>6963</v>
       </c>
       <c r="B372" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C372" t="s">
         <v>50</v>
       </c>
       <c r="D372" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E372" t="s">
         <v>54</v>
       </c>
       <c r="F372" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G372">
-        <v>9088</v>
+        <v>9086</v>
       </c>
       <c r="H372">
         <v>0</v>
       </c>
       <c r="I372" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J372" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N372" s="1">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="O372" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P372">
         <v>9</v>
@@ -29328,31 +29325,31 @@
         <v>2026</v>
       </c>
       <c r="R372">
-        <v>17399383</v>
+        <v>18188680</v>
       </c>
       <c r="S372" t="s">
-        <v>54</v>
+        <v>181</v>
       </c>
       <c r="U372" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="V372" s="1">
-        <v>46282.3651903588</v>
+        <v>46282.36486851852</v>
       </c>
       <c r="W372">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X372" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="Y372" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AB372">
         <v>0</v>
       </c>
       <c r="AC372" t="s">
-        <v>54</v>
+        <v>181</v>
       </c>
       <c r="AH372" t="s">
         <v>349</v>
@@ -29363,16 +29360,16 @@
     </row>
     <row r="373" spans="1:35">
       <c r="A373">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B373" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C373" t="s">
         <v>50</v>
       </c>
       <c r="D373" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E373" t="s">
         <v>54</v>
@@ -29405,7 +29402,7 @@
         <v>2026</v>
       </c>
       <c r="R373">
-        <v>16962400</v>
+        <v>17399383</v>
       </c>
       <c r="S373" t="s">
         <v>54</v>
@@ -29414,13 +29411,13 @@
         <v>193</v>
       </c>
       <c r="V373" s="1">
-        <v>46282.36525856482</v>
+        <v>46282.3651903588</v>
       </c>
       <c r="W373">
         <v>-1</v>
       </c>
       <c r="X373" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="Y373" t="s">
         <v>341</v>
@@ -29440,16 +29437,16 @@
     </row>
     <row r="374" spans="1:35">
       <c r="A374">
-        <v>6486</v>
+        <v>6404</v>
       </c>
       <c r="B374" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C374" t="s">
         <v>50</v>
       </c>
       <c r="D374" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E374" t="s">
         <v>54</v>
@@ -29482,7 +29479,7 @@
         <v>2026</v>
       </c>
       <c r="R374">
-        <v>16976290</v>
+        <v>16962400</v>
       </c>
       <c r="S374" t="s">
         <v>54</v>
@@ -29491,13 +29488,13 @@
         <v>193</v>
       </c>
       <c r="V374" s="1">
-        <v>46282.36526855324</v>
+        <v>46282.36525856482</v>
       </c>
       <c r="W374">
         <v>-1</v>
       </c>
       <c r="X374" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Y374" t="s">
         <v>341</v>
@@ -29517,10 +29514,10 @@
     </row>
     <row r="375" spans="1:35">
       <c r="A375">
-        <v>6548</v>
+        <v>6486</v>
       </c>
       <c r="B375" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C375" t="s">
         <v>50</v>
@@ -29559,7 +29556,7 @@
         <v>2026</v>
       </c>
       <c r="R375">
-        <v>17222899</v>
+        <v>16976290</v>
       </c>
       <c r="S375" t="s">
         <v>54</v>
@@ -29568,13 +29565,13 @@
         <v>193</v>
       </c>
       <c r="V375" s="1">
-        <v>46282.36527959491</v>
+        <v>46282.36526855324</v>
       </c>
       <c r="W375">
         <v>-1</v>
       </c>
       <c r="X375" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="Y375" t="s">
         <v>341</v>
@@ -29594,10 +29591,10 @@
     </row>
     <row r="376" spans="1:35">
       <c r="A376">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B376" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C376" t="s">
         <v>50</v>
@@ -29606,7 +29603,7 @@
         <v>51</v>
       </c>
       <c r="E376" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F376" t="s">
         <v>56</v>
@@ -29636,22 +29633,22 @@
         <v>2026</v>
       </c>
       <c r="R376">
-        <v>17042627</v>
+        <v>17222899</v>
       </c>
       <c r="S376" t="s">
-        <v>182</v>
+        <v>54</v>
       </c>
       <c r="U376" t="s">
         <v>193</v>
       </c>
       <c r="V376" s="1">
-        <v>46282.36528526621</v>
+        <v>46282.36527959491</v>
       </c>
       <c r="W376">
         <v>-1</v>
       </c>
       <c r="X376" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Y376" t="s">
         <v>341</v>
@@ -29660,7 +29657,7 @@
         <v>0</v>
       </c>
       <c r="AC376" t="s">
-        <v>182</v>
+        <v>54</v>
       </c>
       <c r="AH376" t="s">
         <v>349</v>
@@ -29671,16 +29668,16 @@
     </row>
     <row r="377" spans="1:35">
       <c r="A377">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B377" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C377" t="s">
         <v>50</v>
       </c>
       <c r="D377" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E377" t="s">
         <v>55</v>
@@ -29713,16 +29710,16 @@
         <v>2026</v>
       </c>
       <c r="R377">
-        <v>16960098</v>
+        <v>17042627</v>
       </c>
       <c r="S377" t="s">
-        <v>55</v>
+        <v>182</v>
       </c>
       <c r="U377" t="s">
         <v>193</v>
       </c>
       <c r="V377" s="1">
-        <v>46282.36528619213</v>
+        <v>46282.36528526621</v>
       </c>
       <c r="W377">
         <v>-1</v>
@@ -29737,7 +29734,7 @@
         <v>0</v>
       </c>
       <c r="AC377" t="s">
-        <v>55</v>
+        <v>182</v>
       </c>
       <c r="AH377" t="s">
         <v>349</v>
@@ -29748,19 +29745,19 @@
     </row>
     <row r="378" spans="1:35">
       <c r="A378">
-        <v>6703</v>
+        <v>6628</v>
       </c>
       <c r="B378" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C378" t="s">
         <v>50</v>
       </c>
       <c r="D378" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E378" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F378" t="s">
         <v>56</v>
@@ -29790,22 +29787,22 @@
         <v>2026</v>
       </c>
       <c r="R378">
-        <v>17941237</v>
+        <v>16960098</v>
       </c>
       <c r="S378" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="U378" t="s">
         <v>193</v>
       </c>
       <c r="V378" s="1">
-        <v>46282.36529351852</v>
+        <v>46282.36528619213</v>
       </c>
       <c r="W378">
         <v>-1</v>
       </c>
       <c r="X378" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="Y378" t="s">
         <v>341</v>
@@ -29814,7 +29811,7 @@
         <v>0</v>
       </c>
       <c r="AC378" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AH378" t="s">
         <v>349</v>
@@ -29825,16 +29822,16 @@
     </row>
     <row r="379" spans="1:35">
       <c r="A379">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B379" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C379" t="s">
         <v>50</v>
       </c>
       <c r="D379" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E379" t="s">
         <v>54</v>
@@ -29867,7 +29864,7 @@
         <v>2026</v>
       </c>
       <c r="R379">
-        <v>17952466</v>
+        <v>17941237</v>
       </c>
       <c r="S379" t="s">
         <v>54</v>
@@ -29876,13 +29873,13 @@
         <v>193</v>
       </c>
       <c r="V379" s="1">
-        <v>46282.36529424768</v>
+        <v>46282.36529351852</v>
       </c>
       <c r="W379">
         <v>-1</v>
       </c>
       <c r="X379" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="Y379" t="s">
         <v>341</v>
@@ -29902,16 +29899,16 @@
     </row>
     <row r="380" spans="1:35">
       <c r="A380">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B380" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C380" t="s">
         <v>50</v>
       </c>
       <c r="D380" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E380" t="s">
         <v>54</v>
@@ -29944,7 +29941,7 @@
         <v>2026</v>
       </c>
       <c r="R380">
-        <v>17952646</v>
+        <v>17952466</v>
       </c>
       <c r="S380" t="s">
         <v>54</v>
@@ -29953,7 +29950,7 @@
         <v>193</v>
       </c>
       <c r="V380" s="1">
-        <v>46282.36529490741</v>
+        <v>46282.36529424768</v>
       </c>
       <c r="W380">
         <v>-1</v>
@@ -29979,10 +29976,10 @@
     </row>
     <row r="381" spans="1:35">
       <c r="A381">
-        <v>6779</v>
+        <v>6705</v>
       </c>
       <c r="B381" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C381" t="s">
         <v>50</v>
@@ -30021,16 +30018,16 @@
         <v>2026</v>
       </c>
       <c r="R381">
-        <v>18056821</v>
+        <v>17952646</v>
       </c>
       <c r="S381" t="s">
-        <v>182</v>
+        <v>54</v>
       </c>
       <c r="U381" t="s">
         <v>193</v>
       </c>
       <c r="V381" s="1">
-        <v>46282.36529869213</v>
+        <v>46282.36529490741</v>
       </c>
       <c r="W381">
         <v>-1</v>
@@ -30045,7 +30042,7 @@
         <v>0</v>
       </c>
       <c r="AC381" t="s">
-        <v>182</v>
+        <v>54</v>
       </c>
       <c r="AH381" t="s">
         <v>349</v>
@@ -30056,10 +30053,10 @@
     </row>
     <row r="382" spans="1:35">
       <c r="A382">
-        <v>6945</v>
+        <v>6779</v>
       </c>
       <c r="B382" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C382" t="s">
         <v>50</v>
@@ -30071,7 +30068,7 @@
         <v>54</v>
       </c>
       <c r="F382" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G382">
         <v>9088</v>
@@ -30098,22 +30095,22 @@
         <v>2026</v>
       </c>
       <c r="R382">
-        <v>18164565</v>
+        <v>18056821</v>
       </c>
       <c r="S382" t="s">
-        <v>54</v>
+        <v>182</v>
       </c>
       <c r="U382" t="s">
         <v>193</v>
       </c>
       <c r="V382" s="1">
-        <v>46282.36531149306</v>
+        <v>46282.36529869213</v>
       </c>
       <c r="W382">
         <v>-1</v>
       </c>
       <c r="X382" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Y382" t="s">
         <v>341</v>
@@ -30122,7 +30119,7 @@
         <v>0</v>
       </c>
       <c r="AC382" t="s">
-        <v>54</v>
+        <v>182</v>
       </c>
       <c r="AH382" t="s">
         <v>349</v>
@@ -30133,16 +30130,16 @@
     </row>
     <row r="383" spans="1:35">
       <c r="A383">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B383" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C383" t="s">
         <v>50</v>
       </c>
       <c r="D383" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E383" t="s">
         <v>54</v>
@@ -30175,31 +30172,31 @@
         <v>2026</v>
       </c>
       <c r="R383">
-        <v>18178199</v>
+        <v>18164565</v>
       </c>
       <c r="S383" t="s">
-        <v>182</v>
+        <v>54</v>
       </c>
       <c r="U383" t="s">
         <v>193</v>
       </c>
       <c r="V383" s="1">
-        <v>46282.36531554398</v>
+        <v>46282.36531149306</v>
       </c>
       <c r="W383">
         <v>-1</v>
       </c>
       <c r="X383" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Y383" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AB383">
         <v>0</v>
       </c>
       <c r="AC383" t="s">
-        <v>182</v>
+        <v>54</v>
       </c>
       <c r="AH383" t="s">
         <v>349</v>
@@ -30210,16 +30207,16 @@
     </row>
     <row r="384" spans="1:35">
       <c r="A384">
-        <v>6962</v>
+        <v>6949</v>
       </c>
       <c r="B384" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C384" t="s">
         <v>50</v>
       </c>
       <c r="D384" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E384" t="s">
         <v>54</v>
@@ -30252,31 +30249,31 @@
         <v>2026</v>
       </c>
       <c r="R384">
-        <v>18188788</v>
+        <v>18178199</v>
       </c>
       <c r="S384" t="s">
-        <v>54</v>
+        <v>182</v>
       </c>
       <c r="U384" t="s">
         <v>193</v>
       </c>
       <c r="V384" s="1">
-        <v>46282.36531253472</v>
+        <v>46282.36531554398</v>
       </c>
       <c r="W384">
         <v>-1</v>
       </c>
       <c r="X384" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="Y384" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AB384">
         <v>0</v>
       </c>
       <c r="AC384" t="s">
-        <v>54</v>
+        <v>182</v>
       </c>
       <c r="AH384" t="s">
         <v>349</v>
@@ -30287,10 +30284,10 @@
     </row>
     <row r="385" spans="1:35">
       <c r="A385">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B385" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C385" t="s">
         <v>50</v>
@@ -30329,7 +30326,7 @@
         <v>2026</v>
       </c>
       <c r="R385">
-        <v>18188694</v>
+        <v>18188788</v>
       </c>
       <c r="S385" t="s">
         <v>54</v>
@@ -30338,7 +30335,7 @@
         <v>193</v>
       </c>
       <c r="V385" s="1">
-        <v>46282.36531288194</v>
+        <v>46282.36531253472</v>
       </c>
       <c r="W385">
         <v>-1</v>
@@ -30359,6 +30356,83 @@
         <v>349</v>
       </c>
       <c r="AI385" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="386" spans="1:35">
+      <c r="A386">
+        <v>6963</v>
+      </c>
+      <c r="B386" t="s">
+        <v>41</v>
+      </c>
+      <c r="C386" t="s">
+        <v>50</v>
+      </c>
+      <c r="D386" t="s">
+        <v>53</v>
+      </c>
+      <c r="E386" t="s">
+        <v>54</v>
+      </c>
+      <c r="F386" t="s">
+        <v>57</v>
+      </c>
+      <c r="G386">
+        <v>9088</v>
+      </c>
+      <c r="H386">
+        <v>0</v>
+      </c>
+      <c r="I386" t="s">
+        <v>65</v>
+      </c>
+      <c r="J386" t="s">
+        <v>145</v>
+      </c>
+      <c r="N386" s="1">
+        <v>46283</v>
+      </c>
+      <c r="O386" t="s">
+        <v>154</v>
+      </c>
+      <c r="P386">
+        <v>9</v>
+      </c>
+      <c r="Q386">
+        <v>2026</v>
+      </c>
+      <c r="R386">
+        <v>18188694</v>
+      </c>
+      <c r="S386" t="s">
+        <v>54</v>
+      </c>
+      <c r="U386" t="s">
+        <v>193</v>
+      </c>
+      <c r="V386" s="1">
+        <v>46282.36531288194</v>
+      </c>
+      <c r="W386">
+        <v>-1</v>
+      </c>
+      <c r="X386" t="s">
+        <v>199</v>
+      </c>
+      <c r="Y386" t="s">
+        <v>341</v>
+      </c>
+      <c r="AB386">
+        <v>0</v>
+      </c>
+      <c r="AC386" t="s">
+        <v>54</v>
+      </c>
+      <c r="AH386" t="s">
+        <v>349</v>
+      </c>
+      <c r="AI386" t="s">
         <v>352</v>
       </c>
     </row>

--- a/data/base/goias.xlsx
+++ b/data/base/goias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5558" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5572" uniqueCount="354">
   <si>
     <t>CodCliente</t>
   </si>
@@ -1072,6 +1072,9 @@
   </si>
   <si>
     <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 18/09/2026 - Em andamento - Data Comentário: 15/09/2026 09:29</t>
+  </si>
+  <si>
+    <t>Baixado via API integração MGC x Sistema de Analise Fiscal em 17/09/2026 15:25:25. - Data Comentário: 17/09/2026 15:20</t>
   </si>
   <si>
     <t>Karen Ribeiro</t>
@@ -1437,7 +1440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AI386"/>
+  <dimension ref="A1:AI387"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:35">
@@ -1618,10 +1621,10 @@
         <v>159</v>
       </c>
       <c r="AH2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="3" spans="1:35">
@@ -1695,10 +1698,10 @@
         <v>160</v>
       </c>
       <c r="AH3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI3" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="4" spans="1:35">
@@ -1772,10 +1775,10 @@
         <v>159</v>
       </c>
       <c r="AH4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="5" spans="1:35">
@@ -1846,10 +1849,10 @@
         <v>159</v>
       </c>
       <c r="AH5" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="6" spans="1:35">
@@ -1920,10 +1923,10 @@
         <v>160</v>
       </c>
       <c r="AH6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="7" spans="1:35">
@@ -1994,10 +1997,10 @@
         <v>160</v>
       </c>
       <c r="AH7" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI7" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="8" spans="1:35">
@@ -2068,10 +2071,10 @@
         <v>161</v>
       </c>
       <c r="AH8" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI8" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="9" spans="1:35">
@@ -2142,10 +2145,10 @@
         <v>159</v>
       </c>
       <c r="AH9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI9" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="10" spans="1:35">
@@ -2216,10 +2219,10 @@
         <v>162</v>
       </c>
       <c r="AH10" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="11" spans="1:35">
@@ -2290,10 +2293,10 @@
         <v>162</v>
       </c>
       <c r="AH11" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI11" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="12" spans="1:35">
@@ -2364,10 +2367,10 @@
         <v>163</v>
       </c>
       <c r="AH12" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI12" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="13" spans="1:35">
@@ -2435,13 +2438,13 @@
         <v>0</v>
       </c>
       <c r="AC13" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AH13" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI13" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="14" spans="1:35">
@@ -2509,13 +2512,13 @@
         <v>0</v>
       </c>
       <c r="AC14" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AH14" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI14" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="15" spans="1:35">
@@ -2583,10 +2586,10 @@
         <v>0</v>
       </c>
       <c r="AH15" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI15" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="16" spans="1:35">
@@ -2648,10 +2651,10 @@
         <v>0</v>
       </c>
       <c r="AH16" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI16" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="17" spans="1:35">
@@ -2719,10 +2722,10 @@
         <v>0</v>
       </c>
       <c r="AH17" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI17" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="18" spans="1:35">
@@ -2796,10 +2799,10 @@
         <v>165</v>
       </c>
       <c r="AH18" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI18" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="19" spans="1:35">
@@ -2873,10 +2876,10 @@
         <v>164</v>
       </c>
       <c r="AH19" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI19" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="20" spans="1:35">
@@ -2950,10 +2953,10 @@
         <v>165</v>
       </c>
       <c r="AH20" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI20" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="21" spans="1:35">
@@ -3027,10 +3030,10 @@
         <v>163</v>
       </c>
       <c r="AH21" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI21" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="22" spans="1:35">
@@ -3101,10 +3104,10 @@
         <v>166</v>
       </c>
       <c r="AH22" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI22" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="23" spans="1:35">
@@ -3175,10 +3178,10 @@
         <v>163</v>
       </c>
       <c r="AH23" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI23" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="24" spans="1:35">
@@ -3249,10 +3252,10 @@
         <v>163</v>
       </c>
       <c r="AH24" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI24" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="25" spans="1:35">
@@ -3323,10 +3326,10 @@
         <v>163</v>
       </c>
       <c r="AH25" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI25" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="26" spans="1:35">
@@ -3397,10 +3400,10 @@
         <v>164</v>
       </c>
       <c r="AH26" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI26" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="27" spans="1:35">
@@ -3471,10 +3474,10 @@
         <v>163</v>
       </c>
       <c r="AH27" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI27" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="28" spans="1:35">
@@ -3545,10 +3548,10 @@
         <v>163</v>
       </c>
       <c r="AH28" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI28" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="29" spans="1:35">
@@ -3619,10 +3622,10 @@
         <v>163</v>
       </c>
       <c r="AH29" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI29" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="30" spans="1:35">
@@ -3693,10 +3696,10 @@
         <v>167</v>
       </c>
       <c r="AH30" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI30" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="31" spans="1:35">
@@ -3773,10 +3776,10 @@
         <v>168</v>
       </c>
       <c r="AH31" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI31" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="32" spans="1:35">
@@ -3847,10 +3850,10 @@
         <v>169</v>
       </c>
       <c r="AH32" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI32" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="33" spans="1:35">
@@ -3927,10 +3930,10 @@
         <v>170</v>
       </c>
       <c r="AH33" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI33" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="34" spans="1:35">
@@ -4004,10 +4007,10 @@
         <v>171</v>
       </c>
       <c r="AH34" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI34" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="35" spans="1:35">
@@ -4081,13 +4084,13 @@
         <v>0</v>
       </c>
       <c r="AC35" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AH35" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI35" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="36" spans="1:35">
@@ -4164,10 +4167,10 @@
         <v>173</v>
       </c>
       <c r="AH36" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI36" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="37" spans="1:35">
@@ -4244,10 +4247,10 @@
         <v>167</v>
       </c>
       <c r="AH37" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI37" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="38" spans="1:35">
@@ -4321,10 +4324,10 @@
         <v>189</v>
       </c>
       <c r="AH38" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI38" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="39" spans="1:35">
@@ -4401,10 +4404,10 @@
         <v>168</v>
       </c>
       <c r="AH39" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI39" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="40" spans="1:35">
@@ -4481,10 +4484,10 @@
         <v>168</v>
       </c>
       <c r="AH40" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI40" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="41" spans="1:35">
@@ -4561,10 +4564,10 @@
         <v>168</v>
       </c>
       <c r="AH41" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI41" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="42" spans="1:35">
@@ -4641,10 +4644,10 @@
         <v>167</v>
       </c>
       <c r="AH42" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI42" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="43" spans="1:35">
@@ -4721,10 +4724,10 @@
         <v>174</v>
       </c>
       <c r="AH43" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI43" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="44" spans="1:35">
@@ -4801,10 +4804,10 @@
         <v>169</v>
       </c>
       <c r="AH44" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI44" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="45" spans="1:35">
@@ -4881,10 +4884,10 @@
         <v>170</v>
       </c>
       <c r="AH45" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI45" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="46" spans="1:35">
@@ -4952,10 +4955,10 @@
         <v>171</v>
       </c>
       <c r="AH46" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI46" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="47" spans="1:35">
@@ -5026,10 +5029,10 @@
         <v>168</v>
       </c>
       <c r="AH47" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI47" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="48" spans="1:35">
@@ -5100,10 +5103,10 @@
         <v>168</v>
       </c>
       <c r="AH48" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI48" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="49" spans="1:35">
@@ -5174,10 +5177,10 @@
         <v>168</v>
       </c>
       <c r="AH49" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI49" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="50" spans="1:35">
@@ -5248,10 +5251,10 @@
         <v>167</v>
       </c>
       <c r="AH50" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI50" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="51" spans="1:35">
@@ -5322,10 +5325,10 @@
         <v>174</v>
       </c>
       <c r="AH51" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI51" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="52" spans="1:35">
@@ -5402,10 +5405,10 @@
         <v>169</v>
       </c>
       <c r="AH52" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI52" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="53" spans="1:35">
@@ -5476,10 +5479,10 @@
         <v>170</v>
       </c>
       <c r="AH53" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI53" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="54" spans="1:35">
@@ -5556,10 +5559,10 @@
         <v>168</v>
       </c>
       <c r="AH54" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI54" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="55" spans="1:35">
@@ -5636,10 +5639,10 @@
         <v>168</v>
       </c>
       <c r="AH55" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI55" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="56" spans="1:35">
@@ -5716,10 +5719,10 @@
         <v>168</v>
       </c>
       <c r="AH56" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI56" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="57" spans="1:35">
@@ -5796,10 +5799,10 @@
         <v>167</v>
       </c>
       <c r="AH57" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI57" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="58" spans="1:35">
@@ -5873,10 +5876,10 @@
         <v>171</v>
       </c>
       <c r="AH58" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI58" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="59" spans="1:35">
@@ -5950,13 +5953,13 @@
         <v>0</v>
       </c>
       <c r="AC59" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AH59" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI59" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="60" spans="1:35">
@@ -6033,10 +6036,10 @@
         <v>168</v>
       </c>
       <c r="AH60" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI60" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="61" spans="1:35">
@@ -6113,10 +6116,10 @@
         <v>168</v>
       </c>
       <c r="AH61" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI61" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="62" spans="1:35">
@@ -6193,10 +6196,10 @@
         <v>168</v>
       </c>
       <c r="AH62" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI62" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="63" spans="1:35">
@@ -6273,10 +6276,10 @@
         <v>167</v>
       </c>
       <c r="AH63" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI63" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="64" spans="1:35">
@@ -6353,10 +6356,10 @@
         <v>174</v>
       </c>
       <c r="AH64" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI64" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="65" spans="1:35">
@@ -6433,10 +6436,10 @@
         <v>169</v>
       </c>
       <c r="AH65" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI65" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="66" spans="1:35">
@@ -6513,10 +6516,10 @@
         <v>170</v>
       </c>
       <c r="AH66" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI66" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="67" spans="1:35">
@@ -6593,10 +6596,10 @@
         <v>168</v>
       </c>
       <c r="AH67" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI67" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="68" spans="1:35">
@@ -6664,10 +6667,10 @@
         <v>171</v>
       </c>
       <c r="AH68" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI68" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="69" spans="1:35">
@@ -6735,13 +6738,13 @@
         <v>0</v>
       </c>
       <c r="AC69" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AH69" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI69" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="70" spans="1:35">
@@ -6812,10 +6815,10 @@
         <v>168</v>
       </c>
       <c r="AH70" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI70" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="71" spans="1:35">
@@ -6886,10 +6889,10 @@
         <v>168</v>
       </c>
       <c r="AH71" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI71" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="72" spans="1:35">
@@ -6960,10 +6963,10 @@
         <v>168</v>
       </c>
       <c r="AH72" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI72" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="73" spans="1:35">
@@ -7034,10 +7037,10 @@
         <v>167</v>
       </c>
       <c r="AH73" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI73" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="74" spans="1:35">
@@ -7108,10 +7111,10 @@
         <v>174</v>
       </c>
       <c r="AH74" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI74" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="75" spans="1:35">
@@ -7182,10 +7185,10 @@
         <v>169</v>
       </c>
       <c r="AH75" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI75" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="76" spans="1:35">
@@ -7256,10 +7259,10 @@
         <v>170</v>
       </c>
       <c r="AH76" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI76" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="77" spans="1:35">
@@ -7330,10 +7333,10 @@
         <v>170</v>
       </c>
       <c r="AH77" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI77" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="78" spans="1:35">
@@ -7404,10 +7407,10 @@
         <v>170</v>
       </c>
       <c r="AH78" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI78" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="79" spans="1:35">
@@ -7478,10 +7481,10 @@
         <v>170</v>
       </c>
       <c r="AH79" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI79" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="80" spans="1:35">
@@ -7552,10 +7555,10 @@
         <v>190</v>
       </c>
       <c r="AH80" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI80" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="81" spans="1:35">
@@ -7623,10 +7626,10 @@
         <v>190</v>
       </c>
       <c r="AH81" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI81" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="82" spans="1:35">
@@ -7697,10 +7700,10 @@
         <v>177</v>
       </c>
       <c r="AH82" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI82" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="83" spans="1:35">
@@ -7771,10 +7774,10 @@
         <v>190</v>
       </c>
       <c r="AH83" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI83" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="84" spans="1:35">
@@ -7842,10 +7845,10 @@
         <v>190</v>
       </c>
       <c r="AH84" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI84" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="85" spans="1:35">
@@ -7916,10 +7919,10 @@
         <v>190</v>
       </c>
       <c r="AH85" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI85" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:35">
@@ -7984,10 +7987,10 @@
         <v>177</v>
       </c>
       <c r="AH86" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI86" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:35">
@@ -8058,10 +8061,10 @@
         <v>190</v>
       </c>
       <c r="AH87" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI87" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="88" spans="1:35">
@@ -8129,10 +8132,10 @@
         <v>190</v>
       </c>
       <c r="AH88" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI88" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="89" spans="1:35">
@@ -8203,10 +8206,10 @@
         <v>190</v>
       </c>
       <c r="AH89" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI89" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="90" spans="1:35">
@@ -8271,10 +8274,10 @@
         <v>190</v>
       </c>
       <c r="AH90" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI90" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="91" spans="1:35">
@@ -8339,10 +8342,10 @@
         <v>177</v>
       </c>
       <c r="AH91" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI91" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="92" spans="1:35">
@@ -8413,10 +8416,10 @@
         <v>190</v>
       </c>
       <c r="AH92" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI92" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="93" spans="1:35">
@@ -8484,10 +8487,10 @@
         <v>190</v>
       </c>
       <c r="AH93" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI93" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="94" spans="1:35">
@@ -8558,10 +8561,10 @@
         <v>190</v>
       </c>
       <c r="AH94" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI94" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="95" spans="1:35">
@@ -8626,10 +8629,10 @@
         <v>190</v>
       </c>
       <c r="AH95" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI95" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="96" spans="1:35">
@@ -8694,10 +8697,10 @@
         <v>177</v>
       </c>
       <c r="AH96" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI96" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="97" spans="1:35">
@@ -8768,10 +8771,10 @@
         <v>190</v>
       </c>
       <c r="AH97" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI97" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="98" spans="1:35">
@@ -8839,10 +8842,10 @@
         <v>190</v>
       </c>
       <c r="AH98" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI98" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="99" spans="1:35">
@@ -8913,10 +8916,10 @@
         <v>177</v>
       </c>
       <c r="AH99" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI99" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="100" spans="1:35">
@@ -8993,10 +8996,10 @@
         <v>190</v>
       </c>
       <c r="AH100" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI100" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="101" spans="1:35">
@@ -9064,10 +9067,10 @@
         <v>190</v>
       </c>
       <c r="AH101" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI101" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="102" spans="1:35">
@@ -9138,10 +9141,10 @@
         <v>190</v>
       </c>
       <c r="AH102" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI102" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="103" spans="1:35">
@@ -9209,10 +9212,10 @@
         <v>190</v>
       </c>
       <c r="AH103" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI103" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="104" spans="1:35">
@@ -9283,10 +9286,10 @@
         <v>190</v>
       </c>
       <c r="AH104" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI104" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="105" spans="1:35">
@@ -9351,10 +9354,10 @@
         <v>190</v>
       </c>
       <c r="AH105" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI105" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="106" spans="1:35">
@@ -9419,10 +9422,10 @@
         <v>177</v>
       </c>
       <c r="AH106" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI106" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="107" spans="1:35">
@@ -9493,10 +9496,10 @@
         <v>190</v>
       </c>
       <c r="AH107" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI107" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="108" spans="1:35">
@@ -9567,10 +9570,10 @@
         <v>190</v>
       </c>
       <c r="AH108" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI108" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="109" spans="1:35">
@@ -9638,10 +9641,10 @@
         <v>190</v>
       </c>
       <c r="AH109" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI109" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="110" spans="1:35">
@@ -9712,10 +9715,10 @@
         <v>177</v>
       </c>
       <c r="AH110" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI110" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="111" spans="1:35">
@@ -9783,10 +9786,10 @@
         <v>176</v>
       </c>
       <c r="AH111" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI111" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="112" spans="1:35">
@@ -9857,10 +9860,10 @@
         <v>177</v>
       </c>
       <c r="AH112" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI112" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="113" spans="1:35">
@@ -9931,10 +9934,10 @@
         <v>175</v>
       </c>
       <c r="AH113" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI113" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="114" spans="1:35">
@@ -10002,10 +10005,10 @@
         <v>176</v>
       </c>
       <c r="AH114" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI114" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="115" spans="1:35">
@@ -10076,10 +10079,10 @@
         <v>177</v>
       </c>
       <c r="AH115" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI115" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="116" spans="1:35">
@@ -10150,10 +10153,10 @@
         <v>190</v>
       </c>
       <c r="AH116" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI116" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="117" spans="1:35">
@@ -10221,10 +10224,10 @@
         <v>190</v>
       </c>
       <c r="AH117" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI117" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="118" spans="1:35">
@@ -10295,10 +10298,10 @@
         <v>190</v>
       </c>
       <c r="AH118" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI118" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="119" spans="1:35">
@@ -10363,10 +10366,10 @@
         <v>190</v>
       </c>
       <c r="AH119" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI119" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="120" spans="1:35">
@@ -10431,10 +10434,10 @@
         <v>177</v>
       </c>
       <c r="AH120" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI120" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="121" spans="1:35">
@@ -10505,10 +10508,10 @@
         <v>190</v>
       </c>
       <c r="AH121" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI121" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="122" spans="1:35">
@@ -10576,10 +10579,10 @@
         <v>190</v>
       </c>
       <c r="AH122" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI122" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="123" spans="1:35">
@@ -10650,10 +10653,10 @@
         <v>190</v>
       </c>
       <c r="AH123" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI123" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="124" spans="1:35">
@@ -10718,10 +10721,10 @@
         <v>190</v>
       </c>
       <c r="AH124" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI124" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="125" spans="1:35">
@@ -10786,10 +10789,10 @@
         <v>177</v>
       </c>
       <c r="AH125" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI125" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="126" spans="1:35">
@@ -10866,10 +10869,10 @@
         <v>177</v>
       </c>
       <c r="AH126" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI126" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="127" spans="1:35">
@@ -10946,10 +10949,10 @@
         <v>177</v>
       </c>
       <c r="AH127" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI127" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="128" spans="1:35">
@@ -11020,10 +11023,10 @@
         <v>180</v>
       </c>
       <c r="AH128" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI128" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="129" spans="1:35">
@@ -11094,10 +11097,10 @@
         <v>180</v>
       </c>
       <c r="AH129" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI129" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="130" spans="1:35">
@@ -11174,10 +11177,10 @@
         <v>180</v>
       </c>
       <c r="AH130" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI130" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="131" spans="1:35">
@@ -11248,10 +11251,10 @@
         <v>180</v>
       </c>
       <c r="AH131" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI131" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="132" spans="1:35">
@@ -11322,10 +11325,10 @@
         <v>180</v>
       </c>
       <c r="AH132" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI132" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="133" spans="1:35">
@@ -11396,10 +11399,10 @@
         <v>180</v>
       </c>
       <c r="AH133" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI133" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="134" spans="1:35">
@@ -11470,10 +11473,10 @@
         <v>180</v>
       </c>
       <c r="AH134" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI134" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="135" spans="1:35">
@@ -11550,10 +11553,10 @@
         <v>180</v>
       </c>
       <c r="AH135" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI135" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="136" spans="1:35">
@@ -11624,10 +11627,10 @@
         <v>180</v>
       </c>
       <c r="AH136" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI136" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="137" spans="1:35">
@@ -11698,10 +11701,10 @@
         <v>180</v>
       </c>
       <c r="AH137" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI137" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="138" spans="1:35">
@@ -11772,10 +11775,10 @@
         <v>180</v>
       </c>
       <c r="AH138" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI138" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="139" spans="1:35">
@@ -11852,10 +11855,10 @@
         <v>180</v>
       </c>
       <c r="AH139" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI139" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="140" spans="1:35">
@@ -11926,10 +11929,10 @@
         <v>180</v>
       </c>
       <c r="AH140" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI140" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="141" spans="1:35">
@@ -12000,10 +12003,10 @@
         <v>180</v>
       </c>
       <c r="AH141" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI141" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="142" spans="1:35">
@@ -12074,10 +12077,10 @@
         <v>180</v>
       </c>
       <c r="AH142" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI142" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="143" spans="1:35">
@@ -12148,10 +12151,10 @@
         <v>180</v>
       </c>
       <c r="AH143" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI143" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="144" spans="1:35">
@@ -12222,10 +12225,10 @@
         <v>180</v>
       </c>
       <c r="AH144" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI144" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="145" spans="1:35">
@@ -12296,10 +12299,10 @@
         <v>180</v>
       </c>
       <c r="AH145" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI145" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="146" spans="1:35">
@@ -12370,10 +12373,10 @@
         <v>180</v>
       </c>
       <c r="AH146" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI146" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="147" spans="1:35">
@@ -12444,10 +12447,10 @@
         <v>180</v>
       </c>
       <c r="AH147" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI147" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="148" spans="1:35">
@@ -12518,10 +12521,10 @@
         <v>180</v>
       </c>
       <c r="AH148" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI148" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="149" spans="1:35">
@@ -12592,10 +12595,10 @@
         <v>180</v>
       </c>
       <c r="AH149" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI149" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="150" spans="1:35">
@@ -12672,10 +12675,10 @@
         <v>180</v>
       </c>
       <c r="AH150" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI150" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="151" spans="1:35">
@@ -12746,10 +12749,10 @@
         <v>180</v>
       </c>
       <c r="AH151" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI151" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="152" spans="1:35">
@@ -12820,10 +12823,10 @@
         <v>180</v>
       </c>
       <c r="AH152" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI152" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="153" spans="1:35">
@@ -12894,10 +12897,10 @@
         <v>180</v>
       </c>
       <c r="AH153" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI153" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="154" spans="1:35">
@@ -12968,10 +12971,10 @@
         <v>181</v>
       </c>
       <c r="AH154" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI154" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="155" spans="1:35">
@@ -13042,10 +13045,10 @@
         <v>181</v>
       </c>
       <c r="AH155" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI155" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="156" spans="1:35">
@@ -13116,10 +13119,10 @@
         <v>181</v>
       </c>
       <c r="AH156" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI156" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="157" spans="1:35">
@@ -13190,10 +13193,10 @@
         <v>181</v>
       </c>
       <c r="AH157" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI157" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="158" spans="1:35">
@@ -13264,10 +13267,10 @@
         <v>181</v>
       </c>
       <c r="AH158" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI158" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="159" spans="1:35">
@@ -13338,10 +13341,10 @@
         <v>181</v>
       </c>
       <c r="AH159" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI159" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="160" spans="1:35">
@@ -13412,10 +13415,10 @@
         <v>181</v>
       </c>
       <c r="AH160" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI160" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="161" spans="1:35">
@@ -13486,10 +13489,10 @@
         <v>181</v>
       </c>
       <c r="AH161" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI161" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="162" spans="1:35">
@@ -13560,10 +13563,10 @@
         <v>181</v>
       </c>
       <c r="AH162" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI162" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="163" spans="1:35">
@@ -13634,10 +13637,10 @@
         <v>181</v>
       </c>
       <c r="AH163" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI163" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="164" spans="1:35">
@@ -13708,10 +13711,10 @@
         <v>181</v>
       </c>
       <c r="AH164" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI164" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="165" spans="1:35">
@@ -13782,10 +13785,10 @@
         <v>181</v>
       </c>
       <c r="AH165" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI165" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="166" spans="1:35">
@@ -13856,10 +13859,10 @@
         <v>181</v>
       </c>
       <c r="AH166" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI166" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="167" spans="1:35">
@@ -13930,10 +13933,10 @@
         <v>181</v>
       </c>
       <c r="AH167" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI167" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="168" spans="1:35">
@@ -14004,10 +14007,10 @@
         <v>181</v>
       </c>
       <c r="AH168" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI168" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="169" spans="1:35">
@@ -14081,10 +14084,10 @@
         <v>181</v>
       </c>
       <c r="AH169" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI169" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="170" spans="1:35">
@@ -14158,10 +14161,10 @@
         <v>181</v>
       </c>
       <c r="AH170" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI170" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="171" spans="1:35">
@@ -14235,10 +14238,10 @@
         <v>181</v>
       </c>
       <c r="AH171" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI171" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="172" spans="1:35">
@@ -14312,10 +14315,10 @@
         <v>181</v>
       </c>
       <c r="AH172" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI172" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="173" spans="1:35">
@@ -14389,10 +14392,10 @@
         <v>181</v>
       </c>
       <c r="AH173" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI173" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="174" spans="1:35">
@@ -14466,10 +14469,10 @@
         <v>181</v>
       </c>
       <c r="AH174" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI174" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="175" spans="1:35">
@@ -14543,10 +14546,10 @@
         <v>181</v>
       </c>
       <c r="AH175" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI175" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="176" spans="1:35">
@@ -14620,10 +14623,10 @@
         <v>181</v>
       </c>
       <c r="AH176" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI176" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="177" spans="1:35">
@@ -14697,10 +14700,10 @@
         <v>181</v>
       </c>
       <c r="AH177" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI177" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="178" spans="1:35">
@@ -14774,10 +14777,10 @@
         <v>181</v>
       </c>
       <c r="AH178" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI178" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="179" spans="1:35">
@@ -14851,10 +14854,10 @@
         <v>181</v>
       </c>
       <c r="AH179" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI179" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="180" spans="1:35">
@@ -14928,10 +14931,10 @@
         <v>181</v>
       </c>
       <c r="AH180" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI180" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="181" spans="1:35">
@@ -15005,10 +15008,10 @@
         <v>181</v>
       </c>
       <c r="AH181" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI181" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="182" spans="1:35">
@@ -15082,10 +15085,10 @@
         <v>181</v>
       </c>
       <c r="AH182" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI182" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="183" spans="1:35">
@@ -15153,10 +15156,10 @@
         <v>181</v>
       </c>
       <c r="AH183" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI183" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="184" spans="1:35">
@@ -15224,10 +15227,10 @@
         <v>181</v>
       </c>
       <c r="AH184" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI184" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="185" spans="1:35">
@@ -15295,10 +15298,10 @@
         <v>181</v>
       </c>
       <c r="AH185" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI185" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="186" spans="1:35">
@@ -15366,10 +15369,10 @@
         <v>181</v>
       </c>
       <c r="AH186" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI186" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="187" spans="1:35">
@@ -15437,10 +15440,10 @@
         <v>181</v>
       </c>
       <c r="AH187" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI187" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="188" spans="1:35">
@@ -15508,10 +15511,10 @@
         <v>181</v>
       </c>
       <c r="AH188" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI188" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="189" spans="1:35">
@@ -15579,10 +15582,10 @@
         <v>54</v>
       </c>
       <c r="AH189" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI189" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="190" spans="1:35">
@@ -15650,10 +15653,10 @@
         <v>54</v>
       </c>
       <c r="AH190" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI190" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="191" spans="1:35">
@@ -15721,10 +15724,10 @@
         <v>54</v>
       </c>
       <c r="AH191" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI191" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="192" spans="1:35">
@@ -15792,10 +15795,10 @@
         <v>54</v>
       </c>
       <c r="AH192" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI192" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="193" spans="1:35">
@@ -15863,10 +15866,10 @@
         <v>182</v>
       </c>
       <c r="AH193" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI193" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="194" spans="1:35">
@@ -15934,10 +15937,10 @@
         <v>55</v>
       </c>
       <c r="AH194" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI194" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="195" spans="1:35">
@@ -16005,10 +16008,10 @@
         <v>54</v>
       </c>
       <c r="AH195" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI195" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="196" spans="1:35">
@@ -16076,10 +16079,10 @@
         <v>54</v>
       </c>
       <c r="AH196" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI196" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="197" spans="1:35">
@@ -16147,10 +16150,10 @@
         <v>54</v>
       </c>
       <c r="AH197" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI197" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="198" spans="1:35">
@@ -16218,10 +16221,10 @@
         <v>182</v>
       </c>
       <c r="AH198" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI198" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="199" spans="1:35">
@@ -16289,10 +16292,10 @@
         <v>54</v>
       </c>
       <c r="AH199" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI199" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="200" spans="1:35">
@@ -16360,10 +16363,10 @@
         <v>182</v>
       </c>
       <c r="AH200" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI200" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="201" spans="1:35">
@@ -16431,10 +16434,10 @@
         <v>54</v>
       </c>
       <c r="AH201" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI201" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="202" spans="1:35">
@@ -16502,10 +16505,10 @@
         <v>54</v>
       </c>
       <c r="AH202" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI202" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="203" spans="1:35">
@@ -16573,10 +16576,10 @@
         <v>54</v>
       </c>
       <c r="AH203" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI203" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="204" spans="1:35">
@@ -16644,10 +16647,10 @@
         <v>54</v>
       </c>
       <c r="AH204" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI204" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="205" spans="1:35">
@@ -16715,10 +16718,10 @@
         <v>54</v>
       </c>
       <c r="AH205" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI205" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="206" spans="1:35">
@@ -16786,10 +16789,10 @@
         <v>54</v>
       </c>
       <c r="AH206" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI206" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="207" spans="1:35">
@@ -16857,10 +16860,10 @@
         <v>182</v>
       </c>
       <c r="AH207" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI207" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="208" spans="1:35">
@@ -16928,10 +16931,10 @@
         <v>55</v>
       </c>
       <c r="AH208" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI208" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="209" spans="1:35">
@@ -17002,10 +17005,10 @@
         <v>54</v>
       </c>
       <c r="AH209" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI209" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="210" spans="1:35">
@@ -17076,10 +17079,10 @@
         <v>54</v>
       </c>
       <c r="AH210" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI210" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="211" spans="1:35">
@@ -17150,10 +17153,10 @@
         <v>54</v>
       </c>
       <c r="AH211" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI211" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="212" spans="1:35">
@@ -17224,10 +17227,10 @@
         <v>54</v>
       </c>
       <c r="AH212" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI212" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="213" spans="1:35">
@@ -17295,10 +17298,10 @@
         <v>54</v>
       </c>
       <c r="AH213" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI213" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="214" spans="1:35">
@@ -17366,10 +17369,10 @@
         <v>54</v>
       </c>
       <c r="AH214" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI214" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="215" spans="1:35">
@@ -17434,10 +17437,10 @@
         <v>0</v>
       </c>
       <c r="AH215" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI215" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="216" spans="1:35">
@@ -17499,10 +17502,10 @@
         <v>0</v>
       </c>
       <c r="AH216" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI216" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="217" spans="1:35">
@@ -17570,13 +17573,13 @@
         <v>0</v>
       </c>
       <c r="AC217" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AH217" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI217" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="218" spans="1:35">
@@ -17647,10 +17650,10 @@
         <v>164</v>
       </c>
       <c r="AH218" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI218" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="219" spans="1:35">
@@ -17727,10 +17730,10 @@
         <v>168</v>
       </c>
       <c r="AH219" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI219" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="220" spans="1:35">
@@ -17807,10 +17810,10 @@
         <v>168</v>
       </c>
       <c r="AH220" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI220" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="221" spans="1:35">
@@ -17887,10 +17890,10 @@
         <v>169</v>
       </c>
       <c r="AH221" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI221" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="222" spans="1:35">
@@ -17967,10 +17970,10 @@
         <v>174</v>
       </c>
       <c r="AH222" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI222" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="223" spans="1:35">
@@ -18047,10 +18050,10 @@
         <v>168</v>
       </c>
       <c r="AH223" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI223" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="224" spans="1:35">
@@ -18127,10 +18130,10 @@
         <v>173</v>
       </c>
       <c r="AH224" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI224" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="225" spans="1:35">
@@ -18207,10 +18210,10 @@
         <v>168</v>
       </c>
       <c r="AH225" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI225" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="226" spans="1:35">
@@ -18287,10 +18290,10 @@
         <v>168</v>
       </c>
       <c r="AH226" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI226" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="227" spans="1:35">
@@ -18361,10 +18364,10 @@
         <v>167</v>
       </c>
       <c r="AH227" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI227" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="228" spans="1:35">
@@ -18435,10 +18438,10 @@
         <v>174</v>
       </c>
       <c r="AH228" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI228" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="229" spans="1:35">
@@ -18515,10 +18518,10 @@
         <v>168</v>
       </c>
       <c r="AH229" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI229" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="230" spans="1:35">
@@ -18595,10 +18598,10 @@
         <v>173</v>
       </c>
       <c r="AH230" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI230" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="231" spans="1:35">
@@ -18675,10 +18678,10 @@
         <v>168</v>
       </c>
       <c r="AH231" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI231" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="232" spans="1:35">
@@ -18755,10 +18758,10 @@
         <v>168</v>
       </c>
       <c r="AH232" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI232" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="233" spans="1:35">
@@ -18829,10 +18832,10 @@
         <v>167</v>
       </c>
       <c r="AH233" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI233" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="234" spans="1:35">
@@ -18903,10 +18906,10 @@
         <v>174</v>
       </c>
       <c r="AH234" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI234" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="235" spans="1:35">
@@ -18977,10 +18980,10 @@
         <v>171</v>
       </c>
       <c r="AH235" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI235" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="236" spans="1:35">
@@ -19054,10 +19057,10 @@
         <v>172</v>
       </c>
       <c r="AH236" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI236" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="237" spans="1:35">
@@ -19131,10 +19134,10 @@
         <v>168</v>
       </c>
       <c r="AH237" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI237" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="238" spans="1:35">
@@ -19208,10 +19211,10 @@
         <v>173</v>
       </c>
       <c r="AH238" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI238" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="239" spans="1:35">
@@ -19285,10 +19288,10 @@
         <v>168</v>
       </c>
       <c r="AH239" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI239" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="240" spans="1:35">
@@ -19362,10 +19365,10 @@
         <v>168</v>
       </c>
       <c r="AH240" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI240" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="241" spans="1:35">
@@ -19442,10 +19445,10 @@
         <v>167</v>
       </c>
       <c r="AH241" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI241" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="242" spans="1:35">
@@ -19519,10 +19522,10 @@
         <v>174</v>
       </c>
       <c r="AH242" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI242" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="243" spans="1:35">
@@ -19596,10 +19599,10 @@
         <v>169</v>
       </c>
       <c r="AH243" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI243" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="244" spans="1:35">
@@ -19673,10 +19676,10 @@
         <v>170</v>
       </c>
       <c r="AH244" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI244" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="245" spans="1:35">
@@ -19750,10 +19753,10 @@
         <v>171</v>
       </c>
       <c r="AH245" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI245" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="246" spans="1:35">
@@ -19830,10 +19833,10 @@
         <v>168</v>
       </c>
       <c r="AH246" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI246" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="247" spans="1:35">
@@ -19910,10 +19913,10 @@
         <v>168</v>
       </c>
       <c r="AH247" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI247" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="248" spans="1:35">
@@ -19990,10 +19993,10 @@
         <v>168</v>
       </c>
       <c r="AH248" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI248" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="249" spans="1:35">
@@ -20070,10 +20073,10 @@
         <v>174</v>
       </c>
       <c r="AH249" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI249" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="250" spans="1:35">
@@ -20150,10 +20153,10 @@
         <v>169</v>
       </c>
       <c r="AH250" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI250" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="251" spans="1:35">
@@ -20224,10 +20227,10 @@
         <v>170</v>
       </c>
       <c r="AH251" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI251" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="252" spans="1:35">
@@ -20298,10 +20301,10 @@
         <v>171</v>
       </c>
       <c r="AH252" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI252" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="253" spans="1:35">
@@ -20378,10 +20381,10 @@
         <v>168</v>
       </c>
       <c r="AH253" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI253" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="254" spans="1:35">
@@ -20455,10 +20458,10 @@
         <v>173</v>
       </c>
       <c r="AH254" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI254" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="255" spans="1:35">
@@ -20535,10 +20538,10 @@
         <v>168</v>
       </c>
       <c r="AH255" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI255" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="256" spans="1:35">
@@ -20615,10 +20618,10 @@
         <v>168</v>
       </c>
       <c r="AH256" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI256" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="257" spans="1:35">
@@ -20692,10 +20695,10 @@
         <v>167</v>
       </c>
       <c r="AH257" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI257" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="258" spans="1:35">
@@ -20769,10 +20772,10 @@
         <v>174</v>
       </c>
       <c r="AH258" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI258" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="259" spans="1:35">
@@ -20846,10 +20849,10 @@
         <v>169</v>
       </c>
       <c r="AH259" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI259" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="260" spans="1:35">
@@ -20923,10 +20926,10 @@
         <v>170</v>
       </c>
       <c r="AH260" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI260" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="261" spans="1:35">
@@ -21003,10 +21006,10 @@
         <v>174</v>
       </c>
       <c r="AH261" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI261" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="262" spans="1:35">
@@ -21077,10 +21080,10 @@
         <v>168</v>
       </c>
       <c r="AH262" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI262" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="263" spans="1:35">
@@ -21151,10 +21154,10 @@
         <v>168</v>
       </c>
       <c r="AH263" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI263" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="264" spans="1:35">
@@ -21225,10 +21228,10 @@
         <v>168</v>
       </c>
       <c r="AH264" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI264" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="265" spans="1:35">
@@ -21305,10 +21308,10 @@
         <v>179</v>
       </c>
       <c r="AH265" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI265" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="266" spans="1:35">
@@ -21385,10 +21388,10 @@
         <v>179</v>
       </c>
       <c r="AH266" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI266" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="267" spans="1:35">
@@ -21465,10 +21468,10 @@
         <v>178</v>
       </c>
       <c r="AH267" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI267" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="268" spans="1:35">
@@ -21536,10 +21539,10 @@
         <v>176</v>
       </c>
       <c r="AH268" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI268" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="269" spans="1:35">
@@ -21616,10 +21619,10 @@
         <v>175</v>
       </c>
       <c r="AH269" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI269" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="270" spans="1:35">
@@ -21687,10 +21690,10 @@
         <v>190</v>
       </c>
       <c r="AH270" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI270" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="271" spans="1:35">
@@ -21767,10 +21770,10 @@
         <v>190</v>
       </c>
       <c r="AH271" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI271" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="272" spans="1:35">
@@ -21844,10 +21847,10 @@
         <v>176</v>
       </c>
       <c r="AH272" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI272" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="273" spans="1:35">
@@ -21924,10 +21927,10 @@
         <v>177</v>
       </c>
       <c r="AH273" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI273" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="274" spans="1:35">
@@ -22001,10 +22004,10 @@
         <v>179</v>
       </c>
       <c r="AH274" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI274" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="275" spans="1:35">
@@ -22081,10 +22084,10 @@
         <v>179</v>
       </c>
       <c r="AH275" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI275" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="276" spans="1:35">
@@ -22158,10 +22161,10 @@
         <v>178</v>
       </c>
       <c r="AH276" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI276" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="277" spans="1:35">
@@ -22232,10 +22235,10 @@
         <v>176</v>
       </c>
       <c r="AH277" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI277" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="278" spans="1:35">
@@ -22309,10 +22312,10 @@
         <v>179</v>
       </c>
       <c r="AH278" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI278" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="279" spans="1:35">
@@ -22386,10 +22389,10 @@
         <v>179</v>
       </c>
       <c r="AH279" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI279" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="280" spans="1:35">
@@ -22466,10 +22469,10 @@
         <v>175</v>
       </c>
       <c r="AH280" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI280" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="281" spans="1:35">
@@ -22537,10 +22540,10 @@
         <v>190</v>
       </c>
       <c r="AH281" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI281" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="282" spans="1:35">
@@ -22614,10 +22617,10 @@
         <v>176</v>
       </c>
       <c r="AH282" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI282" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="283" spans="1:35">
@@ -22688,10 +22691,10 @@
         <v>179</v>
       </c>
       <c r="AH283" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI283" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="284" spans="1:35">
@@ -22762,10 +22765,10 @@
         <v>179</v>
       </c>
       <c r="AH284" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI284" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="285" spans="1:35">
@@ -22836,10 +22839,10 @@
         <v>177</v>
       </c>
       <c r="AH285" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI285" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="286" spans="1:35">
@@ -22913,10 +22916,10 @@
         <v>176</v>
       </c>
       <c r="AH286" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI286" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="287" spans="1:35">
@@ -22990,10 +22993,10 @@
         <v>176</v>
       </c>
       <c r="AH287" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI287" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="288" spans="1:35">
@@ -23070,10 +23073,10 @@
         <v>177</v>
       </c>
       <c r="AH288" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI288" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="289" spans="1:35">
@@ -23150,10 +23153,10 @@
         <v>180</v>
       </c>
       <c r="AH289" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI289" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="290" spans="1:35">
@@ -23227,10 +23230,10 @@
         <v>180</v>
       </c>
       <c r="AH290" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI290" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="291" spans="1:35">
@@ -23307,10 +23310,10 @@
         <v>180</v>
       </c>
       <c r="AH291" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI291" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="292" spans="1:35">
@@ -23381,10 +23384,10 @@
         <v>180</v>
       </c>
       <c r="AH292" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI292" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="293" spans="1:35">
@@ -23455,10 +23458,10 @@
         <v>180</v>
       </c>
       <c r="AH293" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI293" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="294" spans="1:35">
@@ -23529,10 +23532,10 @@
         <v>180</v>
       </c>
       <c r="AH294" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI294" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="295" spans="1:35">
@@ -23603,10 +23606,10 @@
         <v>180</v>
       </c>
       <c r="AH295" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI295" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="296" spans="1:35">
@@ -23677,10 +23680,10 @@
         <v>180</v>
       </c>
       <c r="AH296" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI296" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="297" spans="1:35">
@@ -23757,10 +23760,10 @@
         <v>180</v>
       </c>
       <c r="AH297" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI297" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="298" spans="1:35">
@@ -23831,10 +23834,10 @@
         <v>180</v>
       </c>
       <c r="AH298" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI298" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="299" spans="1:35">
@@ -23911,10 +23914,10 @@
         <v>180</v>
       </c>
       <c r="AH299" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI299" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="300" spans="1:35">
@@ -23985,10 +23988,10 @@
         <v>180</v>
       </c>
       <c r="AH300" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI300" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="301" spans="1:35">
@@ -24059,10 +24062,10 @@
         <v>180</v>
       </c>
       <c r="AH301" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI301" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="302" spans="1:35">
@@ -24133,10 +24136,10 @@
         <v>180</v>
       </c>
       <c r="AH302" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI302" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="303" spans="1:35">
@@ -24213,10 +24216,10 @@
         <v>180</v>
       </c>
       <c r="AH303" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI303" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="304" spans="1:35">
@@ -24287,10 +24290,10 @@
         <v>180</v>
       </c>
       <c r="AH304" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI304" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="305" spans="1:35">
@@ -24361,10 +24364,10 @@
         <v>180</v>
       </c>
       <c r="AH305" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI305" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="306" spans="1:35">
@@ -24435,10 +24438,10 @@
         <v>180</v>
       </c>
       <c r="AH306" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI306" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="307" spans="1:35">
@@ -24509,10 +24512,10 @@
         <v>180</v>
       </c>
       <c r="AH307" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI307" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="308" spans="1:35">
@@ -24583,10 +24586,10 @@
         <v>180</v>
       </c>
       <c r="AH308" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI308" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="309" spans="1:35">
@@ -24657,10 +24660,10 @@
         <v>180</v>
       </c>
       <c r="AH309" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI309" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="310" spans="1:35">
@@ -24737,10 +24740,10 @@
         <v>180</v>
       </c>
       <c r="AH310" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI310" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="311" spans="1:35">
@@ -24817,10 +24820,10 @@
         <v>180</v>
       </c>
       <c r="AH311" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI311" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="312" spans="1:35">
@@ -24897,10 +24900,10 @@
         <v>180</v>
       </c>
       <c r="AH312" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI312" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="313" spans="1:35">
@@ -24974,10 +24977,10 @@
         <v>180</v>
       </c>
       <c r="AH313" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI313" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="314" spans="1:35">
@@ -25051,10 +25054,10 @@
         <v>180</v>
       </c>
       <c r="AH314" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI314" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="315" spans="1:35">
@@ -25128,10 +25131,10 @@
         <v>181</v>
       </c>
       <c r="AH315" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI315" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="316" spans="1:35">
@@ -25205,10 +25208,10 @@
         <v>181</v>
       </c>
       <c r="AH316" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI316" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="317" spans="1:35">
@@ -25279,10 +25282,10 @@
         <v>181</v>
       </c>
       <c r="AH317" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI317" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="318" spans="1:35">
@@ -25353,10 +25356,10 @@
         <v>181</v>
       </c>
       <c r="AH318" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI318" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="319" spans="1:35">
@@ -25427,10 +25430,10 @@
         <v>181</v>
       </c>
       <c r="AH319" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI319" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="320" spans="1:35">
@@ -25501,10 +25504,10 @@
         <v>181</v>
       </c>
       <c r="AH320" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI320" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="321" spans="1:35">
@@ -25572,10 +25575,10 @@
         <v>181</v>
       </c>
       <c r="AH321" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI321" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="322" spans="1:35">
@@ -25649,10 +25652,10 @@
         <v>181</v>
       </c>
       <c r="AH322" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI322" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="323" spans="1:35">
@@ -25726,10 +25729,10 @@
         <v>181</v>
       </c>
       <c r="AH323" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI323" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="324" spans="1:35">
@@ -25803,10 +25806,10 @@
         <v>181</v>
       </c>
       <c r="AH324" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI324" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="325" spans="1:35">
@@ -25880,10 +25883,10 @@
         <v>181</v>
       </c>
       <c r="AH325" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI325" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="326" spans="1:35">
@@ -25957,10 +25960,10 @@
         <v>181</v>
       </c>
       <c r="AH326" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI326" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="327" spans="1:35">
@@ -26031,10 +26034,10 @@
         <v>181</v>
       </c>
       <c r="AH327" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI327" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="328" spans="1:35">
@@ -26105,10 +26108,10 @@
         <v>181</v>
       </c>
       <c r="AH328" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI328" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="329" spans="1:35">
@@ -26179,10 +26182,10 @@
         <v>181</v>
       </c>
       <c r="AH329" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI329" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="330" spans="1:35">
@@ -26250,10 +26253,10 @@
         <v>181</v>
       </c>
       <c r="AH330" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI330" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="331" spans="1:35">
@@ -26321,10 +26324,10 @@
         <v>181</v>
       </c>
       <c r="AH331" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI331" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="332" spans="1:35">
@@ -26392,10 +26395,10 @@
         <v>181</v>
       </c>
       <c r="AH332" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI332" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="333" spans="1:35">
@@ -26463,10 +26466,10 @@
         <v>181</v>
       </c>
       <c r="AH333" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI333" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="334" spans="1:35">
@@ -26534,10 +26537,10 @@
         <v>181</v>
       </c>
       <c r="AH334" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI334" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="335" spans="1:35">
@@ -26605,10 +26608,10 @@
         <v>54</v>
       </c>
       <c r="AH335" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI335" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="336" spans="1:35">
@@ -26676,10 +26679,10 @@
         <v>54</v>
       </c>
       <c r="AH336" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI336" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="337" spans="1:35">
@@ -26747,10 +26750,10 @@
         <v>54</v>
       </c>
       <c r="AH337" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI337" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="338" spans="1:35">
@@ -26818,10 +26821,10 @@
         <v>54</v>
       </c>
       <c r="AH338" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI338" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="339" spans="1:35">
@@ -26889,10 +26892,10 @@
         <v>182</v>
       </c>
       <c r="AH339" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI339" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="340" spans="1:35">
@@ -26960,10 +26963,10 @@
         <v>182</v>
       </c>
       <c r="AH340" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI340" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="341" spans="1:35">
@@ -27031,10 +27034,10 @@
         <v>182</v>
       </c>
       <c r="AH341" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI341" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="342" spans="1:35">
@@ -27102,10 +27105,10 @@
         <v>182</v>
       </c>
       <c r="AH342" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI342" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="343" spans="1:35">
@@ -27173,10 +27176,10 @@
         <v>182</v>
       </c>
       <c r="AH343" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI343" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="344" spans="1:35">
@@ -27244,10 +27247,10 @@
         <v>182</v>
       </c>
       <c r="AH344" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI344" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="345" spans="1:35">
@@ -27315,10 +27318,10 @@
         <v>182</v>
       </c>
       <c r="AH345" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI345" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="346" spans="1:35">
@@ -27386,10 +27389,10 @@
         <v>182</v>
       </c>
       <c r="AH346" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI346" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="347" spans="1:35">
@@ -27457,10 +27460,10 @@
         <v>182</v>
       </c>
       <c r="AH347" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI347" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="348" spans="1:35">
@@ -27531,10 +27534,10 @@
         <v>54</v>
       </c>
       <c r="AH348" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI348" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="349" spans="1:35">
@@ -27605,10 +27608,10 @@
         <v>54</v>
       </c>
       <c r="AH349" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI349" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="350" spans="1:35">
@@ -27679,10 +27682,10 @@
         <v>54</v>
       </c>
       <c r="AH350" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI350" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="351" spans="1:35">
@@ -27750,13 +27753,13 @@
         <v>0</v>
       </c>
       <c r="AC351" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AH351" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI351" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="352" spans="1:35">
@@ -27827,10 +27830,10 @@
         <v>159</v>
       </c>
       <c r="AH352" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI352" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="353" spans="1:35">
@@ -27901,10 +27904,10 @@
         <v>165</v>
       </c>
       <c r="AH353" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI353" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="354" spans="1:35">
@@ -27972,10 +27975,10 @@
         <v>171</v>
       </c>
       <c r="AH354" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI354" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="355" spans="1:35">
@@ -28043,10 +28046,10 @@
         <v>171</v>
       </c>
       <c r="AH355" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI355" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="356" spans="1:35">
@@ -28123,10 +28126,10 @@
         <v>172</v>
       </c>
       <c r="AH356" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI356" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="357" spans="1:35">
@@ -28197,10 +28200,10 @@
         <v>172</v>
       </c>
       <c r="AH357" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI357" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="358" spans="1:35">
@@ -28274,10 +28277,10 @@
         <v>180</v>
       </c>
       <c r="AH358" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AI358" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="359" spans="1:35">
@@ -28351,10 +28354,10 @@
         <v>181</v>
       </c>
       <c r="AH359" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI359" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="360" spans="1:35">
@@ -28428,10 +28431,10 @@
         <v>181</v>
       </c>
       <c r="AH360" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI360" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="361" spans="1:35">
@@ -28505,10 +28508,10 @@
         <v>181</v>
       </c>
       <c r="AH361" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI361" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="362" spans="1:35">
@@ -28582,10 +28585,10 @@
         <v>181</v>
       </c>
       <c r="AH362" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI362" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="363" spans="1:35">
@@ -28659,10 +28662,10 @@
         <v>181</v>
       </c>
       <c r="AH363" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI363" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="364" spans="1:35">
@@ -28736,10 +28739,10 @@
         <v>181</v>
       </c>
       <c r="AH364" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI364" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="365" spans="1:35">
@@ -28813,10 +28816,10 @@
         <v>181</v>
       </c>
       <c r="AH365" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI365" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="366" spans="1:35">
@@ -28890,10 +28893,10 @@
         <v>181</v>
       </c>
       <c r="AH366" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI366" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="367" spans="1:35">
@@ -28967,10 +28970,10 @@
         <v>181</v>
       </c>
       <c r="AH367" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI367" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="368" spans="1:35">
@@ -29044,10 +29047,10 @@
         <v>181</v>
       </c>
       <c r="AH368" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI368" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="369" spans="1:35">
@@ -29121,10 +29124,10 @@
         <v>181</v>
       </c>
       <c r="AH369" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI369" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="370" spans="1:35">
@@ -29198,10 +29201,10 @@
         <v>181</v>
       </c>
       <c r="AH370" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI370" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="371" spans="1:35">
@@ -29275,10 +29278,10 @@
         <v>181</v>
       </c>
       <c r="AH371" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI371" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="372" spans="1:35">
@@ -29352,10 +29355,10 @@
         <v>181</v>
       </c>
       <c r="AH372" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI372" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="373" spans="1:35">
@@ -29429,10 +29432,10 @@
         <v>54</v>
       </c>
       <c r="AH373" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI373" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="374" spans="1:35">
@@ -29506,10 +29509,10 @@
         <v>54</v>
       </c>
       <c r="AH374" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI374" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="375" spans="1:35">
@@ -29583,10 +29586,10 @@
         <v>54</v>
       </c>
       <c r="AH375" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI375" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="376" spans="1:35">
@@ -29660,10 +29663,10 @@
         <v>54</v>
       </c>
       <c r="AH376" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI376" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="377" spans="1:35">
@@ -29737,10 +29740,10 @@
         <v>182</v>
       </c>
       <c r="AH377" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI377" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="378" spans="1:35">
@@ -29814,10 +29817,10 @@
         <v>55</v>
       </c>
       <c r="AH378" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI378" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="379" spans="1:35">
@@ -29891,10 +29894,10 @@
         <v>54</v>
       </c>
       <c r="AH379" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI379" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="380" spans="1:35">
@@ -29968,10 +29971,10 @@
         <v>54</v>
       </c>
       <c r="AH380" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI380" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="381" spans="1:35">
@@ -30045,10 +30048,10 @@
         <v>54</v>
       </c>
       <c r="AH381" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI381" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="382" spans="1:35">
@@ -30122,10 +30125,10 @@
         <v>182</v>
       </c>
       <c r="AH382" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI382" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="383" spans="1:35">
@@ -30199,10 +30202,10 @@
         <v>54</v>
       </c>
       <c r="AH383" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI383" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="384" spans="1:35">
@@ -30276,10 +30279,10 @@
         <v>182</v>
       </c>
       <c r="AH384" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI384" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="385" spans="1:35">
@@ -30353,10 +30356,10 @@
         <v>54</v>
       </c>
       <c r="AH385" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI385" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="386" spans="1:35">
@@ -30430,10 +30433,84 @@
         <v>54</v>
       </c>
       <c r="AH386" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI386" t="s">
-        <v>352</v>
+        <v>353</v>
+      </c>
+    </row>
+    <row r="387" spans="1:35">
+      <c r="A387">
+        <v>6404</v>
+      </c>
+      <c r="B387" t="s">
+        <v>47</v>
+      </c>
+      <c r="C387" t="s">
+        <v>50</v>
+      </c>
+      <c r="D387" t="s">
+        <v>53</v>
+      </c>
+      <c r="E387" t="s">
+        <v>54</v>
+      </c>
+      <c r="F387" t="s">
+        <v>56</v>
+      </c>
+      <c r="G387">
+        <v>7027</v>
+      </c>
+      <c r="H387">
+        <v>0</v>
+      </c>
+      <c r="I387" t="s">
+        <v>65</v>
+      </c>
+      <c r="J387" t="s">
+        <v>121</v>
+      </c>
+      <c r="N387" s="1">
+        <v>46289</v>
+      </c>
+      <c r="P387">
+        <v>8</v>
+      </c>
+      <c r="Q387">
+        <v>2026</v>
+      </c>
+      <c r="R387">
+        <v>16962348</v>
+      </c>
+      <c r="S387" t="s">
+        <v>54</v>
+      </c>
+      <c r="U387" t="s">
+        <v>193</v>
+      </c>
+      <c r="V387" s="1">
+        <v>46282.64018086805</v>
+      </c>
+      <c r="W387">
+        <v>-7</v>
+      </c>
+      <c r="X387" t="s">
+        <v>205</v>
+      </c>
+      <c r="Y387" t="s">
+        <v>343</v>
+      </c>
+      <c r="AB387">
+        <v>0</v>
+      </c>
+      <c r="AC387" t="s">
+        <v>54</v>
+      </c>
+      <c r="AH387" t="s">
+        <v>348</v>
+      </c>
+      <c r="AI387" t="s">
+        <v>353</v>
       </c>
     </row>
   </sheetData>

--- a/data/base/goias.xlsx
+++ b/data/base/goias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5572" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5604" uniqueCount="355">
   <si>
     <t>CodCliente</t>
   </si>
@@ -1057,6 +1057,9 @@
   <si>
     <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 18/09/2026 
 Em andamento - Data Comentário: 17/09/2026 09:28</t>
+  </si>
+  <si>
+    <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 17/09/2026 Em andamento, será finalizada em 17/09 - Data Comentário: 16/09/2026 18:47</t>
   </si>
   <si>
     <t>Baixado via API integração MGC x Sistema de Analise Fiscal em 17/09/2026 12:58:09. - Data Comentário: 17/09/2026 12:53</t>
@@ -1440,7 +1443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AI387"/>
+  <dimension ref="A1:AI389"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:35">
@@ -1621,10 +1624,10 @@
         <v>159</v>
       </c>
       <c r="AH2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="3" spans="1:35">
@@ -1698,10 +1701,10 @@
         <v>160</v>
       </c>
       <c r="AH3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="4" spans="1:35">
@@ -1775,10 +1778,10 @@
         <v>159</v>
       </c>
       <c r="AH4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="5" spans="1:35">
@@ -1849,10 +1852,10 @@
         <v>159</v>
       </c>
       <c r="AH5" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="6" spans="1:35">
@@ -1923,10 +1926,10 @@
         <v>160</v>
       </c>
       <c r="AH6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="7" spans="1:35">
@@ -1997,10 +2000,10 @@
         <v>160</v>
       </c>
       <c r="AH7" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI7" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="8" spans="1:35">
@@ -2071,10 +2074,10 @@
         <v>161</v>
       </c>
       <c r="AH8" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI8" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9" spans="1:35">
@@ -2145,10 +2148,10 @@
         <v>159</v>
       </c>
       <c r="AH9" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI9" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="10" spans="1:35">
@@ -2219,10 +2222,10 @@
         <v>162</v>
       </c>
       <c r="AH10" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11" spans="1:35">
@@ -2293,10 +2296,10 @@
         <v>162</v>
       </c>
       <c r="AH11" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI11" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="12" spans="1:35">
@@ -2367,10 +2370,10 @@
         <v>163</v>
       </c>
       <c r="AH12" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI12" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="13" spans="1:35">
@@ -2438,13 +2441,13 @@
         <v>0</v>
       </c>
       <c r="AC13" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AH13" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI13" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="14" spans="1:35">
@@ -2512,13 +2515,13 @@
         <v>0</v>
       </c>
       <c r="AC14" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AH14" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI14" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="15" spans="1:35">
@@ -2586,10 +2589,10 @@
         <v>0</v>
       </c>
       <c r="AH15" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI15" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="16" spans="1:35">
@@ -2651,10 +2654,10 @@
         <v>0</v>
       </c>
       <c r="AH16" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI16" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="17" spans="1:35">
@@ -2722,10 +2725,10 @@
         <v>0</v>
       </c>
       <c r="AH17" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI17" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="18" spans="1:35">
@@ -2799,10 +2802,10 @@
         <v>165</v>
       </c>
       <c r="AH18" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI18" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="19" spans="1:35">
@@ -2876,10 +2879,10 @@
         <v>164</v>
       </c>
       <c r="AH19" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI19" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="20" spans="1:35">
@@ -2953,10 +2956,10 @@
         <v>165</v>
       </c>
       <c r="AH20" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI20" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="21" spans="1:35">
@@ -3030,10 +3033,10 @@
         <v>163</v>
       </c>
       <c r="AH21" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI21" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="22" spans="1:35">
@@ -3104,10 +3107,10 @@
         <v>166</v>
       </c>
       <c r="AH22" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI22" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="23" spans="1:35">
@@ -3178,10 +3181,10 @@
         <v>163</v>
       </c>
       <c r="AH23" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI23" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="24" spans="1:35">
@@ -3252,10 +3255,10 @@
         <v>163</v>
       </c>
       <c r="AH24" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI24" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="25" spans="1:35">
@@ -3326,10 +3329,10 @@
         <v>163</v>
       </c>
       <c r="AH25" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI25" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="26" spans="1:35">
@@ -3400,10 +3403,10 @@
         <v>164</v>
       </c>
       <c r="AH26" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI26" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="27" spans="1:35">
@@ -3474,10 +3477,10 @@
         <v>163</v>
       </c>
       <c r="AH27" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI27" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="28" spans="1:35">
@@ -3548,10 +3551,10 @@
         <v>163</v>
       </c>
       <c r="AH28" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI28" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="29" spans="1:35">
@@ -3622,10 +3625,10 @@
         <v>163</v>
       </c>
       <c r="AH29" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI29" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="30" spans="1:35">
@@ -3696,10 +3699,10 @@
         <v>167</v>
       </c>
       <c r="AH30" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI30" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="31" spans="1:35">
@@ -3776,10 +3779,10 @@
         <v>168</v>
       </c>
       <c r="AH31" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI31" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="32" spans="1:35">
@@ -3850,10 +3853,10 @@
         <v>169</v>
       </c>
       <c r="AH32" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI32" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="33" spans="1:35">
@@ -3930,10 +3933,10 @@
         <v>170</v>
       </c>
       <c r="AH33" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI33" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="34" spans="1:35">
@@ -4007,10 +4010,10 @@
         <v>171</v>
       </c>
       <c r="AH34" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI34" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="35" spans="1:35">
@@ -4084,13 +4087,13 @@
         <v>0</v>
       </c>
       <c r="AC35" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AH35" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI35" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="36" spans="1:35">
@@ -4167,10 +4170,10 @@
         <v>173</v>
       </c>
       <c r="AH36" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI36" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="37" spans="1:35">
@@ -4247,10 +4250,10 @@
         <v>167</v>
       </c>
       <c r="AH37" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI37" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="38" spans="1:35">
@@ -4324,10 +4327,10 @@
         <v>189</v>
       </c>
       <c r="AH38" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI38" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="39" spans="1:35">
@@ -4404,10 +4407,10 @@
         <v>168</v>
       </c>
       <c r="AH39" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI39" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="40" spans="1:35">
@@ -4484,10 +4487,10 @@
         <v>168</v>
       </c>
       <c r="AH40" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI40" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="41" spans="1:35">
@@ -4564,10 +4567,10 @@
         <v>168</v>
       </c>
       <c r="AH41" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI41" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="42" spans="1:35">
@@ -4644,10 +4647,10 @@
         <v>167</v>
       </c>
       <c r="AH42" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI42" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="43" spans="1:35">
@@ -4724,10 +4727,10 @@
         <v>174</v>
       </c>
       <c r="AH43" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI43" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="44" spans="1:35">
@@ -4804,10 +4807,10 @@
         <v>169</v>
       </c>
       <c r="AH44" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI44" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="45" spans="1:35">
@@ -4884,10 +4887,10 @@
         <v>170</v>
       </c>
       <c r="AH45" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI45" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="46" spans="1:35">
@@ -4955,10 +4958,10 @@
         <v>171</v>
       </c>
       <c r="AH46" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI46" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="47" spans="1:35">
@@ -5029,10 +5032,10 @@
         <v>168</v>
       </c>
       <c r="AH47" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI47" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="48" spans="1:35">
@@ -5103,10 +5106,10 @@
         <v>168</v>
       </c>
       <c r="AH48" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI48" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="49" spans="1:35">
@@ -5177,10 +5180,10 @@
         <v>168</v>
       </c>
       <c r="AH49" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI49" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="50" spans="1:35">
@@ -5251,10 +5254,10 @@
         <v>167</v>
       </c>
       <c r="AH50" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI50" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="51" spans="1:35">
@@ -5325,10 +5328,10 @@
         <v>174</v>
       </c>
       <c r="AH51" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI51" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="52" spans="1:35">
@@ -5405,10 +5408,10 @@
         <v>169</v>
       </c>
       <c r="AH52" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI52" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="53" spans="1:35">
@@ -5479,10 +5482,10 @@
         <v>170</v>
       </c>
       <c r="AH53" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI53" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="54" spans="1:35">
@@ -5559,10 +5562,10 @@
         <v>168</v>
       </c>
       <c r="AH54" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI54" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="55" spans="1:35">
@@ -5639,10 +5642,10 @@
         <v>168</v>
       </c>
       <c r="AH55" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI55" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="56" spans="1:35">
@@ -5719,10 +5722,10 @@
         <v>168</v>
       </c>
       <c r="AH56" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI56" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="57" spans="1:35">
@@ -5799,10 +5802,10 @@
         <v>167</v>
       </c>
       <c r="AH57" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI57" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="58" spans="1:35">
@@ -5876,10 +5879,10 @@
         <v>171</v>
       </c>
       <c r="AH58" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI58" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="59" spans="1:35">
@@ -5953,13 +5956,13 @@
         <v>0</v>
       </c>
       <c r="AC59" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AH59" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI59" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="60" spans="1:35">
@@ -6036,10 +6039,10 @@
         <v>168</v>
       </c>
       <c r="AH60" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI60" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="61" spans="1:35">
@@ -6116,10 +6119,10 @@
         <v>168</v>
       </c>
       <c r="AH61" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI61" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="62" spans="1:35">
@@ -6196,10 +6199,10 @@
         <v>168</v>
       </c>
       <c r="AH62" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI62" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="63" spans="1:35">
@@ -6276,10 +6279,10 @@
         <v>167</v>
       </c>
       <c r="AH63" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI63" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="64" spans="1:35">
@@ -6356,10 +6359,10 @@
         <v>174</v>
       </c>
       <c r="AH64" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI64" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="65" spans="1:35">
@@ -6436,10 +6439,10 @@
         <v>169</v>
       </c>
       <c r="AH65" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI65" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="66" spans="1:35">
@@ -6516,10 +6519,10 @@
         <v>170</v>
       </c>
       <c r="AH66" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI66" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="67" spans="1:35">
@@ -6596,10 +6599,10 @@
         <v>168</v>
       </c>
       <c r="AH67" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI67" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="68" spans="1:35">
@@ -6667,10 +6670,10 @@
         <v>171</v>
       </c>
       <c r="AH68" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI68" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="69" spans="1:35">
@@ -6738,13 +6741,13 @@
         <v>0</v>
       </c>
       <c r="AC69" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AH69" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI69" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="70" spans="1:35">
@@ -6815,10 +6818,10 @@
         <v>168</v>
       </c>
       <c r="AH70" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI70" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="71" spans="1:35">
@@ -6889,10 +6892,10 @@
         <v>168</v>
       </c>
       <c r="AH71" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI71" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="72" spans="1:35">
@@ -6963,10 +6966,10 @@
         <v>168</v>
       </c>
       <c r="AH72" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI72" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="73" spans="1:35">
@@ -7037,10 +7040,10 @@
         <v>167</v>
       </c>
       <c r="AH73" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI73" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="74" spans="1:35">
@@ -7111,10 +7114,10 @@
         <v>174</v>
       </c>
       <c r="AH74" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI74" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="75" spans="1:35">
@@ -7185,10 +7188,10 @@
         <v>169</v>
       </c>
       <c r="AH75" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI75" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="76" spans="1:35">
@@ -7259,10 +7262,10 @@
         <v>170</v>
       </c>
       <c r="AH76" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI76" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="77" spans="1:35">
@@ -7333,10 +7336,10 @@
         <v>170</v>
       </c>
       <c r="AH77" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI77" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="78" spans="1:35">
@@ -7407,10 +7410,10 @@
         <v>170</v>
       </c>
       <c r="AH78" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI78" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="79" spans="1:35">
@@ -7481,10 +7484,10 @@
         <v>170</v>
       </c>
       <c r="AH79" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI79" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="80" spans="1:35">
@@ -7555,10 +7558,10 @@
         <v>190</v>
       </c>
       <c r="AH80" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI80" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="81" spans="1:35">
@@ -7626,10 +7629,10 @@
         <v>190</v>
       </c>
       <c r="AH81" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI81" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="82" spans="1:35">
@@ -7700,10 +7703,10 @@
         <v>177</v>
       </c>
       <c r="AH82" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI82" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="83" spans="1:35">
@@ -7774,10 +7777,10 @@
         <v>190</v>
       </c>
       <c r="AH83" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI83" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="84" spans="1:35">
@@ -7845,10 +7848,10 @@
         <v>190</v>
       </c>
       <c r="AH84" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI84" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="85" spans="1:35">
@@ -7919,10 +7922,10 @@
         <v>190</v>
       </c>
       <c r="AH85" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI85" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="86" spans="1:35">
@@ -7987,10 +7990,10 @@
         <v>177</v>
       </c>
       <c r="AH86" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI86" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:35">
@@ -8061,10 +8064,10 @@
         <v>190</v>
       </c>
       <c r="AH87" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI87" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:35">
@@ -8132,10 +8135,10 @@
         <v>190</v>
       </c>
       <c r="AH88" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI88" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="89" spans="1:35">
@@ -8206,10 +8209,10 @@
         <v>190</v>
       </c>
       <c r="AH89" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI89" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="90" spans="1:35">
@@ -8274,10 +8277,10 @@
         <v>190</v>
       </c>
       <c r="AH90" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI90" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="91" spans="1:35">
@@ -8342,10 +8345,10 @@
         <v>177</v>
       </c>
       <c r="AH91" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI91" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="92" spans="1:35">
@@ -8416,10 +8419,10 @@
         <v>190</v>
       </c>
       <c r="AH92" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI92" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="93" spans="1:35">
@@ -8487,10 +8490,10 @@
         <v>190</v>
       </c>
       <c r="AH93" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI93" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="94" spans="1:35">
@@ -8561,10 +8564,10 @@
         <v>190</v>
       </c>
       <c r="AH94" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI94" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="95" spans="1:35">
@@ -8629,10 +8632,10 @@
         <v>190</v>
       </c>
       <c r="AH95" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI95" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="96" spans="1:35">
@@ -8697,10 +8700,10 @@
         <v>177</v>
       </c>
       <c r="AH96" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI96" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="97" spans="1:35">
@@ -8771,10 +8774,10 @@
         <v>190</v>
       </c>
       <c r="AH97" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI97" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="98" spans="1:35">
@@ -8842,10 +8845,10 @@
         <v>190</v>
       </c>
       <c r="AH98" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI98" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="99" spans="1:35">
@@ -8916,10 +8919,10 @@
         <v>177</v>
       </c>
       <c r="AH99" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI99" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="100" spans="1:35">
@@ -8996,10 +8999,10 @@
         <v>190</v>
       </c>
       <c r="AH100" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI100" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="101" spans="1:35">
@@ -9067,10 +9070,10 @@
         <v>190</v>
       </c>
       <c r="AH101" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI101" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="102" spans="1:35">
@@ -9141,10 +9144,10 @@
         <v>190</v>
       </c>
       <c r="AH102" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI102" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="103" spans="1:35">
@@ -9212,10 +9215,10 @@
         <v>190</v>
       </c>
       <c r="AH103" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI103" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="104" spans="1:35">
@@ -9286,10 +9289,10 @@
         <v>190</v>
       </c>
       <c r="AH104" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI104" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="105" spans="1:35">
@@ -9354,10 +9357,10 @@
         <v>190</v>
       </c>
       <c r="AH105" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI105" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="106" spans="1:35">
@@ -9422,10 +9425,10 @@
         <v>177</v>
       </c>
       <c r="AH106" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI106" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="107" spans="1:35">
@@ -9496,10 +9499,10 @@
         <v>190</v>
       </c>
       <c r="AH107" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI107" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="108" spans="1:35">
@@ -9570,10 +9573,10 @@
         <v>190</v>
       </c>
       <c r="AH108" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI108" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="109" spans="1:35">
@@ -9641,10 +9644,10 @@
         <v>190</v>
       </c>
       <c r="AH109" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI109" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="110" spans="1:35">
@@ -9715,10 +9718,10 @@
         <v>177</v>
       </c>
       <c r="AH110" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI110" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="111" spans="1:35">
@@ -9786,10 +9789,10 @@
         <v>176</v>
       </c>
       <c r="AH111" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI111" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="112" spans="1:35">
@@ -9860,10 +9863,10 @@
         <v>177</v>
       </c>
       <c r="AH112" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI112" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="113" spans="1:35">
@@ -9934,10 +9937,10 @@
         <v>175</v>
       </c>
       <c r="AH113" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI113" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="114" spans="1:35">
@@ -10005,10 +10008,10 @@
         <v>176</v>
       </c>
       <c r="AH114" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI114" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="115" spans="1:35">
@@ -10079,10 +10082,10 @@
         <v>177</v>
       </c>
       <c r="AH115" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI115" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="116" spans="1:35">
@@ -10153,10 +10156,10 @@
         <v>190</v>
       </c>
       <c r="AH116" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI116" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="117" spans="1:35">
@@ -10224,10 +10227,10 @@
         <v>190</v>
       </c>
       <c r="AH117" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI117" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="118" spans="1:35">
@@ -10298,10 +10301,10 @@
         <v>190</v>
       </c>
       <c r="AH118" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI118" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="119" spans="1:35">
@@ -10366,10 +10369,10 @@
         <v>190</v>
       </c>
       <c r="AH119" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI119" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="120" spans="1:35">
@@ -10434,10 +10437,10 @@
         <v>177</v>
       </c>
       <c r="AH120" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI120" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="121" spans="1:35">
@@ -10508,10 +10511,10 @@
         <v>190</v>
       </c>
       <c r="AH121" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI121" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="122" spans="1:35">
@@ -10579,10 +10582,10 @@
         <v>190</v>
       </c>
       <c r="AH122" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI122" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="123" spans="1:35">
@@ -10653,10 +10656,10 @@
         <v>190</v>
       </c>
       <c r="AH123" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI123" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="124" spans="1:35">
@@ -10721,10 +10724,10 @@
         <v>190</v>
       </c>
       <c r="AH124" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI124" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="125" spans="1:35">
@@ -10789,10 +10792,10 @@
         <v>177</v>
       </c>
       <c r="AH125" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI125" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="126" spans="1:35">
@@ -10869,10 +10872,10 @@
         <v>177</v>
       </c>
       <c r="AH126" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI126" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="127" spans="1:35">
@@ -10949,10 +10952,10 @@
         <v>177</v>
       </c>
       <c r="AH127" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI127" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="128" spans="1:35">
@@ -11023,10 +11026,10 @@
         <v>180</v>
       </c>
       <c r="AH128" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI128" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="129" spans="1:35">
@@ -11097,10 +11100,10 @@
         <v>180</v>
       </c>
       <c r="AH129" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI129" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="130" spans="1:35">
@@ -11177,10 +11180,10 @@
         <v>180</v>
       </c>
       <c r="AH130" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI130" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="131" spans="1:35">
@@ -11251,10 +11254,10 @@
         <v>180</v>
       </c>
       <c r="AH131" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI131" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="132" spans="1:35">
@@ -11325,10 +11328,10 @@
         <v>180</v>
       </c>
       <c r="AH132" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI132" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="133" spans="1:35">
@@ -11399,10 +11402,10 @@
         <v>180</v>
       </c>
       <c r="AH133" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI133" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="134" spans="1:35">
@@ -11473,10 +11476,10 @@
         <v>180</v>
       </c>
       <c r="AH134" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI134" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="135" spans="1:35">
@@ -11553,10 +11556,10 @@
         <v>180</v>
       </c>
       <c r="AH135" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI135" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="136" spans="1:35">
@@ -11627,10 +11630,10 @@
         <v>180</v>
       </c>
       <c r="AH136" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI136" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="137" spans="1:35">
@@ -11701,10 +11704,10 @@
         <v>180</v>
       </c>
       <c r="AH137" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI137" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="138" spans="1:35">
@@ -11775,10 +11778,10 @@
         <v>180</v>
       </c>
       <c r="AH138" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI138" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="139" spans="1:35">
@@ -11855,10 +11858,10 @@
         <v>180</v>
       </c>
       <c r="AH139" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI139" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="140" spans="1:35">
@@ -11929,10 +11932,10 @@
         <v>180</v>
       </c>
       <c r="AH140" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI140" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="141" spans="1:35">
@@ -12003,10 +12006,10 @@
         <v>180</v>
       </c>
       <c r="AH141" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI141" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="142" spans="1:35">
@@ -12077,10 +12080,10 @@
         <v>180</v>
       </c>
       <c r="AH142" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI142" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="143" spans="1:35">
@@ -12151,10 +12154,10 @@
         <v>180</v>
       </c>
       <c r="AH143" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI143" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="144" spans="1:35">
@@ -12225,10 +12228,10 @@
         <v>180</v>
       </c>
       <c r="AH144" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI144" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="145" spans="1:35">
@@ -12299,10 +12302,10 @@
         <v>180</v>
       </c>
       <c r="AH145" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI145" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="146" spans="1:35">
@@ -12373,10 +12376,10 @@
         <v>180</v>
       </c>
       <c r="AH146" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI146" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="147" spans="1:35">
@@ -12447,10 +12450,10 @@
         <v>180</v>
       </c>
       <c r="AH147" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI147" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="148" spans="1:35">
@@ -12521,10 +12524,10 @@
         <v>180</v>
       </c>
       <c r="AH148" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI148" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="149" spans="1:35">
@@ -12595,10 +12598,10 @@
         <v>180</v>
       </c>
       <c r="AH149" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI149" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="150" spans="1:35">
@@ -12675,10 +12678,10 @@
         <v>180</v>
       </c>
       <c r="AH150" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI150" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="151" spans="1:35">
@@ -12749,10 +12752,10 @@
         <v>180</v>
       </c>
       <c r="AH151" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI151" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="152" spans="1:35">
@@ -12823,10 +12826,10 @@
         <v>180</v>
       </c>
       <c r="AH152" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI152" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="153" spans="1:35">
@@ -12897,10 +12900,10 @@
         <v>180</v>
       </c>
       <c r="AH153" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI153" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="154" spans="1:35">
@@ -12971,10 +12974,10 @@
         <v>181</v>
       </c>
       <c r="AH154" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI154" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="155" spans="1:35">
@@ -13045,10 +13048,10 @@
         <v>181</v>
       </c>
       <c r="AH155" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI155" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="156" spans="1:35">
@@ -13119,10 +13122,10 @@
         <v>181</v>
       </c>
       <c r="AH156" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI156" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="157" spans="1:35">
@@ -13193,10 +13196,10 @@
         <v>181</v>
       </c>
       <c r="AH157" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI157" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="158" spans="1:35">
@@ -13267,10 +13270,10 @@
         <v>181</v>
       </c>
       <c r="AH158" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI158" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="159" spans="1:35">
@@ -13341,10 +13344,10 @@
         <v>181</v>
       </c>
       <c r="AH159" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI159" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="160" spans="1:35">
@@ -13415,10 +13418,10 @@
         <v>181</v>
       </c>
       <c r="AH160" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI160" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="161" spans="1:35">
@@ -13489,10 +13492,10 @@
         <v>181</v>
       </c>
       <c r="AH161" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI161" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="162" spans="1:35">
@@ -13563,10 +13566,10 @@
         <v>181</v>
       </c>
       <c r="AH162" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI162" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="163" spans="1:35">
@@ -13637,10 +13640,10 @@
         <v>181</v>
       </c>
       <c r="AH163" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI163" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="164" spans="1:35">
@@ -13711,10 +13714,10 @@
         <v>181</v>
       </c>
       <c r="AH164" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI164" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="165" spans="1:35">
@@ -13785,10 +13788,10 @@
         <v>181</v>
       </c>
       <c r="AH165" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI165" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="166" spans="1:35">
@@ -13859,10 +13862,10 @@
         <v>181</v>
       </c>
       <c r="AH166" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI166" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="167" spans="1:35">
@@ -13933,10 +13936,10 @@
         <v>181</v>
       </c>
       <c r="AH167" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI167" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="168" spans="1:35">
@@ -14007,10 +14010,10 @@
         <v>181</v>
       </c>
       <c r="AH168" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI168" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="169" spans="1:35">
@@ -14084,10 +14087,10 @@
         <v>181</v>
       </c>
       <c r="AH169" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI169" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="170" spans="1:35">
@@ -14161,10 +14164,10 @@
         <v>181</v>
       </c>
       <c r="AH170" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI170" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="171" spans="1:35">
@@ -14238,10 +14241,10 @@
         <v>181</v>
       </c>
       <c r="AH171" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI171" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="172" spans="1:35">
@@ -14315,10 +14318,10 @@
         <v>181</v>
       </c>
       <c r="AH172" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI172" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="173" spans="1:35">
@@ -14392,10 +14395,10 @@
         <v>181</v>
       </c>
       <c r="AH173" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI173" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="174" spans="1:35">
@@ -14469,10 +14472,10 @@
         <v>181</v>
       </c>
       <c r="AH174" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI174" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="175" spans="1:35">
@@ -14546,10 +14549,10 @@
         <v>181</v>
       </c>
       <c r="AH175" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI175" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="176" spans="1:35">
@@ -14623,10 +14626,10 @@
         <v>181</v>
       </c>
       <c r="AH176" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI176" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="177" spans="1:35">
@@ -14700,10 +14703,10 @@
         <v>181</v>
       </c>
       <c r="AH177" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI177" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="178" spans="1:35">
@@ -14777,10 +14780,10 @@
         <v>181</v>
       </c>
       <c r="AH178" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI178" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="179" spans="1:35">
@@ -14854,10 +14857,10 @@
         <v>181</v>
       </c>
       <c r="AH179" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI179" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="180" spans="1:35">
@@ -14931,10 +14934,10 @@
         <v>181</v>
       </c>
       <c r="AH180" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI180" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="181" spans="1:35">
@@ -15008,10 +15011,10 @@
         <v>181</v>
       </c>
       <c r="AH181" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI181" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="182" spans="1:35">
@@ -15085,10 +15088,10 @@
         <v>181</v>
       </c>
       <c r="AH182" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI182" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="183" spans="1:35">
@@ -15156,10 +15159,10 @@
         <v>181</v>
       </c>
       <c r="AH183" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI183" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="184" spans="1:35">
@@ -15227,10 +15230,10 @@
         <v>181</v>
       </c>
       <c r="AH184" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI184" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="185" spans="1:35">
@@ -15298,10 +15301,10 @@
         <v>181</v>
       </c>
       <c r="AH185" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI185" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="186" spans="1:35">
@@ -15369,10 +15372,10 @@
         <v>181</v>
       </c>
       <c r="AH186" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI186" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="187" spans="1:35">
@@ -15440,10 +15443,10 @@
         <v>181</v>
       </c>
       <c r="AH187" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI187" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="188" spans="1:35">
@@ -15511,10 +15514,10 @@
         <v>181</v>
       </c>
       <c r="AH188" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI188" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="189" spans="1:35">
@@ -15582,10 +15585,10 @@
         <v>54</v>
       </c>
       <c r="AH189" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI189" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="190" spans="1:35">
@@ -15653,10 +15656,10 @@
         <v>54</v>
       </c>
       <c r="AH190" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI190" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="191" spans="1:35">
@@ -15724,10 +15727,10 @@
         <v>54</v>
       </c>
       <c r="AH191" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI191" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="192" spans="1:35">
@@ -15795,10 +15798,10 @@
         <v>54</v>
       </c>
       <c r="AH192" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI192" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="193" spans="1:35">
@@ -15866,10 +15869,10 @@
         <v>182</v>
       </c>
       <c r="AH193" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI193" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="194" spans="1:35">
@@ -15937,10 +15940,10 @@
         <v>55</v>
       </c>
       <c r="AH194" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI194" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="195" spans="1:35">
@@ -16008,10 +16011,10 @@
         <v>54</v>
       </c>
       <c r="AH195" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI195" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="196" spans="1:35">
@@ -16079,10 +16082,10 @@
         <v>54</v>
       </c>
       <c r="AH196" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI196" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="197" spans="1:35">
@@ -16150,10 +16153,10 @@
         <v>54</v>
       </c>
       <c r="AH197" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI197" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="198" spans="1:35">
@@ -16221,10 +16224,10 @@
         <v>182</v>
       </c>
       <c r="AH198" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI198" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="199" spans="1:35">
@@ -16292,10 +16295,10 @@
         <v>54</v>
       </c>
       <c r="AH199" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI199" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="200" spans="1:35">
@@ -16363,10 +16366,10 @@
         <v>182</v>
       </c>
       <c r="AH200" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI200" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="201" spans="1:35">
@@ -16434,10 +16437,10 @@
         <v>54</v>
       </c>
       <c r="AH201" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI201" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="202" spans="1:35">
@@ -16505,10 +16508,10 @@
         <v>54</v>
       </c>
       <c r="AH202" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI202" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="203" spans="1:35">
@@ -16576,10 +16579,10 @@
         <v>54</v>
       </c>
       <c r="AH203" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI203" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="204" spans="1:35">
@@ -16647,10 +16650,10 @@
         <v>54</v>
       </c>
       <c r="AH204" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI204" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="205" spans="1:35">
@@ -16718,10 +16721,10 @@
         <v>54</v>
       </c>
       <c r="AH205" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI205" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="206" spans="1:35">
@@ -16789,10 +16792,10 @@
         <v>54</v>
       </c>
       <c r="AH206" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI206" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="207" spans="1:35">
@@ -16860,10 +16863,10 @@
         <v>182</v>
       </c>
       <c r="AH207" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI207" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="208" spans="1:35">
@@ -16931,10 +16934,10 @@
         <v>55</v>
       </c>
       <c r="AH208" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI208" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="209" spans="1:35">
@@ -17005,10 +17008,10 @@
         <v>54</v>
       </c>
       <c r="AH209" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI209" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="210" spans="1:35">
@@ -17079,10 +17082,10 @@
         <v>54</v>
       </c>
       <c r="AH210" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI210" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="211" spans="1:35">
@@ -17153,10 +17156,10 @@
         <v>54</v>
       </c>
       <c r="AH211" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI211" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="212" spans="1:35">
@@ -17227,10 +17230,10 @@
         <v>54</v>
       </c>
       <c r="AH212" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI212" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="213" spans="1:35">
@@ -17298,10 +17301,10 @@
         <v>54</v>
       </c>
       <c r="AH213" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI213" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="214" spans="1:35">
@@ -17369,10 +17372,10 @@
         <v>54</v>
       </c>
       <c r="AH214" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI214" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="215" spans="1:35">
@@ -17437,10 +17440,10 @@
         <v>0</v>
       </c>
       <c r="AH215" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI215" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="216" spans="1:35">
@@ -17502,10 +17505,10 @@
         <v>0</v>
       </c>
       <c r="AH216" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI216" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="217" spans="1:35">
@@ -17573,13 +17576,13 @@
         <v>0</v>
       </c>
       <c r="AC217" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AH217" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI217" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="218" spans="1:35">
@@ -17650,10 +17653,10 @@
         <v>164</v>
       </c>
       <c r="AH218" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI218" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="219" spans="1:35">
@@ -17730,10 +17733,10 @@
         <v>168</v>
       </c>
       <c r="AH219" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI219" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="220" spans="1:35">
@@ -17810,10 +17813,10 @@
         <v>168</v>
       </c>
       <c r="AH220" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI220" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="221" spans="1:35">
@@ -17890,10 +17893,10 @@
         <v>169</v>
       </c>
       <c r="AH221" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI221" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="222" spans="1:35">
@@ -17970,10 +17973,10 @@
         <v>174</v>
       </c>
       <c r="AH222" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI222" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="223" spans="1:35">
@@ -18050,10 +18053,10 @@
         <v>168</v>
       </c>
       <c r="AH223" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI223" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="224" spans="1:35">
@@ -18130,10 +18133,10 @@
         <v>173</v>
       </c>
       <c r="AH224" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI224" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="225" spans="1:35">
@@ -18210,10 +18213,10 @@
         <v>168</v>
       </c>
       <c r="AH225" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI225" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="226" spans="1:35">
@@ -18290,10 +18293,10 @@
         <v>168</v>
       </c>
       <c r="AH226" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI226" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="227" spans="1:35">
@@ -18364,10 +18367,10 @@
         <v>167</v>
       </c>
       <c r="AH227" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI227" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="228" spans="1:35">
@@ -18438,10 +18441,10 @@
         <v>174</v>
       </c>
       <c r="AH228" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI228" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="229" spans="1:35">
@@ -18518,10 +18521,10 @@
         <v>168</v>
       </c>
       <c r="AH229" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI229" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="230" spans="1:35">
@@ -18598,10 +18601,10 @@
         <v>173</v>
       </c>
       <c r="AH230" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI230" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="231" spans="1:35">
@@ -18678,10 +18681,10 @@
         <v>168</v>
       </c>
       <c r="AH231" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI231" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="232" spans="1:35">
@@ -18758,10 +18761,10 @@
         <v>168</v>
       </c>
       <c r="AH232" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI232" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="233" spans="1:35">
@@ -18832,10 +18835,10 @@
         <v>167</v>
       </c>
       <c r="AH233" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI233" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="234" spans="1:35">
@@ -18906,10 +18909,10 @@
         <v>174</v>
       </c>
       <c r="AH234" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI234" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="235" spans="1:35">
@@ -18980,10 +18983,10 @@
         <v>171</v>
       </c>
       <c r="AH235" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI235" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="236" spans="1:35">
@@ -19057,10 +19060,10 @@
         <v>172</v>
       </c>
       <c r="AH236" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI236" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="237" spans="1:35">
@@ -19134,10 +19137,10 @@
         <v>168</v>
       </c>
       <c r="AH237" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI237" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="238" spans="1:35">
@@ -19211,10 +19214,10 @@
         <v>173</v>
       </c>
       <c r="AH238" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI238" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="239" spans="1:35">
@@ -19288,10 +19291,10 @@
         <v>168</v>
       </c>
       <c r="AH239" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI239" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="240" spans="1:35">
@@ -19365,10 +19368,10 @@
         <v>168</v>
       </c>
       <c r="AH240" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI240" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="241" spans="1:35">
@@ -19445,10 +19448,10 @@
         <v>167</v>
       </c>
       <c r="AH241" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI241" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="242" spans="1:35">
@@ -19522,10 +19525,10 @@
         <v>174</v>
       </c>
       <c r="AH242" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI242" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="243" spans="1:35">
@@ -19599,10 +19602,10 @@
         <v>169</v>
       </c>
       <c r="AH243" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI243" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="244" spans="1:35">
@@ -19676,10 +19679,10 @@
         <v>170</v>
       </c>
       <c r="AH244" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI244" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="245" spans="1:35">
@@ -19753,10 +19756,10 @@
         <v>171</v>
       </c>
       <c r="AH245" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI245" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="246" spans="1:35">
@@ -19833,10 +19836,10 @@
         <v>168</v>
       </c>
       <c r="AH246" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI246" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="247" spans="1:35">
@@ -19913,10 +19916,10 @@
         <v>168</v>
       </c>
       <c r="AH247" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI247" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="248" spans="1:35">
@@ -19993,10 +19996,10 @@
         <v>168</v>
       </c>
       <c r="AH248" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI248" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="249" spans="1:35">
@@ -20073,10 +20076,10 @@
         <v>174</v>
       </c>
       <c r="AH249" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI249" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="250" spans="1:35">
@@ -20153,10 +20156,10 @@
         <v>169</v>
       </c>
       <c r="AH250" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI250" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="251" spans="1:35">
@@ -20227,10 +20230,10 @@
         <v>170</v>
       </c>
       <c r="AH251" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI251" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="252" spans="1:35">
@@ -20301,10 +20304,10 @@
         <v>171</v>
       </c>
       <c r="AH252" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI252" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="253" spans="1:35">
@@ -20381,10 +20384,10 @@
         <v>168</v>
       </c>
       <c r="AH253" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI253" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="254" spans="1:35">
@@ -20458,10 +20461,10 @@
         <v>173</v>
       </c>
       <c r="AH254" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI254" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="255" spans="1:35">
@@ -20538,10 +20541,10 @@
         <v>168</v>
       </c>
       <c r="AH255" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI255" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="256" spans="1:35">
@@ -20618,10 +20621,10 @@
         <v>168</v>
       </c>
       <c r="AH256" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI256" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="257" spans="1:35">
@@ -20695,10 +20698,10 @@
         <v>167</v>
       </c>
       <c r="AH257" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI257" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="258" spans="1:35">
@@ -20772,10 +20775,10 @@
         <v>174</v>
       </c>
       <c r="AH258" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI258" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="259" spans="1:35">
@@ -20849,10 +20852,10 @@
         <v>169</v>
       </c>
       <c r="AH259" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI259" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="260" spans="1:35">
@@ -20926,10 +20929,10 @@
         <v>170</v>
       </c>
       <c r="AH260" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI260" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="261" spans="1:35">
@@ -21006,10 +21009,10 @@
         <v>174</v>
       </c>
       <c r="AH261" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI261" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="262" spans="1:35">
@@ -21080,10 +21083,10 @@
         <v>168</v>
       </c>
       <c r="AH262" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI262" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="263" spans="1:35">
@@ -21154,10 +21157,10 @@
         <v>168</v>
       </c>
       <c r="AH263" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI263" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="264" spans="1:35">
@@ -21228,10 +21231,10 @@
         <v>168</v>
       </c>
       <c r="AH264" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI264" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="265" spans="1:35">
@@ -21308,10 +21311,10 @@
         <v>179</v>
       </c>
       <c r="AH265" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI265" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="266" spans="1:35">
@@ -21388,10 +21391,10 @@
         <v>179</v>
       </c>
       <c r="AH266" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI266" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="267" spans="1:35">
@@ -21468,10 +21471,10 @@
         <v>178</v>
       </c>
       <c r="AH267" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI267" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="268" spans="1:35">
@@ -21539,10 +21542,10 @@
         <v>176</v>
       </c>
       <c r="AH268" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI268" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="269" spans="1:35">
@@ -21619,10 +21622,10 @@
         <v>175</v>
       </c>
       <c r="AH269" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI269" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="270" spans="1:35">
@@ -21690,10 +21693,10 @@
         <v>190</v>
       </c>
       <c r="AH270" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI270" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="271" spans="1:35">
@@ -21770,10 +21773,10 @@
         <v>190</v>
       </c>
       <c r="AH271" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI271" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="272" spans="1:35">
@@ -21847,10 +21850,10 @@
         <v>176</v>
       </c>
       <c r="AH272" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI272" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="273" spans="1:35">
@@ -21927,10 +21930,10 @@
         <v>177</v>
       </c>
       <c r="AH273" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI273" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="274" spans="1:35">
@@ -22004,10 +22007,10 @@
         <v>179</v>
       </c>
       <c r="AH274" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI274" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="275" spans="1:35">
@@ -22084,10 +22087,10 @@
         <v>179</v>
       </c>
       <c r="AH275" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI275" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="276" spans="1:35">
@@ -22161,10 +22164,10 @@
         <v>178</v>
       </c>
       <c r="AH276" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI276" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="277" spans="1:35">
@@ -22235,10 +22238,10 @@
         <v>176</v>
       </c>
       <c r="AH277" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI277" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="278" spans="1:35">
@@ -22312,10 +22315,10 @@
         <v>179</v>
       </c>
       <c r="AH278" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI278" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="279" spans="1:35">
@@ -22389,10 +22392,10 @@
         <v>179</v>
       </c>
       <c r="AH279" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI279" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="280" spans="1:35">
@@ -22469,10 +22472,10 @@
         <v>175</v>
       </c>
       <c r="AH280" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI280" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="281" spans="1:35">
@@ -22540,10 +22543,10 @@
         <v>190</v>
       </c>
       <c r="AH281" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI281" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="282" spans="1:35">
@@ -22617,10 +22620,10 @@
         <v>176</v>
       </c>
       <c r="AH282" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI282" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="283" spans="1:35">
@@ -22691,10 +22694,10 @@
         <v>179</v>
       </c>
       <c r="AH283" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI283" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="284" spans="1:35">
@@ -22765,10 +22768,10 @@
         <v>179</v>
       </c>
       <c r="AH284" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI284" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="285" spans="1:35">
@@ -22839,10 +22842,10 @@
         <v>177</v>
       </c>
       <c r="AH285" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI285" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="286" spans="1:35">
@@ -22916,10 +22919,10 @@
         <v>176</v>
       </c>
       <c r="AH286" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI286" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="287" spans="1:35">
@@ -22993,10 +22996,10 @@
         <v>176</v>
       </c>
       <c r="AH287" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI287" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="288" spans="1:35">
@@ -23073,10 +23076,10 @@
         <v>177</v>
       </c>
       <c r="AH288" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI288" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="289" spans="1:35">
@@ -23153,10 +23156,10 @@
         <v>180</v>
       </c>
       <c r="AH289" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI289" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="290" spans="1:35">
@@ -23230,10 +23233,10 @@
         <v>180</v>
       </c>
       <c r="AH290" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI290" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="291" spans="1:35">
@@ -23310,10 +23313,10 @@
         <v>180</v>
       </c>
       <c r="AH291" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI291" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="292" spans="1:35">
@@ -23384,10 +23387,10 @@
         <v>180</v>
       </c>
       <c r="AH292" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI292" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="293" spans="1:35">
@@ -23458,10 +23461,10 @@
         <v>180</v>
       </c>
       <c r="AH293" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI293" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="294" spans="1:35">
@@ -23532,10 +23535,10 @@
         <v>180</v>
       </c>
       <c r="AH294" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI294" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="295" spans="1:35">
@@ -23606,10 +23609,10 @@
         <v>180</v>
       </c>
       <c r="AH295" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI295" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="296" spans="1:35">
@@ -23680,10 +23683,10 @@
         <v>180</v>
       </c>
       <c r="AH296" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI296" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="297" spans="1:35">
@@ -23760,10 +23763,10 @@
         <v>180</v>
       </c>
       <c r="AH297" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI297" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="298" spans="1:35">
@@ -23834,10 +23837,10 @@
         <v>180</v>
       </c>
       <c r="AH298" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI298" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="299" spans="1:35">
@@ -23914,10 +23917,10 @@
         <v>180</v>
       </c>
       <c r="AH299" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI299" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="300" spans="1:35">
@@ -23988,10 +23991,10 @@
         <v>180</v>
       </c>
       <c r="AH300" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI300" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="301" spans="1:35">
@@ -24062,10 +24065,10 @@
         <v>180</v>
       </c>
       <c r="AH301" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI301" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="302" spans="1:35">
@@ -24136,10 +24139,10 @@
         <v>180</v>
       </c>
       <c r="AH302" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI302" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="303" spans="1:35">
@@ -24216,10 +24219,10 @@
         <v>180</v>
       </c>
       <c r="AH303" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI303" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="304" spans="1:35">
@@ -24290,10 +24293,10 @@
         <v>180</v>
       </c>
       <c r="AH304" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI304" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="305" spans="1:35">
@@ -24364,10 +24367,10 @@
         <v>180</v>
       </c>
       <c r="AH305" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI305" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="306" spans="1:35">
@@ -24438,10 +24441,10 @@
         <v>180</v>
       </c>
       <c r="AH306" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI306" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="307" spans="1:35">
@@ -24512,10 +24515,10 @@
         <v>180</v>
       </c>
       <c r="AH307" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI307" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="308" spans="1:35">
@@ -24586,10 +24589,10 @@
         <v>180</v>
       </c>
       <c r="AH308" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI308" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="309" spans="1:35">
@@ -24660,10 +24663,10 @@
         <v>180</v>
       </c>
       <c r="AH309" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI309" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="310" spans="1:35">
@@ -24740,10 +24743,10 @@
         <v>180</v>
       </c>
       <c r="AH310" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI310" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="311" spans="1:35">
@@ -24820,10 +24823,10 @@
         <v>180</v>
       </c>
       <c r="AH311" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI311" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="312" spans="1:35">
@@ -24900,10 +24903,10 @@
         <v>180</v>
       </c>
       <c r="AH312" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI312" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="313" spans="1:35">
@@ -24977,10 +24980,10 @@
         <v>180</v>
       </c>
       <c r="AH313" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI313" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="314" spans="1:35">
@@ -25054,10 +25057,10 @@
         <v>180</v>
       </c>
       <c r="AH314" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI314" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="315" spans="1:35">
@@ -25131,10 +25134,10 @@
         <v>181</v>
       </c>
       <c r="AH315" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI315" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="316" spans="1:35">
@@ -25208,10 +25211,10 @@
         <v>181</v>
       </c>
       <c r="AH316" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI316" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="317" spans="1:35">
@@ -25282,10 +25285,10 @@
         <v>181</v>
       </c>
       <c r="AH317" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI317" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="318" spans="1:35">
@@ -25356,10 +25359,10 @@
         <v>181</v>
       </c>
       <c r="AH318" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI318" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="319" spans="1:35">
@@ -25430,10 +25433,10 @@
         <v>181</v>
       </c>
       <c r="AH319" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI319" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="320" spans="1:35">
@@ -25504,10 +25507,10 @@
         <v>181</v>
       </c>
       <c r="AH320" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI320" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="321" spans="1:35">
@@ -25575,10 +25578,10 @@
         <v>181</v>
       </c>
       <c r="AH321" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI321" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="322" spans="1:35">
@@ -25652,10 +25655,10 @@
         <v>181</v>
       </c>
       <c r="AH322" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI322" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="323" spans="1:35">
@@ -25729,10 +25732,10 @@
         <v>181</v>
       </c>
       <c r="AH323" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI323" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="324" spans="1:35">
@@ -25806,10 +25809,10 @@
         <v>181</v>
       </c>
       <c r="AH324" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI324" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="325" spans="1:35">
@@ -25883,10 +25886,10 @@
         <v>181</v>
       </c>
       <c r="AH325" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI325" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="326" spans="1:35">
@@ -25960,10 +25963,10 @@
         <v>181</v>
       </c>
       <c r="AH326" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI326" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="327" spans="1:35">
@@ -26034,10 +26037,10 @@
         <v>181</v>
       </c>
       <c r="AH327" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI327" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="328" spans="1:35">
@@ -26108,10 +26111,10 @@
         <v>181</v>
       </c>
       <c r="AH328" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI328" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="329" spans="1:35">
@@ -26182,10 +26185,10 @@
         <v>181</v>
       </c>
       <c r="AH329" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AI329" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="330" spans="1:35">
@@ -26253,10 +26256,10 @@
         <v>181</v>
       </c>
       <c r="AH330" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI330" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="331" spans="1:35">
@@ -26324,10 +26327,10 @@
         <v>181</v>
       </c>
       <c r="AH331" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI331" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="332" spans="1:35">
@@ -26395,10 +26398,10 @@
         <v>181</v>
       </c>
       <c r="AH332" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI332" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="333" spans="1:35">
@@ -26466,10 +26469,10 @@
         <v>181</v>
       </c>
       <c r="AH333" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI333" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="334" spans="1:35">
@@ -26537,10 +26540,10 @@
         <v>181</v>
       </c>
       <c r="AH334" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI334" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="335" spans="1:35">
@@ -26608,10 +26611,10 @@
         <v>54</v>
       </c>
       <c r="AH335" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI335" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="336" spans="1:35">
@@ -26679,10 +26682,10 @@
         <v>54</v>
       </c>
       <c r="AH336" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI336" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="337" spans="1:35">
@@ -26750,10 +26753,10 @@
         <v>54</v>
       </c>
       <c r="AH337" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI337" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="338" spans="1:35">
@@ -26821,10 +26824,10 @@
         <v>54</v>
       </c>
       <c r="AH338" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI338" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="339" spans="1:35">
@@ -26892,10 +26895,10 @@
         <v>182</v>
       </c>
       <c r="AH339" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI339" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="340" spans="1:35">
@@ -26963,10 +26966,10 @@
         <v>182</v>
       </c>
       <c r="AH340" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI340" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="341" spans="1:35">
@@ -27034,10 +27037,10 @@
         <v>182</v>
       </c>
       <c r="AH341" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI341" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="342" spans="1:35">
@@ -27105,10 +27108,10 @@
         <v>182</v>
       </c>
       <c r="AH342" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI342" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="343" spans="1:35">
@@ -27176,10 +27179,10 @@
         <v>182</v>
       </c>
       <c r="AH343" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI343" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="344" spans="1:35">
@@ -27247,10 +27250,10 @@
         <v>182</v>
       </c>
       <c r="AH344" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI344" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="345" spans="1:35">
@@ -27318,10 +27321,10 @@
         <v>182</v>
       </c>
       <c r="AH345" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI345" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="346" spans="1:35">
@@ -27389,10 +27392,10 @@
         <v>182</v>
       </c>
       <c r="AH346" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI346" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="347" spans="1:35">
@@ -27460,10 +27463,10 @@
         <v>182</v>
       </c>
       <c r="AH347" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI347" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="348" spans="1:35">
@@ -27534,10 +27537,10 @@
         <v>54</v>
       </c>
       <c r="AH348" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI348" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="349" spans="1:35">
@@ -27608,10 +27611,10 @@
         <v>54</v>
       </c>
       <c r="AH349" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI349" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="350" spans="1:35">
@@ -27682,10 +27685,10 @@
         <v>54</v>
       </c>
       <c r="AH350" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI350" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="351" spans="1:35">
@@ -27753,13 +27756,13 @@
         <v>0</v>
       </c>
       <c r="AC351" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AH351" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI351" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="352" spans="1:35">
@@ -27830,10 +27833,10 @@
         <v>159</v>
       </c>
       <c r="AH352" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI352" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="353" spans="1:35">
@@ -27904,10 +27907,10 @@
         <v>165</v>
       </c>
       <c r="AH353" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI353" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="354" spans="1:35">
@@ -27975,10 +27978,10 @@
         <v>171</v>
       </c>
       <c r="AH354" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI354" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="355" spans="1:35">
@@ -28046,10 +28049,10 @@
         <v>171</v>
       </c>
       <c r="AH355" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI355" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="356" spans="1:35">
@@ -28126,10 +28129,10 @@
         <v>172</v>
       </c>
       <c r="AH356" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI356" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="357" spans="1:35">
@@ -28200,24 +28203,24 @@
         <v>172</v>
       </c>
       <c r="AH357" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AI357" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="358" spans="1:35">
       <c r="A358">
-        <v>6404</v>
+        <v>6704</v>
       </c>
       <c r="B358" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C358" t="s">
         <v>50</v>
       </c>
       <c r="D358" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E358" t="s">
         <v>54</v>
@@ -28226,7 +28229,7 @@
         <v>56</v>
       </c>
       <c r="G358">
-        <v>7025</v>
+        <v>11874</v>
       </c>
       <c r="H358">
         <v>0</v>
@@ -28235,10 +28238,13 @@
         <v>63</v>
       </c>
       <c r="J358" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="N358" s="1">
-        <v>46288</v>
+        <v>46281</v>
+      </c>
+      <c r="O358" t="s">
+        <v>155</v>
       </c>
       <c r="P358">
         <v>8</v>
@@ -28247,7 +28253,7 @@
         <v>2026</v>
       </c>
       <c r="R358">
-        <v>16962338</v>
+        <v>18273589</v>
       </c>
       <c r="S358" t="s">
         <v>180</v>
@@ -28256,16 +28262,16 @@
         <v>191</v>
       </c>
       <c r="U358" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="V358" s="1">
-        <v>46282.54038741898</v>
+        <v>46282.70138376157</v>
       </c>
       <c r="W358">
-        <v>-6</v>
+        <v>1</v>
       </c>
       <c r="X358" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="Y358" t="s">
         <v>338</v>
@@ -28277,24 +28283,24 @@
         <v>180</v>
       </c>
       <c r="AH358" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AI358" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="359" spans="1:35">
       <c r="A359">
-        <v>5417</v>
+        <v>6705</v>
       </c>
       <c r="B359" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C359" t="s">
         <v>50</v>
       </c>
       <c r="D359" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E359" t="s">
         <v>54</v>
@@ -28303,61 +28309,64 @@
         <v>56</v>
       </c>
       <c r="G359">
-        <v>9086</v>
+        <v>11874</v>
       </c>
       <c r="H359">
         <v>0</v>
       </c>
       <c r="I359" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J359" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="N359" s="1">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="O359" t="s">
         <v>155</v>
       </c>
       <c r="P359">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q359">
         <v>2026</v>
       </c>
       <c r="R359">
-        <v>17399363</v>
+        <v>18239293</v>
       </c>
       <c r="S359" t="s">
-        <v>181</v>
+        <v>180</v>
+      </c>
+      <c r="T359" t="s">
+        <v>191</v>
       </c>
       <c r="U359" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="V359" s="1">
-        <v>46282.36440621527</v>
+        <v>46282.7013840625</v>
       </c>
       <c r="W359">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X359" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Y359" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AB359">
         <v>0</v>
       </c>
       <c r="AC359" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AH359" t="s">
         <v>350</v>
       </c>
       <c r="AI359" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="360" spans="1:35">
@@ -28380,43 +28389,43 @@
         <v>56</v>
       </c>
       <c r="G360">
-        <v>9086</v>
+        <v>7025</v>
       </c>
       <c r="H360">
         <v>0</v>
       </c>
       <c r="I360" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J360" t="s">
-        <v>144</v>
+        <v>121</v>
       </c>
       <c r="N360" s="1">
-        <v>46282</v>
-      </c>
-      <c r="O360" t="s">
-        <v>155</v>
+        <v>46288</v>
       </c>
       <c r="P360">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q360">
         <v>2026</v>
       </c>
       <c r="R360">
-        <v>16962380</v>
+        <v>16962338</v>
       </c>
       <c r="S360" t="s">
-        <v>181</v>
+        <v>180</v>
+      </c>
+      <c r="T360" t="s">
+        <v>191</v>
       </c>
       <c r="U360" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="V360" s="1">
-        <v>46282.36462596065</v>
+        <v>46282.54038741898</v>
       </c>
       <c r="W360">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="X360" t="s">
         <v>205</v>
@@ -28428,21 +28437,21 @@
         <v>0</v>
       </c>
       <c r="AC360" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AH360" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AI360" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="361" spans="1:35">
       <c r="A361">
-        <v>6486</v>
+        <v>5417</v>
       </c>
       <c r="B361" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C361" t="s">
         <v>50</v>
@@ -28481,7 +28490,7 @@
         <v>2026</v>
       </c>
       <c r="R361">
-        <v>16976270</v>
+        <v>17399363</v>
       </c>
       <c r="S361" t="s">
         <v>181</v>
@@ -28490,16 +28499,16 @@
         <v>194</v>
       </c>
       <c r="V361" s="1">
-        <v>46282.36464421296</v>
+        <v>46282.36440621527</v>
       </c>
       <c r="W361">
         <v>0</v>
       </c>
       <c r="X361" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Y361" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AB361">
         <v>0</v>
@@ -28508,24 +28517,24 @@
         <v>181</v>
       </c>
       <c r="AH361" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI361" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="362" spans="1:35">
       <c r="A362">
-        <v>6548</v>
+        <v>6404</v>
       </c>
       <c r="B362" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="C362" t="s">
         <v>50</v>
       </c>
       <c r="D362" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E362" t="s">
         <v>54</v>
@@ -28558,7 +28567,7 @@
         <v>2026</v>
       </c>
       <c r="R362">
-        <v>17222865</v>
+        <v>16962380</v>
       </c>
       <c r="S362" t="s">
         <v>181</v>
@@ -28567,16 +28576,16 @@
         <v>194</v>
       </c>
       <c r="V362" s="1">
-        <v>46282.36467337963</v>
+        <v>46282.36462596065</v>
       </c>
       <c r="W362">
         <v>0</v>
       </c>
       <c r="X362" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="Y362" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AB362">
         <v>0</v>
@@ -28585,18 +28594,18 @@
         <v>181</v>
       </c>
       <c r="AH362" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI362" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="363" spans="1:35">
       <c r="A363">
-        <v>6627</v>
+        <v>6486</v>
       </c>
       <c r="B363" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C363" t="s">
         <v>50</v>
@@ -28605,7 +28614,7 @@
         <v>51</v>
       </c>
       <c r="E363" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F363" t="s">
         <v>56</v>
@@ -28635,7 +28644,7 @@
         <v>2026</v>
       </c>
       <c r="R363">
-        <v>17042587</v>
+        <v>16976270</v>
       </c>
       <c r="S363" t="s">
         <v>181</v>
@@ -28644,16 +28653,16 @@
         <v>194</v>
       </c>
       <c r="V363" s="1">
-        <v>46282.36469679398</v>
+        <v>46282.36464421296</v>
       </c>
       <c r="W363">
         <v>0</v>
       </c>
       <c r="X363" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="Y363" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AB363">
         <v>0</v>
@@ -28662,27 +28671,27 @@
         <v>181</v>
       </c>
       <c r="AH363" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI363" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="364" spans="1:35">
       <c r="A364">
-        <v>6628</v>
+        <v>6548</v>
       </c>
       <c r="B364" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C364" t="s">
         <v>50</v>
       </c>
       <c r="D364" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E364" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F364" t="s">
         <v>56</v>
@@ -28712,7 +28721,7 @@
         <v>2026</v>
       </c>
       <c r="R364">
-        <v>16960074</v>
+        <v>17222865</v>
       </c>
       <c r="S364" t="s">
         <v>181</v>
@@ -28721,16 +28730,16 @@
         <v>194</v>
       </c>
       <c r="V364" s="1">
-        <v>46282.36469869213</v>
+        <v>46282.36467337963</v>
       </c>
       <c r="W364">
         <v>0</v>
       </c>
       <c r="X364" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Y364" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AB364">
         <v>0</v>
@@ -28739,27 +28748,27 @@
         <v>181</v>
       </c>
       <c r="AH364" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI364" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="365" spans="1:35">
       <c r="A365">
-        <v>6703</v>
+        <v>6627</v>
       </c>
       <c r="B365" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C365" t="s">
         <v>50</v>
       </c>
       <c r="D365" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E365" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F365" t="s">
         <v>56</v>
@@ -28789,7 +28798,7 @@
         <v>2026</v>
       </c>
       <c r="R365">
-        <v>17941217</v>
+        <v>17042587</v>
       </c>
       <c r="S365" t="s">
         <v>181</v>
@@ -28798,16 +28807,16 @@
         <v>194</v>
       </c>
       <c r="V365" s="1">
-        <v>46282.36473159722</v>
+        <v>46282.36469679398</v>
       </c>
       <c r="W365">
         <v>0</v>
       </c>
       <c r="X365" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="Y365" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AB365">
         <v>0</v>
@@ -28816,27 +28825,27 @@
         <v>181</v>
       </c>
       <c r="AH365" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI365" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="366" spans="1:35">
       <c r="A366">
-        <v>6704</v>
+        <v>6628</v>
       </c>
       <c r="B366" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C366" t="s">
         <v>50</v>
       </c>
       <c r="D366" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E366" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F366" t="s">
         <v>56</v>
@@ -28866,7 +28875,7 @@
         <v>2026</v>
       </c>
       <c r="R366">
-        <v>17952444</v>
+        <v>16960074</v>
       </c>
       <c r="S366" t="s">
         <v>181</v>
@@ -28875,16 +28884,16 @@
         <v>194</v>
       </c>
       <c r="V366" s="1">
-        <v>46282.36473394676</v>
+        <v>46282.36469869213</v>
       </c>
       <c r="W366">
         <v>0</v>
       </c>
       <c r="X366" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="Y366" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AB366">
         <v>0</v>
@@ -28893,24 +28902,24 @@
         <v>181</v>
       </c>
       <c r="AH366" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI366" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="367" spans="1:35">
       <c r="A367">
-        <v>6705</v>
+        <v>6703</v>
       </c>
       <c r="B367" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C367" t="s">
         <v>50</v>
       </c>
       <c r="D367" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E367" t="s">
         <v>54</v>
@@ -28943,7 +28952,7 @@
         <v>2026</v>
       </c>
       <c r="R367">
-        <v>17952624</v>
+        <v>17941217</v>
       </c>
       <c r="S367" t="s">
         <v>181</v>
@@ -28952,16 +28961,16 @@
         <v>194</v>
       </c>
       <c r="V367" s="1">
-        <v>46282.36473579861</v>
+        <v>46282.36473159722</v>
       </c>
       <c r="W367">
         <v>0</v>
       </c>
       <c r="X367" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="Y367" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AB367">
         <v>0</v>
@@ -28970,24 +28979,24 @@
         <v>181</v>
       </c>
       <c r="AH367" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI367" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="368" spans="1:35">
       <c r="A368">
-        <v>6779</v>
+        <v>6704</v>
       </c>
       <c r="B368" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C368" t="s">
         <v>50</v>
       </c>
       <c r="D368" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E368" t="s">
         <v>54</v>
@@ -29020,7 +29029,7 @@
         <v>2026</v>
       </c>
       <c r="R368">
-        <v>18056801</v>
+        <v>17952444</v>
       </c>
       <c r="S368" t="s">
         <v>181</v>
@@ -29029,7 +29038,7 @@
         <v>194</v>
       </c>
       <c r="V368" s="1">
-        <v>46282.36475297454</v>
+        <v>46282.36473394676</v>
       </c>
       <c r="W368">
         <v>0</v>
@@ -29038,7 +29047,7 @@
         <v>200</v>
       </c>
       <c r="Y368" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AB368">
         <v>0</v>
@@ -29047,18 +29056,18 @@
         <v>181</v>
       </c>
       <c r="AH368" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI368" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="369" spans="1:35">
       <c r="A369">
-        <v>6945</v>
+        <v>6705</v>
       </c>
       <c r="B369" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C369" t="s">
         <v>50</v>
@@ -29070,7 +29079,7 @@
         <v>54</v>
       </c>
       <c r="F369" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G369">
         <v>9086</v>
@@ -29097,7 +29106,7 @@
         <v>2026</v>
       </c>
       <c r="R369">
-        <v>18164551</v>
+        <v>17952624</v>
       </c>
       <c r="S369" t="s">
         <v>181</v>
@@ -29106,16 +29115,16 @@
         <v>194</v>
       </c>
       <c r="V369" s="1">
-        <v>46282.36486408565</v>
+        <v>46282.36473579861</v>
       </c>
       <c r="W369">
         <v>0</v>
       </c>
       <c r="X369" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Y369" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AB369">
         <v>0</v>
@@ -29124,30 +29133,30 @@
         <v>181</v>
       </c>
       <c r="AH369" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI369" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="370" spans="1:35">
       <c r="A370">
-        <v>6949</v>
+        <v>6779</v>
       </c>
       <c r="B370" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C370" t="s">
         <v>50</v>
       </c>
       <c r="D370" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E370" t="s">
         <v>54</v>
       </c>
       <c r="F370" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G370">
         <v>9086</v>
@@ -29174,7 +29183,7 @@
         <v>2026</v>
       </c>
       <c r="R370">
-        <v>18178187</v>
+        <v>18056801</v>
       </c>
       <c r="S370" t="s">
         <v>181</v>
@@ -29183,13 +29192,13 @@
         <v>194</v>
       </c>
       <c r="V370" s="1">
-        <v>46282.36487561343</v>
+        <v>46282.36475297454</v>
       </c>
       <c r="W370">
         <v>0</v>
       </c>
       <c r="X370" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Y370" t="s">
         <v>340</v>
@@ -29201,24 +29210,24 @@
         <v>181</v>
       </c>
       <c r="AH370" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI370" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="371" spans="1:35">
       <c r="A371">
-        <v>6962</v>
+        <v>6945</v>
       </c>
       <c r="B371" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C371" t="s">
         <v>50</v>
       </c>
       <c r="D371" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E371" t="s">
         <v>54</v>
@@ -29251,7 +29260,7 @@
         <v>2026</v>
       </c>
       <c r="R371">
-        <v>18188774</v>
+        <v>18164551</v>
       </c>
       <c r="S371" t="s">
         <v>181</v>
@@ -29260,16 +29269,16 @@
         <v>194</v>
       </c>
       <c r="V371" s="1">
-        <v>46282.36486778935</v>
+        <v>46282.36486408565</v>
       </c>
       <c r="W371">
         <v>0</v>
       </c>
       <c r="X371" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Y371" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AB371">
         <v>0</v>
@@ -29278,24 +29287,24 @@
         <v>181</v>
       </c>
       <c r="AH371" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI371" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="372" spans="1:35">
       <c r="A372">
-        <v>6963</v>
+        <v>6949</v>
       </c>
       <c r="B372" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C372" t="s">
         <v>50</v>
       </c>
       <c r="D372" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E372" t="s">
         <v>54</v>
@@ -29328,7 +29337,7 @@
         <v>2026</v>
       </c>
       <c r="R372">
-        <v>18188680</v>
+        <v>18178187</v>
       </c>
       <c r="S372" t="s">
         <v>181</v>
@@ -29337,16 +29346,16 @@
         <v>194</v>
       </c>
       <c r="V372" s="1">
-        <v>46282.36486851852</v>
+        <v>46282.36487561343</v>
       </c>
       <c r="W372">
         <v>0</v>
       </c>
       <c r="X372" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="Y372" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AB372">
         <v>0</v>
@@ -29355,48 +29364,48 @@
         <v>181</v>
       </c>
       <c r="AH372" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI372" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="373" spans="1:35">
       <c r="A373">
-        <v>5417</v>
+        <v>6962</v>
       </c>
       <c r="B373" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C373" t="s">
         <v>50</v>
       </c>
       <c r="D373" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E373" t="s">
         <v>54</v>
       </c>
       <c r="F373" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G373">
-        <v>9088</v>
+        <v>9086</v>
       </c>
       <c r="H373">
         <v>0</v>
       </c>
       <c r="I373" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J373" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N373" s="1">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="O373" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P373">
         <v>9</v>
@@ -29405,45 +29414,45 @@
         <v>2026</v>
       </c>
       <c r="R373">
-        <v>17399383</v>
+        <v>18188774</v>
       </c>
       <c r="S373" t="s">
-        <v>54</v>
+        <v>181</v>
       </c>
       <c r="U373" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="V373" s="1">
-        <v>46282.3651903588</v>
+        <v>46282.36486778935</v>
       </c>
       <c r="W373">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X373" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="Y373" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AB373">
         <v>0</v>
       </c>
       <c r="AC373" t="s">
-        <v>54</v>
+        <v>181</v>
       </c>
       <c r="AH373" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI373" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="374" spans="1:35">
       <c r="A374">
-        <v>6404</v>
+        <v>6963</v>
       </c>
       <c r="B374" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C374" t="s">
         <v>50</v>
@@ -29455,25 +29464,25 @@
         <v>54</v>
       </c>
       <c r="F374" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G374">
-        <v>9088</v>
+        <v>9086</v>
       </c>
       <c r="H374">
         <v>0</v>
       </c>
       <c r="I374" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J374" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N374" s="1">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="O374" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P374">
         <v>9</v>
@@ -29482,45 +29491,45 @@
         <v>2026</v>
       </c>
       <c r="R374">
-        <v>16962400</v>
+        <v>18188680</v>
       </c>
       <c r="S374" t="s">
-        <v>54</v>
+        <v>181</v>
       </c>
       <c r="U374" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="V374" s="1">
-        <v>46282.36525856482</v>
+        <v>46282.36486851852</v>
       </c>
       <c r="W374">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X374" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="Y374" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AB374">
         <v>0</v>
       </c>
       <c r="AC374" t="s">
-        <v>54</v>
+        <v>181</v>
       </c>
       <c r="AH374" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI374" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="375" spans="1:35">
       <c r="A375">
-        <v>6486</v>
+        <v>5417</v>
       </c>
       <c r="B375" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C375" t="s">
         <v>50</v>
@@ -29559,7 +29568,7 @@
         <v>2026</v>
       </c>
       <c r="R375">
-        <v>16976290</v>
+        <v>17399383</v>
       </c>
       <c r="S375" t="s">
         <v>54</v>
@@ -29568,16 +29577,16 @@
         <v>193</v>
       </c>
       <c r="V375" s="1">
-        <v>46282.36526855324</v>
+        <v>46282.3651903588</v>
       </c>
       <c r="W375">
         <v>-1</v>
       </c>
       <c r="X375" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Y375" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AB375">
         <v>0</v>
@@ -29586,24 +29595,24 @@
         <v>54</v>
       </c>
       <c r="AH375" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI375" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="376" spans="1:35">
       <c r="A376">
-        <v>6548</v>
+        <v>6404</v>
       </c>
       <c r="B376" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="C376" t="s">
         <v>50</v>
       </c>
       <c r="D376" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E376" t="s">
         <v>54</v>
@@ -29636,7 +29645,7 @@
         <v>2026</v>
       </c>
       <c r="R376">
-        <v>17222899</v>
+        <v>16962400</v>
       </c>
       <c r="S376" t="s">
         <v>54</v>
@@ -29645,16 +29654,16 @@
         <v>193</v>
       </c>
       <c r="V376" s="1">
-        <v>46282.36527959491</v>
+        <v>46282.36525856482</v>
       </c>
       <c r="W376">
         <v>-1</v>
       </c>
       <c r="X376" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="Y376" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AB376">
         <v>0</v>
@@ -29663,18 +29672,18 @@
         <v>54</v>
       </c>
       <c r="AH376" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI376" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="377" spans="1:35">
       <c r="A377">
-        <v>6627</v>
+        <v>6486</v>
       </c>
       <c r="B377" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C377" t="s">
         <v>50</v>
@@ -29683,7 +29692,7 @@
         <v>51</v>
       </c>
       <c r="E377" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F377" t="s">
         <v>56</v>
@@ -29713,54 +29722,54 @@
         <v>2026</v>
       </c>
       <c r="R377">
-        <v>17042627</v>
+        <v>16976290</v>
       </c>
       <c r="S377" t="s">
-        <v>182</v>
+        <v>54</v>
       </c>
       <c r="U377" t="s">
         <v>193</v>
       </c>
       <c r="V377" s="1">
-        <v>46282.36528526621</v>
+        <v>46282.36526855324</v>
       </c>
       <c r="W377">
         <v>-1</v>
       </c>
       <c r="X377" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="Y377" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AB377">
         <v>0</v>
       </c>
       <c r="AC377" t="s">
-        <v>182</v>
+        <v>54</v>
       </c>
       <c r="AH377" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI377" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="378" spans="1:35">
       <c r="A378">
-        <v>6628</v>
+        <v>6548</v>
       </c>
       <c r="B378" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C378" t="s">
         <v>50</v>
       </c>
       <c r="D378" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E378" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F378" t="s">
         <v>56</v>
@@ -29790,54 +29799,54 @@
         <v>2026</v>
       </c>
       <c r="R378">
-        <v>16960098</v>
+        <v>17222899</v>
       </c>
       <c r="S378" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="U378" t="s">
         <v>193</v>
       </c>
       <c r="V378" s="1">
-        <v>46282.36528619213</v>
+        <v>46282.36527959491</v>
       </c>
       <c r="W378">
         <v>-1</v>
       </c>
       <c r="X378" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Y378" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AB378">
         <v>0</v>
       </c>
       <c r="AC378" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AH378" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI378" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="379" spans="1:35">
       <c r="A379">
-        <v>6703</v>
+        <v>6627</v>
       </c>
       <c r="B379" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C379" t="s">
         <v>50</v>
       </c>
       <c r="D379" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E379" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F379" t="s">
         <v>56</v>
@@ -29867,54 +29876,54 @@
         <v>2026</v>
       </c>
       <c r="R379">
-        <v>17941237</v>
+        <v>17042627</v>
       </c>
       <c r="S379" t="s">
-        <v>54</v>
+        <v>182</v>
       </c>
       <c r="U379" t="s">
         <v>193</v>
       </c>
       <c r="V379" s="1">
-        <v>46282.36529351852</v>
+        <v>46282.36528526621</v>
       </c>
       <c r="W379">
         <v>-1</v>
       </c>
       <c r="X379" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="Y379" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AB379">
         <v>0</v>
       </c>
       <c r="AC379" t="s">
-        <v>54</v>
+        <v>182</v>
       </c>
       <c r="AH379" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI379" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="380" spans="1:35">
       <c r="A380">
-        <v>6704</v>
+        <v>6628</v>
       </c>
       <c r="B380" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C380" t="s">
         <v>50</v>
       </c>
       <c r="D380" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E380" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F380" t="s">
         <v>56</v>
@@ -29944,51 +29953,51 @@
         <v>2026</v>
       </c>
       <c r="R380">
-        <v>17952466</v>
+        <v>16960098</v>
       </c>
       <c r="S380" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="U380" t="s">
         <v>193</v>
       </c>
       <c r="V380" s="1">
-        <v>46282.36529424768</v>
+        <v>46282.36528619213</v>
       </c>
       <c r="W380">
         <v>-1</v>
       </c>
       <c r="X380" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="Y380" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AB380">
         <v>0</v>
       </c>
       <c r="AC380" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AH380" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI380" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="381" spans="1:35">
       <c r="A381">
-        <v>6705</v>
+        <v>6703</v>
       </c>
       <c r="B381" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C381" t="s">
         <v>50</v>
       </c>
       <c r="D381" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E381" t="s">
         <v>54</v>
@@ -30021,7 +30030,7 @@
         <v>2026</v>
       </c>
       <c r="R381">
-        <v>17952646</v>
+        <v>17941237</v>
       </c>
       <c r="S381" t="s">
         <v>54</v>
@@ -30030,16 +30039,16 @@
         <v>193</v>
       </c>
       <c r="V381" s="1">
-        <v>46282.36529490741</v>
+        <v>46282.36529351852</v>
       </c>
       <c r="W381">
         <v>-1</v>
       </c>
       <c r="X381" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="Y381" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AB381">
         <v>0</v>
@@ -30048,24 +30057,24 @@
         <v>54</v>
       </c>
       <c r="AH381" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI381" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="382" spans="1:35">
       <c r="A382">
-        <v>6779</v>
+        <v>6704</v>
       </c>
       <c r="B382" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C382" t="s">
         <v>50</v>
       </c>
       <c r="D382" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E382" t="s">
         <v>54</v>
@@ -30098,16 +30107,16 @@
         <v>2026</v>
       </c>
       <c r="R382">
-        <v>18056821</v>
+        <v>17952466</v>
       </c>
       <c r="S382" t="s">
-        <v>182</v>
+        <v>54</v>
       </c>
       <c r="U382" t="s">
         <v>193</v>
       </c>
       <c r="V382" s="1">
-        <v>46282.36529869213</v>
+        <v>46282.36529424768</v>
       </c>
       <c r="W382">
         <v>-1</v>
@@ -30116,27 +30125,27 @@
         <v>200</v>
       </c>
       <c r="Y382" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AB382">
         <v>0</v>
       </c>
       <c r="AC382" t="s">
-        <v>182</v>
+        <v>54</v>
       </c>
       <c r="AH382" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI382" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="383" spans="1:35">
       <c r="A383">
-        <v>6945</v>
+        <v>6705</v>
       </c>
       <c r="B383" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C383" t="s">
         <v>50</v>
@@ -30148,7 +30157,7 @@
         <v>54</v>
       </c>
       <c r="F383" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G383">
         <v>9088</v>
@@ -30175,7 +30184,7 @@
         <v>2026</v>
       </c>
       <c r="R383">
-        <v>18164565</v>
+        <v>17952646</v>
       </c>
       <c r="S383" t="s">
         <v>54</v>
@@ -30184,16 +30193,16 @@
         <v>193</v>
       </c>
       <c r="V383" s="1">
-        <v>46282.36531149306</v>
+        <v>46282.36529490741</v>
       </c>
       <c r="W383">
         <v>-1</v>
       </c>
       <c r="X383" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Y383" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AB383">
         <v>0</v>
@@ -30202,30 +30211,30 @@
         <v>54</v>
       </c>
       <c r="AH383" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI383" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="384" spans="1:35">
       <c r="A384">
-        <v>6949</v>
+        <v>6779</v>
       </c>
       <c r="B384" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C384" t="s">
         <v>50</v>
       </c>
       <c r="D384" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E384" t="s">
         <v>54</v>
       </c>
       <c r="F384" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G384">
         <v>9088</v>
@@ -30252,7 +30261,7 @@
         <v>2026</v>
       </c>
       <c r="R384">
-        <v>18178199</v>
+        <v>18056821</v>
       </c>
       <c r="S384" t="s">
         <v>182</v>
@@ -30261,13 +30270,13 @@
         <v>193</v>
       </c>
       <c r="V384" s="1">
-        <v>46282.36531554398</v>
+        <v>46282.36529869213</v>
       </c>
       <c r="W384">
         <v>-1</v>
       </c>
       <c r="X384" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Y384" t="s">
         <v>342</v>
@@ -30279,24 +30288,24 @@
         <v>182</v>
       </c>
       <c r="AH384" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI384" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="385" spans="1:35">
       <c r="A385">
-        <v>6962</v>
+        <v>6945</v>
       </c>
       <c r="B385" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C385" t="s">
         <v>50</v>
       </c>
       <c r="D385" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E385" t="s">
         <v>54</v>
@@ -30329,7 +30338,7 @@
         <v>2026</v>
       </c>
       <c r="R385">
-        <v>18188788</v>
+        <v>18164565</v>
       </c>
       <c r="S385" t="s">
         <v>54</v>
@@ -30338,16 +30347,16 @@
         <v>193</v>
       </c>
       <c r="V385" s="1">
-        <v>46282.36531253472</v>
+        <v>46282.36531149306</v>
       </c>
       <c r="W385">
         <v>-1</v>
       </c>
       <c r="X385" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Y385" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AB385">
         <v>0</v>
@@ -30356,24 +30365,24 @@
         <v>54</v>
       </c>
       <c r="AH385" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI385" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="386" spans="1:35">
       <c r="A386">
-        <v>6963</v>
+        <v>6949</v>
       </c>
       <c r="B386" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C386" t="s">
         <v>50</v>
       </c>
       <c r="D386" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E386" t="s">
         <v>54</v>
@@ -30406,45 +30415,45 @@
         <v>2026</v>
       </c>
       <c r="R386">
-        <v>18188694</v>
+        <v>18178199</v>
       </c>
       <c r="S386" t="s">
-        <v>54</v>
+        <v>182</v>
       </c>
       <c r="U386" t="s">
         <v>193</v>
       </c>
       <c r="V386" s="1">
-        <v>46282.36531288194</v>
+        <v>46282.36531554398</v>
       </c>
       <c r="W386">
         <v>-1</v>
       </c>
       <c r="X386" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="Y386" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AB386">
         <v>0</v>
       </c>
       <c r="AC386" t="s">
-        <v>54</v>
+        <v>182</v>
       </c>
       <c r="AH386" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AI386" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="387" spans="1:35">
       <c r="A387">
-        <v>6404</v>
+        <v>6962</v>
       </c>
       <c r="B387" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C387" t="s">
         <v>50</v>
@@ -30456,10 +30465,10 @@
         <v>54</v>
       </c>
       <c r="F387" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G387">
-        <v>7027</v>
+        <v>9088</v>
       </c>
       <c r="H387">
         <v>0</v>
@@ -30468,19 +30477,22 @@
         <v>65</v>
       </c>
       <c r="J387" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="N387" s="1">
-        <v>46289</v>
+        <v>46283</v>
+      </c>
+      <c r="O387" t="s">
+        <v>154</v>
       </c>
       <c r="P387">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q387">
         <v>2026</v>
       </c>
       <c r="R387">
-        <v>16962348</v>
+        <v>18188788</v>
       </c>
       <c r="S387" t="s">
         <v>54</v>
@@ -30489,28 +30501,179 @@
         <v>193</v>
       </c>
       <c r="V387" s="1">
+        <v>46282.36531253472</v>
+      </c>
+      <c r="W387">
+        <v>-1</v>
+      </c>
+      <c r="X387" t="s">
+        <v>199</v>
+      </c>
+      <c r="Y387" t="s">
+        <v>342</v>
+      </c>
+      <c r="AB387">
+        <v>0</v>
+      </c>
+      <c r="AC387" t="s">
+        <v>54</v>
+      </c>
+      <c r="AH387" t="s">
+        <v>351</v>
+      </c>
+      <c r="AI387" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="388" spans="1:35">
+      <c r="A388">
+        <v>6963</v>
+      </c>
+      <c r="B388" t="s">
+        <v>41</v>
+      </c>
+      <c r="C388" t="s">
+        <v>50</v>
+      </c>
+      <c r="D388" t="s">
+        <v>53</v>
+      </c>
+      <c r="E388" t="s">
+        <v>54</v>
+      </c>
+      <c r="F388" t="s">
+        <v>57</v>
+      </c>
+      <c r="G388">
+        <v>9088</v>
+      </c>
+      <c r="H388">
+        <v>0</v>
+      </c>
+      <c r="I388" t="s">
+        <v>65</v>
+      </c>
+      <c r="J388" t="s">
+        <v>145</v>
+      </c>
+      <c r="N388" s="1">
+        <v>46283</v>
+      </c>
+      <c r="O388" t="s">
+        <v>154</v>
+      </c>
+      <c r="P388">
+        <v>9</v>
+      </c>
+      <c r="Q388">
+        <v>2026</v>
+      </c>
+      <c r="R388">
+        <v>18188694</v>
+      </c>
+      <c r="S388" t="s">
+        <v>54</v>
+      </c>
+      <c r="U388" t="s">
+        <v>193</v>
+      </c>
+      <c r="V388" s="1">
+        <v>46282.36531288194</v>
+      </c>
+      <c r="W388">
+        <v>-1</v>
+      </c>
+      <c r="X388" t="s">
+        <v>199</v>
+      </c>
+      <c r="Y388" t="s">
+        <v>342</v>
+      </c>
+      <c r="AB388">
+        <v>0</v>
+      </c>
+      <c r="AC388" t="s">
+        <v>54</v>
+      </c>
+      <c r="AH388" t="s">
+        <v>351</v>
+      </c>
+      <c r="AI388" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="389" spans="1:35">
+      <c r="A389">
+        <v>6404</v>
+      </c>
+      <c r="B389" t="s">
+        <v>47</v>
+      </c>
+      <c r="C389" t="s">
+        <v>50</v>
+      </c>
+      <c r="D389" t="s">
+        <v>53</v>
+      </c>
+      <c r="E389" t="s">
+        <v>54</v>
+      </c>
+      <c r="F389" t="s">
+        <v>56</v>
+      </c>
+      <c r="G389">
+        <v>7027</v>
+      </c>
+      <c r="H389">
+        <v>0</v>
+      </c>
+      <c r="I389" t="s">
+        <v>65</v>
+      </c>
+      <c r="J389" t="s">
+        <v>121</v>
+      </c>
+      <c r="N389" s="1">
+        <v>46289</v>
+      </c>
+      <c r="P389">
+        <v>8</v>
+      </c>
+      <c r="Q389">
+        <v>2026</v>
+      </c>
+      <c r="R389">
+        <v>16962348</v>
+      </c>
+      <c r="S389" t="s">
+        <v>54</v>
+      </c>
+      <c r="U389" t="s">
+        <v>193</v>
+      </c>
+      <c r="V389" s="1">
         <v>46282.64018086805</v>
       </c>
-      <c r="W387">
+      <c r="W389">
         <v>-7</v>
       </c>
-      <c r="X387" t="s">
+      <c r="X389" t="s">
         <v>205</v>
       </c>
-      <c r="Y387" t="s">
-        <v>343</v>
-      </c>
-      <c r="AB387">
-        <v>0</v>
-      </c>
-      <c r="AC387" t="s">
-        <v>54</v>
-      </c>
-      <c r="AH387" t="s">
-        <v>348</v>
-      </c>
-      <c r="AI387" t="s">
-        <v>353</v>
+      <c r="Y389" t="s">
+        <v>344</v>
+      </c>
+      <c r="AB389">
+        <v>0</v>
+      </c>
+      <c r="AC389" t="s">
+        <v>54</v>
+      </c>
+      <c r="AH389" t="s">
+        <v>349</v>
+      </c>
+      <c r="AI389" t="s">
+        <v>354</v>
       </c>
     </row>
   </sheetData>

--- a/data/base/goias.xlsx
+++ b/data/base/goias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6008" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6022" uniqueCount="364">
   <si>
     <t>CodCliente</t>
   </si>
@@ -1468,7 +1468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AI416"/>
+  <dimension ref="A1:AI417"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:35">
@@ -27644,31 +27644,31 @@
     </row>
     <row r="350" spans="1:35">
       <c r="A350">
-        <v>6703</v>
+        <v>6949</v>
       </c>
       <c r="B350" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C350" t="s">
         <v>50</v>
       </c>
       <c r="D350" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E350" t="s">
         <v>54</v>
       </c>
       <c r="F350" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G350">
-        <v>1628</v>
+        <v>1697</v>
       </c>
       <c r="H350">
-        <v>1581</v>
+        <v>1650</v>
       </c>
       <c r="I350" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J350" t="s">
         <v>75</v>
@@ -27683,31 +27683,31 @@
         <v>2026</v>
       </c>
       <c r="R350">
-        <v>17955176</v>
+        <v>18178280</v>
       </c>
       <c r="S350" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="T350" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="U350" t="s">
         <v>198</v>
       </c>
       <c r="V350" s="1">
-        <v>46282.42251184028</v>
+        <v>46283.44840582176</v>
       </c>
       <c r="W350">
         <v>-3</v>
       </c>
       <c r="X350" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="AB350">
         <v>0</v>
       </c>
       <c r="AC350" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="AH350" t="s">
         <v>358</v>
@@ -27718,16 +27718,16 @@
     </row>
     <row r="351" spans="1:35">
       <c r="A351">
-        <v>5417</v>
+        <v>6703</v>
       </c>
       <c r="B351" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C351" t="s">
         <v>50</v>
       </c>
       <c r="D351" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E351" t="s">
         <v>54</v>
@@ -27736,49 +27736,52 @@
         <v>56</v>
       </c>
       <c r="G351">
-        <v>5883</v>
+        <v>1628</v>
       </c>
       <c r="H351">
-        <v>5792</v>
+        <v>1581</v>
       </c>
       <c r="I351" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J351" t="s">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="N351" s="1">
         <v>46286</v>
       </c>
       <c r="P351">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q351">
         <v>2026</v>
       </c>
       <c r="R351">
-        <v>17399067</v>
+        <v>17955176</v>
       </c>
       <c r="S351" t="s">
-        <v>176</v>
+        <v>170</v>
+      </c>
+      <c r="T351" t="s">
+        <v>191</v>
       </c>
       <c r="U351" t="s">
         <v>198</v>
       </c>
       <c r="V351" s="1">
-        <v>46282.47420876157</v>
+        <v>46282.42251184028</v>
       </c>
       <c r="W351">
         <v>-3</v>
       </c>
       <c r="X351" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="AB351">
         <v>0</v>
       </c>
       <c r="AC351" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="AH351" t="s">
         <v>358</v>
@@ -27807,7 +27810,7 @@
         <v>56</v>
       </c>
       <c r="G352">
-        <v>5884</v>
+        <v>5883</v>
       </c>
       <c r="H352">
         <v>5792</v>
@@ -27816,7 +27819,7 @@
         <v>61</v>
       </c>
       <c r="J352" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N352" s="1">
         <v>46286</v>
@@ -27828,7 +27831,7 @@
         <v>2026</v>
       </c>
       <c r="R352">
-        <v>17399077</v>
+        <v>17399067</v>
       </c>
       <c r="S352" t="s">
         <v>176</v>
@@ -27837,7 +27840,7 @@
         <v>198</v>
       </c>
       <c r="V352" s="1">
-        <v>46282.47437324074</v>
+        <v>46282.47420876157</v>
       </c>
       <c r="W352">
         <v>-3</v>
@@ -27860,16 +27863,16 @@
     </row>
     <row r="353" spans="1:35">
       <c r="A353">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B353" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C353" t="s">
         <v>50</v>
       </c>
       <c r="D353" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E353" t="s">
         <v>54</v>
@@ -27878,23 +27881,20 @@
         <v>56</v>
       </c>
       <c r="G353">
-        <v>5903</v>
+        <v>5884</v>
       </c>
       <c r="H353">
-        <v>5830</v>
+        <v>5792</v>
       </c>
       <c r="I353" t="s">
         <v>61</v>
       </c>
       <c r="J353" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="N353" s="1">
         <v>46286</v>
       </c>
-      <c r="O353" t="s">
-        <v>159</v>
-      </c>
       <c r="P353">
         <v>9</v>
       </c>
@@ -27902,34 +27902,28 @@
         <v>2026</v>
       </c>
       <c r="R353">
-        <v>16962221</v>
+        <v>17399077</v>
       </c>
       <c r="S353" t="s">
-        <v>177</v>
-      </c>
-      <c r="T353" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="U353" t="s">
         <v>198</v>
       </c>
       <c r="V353" s="1">
-        <v>46282.42048836806</v>
+        <v>46282.47437324074</v>
       </c>
       <c r="W353">
         <v>-3</v>
       </c>
       <c r="X353" t="s">
-        <v>210</v>
-      </c>
-      <c r="Y353" t="s">
-        <v>339</v>
+        <v>206</v>
       </c>
       <c r="AB353">
         <v>0</v>
       </c>
       <c r="AC353" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AH353" t="s">
         <v>358</v>
@@ -27958,20 +27952,23 @@
         <v>56</v>
       </c>
       <c r="G354">
+        <v>5903</v>
+      </c>
+      <c r="H354">
         <v>5830</v>
-      </c>
-      <c r="H354">
-        <v>5784</v>
       </c>
       <c r="I354" t="s">
         <v>61</v>
       </c>
       <c r="J354" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="N354" s="1">
         <v>46286</v>
       </c>
+      <c r="O354" t="s">
+        <v>159</v>
+      </c>
       <c r="P354">
         <v>9</v>
       </c>
@@ -27979,7 +27976,7 @@
         <v>2026</v>
       </c>
       <c r="R354">
-        <v>16962211</v>
+        <v>16962221</v>
       </c>
       <c r="S354" t="s">
         <v>177</v>
@@ -27991,7 +27988,7 @@
         <v>198</v>
       </c>
       <c r="V354" s="1">
-        <v>46282.42138976852</v>
+        <v>46282.42048836806</v>
       </c>
       <c r="W354">
         <v>-3</v>
@@ -27999,6 +27996,9 @@
       <c r="X354" t="s">
         <v>210</v>
       </c>
+      <c r="Y354" t="s">
+        <v>339</v>
+      </c>
       <c r="AB354">
         <v>0</v>
       </c>
@@ -28014,16 +28014,16 @@
     </row>
     <row r="355" spans="1:35">
       <c r="A355">
-        <v>6548</v>
+        <v>6404</v>
       </c>
       <c r="B355" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="C355" t="s">
         <v>50</v>
       </c>
       <c r="D355" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E355" t="s">
         <v>54</v>
@@ -28032,52 +28032,52 @@
         <v>56</v>
       </c>
       <c r="G355">
-        <v>1913</v>
+        <v>5830</v>
       </c>
       <c r="H355">
-        <v>1862</v>
+        <v>5784</v>
       </c>
       <c r="I355" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J355" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N355" s="1">
         <v>46286</v>
       </c>
       <c r="P355">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q355">
         <v>2026</v>
       </c>
       <c r="R355">
-        <v>17988579</v>
+        <v>16962211</v>
       </c>
       <c r="S355" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="T355" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="U355" t="s">
         <v>198</v>
       </c>
       <c r="V355" s="1">
-        <v>46283.3939177662</v>
+        <v>46282.42138976852</v>
       </c>
       <c r="W355">
         <v>-3</v>
       </c>
       <c r="X355" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AB355">
         <v>0</v>
       </c>
       <c r="AC355" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="AH355" t="s">
         <v>358</v>
@@ -28088,37 +28088,37 @@
     </row>
     <row r="356" spans="1:35">
       <c r="A356">
-        <v>6628</v>
+        <v>6548</v>
       </c>
       <c r="B356" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C356" t="s">
         <v>50</v>
       </c>
       <c r="D356" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E356" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F356" t="s">
         <v>56</v>
       </c>
       <c r="G356">
-        <v>1879</v>
+        <v>1913</v>
       </c>
       <c r="H356">
-        <v>0</v>
+        <v>1862</v>
       </c>
       <c r="I356" t="s">
         <v>62</v>
       </c>
       <c r="J356" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N356" s="1">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="P356">
         <v>8</v>
@@ -28127,37 +28127,34 @@
         <v>2026</v>
       </c>
       <c r="R356">
-        <v>17988684</v>
+        <v>17988579</v>
       </c>
       <c r="S356" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="T356" t="s">
         <v>195</v>
       </c>
       <c r="U356" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="V356" s="1">
-        <v>46283.41459880787</v>
+        <v>46283.3939177662</v>
       </c>
       <c r="W356">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="X356" t="s">
-        <v>201</v>
-      </c>
-      <c r="Y356" t="s">
-        <v>340</v>
+        <v>200</v>
       </c>
       <c r="AB356">
         <v>0</v>
       </c>
       <c r="AC356" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="AH356" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AI356" t="s">
         <v>363</v>
@@ -28165,25 +28162,25 @@
     </row>
     <row r="357" spans="1:35">
       <c r="A357">
-        <v>6548</v>
+        <v>6628</v>
       </c>
       <c r="B357" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C357" t="s">
         <v>50</v>
       </c>
       <c r="D357" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E357" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F357" t="s">
         <v>56</v>
       </c>
       <c r="G357">
-        <v>7026</v>
+        <v>1879</v>
       </c>
       <c r="H357">
         <v>0</v>
@@ -28192,10 +28189,10 @@
         <v>62</v>
       </c>
       <c r="J357" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="N357" s="1">
-        <v>46288</v>
+        <v>46283</v>
       </c>
       <c r="P357">
         <v>8</v>
@@ -28204,37 +28201,37 @@
         <v>2026</v>
       </c>
       <c r="R357">
-        <v>18094899</v>
+        <v>17988684</v>
       </c>
       <c r="S357" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="T357" t="s">
         <v>195</v>
       </c>
       <c r="U357" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="V357" s="1">
-        <v>46282.74573174769</v>
+        <v>46283.41459880787</v>
       </c>
       <c r="W357">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="X357" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Y357" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AB357">
         <v>0</v>
       </c>
       <c r="AC357" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="AH357" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AI357" t="s">
         <v>363</v>
@@ -28242,10 +28239,10 @@
     </row>
     <row r="358" spans="1:35">
       <c r="A358">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B358" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C358" t="s">
         <v>50</v>
@@ -28254,7 +28251,7 @@
         <v>51</v>
       </c>
       <c r="E358" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F358" t="s">
         <v>56</v>
@@ -28281,31 +28278,34 @@
         <v>2026</v>
       </c>
       <c r="R358">
-        <v>18048473</v>
+        <v>18094899</v>
       </c>
       <c r="S358" t="s">
-        <v>181</v>
+        <v>180</v>
+      </c>
+      <c r="T358" t="s">
+        <v>195</v>
       </c>
       <c r="U358" t="s">
         <v>198</v>
       </c>
       <c r="V358" s="1">
-        <v>46282.74485532408</v>
+        <v>46282.74573174769</v>
       </c>
       <c r="W358">
         <v>-5</v>
       </c>
       <c r="X358" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Y358" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AB358">
         <v>0</v>
       </c>
       <c r="AC358" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AH358" t="s">
         <v>358</v>
@@ -28316,10 +28316,10 @@
     </row>
     <row r="359" spans="1:35">
       <c r="A359">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B359" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C359" t="s">
         <v>50</v>
@@ -28328,25 +28328,25 @@
         <v>51</v>
       </c>
       <c r="E359" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F359" t="s">
         <v>56</v>
       </c>
       <c r="G359">
-        <v>1914</v>
+        <v>7026</v>
       </c>
       <c r="H359">
-        <v>1862</v>
+        <v>0</v>
       </c>
       <c r="I359" t="s">
         <v>62</v>
       </c>
       <c r="J359" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="N359" s="1">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="P359">
         <v>8</v>
@@ -28355,31 +28355,31 @@
         <v>2026</v>
       </c>
       <c r="R359">
-        <v>17988591</v>
+        <v>18048473</v>
       </c>
       <c r="S359" t="s">
-        <v>180</v>
-      </c>
-      <c r="T359" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="U359" t="s">
         <v>198</v>
       </c>
       <c r="V359" s="1">
-        <v>46283.39413969908</v>
+        <v>46282.74485532408</v>
       </c>
       <c r="W359">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="X359" t="s">
-        <v>200</v>
+        <v>201</v>
+      </c>
+      <c r="Y359" t="s">
+        <v>342</v>
       </c>
       <c r="AB359">
         <v>0</v>
       </c>
       <c r="AC359" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AH359" t="s">
         <v>358</v>
@@ -28390,10 +28390,10 @@
     </row>
     <row r="360" spans="1:35">
       <c r="A360">
-        <v>6704</v>
+        <v>6548</v>
       </c>
       <c r="B360" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C360" t="s">
         <v>50</v>
@@ -28408,22 +28408,19 @@
         <v>56</v>
       </c>
       <c r="G360">
-        <v>11874</v>
+        <v>1914</v>
       </c>
       <c r="H360">
-        <v>0</v>
+        <v>1862</v>
       </c>
       <c r="I360" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J360" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="N360" s="1">
-        <v>46281</v>
-      </c>
-      <c r="O360" t="s">
-        <v>160</v>
+        <v>46286</v>
       </c>
       <c r="P360">
         <v>8</v>
@@ -28432,37 +28429,34 @@
         <v>2026</v>
       </c>
       <c r="R360">
-        <v>18273589</v>
+        <v>17988591</v>
       </c>
       <c r="S360" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="T360" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="U360" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="V360" s="1">
-        <v>46282.70138376157</v>
+        <v>46283.39413969908</v>
       </c>
       <c r="W360">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="X360" t="s">
-        <v>205</v>
-      </c>
-      <c r="Y360" t="s">
-        <v>343</v>
+        <v>200</v>
       </c>
       <c r="AB360">
         <v>0</v>
       </c>
       <c r="AC360" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="AH360" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AI360" t="s">
         <v>363</v>
@@ -28470,16 +28464,16 @@
     </row>
     <row r="361" spans="1:35">
       <c r="A361">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B361" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C361" t="s">
         <v>50</v>
       </c>
       <c r="D361" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E361" t="s">
         <v>54</v>
@@ -28512,7 +28506,7 @@
         <v>2026</v>
       </c>
       <c r="R361">
-        <v>18239293</v>
+        <v>18273589</v>
       </c>
       <c r="S361" t="s">
         <v>185</v>
@@ -28524,7 +28518,7 @@
         <v>197</v>
       </c>
       <c r="V361" s="1">
-        <v>46282.7013840625</v>
+        <v>46282.70138376157</v>
       </c>
       <c r="W361">
         <v>2</v>
@@ -28568,7 +28562,7 @@
         <v>56</v>
       </c>
       <c r="G362">
-        <v>1805</v>
+        <v>11874</v>
       </c>
       <c r="H362">
         <v>0</v>
@@ -28577,10 +28571,13 @@
         <v>63</v>
       </c>
       <c r="J362" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="N362" s="1">
-        <v>46283</v>
+        <v>46281</v>
+      </c>
+      <c r="O362" t="s">
+        <v>160</v>
       </c>
       <c r="P362">
         <v>8</v>
@@ -28589,7 +28586,7 @@
         <v>2026</v>
       </c>
       <c r="R362">
-        <v>17948948</v>
+        <v>18239293</v>
       </c>
       <c r="S362" t="s">
         <v>185</v>
@@ -28598,19 +28595,19 @@
         <v>196</v>
       </c>
       <c r="U362" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="V362" s="1">
-        <v>46283.35452896991</v>
+        <v>46282.7013840625</v>
       </c>
       <c r="W362">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X362" t="s">
         <v>205</v>
       </c>
       <c r="Y362" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AB362">
         <v>0</v>
@@ -28627,10 +28624,10 @@
     </row>
     <row r="363" spans="1:35">
       <c r="A363">
-        <v>6779</v>
+        <v>6705</v>
       </c>
       <c r="B363" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C363" t="s">
         <v>50</v>
@@ -28666,7 +28663,7 @@
         <v>2026</v>
       </c>
       <c r="R363">
-        <v>18084966</v>
+        <v>17948948</v>
       </c>
       <c r="S363" t="s">
         <v>185</v>
@@ -28678,7 +28675,7 @@
         <v>199</v>
       </c>
       <c r="V363" s="1">
-        <v>46283.35453171296</v>
+        <v>46283.35452896991</v>
       </c>
       <c r="W363">
         <v>0</v>
@@ -28704,16 +28701,16 @@
     </row>
     <row r="364" spans="1:35">
       <c r="A364">
-        <v>5417</v>
+        <v>6779</v>
       </c>
       <c r="B364" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C364" t="s">
         <v>50</v>
       </c>
       <c r="D364" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E364" t="s">
         <v>54</v>
@@ -28722,7 +28719,7 @@
         <v>56</v>
       </c>
       <c r="G364">
-        <v>7025</v>
+        <v>1805</v>
       </c>
       <c r="H364">
         <v>0</v>
@@ -28731,10 +28728,10 @@
         <v>63</v>
       </c>
       <c r="J364" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="N364" s="1">
-        <v>46288</v>
+        <v>46283</v>
       </c>
       <c r="P364">
         <v>8</v>
@@ -28743,7 +28740,7 @@
         <v>2026</v>
       </c>
       <c r="R364">
-        <v>17399280</v>
+        <v>18084966</v>
       </c>
       <c r="S364" t="s">
         <v>185</v>
@@ -28752,19 +28749,19 @@
         <v>196</v>
       </c>
       <c r="U364" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="V364" s="1">
-        <v>46283.38367943287</v>
+        <v>46283.35453171296</v>
       </c>
       <c r="W364">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="X364" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Y364" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AB364">
         <v>0</v>
@@ -28773,7 +28770,7 @@
         <v>185</v>
       </c>
       <c r="AH364" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AI364" t="s">
         <v>363</v>
@@ -28781,16 +28778,16 @@
     </row>
     <row r="365" spans="1:35">
       <c r="A365">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B365" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C365" t="s">
         <v>50</v>
       </c>
       <c r="D365" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E365" t="s">
         <v>54</v>
@@ -28820,7 +28817,7 @@
         <v>2026</v>
       </c>
       <c r="R365">
-        <v>16962338</v>
+        <v>17399280</v>
       </c>
       <c r="S365" t="s">
         <v>185</v>
@@ -28832,16 +28829,16 @@
         <v>198</v>
       </c>
       <c r="V365" s="1">
-        <v>46282.54038741898</v>
+        <v>46283.38367943287</v>
       </c>
       <c r="W365">
         <v>-5</v>
       </c>
       <c r="X365" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="Y365" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AB365">
         <v>0</v>
@@ -28858,16 +28855,16 @@
     </row>
     <row r="366" spans="1:35">
       <c r="A366">
-        <v>6705</v>
+        <v>6404</v>
       </c>
       <c r="B366" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C366" t="s">
         <v>50</v>
       </c>
       <c r="D366" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E366" t="s">
         <v>54</v>
@@ -28876,22 +28873,19 @@
         <v>56</v>
       </c>
       <c r="G366">
-        <v>7022</v>
+        <v>7025</v>
       </c>
       <c r="H366">
         <v>0</v>
       </c>
       <c r="I366" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J366" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="N366" s="1">
-        <v>46283</v>
-      </c>
-      <c r="O366" t="s">
-        <v>159</v>
+        <v>46288</v>
       </c>
       <c r="P366">
         <v>8</v>
@@ -28900,34 +28894,37 @@
         <v>2026</v>
       </c>
       <c r="R366">
-        <v>17952601</v>
+        <v>16962338</v>
       </c>
       <c r="S366" t="s">
-        <v>186</v>
+        <v>185</v>
+      </c>
+      <c r="T366" t="s">
+        <v>196</v>
       </c>
       <c r="U366" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="V366" s="1">
-        <v>46283.38329579861</v>
+        <v>46282.54038741898</v>
       </c>
       <c r="W366">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="X366" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="Y366" t="s">
-        <v>317</v>
+        <v>346</v>
       </c>
       <c r="AB366">
         <v>0</v>
       </c>
       <c r="AC366" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AH366" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AI366" t="s">
         <v>363</v>
@@ -28935,16 +28932,16 @@
     </row>
     <row r="367" spans="1:35">
       <c r="A367">
-        <v>5417</v>
+        <v>6705</v>
       </c>
       <c r="B367" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C367" t="s">
         <v>50</v>
       </c>
       <c r="D367" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E367" t="s">
         <v>54</v>
@@ -28953,7 +28950,7 @@
         <v>56</v>
       </c>
       <c r="G367">
-        <v>9086</v>
+        <v>7022</v>
       </c>
       <c r="H367">
         <v>0</v>
@@ -28962,22 +28959,22 @@
         <v>64</v>
       </c>
       <c r="J367" t="s">
-        <v>147</v>
+        <v>115</v>
       </c>
       <c r="N367" s="1">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="O367" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P367">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q367">
         <v>2026</v>
       </c>
       <c r="R367">
-        <v>17399363</v>
+        <v>17952601</v>
       </c>
       <c r="S367" t="s">
         <v>186</v>
@@ -28986,16 +28983,16 @@
         <v>199</v>
       </c>
       <c r="V367" s="1">
-        <v>46282.36440621527</v>
+        <v>46283.38329579861</v>
       </c>
       <c r="W367">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X367" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Y367" t="s">
-        <v>347</v>
+        <v>317</v>
       </c>
       <c r="AB367">
         <v>0</v>
@@ -29004,7 +29001,7 @@
         <v>186</v>
       </c>
       <c r="AH367" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AI367" t="s">
         <v>363</v>
@@ -29012,16 +29009,16 @@
     </row>
     <row r="368" spans="1:35">
       <c r="A368">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B368" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C368" t="s">
         <v>50</v>
       </c>
       <c r="D368" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E368" t="s">
         <v>54</v>
@@ -29054,7 +29051,7 @@
         <v>2026</v>
       </c>
       <c r="R368">
-        <v>16962380</v>
+        <v>17399363</v>
       </c>
       <c r="S368" t="s">
         <v>186</v>
@@ -29063,13 +29060,13 @@
         <v>199</v>
       </c>
       <c r="V368" s="1">
-        <v>46282.36462596065</v>
+        <v>46282.36440621527</v>
       </c>
       <c r="W368">
         <v>1</v>
       </c>
       <c r="X368" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="Y368" t="s">
         <v>347</v>
@@ -29089,16 +29086,16 @@
     </row>
     <row r="369" spans="1:35">
       <c r="A369">
-        <v>6486</v>
+        <v>6404</v>
       </c>
       <c r="B369" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C369" t="s">
         <v>50</v>
       </c>
       <c r="D369" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E369" t="s">
         <v>54</v>
@@ -29131,7 +29128,7 @@
         <v>2026</v>
       </c>
       <c r="R369">
-        <v>16976270</v>
+        <v>16962380</v>
       </c>
       <c r="S369" t="s">
         <v>186</v>
@@ -29140,13 +29137,13 @@
         <v>199</v>
       </c>
       <c r="V369" s="1">
-        <v>46282.36464421296</v>
+        <v>46282.36462596065</v>
       </c>
       <c r="W369">
         <v>1</v>
       </c>
       <c r="X369" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Y369" t="s">
         <v>347</v>
@@ -29166,10 +29163,10 @@
     </row>
     <row r="370" spans="1:35">
       <c r="A370">
-        <v>6548</v>
+        <v>6486</v>
       </c>
       <c r="B370" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C370" t="s">
         <v>50</v>
@@ -29208,7 +29205,7 @@
         <v>2026</v>
       </c>
       <c r="R370">
-        <v>17222865</v>
+        <v>16976270</v>
       </c>
       <c r="S370" t="s">
         <v>186</v>
@@ -29217,13 +29214,13 @@
         <v>199</v>
       </c>
       <c r="V370" s="1">
-        <v>46282.36467337963</v>
+        <v>46282.36464421296</v>
       </c>
       <c r="W370">
         <v>1</v>
       </c>
       <c r="X370" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="Y370" t="s">
         <v>347</v>
@@ -29243,10 +29240,10 @@
     </row>
     <row r="371" spans="1:35">
       <c r="A371">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B371" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C371" t="s">
         <v>50</v>
@@ -29255,7 +29252,7 @@
         <v>51</v>
       </c>
       <c r="E371" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F371" t="s">
         <v>56</v>
@@ -29285,7 +29282,7 @@
         <v>2026</v>
       </c>
       <c r="R371">
-        <v>17042587</v>
+        <v>17222865</v>
       </c>
       <c r="S371" t="s">
         <v>186</v>
@@ -29294,13 +29291,13 @@
         <v>199</v>
       </c>
       <c r="V371" s="1">
-        <v>46282.36469679398</v>
+        <v>46282.36467337963</v>
       </c>
       <c r="W371">
         <v>1</v>
       </c>
       <c r="X371" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Y371" t="s">
         <v>347</v>
@@ -29320,16 +29317,16 @@
     </row>
     <row r="372" spans="1:35">
       <c r="A372">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B372" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C372" t="s">
         <v>50</v>
       </c>
       <c r="D372" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E372" t="s">
         <v>55</v>
@@ -29362,7 +29359,7 @@
         <v>2026</v>
       </c>
       <c r="R372">
-        <v>16960074</v>
+        <v>17042587</v>
       </c>
       <c r="S372" t="s">
         <v>186</v>
@@ -29371,7 +29368,7 @@
         <v>199</v>
       </c>
       <c r="V372" s="1">
-        <v>46282.36469869213</v>
+        <v>46282.36469679398</v>
       </c>
       <c r="W372">
         <v>1</v>
@@ -29397,19 +29394,19 @@
     </row>
     <row r="373" spans="1:35">
       <c r="A373">
-        <v>6703</v>
+        <v>6628</v>
       </c>
       <c r="B373" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C373" t="s">
         <v>50</v>
       </c>
       <c r="D373" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E373" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F373" t="s">
         <v>56</v>
@@ -29439,7 +29436,7 @@
         <v>2026</v>
       </c>
       <c r="R373">
-        <v>17941217</v>
+        <v>16960074</v>
       </c>
       <c r="S373" t="s">
         <v>186</v>
@@ -29448,13 +29445,13 @@
         <v>199</v>
       </c>
       <c r="V373" s="1">
-        <v>46282.36473159722</v>
+        <v>46282.36469869213</v>
       </c>
       <c r="W373">
         <v>1</v>
       </c>
       <c r="X373" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="Y373" t="s">
         <v>347</v>
@@ -29474,16 +29471,16 @@
     </row>
     <row r="374" spans="1:35">
       <c r="A374">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B374" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C374" t="s">
         <v>50</v>
       </c>
       <c r="D374" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E374" t="s">
         <v>54</v>
@@ -29516,7 +29513,7 @@
         <v>2026</v>
       </c>
       <c r="R374">
-        <v>17952444</v>
+        <v>17941217</v>
       </c>
       <c r="S374" t="s">
         <v>186</v>
@@ -29525,13 +29522,13 @@
         <v>199</v>
       </c>
       <c r="V374" s="1">
-        <v>46282.36473394676</v>
+        <v>46282.36473159722</v>
       </c>
       <c r="W374">
         <v>1</v>
       </c>
       <c r="X374" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="Y374" t="s">
         <v>347</v>
@@ -29551,16 +29548,16 @@
     </row>
     <row r="375" spans="1:35">
       <c r="A375">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B375" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C375" t="s">
         <v>50</v>
       </c>
       <c r="D375" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E375" t="s">
         <v>54</v>
@@ -29593,7 +29590,7 @@
         <v>2026</v>
       </c>
       <c r="R375">
-        <v>17952624</v>
+        <v>17952444</v>
       </c>
       <c r="S375" t="s">
         <v>186</v>
@@ -29602,7 +29599,7 @@
         <v>199</v>
       </c>
       <c r="V375" s="1">
-        <v>46282.36473579861</v>
+        <v>46282.36473394676</v>
       </c>
       <c r="W375">
         <v>1</v>
@@ -29628,10 +29625,10 @@
     </row>
     <row r="376" spans="1:35">
       <c r="A376">
-        <v>6779</v>
+        <v>6705</v>
       </c>
       <c r="B376" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C376" t="s">
         <v>50</v>
@@ -29670,7 +29667,7 @@
         <v>2026</v>
       </c>
       <c r="R376">
-        <v>18056801</v>
+        <v>17952624</v>
       </c>
       <c r="S376" t="s">
         <v>186</v>
@@ -29679,7 +29676,7 @@
         <v>199</v>
       </c>
       <c r="V376" s="1">
-        <v>46282.36475297454</v>
+        <v>46282.36473579861</v>
       </c>
       <c r="W376">
         <v>1</v>
@@ -29705,10 +29702,10 @@
     </row>
     <row r="377" spans="1:35">
       <c r="A377">
-        <v>6945</v>
+        <v>6779</v>
       </c>
       <c r="B377" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C377" t="s">
         <v>50</v>
@@ -29720,7 +29717,7 @@
         <v>54</v>
       </c>
       <c r="F377" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G377">
         <v>9086</v>
@@ -29747,7 +29744,7 @@
         <v>2026</v>
       </c>
       <c r="R377">
-        <v>18164551</v>
+        <v>18056801</v>
       </c>
       <c r="S377" t="s">
         <v>186</v>
@@ -29756,13 +29753,13 @@
         <v>199</v>
       </c>
       <c r="V377" s="1">
-        <v>46282.36486408565</v>
+        <v>46282.36475297454</v>
       </c>
       <c r="W377">
         <v>1</v>
       </c>
       <c r="X377" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Y377" t="s">
         <v>347</v>
@@ -29782,16 +29779,16 @@
     </row>
     <row r="378" spans="1:35">
       <c r="A378">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B378" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C378" t="s">
         <v>50</v>
       </c>
       <c r="D378" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E378" t="s">
         <v>54</v>
@@ -29824,7 +29821,7 @@
         <v>2026</v>
       </c>
       <c r="R378">
-        <v>18178187</v>
+        <v>18164551</v>
       </c>
       <c r="S378" t="s">
         <v>186</v>
@@ -29833,16 +29830,16 @@
         <v>199</v>
       </c>
       <c r="V378" s="1">
-        <v>46282.36487561343</v>
+        <v>46282.36486408565</v>
       </c>
       <c r="W378">
         <v>1</v>
       </c>
       <c r="X378" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Y378" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AB378">
         <v>0</v>
@@ -29859,16 +29856,16 @@
     </row>
     <row r="379" spans="1:35">
       <c r="A379">
-        <v>6962</v>
+        <v>6949</v>
       </c>
       <c r="B379" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C379" t="s">
         <v>50</v>
       </c>
       <c r="D379" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E379" t="s">
         <v>54</v>
@@ -29901,7 +29898,7 @@
         <v>2026</v>
       </c>
       <c r="R379">
-        <v>18188774</v>
+        <v>18178187</v>
       </c>
       <c r="S379" t="s">
         <v>186</v>
@@ -29910,16 +29907,16 @@
         <v>199</v>
       </c>
       <c r="V379" s="1">
-        <v>46282.36486778935</v>
+        <v>46282.36487561343</v>
       </c>
       <c r="W379">
         <v>1</v>
       </c>
       <c r="X379" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="Y379" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AB379">
         <v>0</v>
@@ -29936,10 +29933,10 @@
     </row>
     <row r="380" spans="1:35">
       <c r="A380">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B380" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C380" t="s">
         <v>50</v>
@@ -29978,7 +29975,7 @@
         <v>2026</v>
       </c>
       <c r="R380">
-        <v>18188680</v>
+        <v>18188774</v>
       </c>
       <c r="S380" t="s">
         <v>186</v>
@@ -29987,7 +29984,7 @@
         <v>199</v>
       </c>
       <c r="V380" s="1">
-        <v>46282.36486851852</v>
+        <v>46282.36486778935</v>
       </c>
       <c r="W380">
         <v>1</v>
@@ -30013,10 +30010,10 @@
     </row>
     <row r="381" spans="1:35">
       <c r="A381">
-        <v>6404</v>
+        <v>6963</v>
       </c>
       <c r="B381" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C381" t="s">
         <v>50</v>
@@ -30028,10 +30025,10 @@
         <v>54</v>
       </c>
       <c r="F381" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G381">
-        <v>940</v>
+        <v>9086</v>
       </c>
       <c r="H381">
         <v>0</v>
@@ -30040,13 +30037,13 @@
         <v>64</v>
       </c>
       <c r="J381" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N381" s="1">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="O381" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P381">
         <v>9</v>
@@ -30055,25 +30052,25 @@
         <v>2026</v>
       </c>
       <c r="R381">
-        <v>16962074</v>
+        <v>18188680</v>
       </c>
       <c r="S381" t="s">
         <v>186</v>
       </c>
       <c r="U381" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="V381" s="1">
-        <v>46282.79619427084</v>
+        <v>46282.36486851852</v>
       </c>
       <c r="W381">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X381" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="Y381" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="AB381">
         <v>0</v>
@@ -30090,16 +30087,16 @@
     </row>
     <row r="382" spans="1:35">
       <c r="A382">
-        <v>6486</v>
+        <v>6404</v>
       </c>
       <c r="B382" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C382" t="s">
         <v>50</v>
       </c>
       <c r="D382" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E382" t="s">
         <v>54</v>
@@ -30132,7 +30129,7 @@
         <v>2026</v>
       </c>
       <c r="R382">
-        <v>16975871</v>
+        <v>16962074</v>
       </c>
       <c r="S382" t="s">
         <v>186</v>
@@ -30141,13 +30138,13 @@
         <v>198</v>
       </c>
       <c r="V382" s="1">
-        <v>46282.79620872685</v>
+        <v>46282.79619427084</v>
       </c>
       <c r="W382">
         <v>0</v>
       </c>
       <c r="X382" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Y382" t="s">
         <v>349</v>
@@ -30167,10 +30164,10 @@
     </row>
     <row r="383" spans="1:35">
       <c r="A383">
-        <v>6548</v>
+        <v>6486</v>
       </c>
       <c r="B383" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C383" t="s">
         <v>50</v>
@@ -30209,7 +30206,7 @@
         <v>2026</v>
       </c>
       <c r="R383">
-        <v>17222366</v>
+        <v>16975871</v>
       </c>
       <c r="S383" t="s">
         <v>186</v>
@@ -30218,13 +30215,13 @@
         <v>198</v>
       </c>
       <c r="V383" s="1">
-        <v>46282.79623825232</v>
+        <v>46282.79620872685</v>
       </c>
       <c r="W383">
         <v>0</v>
       </c>
       <c r="X383" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="Y383" t="s">
         <v>349</v>
@@ -30244,10 +30241,10 @@
     </row>
     <row r="384" spans="1:35">
       <c r="A384">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B384" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C384" t="s">
         <v>50</v>
@@ -30256,7 +30253,7 @@
         <v>51</v>
       </c>
       <c r="E384" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F384" t="s">
         <v>56</v>
@@ -30286,7 +30283,7 @@
         <v>2026</v>
       </c>
       <c r="R384">
-        <v>17042221</v>
+        <v>17222366</v>
       </c>
       <c r="S384" t="s">
         <v>186</v>
@@ -30295,13 +30292,13 @@
         <v>198</v>
       </c>
       <c r="V384" s="1">
-        <v>46282.7962541551</v>
+        <v>46282.79623825232</v>
       </c>
       <c r="W384">
         <v>0</v>
       </c>
       <c r="X384" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Y384" t="s">
         <v>349</v>
@@ -30321,16 +30318,16 @@
     </row>
     <row r="385" spans="1:35">
       <c r="A385">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B385" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C385" t="s">
         <v>50</v>
       </c>
       <c r="D385" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E385" t="s">
         <v>55</v>
@@ -30363,7 +30360,7 @@
         <v>2026</v>
       </c>
       <c r="R385">
-        <v>16959926</v>
+        <v>17042221</v>
       </c>
       <c r="S385" t="s">
         <v>186</v>
@@ -30372,7 +30369,7 @@
         <v>198</v>
       </c>
       <c r="V385" s="1">
-        <v>46282.7962703125</v>
+        <v>46282.7962541551</v>
       </c>
       <c r="W385">
         <v>0</v>
@@ -30398,19 +30395,19 @@
     </row>
     <row r="386" spans="1:35">
       <c r="A386">
-        <v>6703</v>
+        <v>6628</v>
       </c>
       <c r="B386" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C386" t="s">
         <v>50</v>
       </c>
       <c r="D386" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E386" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F386" t="s">
         <v>56</v>
@@ -30440,7 +30437,7 @@
         <v>2026</v>
       </c>
       <c r="R386">
-        <v>17941112</v>
+        <v>16959926</v>
       </c>
       <c r="S386" t="s">
         <v>186</v>
@@ -30449,13 +30446,13 @@
         <v>198</v>
       </c>
       <c r="V386" s="1">
-        <v>46282.79628381944</v>
+        <v>46282.7962703125</v>
       </c>
       <c r="W386">
         <v>0</v>
       </c>
       <c r="X386" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="Y386" t="s">
         <v>349</v>
@@ -30475,16 +30472,16 @@
     </row>
     <row r="387" spans="1:35">
       <c r="A387">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B387" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C387" t="s">
         <v>50</v>
       </c>
       <c r="D387" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E387" t="s">
         <v>54</v>
@@ -30517,7 +30514,7 @@
         <v>2026</v>
       </c>
       <c r="R387">
-        <v>17952292</v>
+        <v>17941112</v>
       </c>
       <c r="S387" t="s">
         <v>186</v>
@@ -30526,13 +30523,13 @@
         <v>198</v>
       </c>
       <c r="V387" s="1">
-        <v>46282.79630119213</v>
+        <v>46282.79628381944</v>
       </c>
       <c r="W387">
         <v>0</v>
       </c>
       <c r="X387" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="Y387" t="s">
         <v>349</v>
@@ -30552,16 +30549,16 @@
     </row>
     <row r="388" spans="1:35">
       <c r="A388">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B388" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C388" t="s">
         <v>50</v>
       </c>
       <c r="D388" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E388" t="s">
         <v>54</v>
@@ -30594,7 +30591,7 @@
         <v>2026</v>
       </c>
       <c r="R388">
-        <v>17952491</v>
+        <v>17952292</v>
       </c>
       <c r="S388" t="s">
         <v>186</v>
@@ -30603,7 +30600,7 @@
         <v>198</v>
       </c>
       <c r="V388" s="1">
-        <v>46282.79631224537</v>
+        <v>46282.79630119213</v>
       </c>
       <c r="W388">
         <v>0</v>
@@ -30629,10 +30626,10 @@
     </row>
     <row r="389" spans="1:35">
       <c r="A389">
-        <v>6945</v>
+        <v>6705</v>
       </c>
       <c r="B389" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C389" t="s">
         <v>50</v>
@@ -30644,7 +30641,7 @@
         <v>54</v>
       </c>
       <c r="F389" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G389">
         <v>940</v>
@@ -30671,7 +30668,7 @@
         <v>2026</v>
       </c>
       <c r="R389">
-        <v>18164473</v>
+        <v>17952491</v>
       </c>
       <c r="S389" t="s">
         <v>186</v>
@@ -30680,16 +30677,16 @@
         <v>198</v>
       </c>
       <c r="V389" s="1">
-        <v>46282.79637734954</v>
+        <v>46282.79631224537</v>
       </c>
       <c r="W389">
         <v>0</v>
       </c>
       <c r="X389" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Y389" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AB389">
         <v>0</v>
@@ -30706,16 +30703,16 @@
     </row>
     <row r="390" spans="1:35">
       <c r="A390">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B390" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C390" t="s">
         <v>50</v>
       </c>
       <c r="D390" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E390" t="s">
         <v>54</v>
@@ -30748,7 +30745,7 @@
         <v>2026</v>
       </c>
       <c r="R390">
-        <v>18178120</v>
+        <v>18164473</v>
       </c>
       <c r="S390" t="s">
         <v>186</v>
@@ -30757,13 +30754,13 @@
         <v>198</v>
       </c>
       <c r="V390" s="1">
-        <v>46282.79638922454</v>
+        <v>46282.79637734954</v>
       </c>
       <c r="W390">
         <v>0</v>
       </c>
       <c r="X390" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Y390" t="s">
         <v>350</v>
@@ -30783,10 +30780,10 @@
     </row>
     <row r="391" spans="1:35">
       <c r="A391">
-        <v>5417</v>
+        <v>6949</v>
       </c>
       <c r="B391" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C391" t="s">
         <v>50</v>
@@ -30798,19 +30795,19 @@
         <v>54</v>
       </c>
       <c r="F391" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G391">
-        <v>9088</v>
+        <v>940</v>
       </c>
       <c r="H391">
         <v>0</v>
       </c>
       <c r="I391" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J391" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="N391" s="1">
         <v>46283</v>
@@ -30825,22 +30822,22 @@
         <v>2026</v>
       </c>
       <c r="R391">
-        <v>17399383</v>
+        <v>18178120</v>
       </c>
       <c r="S391" t="s">
-        <v>54</v>
+        <v>186</v>
       </c>
       <c r="U391" t="s">
         <v>198</v>
       </c>
       <c r="V391" s="1">
-        <v>46282.3651903588</v>
+        <v>46282.79638922454</v>
       </c>
       <c r="W391">
         <v>0</v>
       </c>
       <c r="X391" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="Y391" t="s">
         <v>350</v>
@@ -30849,7 +30846,7 @@
         <v>0</v>
       </c>
       <c r="AC391" t="s">
-        <v>54</v>
+        <v>186</v>
       </c>
       <c r="AH391" t="s">
         <v>360</v>
@@ -30860,16 +30857,16 @@
     </row>
     <row r="392" spans="1:35">
       <c r="A392">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B392" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C392" t="s">
         <v>50</v>
       </c>
       <c r="D392" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E392" t="s">
         <v>54</v>
@@ -30902,7 +30899,7 @@
         <v>2026</v>
       </c>
       <c r="R392">
-        <v>16962400</v>
+        <v>17399383</v>
       </c>
       <c r="S392" t="s">
         <v>54</v>
@@ -30911,13 +30908,13 @@
         <v>198</v>
       </c>
       <c r="V392" s="1">
-        <v>46282.36525856482</v>
+        <v>46282.3651903588</v>
       </c>
       <c r="W392">
         <v>0</v>
       </c>
       <c r="X392" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="Y392" t="s">
         <v>350</v>
@@ -30937,16 +30934,16 @@
     </row>
     <row r="393" spans="1:35">
       <c r="A393">
-        <v>6486</v>
+        <v>6404</v>
       </c>
       <c r="B393" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C393" t="s">
         <v>50</v>
       </c>
       <c r="D393" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E393" t="s">
         <v>54</v>
@@ -30979,7 +30976,7 @@
         <v>2026</v>
       </c>
       <c r="R393">
-        <v>16976290</v>
+        <v>16962400</v>
       </c>
       <c r="S393" t="s">
         <v>54</v>
@@ -30988,13 +30985,13 @@
         <v>198</v>
       </c>
       <c r="V393" s="1">
-        <v>46282.36526855324</v>
+        <v>46282.36525856482</v>
       </c>
       <c r="W393">
         <v>0</v>
       </c>
       <c r="X393" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Y393" t="s">
         <v>350</v>
@@ -31014,10 +31011,10 @@
     </row>
     <row r="394" spans="1:35">
       <c r="A394">
-        <v>6548</v>
+        <v>6486</v>
       </c>
       <c r="B394" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C394" t="s">
         <v>50</v>
@@ -31056,7 +31053,7 @@
         <v>2026</v>
       </c>
       <c r="R394">
-        <v>17222899</v>
+        <v>16976290</v>
       </c>
       <c r="S394" t="s">
         <v>54</v>
@@ -31065,13 +31062,13 @@
         <v>198</v>
       </c>
       <c r="V394" s="1">
-        <v>46282.36527959491</v>
+        <v>46282.36526855324</v>
       </c>
       <c r="W394">
         <v>0</v>
       </c>
       <c r="X394" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="Y394" t="s">
         <v>350</v>
@@ -31091,10 +31088,10 @@
     </row>
     <row r="395" spans="1:35">
       <c r="A395">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B395" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C395" t="s">
         <v>50</v>
@@ -31103,7 +31100,7 @@
         <v>51</v>
       </c>
       <c r="E395" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F395" t="s">
         <v>56</v>
@@ -31133,22 +31130,22 @@
         <v>2026</v>
       </c>
       <c r="R395">
-        <v>17042627</v>
+        <v>17222899</v>
       </c>
       <c r="S395" t="s">
-        <v>187</v>
+        <v>54</v>
       </c>
       <c r="U395" t="s">
         <v>198</v>
       </c>
       <c r="V395" s="1">
-        <v>46282.36528526621</v>
+        <v>46282.36527959491</v>
       </c>
       <c r="W395">
         <v>0</v>
       </c>
       <c r="X395" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Y395" t="s">
         <v>350</v>
@@ -31157,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="AC395" t="s">
-        <v>187</v>
+        <v>54</v>
       </c>
       <c r="AH395" t="s">
         <v>360</v>
@@ -31168,16 +31165,16 @@
     </row>
     <row r="396" spans="1:35">
       <c r="A396">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B396" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C396" t="s">
         <v>50</v>
       </c>
       <c r="D396" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E396" t="s">
         <v>55</v>
@@ -31210,16 +31207,16 @@
         <v>2026</v>
       </c>
       <c r="R396">
-        <v>16960098</v>
+        <v>17042627</v>
       </c>
       <c r="S396" t="s">
-        <v>55</v>
+        <v>187</v>
       </c>
       <c r="U396" t="s">
         <v>198</v>
       </c>
       <c r="V396" s="1">
-        <v>46282.36528619213</v>
+        <v>46282.36528526621</v>
       </c>
       <c r="W396">
         <v>0</v>
@@ -31234,7 +31231,7 @@
         <v>0</v>
       </c>
       <c r="AC396" t="s">
-        <v>55</v>
+        <v>187</v>
       </c>
       <c r="AH396" t="s">
         <v>360</v>
@@ -31245,19 +31242,19 @@
     </row>
     <row r="397" spans="1:35">
       <c r="A397">
-        <v>6703</v>
+        <v>6628</v>
       </c>
       <c r="B397" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C397" t="s">
         <v>50</v>
       </c>
       <c r="D397" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E397" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F397" t="s">
         <v>56</v>
@@ -31287,22 +31284,22 @@
         <v>2026</v>
       </c>
       <c r="R397">
-        <v>17941237</v>
+        <v>16960098</v>
       </c>
       <c r="S397" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="U397" t="s">
         <v>198</v>
       </c>
       <c r="V397" s="1">
-        <v>46282.36529351852</v>
+        <v>46282.36528619213</v>
       </c>
       <c r="W397">
         <v>0</v>
       </c>
       <c r="X397" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="Y397" t="s">
         <v>350</v>
@@ -31311,7 +31308,7 @@
         <v>0</v>
       </c>
       <c r="AC397" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AH397" t="s">
         <v>360</v>
@@ -31322,16 +31319,16 @@
     </row>
     <row r="398" spans="1:35">
       <c r="A398">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B398" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C398" t="s">
         <v>50</v>
       </c>
       <c r="D398" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E398" t="s">
         <v>54</v>
@@ -31364,7 +31361,7 @@
         <v>2026</v>
       </c>
       <c r="R398">
-        <v>17952466</v>
+        <v>17941237</v>
       </c>
       <c r="S398" t="s">
         <v>54</v>
@@ -31373,13 +31370,13 @@
         <v>198</v>
       </c>
       <c r="V398" s="1">
-        <v>46282.36529424768</v>
+        <v>46282.36529351852</v>
       </c>
       <c r="W398">
         <v>0</v>
       </c>
       <c r="X398" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="Y398" t="s">
         <v>350</v>
@@ -31399,16 +31396,16 @@
     </row>
     <row r="399" spans="1:35">
       <c r="A399">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B399" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C399" t="s">
         <v>50</v>
       </c>
       <c r="D399" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E399" t="s">
         <v>54</v>
@@ -31441,7 +31438,7 @@
         <v>2026</v>
       </c>
       <c r="R399">
-        <v>17952646</v>
+        <v>17952466</v>
       </c>
       <c r="S399" t="s">
         <v>54</v>
@@ -31450,7 +31447,7 @@
         <v>198</v>
       </c>
       <c r="V399" s="1">
-        <v>46282.36529490741</v>
+        <v>46282.36529424768</v>
       </c>
       <c r="W399">
         <v>0</v>
@@ -31476,10 +31473,10 @@
     </row>
     <row r="400" spans="1:35">
       <c r="A400">
-        <v>6779</v>
+        <v>6705</v>
       </c>
       <c r="B400" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C400" t="s">
         <v>50</v>
@@ -31518,16 +31515,16 @@
         <v>2026</v>
       </c>
       <c r="R400">
-        <v>18056821</v>
+        <v>17952646</v>
       </c>
       <c r="S400" t="s">
-        <v>187</v>
+        <v>54</v>
       </c>
       <c r="U400" t="s">
         <v>198</v>
       </c>
       <c r="V400" s="1">
-        <v>46282.36529869213</v>
+        <v>46282.36529490741</v>
       </c>
       <c r="W400">
         <v>0</v>
@@ -31542,7 +31539,7 @@
         <v>0</v>
       </c>
       <c r="AC400" t="s">
-        <v>187</v>
+        <v>54</v>
       </c>
       <c r="AH400" t="s">
         <v>360</v>
@@ -31553,10 +31550,10 @@
     </row>
     <row r="401" spans="1:35">
       <c r="A401">
-        <v>6945</v>
+        <v>6779</v>
       </c>
       <c r="B401" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C401" t="s">
         <v>50</v>
@@ -31568,7 +31565,7 @@
         <v>54</v>
       </c>
       <c r="F401" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G401">
         <v>9088</v>
@@ -31595,22 +31592,22 @@
         <v>2026</v>
       </c>
       <c r="R401">
-        <v>18164565</v>
+        <v>18056821</v>
       </c>
       <c r="S401" t="s">
-        <v>54</v>
+        <v>187</v>
       </c>
       <c r="U401" t="s">
         <v>198</v>
       </c>
       <c r="V401" s="1">
-        <v>46282.36531149306</v>
+        <v>46282.36529869213</v>
       </c>
       <c r="W401">
         <v>0</v>
       </c>
       <c r="X401" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Y401" t="s">
         <v>350</v>
@@ -31619,7 +31616,7 @@
         <v>0</v>
       </c>
       <c r="AC401" t="s">
-        <v>54</v>
+        <v>187</v>
       </c>
       <c r="AH401" t="s">
         <v>360</v>
@@ -31630,16 +31627,16 @@
     </row>
     <row r="402" spans="1:35">
       <c r="A402">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B402" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C402" t="s">
         <v>50</v>
       </c>
       <c r="D402" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E402" t="s">
         <v>54</v>
@@ -31672,31 +31669,31 @@
         <v>2026</v>
       </c>
       <c r="R402">
-        <v>18178199</v>
+        <v>18164565</v>
       </c>
       <c r="S402" t="s">
-        <v>187</v>
+        <v>54</v>
       </c>
       <c r="U402" t="s">
         <v>198</v>
       </c>
       <c r="V402" s="1">
-        <v>46282.36531554398</v>
+        <v>46282.36531149306</v>
       </c>
       <c r="W402">
         <v>0</v>
       </c>
       <c r="X402" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Y402" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AB402">
         <v>0</v>
       </c>
       <c r="AC402" t="s">
-        <v>187</v>
+        <v>54</v>
       </c>
       <c r="AH402" t="s">
         <v>360</v>
@@ -31707,16 +31704,16 @@
     </row>
     <row r="403" spans="1:35">
       <c r="A403">
-        <v>6962</v>
+        <v>6949</v>
       </c>
       <c r="B403" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C403" t="s">
         <v>50</v>
       </c>
       <c r="D403" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E403" t="s">
         <v>54</v>
@@ -31749,31 +31746,31 @@
         <v>2026</v>
       </c>
       <c r="R403">
-        <v>18188788</v>
+        <v>18178199</v>
       </c>
       <c r="S403" t="s">
-        <v>54</v>
+        <v>187</v>
       </c>
       <c r="U403" t="s">
         <v>198</v>
       </c>
       <c r="V403" s="1">
-        <v>46282.36531253472</v>
+        <v>46282.36531554398</v>
       </c>
       <c r="W403">
         <v>0</v>
       </c>
       <c r="X403" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="Y403" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AB403">
         <v>0</v>
       </c>
       <c r="AC403" t="s">
-        <v>54</v>
+        <v>187</v>
       </c>
       <c r="AH403" t="s">
         <v>360</v>
@@ -31784,10 +31781,10 @@
     </row>
     <row r="404" spans="1:35">
       <c r="A404">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B404" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C404" t="s">
         <v>50</v>
@@ -31826,7 +31823,7 @@
         <v>2026</v>
       </c>
       <c r="R404">
-        <v>18188694</v>
+        <v>18188788</v>
       </c>
       <c r="S404" t="s">
         <v>54</v>
@@ -31835,7 +31832,7 @@
         <v>198</v>
       </c>
       <c r="V404" s="1">
-        <v>46282.36531288194</v>
+        <v>46282.36531253472</v>
       </c>
       <c r="W404">
         <v>0</v>
@@ -31861,10 +31858,10 @@
     </row>
     <row r="405" spans="1:35">
       <c r="A405">
-        <v>6404</v>
+        <v>6963</v>
       </c>
       <c r="B405" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C405" t="s">
         <v>50</v>
@@ -31876,10 +31873,10 @@
         <v>54</v>
       </c>
       <c r="F405" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G405">
-        <v>6813</v>
+        <v>9088</v>
       </c>
       <c r="H405">
         <v>0</v>
@@ -31888,7 +31885,7 @@
         <v>65</v>
       </c>
       <c r="J405" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N405" s="1">
         <v>46283</v>
@@ -31903,7 +31900,7 @@
         <v>2026</v>
       </c>
       <c r="R405">
-        <v>16962319</v>
+        <v>18188694</v>
       </c>
       <c r="S405" t="s">
         <v>54</v>
@@ -31912,13 +31909,13 @@
         <v>198</v>
       </c>
       <c r="V405" s="1">
-        <v>46282.79619331018</v>
+        <v>46282.36531288194</v>
       </c>
       <c r="W405">
         <v>0</v>
       </c>
       <c r="X405" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="Y405" t="s">
         <v>350</v>
@@ -31938,16 +31935,16 @@
     </row>
     <row r="406" spans="1:35">
       <c r="A406">
-        <v>6486</v>
+        <v>6404</v>
       </c>
       <c r="B406" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C406" t="s">
         <v>50</v>
       </c>
       <c r="D406" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E406" t="s">
         <v>54</v>
@@ -31980,7 +31977,7 @@
         <v>2026</v>
       </c>
       <c r="R406">
-        <v>16976198</v>
+        <v>16962319</v>
       </c>
       <c r="S406" t="s">
         <v>54</v>
@@ -31989,13 +31986,13 @@
         <v>198</v>
       </c>
       <c r="V406" s="1">
-        <v>46282.79620888889</v>
+        <v>46282.79619331018</v>
       </c>
       <c r="W406">
         <v>0</v>
       </c>
       <c r="X406" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Y406" t="s">
         <v>350</v>
@@ -32015,10 +32012,10 @@
     </row>
     <row r="407" spans="1:35">
       <c r="A407">
-        <v>6548</v>
+        <v>6486</v>
       </c>
       <c r="B407" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C407" t="s">
         <v>50</v>
@@ -32057,7 +32054,7 @@
         <v>2026</v>
       </c>
       <c r="R407">
-        <v>17222763</v>
+        <v>16976198</v>
       </c>
       <c r="S407" t="s">
         <v>54</v>
@@ -32066,13 +32063,13 @@
         <v>198</v>
       </c>
       <c r="V407" s="1">
-        <v>46282.79623803241</v>
+        <v>46282.79620888889</v>
       </c>
       <c r="W407">
         <v>0</v>
       </c>
       <c r="X407" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="Y407" t="s">
         <v>350</v>
@@ -32092,10 +32089,10 @@
     </row>
     <row r="408" spans="1:35">
       <c r="A408">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B408" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C408" t="s">
         <v>50</v>
@@ -32104,7 +32101,7 @@
         <v>51</v>
       </c>
       <c r="E408" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F408" t="s">
         <v>56</v>
@@ -32134,22 +32131,22 @@
         <v>2026</v>
       </c>
       <c r="R408">
-        <v>17042469</v>
+        <v>17222763</v>
       </c>
       <c r="S408" t="s">
-        <v>187</v>
+        <v>54</v>
       </c>
       <c r="U408" t="s">
         <v>198</v>
       </c>
       <c r="V408" s="1">
-        <v>46282.79625384259</v>
+        <v>46282.79623803241</v>
       </c>
       <c r="W408">
         <v>0</v>
       </c>
       <c r="X408" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Y408" t="s">
         <v>350</v>
@@ -32158,7 +32155,7 @@
         <v>0</v>
       </c>
       <c r="AC408" t="s">
-        <v>187</v>
+        <v>54</v>
       </c>
       <c r="AH408" t="s">
         <v>360</v>
@@ -32169,16 +32166,16 @@
     </row>
     <row r="409" spans="1:35">
       <c r="A409">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B409" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C409" t="s">
         <v>50</v>
       </c>
       <c r="D409" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E409" t="s">
         <v>55</v>
@@ -32211,16 +32208,16 @@
         <v>2026</v>
       </c>
       <c r="R409">
-        <v>16960013</v>
+        <v>17042469</v>
       </c>
       <c r="S409" t="s">
-        <v>55</v>
+        <v>187</v>
       </c>
       <c r="U409" t="s">
         <v>198</v>
       </c>
       <c r="V409" s="1">
-        <v>46282.79626969907</v>
+        <v>46282.79625384259</v>
       </c>
       <c r="W409">
         <v>0</v>
@@ -32235,7 +32232,7 @@
         <v>0</v>
       </c>
       <c r="AC409" t="s">
-        <v>55</v>
+        <v>187</v>
       </c>
       <c r="AH409" t="s">
         <v>360</v>
@@ -32246,19 +32243,19 @@
     </row>
     <row r="410" spans="1:35">
       <c r="A410">
-        <v>6703</v>
+        <v>6628</v>
       </c>
       <c r="B410" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C410" t="s">
         <v>50</v>
       </c>
       <c r="D410" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E410" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F410" t="s">
         <v>56</v>
@@ -32288,22 +32285,22 @@
         <v>2026</v>
       </c>
       <c r="R410">
-        <v>17941197</v>
+        <v>16960013</v>
       </c>
       <c r="S410" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="U410" t="s">
         <v>198</v>
       </c>
       <c r="V410" s="1">
-        <v>46282.79628394676</v>
+        <v>46282.79626969907</v>
       </c>
       <c r="W410">
         <v>0</v>
       </c>
       <c r="X410" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="Y410" t="s">
         <v>350</v>
@@ -32312,7 +32309,7 @@
         <v>0</v>
       </c>
       <c r="AC410" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AH410" t="s">
         <v>360</v>
@@ -32323,16 +32320,16 @@
     </row>
     <row r="411" spans="1:35">
       <c r="A411">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B411" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C411" t="s">
         <v>50</v>
       </c>
       <c r="D411" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E411" t="s">
         <v>54</v>
@@ -32365,7 +32362,7 @@
         <v>2026</v>
       </c>
       <c r="R411">
-        <v>17952411</v>
+        <v>17941197</v>
       </c>
       <c r="S411" t="s">
         <v>54</v>
@@ -32374,13 +32371,13 @@
         <v>198</v>
       </c>
       <c r="V411" s="1">
-        <v>46282.79630097222</v>
+        <v>46282.79628394676</v>
       </c>
       <c r="W411">
         <v>0</v>
       </c>
       <c r="X411" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="Y411" t="s">
         <v>350</v>
@@ -32400,16 +32397,16 @@
     </row>
     <row r="412" spans="1:35">
       <c r="A412">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B412" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C412" t="s">
         <v>50</v>
       </c>
       <c r="D412" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E412" t="s">
         <v>54</v>
@@ -32442,7 +32439,7 @@
         <v>2026</v>
       </c>
       <c r="R412">
-        <v>17952591</v>
+        <v>17952411</v>
       </c>
       <c r="S412" t="s">
         <v>54</v>
@@ -32451,7 +32448,7 @@
         <v>198</v>
       </c>
       <c r="V412" s="1">
-        <v>46282.79631204861</v>
+        <v>46282.79630097222</v>
       </c>
       <c r="W412">
         <v>0</v>
@@ -32477,10 +32474,10 @@
     </row>
     <row r="413" spans="1:35">
       <c r="A413">
-        <v>6945</v>
+        <v>6705</v>
       </c>
       <c r="B413" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C413" t="s">
         <v>50</v>
@@ -32492,7 +32489,7 @@
         <v>54</v>
       </c>
       <c r="F413" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G413">
         <v>6813</v>
@@ -32519,7 +32516,7 @@
         <v>2026</v>
       </c>
       <c r="R413">
-        <v>18164530</v>
+        <v>17952591</v>
       </c>
       <c r="S413" t="s">
         <v>54</v>
@@ -32528,16 +32525,16 @@
         <v>198</v>
       </c>
       <c r="V413" s="1">
-        <v>46282.79637748843</v>
+        <v>46282.79631204861</v>
       </c>
       <c r="W413">
         <v>0</v>
       </c>
       <c r="X413" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Y413" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AB413">
         <v>0</v>
@@ -32554,16 +32551,16 @@
     </row>
     <row r="414" spans="1:35">
       <c r="A414">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B414" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C414" t="s">
         <v>50</v>
       </c>
       <c r="D414" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E414" t="s">
         <v>54</v>
@@ -32596,22 +32593,22 @@
         <v>2026</v>
       </c>
       <c r="R414">
-        <v>18178169</v>
+        <v>18164530</v>
       </c>
       <c r="S414" t="s">
-        <v>187</v>
+        <v>54</v>
       </c>
       <c r="U414" t="s">
         <v>198</v>
       </c>
       <c r="V414" s="1">
-        <v>46282.79638901621</v>
+        <v>46282.79637748843</v>
       </c>
       <c r="W414">
         <v>0</v>
       </c>
       <c r="X414" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Y414" t="s">
         <v>351</v>
@@ -32620,7 +32617,7 @@
         <v>0</v>
       </c>
       <c r="AC414" t="s">
-        <v>187</v>
+        <v>54</v>
       </c>
       <c r="AH414" t="s">
         <v>360</v>
@@ -32631,10 +32628,10 @@
     </row>
     <row r="415" spans="1:35">
       <c r="A415">
-        <v>5417</v>
+        <v>6949</v>
       </c>
       <c r="B415" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C415" t="s">
         <v>50</v>
@@ -32646,10 +32643,10 @@
         <v>54</v>
       </c>
       <c r="F415" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G415">
-        <v>7027</v>
+        <v>6813</v>
       </c>
       <c r="H415">
         <v>0</v>
@@ -32658,46 +32655,49 @@
         <v>65</v>
       </c>
       <c r="J415" t="s">
-        <v>121</v>
+        <v>150</v>
       </c>
       <c r="N415" s="1">
-        <v>46289</v>
+        <v>46283</v>
+      </c>
+      <c r="O415" t="s">
+        <v>159</v>
       </c>
       <c r="P415">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q415">
         <v>2026</v>
       </c>
       <c r="R415">
-        <v>17399290</v>
+        <v>18178169</v>
       </c>
       <c r="S415" t="s">
-        <v>54</v>
+        <v>187</v>
       </c>
       <c r="U415" t="s">
         <v>198</v>
       </c>
       <c r="V415" s="1">
-        <v>46283.39832862269</v>
+        <v>46282.79638901621</v>
       </c>
       <c r="W415">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="X415" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="Y415" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AB415">
         <v>0</v>
       </c>
       <c r="AC415" t="s">
-        <v>54</v>
+        <v>187</v>
       </c>
       <c r="AH415" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AI415" t="s">
         <v>363</v>
@@ -32705,16 +32705,16 @@
     </row>
     <row r="416" spans="1:35">
       <c r="A416">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B416" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C416" t="s">
         <v>50</v>
       </c>
       <c r="D416" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E416" t="s">
         <v>54</v>
@@ -32744,7 +32744,7 @@
         <v>2026</v>
       </c>
       <c r="R416">
-        <v>16962348</v>
+        <v>17399290</v>
       </c>
       <c r="S416" t="s">
         <v>54</v>
@@ -32753,16 +32753,16 @@
         <v>198</v>
       </c>
       <c r="V416" s="1">
-        <v>46282.64018086805</v>
+        <v>46283.39832862269</v>
       </c>
       <c r="W416">
         <v>-6</v>
       </c>
       <c r="X416" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="Y416" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AB416">
         <v>0</v>
@@ -32774,6 +32774,80 @@
         <v>358</v>
       </c>
       <c r="AI416" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="417" spans="1:35">
+      <c r="A417">
+        <v>6404</v>
+      </c>
+      <c r="B417" t="s">
+        <v>47</v>
+      </c>
+      <c r="C417" t="s">
+        <v>50</v>
+      </c>
+      <c r="D417" t="s">
+        <v>53</v>
+      </c>
+      <c r="E417" t="s">
+        <v>54</v>
+      </c>
+      <c r="F417" t="s">
+        <v>56</v>
+      </c>
+      <c r="G417">
+        <v>7027</v>
+      </c>
+      <c r="H417">
+        <v>0</v>
+      </c>
+      <c r="I417" t="s">
+        <v>65</v>
+      </c>
+      <c r="J417" t="s">
+        <v>121</v>
+      </c>
+      <c r="N417" s="1">
+        <v>46289</v>
+      </c>
+      <c r="P417">
+        <v>8</v>
+      </c>
+      <c r="Q417">
+        <v>2026</v>
+      </c>
+      <c r="R417">
+        <v>16962348</v>
+      </c>
+      <c r="S417" t="s">
+        <v>54</v>
+      </c>
+      <c r="U417" t="s">
+        <v>198</v>
+      </c>
+      <c r="V417" s="1">
+        <v>46282.64018086805</v>
+      </c>
+      <c r="W417">
+        <v>-6</v>
+      </c>
+      <c r="X417" t="s">
+        <v>210</v>
+      </c>
+      <c r="Y417" t="s">
+        <v>353</v>
+      </c>
+      <c r="AB417">
+        <v>0</v>
+      </c>
+      <c r="AC417" t="s">
+        <v>54</v>
+      </c>
+      <c r="AH417" t="s">
+        <v>358</v>
+      </c>
+      <c r="AI417" t="s">
         <v>363</v>
       </c>
     </row>

--- a/data/base/goias.xlsx
+++ b/data/base/goias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6244" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6316" uniqueCount="382">
   <si>
     <t>CodCliente</t>
   </si>
@@ -1121,6 +1121,18 @@
   </si>
   <si>
     <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1805] sendo a ultima baixa feita [1805]-18/09/2026 08:30:31.. - Data Comentário: 18/09/2026 15:28</t>
+  </si>
+  <si>
+    <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1879] sendo a ultima baixa feita [1879]-21/09/2026 17:43:16.. - Data Comentário: 21/09/2026 08:55</t>
+  </si>
+  <si>
+    <t>Reaberto via Rotina Configuração Após Baixa de tarefa [11286] sendo a ultima baixa feita [11286]-21/09/2026 08:40:46.. - Data Comentário: 21/09/2026 08:35</t>
+  </si>
+  <si>
+    <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1802] sendo a ultima baixa feita [1802]-21/09/2026 18:01:06.. - Data Comentário: 21/09/2026 08:55</t>
+  </si>
+  <si>
+    <t>Reaberto via Rotina Configuração Após Baixa de tarefa [1802] sendo a ultima baixa feita [1802]-21/09/2026 08:40:45.. - Data Comentário: 21/09/2026 08:35</t>
   </si>
   <si>
     <t>Comentário Colaborador + Previsão De Conclusão  Previsão para conclusão dia 17/09/2026 - Data Comentário: 15/09/2026 09:27</t>
@@ -1510,7 +1522,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AI431"/>
+  <dimension ref="A1:AI436"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:35">
@@ -1691,10 +1703,10 @@
         <v>170</v>
       </c>
       <c r="AH2" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI2" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="3" spans="1:35">
@@ -1768,10 +1780,10 @@
         <v>171</v>
       </c>
       <c r="AH3" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI3" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="4" spans="1:35">
@@ -1845,10 +1857,10 @@
         <v>170</v>
       </c>
       <c r="AH4" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI4" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="5" spans="1:35">
@@ -1919,10 +1931,10 @@
         <v>170</v>
       </c>
       <c r="AH5" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI5" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="6" spans="1:35">
@@ -1993,10 +2005,10 @@
         <v>171</v>
       </c>
       <c r="AH6" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI6" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="7" spans="1:35">
@@ -2067,10 +2079,10 @@
         <v>171</v>
       </c>
       <c r="AH7" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI7" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="8" spans="1:35">
@@ -2141,10 +2153,10 @@
         <v>172</v>
       </c>
       <c r="AH8" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI8" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="9" spans="1:35">
@@ -2215,10 +2227,10 @@
         <v>170</v>
       </c>
       <c r="AH9" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10" spans="1:35">
@@ -2289,10 +2301,10 @@
         <v>173</v>
       </c>
       <c r="AH10" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI10" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="11" spans="1:35">
@@ -2363,10 +2375,10 @@
         <v>173</v>
       </c>
       <c r="AH11" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI11" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="12" spans="1:35">
@@ -2437,10 +2449,10 @@
         <v>174</v>
       </c>
       <c r="AH12" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI12" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="13" spans="1:35">
@@ -2508,13 +2520,13 @@
         <v>0</v>
       </c>
       <c r="AC13" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="AH13" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI13" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="14" spans="1:35">
@@ -2582,13 +2594,13 @@
         <v>0</v>
       </c>
       <c r="AC14" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="AH14" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI14" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="15" spans="1:35">
@@ -2656,10 +2668,10 @@
         <v>0</v>
       </c>
       <c r="AH15" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI15" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="16" spans="1:35">
@@ -2721,10 +2733,10 @@
         <v>0</v>
       </c>
       <c r="AH16" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI16" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="17" spans="1:35">
@@ -2792,10 +2804,10 @@
         <v>0</v>
       </c>
       <c r="AH17" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI17" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="18" spans="1:35">
@@ -2869,10 +2881,10 @@
         <v>176</v>
       </c>
       <c r="AH18" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI18" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="19" spans="1:35">
@@ -2946,10 +2958,10 @@
         <v>175</v>
       </c>
       <c r="AH19" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI19" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="20" spans="1:35">
@@ -3023,10 +3035,10 @@
         <v>176</v>
       </c>
       <c r="AH20" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI20" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="21" spans="1:35">
@@ -3100,10 +3112,10 @@
         <v>174</v>
       </c>
       <c r="AH21" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI21" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="22" spans="1:35">
@@ -3174,10 +3186,10 @@
         <v>177</v>
       </c>
       <c r="AH22" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI22" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="23" spans="1:35">
@@ -3248,10 +3260,10 @@
         <v>174</v>
       </c>
       <c r="AH23" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI23" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="24" spans="1:35">
@@ -3322,10 +3334,10 @@
         <v>174</v>
       </c>
       <c r="AH24" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI24" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="25" spans="1:35">
@@ -3396,10 +3408,10 @@
         <v>174</v>
       </c>
       <c r="AH25" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI25" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="26" spans="1:35">
@@ -3470,10 +3482,10 @@
         <v>175</v>
       </c>
       <c r="AH26" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI26" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="27" spans="1:35">
@@ -3544,10 +3556,10 @@
         <v>174</v>
       </c>
       <c r="AH27" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI27" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="28" spans="1:35">
@@ -3618,10 +3630,10 @@
         <v>174</v>
       </c>
       <c r="AH28" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI28" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="29" spans="1:35">
@@ -3692,10 +3704,10 @@
         <v>174</v>
       </c>
       <c r="AH29" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI29" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="30" spans="1:35">
@@ -3766,10 +3778,10 @@
         <v>178</v>
       </c>
       <c r="AH30" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI30" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="31" spans="1:35">
@@ -3846,10 +3858,10 @@
         <v>179</v>
       </c>
       <c r="AH31" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI31" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="32" spans="1:35">
@@ -3920,10 +3932,10 @@
         <v>180</v>
       </c>
       <c r="AH32" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI32" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="33" spans="1:35">
@@ -4000,10 +4012,10 @@
         <v>181</v>
       </c>
       <c r="AH33" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI33" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="34" spans="1:35">
@@ -4077,10 +4089,10 @@
         <v>182</v>
       </c>
       <c r="AH34" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI34" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="35" spans="1:35">
@@ -4154,13 +4166,13 @@
         <v>0</v>
       </c>
       <c r="AC35" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="AH35" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI35" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="36" spans="1:35">
@@ -4237,10 +4249,10 @@
         <v>184</v>
       </c>
       <c r="AH36" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI36" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="37" spans="1:35">
@@ -4317,10 +4329,10 @@
         <v>178</v>
       </c>
       <c r="AH37" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI37" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="38" spans="1:35">
@@ -4394,10 +4406,10 @@
         <v>200</v>
       </c>
       <c r="AH38" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI38" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="39" spans="1:35">
@@ -4474,10 +4486,10 @@
         <v>179</v>
       </c>
       <c r="AH39" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI39" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="40" spans="1:35">
@@ -4554,10 +4566,10 @@
         <v>179</v>
       </c>
       <c r="AH40" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI40" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="41" spans="1:35">
@@ -4634,10 +4646,10 @@
         <v>179</v>
       </c>
       <c r="AH41" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI41" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="42" spans="1:35">
@@ -4714,10 +4726,10 @@
         <v>178</v>
       </c>
       <c r="AH42" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI42" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="43" spans="1:35">
@@ -4794,10 +4806,10 @@
         <v>185</v>
       </c>
       <c r="AH43" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI43" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="44" spans="1:35">
@@ -4874,10 +4886,10 @@
         <v>180</v>
       </c>
       <c r="AH44" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI44" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="45" spans="1:35">
@@ -4954,10 +4966,10 @@
         <v>181</v>
       </c>
       <c r="AH45" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI45" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="46" spans="1:35">
@@ -5025,10 +5037,10 @@
         <v>182</v>
       </c>
       <c r="AH46" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI46" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="47" spans="1:35">
@@ -5099,10 +5111,10 @@
         <v>179</v>
       </c>
       <c r="AH47" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI47" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="48" spans="1:35">
@@ -5173,10 +5185,10 @@
         <v>179</v>
       </c>
       <c r="AH48" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI48" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="49" spans="1:35">
@@ -5247,10 +5259,10 @@
         <v>179</v>
       </c>
       <c r="AH49" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI49" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="50" spans="1:35">
@@ -5321,10 +5333,10 @@
         <v>178</v>
       </c>
       <c r="AH50" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI50" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="51" spans="1:35">
@@ -5395,10 +5407,10 @@
         <v>185</v>
       </c>
       <c r="AH51" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI51" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="52" spans="1:35">
@@ -5475,10 +5487,10 @@
         <v>180</v>
       </c>
       <c r="AH52" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI52" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="53" spans="1:35">
@@ -5549,10 +5561,10 @@
         <v>181</v>
       </c>
       <c r="AH53" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI53" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="54" spans="1:35">
@@ -5629,10 +5641,10 @@
         <v>179</v>
       </c>
       <c r="AH54" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI54" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="55" spans="1:35">
@@ -5709,10 +5721,10 @@
         <v>179</v>
       </c>
       <c r="AH55" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI55" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="56" spans="1:35">
@@ -5789,10 +5801,10 @@
         <v>179</v>
       </c>
       <c r="AH56" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI56" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="57" spans="1:35">
@@ -5869,10 +5881,10 @@
         <v>178</v>
       </c>
       <c r="AH57" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI57" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="58" spans="1:35">
@@ -5946,10 +5958,10 @@
         <v>182</v>
       </c>
       <c r="AH58" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI58" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="59" spans="1:35">
@@ -6023,13 +6035,13 @@
         <v>0</v>
       </c>
       <c r="AC59" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="AH59" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI59" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="60" spans="1:35">
@@ -6106,10 +6118,10 @@
         <v>179</v>
       </c>
       <c r="AH60" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI60" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="61" spans="1:35">
@@ -6186,10 +6198,10 @@
         <v>179</v>
       </c>
       <c r="AH61" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI61" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="62" spans="1:35">
@@ -6266,10 +6278,10 @@
         <v>179</v>
       </c>
       <c r="AH62" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI62" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="63" spans="1:35">
@@ -6346,10 +6358,10 @@
         <v>178</v>
       </c>
       <c r="AH63" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI63" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="64" spans="1:35">
@@ -6426,10 +6438,10 @@
         <v>185</v>
       </c>
       <c r="AH64" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI64" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="65" spans="1:35">
@@ -6506,10 +6518,10 @@
         <v>180</v>
       </c>
       <c r="AH65" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI65" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="66" spans="1:35">
@@ -6586,10 +6598,10 @@
         <v>181</v>
       </c>
       <c r="AH66" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI66" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="67" spans="1:35">
@@ -6666,10 +6678,10 @@
         <v>179</v>
       </c>
       <c r="AH67" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI67" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="68" spans="1:35">
@@ -6737,10 +6749,10 @@
         <v>182</v>
       </c>
       <c r="AH68" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI68" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="69" spans="1:35">
@@ -6808,13 +6820,13 @@
         <v>0</v>
       </c>
       <c r="AC69" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="AH69" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI69" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="70" spans="1:35">
@@ -6885,10 +6897,10 @@
         <v>179</v>
       </c>
       <c r="AH70" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI70" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="71" spans="1:35">
@@ -6959,10 +6971,10 @@
         <v>179</v>
       </c>
       <c r="AH71" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI71" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="72" spans="1:35">
@@ -7033,10 +7045,10 @@
         <v>179</v>
       </c>
       <c r="AH72" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI72" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="73" spans="1:35">
@@ -7107,10 +7119,10 @@
         <v>178</v>
       </c>
       <c r="AH73" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI73" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="74" spans="1:35">
@@ -7181,10 +7193,10 @@
         <v>185</v>
       </c>
       <c r="AH74" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI74" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="75" spans="1:35">
@@ -7255,10 +7267,10 @@
         <v>180</v>
       </c>
       <c r="AH75" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI75" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="76" spans="1:35">
@@ -7329,10 +7341,10 @@
         <v>181</v>
       </c>
       <c r="AH76" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI76" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="77" spans="1:35">
@@ -7403,10 +7415,10 @@
         <v>181</v>
       </c>
       <c r="AH77" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI77" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="78" spans="1:35">
@@ -7477,10 +7489,10 @@
         <v>181</v>
       </c>
       <c r="AH78" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI78" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="79" spans="1:35">
@@ -7551,10 +7563,10 @@
         <v>181</v>
       </c>
       <c r="AH79" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI79" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="80" spans="1:35">
@@ -7625,10 +7637,10 @@
         <v>201</v>
       </c>
       <c r="AH80" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI80" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="81" spans="1:35">
@@ -7696,10 +7708,10 @@
         <v>201</v>
       </c>
       <c r="AH81" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI81" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="82" spans="1:35">
@@ -7770,10 +7782,10 @@
         <v>188</v>
       </c>
       <c r="AH82" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI82" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="83" spans="1:35">
@@ -7844,10 +7856,10 @@
         <v>201</v>
       </c>
       <c r="AH83" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI83" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="84" spans="1:35">
@@ -7915,10 +7927,10 @@
         <v>201</v>
       </c>
       <c r="AH84" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI84" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="85" spans="1:35">
@@ -7989,10 +8001,10 @@
         <v>201</v>
       </c>
       <c r="AH85" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI85" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="86" spans="1:35">
@@ -8057,10 +8069,10 @@
         <v>188</v>
       </c>
       <c r="AH86" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI86" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="87" spans="1:35">
@@ -8131,10 +8143,10 @@
         <v>201</v>
       </c>
       <c r="AH87" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI87" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="88" spans="1:35">
@@ -8202,10 +8214,10 @@
         <v>201</v>
       </c>
       <c r="AH88" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI88" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="89" spans="1:35">
@@ -8276,10 +8288,10 @@
         <v>201</v>
       </c>
       <c r="AH89" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI89" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="90" spans="1:35">
@@ -8344,10 +8356,10 @@
         <v>201</v>
       </c>
       <c r="AH90" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI90" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="91" spans="1:35">
@@ -8412,10 +8424,10 @@
         <v>188</v>
       </c>
       <c r="AH91" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI91" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="92" spans="1:35">
@@ -8486,10 +8498,10 @@
         <v>201</v>
       </c>
       <c r="AH92" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI92" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="93" spans="1:35">
@@ -8557,10 +8569,10 @@
         <v>201</v>
       </c>
       <c r="AH93" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI93" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="94" spans="1:35">
@@ -8631,10 +8643,10 @@
         <v>201</v>
       </c>
       <c r="AH94" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI94" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="95" spans="1:35">
@@ -8699,10 +8711,10 @@
         <v>201</v>
       </c>
       <c r="AH95" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI95" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="96" spans="1:35">
@@ -8767,10 +8779,10 @@
         <v>188</v>
       </c>
       <c r="AH96" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI96" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="97" spans="1:35">
@@ -8841,10 +8853,10 @@
         <v>201</v>
       </c>
       <c r="AH97" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI97" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="98" spans="1:35">
@@ -8912,10 +8924,10 @@
         <v>201</v>
       </c>
       <c r="AH98" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI98" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="99" spans="1:35">
@@ -8986,10 +8998,10 @@
         <v>188</v>
       </c>
       <c r="AH99" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI99" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="100" spans="1:35">
@@ -9066,10 +9078,10 @@
         <v>201</v>
       </c>
       <c r="AH100" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI100" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="101" spans="1:35">
@@ -9137,10 +9149,10 @@
         <v>201</v>
       </c>
       <c r="AH101" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI101" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="102" spans="1:35">
@@ -9211,10 +9223,10 @@
         <v>201</v>
       </c>
       <c r="AH102" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI102" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="103" spans="1:35">
@@ -9282,10 +9294,10 @@
         <v>201</v>
       </c>
       <c r="AH103" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI103" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="104" spans="1:35">
@@ -9356,10 +9368,10 @@
         <v>201</v>
       </c>
       <c r="AH104" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI104" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="105" spans="1:35">
@@ -9424,10 +9436,10 @@
         <v>201</v>
       </c>
       <c r="AH105" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI105" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="106" spans="1:35">
@@ -9492,10 +9504,10 @@
         <v>188</v>
       </c>
       <c r="AH106" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI106" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="107" spans="1:35">
@@ -9566,10 +9578,10 @@
         <v>201</v>
       </c>
       <c r="AH107" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI107" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="108" spans="1:35">
@@ -9640,10 +9652,10 @@
         <v>201</v>
       </c>
       <c r="AH108" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI108" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="109" spans="1:35">
@@ -9711,10 +9723,10 @@
         <v>201</v>
       </c>
       <c r="AH109" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI109" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="110" spans="1:35">
@@ -9785,10 +9797,10 @@
         <v>188</v>
       </c>
       <c r="AH110" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI110" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="111" spans="1:35">
@@ -9856,10 +9868,10 @@
         <v>187</v>
       </c>
       <c r="AH111" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI111" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="112" spans="1:35">
@@ -9930,10 +9942,10 @@
         <v>188</v>
       </c>
       <c r="AH112" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI112" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:35">
@@ -10004,10 +10016,10 @@
         <v>186</v>
       </c>
       <c r="AH113" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI113" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:35">
@@ -10075,10 +10087,10 @@
         <v>187</v>
       </c>
       <c r="AH114" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI114" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="115" spans="1:35">
@@ -10149,10 +10161,10 @@
         <v>188</v>
       </c>
       <c r="AH115" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI115" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="116" spans="1:35">
@@ -10223,10 +10235,10 @@
         <v>201</v>
       </c>
       <c r="AH116" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI116" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="117" spans="1:35">
@@ -10294,10 +10306,10 @@
         <v>201</v>
       </c>
       <c r="AH117" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI117" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="118" spans="1:35">
@@ -10368,10 +10380,10 @@
         <v>201</v>
       </c>
       <c r="AH118" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI118" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="119" spans="1:35">
@@ -10436,10 +10448,10 @@
         <v>201</v>
       </c>
       <c r="AH119" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI119" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="120" spans="1:35">
@@ -10504,10 +10516,10 @@
         <v>188</v>
       </c>
       <c r="AH120" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI120" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="121" spans="1:35">
@@ -10578,10 +10590,10 @@
         <v>201</v>
       </c>
       <c r="AH121" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI121" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="122" spans="1:35">
@@ -10649,10 +10661,10 @@
         <v>201</v>
       </c>
       <c r="AH122" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI122" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="123" spans="1:35">
@@ -10723,10 +10735,10 @@
         <v>201</v>
       </c>
       <c r="AH123" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI123" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="124" spans="1:35">
@@ -10791,10 +10803,10 @@
         <v>201</v>
       </c>
       <c r="AH124" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI124" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="125" spans="1:35">
@@ -10859,10 +10871,10 @@
         <v>188</v>
       </c>
       <c r="AH125" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI125" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="126" spans="1:35">
@@ -10939,10 +10951,10 @@
         <v>188</v>
       </c>
       <c r="AH126" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI126" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="127" spans="1:35">
@@ -11019,10 +11031,10 @@
         <v>188</v>
       </c>
       <c r="AH127" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI127" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="128" spans="1:35">
@@ -11093,10 +11105,10 @@
         <v>191</v>
       </c>
       <c r="AH128" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI128" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="129" spans="1:35">
@@ -11167,10 +11179,10 @@
         <v>191</v>
       </c>
       <c r="AH129" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI129" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="130" spans="1:35">
@@ -11247,10 +11259,10 @@
         <v>191</v>
       </c>
       <c r="AH130" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI130" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="131" spans="1:35">
@@ -11321,10 +11333,10 @@
         <v>191</v>
       </c>
       <c r="AH131" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI131" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="132" spans="1:35">
@@ -11395,10 +11407,10 @@
         <v>191</v>
       </c>
       <c r="AH132" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI132" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="133" spans="1:35">
@@ -11469,10 +11481,10 @@
         <v>191</v>
       </c>
       <c r="AH133" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI133" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="134" spans="1:35">
@@ -11543,10 +11555,10 @@
         <v>191</v>
       </c>
       <c r="AH134" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI134" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="135" spans="1:35">
@@ -11623,10 +11635,10 @@
         <v>191</v>
       </c>
       <c r="AH135" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI135" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="136" spans="1:35">
@@ -11697,10 +11709,10 @@
         <v>191</v>
       </c>
       <c r="AH136" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI136" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="137" spans="1:35">
@@ -11771,10 +11783,10 @@
         <v>191</v>
       </c>
       <c r="AH137" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI137" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="138" spans="1:35">
@@ -11845,10 +11857,10 @@
         <v>191</v>
       </c>
       <c r="AH138" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI138" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="139" spans="1:35">
@@ -11925,10 +11937,10 @@
         <v>191</v>
       </c>
       <c r="AH139" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI139" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="140" spans="1:35">
@@ -11999,10 +12011,10 @@
         <v>191</v>
       </c>
       <c r="AH140" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI140" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="141" spans="1:35">
@@ -12073,10 +12085,10 @@
         <v>191</v>
       </c>
       <c r="AH141" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI141" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="142" spans="1:35">
@@ -12147,10 +12159,10 @@
         <v>191</v>
       </c>
       <c r="AH142" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI142" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="143" spans="1:35">
@@ -12221,10 +12233,10 @@
         <v>191</v>
       </c>
       <c r="AH143" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI143" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="144" spans="1:35">
@@ -12295,10 +12307,10 @@
         <v>191</v>
       </c>
       <c r="AH144" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI144" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="145" spans="1:35">
@@ -12369,10 +12381,10 @@
         <v>191</v>
       </c>
       <c r="AH145" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI145" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="146" spans="1:35">
@@ -12443,10 +12455,10 @@
         <v>191</v>
       </c>
       <c r="AH146" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI146" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="147" spans="1:35">
@@ -12517,10 +12529,10 @@
         <v>191</v>
       </c>
       <c r="AH147" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI147" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="148" spans="1:35">
@@ -12591,10 +12603,10 @@
         <v>191</v>
       </c>
       <c r="AH148" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI148" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="149" spans="1:35">
@@ -12665,10 +12677,10 @@
         <v>191</v>
       </c>
       <c r="AH149" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI149" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="150" spans="1:35">
@@ -12745,10 +12757,10 @@
         <v>191</v>
       </c>
       <c r="AH150" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI150" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="151" spans="1:35">
@@ -12819,10 +12831,10 @@
         <v>191</v>
       </c>
       <c r="AH151" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI151" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="152" spans="1:35">
@@ -12893,10 +12905,10 @@
         <v>191</v>
       </c>
       <c r="AH152" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI152" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="153" spans="1:35">
@@ -12967,10 +12979,10 @@
         <v>191</v>
       </c>
       <c r="AH153" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI153" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="154" spans="1:35">
@@ -13041,10 +13053,10 @@
         <v>192</v>
       </c>
       <c r="AH154" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI154" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="155" spans="1:35">
@@ -13115,10 +13127,10 @@
         <v>192</v>
       </c>
       <c r="AH155" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI155" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="156" spans="1:35">
@@ -13189,10 +13201,10 @@
         <v>192</v>
       </c>
       <c r="AH156" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI156" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="157" spans="1:35">
@@ -13263,10 +13275,10 @@
         <v>192</v>
       </c>
       <c r="AH157" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI157" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="158" spans="1:35">
@@ -13337,10 +13349,10 @@
         <v>192</v>
       </c>
       <c r="AH158" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI158" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="159" spans="1:35">
@@ -13411,10 +13423,10 @@
         <v>192</v>
       </c>
       <c r="AH159" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI159" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="160" spans="1:35">
@@ -13485,10 +13497,10 @@
         <v>192</v>
       </c>
       <c r="AH160" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI160" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="161" spans="1:35">
@@ -13559,10 +13571,10 @@
         <v>192</v>
       </c>
       <c r="AH161" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI161" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="162" spans="1:35">
@@ -13636,10 +13648,10 @@
         <v>192</v>
       </c>
       <c r="AH162" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI162" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="163" spans="1:35">
@@ -13713,10 +13725,10 @@
         <v>192</v>
       </c>
       <c r="AH163" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI163" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="164" spans="1:35">
@@ -13790,10 +13802,10 @@
         <v>192</v>
       </c>
       <c r="AH164" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI164" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="165" spans="1:35">
@@ -13867,10 +13879,10 @@
         <v>192</v>
       </c>
       <c r="AH165" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI165" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="166" spans="1:35">
@@ -13944,10 +13956,10 @@
         <v>192</v>
       </c>
       <c r="AH166" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI166" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="167" spans="1:35">
@@ -14021,10 +14033,10 @@
         <v>192</v>
       </c>
       <c r="AH167" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI167" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="168" spans="1:35">
@@ -14098,10 +14110,10 @@
         <v>192</v>
       </c>
       <c r="AH168" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI168" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="169" spans="1:35">
@@ -14175,10 +14187,10 @@
         <v>192</v>
       </c>
       <c r="AH169" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI169" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="170" spans="1:35">
@@ -14252,10 +14264,10 @@
         <v>192</v>
       </c>
       <c r="AH170" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI170" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="171" spans="1:35">
@@ -14329,10 +14341,10 @@
         <v>192</v>
       </c>
       <c r="AH171" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI171" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="172" spans="1:35">
@@ -14406,10 +14418,10 @@
         <v>192</v>
       </c>
       <c r="AH172" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI172" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="173" spans="1:35">
@@ -14483,10 +14495,10 @@
         <v>192</v>
       </c>
       <c r="AH173" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI173" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="174" spans="1:35">
@@ -14560,10 +14572,10 @@
         <v>192</v>
       </c>
       <c r="AH174" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI174" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="175" spans="1:35">
@@ -14637,10 +14649,10 @@
         <v>192</v>
       </c>
       <c r="AH175" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI175" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="176" spans="1:35">
@@ -14708,10 +14720,10 @@
         <v>192</v>
       </c>
       <c r="AH176" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI176" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="177" spans="1:35">
@@ -14779,10 +14791,10 @@
         <v>192</v>
       </c>
       <c r="AH177" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI177" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="178" spans="1:35">
@@ -14850,10 +14862,10 @@
         <v>192</v>
       </c>
       <c r="AH178" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI178" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="179" spans="1:35">
@@ -14921,10 +14933,10 @@
         <v>192</v>
       </c>
       <c r="AH179" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI179" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="180" spans="1:35">
@@ -14992,10 +15004,10 @@
         <v>192</v>
       </c>
       <c r="AH180" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI180" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="181" spans="1:35">
@@ -15063,10 +15075,10 @@
         <v>192</v>
       </c>
       <c r="AH181" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI181" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="182" spans="1:35">
@@ -15134,10 +15146,10 @@
         <v>54</v>
       </c>
       <c r="AH182" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI182" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="183" spans="1:35">
@@ -15205,10 +15217,10 @@
         <v>54</v>
       </c>
       <c r="AH183" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI183" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="184" spans="1:35">
@@ -15276,10 +15288,10 @@
         <v>54</v>
       </c>
       <c r="AH184" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI184" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="185" spans="1:35">
@@ -15347,10 +15359,10 @@
         <v>54</v>
       </c>
       <c r="AH185" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI185" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="186" spans="1:35">
@@ -15418,10 +15430,10 @@
         <v>193</v>
       </c>
       <c r="AH186" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI186" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="187" spans="1:35">
@@ -15489,10 +15501,10 @@
         <v>55</v>
       </c>
       <c r="AH187" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI187" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="188" spans="1:35">
@@ -15560,10 +15572,10 @@
         <v>54</v>
       </c>
       <c r="AH188" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI188" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="189" spans="1:35">
@@ -15631,10 +15643,10 @@
         <v>54</v>
       </c>
       <c r="AH189" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI189" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="190" spans="1:35">
@@ -15702,10 +15714,10 @@
         <v>54</v>
       </c>
       <c r="AH190" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI190" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="191" spans="1:35">
@@ -15773,10 +15785,10 @@
         <v>193</v>
       </c>
       <c r="AH191" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI191" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="192" spans="1:35">
@@ -15844,10 +15856,10 @@
         <v>54</v>
       </c>
       <c r="AH192" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI192" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="193" spans="1:35">
@@ -15915,10 +15927,10 @@
         <v>193</v>
       </c>
       <c r="AH193" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI193" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="194" spans="1:35">
@@ -15986,10 +15998,10 @@
         <v>54</v>
       </c>
       <c r="AH194" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI194" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="195" spans="1:35">
@@ -16057,10 +16069,10 @@
         <v>54</v>
       </c>
       <c r="AH195" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI195" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="196" spans="1:35">
@@ -16128,10 +16140,10 @@
         <v>54</v>
       </c>
       <c r="AH196" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI196" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="197" spans="1:35">
@@ -16199,10 +16211,10 @@
         <v>54</v>
       </c>
       <c r="AH197" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI197" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="198" spans="1:35">
@@ -16270,10 +16282,10 @@
         <v>54</v>
       </c>
       <c r="AH198" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI198" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="199" spans="1:35">
@@ -16341,10 +16353,10 @@
         <v>54</v>
       </c>
       <c r="AH199" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI199" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="200" spans="1:35">
@@ -16412,10 +16424,10 @@
         <v>193</v>
       </c>
       <c r="AH200" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI200" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="201" spans="1:35">
@@ -16483,10 +16495,10 @@
         <v>55</v>
       </c>
       <c r="AH201" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI201" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="202" spans="1:35">
@@ -16557,10 +16569,10 @@
         <v>54</v>
       </c>
       <c r="AH202" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI202" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="203" spans="1:35">
@@ -16631,10 +16643,10 @@
         <v>54</v>
       </c>
       <c r="AH203" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI203" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="204" spans="1:35">
@@ -16705,10 +16717,10 @@
         <v>54</v>
       </c>
       <c r="AH204" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI204" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="205" spans="1:35">
@@ -16779,10 +16791,10 @@
         <v>54</v>
       </c>
       <c r="AH205" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI205" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="206" spans="1:35">
@@ -16850,10 +16862,10 @@
         <v>54</v>
       </c>
       <c r="AH206" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI206" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="207" spans="1:35">
@@ -16921,10 +16933,10 @@
         <v>54</v>
       </c>
       <c r="AH207" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI207" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="208" spans="1:35">
@@ -16989,10 +17001,10 @@
         <v>0</v>
       </c>
       <c r="AH208" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI208" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="209" spans="1:35">
@@ -17054,10 +17066,10 @@
         <v>0</v>
       </c>
       <c r="AH209" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI209" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="210" spans="1:35">
@@ -17125,13 +17137,13 @@
         <v>0</v>
       </c>
       <c r="AC210" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="AH210" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI210" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="211" spans="1:35">
@@ -17202,10 +17214,10 @@
         <v>175</v>
       </c>
       <c r="AH211" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI211" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="212" spans="1:35">
@@ -17282,10 +17294,10 @@
         <v>179</v>
       </c>
       <c r="AH212" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI212" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="213" spans="1:35">
@@ -17362,10 +17374,10 @@
         <v>179</v>
       </c>
       <c r="AH213" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI213" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="214" spans="1:35">
@@ -17442,10 +17454,10 @@
         <v>180</v>
       </c>
       <c r="AH214" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI214" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="215" spans="1:35">
@@ -17522,10 +17534,10 @@
         <v>185</v>
       </c>
       <c r="AH215" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI215" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="216" spans="1:35">
@@ -17602,10 +17614,10 @@
         <v>179</v>
       </c>
       <c r="AH216" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI216" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="217" spans="1:35">
@@ -17682,10 +17694,10 @@
         <v>184</v>
       </c>
       <c r="AH217" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI217" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="218" spans="1:35">
@@ -17762,10 +17774,10 @@
         <v>179</v>
       </c>
       <c r="AH218" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI218" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="219" spans="1:35">
@@ -17842,10 +17854,10 @@
         <v>179</v>
       </c>
       <c r="AH219" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI219" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="220" spans="1:35">
@@ -17916,10 +17928,10 @@
         <v>178</v>
       </c>
       <c r="AH220" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI220" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="221" spans="1:35">
@@ -17990,10 +18002,10 @@
         <v>185</v>
       </c>
       <c r="AH221" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI221" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="222" spans="1:35">
@@ -18070,10 +18082,10 @@
         <v>179</v>
       </c>
       <c r="AH222" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI222" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="223" spans="1:35">
@@ -18150,10 +18162,10 @@
         <v>184</v>
       </c>
       <c r="AH223" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI223" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="224" spans="1:35">
@@ -18230,10 +18242,10 @@
         <v>179</v>
       </c>
       <c r="AH224" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI224" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="225" spans="1:35">
@@ -18310,10 +18322,10 @@
         <v>179</v>
       </c>
       <c r="AH225" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI225" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="226" spans="1:35">
@@ -18384,10 +18396,10 @@
         <v>178</v>
       </c>
       <c r="AH226" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI226" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="227" spans="1:35">
@@ -18458,10 +18470,10 @@
         <v>185</v>
       </c>
       <c r="AH227" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI227" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="228" spans="1:35">
@@ -18532,10 +18544,10 @@
         <v>182</v>
       </c>
       <c r="AH228" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI228" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="229" spans="1:35">
@@ -18609,10 +18621,10 @@
         <v>183</v>
       </c>
       <c r="AH229" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI229" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="230" spans="1:35">
@@ -18686,10 +18698,10 @@
         <v>179</v>
       </c>
       <c r="AH230" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI230" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="231" spans="1:35">
@@ -18763,10 +18775,10 @@
         <v>184</v>
       </c>
       <c r="AH231" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI231" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="232" spans="1:35">
@@ -18840,10 +18852,10 @@
         <v>179</v>
       </c>
       <c r="AH232" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI232" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="233" spans="1:35">
@@ -18917,10 +18929,10 @@
         <v>179</v>
       </c>
       <c r="AH233" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI233" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="234" spans="1:35">
@@ -18997,10 +19009,10 @@
         <v>178</v>
       </c>
       <c r="AH234" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI234" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="235" spans="1:35">
@@ -19074,10 +19086,10 @@
         <v>185</v>
       </c>
       <c r="AH235" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI235" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="236" spans="1:35">
@@ -19151,10 +19163,10 @@
         <v>180</v>
       </c>
       <c r="AH236" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI236" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="237" spans="1:35">
@@ -19228,10 +19240,10 @@
         <v>181</v>
       </c>
       <c r="AH237" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI237" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="238" spans="1:35">
@@ -19305,10 +19317,10 @@
         <v>182</v>
       </c>
       <c r="AH238" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI238" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="239" spans="1:35">
@@ -19385,10 +19397,10 @@
         <v>179</v>
       </c>
       <c r="AH239" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI239" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="240" spans="1:35">
@@ -19465,10 +19477,10 @@
         <v>179</v>
       </c>
       <c r="AH240" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI240" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="241" spans="1:35">
@@ -19545,10 +19557,10 @@
         <v>179</v>
       </c>
       <c r="AH241" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI241" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="242" spans="1:35">
@@ -19625,10 +19637,10 @@
         <v>185</v>
       </c>
       <c r="AH242" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI242" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="243" spans="1:35">
@@ -19705,10 +19717,10 @@
         <v>180</v>
       </c>
       <c r="AH243" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI243" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="244" spans="1:35">
@@ -19779,10 +19791,10 @@
         <v>181</v>
       </c>
       <c r="AH244" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI244" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="245" spans="1:35">
@@ -19853,10 +19865,10 @@
         <v>182</v>
       </c>
       <c r="AH245" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI245" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="246" spans="1:35">
@@ -19933,10 +19945,10 @@
         <v>179</v>
       </c>
       <c r="AH246" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI246" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="247" spans="1:35">
@@ -20010,10 +20022,10 @@
         <v>184</v>
       </c>
       <c r="AH247" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI247" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="248" spans="1:35">
@@ -20090,10 +20102,10 @@
         <v>179</v>
       </c>
       <c r="AH248" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI248" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="249" spans="1:35">
@@ -20170,10 +20182,10 @@
         <v>179</v>
       </c>
       <c r="AH249" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI249" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="250" spans="1:35">
@@ -20247,10 +20259,10 @@
         <v>178</v>
       </c>
       <c r="AH250" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI250" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="251" spans="1:35">
@@ -20324,10 +20336,10 @@
         <v>185</v>
       </c>
       <c r="AH251" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI251" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="252" spans="1:35">
@@ -20401,10 +20413,10 @@
         <v>180</v>
       </c>
       <c r="AH252" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI252" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="253" spans="1:35">
@@ -20478,10 +20490,10 @@
         <v>181</v>
       </c>
       <c r="AH253" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI253" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="254" spans="1:35">
@@ -20558,10 +20570,10 @@
         <v>185</v>
       </c>
       <c r="AH254" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI254" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="255" spans="1:35">
@@ -20632,10 +20644,10 @@
         <v>179</v>
       </c>
       <c r="AH255" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI255" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="256" spans="1:35">
@@ -20706,10 +20718,10 @@
         <v>179</v>
       </c>
       <c r="AH256" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI256" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="257" spans="1:35">
@@ -20780,10 +20792,10 @@
         <v>179</v>
       </c>
       <c r="AH257" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI257" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="258" spans="1:35">
@@ -20860,10 +20872,10 @@
         <v>190</v>
       </c>
       <c r="AH258" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI258" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="259" spans="1:35">
@@ -20940,10 +20952,10 @@
         <v>190</v>
       </c>
       <c r="AH259" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI259" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="260" spans="1:35">
@@ -21020,10 +21032,10 @@
         <v>189</v>
       </c>
       <c r="AH260" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI260" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="261" spans="1:35">
@@ -21091,10 +21103,10 @@
         <v>187</v>
       </c>
       <c r="AH261" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI261" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="262" spans="1:35">
@@ -21171,10 +21183,10 @@
         <v>186</v>
       </c>
       <c r="AH262" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI262" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="263" spans="1:35">
@@ -21242,10 +21254,10 @@
         <v>201</v>
       </c>
       <c r="AH263" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI263" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="264" spans="1:35">
@@ -21322,10 +21334,10 @@
         <v>201</v>
       </c>
       <c r="AH264" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI264" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="265" spans="1:35">
@@ -21399,10 +21411,10 @@
         <v>187</v>
       </c>
       <c r="AH265" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI265" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="266" spans="1:35">
@@ -21479,10 +21491,10 @@
         <v>188</v>
       </c>
       <c r="AH266" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI266" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="267" spans="1:35">
@@ -21556,10 +21568,10 @@
         <v>190</v>
       </c>
       <c r="AH267" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI267" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="268" spans="1:35">
@@ -21636,10 +21648,10 @@
         <v>190</v>
       </c>
       <c r="AH268" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI268" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="269" spans="1:35">
@@ -21713,10 +21725,10 @@
         <v>189</v>
       </c>
       <c r="AH269" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI269" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="270" spans="1:35">
@@ -21787,10 +21799,10 @@
         <v>187</v>
       </c>
       <c r="AH270" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI270" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="271" spans="1:35">
@@ -21864,10 +21876,10 @@
         <v>190</v>
       </c>
       <c r="AH271" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI271" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="272" spans="1:35">
@@ -21941,10 +21953,10 @@
         <v>190</v>
       </c>
       <c r="AH272" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI272" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="273" spans="1:35">
@@ -22021,10 +22033,10 @@
         <v>186</v>
       </c>
       <c r="AH273" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI273" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="274" spans="1:35">
@@ -22092,10 +22104,10 @@
         <v>201</v>
       </c>
       <c r="AH274" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI274" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="275" spans="1:35">
@@ -22169,10 +22181,10 @@
         <v>187</v>
       </c>
       <c r="AH275" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI275" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="276" spans="1:35">
@@ -22243,10 +22255,10 @@
         <v>190</v>
       </c>
       <c r="AH276" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI276" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="277" spans="1:35">
@@ -22317,10 +22329,10 @@
         <v>190</v>
       </c>
       <c r="AH277" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI277" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="278" spans="1:35">
@@ -22391,10 +22403,10 @@
         <v>188</v>
       </c>
       <c r="AH278" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI278" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="279" spans="1:35">
@@ -22468,10 +22480,10 @@
         <v>187</v>
       </c>
       <c r="AH279" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI279" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="280" spans="1:35">
@@ -22545,10 +22557,10 @@
         <v>187</v>
       </c>
       <c r="AH280" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI280" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="281" spans="1:35">
@@ -22625,10 +22637,10 @@
         <v>188</v>
       </c>
       <c r="AH281" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI281" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="282" spans="1:35">
@@ -22705,10 +22717,10 @@
         <v>191</v>
       </c>
       <c r="AH282" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI282" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="283" spans="1:35">
@@ -22782,10 +22794,10 @@
         <v>191</v>
       </c>
       <c r="AH283" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI283" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="284" spans="1:35">
@@ -22862,10 +22874,10 @@
         <v>191</v>
       </c>
       <c r="AH284" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI284" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="285" spans="1:35">
@@ -22936,10 +22948,10 @@
         <v>191</v>
       </c>
       <c r="AH285" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI285" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="286" spans="1:35">
@@ -23010,10 +23022,10 @@
         <v>191</v>
       </c>
       <c r="AH286" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI286" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="287" spans="1:35">
@@ -23084,10 +23096,10 @@
         <v>191</v>
       </c>
       <c r="AH287" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI287" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="288" spans="1:35">
@@ -23158,10 +23170,10 @@
         <v>191</v>
       </c>
       <c r="AH288" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI288" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="289" spans="1:35">
@@ -23232,10 +23244,10 @@
         <v>191</v>
       </c>
       <c r="AH289" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI289" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="290" spans="1:35">
@@ -23312,10 +23324,10 @@
         <v>191</v>
       </c>
       <c r="AH290" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI290" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="291" spans="1:35">
@@ -23386,10 +23398,10 @@
         <v>191</v>
       </c>
       <c r="AH291" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI291" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="292" spans="1:35">
@@ -23466,10 +23478,10 @@
         <v>191</v>
       </c>
       <c r="AH292" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI292" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="293" spans="1:35">
@@ -23540,10 +23552,10 @@
         <v>191</v>
       </c>
       <c r="AH293" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI293" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="294" spans="1:35">
@@ -23614,10 +23626,10 @@
         <v>191</v>
       </c>
       <c r="AH294" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI294" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="295" spans="1:35">
@@ -23688,10 +23700,10 @@
         <v>191</v>
       </c>
       <c r="AH295" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI295" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="296" spans="1:35">
@@ -23768,10 +23780,10 @@
         <v>191</v>
       </c>
       <c r="AH296" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI296" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="297" spans="1:35">
@@ -23842,10 +23854,10 @@
         <v>191</v>
       </c>
       <c r="AH297" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI297" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="298" spans="1:35">
@@ -23916,10 +23928,10 @@
         <v>191</v>
       </c>
       <c r="AH298" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI298" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="299" spans="1:35">
@@ -23990,10 +24002,10 @@
         <v>191</v>
       </c>
       <c r="AH299" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI299" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="300" spans="1:35">
@@ -24064,10 +24076,10 @@
         <v>191</v>
       </c>
       <c r="AH300" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI300" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="301" spans="1:35">
@@ -24138,10 +24150,10 @@
         <v>191</v>
       </c>
       <c r="AH301" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI301" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="302" spans="1:35">
@@ -24212,10 +24224,10 @@
         <v>191</v>
       </c>
       <c r="AH302" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI302" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="303" spans="1:35">
@@ -24292,10 +24304,10 @@
         <v>191</v>
       </c>
       <c r="AH303" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI303" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="304" spans="1:35">
@@ -24372,10 +24384,10 @@
         <v>191</v>
       </c>
       <c r="AH304" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI304" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="305" spans="1:35">
@@ -24452,10 +24464,10 @@
         <v>191</v>
       </c>
       <c r="AH305" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI305" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="306" spans="1:35">
@@ -24529,10 +24541,10 @@
         <v>191</v>
       </c>
       <c r="AH306" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI306" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="307" spans="1:35">
@@ -24606,10 +24618,10 @@
         <v>191</v>
       </c>
       <c r="AH307" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI307" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="308" spans="1:35">
@@ -24683,10 +24695,10 @@
         <v>192</v>
       </c>
       <c r="AH308" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI308" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="309" spans="1:35">
@@ -24760,10 +24772,10 @@
         <v>192</v>
       </c>
       <c r="AH309" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI309" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="310" spans="1:35">
@@ -24834,10 +24846,10 @@
         <v>192</v>
       </c>
       <c r="AH310" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI310" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="311" spans="1:35">
@@ -24908,10 +24920,10 @@
         <v>192</v>
       </c>
       <c r="AH311" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI311" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="312" spans="1:35">
@@ -24982,10 +24994,10 @@
         <v>192</v>
       </c>
       <c r="AH312" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI312" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="313" spans="1:35">
@@ -25056,10 +25068,10 @@
         <v>192</v>
       </c>
       <c r="AH313" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI313" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="314" spans="1:35">
@@ -25127,10 +25139,10 @@
         <v>192</v>
       </c>
       <c r="AH314" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI314" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="315" spans="1:35">
@@ -25204,10 +25216,10 @@
         <v>192</v>
       </c>
       <c r="AH315" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI315" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="316" spans="1:35">
@@ -25281,10 +25293,10 @@
         <v>192</v>
       </c>
       <c r="AH316" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI316" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="317" spans="1:35">
@@ -25358,10 +25370,10 @@
         <v>192</v>
       </c>
       <c r="AH317" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI317" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="318" spans="1:35">
@@ -25435,10 +25447,10 @@
         <v>192</v>
       </c>
       <c r="AH318" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI318" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="319" spans="1:35">
@@ -25512,10 +25524,10 @@
         <v>192</v>
       </c>
       <c r="AH319" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI319" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="320" spans="1:35">
@@ -25586,10 +25598,10 @@
         <v>192</v>
       </c>
       <c r="AH320" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI320" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="321" spans="1:35">
@@ -25660,10 +25672,10 @@
         <v>192</v>
       </c>
       <c r="AH321" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI321" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="322" spans="1:35">
@@ -25734,10 +25746,10 @@
         <v>192</v>
       </c>
       <c r="AH322" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI322" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="323" spans="1:35">
@@ -25805,10 +25817,10 @@
         <v>192</v>
       </c>
       <c r="AH323" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI323" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="324" spans="1:35">
@@ -25876,10 +25888,10 @@
         <v>192</v>
       </c>
       <c r="AH324" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI324" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="325" spans="1:35">
@@ -25947,10 +25959,10 @@
         <v>192</v>
       </c>
       <c r="AH325" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI325" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="326" spans="1:35">
@@ -26018,10 +26030,10 @@
         <v>192</v>
       </c>
       <c r="AH326" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI326" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="327" spans="1:35">
@@ -26089,10 +26101,10 @@
         <v>192</v>
       </c>
       <c r="AH327" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI327" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="328" spans="1:35">
@@ -26160,10 +26172,10 @@
         <v>54</v>
       </c>
       <c r="AH328" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI328" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="329" spans="1:35">
@@ -26231,10 +26243,10 @@
         <v>54</v>
       </c>
       <c r="AH329" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI329" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="330" spans="1:35">
@@ -26302,10 +26314,10 @@
         <v>54</v>
       </c>
       <c r="AH330" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI330" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="331" spans="1:35">
@@ -26373,10 +26385,10 @@
         <v>54</v>
       </c>
       <c r="AH331" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI331" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="332" spans="1:35">
@@ -26444,10 +26456,10 @@
         <v>193</v>
       </c>
       <c r="AH332" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI332" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="333" spans="1:35">
@@ -26515,10 +26527,10 @@
         <v>193</v>
       </c>
       <c r="AH333" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI333" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="334" spans="1:35">
@@ -26586,10 +26598,10 @@
         <v>193</v>
       </c>
       <c r="AH334" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI334" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="335" spans="1:35">
@@ -26657,10 +26669,10 @@
         <v>193</v>
       </c>
       <c r="AH335" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI335" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="336" spans="1:35">
@@ -26728,10 +26740,10 @@
         <v>193</v>
       </c>
       <c r="AH336" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI336" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="337" spans="1:35">
@@ -26799,10 +26811,10 @@
         <v>193</v>
       </c>
       <c r="AH337" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI337" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="338" spans="1:35">
@@ -26870,10 +26882,10 @@
         <v>193</v>
       </c>
       <c r="AH338" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI338" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="339" spans="1:35">
@@ -26941,10 +26953,10 @@
         <v>193</v>
       </c>
       <c r="AH339" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI339" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="340" spans="1:35">
@@ -27012,10 +27024,10 @@
         <v>193</v>
       </c>
       <c r="AH340" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI340" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="341" spans="1:35">
@@ -27086,10 +27098,10 @@
         <v>54</v>
       </c>
       <c r="AH341" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI341" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="342" spans="1:35">
@@ -27160,10 +27172,10 @@
         <v>54</v>
       </c>
       <c r="AH342" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI342" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="343" spans="1:35">
@@ -27231,13 +27243,13 @@
         <v>0</v>
       </c>
       <c r="AC343" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="AH343" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI343" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="344" spans="1:35">
@@ -27308,10 +27320,10 @@
         <v>170</v>
       </c>
       <c r="AH344" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI344" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="345" spans="1:35">
@@ -27382,10 +27394,10 @@
         <v>170</v>
       </c>
       <c r="AH345" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI345" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="346" spans="1:35">
@@ -27459,10 +27471,10 @@
         <v>175</v>
       </c>
       <c r="AH346" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI346" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="347" spans="1:35">
@@ -27533,10 +27545,10 @@
         <v>176</v>
       </c>
       <c r="AH347" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI347" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="348" spans="1:35">
@@ -27604,10 +27616,10 @@
         <v>182</v>
       </c>
       <c r="AH348" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI348" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="349" spans="1:35">
@@ -27675,10 +27687,10 @@
         <v>182</v>
       </c>
       <c r="AH349" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI349" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="350" spans="1:35">
@@ -27755,10 +27767,10 @@
         <v>179</v>
       </c>
       <c r="AH350" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI350" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="351" spans="1:35">
@@ -27835,10 +27847,10 @@
         <v>184</v>
       </c>
       <c r="AH351" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI351" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="352" spans="1:35">
@@ -27915,10 +27927,10 @@
         <v>179</v>
       </c>
       <c r="AH352" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI352" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="353" spans="1:35">
@@ -27995,10 +28007,10 @@
         <v>179</v>
       </c>
       <c r="AH353" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI353" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="354" spans="1:35">
@@ -28075,10 +28087,10 @@
         <v>178</v>
       </c>
       <c r="AH354" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI354" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="355" spans="1:35">
@@ -28155,10 +28167,10 @@
         <v>183</v>
       </c>
       <c r="AH355" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI355" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="356" spans="1:35">
@@ -28229,10 +28241,10 @@
         <v>183</v>
       </c>
       <c r="AH356" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI356" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="357" spans="1:35">
@@ -28303,10 +28315,10 @@
         <v>186</v>
       </c>
       <c r="AH357" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI357" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="358" spans="1:35">
@@ -28380,10 +28392,10 @@
         <v>186</v>
       </c>
       <c r="AH358" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI358" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="359" spans="1:35">
@@ -28457,10 +28469,10 @@
         <v>189</v>
       </c>
       <c r="AH359" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI359" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="360" spans="1:35">
@@ -28531,10 +28543,10 @@
         <v>187</v>
       </c>
       <c r="AH360" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI360" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="361" spans="1:35">
@@ -28605,10 +28617,10 @@
         <v>187</v>
       </c>
       <c r="AH361" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI361" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="362" spans="1:35">
@@ -28682,10 +28694,10 @@
         <v>186</v>
       </c>
       <c r="AH362" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI362" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="363" spans="1:35">
@@ -28756,10 +28768,10 @@
         <v>187</v>
       </c>
       <c r="AH363" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI363" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="364" spans="1:35">
@@ -28830,10 +28842,10 @@
         <v>186</v>
       </c>
       <c r="AH364" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI364" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="365" spans="1:35">
@@ -28910,10 +28922,10 @@
         <v>191</v>
       </c>
       <c r="AH365" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI365" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="366" spans="1:35">
@@ -28990,10 +29002,10 @@
         <v>191</v>
       </c>
       <c r="AH366" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI366" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="367" spans="1:35">
@@ -29070,10 +29082,10 @@
         <v>191</v>
       </c>
       <c r="AH367" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI367" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="368" spans="1:35">
@@ -29147,10 +29159,10 @@
         <v>191</v>
       </c>
       <c r="AH368" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI368" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="369" spans="1:35">
@@ -29227,10 +29239,10 @@
         <v>191</v>
       </c>
       <c r="AH369" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI369" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="370" spans="1:35">
@@ -29307,10 +29319,10 @@
         <v>191</v>
       </c>
       <c r="AH370" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI370" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="371" spans="1:35">
@@ -29387,10 +29399,10 @@
         <v>191</v>
       </c>
       <c r="AH371" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI371" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="372" spans="1:35">
@@ -29464,10 +29476,10 @@
         <v>191</v>
       </c>
       <c r="AH372" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI372" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="373" spans="1:35">
@@ -29541,10 +29553,10 @@
         <v>191</v>
       </c>
       <c r="AH373" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI373" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="374" spans="1:35">
@@ -29618,10 +29630,10 @@
         <v>191</v>
       </c>
       <c r="AH374" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI374" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="375" spans="1:35">
@@ -29695,10 +29707,10 @@
         <v>191</v>
       </c>
       <c r="AH375" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="AI375" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="376" spans="1:35">
@@ -29772,10 +29784,10 @@
         <v>192</v>
       </c>
       <c r="AH376" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI376" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="377" spans="1:35">
@@ -29849,10 +29861,10 @@
         <v>192</v>
       </c>
       <c r="AH377" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI377" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="378" spans="1:35">
@@ -29926,33 +29938,33 @@
         <v>192</v>
       </c>
       <c r="AH378" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI378" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="379" spans="1:35">
       <c r="A379">
-        <v>6627</v>
+        <v>6945</v>
       </c>
       <c r="B379" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C379" t="s">
         <v>50</v>
       </c>
       <c r="D379" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E379" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F379" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G379">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H379">
         <v>0</v>
@@ -29961,13 +29973,13 @@
         <v>64</v>
       </c>
       <c r="J379" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N379" s="1">
         <v>46283</v>
       </c>
       <c r="O379" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="P379">
         <v>8</v>
@@ -29976,25 +29988,25 @@
         <v>2026</v>
       </c>
       <c r="R379">
-        <v>17042272</v>
+        <v>18164487</v>
       </c>
       <c r="S379" t="s">
         <v>192</v>
       </c>
       <c r="U379" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="V379" s="1">
-        <v>46283.67999300926</v>
+        <v>46286.39955256944</v>
       </c>
       <c r="W379">
         <v>3</v>
       </c>
       <c r="X379" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Y379" t="s">
-        <v>318</v>
+        <v>360</v>
       </c>
       <c r="AB379">
         <v>0</v>
@@ -30003,30 +30015,30 @@
         <v>192</v>
       </c>
       <c r="AH379" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI379" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="380" spans="1:35">
       <c r="A380">
-        <v>6945</v>
+        <v>5417</v>
       </c>
       <c r="B380" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C380" t="s">
         <v>50</v>
       </c>
       <c r="D380" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E380" t="s">
         <v>54</v>
       </c>
       <c r="F380" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G380">
         <v>946</v>
@@ -30043,9 +30055,6 @@
       <c r="N380" s="1">
         <v>46283</v>
       </c>
-      <c r="O380" t="s">
-        <v>163</v>
-      </c>
       <c r="P380">
         <v>8</v>
       </c>
@@ -30053,25 +30062,25 @@
         <v>2026</v>
       </c>
       <c r="R380">
-        <v>18164494</v>
+        <v>17398869</v>
       </c>
       <c r="S380" t="s">
         <v>192</v>
       </c>
       <c r="U380" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="V380" s="1">
-        <v>46283.67625043981</v>
+        <v>46286.42397924769</v>
       </c>
       <c r="W380">
         <v>3</v>
       </c>
       <c r="X380" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Y380" t="s">
-        <v>318</v>
+        <v>361</v>
       </c>
       <c r="AB380">
         <v>0</v>
@@ -30080,24 +30089,24 @@
         <v>192</v>
       </c>
       <c r="AH380" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI380" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="381" spans="1:35">
       <c r="A381">
-        <v>6705</v>
+        <v>6404</v>
       </c>
       <c r="B381" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C381" t="s">
         <v>50</v>
       </c>
       <c r="D381" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E381" t="s">
         <v>54</v>
@@ -30106,7 +30115,7 @@
         <v>56</v>
       </c>
       <c r="G381">
-        <v>7022</v>
+        <v>946</v>
       </c>
       <c r="H381">
         <v>0</v>
@@ -30115,14 +30124,11 @@
         <v>64</v>
       </c>
       <c r="J381" t="s">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="N381" s="1">
         <v>46283</v>
       </c>
-      <c r="O381" t="s">
-        <v>163</v>
-      </c>
       <c r="P381">
         <v>8</v>
       </c>
@@ -30130,25 +30136,25 @@
         <v>2026</v>
       </c>
       <c r="R381">
-        <v>17952601</v>
+        <v>16962093</v>
       </c>
       <c r="S381" t="s">
         <v>192</v>
       </c>
       <c r="U381" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="V381" s="1">
-        <v>46283.38329579861</v>
+        <v>46286.42389136574</v>
       </c>
       <c r="W381">
         <v>3</v>
       </c>
       <c r="X381" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="Y381" t="s">
-        <v>318</v>
+        <v>361</v>
       </c>
       <c r="AB381">
         <v>0</v>
@@ -30157,18 +30163,18 @@
         <v>192</v>
       </c>
       <c r="AH381" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AI381" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="382" spans="1:35">
       <c r="A382">
-        <v>5417</v>
+        <v>6627</v>
       </c>
       <c r="B382" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C382" t="s">
         <v>50</v>
@@ -30177,13 +30183,13 @@
         <v>51</v>
       </c>
       <c r="E382" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F382" t="s">
         <v>56</v>
       </c>
       <c r="G382">
-        <v>9086</v>
+        <v>946</v>
       </c>
       <c r="H382">
         <v>0</v>
@@ -30192,22 +30198,22 @@
         <v>64</v>
       </c>
       <c r="J382" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="N382" s="1">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="O382" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="P382">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q382">
         <v>2026</v>
       </c>
       <c r="R382">
-        <v>17399363</v>
+        <v>17042272</v>
       </c>
       <c r="S382" t="s">
         <v>192</v>
@@ -30216,16 +30222,16 @@
         <v>205</v>
       </c>
       <c r="V382" s="1">
-        <v>46282.36440621527</v>
+        <v>46283.67999300926</v>
       </c>
       <c r="W382">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X382" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="Y382" t="s">
-        <v>360</v>
+        <v>318</v>
       </c>
       <c r="AB382">
         <v>0</v>
@@ -30234,18 +30240,18 @@
         <v>192</v>
       </c>
       <c r="AH382" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AI382" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="383" spans="1:35">
       <c r="A383">
-        <v>6404</v>
+        <v>6703</v>
       </c>
       <c r="B383" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C383" t="s">
         <v>50</v>
@@ -30260,7 +30266,7 @@
         <v>56</v>
       </c>
       <c r="G383">
-        <v>9086</v>
+        <v>946</v>
       </c>
       <c r="H383">
         <v>0</v>
@@ -30269,40 +30275,40 @@
         <v>64</v>
       </c>
       <c r="J383" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="N383" s="1">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="O383" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="P383">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q383">
         <v>2026</v>
       </c>
       <c r="R383">
-        <v>16962380</v>
+        <v>17941132</v>
       </c>
       <c r="S383" t="s">
         <v>192</v>
       </c>
       <c r="U383" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="V383" s="1">
-        <v>46282.36462596065</v>
+        <v>46286.42398471065</v>
       </c>
       <c r="W383">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X383" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Y383" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AB383">
         <v>0</v>
@@ -30311,18 +30317,18 @@
         <v>192</v>
       </c>
       <c r="AH383" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AI383" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="384" spans="1:35">
       <c r="A384">
-        <v>6486</v>
+        <v>6704</v>
       </c>
       <c r="B384" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C384" t="s">
         <v>50</v>
@@ -30337,7 +30343,7 @@
         <v>56</v>
       </c>
       <c r="G384">
-        <v>9086</v>
+        <v>946</v>
       </c>
       <c r="H384">
         <v>0</v>
@@ -30346,40 +30352,37 @@
         <v>64</v>
       </c>
       <c r="J384" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="N384" s="1">
-        <v>46282</v>
-      </c>
-      <c r="O384" t="s">
-        <v>164</v>
+        <v>46283</v>
       </c>
       <c r="P384">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q384">
         <v>2026</v>
       </c>
       <c r="R384">
-        <v>16976270</v>
+        <v>17952325</v>
       </c>
       <c r="S384" t="s">
         <v>192</v>
       </c>
       <c r="U384" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="V384" s="1">
-        <v>46282.36464421296</v>
+        <v>46286.42398568287</v>
       </c>
       <c r="W384">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X384" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="Y384" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="AB384">
         <v>0</v>
@@ -30388,33 +30391,33 @@
         <v>192</v>
       </c>
       <c r="AH384" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AI384" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="385" spans="1:35">
       <c r="A385">
-        <v>6548</v>
+        <v>6945</v>
       </c>
       <c r="B385" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C385" t="s">
         <v>50</v>
       </c>
       <c r="D385" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E385" t="s">
         <v>54</v>
       </c>
       <c r="F385" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G385">
-        <v>9086</v>
+        <v>946</v>
       </c>
       <c r="H385">
         <v>0</v>
@@ -30423,22 +30426,22 @@
         <v>64</v>
       </c>
       <c r="J385" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="N385" s="1">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="O385" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="P385">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q385">
         <v>2026</v>
       </c>
       <c r="R385">
-        <v>17222865</v>
+        <v>18164494</v>
       </c>
       <c r="S385" t="s">
         <v>192</v>
@@ -30447,16 +30450,16 @@
         <v>205</v>
       </c>
       <c r="V385" s="1">
-        <v>46282.36467337963</v>
+        <v>46283.67625043981</v>
       </c>
       <c r="W385">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X385" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Y385" t="s">
-        <v>360</v>
+        <v>318</v>
       </c>
       <c r="AB385">
         <v>0</v>
@@ -30465,33 +30468,33 @@
         <v>192</v>
       </c>
       <c r="AH385" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AI385" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="386" spans="1:35">
       <c r="A386">
-        <v>6627</v>
+        <v>6705</v>
       </c>
       <c r="B386" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="C386" t="s">
         <v>50</v>
       </c>
       <c r="D386" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E386" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F386" t="s">
         <v>56</v>
       </c>
       <c r="G386">
-        <v>9086</v>
+        <v>7022</v>
       </c>
       <c r="H386">
         <v>0</v>
@@ -30500,22 +30503,22 @@
         <v>64</v>
       </c>
       <c r="J386" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="N386" s="1">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="O386" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="P386">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q386">
         <v>2026</v>
       </c>
       <c r="R386">
-        <v>17042587</v>
+        <v>17952601</v>
       </c>
       <c r="S386" t="s">
         <v>192</v>
@@ -30524,16 +30527,16 @@
         <v>205</v>
       </c>
       <c r="V386" s="1">
-        <v>46282.36469679398</v>
+        <v>46283.38329579861</v>
       </c>
       <c r="W386">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X386" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="Y386" t="s">
-        <v>360</v>
+        <v>318</v>
       </c>
       <c r="AB386">
         <v>0</v>
@@ -30542,27 +30545,27 @@
         <v>192</v>
       </c>
       <c r="AH386" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AI386" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="387" spans="1:35">
       <c r="A387">
-        <v>6628</v>
+        <v>5417</v>
       </c>
       <c r="B387" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C387" t="s">
         <v>50</v>
       </c>
       <c r="D387" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E387" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F387" t="s">
         <v>56</v>
@@ -30592,7 +30595,7 @@
         <v>2026</v>
       </c>
       <c r="R387">
-        <v>16960074</v>
+        <v>17399363</v>
       </c>
       <c r="S387" t="s">
         <v>192</v>
@@ -30601,16 +30604,16 @@
         <v>205</v>
       </c>
       <c r="V387" s="1">
-        <v>46282.36469869213</v>
+        <v>46282.36440621527</v>
       </c>
       <c r="W387">
         <v>4</v>
       </c>
       <c r="X387" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="Y387" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="AB387">
         <v>0</v>
@@ -30619,18 +30622,18 @@
         <v>192</v>
       </c>
       <c r="AH387" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI387" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="388" spans="1:35">
       <c r="A388">
-        <v>6703</v>
+        <v>6404</v>
       </c>
       <c r="B388" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C388" t="s">
         <v>50</v>
@@ -30669,7 +30672,7 @@
         <v>2026</v>
       </c>
       <c r="R388">
-        <v>17941217</v>
+        <v>16962380</v>
       </c>
       <c r="S388" t="s">
         <v>192</v>
@@ -30678,16 +30681,16 @@
         <v>205</v>
       </c>
       <c r="V388" s="1">
-        <v>46282.36473159722</v>
+        <v>46282.36462596065</v>
       </c>
       <c r="W388">
         <v>4</v>
       </c>
       <c r="X388" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Y388" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="AB388">
         <v>0</v>
@@ -30696,18 +30699,18 @@
         <v>192</v>
       </c>
       <c r="AH388" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI388" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="389" spans="1:35">
       <c r="A389">
-        <v>6704</v>
+        <v>6486</v>
       </c>
       <c r="B389" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C389" t="s">
         <v>50</v>
@@ -30746,7 +30749,7 @@
         <v>2026</v>
       </c>
       <c r="R389">
-        <v>17952444</v>
+        <v>16976270</v>
       </c>
       <c r="S389" t="s">
         <v>192</v>
@@ -30755,16 +30758,16 @@
         <v>205</v>
       </c>
       <c r="V389" s="1">
-        <v>46282.36473394676</v>
+        <v>46282.36464421296</v>
       </c>
       <c r="W389">
         <v>4</v>
       </c>
       <c r="X389" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Y389" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="AB389">
         <v>0</v>
@@ -30773,24 +30776,24 @@
         <v>192</v>
       </c>
       <c r="AH389" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI389" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="390" spans="1:35">
       <c r="A390">
-        <v>6705</v>
+        <v>6548</v>
       </c>
       <c r="B390" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="C390" t="s">
         <v>50</v>
       </c>
       <c r="D390" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E390" t="s">
         <v>54</v>
@@ -30823,7 +30826,7 @@
         <v>2026</v>
       </c>
       <c r="R390">
-        <v>17952624</v>
+        <v>17222865</v>
       </c>
       <c r="S390" t="s">
         <v>192</v>
@@ -30832,16 +30835,16 @@
         <v>205</v>
       </c>
       <c r="V390" s="1">
-        <v>46282.36473579861</v>
+        <v>46282.36467337963</v>
       </c>
       <c r="W390">
         <v>4</v>
       </c>
       <c r="X390" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="Y390" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="AB390">
         <v>0</v>
@@ -30850,27 +30853,27 @@
         <v>192</v>
       </c>
       <c r="AH390" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI390" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="391" spans="1:35">
       <c r="A391">
-        <v>6779</v>
+        <v>6627</v>
       </c>
       <c r="B391" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="C391" t="s">
         <v>50</v>
       </c>
       <c r="D391" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E391" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F391" t="s">
         <v>56</v>
@@ -30900,7 +30903,7 @@
         <v>2026</v>
       </c>
       <c r="R391">
-        <v>18056801</v>
+        <v>17042587</v>
       </c>
       <c r="S391" t="s">
         <v>192</v>
@@ -30909,16 +30912,16 @@
         <v>205</v>
       </c>
       <c r="V391" s="1">
-        <v>46282.36475297454</v>
+        <v>46282.36469679398</v>
       </c>
       <c r="W391">
         <v>4</v>
       </c>
       <c r="X391" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="Y391" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="AB391">
         <v>0</v>
@@ -30927,18 +30930,18 @@
         <v>192</v>
       </c>
       <c r="AH391" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI391" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="392" spans="1:35">
       <c r="A392">
-        <v>6945</v>
+        <v>6628</v>
       </c>
       <c r="B392" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C392" t="s">
         <v>50</v>
@@ -30947,10 +30950,10 @@
         <v>52</v>
       </c>
       <c r="E392" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F392" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G392">
         <v>9086</v>
@@ -30977,7 +30980,7 @@
         <v>2026</v>
       </c>
       <c r="R392">
-        <v>18164551</v>
+        <v>16960074</v>
       </c>
       <c r="S392" t="s">
         <v>192</v>
@@ -30986,16 +30989,16 @@
         <v>205</v>
       </c>
       <c r="V392" s="1">
-        <v>46282.36486408565</v>
+        <v>46282.36469869213</v>
       </c>
       <c r="W392">
         <v>4</v>
       </c>
       <c r="X392" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="Y392" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="AB392">
         <v>0</v>
@@ -31004,30 +31007,30 @@
         <v>192</v>
       </c>
       <c r="AH392" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI392" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="393" spans="1:35">
       <c r="A393">
-        <v>6949</v>
+        <v>6703</v>
       </c>
       <c r="B393" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C393" t="s">
         <v>50</v>
       </c>
       <c r="D393" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E393" t="s">
         <v>54</v>
       </c>
       <c r="F393" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G393">
         <v>9086</v>
@@ -31054,7 +31057,7 @@
         <v>2026</v>
       </c>
       <c r="R393">
-        <v>18178187</v>
+        <v>17941217</v>
       </c>
       <c r="S393" t="s">
         <v>192</v>
@@ -31063,16 +31066,16 @@
         <v>205</v>
       </c>
       <c r="V393" s="1">
-        <v>46282.36487561343</v>
+        <v>46282.36473159722</v>
       </c>
       <c r="W393">
         <v>4</v>
       </c>
       <c r="X393" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="Y393" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="AB393">
         <v>0</v>
@@ -31081,30 +31084,30 @@
         <v>192</v>
       </c>
       <c r="AH393" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI393" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="394" spans="1:35">
       <c r="A394">
-        <v>6962</v>
+        <v>6704</v>
       </c>
       <c r="B394" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C394" t="s">
         <v>50</v>
       </c>
       <c r="D394" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E394" t="s">
         <v>54</v>
       </c>
       <c r="F394" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G394">
         <v>9086</v>
@@ -31131,7 +31134,7 @@
         <v>2026</v>
       </c>
       <c r="R394">
-        <v>18188774</v>
+        <v>17952444</v>
       </c>
       <c r="S394" t="s">
         <v>192</v>
@@ -31140,16 +31143,16 @@
         <v>205</v>
       </c>
       <c r="V394" s="1">
-        <v>46282.36486778935</v>
+        <v>46282.36473394676</v>
       </c>
       <c r="W394">
         <v>4</v>
       </c>
       <c r="X394" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Y394" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="AB394">
         <v>0</v>
@@ -31158,30 +31161,30 @@
         <v>192</v>
       </c>
       <c r="AH394" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI394" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="395" spans="1:35">
       <c r="A395">
-        <v>6963</v>
+        <v>6705</v>
       </c>
       <c r="B395" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C395" t="s">
         <v>50</v>
       </c>
       <c r="D395" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E395" t="s">
         <v>54</v>
       </c>
       <c r="F395" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G395">
         <v>9086</v>
@@ -31208,7 +31211,7 @@
         <v>2026</v>
       </c>
       <c r="R395">
-        <v>18188680</v>
+        <v>17952624</v>
       </c>
       <c r="S395" t="s">
         <v>192</v>
@@ -31217,16 +31220,16 @@
         <v>205</v>
       </c>
       <c r="V395" s="1">
-        <v>46282.36486851852</v>
+        <v>46282.36473579861</v>
       </c>
       <c r="W395">
         <v>4</v>
       </c>
       <c r="X395" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Y395" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="AB395">
         <v>0</v>
@@ -31235,24 +31238,24 @@
         <v>192</v>
       </c>
       <c r="AH395" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI395" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="396" spans="1:35">
       <c r="A396">
-        <v>6404</v>
+        <v>6779</v>
       </c>
       <c r="B396" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C396" t="s">
         <v>50</v>
       </c>
       <c r="D396" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E396" t="s">
         <v>54</v>
@@ -31261,7 +31264,7 @@
         <v>56</v>
       </c>
       <c r="G396">
-        <v>940</v>
+        <v>9086</v>
       </c>
       <c r="H396">
         <v>0</v>
@@ -31270,13 +31273,13 @@
         <v>64</v>
       </c>
       <c r="J396" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N396" s="1">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="O396" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P396">
         <v>9</v>
@@ -31285,25 +31288,25 @@
         <v>2026</v>
       </c>
       <c r="R396">
-        <v>16962074</v>
+        <v>18056801</v>
       </c>
       <c r="S396" t="s">
         <v>192</v>
       </c>
       <c r="U396" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="V396" s="1">
-        <v>46282.79619427084</v>
+        <v>46282.36475297454</v>
       </c>
       <c r="W396">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X396" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="Y396" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AB396">
         <v>0</v>
@@ -31312,33 +31315,33 @@
         <v>192</v>
       </c>
       <c r="AH396" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI396" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="397" spans="1:35">
       <c r="A397">
-        <v>6486</v>
+        <v>6945</v>
       </c>
       <c r="B397" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C397" t="s">
         <v>50</v>
       </c>
       <c r="D397" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E397" t="s">
         <v>54</v>
       </c>
       <c r="F397" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G397">
-        <v>940</v>
+        <v>9086</v>
       </c>
       <c r="H397">
         <v>0</v>
@@ -31347,13 +31350,13 @@
         <v>64</v>
       </c>
       <c r="J397" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N397" s="1">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="O397" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P397">
         <v>9</v>
@@ -31362,25 +31365,25 @@
         <v>2026</v>
       </c>
       <c r="R397">
-        <v>16975871</v>
+        <v>18164551</v>
       </c>
       <c r="S397" t="s">
         <v>192</v>
       </c>
       <c r="U397" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="V397" s="1">
-        <v>46282.79620872685</v>
+        <v>46282.36486408565</v>
       </c>
       <c r="W397">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X397" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="Y397" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AB397">
         <v>0</v>
@@ -31389,18 +31392,18 @@
         <v>192</v>
       </c>
       <c r="AH397" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI397" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="398" spans="1:35">
       <c r="A398">
-        <v>6548</v>
+        <v>6949</v>
       </c>
       <c r="B398" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C398" t="s">
         <v>50</v>
@@ -31412,10 +31415,10 @@
         <v>54</v>
       </c>
       <c r="F398" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G398">
-        <v>940</v>
+        <v>9086</v>
       </c>
       <c r="H398">
         <v>0</v>
@@ -31424,13 +31427,13 @@
         <v>64</v>
       </c>
       <c r="J398" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N398" s="1">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="O398" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P398">
         <v>9</v>
@@ -31439,25 +31442,25 @@
         <v>2026</v>
       </c>
       <c r="R398">
-        <v>17222366</v>
+        <v>18178187</v>
       </c>
       <c r="S398" t="s">
         <v>192</v>
       </c>
       <c r="U398" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="V398" s="1">
-        <v>46282.79623825232</v>
+        <v>46282.36487561343</v>
       </c>
       <c r="W398">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X398" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Y398" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="AB398">
         <v>0</v>
@@ -31466,33 +31469,33 @@
         <v>192</v>
       </c>
       <c r="AH398" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI398" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="399" spans="1:35">
       <c r="A399">
-        <v>6627</v>
+        <v>6962</v>
       </c>
       <c r="B399" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C399" t="s">
         <v>50</v>
       </c>
       <c r="D399" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E399" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F399" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G399">
-        <v>940</v>
+        <v>9086</v>
       </c>
       <c r="H399">
         <v>0</v>
@@ -31501,13 +31504,13 @@
         <v>64</v>
       </c>
       <c r="J399" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N399" s="1">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="O399" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P399">
         <v>9</v>
@@ -31516,25 +31519,25 @@
         <v>2026</v>
       </c>
       <c r="R399">
-        <v>17042221</v>
+        <v>18188774</v>
       </c>
       <c r="S399" t="s">
         <v>192</v>
       </c>
       <c r="U399" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="V399" s="1">
-        <v>46282.7962541551</v>
+        <v>46282.36486778935</v>
       </c>
       <c r="W399">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X399" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Y399" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AB399">
         <v>0</v>
@@ -31543,33 +31546,33 @@
         <v>192</v>
       </c>
       <c r="AH399" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI399" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="400" spans="1:35">
       <c r="A400">
-        <v>6628</v>
+        <v>6963</v>
       </c>
       <c r="B400" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C400" t="s">
         <v>50</v>
       </c>
       <c r="D400" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E400" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F400" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G400">
-        <v>940</v>
+        <v>9086</v>
       </c>
       <c r="H400">
         <v>0</v>
@@ -31578,13 +31581,13 @@
         <v>64</v>
       </c>
       <c r="J400" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N400" s="1">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="O400" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P400">
         <v>9</v>
@@ -31593,25 +31596,25 @@
         <v>2026</v>
       </c>
       <c r="R400">
-        <v>16959926</v>
+        <v>18188680</v>
       </c>
       <c r="S400" t="s">
         <v>192</v>
       </c>
       <c r="U400" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="V400" s="1">
-        <v>46282.7962703125</v>
+        <v>46282.36486851852</v>
       </c>
       <c r="W400">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X400" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Y400" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AB400">
         <v>0</v>
@@ -31620,18 +31623,18 @@
         <v>192</v>
       </c>
       <c r="AH400" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI400" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="401" spans="1:35">
       <c r="A401">
-        <v>6703</v>
+        <v>6404</v>
       </c>
       <c r="B401" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C401" t="s">
         <v>50</v>
@@ -31670,7 +31673,7 @@
         <v>2026</v>
       </c>
       <c r="R401">
-        <v>17941112</v>
+        <v>16962074</v>
       </c>
       <c r="S401" t="s">
         <v>192</v>
@@ -31679,16 +31682,16 @@
         <v>204</v>
       </c>
       <c r="V401" s="1">
-        <v>46282.79628381944</v>
+        <v>46282.79619427084</v>
       </c>
       <c r="W401">
         <v>3</v>
       </c>
       <c r="X401" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Y401" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="AB401">
         <v>0</v>
@@ -31697,18 +31700,18 @@
         <v>192</v>
       </c>
       <c r="AH401" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI401" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="402" spans="1:35">
       <c r="A402">
-        <v>6704</v>
+        <v>6486</v>
       </c>
       <c r="B402" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C402" t="s">
         <v>50</v>
@@ -31747,7 +31750,7 @@
         <v>2026</v>
       </c>
       <c r="R402">
-        <v>17952292</v>
+        <v>16975871</v>
       </c>
       <c r="S402" t="s">
         <v>192</v>
@@ -31756,16 +31759,16 @@
         <v>204</v>
       </c>
       <c r="V402" s="1">
-        <v>46282.79630119213</v>
+        <v>46282.79620872685</v>
       </c>
       <c r="W402">
         <v>3</v>
       </c>
       <c r="X402" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Y402" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="AB402">
         <v>0</v>
@@ -31774,24 +31777,24 @@
         <v>192</v>
       </c>
       <c r="AH402" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI402" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="403" spans="1:35">
       <c r="A403">
-        <v>6705</v>
+        <v>6548</v>
       </c>
       <c r="B403" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="C403" t="s">
         <v>50</v>
       </c>
       <c r="D403" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E403" t="s">
         <v>54</v>
@@ -31824,7 +31827,7 @@
         <v>2026</v>
       </c>
       <c r="R403">
-        <v>17952491</v>
+        <v>17222366</v>
       </c>
       <c r="S403" t="s">
         <v>192</v>
@@ -31833,16 +31836,16 @@
         <v>204</v>
       </c>
       <c r="V403" s="1">
-        <v>46282.79631224537</v>
+        <v>46282.79623825232</v>
       </c>
       <c r="W403">
         <v>3</v>
       </c>
       <c r="X403" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="Y403" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="AB403">
         <v>0</v>
@@ -31851,30 +31854,30 @@
         <v>192</v>
       </c>
       <c r="AH403" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI403" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="404" spans="1:35">
       <c r="A404">
-        <v>6945</v>
+        <v>6627</v>
       </c>
       <c r="B404" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C404" t="s">
         <v>50</v>
       </c>
       <c r="D404" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E404" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F404" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G404">
         <v>940</v>
@@ -31901,7 +31904,7 @@
         <v>2026</v>
       </c>
       <c r="R404">
-        <v>18164473</v>
+        <v>17042221</v>
       </c>
       <c r="S404" t="s">
         <v>192</v>
@@ -31910,16 +31913,16 @@
         <v>204</v>
       </c>
       <c r="V404" s="1">
-        <v>46282.79637734954</v>
+        <v>46282.7962541551</v>
       </c>
       <c r="W404">
         <v>3</v>
       </c>
       <c r="X404" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="Y404" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AB404">
         <v>0</v>
@@ -31928,30 +31931,30 @@
         <v>192</v>
       </c>
       <c r="AH404" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI404" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="405" spans="1:35">
       <c r="A405">
-        <v>6949</v>
+        <v>6628</v>
       </c>
       <c r="B405" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C405" t="s">
         <v>50</v>
       </c>
       <c r="D405" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E405" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F405" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G405">
         <v>940</v>
@@ -31978,7 +31981,7 @@
         <v>2026</v>
       </c>
       <c r="R405">
-        <v>18178120</v>
+        <v>16959926</v>
       </c>
       <c r="S405" t="s">
         <v>192</v>
@@ -31987,16 +31990,16 @@
         <v>204</v>
       </c>
       <c r="V405" s="1">
-        <v>46282.79638922454</v>
+        <v>46282.7962703125</v>
       </c>
       <c r="W405">
         <v>3</v>
       </c>
       <c r="X405" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Y405" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AB405">
         <v>0</v>
@@ -32005,24 +32008,24 @@
         <v>192</v>
       </c>
       <c r="AH405" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI405" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="406" spans="1:35">
       <c r="A406">
-        <v>5417</v>
+        <v>6703</v>
       </c>
       <c r="B406" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C406" t="s">
         <v>50</v>
       </c>
       <c r="D406" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E406" t="s">
         <v>54</v>
@@ -32031,16 +32034,16 @@
         <v>56</v>
       </c>
       <c r="G406">
-        <v>9088</v>
+        <v>940</v>
       </c>
       <c r="H406">
         <v>0</v>
       </c>
       <c r="I406" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J406" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N406" s="1">
         <v>46283</v>
@@ -32055,51 +32058,51 @@
         <v>2026</v>
       </c>
       <c r="R406">
-        <v>17399383</v>
+        <v>17941112</v>
       </c>
       <c r="S406" t="s">
-        <v>54</v>
+        <v>192</v>
       </c>
       <c r="U406" t="s">
         <v>204</v>
       </c>
       <c r="V406" s="1">
-        <v>46282.3651903588</v>
+        <v>46282.79628381944</v>
       </c>
       <c r="W406">
         <v>3</v>
       </c>
       <c r="X406" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Y406" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AB406">
         <v>0</v>
       </c>
       <c r="AC406" t="s">
-        <v>54</v>
+        <v>192</v>
       </c>
       <c r="AH406" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI406" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="407" spans="1:35">
       <c r="A407">
-        <v>6404</v>
+        <v>6704</v>
       </c>
       <c r="B407" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C407" t="s">
         <v>50</v>
       </c>
       <c r="D407" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E407" t="s">
         <v>54</v>
@@ -32108,16 +32111,16 @@
         <v>56</v>
       </c>
       <c r="G407">
-        <v>9088</v>
+        <v>940</v>
       </c>
       <c r="H407">
         <v>0</v>
       </c>
       <c r="I407" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J407" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N407" s="1">
         <v>46283</v>
@@ -32132,51 +32135,51 @@
         <v>2026</v>
       </c>
       <c r="R407">
-        <v>16962400</v>
+        <v>17952292</v>
       </c>
       <c r="S407" t="s">
-        <v>54</v>
+        <v>192</v>
       </c>
       <c r="U407" t="s">
         <v>204</v>
       </c>
       <c r="V407" s="1">
-        <v>46282.36525856482</v>
+        <v>46282.79630119213</v>
       </c>
       <c r="W407">
         <v>3</v>
       </c>
       <c r="X407" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="Y407" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AB407">
         <v>0</v>
       </c>
       <c r="AC407" t="s">
-        <v>54</v>
+        <v>192</v>
       </c>
       <c r="AH407" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI407" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="408" spans="1:35">
       <c r="A408">
-        <v>6486</v>
+        <v>6705</v>
       </c>
       <c r="B408" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C408" t="s">
         <v>50</v>
       </c>
       <c r="D408" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E408" t="s">
         <v>54</v>
@@ -32185,16 +32188,16 @@
         <v>56</v>
       </c>
       <c r="G408">
-        <v>9088</v>
+        <v>940</v>
       </c>
       <c r="H408">
         <v>0</v>
       </c>
       <c r="I408" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J408" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N408" s="1">
         <v>46283</v>
@@ -32209,69 +32212,69 @@
         <v>2026</v>
       </c>
       <c r="R408">
-        <v>16976290</v>
+        <v>17952491</v>
       </c>
       <c r="S408" t="s">
-        <v>54</v>
+        <v>192</v>
       </c>
       <c r="U408" t="s">
         <v>204</v>
       </c>
       <c r="V408" s="1">
-        <v>46282.36526855324</v>
+        <v>46282.79631224537</v>
       </c>
       <c r="W408">
         <v>3</v>
       </c>
       <c r="X408" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="Y408" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AB408">
         <v>0</v>
       </c>
       <c r="AC408" t="s">
-        <v>54</v>
+        <v>192</v>
       </c>
       <c r="AH408" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI408" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="409" spans="1:35">
       <c r="A409">
-        <v>6548</v>
+        <v>6945</v>
       </c>
       <c r="B409" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C409" t="s">
         <v>50</v>
       </c>
       <c r="D409" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E409" t="s">
         <v>54</v>
       </c>
       <c r="F409" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G409">
-        <v>9088</v>
+        <v>940</v>
       </c>
       <c r="H409">
         <v>0</v>
       </c>
       <c r="I409" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J409" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N409" s="1">
         <v>46283</v>
@@ -32286,45 +32289,45 @@
         <v>2026</v>
       </c>
       <c r="R409">
-        <v>17222899</v>
+        <v>18164473</v>
       </c>
       <c r="S409" t="s">
-        <v>54</v>
+        <v>192</v>
       </c>
       <c r="U409" t="s">
         <v>204</v>
       </c>
       <c r="V409" s="1">
-        <v>46282.36527959491</v>
+        <v>46282.79637734954</v>
       </c>
       <c r="W409">
         <v>3</v>
       </c>
       <c r="X409" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Y409" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="AB409">
         <v>0</v>
       </c>
       <c r="AC409" t="s">
-        <v>54</v>
+        <v>192</v>
       </c>
       <c r="AH409" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI409" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="410" spans="1:35">
       <c r="A410">
-        <v>6627</v>
+        <v>6949</v>
       </c>
       <c r="B410" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C410" t="s">
         <v>50</v>
@@ -32333,22 +32336,22 @@
         <v>51</v>
       </c>
       <c r="E410" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F410" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G410">
-        <v>9088</v>
+        <v>940</v>
       </c>
       <c r="H410">
         <v>0</v>
       </c>
       <c r="I410" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J410" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N410" s="1">
         <v>46283</v>
@@ -32363,54 +32366,54 @@
         <v>2026</v>
       </c>
       <c r="R410">
-        <v>17042627</v>
+        <v>18178120</v>
       </c>
       <c r="S410" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="U410" t="s">
         <v>204</v>
       </c>
       <c r="V410" s="1">
-        <v>46282.36528526621</v>
+        <v>46282.79638922454</v>
       </c>
       <c r="W410">
         <v>3</v>
       </c>
       <c r="X410" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Y410" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="AB410">
         <v>0</v>
       </c>
       <c r="AC410" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AH410" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI410" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="411" spans="1:35">
       <c r="A411">
-        <v>6628</v>
+        <v>5417</v>
       </c>
       <c r="B411" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C411" t="s">
         <v>50</v>
       </c>
       <c r="D411" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E411" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F411" t="s">
         <v>56</v>
@@ -32440,45 +32443,45 @@
         <v>2026</v>
       </c>
       <c r="R411">
-        <v>16960098</v>
+        <v>17399383</v>
       </c>
       <c r="S411" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="U411" t="s">
         <v>204</v>
       </c>
       <c r="V411" s="1">
-        <v>46282.36528619213</v>
+        <v>46282.3651903588</v>
       </c>
       <c r="W411">
         <v>3</v>
       </c>
       <c r="X411" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="Y411" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="AB411">
         <v>0</v>
       </c>
       <c r="AC411" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AH411" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI411" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="412" spans="1:35">
       <c r="A412">
-        <v>6703</v>
+        <v>6404</v>
       </c>
       <c r="B412" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C412" t="s">
         <v>50</v>
@@ -32517,7 +32520,7 @@
         <v>2026</v>
       </c>
       <c r="R412">
-        <v>17941237</v>
+        <v>16962400</v>
       </c>
       <c r="S412" t="s">
         <v>54</v>
@@ -32526,16 +32529,16 @@
         <v>204</v>
       </c>
       <c r="V412" s="1">
-        <v>46282.36529351852</v>
+        <v>46282.36525856482</v>
       </c>
       <c r="W412">
         <v>3</v>
       </c>
       <c r="X412" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Y412" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="AB412">
         <v>0</v>
@@ -32544,18 +32547,18 @@
         <v>54</v>
       </c>
       <c r="AH412" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI412" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="413" spans="1:35">
       <c r="A413">
-        <v>6704</v>
+        <v>6486</v>
       </c>
       <c r="B413" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C413" t="s">
         <v>50</v>
@@ -32594,7 +32597,7 @@
         <v>2026</v>
       </c>
       <c r="R413">
-        <v>17952466</v>
+        <v>16976290</v>
       </c>
       <c r="S413" t="s">
         <v>54</v>
@@ -32603,16 +32606,16 @@
         <v>204</v>
       </c>
       <c r="V413" s="1">
-        <v>46282.36529424768</v>
+        <v>46282.36526855324</v>
       </c>
       <c r="W413">
         <v>3</v>
       </c>
       <c r="X413" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Y413" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="AB413">
         <v>0</v>
@@ -32621,24 +32624,24 @@
         <v>54</v>
       </c>
       <c r="AH413" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI413" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="414" spans="1:35">
       <c r="A414">
-        <v>6705</v>
+        <v>6548</v>
       </c>
       <c r="B414" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="C414" t="s">
         <v>50</v>
       </c>
       <c r="D414" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E414" t="s">
         <v>54</v>
@@ -32671,7 +32674,7 @@
         <v>2026</v>
       </c>
       <c r="R414">
-        <v>17952646</v>
+        <v>17222899</v>
       </c>
       <c r="S414" t="s">
         <v>54</v>
@@ -32680,16 +32683,16 @@
         <v>204</v>
       </c>
       <c r="V414" s="1">
-        <v>46282.36529490741</v>
+        <v>46282.36527959491</v>
       </c>
       <c r="W414">
         <v>3</v>
       </c>
       <c r="X414" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="Y414" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="AB414">
         <v>0</v>
@@ -32698,27 +32701,27 @@
         <v>54</v>
       </c>
       <c r="AH414" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI414" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="415" spans="1:35">
       <c r="A415">
-        <v>6779</v>
+        <v>6627</v>
       </c>
       <c r="B415" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="C415" t="s">
         <v>50</v>
       </c>
       <c r="D415" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E415" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F415" t="s">
         <v>56</v>
@@ -32748,7 +32751,7 @@
         <v>2026</v>
       </c>
       <c r="R415">
-        <v>18056821</v>
+        <v>17042627</v>
       </c>
       <c r="S415" t="s">
         <v>193</v>
@@ -32757,16 +32760,16 @@
         <v>204</v>
       </c>
       <c r="V415" s="1">
-        <v>46282.36529869213</v>
+        <v>46282.36528526621</v>
       </c>
       <c r="W415">
         <v>3</v>
       </c>
       <c r="X415" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="Y415" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="AB415">
         <v>0</v>
@@ -32775,18 +32778,18 @@
         <v>193</v>
       </c>
       <c r="AH415" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI415" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="416" spans="1:35">
       <c r="A416">
-        <v>6945</v>
+        <v>6628</v>
       </c>
       <c r="B416" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C416" t="s">
         <v>50</v>
@@ -32795,10 +32798,10 @@
         <v>52</v>
       </c>
       <c r="E416" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F416" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G416">
         <v>9088</v>
@@ -32825,57 +32828,57 @@
         <v>2026</v>
       </c>
       <c r="R416">
-        <v>18164565</v>
+        <v>16960098</v>
       </c>
       <c r="S416" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="U416" t="s">
         <v>204</v>
       </c>
       <c r="V416" s="1">
-        <v>46282.36531149306</v>
+        <v>46282.36528619213</v>
       </c>
       <c r="W416">
         <v>3</v>
       </c>
       <c r="X416" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="Y416" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="AB416">
         <v>0</v>
       </c>
       <c r="AC416" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AH416" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI416" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="417" spans="1:35">
       <c r="A417">
-        <v>6949</v>
+        <v>6703</v>
       </c>
       <c r="B417" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C417" t="s">
         <v>50</v>
       </c>
       <c r="D417" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E417" t="s">
         <v>54</v>
       </c>
       <c r="F417" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G417">
         <v>9088</v>
@@ -32902,57 +32905,57 @@
         <v>2026</v>
       </c>
       <c r="R417">
-        <v>18178199</v>
+        <v>17941237</v>
       </c>
       <c r="S417" t="s">
-        <v>193</v>
+        <v>54</v>
       </c>
       <c r="U417" t="s">
         <v>204</v>
       </c>
       <c r="V417" s="1">
-        <v>46282.36531554398</v>
+        <v>46282.36529351852</v>
       </c>
       <c r="W417">
         <v>3</v>
       </c>
       <c r="X417" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="Y417" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="AB417">
         <v>0</v>
       </c>
       <c r="AC417" t="s">
-        <v>193</v>
+        <v>54</v>
       </c>
       <c r="AH417" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI417" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="418" spans="1:35">
       <c r="A418">
-        <v>6962</v>
+        <v>6704</v>
       </c>
       <c r="B418" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C418" t="s">
         <v>50</v>
       </c>
       <c r="D418" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E418" t="s">
         <v>54</v>
       </c>
       <c r="F418" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G418">
         <v>9088</v>
@@ -32979,7 +32982,7 @@
         <v>2026</v>
       </c>
       <c r="R418">
-        <v>18188788</v>
+        <v>17952466</v>
       </c>
       <c r="S418" t="s">
         <v>54</v>
@@ -32988,16 +32991,16 @@
         <v>204</v>
       </c>
       <c r="V418" s="1">
-        <v>46282.36531253472</v>
+        <v>46282.36529424768</v>
       </c>
       <c r="W418">
         <v>3</v>
       </c>
       <c r="X418" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Y418" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="AB418">
         <v>0</v>
@@ -33006,30 +33009,30 @@
         <v>54</v>
       </c>
       <c r="AH418" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI418" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="419" spans="1:35">
       <c r="A419">
-        <v>6963</v>
+        <v>6705</v>
       </c>
       <c r="B419" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C419" t="s">
         <v>50</v>
       </c>
       <c r="D419" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E419" t="s">
         <v>54</v>
       </c>
       <c r="F419" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G419">
         <v>9088</v>
@@ -33056,7 +33059,7 @@
         <v>2026</v>
       </c>
       <c r="R419">
-        <v>18188694</v>
+        <v>17952646</v>
       </c>
       <c r="S419" t="s">
         <v>54</v>
@@ -33065,16 +33068,16 @@
         <v>204</v>
       </c>
       <c r="V419" s="1">
-        <v>46282.36531288194</v>
+        <v>46282.36529490741</v>
       </c>
       <c r="W419">
         <v>3</v>
       </c>
       <c r="X419" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Y419" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="AB419">
         <v>0</v>
@@ -33083,24 +33086,24 @@
         <v>54</v>
       </c>
       <c r="AH419" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI419" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="420" spans="1:35">
       <c r="A420">
-        <v>6404</v>
+        <v>6779</v>
       </c>
       <c r="B420" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C420" t="s">
         <v>50</v>
       </c>
       <c r="D420" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E420" t="s">
         <v>54</v>
@@ -33109,7 +33112,7 @@
         <v>56</v>
       </c>
       <c r="G420">
-        <v>6813</v>
+        <v>9088</v>
       </c>
       <c r="H420">
         <v>0</v>
@@ -33118,7 +33121,7 @@
         <v>65</v>
       </c>
       <c r="J420" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="N420" s="1">
         <v>46283</v>
@@ -33133,60 +33136,60 @@
         <v>2026</v>
       </c>
       <c r="R420">
-        <v>16962319</v>
+        <v>18056821</v>
       </c>
       <c r="S420" t="s">
-        <v>54</v>
+        <v>193</v>
       </c>
       <c r="U420" t="s">
         <v>204</v>
       </c>
       <c r="V420" s="1">
-        <v>46282.79619331018</v>
+        <v>46282.36529869213</v>
       </c>
       <c r="W420">
         <v>3</v>
       </c>
       <c r="X420" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="Y420" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="AB420">
         <v>0</v>
       </c>
       <c r="AC420" t="s">
-        <v>54</v>
+        <v>193</v>
       </c>
       <c r="AH420" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI420" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="421" spans="1:35">
       <c r="A421">
-        <v>6486</v>
+        <v>6945</v>
       </c>
       <c r="B421" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C421" t="s">
         <v>50</v>
       </c>
       <c r="D421" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E421" t="s">
         <v>54</v>
       </c>
       <c r="F421" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G421">
-        <v>6813</v>
+        <v>9088</v>
       </c>
       <c r="H421">
         <v>0</v>
@@ -33195,7 +33198,7 @@
         <v>65</v>
       </c>
       <c r="J421" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="N421" s="1">
         <v>46283</v>
@@ -33210,7 +33213,7 @@
         <v>2026</v>
       </c>
       <c r="R421">
-        <v>16976198</v>
+        <v>18164565</v>
       </c>
       <c r="S421" t="s">
         <v>54</v>
@@ -33219,16 +33222,16 @@
         <v>204</v>
       </c>
       <c r="V421" s="1">
-        <v>46282.79620888889</v>
+        <v>46282.36531149306</v>
       </c>
       <c r="W421">
         <v>3</v>
       </c>
       <c r="X421" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="Y421" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="AB421">
         <v>0</v>
@@ -33237,18 +33240,18 @@
         <v>54</v>
       </c>
       <c r="AH421" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI421" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="422" spans="1:35">
       <c r="A422">
-        <v>6548</v>
+        <v>6949</v>
       </c>
       <c r="B422" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C422" t="s">
         <v>50</v>
@@ -33260,10 +33263,10 @@
         <v>54</v>
       </c>
       <c r="F422" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G422">
-        <v>6813</v>
+        <v>9088</v>
       </c>
       <c r="H422">
         <v>0</v>
@@ -33272,7 +33275,7 @@
         <v>65</v>
       </c>
       <c r="J422" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="N422" s="1">
         <v>46283</v>
@@ -33287,60 +33290,60 @@
         <v>2026</v>
       </c>
       <c r="R422">
-        <v>17222763</v>
+        <v>18178199</v>
       </c>
       <c r="S422" t="s">
-        <v>54</v>
+        <v>193</v>
       </c>
       <c r="U422" t="s">
         <v>204</v>
       </c>
       <c r="V422" s="1">
-        <v>46282.79623803241</v>
+        <v>46282.36531554398</v>
       </c>
       <c r="W422">
         <v>3</v>
       </c>
       <c r="X422" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Y422" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="AB422">
         <v>0</v>
       </c>
       <c r="AC422" t="s">
-        <v>54</v>
+        <v>193</v>
       </c>
       <c r="AH422" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI422" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="423" spans="1:35">
       <c r="A423">
-        <v>6627</v>
+        <v>6962</v>
       </c>
       <c r="B423" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C423" t="s">
         <v>50</v>
       </c>
       <c r="D423" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E423" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F423" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G423">
-        <v>6813</v>
+        <v>9088</v>
       </c>
       <c r="H423">
         <v>0</v>
@@ -33349,7 +33352,7 @@
         <v>65</v>
       </c>
       <c r="J423" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="N423" s="1">
         <v>46283</v>
@@ -33364,60 +33367,60 @@
         <v>2026</v>
       </c>
       <c r="R423">
-        <v>17042469</v>
+        <v>18188788</v>
       </c>
       <c r="S423" t="s">
-        <v>193</v>
+        <v>54</v>
       </c>
       <c r="U423" t="s">
         <v>204</v>
       </c>
       <c r="V423" s="1">
-        <v>46282.79625384259</v>
+        <v>46282.36531253472</v>
       </c>
       <c r="W423">
         <v>3</v>
       </c>
       <c r="X423" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Y423" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="AB423">
         <v>0</v>
       </c>
       <c r="AC423" t="s">
-        <v>193</v>
+        <v>54</v>
       </c>
       <c r="AH423" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI423" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="424" spans="1:35">
       <c r="A424">
-        <v>6628</v>
+        <v>6963</v>
       </c>
       <c r="B424" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C424" t="s">
         <v>50</v>
       </c>
       <c r="D424" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E424" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F424" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G424">
-        <v>6813</v>
+        <v>9088</v>
       </c>
       <c r="H424">
         <v>0</v>
@@ -33426,7 +33429,7 @@
         <v>65</v>
       </c>
       <c r="J424" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="N424" s="1">
         <v>46283</v>
@@ -33441,45 +33444,45 @@
         <v>2026</v>
       </c>
       <c r="R424">
-        <v>16960013</v>
+        <v>18188694</v>
       </c>
       <c r="S424" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="U424" t="s">
         <v>204</v>
       </c>
       <c r="V424" s="1">
-        <v>46282.79626969907</v>
+        <v>46282.36531288194</v>
       </c>
       <c r="W424">
         <v>3</v>
       </c>
       <c r="X424" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Y424" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="AB424">
         <v>0</v>
       </c>
       <c r="AC424" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AH424" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI424" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="425" spans="1:35">
       <c r="A425">
-        <v>6703</v>
+        <v>6404</v>
       </c>
       <c r="B425" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C425" t="s">
         <v>50</v>
@@ -33518,7 +33521,7 @@
         <v>2026</v>
       </c>
       <c r="R425">
-        <v>17941197</v>
+        <v>16962319</v>
       </c>
       <c r="S425" t="s">
         <v>54</v>
@@ -33527,16 +33530,16 @@
         <v>204</v>
       </c>
       <c r="V425" s="1">
-        <v>46282.79628394676</v>
+        <v>46282.79619331018</v>
       </c>
       <c r="W425">
         <v>3</v>
       </c>
       <c r="X425" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Y425" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="AB425">
         <v>0</v>
@@ -33545,18 +33548,18 @@
         <v>54</v>
       </c>
       <c r="AH425" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI425" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="426" spans="1:35">
       <c r="A426">
-        <v>6704</v>
+        <v>6486</v>
       </c>
       <c r="B426" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C426" t="s">
         <v>50</v>
@@ -33595,7 +33598,7 @@
         <v>2026</v>
       </c>
       <c r="R426">
-        <v>17952411</v>
+        <v>16976198</v>
       </c>
       <c r="S426" t="s">
         <v>54</v>
@@ -33604,16 +33607,16 @@
         <v>204</v>
       </c>
       <c r="V426" s="1">
-        <v>46282.79630097222</v>
+        <v>46282.79620888889</v>
       </c>
       <c r="W426">
         <v>3</v>
       </c>
       <c r="X426" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Y426" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="AB426">
         <v>0</v>
@@ -33622,24 +33625,24 @@
         <v>54</v>
       </c>
       <c r="AH426" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI426" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="427" spans="1:35">
       <c r="A427">
-        <v>6705</v>
+        <v>6548</v>
       </c>
       <c r="B427" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="C427" t="s">
         <v>50</v>
       </c>
       <c r="D427" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E427" t="s">
         <v>54</v>
@@ -33672,7 +33675,7 @@
         <v>2026</v>
       </c>
       <c r="R427">
-        <v>17952591</v>
+        <v>17222763</v>
       </c>
       <c r="S427" t="s">
         <v>54</v>
@@ -33681,16 +33684,16 @@
         <v>204</v>
       </c>
       <c r="V427" s="1">
-        <v>46282.79631204861</v>
+        <v>46282.79623803241</v>
       </c>
       <c r="W427">
         <v>3</v>
       </c>
       <c r="X427" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="Y427" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="AB427">
         <v>0</v>
@@ -33699,30 +33702,30 @@
         <v>54</v>
       </c>
       <c r="AH427" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI427" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="428" spans="1:35">
       <c r="A428">
-        <v>6945</v>
+        <v>6627</v>
       </c>
       <c r="B428" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C428" t="s">
         <v>50</v>
       </c>
       <c r="D428" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E428" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F428" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G428">
         <v>6813</v>
@@ -33749,57 +33752,57 @@
         <v>2026</v>
       </c>
       <c r="R428">
-        <v>18164530</v>
+        <v>17042469</v>
       </c>
       <c r="S428" t="s">
-        <v>54</v>
+        <v>193</v>
       </c>
       <c r="U428" t="s">
         <v>204</v>
       </c>
       <c r="V428" s="1">
-        <v>46282.79637748843</v>
+        <v>46282.79625384259</v>
       </c>
       <c r="W428">
         <v>3</v>
       </c>
       <c r="X428" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="Y428" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="AB428">
         <v>0</v>
       </c>
       <c r="AC428" t="s">
-        <v>54</v>
+        <v>193</v>
       </c>
       <c r="AH428" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI428" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="429" spans="1:35">
       <c r="A429">
-        <v>6949</v>
+        <v>6628</v>
       </c>
       <c r="B429" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C429" t="s">
         <v>50</v>
       </c>
       <c r="D429" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E429" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F429" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G429">
         <v>6813</v>
@@ -33826,51 +33829,51 @@
         <v>2026</v>
       </c>
       <c r="R429">
-        <v>18178169</v>
+        <v>16960013</v>
       </c>
       <c r="S429" t="s">
-        <v>193</v>
+        <v>55</v>
       </c>
       <c r="U429" t="s">
         <v>204</v>
       </c>
       <c r="V429" s="1">
-        <v>46282.79638901621</v>
+        <v>46282.79626969907</v>
       </c>
       <c r="W429">
         <v>3</v>
       </c>
       <c r="X429" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Y429" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="AB429">
         <v>0</v>
       </c>
       <c r="AC429" t="s">
-        <v>193</v>
+        <v>55</v>
       </c>
       <c r="AH429" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AI429" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="430" spans="1:35">
       <c r="A430">
-        <v>5417</v>
+        <v>6703</v>
       </c>
       <c r="B430" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C430" t="s">
         <v>50</v>
       </c>
       <c r="D430" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E430" t="s">
         <v>54</v>
@@ -33879,7 +33882,7 @@
         <v>56</v>
       </c>
       <c r="G430">
-        <v>7027</v>
+        <v>6813</v>
       </c>
       <c r="H430">
         <v>0</v>
@@ -33888,19 +33891,22 @@
         <v>65</v>
       </c>
       <c r="J430" t="s">
-        <v>119</v>
+        <v>154</v>
       </c>
       <c r="N430" s="1">
-        <v>46289</v>
+        <v>46283</v>
+      </c>
+      <c r="O430" t="s">
+        <v>163</v>
       </c>
       <c r="P430">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q430">
         <v>2026</v>
       </c>
       <c r="R430">
-        <v>17399290</v>
+        <v>17941197</v>
       </c>
       <c r="S430" t="s">
         <v>54</v>
@@ -33909,16 +33915,16 @@
         <v>204</v>
       </c>
       <c r="V430" s="1">
-        <v>46283.39832862269</v>
+        <v>46282.79628394676</v>
       </c>
       <c r="W430">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="X430" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Y430" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AB430">
         <v>0</v>
@@ -33927,24 +33933,24 @@
         <v>54</v>
       </c>
       <c r="AH430" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="AI430" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="431" spans="1:35">
       <c r="A431">
-        <v>6404</v>
+        <v>6704</v>
       </c>
       <c r="B431" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C431" t="s">
         <v>50</v>
       </c>
       <c r="D431" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E431" t="s">
         <v>54</v>
@@ -33953,7 +33959,7 @@
         <v>56</v>
       </c>
       <c r="G431">
-        <v>7027</v>
+        <v>6813</v>
       </c>
       <c r="H431">
         <v>0</v>
@@ -33962,19 +33968,22 @@
         <v>65</v>
       </c>
       <c r="J431" t="s">
-        <v>119</v>
+        <v>154</v>
       </c>
       <c r="N431" s="1">
-        <v>46289</v>
+        <v>46283</v>
+      </c>
+      <c r="O431" t="s">
+        <v>163</v>
       </c>
       <c r="P431">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q431">
         <v>2026</v>
       </c>
       <c r="R431">
-        <v>16962348</v>
+        <v>17952411</v>
       </c>
       <c r="S431" t="s">
         <v>54</v>
@@ -33983,28 +33992,407 @@
         <v>204</v>
       </c>
       <c r="V431" s="1">
+        <v>46282.79630097222</v>
+      </c>
+      <c r="W431">
+        <v>3</v>
+      </c>
+      <c r="X431" t="s">
+        <v>211</v>
+      </c>
+      <c r="Y431" t="s">
+        <v>367</v>
+      </c>
+      <c r="AB431">
+        <v>0</v>
+      </c>
+      <c r="AC431" t="s">
+        <v>54</v>
+      </c>
+      <c r="AH431" t="s">
+        <v>377</v>
+      </c>
+      <c r="AI431" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="432" spans="1:35">
+      <c r="A432">
+        <v>6705</v>
+      </c>
+      <c r="B432" t="s">
+        <v>48</v>
+      </c>
+      <c r="C432" t="s">
+        <v>50</v>
+      </c>
+      <c r="D432" t="s">
+        <v>52</v>
+      </c>
+      <c r="E432" t="s">
+        <v>54</v>
+      </c>
+      <c r="F432" t="s">
+        <v>56</v>
+      </c>
+      <c r="G432">
+        <v>6813</v>
+      </c>
+      <c r="H432">
+        <v>0</v>
+      </c>
+      <c r="I432" t="s">
+        <v>65</v>
+      </c>
+      <c r="J432" t="s">
+        <v>154</v>
+      </c>
+      <c r="N432" s="1">
+        <v>46283</v>
+      </c>
+      <c r="O432" t="s">
+        <v>163</v>
+      </c>
+      <c r="P432">
+        <v>9</v>
+      </c>
+      <c r="Q432">
+        <v>2026</v>
+      </c>
+      <c r="R432">
+        <v>17952591</v>
+      </c>
+      <c r="S432" t="s">
+        <v>54</v>
+      </c>
+      <c r="U432" t="s">
+        <v>204</v>
+      </c>
+      <c r="V432" s="1">
+        <v>46282.79631204861</v>
+      </c>
+      <c r="W432">
+        <v>3</v>
+      </c>
+      <c r="X432" t="s">
+        <v>211</v>
+      </c>
+      <c r="Y432" t="s">
+        <v>367</v>
+      </c>
+      <c r="AB432">
+        <v>0</v>
+      </c>
+      <c r="AC432" t="s">
+        <v>54</v>
+      </c>
+      <c r="AH432" t="s">
+        <v>377</v>
+      </c>
+      <c r="AI432" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="433" spans="1:35">
+      <c r="A433">
+        <v>6945</v>
+      </c>
+      <c r="B433" t="s">
+        <v>39</v>
+      </c>
+      <c r="C433" t="s">
+        <v>50</v>
+      </c>
+      <c r="D433" t="s">
+        <v>52</v>
+      </c>
+      <c r="E433" t="s">
+        <v>54</v>
+      </c>
+      <c r="F433" t="s">
+        <v>57</v>
+      </c>
+      <c r="G433">
+        <v>6813</v>
+      </c>
+      <c r="H433">
+        <v>0</v>
+      </c>
+      <c r="I433" t="s">
+        <v>65</v>
+      </c>
+      <c r="J433" t="s">
+        <v>154</v>
+      </c>
+      <c r="N433" s="1">
+        <v>46283</v>
+      </c>
+      <c r="O433" t="s">
+        <v>163</v>
+      </c>
+      <c r="P433">
+        <v>9</v>
+      </c>
+      <c r="Q433">
+        <v>2026</v>
+      </c>
+      <c r="R433">
+        <v>18164530</v>
+      </c>
+      <c r="S433" t="s">
+        <v>54</v>
+      </c>
+      <c r="U433" t="s">
+        <v>204</v>
+      </c>
+      <c r="V433" s="1">
+        <v>46282.79637748843</v>
+      </c>
+      <c r="W433">
+        <v>3</v>
+      </c>
+      <c r="X433" t="s">
+        <v>209</v>
+      </c>
+      <c r="Y433" t="s">
+        <v>368</v>
+      </c>
+      <c r="AB433">
+        <v>0</v>
+      </c>
+      <c r="AC433" t="s">
+        <v>54</v>
+      </c>
+      <c r="AH433" t="s">
+        <v>377</v>
+      </c>
+      <c r="AI433" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="434" spans="1:35">
+      <c r="A434">
+        <v>6949</v>
+      </c>
+      <c r="B434" t="s">
+        <v>37</v>
+      </c>
+      <c r="C434" t="s">
+        <v>50</v>
+      </c>
+      <c r="D434" t="s">
+        <v>51</v>
+      </c>
+      <c r="E434" t="s">
+        <v>54</v>
+      </c>
+      <c r="F434" t="s">
+        <v>57</v>
+      </c>
+      <c r="G434">
+        <v>6813</v>
+      </c>
+      <c r="H434">
+        <v>0</v>
+      </c>
+      <c r="I434" t="s">
+        <v>65</v>
+      </c>
+      <c r="J434" t="s">
+        <v>154</v>
+      </c>
+      <c r="N434" s="1">
+        <v>46283</v>
+      </c>
+      <c r="O434" t="s">
+        <v>163</v>
+      </c>
+      <c r="P434">
+        <v>9</v>
+      </c>
+      <c r="Q434">
+        <v>2026</v>
+      </c>
+      <c r="R434">
+        <v>18178169</v>
+      </c>
+      <c r="S434" t="s">
+        <v>193</v>
+      </c>
+      <c r="U434" t="s">
+        <v>204</v>
+      </c>
+      <c r="V434" s="1">
+        <v>46282.79638901621</v>
+      </c>
+      <c r="W434">
+        <v>3</v>
+      </c>
+      <c r="X434" t="s">
+        <v>208</v>
+      </c>
+      <c r="Y434" t="s">
+        <v>368</v>
+      </c>
+      <c r="AB434">
+        <v>0</v>
+      </c>
+      <c r="AC434" t="s">
+        <v>193</v>
+      </c>
+      <c r="AH434" t="s">
+        <v>377</v>
+      </c>
+      <c r="AI434" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="435" spans="1:35">
+      <c r="A435">
+        <v>5417</v>
+      </c>
+      <c r="B435" t="s">
+        <v>43</v>
+      </c>
+      <c r="C435" t="s">
+        <v>50</v>
+      </c>
+      <c r="D435" t="s">
+        <v>51</v>
+      </c>
+      <c r="E435" t="s">
+        <v>54</v>
+      </c>
+      <c r="F435" t="s">
+        <v>56</v>
+      </c>
+      <c r="G435">
+        <v>7027</v>
+      </c>
+      <c r="H435">
+        <v>0</v>
+      </c>
+      <c r="I435" t="s">
+        <v>65</v>
+      </c>
+      <c r="J435" t="s">
+        <v>119</v>
+      </c>
+      <c r="N435" s="1">
+        <v>46289</v>
+      </c>
+      <c r="P435">
+        <v>8</v>
+      </c>
+      <c r="Q435">
+        <v>2026</v>
+      </c>
+      <c r="R435">
+        <v>17399290</v>
+      </c>
+      <c r="S435" t="s">
+        <v>54</v>
+      </c>
+      <c r="U435" t="s">
+        <v>204</v>
+      </c>
+      <c r="V435" s="1">
+        <v>46283.39832862269</v>
+      </c>
+      <c r="W435">
+        <v>-3</v>
+      </c>
+      <c r="X435" t="s">
+        <v>212</v>
+      </c>
+      <c r="Y435" t="s">
+        <v>369</v>
+      </c>
+      <c r="AB435">
+        <v>0</v>
+      </c>
+      <c r="AC435" t="s">
+        <v>54</v>
+      </c>
+      <c r="AH435" t="s">
+        <v>375</v>
+      </c>
+      <c r="AI435" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="436" spans="1:35">
+      <c r="A436">
+        <v>6404</v>
+      </c>
+      <c r="B436" t="s">
+        <v>47</v>
+      </c>
+      <c r="C436" t="s">
+        <v>50</v>
+      </c>
+      <c r="D436" t="s">
+        <v>53</v>
+      </c>
+      <c r="E436" t="s">
+        <v>54</v>
+      </c>
+      <c r="F436" t="s">
+        <v>56</v>
+      </c>
+      <c r="G436">
+        <v>7027</v>
+      </c>
+      <c r="H436">
+        <v>0</v>
+      </c>
+      <c r="I436" t="s">
+        <v>65</v>
+      </c>
+      <c r="J436" t="s">
+        <v>119</v>
+      </c>
+      <c r="N436" s="1">
+        <v>46289</v>
+      </c>
+      <c r="P436">
+        <v>8</v>
+      </c>
+      <c r="Q436">
+        <v>2026</v>
+      </c>
+      <c r="R436">
+        <v>16962348</v>
+      </c>
+      <c r="S436" t="s">
+        <v>54</v>
+      </c>
+      <c r="U436" t="s">
+        <v>204</v>
+      </c>
+      <c r="V436" s="1">
         <v>46282.64018086805</v>
       </c>
-      <c r="W431">
+      <c r="W436">
         <v>-3</v>
       </c>
-      <c r="X431" t="s">
+      <c r="X436" t="s">
         <v>216</v>
       </c>
-      <c r="Y431" t="s">
-        <v>366</v>
-      </c>
-      <c r="AB431">
-        <v>0</v>
-      </c>
-      <c r="AC431" t="s">
-        <v>54</v>
-      </c>
-      <c r="AH431" t="s">
-        <v>371</v>
-      </c>
-      <c r="AI431" t="s">
-        <v>376</v>
+      <c r="Y436" t="s">
+        <v>370</v>
+      </c>
+      <c r="AB436">
+        <v>0</v>
+      </c>
+      <c r="AC436" t="s">
+        <v>54</v>
+      </c>
+      <c r="AH436" t="s">
+        <v>375</v>
+      </c>
+      <c r="AI436" t="s">
+        <v>380</v>
       </c>
     </row>
   </sheetData>

--- a/data/base/goias.xlsx
+++ b/data/base/goias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6272" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6257" uniqueCount="384">
   <si>
     <t>CodCliente</t>
   </si>
@@ -1067,9 +1067,6 @@
   </si>
   <si>
     <t>Tarefa baixada via Rotina SisAnalise x MGC - ExecutarPisCofinsZeradosOuComCredito. - Data Comentário: 18/09/2026 18:03</t>
-  </si>
-  <si>
-    <t>Baixado via API integração MGC x Sistema de Analise Fiscal em 17/09/2026 17:56:12. - Data Comentário: 17/09/2026 17:51</t>
   </si>
   <si>
     <t>Baixado via API integração MGC x Sistema de Analise Fiscal em 17/09/2026 17:55:53. - Data Comentário: 17/09/2026 17:50</t>
@@ -1531,7 +1528,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AI439"/>
+  <dimension ref="A1:AI438"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:35">
@@ -1712,10 +1709,10 @@
         <v>170</v>
       </c>
       <c r="AH2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="3" spans="1:35">
@@ -1789,10 +1786,10 @@
         <v>171</v>
       </c>
       <c r="AH3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="4" spans="1:35">
@@ -1866,10 +1863,10 @@
         <v>170</v>
       </c>
       <c r="AH4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="5" spans="1:35">
@@ -1940,10 +1937,10 @@
         <v>170</v>
       </c>
       <c r="AH5" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI5" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="6" spans="1:35">
@@ -2014,10 +2011,10 @@
         <v>171</v>
       </c>
       <c r="AH6" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI6" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="7" spans="1:35">
@@ -2088,10 +2085,10 @@
         <v>171</v>
       </c>
       <c r="AH7" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI7" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="8" spans="1:35">
@@ -2162,10 +2159,10 @@
         <v>172</v>
       </c>
       <c r="AH8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI8" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="9" spans="1:35">
@@ -2236,10 +2233,10 @@
         <v>170</v>
       </c>
       <c r="AH9" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI9" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10" spans="1:35">
@@ -2310,10 +2307,10 @@
         <v>173</v>
       </c>
       <c r="AH10" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI10" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="11" spans="1:35">
@@ -2384,10 +2381,10 @@
         <v>173</v>
       </c>
       <c r="AH11" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI11" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="12" spans="1:35">
@@ -2458,10 +2455,10 @@
         <v>174</v>
       </c>
       <c r="AH12" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI12" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="13" spans="1:35">
@@ -2529,13 +2526,13 @@
         <v>0</v>
       </c>
       <c r="AC13" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AH13" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI13" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="14" spans="1:35">
@@ -2603,13 +2600,13 @@
         <v>0</v>
       </c>
       <c r="AC14" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AH14" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI14" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="15" spans="1:35">
@@ -2677,10 +2674,10 @@
         <v>0</v>
       </c>
       <c r="AH15" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI15" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="16" spans="1:35">
@@ -2742,10 +2739,10 @@
         <v>0</v>
       </c>
       <c r="AH16" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI16" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="17" spans="1:35">
@@ -2813,10 +2810,10 @@
         <v>0</v>
       </c>
       <c r="AH17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI17" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="18" spans="1:35">
@@ -2890,10 +2887,10 @@
         <v>176</v>
       </c>
       <c r="AH18" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI18" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="19" spans="1:35">
@@ -2967,10 +2964,10 @@
         <v>175</v>
       </c>
       <c r="AH19" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI19" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="20" spans="1:35">
@@ -3044,10 +3041,10 @@
         <v>176</v>
       </c>
       <c r="AH20" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI20" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="21" spans="1:35">
@@ -3121,10 +3118,10 @@
         <v>174</v>
       </c>
       <c r="AH21" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI21" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="22" spans="1:35">
@@ -3195,10 +3192,10 @@
         <v>177</v>
       </c>
       <c r="AH22" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI22" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="23" spans="1:35">
@@ -3269,10 +3266,10 @@
         <v>174</v>
       </c>
       <c r="AH23" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI23" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="24" spans="1:35">
@@ -3343,10 +3340,10 @@
         <v>174</v>
       </c>
       <c r="AH24" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI24" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="25" spans="1:35">
@@ -3417,10 +3414,10 @@
         <v>174</v>
       </c>
       <c r="AH25" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI25" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="26" spans="1:35">
@@ -3491,10 +3488,10 @@
         <v>175</v>
       </c>
       <c r="AH26" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI26" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="27" spans="1:35">
@@ -3565,10 +3562,10 @@
         <v>174</v>
       </c>
       <c r="AH27" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI27" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="28" spans="1:35">
@@ -3639,10 +3636,10 @@
         <v>174</v>
       </c>
       <c r="AH28" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI28" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="29" spans="1:35">
@@ -3713,10 +3710,10 @@
         <v>174</v>
       </c>
       <c r="AH29" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI29" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="30" spans="1:35">
@@ -3781,13 +3778,13 @@
         <v>0</v>
       </c>
       <c r="AC30" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AH30" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI30" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="31" spans="1:35">
@@ -3861,10 +3858,10 @@
         <v>179</v>
       </c>
       <c r="AH31" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI31" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="32" spans="1:35">
@@ -3929,13 +3926,13 @@
         <v>0</v>
       </c>
       <c r="AC32" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AH32" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI32" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="33" spans="1:35">
@@ -4006,13 +4003,13 @@
         <v>0</v>
       </c>
       <c r="AC33" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AH33" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI33" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="34" spans="1:35">
@@ -4083,13 +4080,13 @@
         <v>0</v>
       </c>
       <c r="AC34" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AH34" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI34" t="s">
         <v>380</v>
-      </c>
-      <c r="AI34" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="35" spans="1:35">
@@ -4160,13 +4157,13 @@
         <v>0</v>
       </c>
       <c r="AC35" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AH35" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI35" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="36" spans="1:35">
@@ -4237,13 +4234,13 @@
         <v>0</v>
       </c>
       <c r="AC36" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AH36" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI36" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="37" spans="1:35">
@@ -4314,13 +4311,13 @@
         <v>0</v>
       </c>
       <c r="AC37" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AH37" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI37" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="38" spans="1:35">
@@ -4391,13 +4388,13 @@
         <v>0</v>
       </c>
       <c r="AC38" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AH38" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI38" t="s">
         <v>380</v>
-      </c>
-      <c r="AI38" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="39" spans="1:35">
@@ -4471,10 +4468,10 @@
         <v>179</v>
       </c>
       <c r="AH39" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI39" t="s">
         <v>380</v>
-      </c>
-      <c r="AI39" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="40" spans="1:35">
@@ -4548,10 +4545,10 @@
         <v>179</v>
       </c>
       <c r="AH40" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI40" t="s">
         <v>380</v>
-      </c>
-      <c r="AI40" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="41" spans="1:35">
@@ -4625,10 +4622,10 @@
         <v>179</v>
       </c>
       <c r="AH41" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI41" t="s">
         <v>380</v>
-      </c>
-      <c r="AI41" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="42" spans="1:35">
@@ -4699,13 +4696,13 @@
         <v>0</v>
       </c>
       <c r="AC42" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AH42" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI42" t="s">
         <v>380</v>
-      </c>
-      <c r="AI42" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="43" spans="1:35">
@@ -4776,13 +4773,13 @@
         <v>0</v>
       </c>
       <c r="AC43" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AH43" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI43" t="s">
         <v>380</v>
-      </c>
-      <c r="AI43" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="44" spans="1:35">
@@ -4853,13 +4850,13 @@
         <v>0</v>
       </c>
       <c r="AC44" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AH44" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI44" t="s">
         <v>380</v>
-      </c>
-      <c r="AI44" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="45" spans="1:35">
@@ -4930,13 +4927,13 @@
         <v>0</v>
       </c>
       <c r="AC45" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AH45" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI45" t="s">
         <v>380</v>
-      </c>
-      <c r="AI45" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="46" spans="1:35">
@@ -5001,13 +4998,13 @@
         <v>0</v>
       </c>
       <c r="AC46" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AH46" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI46" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="47" spans="1:35">
@@ -5075,10 +5072,10 @@
         <v>179</v>
       </c>
       <c r="AH47" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI47" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="48" spans="1:35">
@@ -5146,10 +5143,10 @@
         <v>179</v>
       </c>
       <c r="AH48" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI48" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="49" spans="1:35">
@@ -5217,10 +5214,10 @@
         <v>179</v>
       </c>
       <c r="AH49" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI49" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="50" spans="1:35">
@@ -5285,13 +5282,13 @@
         <v>0</v>
       </c>
       <c r="AC50" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AH50" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI50" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="51" spans="1:35">
@@ -5356,13 +5353,13 @@
         <v>0</v>
       </c>
       <c r="AC51" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AH51" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI51" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="52" spans="1:35">
@@ -5433,13 +5430,13 @@
         <v>0</v>
       </c>
       <c r="AC52" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AH52" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI52" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="53" spans="1:35">
@@ -5504,13 +5501,13 @@
         <v>0</v>
       </c>
       <c r="AC53" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AH53" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI53" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="54" spans="1:35">
@@ -5584,10 +5581,10 @@
         <v>179</v>
       </c>
       <c r="AH54" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI54" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="55" spans="1:35">
@@ -5661,10 +5658,10 @@
         <v>179</v>
       </c>
       <c r="AH55" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI55" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="56" spans="1:35">
@@ -5738,10 +5735,10 @@
         <v>179</v>
       </c>
       <c r="AH56" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI56" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="57" spans="1:35">
@@ -5812,13 +5809,13 @@
         <v>0</v>
       </c>
       <c r="AC57" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AH57" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI57" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="58" spans="1:35">
@@ -5889,13 +5886,13 @@
         <v>0</v>
       </c>
       <c r="AC58" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AH58" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI58" t="s">
         <v>380</v>
-      </c>
-      <c r="AI58" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="59" spans="1:35">
@@ -5966,13 +5963,13 @@
         <v>0</v>
       </c>
       <c r="AC59" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AH59" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI59" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="60" spans="1:35">
@@ -6046,10 +6043,10 @@
         <v>179</v>
       </c>
       <c r="AH60" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI60" t="s">
         <v>380</v>
-      </c>
-      <c r="AI60" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="61" spans="1:35">
@@ -6123,10 +6120,10 @@
         <v>179</v>
       </c>
       <c r="AH61" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI61" t="s">
         <v>380</v>
-      </c>
-      <c r="AI61" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="62" spans="1:35">
@@ -6200,10 +6197,10 @@
         <v>179</v>
       </c>
       <c r="AH62" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI62" t="s">
         <v>380</v>
-      </c>
-      <c r="AI62" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="63" spans="1:35">
@@ -6274,13 +6271,13 @@
         <v>0</v>
       </c>
       <c r="AC63" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AH63" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI63" t="s">
         <v>380</v>
-      </c>
-      <c r="AI63" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="64" spans="1:35">
@@ -6351,13 +6348,13 @@
         <v>0</v>
       </c>
       <c r="AC64" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AH64" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI64" t="s">
         <v>380</v>
-      </c>
-      <c r="AI64" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="65" spans="1:35">
@@ -6428,13 +6425,13 @@
         <v>0</v>
       </c>
       <c r="AC65" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AH65" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI65" t="s">
         <v>380</v>
-      </c>
-      <c r="AI65" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="66" spans="1:35">
@@ -6505,13 +6502,13 @@
         <v>0</v>
       </c>
       <c r="AC66" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AH66" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI66" t="s">
         <v>380</v>
-      </c>
-      <c r="AI66" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="67" spans="1:35">
@@ -6588,10 +6585,10 @@
         <v>179</v>
       </c>
       <c r="AH67" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI67" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="68" spans="1:35">
@@ -6656,13 +6653,13 @@
         <v>0</v>
       </c>
       <c r="AC68" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AH68" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI68" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="69" spans="1:35">
@@ -6727,13 +6724,13 @@
         <v>0</v>
       </c>
       <c r="AC69" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AH69" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI69" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="70" spans="1:35">
@@ -6801,10 +6798,10 @@
         <v>179</v>
       </c>
       <c r="AH70" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI70" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="71" spans="1:35">
@@ -6872,10 +6869,10 @@
         <v>179</v>
       </c>
       <c r="AH71" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI71" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="72" spans="1:35">
@@ -6943,10 +6940,10 @@
         <v>179</v>
       </c>
       <c r="AH72" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI72" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="73" spans="1:35">
@@ -7011,13 +7008,13 @@
         <v>0</v>
       </c>
       <c r="AC73" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AH73" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI73" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="74" spans="1:35">
@@ -7082,13 +7079,13 @@
         <v>0</v>
       </c>
       <c r="AC74" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AH74" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI74" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="75" spans="1:35">
@@ -7153,13 +7150,13 @@
         <v>0</v>
       </c>
       <c r="AC75" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AH75" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI75" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="76" spans="1:35">
@@ -7224,13 +7221,13 @@
         <v>0</v>
       </c>
       <c r="AC76" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AH76" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI76" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="77" spans="1:35">
@@ -7298,13 +7295,13 @@
         <v>0</v>
       </c>
       <c r="AC77" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AH77" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI77" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="78" spans="1:35">
@@ -7372,13 +7369,13 @@
         <v>0</v>
       </c>
       <c r="AC78" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AH78" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI78" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="79" spans="1:35">
@@ -7446,13 +7443,13 @@
         <v>0</v>
       </c>
       <c r="AC79" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AH79" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI79" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="80" spans="1:35">
@@ -7523,10 +7520,10 @@
         <v>193</v>
       </c>
       <c r="AH80" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI80" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="81" spans="1:35">
@@ -7594,10 +7591,10 @@
         <v>193</v>
       </c>
       <c r="AH81" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI81" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="82" spans="1:35">
@@ -7668,10 +7665,10 @@
         <v>182</v>
       </c>
       <c r="AH82" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI82" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="83" spans="1:35">
@@ -7742,10 +7739,10 @@
         <v>193</v>
       </c>
       <c r="AH83" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI83" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="84" spans="1:35">
@@ -7813,10 +7810,10 @@
         <v>193</v>
       </c>
       <c r="AH84" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI84" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="85" spans="1:35">
@@ -7887,10 +7884,10 @@
         <v>193</v>
       </c>
       <c r="AH85" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI85" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="86" spans="1:35">
@@ -7955,10 +7952,10 @@
         <v>182</v>
       </c>
       <c r="AH86" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI86" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="87" spans="1:35">
@@ -8029,10 +8026,10 @@
         <v>193</v>
       </c>
       <c r="AH87" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI87" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="88" spans="1:35">
@@ -8100,10 +8097,10 @@
         <v>193</v>
       </c>
       <c r="AH88" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI88" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="89" spans="1:35">
@@ -8174,10 +8171,10 @@
         <v>193</v>
       </c>
       <c r="AH89" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI89" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="90" spans="1:35">
@@ -8242,10 +8239,10 @@
         <v>193</v>
       </c>
       <c r="AH90" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI90" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="91" spans="1:35">
@@ -8310,10 +8307,10 @@
         <v>182</v>
       </c>
       <c r="AH91" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI91" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="92" spans="1:35">
@@ -8384,10 +8381,10 @@
         <v>193</v>
       </c>
       <c r="AH92" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI92" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="93" spans="1:35">
@@ -8455,10 +8452,10 @@
         <v>193</v>
       </c>
       <c r="AH93" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI93" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="94" spans="1:35">
@@ -8529,10 +8526,10 @@
         <v>193</v>
       </c>
       <c r="AH94" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI94" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="95" spans="1:35">
@@ -8597,10 +8594,10 @@
         <v>193</v>
       </c>
       <c r="AH95" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI95" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="96" spans="1:35">
@@ -8665,10 +8662,10 @@
         <v>182</v>
       </c>
       <c r="AH96" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI96" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="97" spans="1:35">
@@ -8739,10 +8736,10 @@
         <v>193</v>
       </c>
       <c r="AH97" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI97" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="98" spans="1:35">
@@ -8810,10 +8807,10 @@
         <v>193</v>
       </c>
       <c r="AH98" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI98" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="99" spans="1:35">
@@ -8884,10 +8881,10 @@
         <v>182</v>
       </c>
       <c r="AH99" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI99" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="100" spans="1:35">
@@ -8964,10 +8961,10 @@
         <v>193</v>
       </c>
       <c r="AH100" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI100" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="101" spans="1:35">
@@ -9035,10 +9032,10 @@
         <v>193</v>
       </c>
       <c r="AH101" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI101" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="102" spans="1:35">
@@ -9109,10 +9106,10 @@
         <v>193</v>
       </c>
       <c r="AH102" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI102" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="103" spans="1:35">
@@ -9180,10 +9177,10 @@
         <v>193</v>
       </c>
       <c r="AH103" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI103" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="104" spans="1:35">
@@ -9254,10 +9251,10 @@
         <v>193</v>
       </c>
       <c r="AH104" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI104" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="105" spans="1:35">
@@ -9322,10 +9319,10 @@
         <v>193</v>
       </c>
       <c r="AH105" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI105" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="106" spans="1:35">
@@ -9390,10 +9387,10 @@
         <v>182</v>
       </c>
       <c r="AH106" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI106" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="107" spans="1:35">
@@ -9464,10 +9461,10 @@
         <v>193</v>
       </c>
       <c r="AH107" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI107" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="108" spans="1:35">
@@ -9538,10 +9535,10 @@
         <v>193</v>
       </c>
       <c r="AH108" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI108" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="109" spans="1:35">
@@ -9609,10 +9606,10 @@
         <v>193</v>
       </c>
       <c r="AH109" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI109" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="110" spans="1:35">
@@ -9683,10 +9680,10 @@
         <v>182</v>
       </c>
       <c r="AH110" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI110" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="111" spans="1:35">
@@ -9754,10 +9751,10 @@
         <v>181</v>
       </c>
       <c r="AH111" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI111" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="112" spans="1:35">
@@ -9828,10 +9825,10 @@
         <v>182</v>
       </c>
       <c r="AH112" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI112" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="113" spans="1:35">
@@ -9902,10 +9899,10 @@
         <v>180</v>
       </c>
       <c r="AH113" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI113" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="114" spans="1:35">
@@ -9973,10 +9970,10 @@
         <v>181</v>
       </c>
       <c r="AH114" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI114" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:35">
@@ -10047,10 +10044,10 @@
         <v>182</v>
       </c>
       <c r="AH115" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI115" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:35">
@@ -10121,10 +10118,10 @@
         <v>193</v>
       </c>
       <c r="AH116" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI116" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="117" spans="1:35">
@@ -10192,10 +10189,10 @@
         <v>193</v>
       </c>
       <c r="AH117" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI117" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="118" spans="1:35">
@@ -10266,10 +10263,10 @@
         <v>193</v>
       </c>
       <c r="AH118" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI118" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="119" spans="1:35">
@@ -10334,10 +10331,10 @@
         <v>193</v>
       </c>
       <c r="AH119" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI119" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="120" spans="1:35">
@@ -10402,10 +10399,10 @@
         <v>182</v>
       </c>
       <c r="AH120" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI120" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="121" spans="1:35">
@@ -10476,10 +10473,10 @@
         <v>193</v>
       </c>
       <c r="AH121" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI121" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="122" spans="1:35">
@@ -10547,10 +10544,10 @@
         <v>193</v>
       </c>
       <c r="AH122" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI122" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="123" spans="1:35">
@@ -10621,10 +10618,10 @@
         <v>193</v>
       </c>
       <c r="AH123" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI123" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="124" spans="1:35">
@@ -10689,10 +10686,10 @@
         <v>193</v>
       </c>
       <c r="AH124" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI124" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="125" spans="1:35">
@@ -10757,10 +10754,10 @@
         <v>182</v>
       </c>
       <c r="AH125" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI125" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="126" spans="1:35">
@@ -10837,10 +10834,10 @@
         <v>182</v>
       </c>
       <c r="AH126" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI126" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="127" spans="1:35">
@@ -10917,10 +10914,10 @@
         <v>182</v>
       </c>
       <c r="AH127" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI127" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="128" spans="1:35">
@@ -10991,10 +10988,10 @@
         <v>185</v>
       </c>
       <c r="AH128" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI128" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="129" spans="1:35">
@@ -11065,10 +11062,10 @@
         <v>185</v>
       </c>
       <c r="AH129" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI129" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="130" spans="1:35">
@@ -11145,10 +11142,10 @@
         <v>185</v>
       </c>
       <c r="AH130" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI130" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="131" spans="1:35">
@@ -11219,10 +11216,10 @@
         <v>185</v>
       </c>
       <c r="AH131" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI131" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="132" spans="1:35">
@@ -11293,10 +11290,10 @@
         <v>185</v>
       </c>
       <c r="AH132" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI132" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="133" spans="1:35">
@@ -11367,10 +11364,10 @@
         <v>185</v>
       </c>
       <c r="AH133" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI133" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="134" spans="1:35">
@@ -11441,10 +11438,10 @@
         <v>185</v>
       </c>
       <c r="AH134" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI134" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="135" spans="1:35">
@@ -11521,10 +11518,10 @@
         <v>185</v>
       </c>
       <c r="AH135" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI135" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="136" spans="1:35">
@@ -11595,10 +11592,10 @@
         <v>185</v>
       </c>
       <c r="AH136" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI136" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="137" spans="1:35">
@@ -11669,10 +11666,10 @@
         <v>185</v>
       </c>
       <c r="AH137" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI137" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="138" spans="1:35">
@@ -11743,10 +11740,10 @@
         <v>185</v>
       </c>
       <c r="AH138" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI138" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="139" spans="1:35">
@@ -11823,10 +11820,10 @@
         <v>185</v>
       </c>
       <c r="AH139" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI139" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="140" spans="1:35">
@@ -11897,10 +11894,10 @@
         <v>185</v>
       </c>
       <c r="AH140" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI140" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="141" spans="1:35">
@@ -11971,10 +11968,10 @@
         <v>185</v>
       </c>
       <c r="AH141" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI141" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="142" spans="1:35">
@@ -12045,10 +12042,10 @@
         <v>185</v>
       </c>
       <c r="AH142" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI142" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="143" spans="1:35">
@@ -12119,10 +12116,10 @@
         <v>185</v>
       </c>
       <c r="AH143" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI143" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="144" spans="1:35">
@@ -12193,10 +12190,10 @@
         <v>185</v>
       </c>
       <c r="AH144" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI144" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="145" spans="1:35">
@@ -12267,10 +12264,10 @@
         <v>185</v>
       </c>
       <c r="AH145" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI145" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="146" spans="1:35">
@@ -12341,10 +12338,10 @@
         <v>185</v>
       </c>
       <c r="AH146" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI146" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="147" spans="1:35">
@@ -12415,10 +12412,10 @@
         <v>185</v>
       </c>
       <c r="AH147" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI147" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="148" spans="1:35">
@@ -12489,10 +12486,10 @@
         <v>185</v>
       </c>
       <c r="AH148" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI148" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="149" spans="1:35">
@@ -12563,10 +12560,10 @@
         <v>185</v>
       </c>
       <c r="AH149" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI149" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="150" spans="1:35">
@@ -12643,10 +12640,10 @@
         <v>185</v>
       </c>
       <c r="AH150" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI150" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="151" spans="1:35">
@@ -12717,10 +12714,10 @@
         <v>185</v>
       </c>
       <c r="AH151" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI151" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="152" spans="1:35">
@@ -12791,10 +12788,10 @@
         <v>185</v>
       </c>
       <c r="AH152" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI152" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="153" spans="1:35">
@@ -12865,10 +12862,10 @@
         <v>185</v>
       </c>
       <c r="AH153" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI153" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="154" spans="1:35">
@@ -12939,10 +12936,10 @@
         <v>186</v>
       </c>
       <c r="AH154" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI154" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="155" spans="1:35">
@@ -13013,10 +13010,10 @@
         <v>186</v>
       </c>
       <c r="AH155" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI155" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="156" spans="1:35">
@@ -13087,10 +13084,10 @@
         <v>186</v>
       </c>
       <c r="AH156" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI156" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="157" spans="1:35">
@@ -13161,10 +13158,10 @@
         <v>186</v>
       </c>
       <c r="AH157" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI157" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="158" spans="1:35">
@@ -13235,10 +13232,10 @@
         <v>186</v>
       </c>
       <c r="AH158" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI158" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="159" spans="1:35">
@@ -13309,10 +13306,10 @@
         <v>186</v>
       </c>
       <c r="AH159" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI159" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="160" spans="1:35">
@@ -13383,10 +13380,10 @@
         <v>186</v>
       </c>
       <c r="AH160" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI160" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="161" spans="1:35">
@@ -13457,10 +13454,10 @@
         <v>186</v>
       </c>
       <c r="AH161" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI161" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="162" spans="1:35">
@@ -13534,10 +13531,10 @@
         <v>186</v>
       </c>
       <c r="AH162" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI162" t="s">
         <v>380</v>
-      </c>
-      <c r="AI162" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="163" spans="1:35">
@@ -13611,10 +13608,10 @@
         <v>186</v>
       </c>
       <c r="AH163" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI163" t="s">
         <v>380</v>
-      </c>
-      <c r="AI163" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="164" spans="1:35">
@@ -13688,10 +13685,10 @@
         <v>186</v>
       </c>
       <c r="AH164" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI164" t="s">
         <v>380</v>
-      </c>
-      <c r="AI164" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="165" spans="1:35">
@@ -13765,10 +13762,10 @@
         <v>186</v>
       </c>
       <c r="AH165" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI165" t="s">
         <v>380</v>
-      </c>
-      <c r="AI165" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="166" spans="1:35">
@@ -13842,10 +13839,10 @@
         <v>186</v>
       </c>
       <c r="AH166" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI166" t="s">
         <v>380</v>
-      </c>
-      <c r="AI166" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="167" spans="1:35">
@@ -13919,10 +13916,10 @@
         <v>186</v>
       </c>
       <c r="AH167" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI167" t="s">
         <v>380</v>
-      </c>
-      <c r="AI167" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="168" spans="1:35">
@@ -13996,10 +13993,10 @@
         <v>186</v>
       </c>
       <c r="AH168" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI168" t="s">
         <v>380</v>
-      </c>
-      <c r="AI168" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="169" spans="1:35">
@@ -14073,10 +14070,10 @@
         <v>186</v>
       </c>
       <c r="AH169" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI169" t="s">
         <v>380</v>
-      </c>
-      <c r="AI169" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="170" spans="1:35">
@@ -14150,10 +14147,10 @@
         <v>186</v>
       </c>
       <c r="AH170" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI170" t="s">
         <v>380</v>
-      </c>
-      <c r="AI170" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="171" spans="1:35">
@@ -14227,10 +14224,10 @@
         <v>186</v>
       </c>
       <c r="AH171" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI171" t="s">
         <v>380</v>
-      </c>
-      <c r="AI171" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="172" spans="1:35">
@@ -14304,10 +14301,10 @@
         <v>186</v>
       </c>
       <c r="AH172" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI172" t="s">
         <v>380</v>
-      </c>
-      <c r="AI172" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="173" spans="1:35">
@@ -14381,10 +14378,10 @@
         <v>186</v>
       </c>
       <c r="AH173" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI173" t="s">
         <v>380</v>
-      </c>
-      <c r="AI173" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="174" spans="1:35">
@@ -14458,10 +14455,10 @@
         <v>186</v>
       </c>
       <c r="AH174" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI174" t="s">
         <v>380</v>
-      </c>
-      <c r="AI174" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="175" spans="1:35">
@@ -14535,10 +14532,10 @@
         <v>186</v>
       </c>
       <c r="AH175" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI175" t="s">
         <v>380</v>
-      </c>
-      <c r="AI175" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="176" spans="1:35">
@@ -14606,10 +14603,10 @@
         <v>186</v>
       </c>
       <c r="AH176" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI176" t="s">
         <v>380</v>
-      </c>
-      <c r="AI176" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="177" spans="1:35">
@@ -14677,10 +14674,10 @@
         <v>186</v>
       </c>
       <c r="AH177" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI177" t="s">
         <v>380</v>
-      </c>
-      <c r="AI177" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="178" spans="1:35">
@@ -14748,10 +14745,10 @@
         <v>186</v>
       </c>
       <c r="AH178" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI178" t="s">
         <v>380</v>
-      </c>
-      <c r="AI178" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="179" spans="1:35">
@@ -14819,10 +14816,10 @@
         <v>186</v>
       </c>
       <c r="AH179" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI179" t="s">
         <v>380</v>
-      </c>
-      <c r="AI179" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="180" spans="1:35">
@@ -14890,10 +14887,10 @@
         <v>186</v>
       </c>
       <c r="AH180" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI180" t="s">
         <v>380</v>
-      </c>
-      <c r="AI180" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="181" spans="1:35">
@@ -14961,10 +14958,10 @@
         <v>186</v>
       </c>
       <c r="AH181" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI181" t="s">
         <v>380</v>
-      </c>
-      <c r="AI181" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="182" spans="1:35">
@@ -15032,10 +15029,10 @@
         <v>54</v>
       </c>
       <c r="AH182" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI182" t="s">
         <v>380</v>
-      </c>
-      <c r="AI182" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="183" spans="1:35">
@@ -15103,10 +15100,10 @@
         <v>54</v>
       </c>
       <c r="AH183" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI183" t="s">
         <v>380</v>
-      </c>
-      <c r="AI183" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="184" spans="1:35">
@@ -15174,10 +15171,10 @@
         <v>54</v>
       </c>
       <c r="AH184" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI184" t="s">
         <v>380</v>
-      </c>
-      <c r="AI184" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="185" spans="1:35">
@@ -15245,10 +15242,10 @@
         <v>54</v>
       </c>
       <c r="AH185" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI185" t="s">
         <v>380</v>
-      </c>
-      <c r="AI185" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="186" spans="1:35">
@@ -15316,10 +15313,10 @@
         <v>187</v>
       </c>
       <c r="AH186" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI186" t="s">
         <v>380</v>
-      </c>
-      <c r="AI186" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="187" spans="1:35">
@@ -15387,10 +15384,10 @@
         <v>55</v>
       </c>
       <c r="AH187" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI187" t="s">
         <v>380</v>
-      </c>
-      <c r="AI187" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="188" spans="1:35">
@@ -15458,10 +15455,10 @@
         <v>54</v>
       </c>
       <c r="AH188" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI188" t="s">
         <v>380</v>
-      </c>
-      <c r="AI188" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="189" spans="1:35">
@@ -15529,10 +15526,10 @@
         <v>54</v>
       </c>
       <c r="AH189" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI189" t="s">
         <v>380</v>
-      </c>
-      <c r="AI189" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="190" spans="1:35">
@@ -15600,10 +15597,10 @@
         <v>54</v>
       </c>
       <c r="AH190" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI190" t="s">
         <v>380</v>
-      </c>
-      <c r="AI190" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="191" spans="1:35">
@@ -15671,10 +15668,10 @@
         <v>187</v>
       </c>
       <c r="AH191" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI191" t="s">
         <v>380</v>
-      </c>
-      <c r="AI191" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="192" spans="1:35">
@@ -15742,10 +15739,10 @@
         <v>54</v>
       </c>
       <c r="AH192" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI192" t="s">
         <v>380</v>
-      </c>
-      <c r="AI192" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="193" spans="1:35">
@@ -15813,10 +15810,10 @@
         <v>187</v>
       </c>
       <c r="AH193" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI193" t="s">
         <v>380</v>
-      </c>
-      <c r="AI193" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="194" spans="1:35">
@@ -15884,10 +15881,10 @@
         <v>54</v>
       </c>
       <c r="AH194" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI194" t="s">
         <v>380</v>
-      </c>
-      <c r="AI194" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="195" spans="1:35">
@@ -15955,10 +15952,10 @@
         <v>54</v>
       </c>
       <c r="AH195" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI195" t="s">
         <v>380</v>
-      </c>
-      <c r="AI195" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="196" spans="1:35">
@@ -16026,10 +16023,10 @@
         <v>54</v>
       </c>
       <c r="AH196" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI196" t="s">
         <v>380</v>
-      </c>
-      <c r="AI196" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="197" spans="1:35">
@@ -16097,10 +16094,10 @@
         <v>54</v>
       </c>
       <c r="AH197" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI197" t="s">
         <v>380</v>
-      </c>
-      <c r="AI197" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="198" spans="1:35">
@@ -16168,10 +16165,10 @@
         <v>54</v>
       </c>
       <c r="AH198" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI198" t="s">
         <v>380</v>
-      </c>
-      <c r="AI198" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="199" spans="1:35">
@@ -16239,10 +16236,10 @@
         <v>54</v>
       </c>
       <c r="AH199" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI199" t="s">
         <v>380</v>
-      </c>
-      <c r="AI199" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="200" spans="1:35">
@@ -16310,10 +16307,10 @@
         <v>187</v>
       </c>
       <c r="AH200" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI200" t="s">
         <v>380</v>
-      </c>
-      <c r="AI200" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="201" spans="1:35">
@@ -16381,10 +16378,10 @@
         <v>55</v>
       </c>
       <c r="AH201" t="s">
+        <v>379</v>
+      </c>
+      <c r="AI201" t="s">
         <v>380</v>
-      </c>
-      <c r="AI201" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="202" spans="1:35">
@@ -16455,10 +16452,10 @@
         <v>54</v>
       </c>
       <c r="AH202" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI202" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="203" spans="1:35">
@@ -16529,10 +16526,10 @@
         <v>54</v>
       </c>
       <c r="AH203" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI203" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="204" spans="1:35">
@@ -16603,10 +16600,10 @@
         <v>54</v>
       </c>
       <c r="AH204" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI204" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="205" spans="1:35">
@@ -16677,10 +16674,10 @@
         <v>54</v>
       </c>
       <c r="AH205" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI205" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="206" spans="1:35">
@@ -16748,10 +16745,10 @@
         <v>54</v>
       </c>
       <c r="AH206" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI206" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="207" spans="1:35">
@@ -16819,10 +16816,10 @@
         <v>54</v>
       </c>
       <c r="AH207" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI207" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="208" spans="1:35">
@@ -16887,10 +16884,10 @@
         <v>0</v>
       </c>
       <c r="AH208" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI208" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="209" spans="1:35">
@@ -16952,10 +16949,10 @@
         <v>0</v>
       </c>
       <c r="AH209" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI209" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="210" spans="1:35">
@@ -17023,13 +17020,13 @@
         <v>0</v>
       </c>
       <c r="AC210" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AH210" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI210" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="211" spans="1:35">
@@ -17100,10 +17097,10 @@
         <v>175</v>
       </c>
       <c r="AH211" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI211" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="212" spans="1:35">
@@ -17177,10 +17174,10 @@
         <v>179</v>
       </c>
       <c r="AH212" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI212" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="213" spans="1:35">
@@ -17254,10 +17251,10 @@
         <v>179</v>
       </c>
       <c r="AH213" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI213" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="214" spans="1:35">
@@ -17328,13 +17325,13 @@
         <v>0</v>
       </c>
       <c r="AC214" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AH214" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI214" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="215" spans="1:35">
@@ -17405,13 +17402,13 @@
         <v>0</v>
       </c>
       <c r="AC215" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AH215" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI215" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="216" spans="1:35">
@@ -17485,10 +17482,10 @@
         <v>179</v>
       </c>
       <c r="AH216" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI216" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="217" spans="1:35">
@@ -17559,13 +17556,13 @@
         <v>0</v>
       </c>
       <c r="AC217" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AH217" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI217" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="218" spans="1:35">
@@ -17639,10 +17636,10 @@
         <v>179</v>
       </c>
       <c r="AH218" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI218" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="219" spans="1:35">
@@ -17716,10 +17713,10 @@
         <v>179</v>
       </c>
       <c r="AH219" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI219" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="220" spans="1:35">
@@ -17784,13 +17781,13 @@
         <v>0</v>
       </c>
       <c r="AC220" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AH220" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI220" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="221" spans="1:35">
@@ -17855,13 +17852,13 @@
         <v>0</v>
       </c>
       <c r="AC221" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AH221" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI221" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="222" spans="1:35">
@@ -17935,10 +17932,10 @@
         <v>179</v>
       </c>
       <c r="AH222" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI222" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="223" spans="1:35">
@@ -18009,13 +18006,13 @@
         <v>0</v>
       </c>
       <c r="AC223" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AH223" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI223" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="224" spans="1:35">
@@ -18089,10 +18086,10 @@
         <v>179</v>
       </c>
       <c r="AH224" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI224" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="225" spans="1:35">
@@ -18166,10 +18163,10 @@
         <v>179</v>
       </c>
       <c r="AH225" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI225" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="226" spans="1:35">
@@ -18234,13 +18231,13 @@
         <v>0</v>
       </c>
       <c r="AC226" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AH226" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI226" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="227" spans="1:35">
@@ -18305,13 +18302,13 @@
         <v>0</v>
       </c>
       <c r="AC227" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AH227" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI227" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="228" spans="1:35">
@@ -18382,10 +18379,10 @@
         <v>178</v>
       </c>
       <c r="AH228" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI228" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="229" spans="1:35">
@@ -18456,10 +18453,10 @@
         <v>178</v>
       </c>
       <c r="AH229" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI229" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="230" spans="1:35">
@@ -18530,10 +18527,10 @@
         <v>178</v>
       </c>
       <c r="AH230" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI230" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="231" spans="1:35">
@@ -18604,10 +18601,10 @@
         <v>178</v>
       </c>
       <c r="AH231" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI231" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="232" spans="1:35">
@@ -18678,10 +18675,10 @@
         <v>178</v>
       </c>
       <c r="AH232" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI232" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="233" spans="1:35">
@@ -18752,10 +18749,10 @@
         <v>178</v>
       </c>
       <c r="AH233" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI233" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="234" spans="1:35">
@@ -18829,10 +18826,10 @@
         <v>178</v>
       </c>
       <c r="AH234" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI234" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="235" spans="1:35">
@@ -18903,10 +18900,10 @@
         <v>178</v>
       </c>
       <c r="AH235" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI235" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="236" spans="1:35">
@@ -18977,10 +18974,10 @@
         <v>178</v>
       </c>
       <c r="AH236" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI236" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="237" spans="1:35">
@@ -19051,10 +19048,10 @@
         <v>178</v>
       </c>
       <c r="AH237" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI237" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="238" spans="1:35">
@@ -19125,13 +19122,13 @@
         <v>0</v>
       </c>
       <c r="AC238" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AH238" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI238" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="239" spans="1:35">
@@ -19205,10 +19202,10 @@
         <v>179</v>
       </c>
       <c r="AH239" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI239" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="240" spans="1:35">
@@ -19282,10 +19279,10 @@
         <v>179</v>
       </c>
       <c r="AH240" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI240" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="241" spans="1:35">
@@ -19359,10 +19356,10 @@
         <v>178</v>
       </c>
       <c r="AH241" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI241" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="242" spans="1:35">
@@ -19433,13 +19430,13 @@
         <v>0</v>
       </c>
       <c r="AC242" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AH242" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI242" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="243" spans="1:35">
@@ -19510,13 +19507,13 @@
         <v>0</v>
       </c>
       <c r="AC243" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AH243" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI243" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="244" spans="1:35">
@@ -19581,13 +19578,13 @@
         <v>0</v>
       </c>
       <c r="AC244" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AH244" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI244" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="245" spans="1:35">
@@ -19658,10 +19655,10 @@
         <v>178</v>
       </c>
       <c r="AH245" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI245" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="246" spans="1:35">
@@ -19735,10 +19732,10 @@
         <v>179</v>
       </c>
       <c r="AH246" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI246" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="247" spans="1:35">
@@ -19809,10 +19806,10 @@
         <v>178</v>
       </c>
       <c r="AH247" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI247" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="248" spans="1:35">
@@ -19886,10 +19883,10 @@
         <v>179</v>
       </c>
       <c r="AH248" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI248" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="249" spans="1:35">
@@ -19963,10 +19960,10 @@
         <v>179</v>
       </c>
       <c r="AH249" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI249" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="250" spans="1:35">
@@ -20037,10 +20034,10 @@
         <v>178</v>
       </c>
       <c r="AH250" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI250" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="251" spans="1:35">
@@ -20111,10 +20108,10 @@
         <v>178</v>
       </c>
       <c r="AH251" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI251" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="252" spans="1:35">
@@ -20185,10 +20182,10 @@
         <v>178</v>
       </c>
       <c r="AH252" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI252" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="253" spans="1:35">
@@ -20259,10 +20256,10 @@
         <v>178</v>
       </c>
       <c r="AH253" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI253" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="254" spans="1:35">
@@ -20333,13 +20330,13 @@
         <v>0</v>
       </c>
       <c r="AC254" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AH254" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI254" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="255" spans="1:35">
@@ -20410,10 +20407,10 @@
         <v>179</v>
       </c>
       <c r="AH255" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI255" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="256" spans="1:35">
@@ -20484,10 +20481,10 @@
         <v>179</v>
       </c>
       <c r="AH256" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI256" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="257" spans="1:35">
@@ -20558,10 +20555,10 @@
         <v>179</v>
       </c>
       <c r="AH257" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI257" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="258" spans="1:35">
@@ -20638,10 +20635,10 @@
         <v>184</v>
       </c>
       <c r="AH258" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI258" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="259" spans="1:35">
@@ -20718,10 +20715,10 @@
         <v>184</v>
       </c>
       <c r="AH259" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI259" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="260" spans="1:35">
@@ -20798,10 +20795,10 @@
         <v>183</v>
       </c>
       <c r="AH260" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI260" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="261" spans="1:35">
@@ -20869,10 +20866,10 @@
         <v>181</v>
       </c>
       <c r="AH261" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI261" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="262" spans="1:35">
@@ -20949,10 +20946,10 @@
         <v>180</v>
       </c>
       <c r="AH262" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI262" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="263" spans="1:35">
@@ -21020,10 +21017,10 @@
         <v>193</v>
       </c>
       <c r="AH263" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI263" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="264" spans="1:35">
@@ -21100,10 +21097,10 @@
         <v>193</v>
       </c>
       <c r="AH264" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI264" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="265" spans="1:35">
@@ -21177,10 +21174,10 @@
         <v>181</v>
       </c>
       <c r="AH265" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI265" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="266" spans="1:35">
@@ -21257,10 +21254,10 @@
         <v>182</v>
       </c>
       <c r="AH266" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI266" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="267" spans="1:35">
@@ -21334,10 +21331,10 @@
         <v>184</v>
       </c>
       <c r="AH267" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI267" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="268" spans="1:35">
@@ -21414,10 +21411,10 @@
         <v>184</v>
       </c>
       <c r="AH268" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI268" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="269" spans="1:35">
@@ -21491,10 +21488,10 @@
         <v>183</v>
       </c>
       <c r="AH269" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI269" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="270" spans="1:35">
@@ -21565,10 +21562,10 @@
         <v>181</v>
       </c>
       <c r="AH270" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI270" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="271" spans="1:35">
@@ -21642,10 +21639,10 @@
         <v>184</v>
       </c>
       <c r="AH271" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI271" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="272" spans="1:35">
@@ -21719,10 +21716,10 @@
         <v>184</v>
       </c>
       <c r="AH272" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI272" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="273" spans="1:35">
@@ -21799,10 +21796,10 @@
         <v>180</v>
       </c>
       <c r="AH273" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI273" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="274" spans="1:35">
@@ -21870,10 +21867,10 @@
         <v>193</v>
       </c>
       <c r="AH274" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI274" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="275" spans="1:35">
@@ -21947,10 +21944,10 @@
         <v>181</v>
       </c>
       <c r="AH275" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI275" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="276" spans="1:35">
@@ -22021,10 +22018,10 @@
         <v>184</v>
       </c>
       <c r="AH276" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI276" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="277" spans="1:35">
@@ -22095,10 +22092,10 @@
         <v>184</v>
       </c>
       <c r="AH277" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI277" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="278" spans="1:35">
@@ -22169,10 +22166,10 @@
         <v>182</v>
       </c>
       <c r="AH278" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI278" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="279" spans="1:35">
@@ -22246,10 +22243,10 @@
         <v>181</v>
       </c>
       <c r="AH279" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI279" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="280" spans="1:35">
@@ -22323,10 +22320,10 @@
         <v>181</v>
       </c>
       <c r="AH280" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI280" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="281" spans="1:35">
@@ -22403,10 +22400,10 @@
         <v>182</v>
       </c>
       <c r="AH281" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI281" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="282" spans="1:35">
@@ -22483,10 +22480,10 @@
         <v>185</v>
       </c>
       <c r="AH282" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI282" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="283" spans="1:35">
@@ -22560,10 +22557,10 @@
         <v>185</v>
       </c>
       <c r="AH283" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI283" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="284" spans="1:35">
@@ -22640,10 +22637,10 @@
         <v>185</v>
       </c>
       <c r="AH284" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI284" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="285" spans="1:35">
@@ -22714,10 +22711,10 @@
         <v>185</v>
       </c>
       <c r="AH285" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI285" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="286" spans="1:35">
@@ -22788,10 +22785,10 @@
         <v>185</v>
       </c>
       <c r="AH286" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI286" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="287" spans="1:35">
@@ -22862,10 +22859,10 @@
         <v>185</v>
       </c>
       <c r="AH287" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI287" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="288" spans="1:35">
@@ -22936,10 +22933,10 @@
         <v>185</v>
       </c>
       <c r="AH288" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI288" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="289" spans="1:35">
@@ -23010,10 +23007,10 @@
         <v>185</v>
       </c>
       <c r="AH289" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI289" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="290" spans="1:35">
@@ -23090,10 +23087,10 @@
         <v>185</v>
       </c>
       <c r="AH290" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI290" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="291" spans="1:35">
@@ -23164,10 +23161,10 @@
         <v>185</v>
       </c>
       <c r="AH291" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI291" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="292" spans="1:35">
@@ -23244,10 +23241,10 @@
         <v>185</v>
       </c>
       <c r="AH292" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI292" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="293" spans="1:35">
@@ -23318,10 +23315,10 @@
         <v>185</v>
       </c>
       <c r="AH293" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI293" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="294" spans="1:35">
@@ -23392,10 +23389,10 @@
         <v>185</v>
       </c>
       <c r="AH294" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI294" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="295" spans="1:35">
@@ -23466,10 +23463,10 @@
         <v>185</v>
       </c>
       <c r="AH295" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI295" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="296" spans="1:35">
@@ -23546,10 +23543,10 @@
         <v>185</v>
       </c>
       <c r="AH296" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI296" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="297" spans="1:35">
@@ -23620,10 +23617,10 @@
         <v>185</v>
       </c>
       <c r="AH297" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI297" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="298" spans="1:35">
@@ -23694,10 +23691,10 @@
         <v>185</v>
       </c>
       <c r="AH298" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI298" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="299" spans="1:35">
@@ -23768,10 +23765,10 @@
         <v>185</v>
       </c>
       <c r="AH299" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI299" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="300" spans="1:35">
@@ -23842,10 +23839,10 @@
         <v>185</v>
       </c>
       <c r="AH300" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI300" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="301" spans="1:35">
@@ -23916,10 +23913,10 @@
         <v>185</v>
       </c>
       <c r="AH301" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI301" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="302" spans="1:35">
@@ -23990,10 +23987,10 @@
         <v>185</v>
       </c>
       <c r="AH302" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI302" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="303" spans="1:35">
@@ -24070,10 +24067,10 @@
         <v>185</v>
       </c>
       <c r="AH303" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI303" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="304" spans="1:35">
@@ -24150,10 +24147,10 @@
         <v>185</v>
       </c>
       <c r="AH304" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI304" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="305" spans="1:35">
@@ -24230,10 +24227,10 @@
         <v>185</v>
       </c>
       <c r="AH305" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI305" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="306" spans="1:35">
@@ -24307,10 +24304,10 @@
         <v>185</v>
       </c>
       <c r="AH306" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI306" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="307" spans="1:35">
@@ -24384,10 +24381,10 @@
         <v>185</v>
       </c>
       <c r="AH307" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI307" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="308" spans="1:35">
@@ -24461,10 +24458,10 @@
         <v>186</v>
       </c>
       <c r="AH308" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI308" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="309" spans="1:35">
@@ -24538,10 +24535,10 @@
         <v>186</v>
       </c>
       <c r="AH309" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI309" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="310" spans="1:35">
@@ -24612,10 +24609,10 @@
         <v>186</v>
       </c>
       <c r="AH310" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI310" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="311" spans="1:35">
@@ -24686,10 +24683,10 @@
         <v>186</v>
       </c>
       <c r="AH311" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI311" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="312" spans="1:35">
@@ -24760,10 +24757,10 @@
         <v>186</v>
       </c>
       <c r="AH312" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI312" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="313" spans="1:35">
@@ -24834,10 +24831,10 @@
         <v>186</v>
       </c>
       <c r="AH313" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI313" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="314" spans="1:35">
@@ -24905,10 +24902,10 @@
         <v>186</v>
       </c>
       <c r="AH314" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI314" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="315" spans="1:35">
@@ -24982,10 +24979,10 @@
         <v>186</v>
       </c>
       <c r="AH315" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI315" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="316" spans="1:35">
@@ -25059,10 +25056,10 @@
         <v>186</v>
       </c>
       <c r="AH316" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI316" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="317" spans="1:35">
@@ -25136,10 +25133,10 @@
         <v>186</v>
       </c>
       <c r="AH317" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI317" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="318" spans="1:35">
@@ -25213,10 +25210,10 @@
         <v>186</v>
       </c>
       <c r="AH318" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI318" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="319" spans="1:35">
@@ -25290,10 +25287,10 @@
         <v>186</v>
       </c>
       <c r="AH319" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI319" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="320" spans="1:35">
@@ -25364,10 +25361,10 @@
         <v>186</v>
       </c>
       <c r="AH320" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI320" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="321" spans="1:35">
@@ -25438,10 +25435,10 @@
         <v>186</v>
       </c>
       <c r="AH321" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI321" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="322" spans="1:35">
@@ -25512,10 +25509,10 @@
         <v>186</v>
       </c>
       <c r="AH322" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI322" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="323" spans="1:35">
@@ -25583,10 +25580,10 @@
         <v>186</v>
       </c>
       <c r="AH323" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI323" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="324" spans="1:35">
@@ -25654,10 +25651,10 @@
         <v>186</v>
       </c>
       <c r="AH324" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI324" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="325" spans="1:35">
@@ -25725,10 +25722,10 @@
         <v>186</v>
       </c>
       <c r="AH325" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI325" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="326" spans="1:35">
@@ -25796,10 +25793,10 @@
         <v>186</v>
       </c>
       <c r="AH326" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI326" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="327" spans="1:35">
@@ -25867,10 +25864,10 @@
         <v>186</v>
       </c>
       <c r="AH327" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI327" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="328" spans="1:35">
@@ -25938,10 +25935,10 @@
         <v>54</v>
       </c>
       <c r="AH328" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI328" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="329" spans="1:35">
@@ -26009,10 +26006,10 @@
         <v>54</v>
       </c>
       <c r="AH329" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI329" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="330" spans="1:35">
@@ -26080,10 +26077,10 @@
         <v>54</v>
       </c>
       <c r="AH330" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI330" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="331" spans="1:35">
@@ -26151,10 +26148,10 @@
         <v>54</v>
       </c>
       <c r="AH331" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI331" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="332" spans="1:35">
@@ -26222,10 +26219,10 @@
         <v>187</v>
       </c>
       <c r="AH332" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI332" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="333" spans="1:35">
@@ -26293,10 +26290,10 @@
         <v>187</v>
       </c>
       <c r="AH333" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI333" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="334" spans="1:35">
@@ -26364,10 +26361,10 @@
         <v>187</v>
       </c>
       <c r="AH334" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI334" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="335" spans="1:35">
@@ -26435,10 +26432,10 @@
         <v>187</v>
       </c>
       <c r="AH335" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI335" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="336" spans="1:35">
@@ -26506,10 +26503,10 @@
         <v>187</v>
       </c>
       <c r="AH336" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI336" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="337" spans="1:35">
@@ -26577,10 +26574,10 @@
         <v>187</v>
       </c>
       <c r="AH337" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI337" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="338" spans="1:35">
@@ -26648,10 +26645,10 @@
         <v>187</v>
       </c>
       <c r="AH338" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI338" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="339" spans="1:35">
@@ -26719,10 +26716,10 @@
         <v>187</v>
       </c>
       <c r="AH339" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI339" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="340" spans="1:35">
@@ -26790,10 +26787,10 @@
         <v>187</v>
       </c>
       <c r="AH340" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI340" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="341" spans="1:35">
@@ -26864,10 +26861,10 @@
         <v>54</v>
       </c>
       <c r="AH341" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI341" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="342" spans="1:35">
@@ -26938,10 +26935,10 @@
         <v>54</v>
       </c>
       <c r="AH342" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI342" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="343" spans="1:35">
@@ -27009,13 +27006,13 @@
         <v>0</v>
       </c>
       <c r="AC343" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AH343" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI343" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="344" spans="1:35">
@@ -27086,10 +27083,10 @@
         <v>170</v>
       </c>
       <c r="AH344" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI344" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="345" spans="1:35">
@@ -27160,10 +27157,10 @@
         <v>170</v>
       </c>
       <c r="AH345" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI345" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="346" spans="1:35">
@@ -27237,10 +27234,10 @@
         <v>175</v>
       </c>
       <c r="AH346" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI346" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="347" spans="1:35">
@@ -27311,10 +27308,10 @@
         <v>176</v>
       </c>
       <c r="AH347" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI347" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="348" spans="1:35">
@@ -27379,13 +27376,13 @@
         <v>0</v>
       </c>
       <c r="AC348" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AH348" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI348" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="349" spans="1:35">
@@ -27450,13 +27447,13 @@
         <v>0</v>
       </c>
       <c r="AC349" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AH349" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI349" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="350" spans="1:35">
@@ -27530,10 +27527,10 @@
         <v>179</v>
       </c>
       <c r="AH350" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI350" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="351" spans="1:35">
@@ -27604,13 +27601,13 @@
         <v>0</v>
       </c>
       <c r="AC351" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AH351" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI351" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="352" spans="1:35">
@@ -27684,10 +27681,10 @@
         <v>179</v>
       </c>
       <c r="AH352" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI352" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="353" spans="1:35">
@@ -27761,10 +27758,10 @@
         <v>179</v>
       </c>
       <c r="AH353" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI353" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="354" spans="1:35">
@@ -27835,13 +27832,13 @@
         <v>0</v>
       </c>
       <c r="AC354" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AH354" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI354" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="355" spans="1:35">
@@ -27912,13 +27909,13 @@
         <v>0</v>
       </c>
       <c r="AC355" t="s">
+        <v>376</v>
+      </c>
+      <c r="AH355" t="s">
         <v>377</v>
       </c>
-      <c r="AH355" t="s">
-        <v>378</v>
-      </c>
       <c r="AI355" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="356" spans="1:35">
@@ -27983,13 +27980,13 @@
         <v>0</v>
       </c>
       <c r="AC356" t="s">
+        <v>376</v>
+      </c>
+      <c r="AH356" t="s">
         <v>377</v>
       </c>
-      <c r="AH356" t="s">
-        <v>378</v>
-      </c>
       <c r="AI356" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="357" spans="1:35">
@@ -28060,10 +28057,10 @@
         <v>180</v>
       </c>
       <c r="AH357" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI357" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="358" spans="1:35">
@@ -28137,10 +28134,10 @@
         <v>180</v>
       </c>
       <c r="AH358" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI358" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="359" spans="1:35">
@@ -28211,10 +28208,10 @@
         <v>181</v>
       </c>
       <c r="AH359" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI359" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="360" spans="1:35">
@@ -28288,10 +28285,10 @@
         <v>183</v>
       </c>
       <c r="AH360" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI360" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="361" spans="1:35">
@@ -28362,10 +28359,10 @@
         <v>181</v>
       </c>
       <c r="AH361" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI361" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="362" spans="1:35">
@@ -28436,18 +28433,18 @@
         <v>181</v>
       </c>
       <c r="AH362" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI362" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="363" spans="1:35">
       <c r="A363">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B363" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C363" t="s">
         <v>50</v>
@@ -28456,7 +28453,7 @@
         <v>51</v>
       </c>
       <c r="E363" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F363" t="s">
         <v>56</v>
@@ -28483,25 +28480,22 @@
         <v>2026</v>
       </c>
       <c r="R363">
-        <v>18094899</v>
+        <v>18048473</v>
       </c>
       <c r="S363" t="s">
-        <v>180</v>
-      </c>
-      <c r="T363" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="U363" t="s">
         <v>196</v>
       </c>
       <c r="V363" s="1">
-        <v>46282.74573174769</v>
+        <v>46282.74485532408</v>
       </c>
       <c r="W363">
         <v>-2</v>
       </c>
       <c r="X363" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Y363" t="s">
         <v>342</v>
@@ -28510,21 +28504,21 @@
         <v>0</v>
       </c>
       <c r="AC363" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AH363" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI363" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="364" spans="1:35">
       <c r="A364">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B364" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C364" t="s">
         <v>50</v>
@@ -28533,25 +28527,25 @@
         <v>51</v>
       </c>
       <c r="E364" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F364" t="s">
         <v>56</v>
       </c>
       <c r="G364">
-        <v>7026</v>
+        <v>1914</v>
       </c>
       <c r="H364">
-        <v>0</v>
+        <v>1862</v>
       </c>
       <c r="I364" t="s">
         <v>62</v>
       </c>
       <c r="J364" t="s">
-        <v>119</v>
+        <v>147</v>
       </c>
       <c r="N364" s="1">
-        <v>46288</v>
+        <v>46286</v>
       </c>
       <c r="P364">
         <v>8</v>
@@ -28560,45 +28554,45 @@
         <v>2026</v>
       </c>
       <c r="R364">
-        <v>18048473</v>
+        <v>17988591</v>
       </c>
       <c r="S364" t="s">
-        <v>181</v>
+        <v>180</v>
+      </c>
+      <c r="T364" t="s">
+        <v>193</v>
       </c>
       <c r="U364" t="s">
         <v>196</v>
       </c>
       <c r="V364" s="1">
-        <v>46282.74485532408</v>
+        <v>46283.39413969908</v>
       </c>
       <c r="W364">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="X364" t="s">
-        <v>199</v>
-      </c>
-      <c r="Y364" t="s">
-        <v>343</v>
+        <v>198</v>
       </c>
       <c r="AB364">
         <v>0</v>
       </c>
       <c r="AC364" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AH364" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI364" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="365" spans="1:35">
       <c r="A365">
-        <v>6548</v>
+        <v>5417</v>
       </c>
       <c r="B365" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C365" t="s">
         <v>50</v>
@@ -28613,19 +28607,22 @@
         <v>56</v>
       </c>
       <c r="G365">
-        <v>1914</v>
+        <v>6759</v>
       </c>
       <c r="H365">
-        <v>1862</v>
+        <v>1788</v>
       </c>
       <c r="I365" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J365" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N365" s="1">
-        <v>46286</v>
+        <v>46289</v>
+      </c>
+      <c r="O365" t="s">
+        <v>168</v>
       </c>
       <c r="P365">
         <v>8</v>
@@ -28634,45 +28631,48 @@
         <v>2026</v>
       </c>
       <c r="R365">
-        <v>17988591</v>
+        <v>17399190</v>
       </c>
       <c r="S365" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="T365" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="U365" t="s">
         <v>196</v>
       </c>
       <c r="V365" s="1">
-        <v>46283.39413969908</v>
+        <v>46283.54620269676</v>
       </c>
       <c r="W365">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="X365" t="s">
-        <v>198</v>
+        <v>204</v>
+      </c>
+      <c r="Y365" t="s">
+        <v>343</v>
       </c>
       <c r="AB365">
         <v>0</v>
       </c>
       <c r="AC365" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="AH365" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI365" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="366" spans="1:35">
       <c r="A366">
-        <v>5417</v>
+        <v>6704</v>
       </c>
       <c r="B366" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C366" t="s">
         <v>50</v>
@@ -28687,22 +28687,22 @@
         <v>56</v>
       </c>
       <c r="G366">
-        <v>6759</v>
+        <v>11874</v>
       </c>
       <c r="H366">
-        <v>1788</v>
+        <v>0</v>
       </c>
       <c r="I366" t="s">
         <v>63</v>
       </c>
       <c r="J366" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="N366" s="1">
-        <v>46289</v>
+        <v>46281</v>
       </c>
       <c r="O366" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="P366">
         <v>8</v>
@@ -28711,7 +28711,7 @@
         <v>2026</v>
       </c>
       <c r="R366">
-        <v>17399190</v>
+        <v>18273589</v>
       </c>
       <c r="S366" t="s">
         <v>185</v>
@@ -28720,16 +28720,16 @@
         <v>194</v>
       </c>
       <c r="U366" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="V366" s="1">
-        <v>46283.54620269676</v>
+        <v>46282.70138376157</v>
       </c>
       <c r="W366">
-        <v>-3</v>
+        <v>5</v>
       </c>
       <c r="X366" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Y366" t="s">
         <v>344</v>
@@ -28744,21 +28744,21 @@
         <v>378</v>
       </c>
       <c r="AI366" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="367" spans="1:35">
       <c r="A367">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B367" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C367" t="s">
         <v>50</v>
       </c>
       <c r="D367" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E367" t="s">
         <v>54</v>
@@ -28791,7 +28791,7 @@
         <v>2026</v>
       </c>
       <c r="R367">
-        <v>18273589</v>
+        <v>18239293</v>
       </c>
       <c r="S367" t="s">
         <v>185</v>
@@ -28803,7 +28803,7 @@
         <v>195</v>
       </c>
       <c r="V367" s="1">
-        <v>46282.70138376157</v>
+        <v>46282.7013840625</v>
       </c>
       <c r="W367">
         <v>5</v>
@@ -28812,7 +28812,7 @@
         <v>203</v>
       </c>
       <c r="Y367" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AB367">
         <v>0</v>
@@ -28821,24 +28821,24 @@
         <v>185</v>
       </c>
       <c r="AH367" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI367" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="368" spans="1:35">
       <c r="A368">
-        <v>6705</v>
+        <v>6703</v>
       </c>
       <c r="B368" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C368" t="s">
         <v>50</v>
       </c>
       <c r="D368" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E368" t="s">
         <v>54</v>
@@ -28847,7 +28847,7 @@
         <v>56</v>
       </c>
       <c r="G368">
-        <v>11874</v>
+        <v>1802</v>
       </c>
       <c r="H368">
         <v>0</v>
@@ -28856,13 +28856,10 @@
         <v>63</v>
       </c>
       <c r="J368" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="N368" s="1">
-        <v>46281</v>
-      </c>
-      <c r="O368" t="s">
-        <v>164</v>
+        <v>46283</v>
       </c>
       <c r="P368">
         <v>8</v>
@@ -28871,7 +28868,7 @@
         <v>2026</v>
       </c>
       <c r="R368">
-        <v>18239293</v>
+        <v>17948796</v>
       </c>
       <c r="S368" t="s">
         <v>185</v>
@@ -28880,16 +28877,16 @@
         <v>194</v>
       </c>
       <c r="U368" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="V368" s="1">
-        <v>46282.7013840625</v>
+        <v>46283.75077045139</v>
       </c>
       <c r="W368">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X368" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="Y368" t="s">
         <v>345</v>
@@ -28901,24 +28898,24 @@
         <v>185</v>
       </c>
       <c r="AH368" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI368" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="369" spans="1:35">
       <c r="A369">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B369" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C369" t="s">
         <v>50</v>
       </c>
       <c r="D369" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E369" t="s">
         <v>54</v>
@@ -28941,6 +28938,9 @@
       <c r="N369" s="1">
         <v>46283</v>
       </c>
+      <c r="O369" t="s">
+        <v>169</v>
+      </c>
       <c r="P369">
         <v>8</v>
       </c>
@@ -28948,7 +28948,7 @@
         <v>2026</v>
       </c>
       <c r="R369">
-        <v>17948796</v>
+        <v>18085198</v>
       </c>
       <c r="S369" t="s">
         <v>185</v>
@@ -28957,16 +28957,16 @@
         <v>194</v>
       </c>
       <c r="U369" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="V369" s="1">
-        <v>46283.75077045139</v>
+        <v>46286.36164050926</v>
       </c>
       <c r="W369">
         <v>3</v>
       </c>
       <c r="X369" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="Y369" t="s">
         <v>346</v>
@@ -28978,7 +28978,7 @@
         <v>185</v>
       </c>
       <c r="AH369" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI369" t="s">
         <v>383</v>
@@ -28986,10 +28986,10 @@
     </row>
     <row r="370" spans="1:35">
       <c r="A370">
-        <v>6704</v>
+        <v>5417</v>
       </c>
       <c r="B370" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C370" t="s">
         <v>50</v>
@@ -29004,7 +29004,7 @@
         <v>56</v>
       </c>
       <c r="G370">
-        <v>1802</v>
+        <v>11286</v>
       </c>
       <c r="H370">
         <v>0</v>
@@ -29013,7 +29013,7 @@
         <v>63</v>
       </c>
       <c r="J370" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="N370" s="1">
         <v>46283</v>
@@ -29028,7 +29028,7 @@
         <v>2026</v>
       </c>
       <c r="R370">
-        <v>18085198</v>
+        <v>17399434</v>
       </c>
       <c r="S370" t="s">
         <v>185</v>
@@ -29040,16 +29040,16 @@
         <v>195</v>
       </c>
       <c r="V370" s="1">
-        <v>46286.36164050926</v>
+        <v>46286.36164494213</v>
       </c>
       <c r="W370">
         <v>3</v>
       </c>
       <c r="X370" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Y370" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AB370">
         <v>0</v>
@@ -29058,24 +29058,24 @@
         <v>185</v>
       </c>
       <c r="AH370" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI370" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="371" spans="1:35">
       <c r="A371">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B371" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C371" t="s">
         <v>50</v>
       </c>
       <c r="D371" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E371" t="s">
         <v>54</v>
@@ -29108,7 +29108,7 @@
         <v>2026</v>
       </c>
       <c r="R371">
-        <v>17399434</v>
+        <v>16962464</v>
       </c>
       <c r="S371" t="s">
         <v>185</v>
@@ -29120,16 +29120,16 @@
         <v>195</v>
       </c>
       <c r="V371" s="1">
-        <v>46286.36164494213</v>
+        <v>46286.36164826389</v>
       </c>
       <c r="W371">
         <v>3</v>
       </c>
       <c r="X371" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="Y371" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AB371">
         <v>0</v>
@@ -29138,24 +29138,24 @@
         <v>185</v>
       </c>
       <c r="AH371" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI371" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="372" spans="1:35">
       <c r="A372">
-        <v>6404</v>
+        <v>6705</v>
       </c>
       <c r="B372" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C372" t="s">
         <v>50</v>
       </c>
       <c r="D372" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E372" t="s">
         <v>54</v>
@@ -29164,7 +29164,7 @@
         <v>56</v>
       </c>
       <c r="G372">
-        <v>11286</v>
+        <v>1805</v>
       </c>
       <c r="H372">
         <v>0</v>
@@ -29173,14 +29173,11 @@
         <v>63</v>
       </c>
       <c r="J372" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="N372" s="1">
         <v>46283</v>
       </c>
-      <c r="O372" t="s">
-        <v>169</v>
-      </c>
       <c r="P372">
         <v>8</v>
       </c>
@@ -29188,7 +29185,7 @@
         <v>2026</v>
       </c>
       <c r="R372">
-        <v>16962464</v>
+        <v>17948948</v>
       </c>
       <c r="S372" t="s">
         <v>185</v>
@@ -29197,16 +29194,16 @@
         <v>194</v>
       </c>
       <c r="U372" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="V372" s="1">
-        <v>46286.36164826389</v>
+        <v>46283.35452896991</v>
       </c>
       <c r="W372">
         <v>3</v>
       </c>
       <c r="X372" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="Y372" t="s">
         <v>347</v>
@@ -29218,18 +29215,18 @@
         <v>185</v>
       </c>
       <c r="AH372" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI372" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="373" spans="1:35">
       <c r="A373">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B373" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C373" t="s">
         <v>50</v>
@@ -29265,7 +29262,7 @@
         <v>2026</v>
       </c>
       <c r="R373">
-        <v>17948948</v>
+        <v>18084966</v>
       </c>
       <c r="S373" t="s">
         <v>185</v>
@@ -29277,7 +29274,7 @@
         <v>197</v>
       </c>
       <c r="V373" s="1">
-        <v>46283.35452896991</v>
+        <v>46283.35453171296</v>
       </c>
       <c r="W373">
         <v>3</v>
@@ -29286,7 +29283,7 @@
         <v>203</v>
       </c>
       <c r="Y373" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AB373">
         <v>0</v>
@@ -29295,24 +29292,24 @@
         <v>185</v>
       </c>
       <c r="AH373" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI373" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="374" spans="1:35">
       <c r="A374">
-        <v>6779</v>
+        <v>5417</v>
       </c>
       <c r="B374" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C374" t="s">
         <v>50</v>
       </c>
       <c r="D374" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E374" t="s">
         <v>54</v>
@@ -29321,7 +29318,7 @@
         <v>56</v>
       </c>
       <c r="G374">
-        <v>1805</v>
+        <v>7025</v>
       </c>
       <c r="H374">
         <v>0</v>
@@ -29330,10 +29327,10 @@
         <v>63</v>
       </c>
       <c r="J374" t="s">
-        <v>145</v>
+        <v>119</v>
       </c>
       <c r="N374" s="1">
-        <v>46283</v>
+        <v>46288</v>
       </c>
       <c r="P374">
         <v>8</v>
@@ -29342,7 +29339,7 @@
         <v>2026</v>
       </c>
       <c r="R374">
-        <v>18084966</v>
+        <v>17399280</v>
       </c>
       <c r="S374" t="s">
         <v>185</v>
@@ -29351,16 +29348,16 @@
         <v>194</v>
       </c>
       <c r="U374" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="V374" s="1">
-        <v>46283.35453171296</v>
+        <v>46283.38367943287</v>
       </c>
       <c r="W374">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="X374" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Y374" t="s">
         <v>348</v>
@@ -29372,24 +29369,24 @@
         <v>185</v>
       </c>
       <c r="AH374" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="AI374" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="375" spans="1:35">
       <c r="A375">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B375" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C375" t="s">
         <v>50</v>
       </c>
       <c r="D375" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E375" t="s">
         <v>54</v>
@@ -29419,7 +29416,7 @@
         <v>2026</v>
       </c>
       <c r="R375">
-        <v>17399280</v>
+        <v>16962338</v>
       </c>
       <c r="S375" t="s">
         <v>185</v>
@@ -29431,13 +29428,13 @@
         <v>196</v>
       </c>
       <c r="V375" s="1">
-        <v>46283.38367943287</v>
+        <v>46282.54038741898</v>
       </c>
       <c r="W375">
         <v>-2</v>
       </c>
       <c r="X375" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="Y375" t="s">
         <v>349</v>
@@ -29449,45 +29446,48 @@
         <v>185</v>
       </c>
       <c r="AH375" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI375" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="376" spans="1:35">
       <c r="A376">
-        <v>6404</v>
+        <v>6628</v>
       </c>
       <c r="B376" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="C376" t="s">
         <v>50</v>
       </c>
       <c r="D376" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E376" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F376" t="s">
         <v>56</v>
       </c>
       <c r="G376">
-        <v>7025</v>
+        <v>945</v>
       </c>
       <c r="H376">
         <v>0</v>
       </c>
       <c r="I376" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J376" t="s">
-        <v>119</v>
+        <v>149</v>
       </c>
       <c r="N376" s="1">
-        <v>46288</v>
+        <v>46283</v>
+      </c>
+      <c r="O376" t="s">
+        <v>163</v>
       </c>
       <c r="P376">
         <v>8</v>
@@ -29496,25 +29496,22 @@
         <v>2026</v>
       </c>
       <c r="R376">
-        <v>16962338</v>
+        <v>16959938</v>
       </c>
       <c r="S376" t="s">
-        <v>185</v>
-      </c>
-      <c r="T376" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="U376" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="V376" s="1">
-        <v>46282.54038741898</v>
+        <v>46283.64213659722</v>
       </c>
       <c r="W376">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="X376" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="Y376" t="s">
         <v>350</v>
@@ -29523,21 +29520,21 @@
         <v>0</v>
       </c>
       <c r="AC376" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AH376" t="s">
         <v>378</v>
       </c>
       <c r="AI376" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="377" spans="1:35">
       <c r="A377">
-        <v>6628</v>
+        <v>6705</v>
       </c>
       <c r="B377" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C377" t="s">
         <v>50</v>
@@ -29546,7 +29543,7 @@
         <v>52</v>
       </c>
       <c r="E377" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F377" t="s">
         <v>56</v>
@@ -29576,7 +29573,7 @@
         <v>2026</v>
       </c>
       <c r="R377">
-        <v>16959938</v>
+        <v>17952524</v>
       </c>
       <c r="S377" t="s">
         <v>186</v>
@@ -29585,13 +29582,13 @@
         <v>197</v>
       </c>
       <c r="V377" s="1">
-        <v>46283.64213659722</v>
+        <v>46283.65291121528</v>
       </c>
       <c r="W377">
         <v>3</v>
       </c>
       <c r="X377" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="Y377" t="s">
         <v>351</v>
@@ -29603,18 +29600,18 @@
         <v>186</v>
       </c>
       <c r="AH377" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI377" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="378" spans="1:35">
       <c r="A378">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B378" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C378" t="s">
         <v>50</v>
@@ -29653,7 +29650,7 @@
         <v>2026</v>
       </c>
       <c r="R378">
-        <v>17952524</v>
+        <v>18056695</v>
       </c>
       <c r="S378" t="s">
         <v>186</v>
@@ -29662,7 +29659,7 @@
         <v>197</v>
       </c>
       <c r="V378" s="1">
-        <v>46283.65291121528</v>
+        <v>46283.65291194445</v>
       </c>
       <c r="W378">
         <v>3</v>
@@ -29671,7 +29668,7 @@
         <v>203</v>
       </c>
       <c r="Y378" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AB378">
         <v>0</v>
@@ -29680,18 +29677,18 @@
         <v>186</v>
       </c>
       <c r="AH378" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI378" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="379" spans="1:35">
       <c r="A379">
-        <v>6779</v>
+        <v>6945</v>
       </c>
       <c r="B379" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C379" t="s">
         <v>50</v>
@@ -29703,7 +29700,7 @@
         <v>54</v>
       </c>
       <c r="F379" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G379">
         <v>945</v>
@@ -29721,7 +29718,7 @@
         <v>46283</v>
       </c>
       <c r="O379" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="P379">
         <v>8</v>
@@ -29730,22 +29727,22 @@
         <v>2026</v>
       </c>
       <c r="R379">
-        <v>18056695</v>
+        <v>18164487</v>
       </c>
       <c r="S379" t="s">
         <v>186</v>
       </c>
       <c r="U379" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="V379" s="1">
-        <v>46283.65291194445</v>
+        <v>46286.39955256944</v>
       </c>
       <c r="W379">
         <v>3</v>
       </c>
       <c r="X379" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="Y379" t="s">
         <v>352</v>
@@ -29757,7 +29754,7 @@
         <v>186</v>
       </c>
       <c r="AH379" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI379" t="s">
         <v>383</v>
@@ -29765,25 +29762,25 @@
     </row>
     <row r="380" spans="1:35">
       <c r="A380">
-        <v>6945</v>
+        <v>5417</v>
       </c>
       <c r="B380" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C380" t="s">
         <v>50</v>
       </c>
       <c r="D380" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E380" t="s">
         <v>54</v>
       </c>
       <c r="F380" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G380">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="H380">
         <v>0</v>
@@ -29792,14 +29789,11 @@
         <v>64</v>
       </c>
       <c r="J380" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N380" s="1">
         <v>46283</v>
       </c>
-      <c r="O380" t="s">
-        <v>169</v>
-      </c>
       <c r="P380">
         <v>8</v>
       </c>
@@ -29807,7 +29801,7 @@
         <v>2026</v>
       </c>
       <c r="R380">
-        <v>18164487</v>
+        <v>17398869</v>
       </c>
       <c r="S380" t="s">
         <v>186</v>
@@ -29816,13 +29810,13 @@
         <v>195</v>
       </c>
       <c r="V380" s="1">
-        <v>46286.39955256944</v>
+        <v>46286.42397924769</v>
       </c>
       <c r="W380">
         <v>3</v>
       </c>
       <c r="X380" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Y380" t="s">
         <v>353</v>
@@ -29834,24 +29828,24 @@
         <v>186</v>
       </c>
       <c r="AH380" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI380" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="381" spans="1:35">
       <c r="A381">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B381" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C381" t="s">
         <v>50</v>
       </c>
       <c r="D381" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E381" t="s">
         <v>54</v>
@@ -29881,7 +29875,7 @@
         <v>2026</v>
       </c>
       <c r="R381">
-        <v>17398869</v>
+        <v>16962093</v>
       </c>
       <c r="S381" t="s">
         <v>186</v>
@@ -29890,16 +29884,16 @@
         <v>195</v>
       </c>
       <c r="V381" s="1">
-        <v>46286.42397924769</v>
+        <v>46286.42389136574</v>
       </c>
       <c r="W381">
         <v>3</v>
       </c>
       <c r="X381" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="Y381" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AB381">
         <v>0</v>
@@ -29908,27 +29902,27 @@
         <v>186</v>
       </c>
       <c r="AH381" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI381" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="382" spans="1:35">
       <c r="A382">
-        <v>6404</v>
+        <v>6627</v>
       </c>
       <c r="B382" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C382" t="s">
         <v>50</v>
       </c>
       <c r="D382" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E382" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F382" t="s">
         <v>56</v>
@@ -29948,6 +29942,9 @@
       <c r="N382" s="1">
         <v>46283</v>
       </c>
+      <c r="O382" t="s">
+        <v>163</v>
+      </c>
       <c r="P382">
         <v>8</v>
       </c>
@@ -29955,25 +29952,25 @@
         <v>2026</v>
       </c>
       <c r="R382">
-        <v>16962093</v>
+        <v>17042272</v>
       </c>
       <c r="S382" t="s">
         <v>186</v>
       </c>
       <c r="U382" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="V382" s="1">
-        <v>46286.42389136574</v>
+        <v>46283.67999300926</v>
       </c>
       <c r="W382">
         <v>3</v>
       </c>
       <c r="X382" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="Y382" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="AB382">
         <v>0</v>
@@ -29982,27 +29979,27 @@
         <v>186</v>
       </c>
       <c r="AH382" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI382" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="383" spans="1:35">
       <c r="A383">
-        <v>6627</v>
+        <v>6703</v>
       </c>
       <c r="B383" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C383" t="s">
         <v>50</v>
       </c>
       <c r="D383" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E383" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F383" t="s">
         <v>56</v>
@@ -30023,7 +30020,7 @@
         <v>46283</v>
       </c>
       <c r="O383" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="P383">
         <v>8</v>
@@ -30032,25 +30029,25 @@
         <v>2026</v>
       </c>
       <c r="R383">
-        <v>17042272</v>
+        <v>17941132</v>
       </c>
       <c r="S383" t="s">
         <v>186</v>
       </c>
       <c r="U383" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="V383" s="1">
-        <v>46283.67999300926</v>
+        <v>46286.42398471065</v>
       </c>
       <c r="W383">
         <v>3</v>
       </c>
       <c r="X383" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="Y383" t="s">
-        <v>310</v>
+        <v>354</v>
       </c>
       <c r="AB383">
         <v>0</v>
@@ -30059,7 +30056,7 @@
         <v>186</v>
       </c>
       <c r="AH383" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI383" t="s">
         <v>383</v>
@@ -30067,16 +30064,16 @@
     </row>
     <row r="384" spans="1:35">
       <c r="A384">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B384" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C384" t="s">
         <v>50</v>
       </c>
       <c r="D384" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E384" t="s">
         <v>54</v>
@@ -30099,9 +30096,6 @@
       <c r="N384" s="1">
         <v>46283</v>
       </c>
-      <c r="O384" t="s">
-        <v>169</v>
-      </c>
       <c r="P384">
         <v>8</v>
       </c>
@@ -30109,7 +30103,7 @@
         <v>2026</v>
       </c>
       <c r="R384">
-        <v>17941132</v>
+        <v>17952325</v>
       </c>
       <c r="S384" t="s">
         <v>186</v>
@@ -30118,13 +30112,13 @@
         <v>195</v>
       </c>
       <c r="V384" s="1">
-        <v>46286.42398471065</v>
+        <v>46286.42398568287</v>
       </c>
       <c r="W384">
         <v>3</v>
       </c>
       <c r="X384" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="Y384" t="s">
         <v>355</v>
@@ -30136,30 +30130,30 @@
         <v>186</v>
       </c>
       <c r="AH384" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI384" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="385" spans="1:35">
       <c r="A385">
-        <v>6704</v>
+        <v>6945</v>
       </c>
       <c r="B385" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C385" t="s">
         <v>50</v>
       </c>
       <c r="D385" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E385" t="s">
         <v>54</v>
       </c>
       <c r="F385" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G385">
         <v>946</v>
@@ -30176,6 +30170,9 @@
       <c r="N385" s="1">
         <v>46283</v>
       </c>
+      <c r="O385" t="s">
+        <v>163</v>
+      </c>
       <c r="P385">
         <v>8</v>
       </c>
@@ -30183,25 +30180,25 @@
         <v>2026</v>
       </c>
       <c r="R385">
-        <v>17952325</v>
+        <v>18164494</v>
       </c>
       <c r="S385" t="s">
         <v>186</v>
       </c>
       <c r="U385" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="V385" s="1">
-        <v>46286.42398568287</v>
+        <v>46283.67625043981</v>
       </c>
       <c r="W385">
         <v>3</v>
       </c>
       <c r="X385" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="Y385" t="s">
-        <v>356</v>
+        <v>310</v>
       </c>
       <c r="AB385">
         <v>0</v>
@@ -30210,18 +30207,18 @@
         <v>186</v>
       </c>
       <c r="AH385" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI385" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="386" spans="1:35">
       <c r="A386">
-        <v>6945</v>
+        <v>6705</v>
       </c>
       <c r="B386" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C386" t="s">
         <v>50</v>
@@ -30233,10 +30230,10 @@
         <v>54</v>
       </c>
       <c r="F386" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G386">
-        <v>946</v>
+        <v>7022</v>
       </c>
       <c r="H386">
         <v>0</v>
@@ -30245,7 +30242,7 @@
         <v>64</v>
       </c>
       <c r="J386" t="s">
-        <v>150</v>
+        <v>113</v>
       </c>
       <c r="N386" s="1">
         <v>46283</v>
@@ -30260,7 +30257,7 @@
         <v>2026</v>
       </c>
       <c r="R386">
-        <v>18164494</v>
+        <v>17952601</v>
       </c>
       <c r="S386" t="s">
         <v>186</v>
@@ -30269,13 +30266,13 @@
         <v>197</v>
       </c>
       <c r="V386" s="1">
-        <v>46283.67625043981</v>
+        <v>46283.38329579861</v>
       </c>
       <c r="W386">
         <v>3</v>
       </c>
       <c r="X386" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Y386" t="s">
         <v>310</v>
@@ -30287,24 +30284,24 @@
         <v>186</v>
       </c>
       <c r="AH386" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AI386" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="387" spans="1:35">
       <c r="A387">
-        <v>6705</v>
+        <v>5417</v>
       </c>
       <c r="B387" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C387" t="s">
         <v>50</v>
       </c>
       <c r="D387" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E387" t="s">
         <v>54</v>
@@ -30313,7 +30310,7 @@
         <v>56</v>
       </c>
       <c r="G387">
-        <v>7022</v>
+        <v>9086</v>
       </c>
       <c r="H387">
         <v>0</v>
@@ -30322,22 +30319,22 @@
         <v>64</v>
       </c>
       <c r="J387" t="s">
-        <v>113</v>
+        <v>151</v>
       </c>
       <c r="N387" s="1">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="O387" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P387">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q387">
         <v>2026</v>
       </c>
       <c r="R387">
-        <v>17952601</v>
+        <v>17399363</v>
       </c>
       <c r="S387" t="s">
         <v>186</v>
@@ -30346,16 +30343,16 @@
         <v>197</v>
       </c>
       <c r="V387" s="1">
-        <v>46283.38329579861</v>
+        <v>46282.36440621527</v>
       </c>
       <c r="W387">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X387" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Y387" t="s">
-        <v>310</v>
+        <v>356</v>
       </c>
       <c r="AB387">
         <v>0</v>
@@ -30367,21 +30364,21 @@
         <v>379</v>
       </c>
       <c r="AI387" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="388" spans="1:35">
       <c r="A388">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B388" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C388" t="s">
         <v>50</v>
       </c>
       <c r="D388" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E388" t="s">
         <v>54</v>
@@ -30414,7 +30411,7 @@
         <v>2026</v>
       </c>
       <c r="R388">
-        <v>17399363</v>
+        <v>16962380</v>
       </c>
       <c r="S388" t="s">
         <v>186</v>
@@ -30423,16 +30420,16 @@
         <v>197</v>
       </c>
       <c r="V388" s="1">
-        <v>46282.36440621527</v>
+        <v>46282.36462596065</v>
       </c>
       <c r="W388">
         <v>4</v>
       </c>
       <c r="X388" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="Y388" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AB388">
         <v>0</v>
@@ -30441,24 +30438,24 @@
         <v>186</v>
       </c>
       <c r="AH388" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI388" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="389" spans="1:35">
       <c r="A389">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B389" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C389" t="s">
         <v>50</v>
       </c>
       <c r="D389" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E389" t="s">
         <v>54</v>
@@ -30491,7 +30488,7 @@
         <v>2026</v>
       </c>
       <c r="R389">
-        <v>16962380</v>
+        <v>16976270</v>
       </c>
       <c r="S389" t="s">
         <v>186</v>
@@ -30500,16 +30497,16 @@
         <v>197</v>
       </c>
       <c r="V389" s="1">
-        <v>46282.36462596065</v>
+        <v>46282.36464421296</v>
       </c>
       <c r="W389">
         <v>4</v>
       </c>
       <c r="X389" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="Y389" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AB389">
         <v>0</v>
@@ -30518,18 +30515,18 @@
         <v>186</v>
       </c>
       <c r="AH389" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI389" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="390" spans="1:35">
       <c r="A390">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B390" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="C390" t="s">
         <v>50</v>
@@ -30568,7 +30565,7 @@
         <v>2026</v>
       </c>
       <c r="R390">
-        <v>16976270</v>
+        <v>17222865</v>
       </c>
       <c r="S390" t="s">
         <v>186</v>
@@ -30577,16 +30574,16 @@
         <v>197</v>
       </c>
       <c r="V390" s="1">
-        <v>46282.36464421296</v>
+        <v>46282.36467337963</v>
       </c>
       <c r="W390">
         <v>4</v>
       </c>
       <c r="X390" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="Y390" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AB390">
         <v>0</v>
@@ -30595,18 +30592,18 @@
         <v>186</v>
       </c>
       <c r="AH390" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI390" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="391" spans="1:35">
       <c r="A391">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B391" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C391" t="s">
         <v>50</v>
@@ -30615,7 +30612,7 @@
         <v>51</v>
       </c>
       <c r="E391" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F391" t="s">
         <v>56</v>
@@ -30645,7 +30642,7 @@
         <v>2026</v>
       </c>
       <c r="R391">
-        <v>17222865</v>
+        <v>17042587</v>
       </c>
       <c r="S391" t="s">
         <v>186</v>
@@ -30654,16 +30651,16 @@
         <v>197</v>
       </c>
       <c r="V391" s="1">
-        <v>46282.36467337963</v>
+        <v>46282.36469679398</v>
       </c>
       <c r="W391">
         <v>4</v>
       </c>
       <c r="X391" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Y391" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AB391">
         <v>0</v>
@@ -30672,24 +30669,24 @@
         <v>186</v>
       </c>
       <c r="AH391" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI391" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="392" spans="1:35">
       <c r="A392">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B392" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C392" t="s">
         <v>50</v>
       </c>
       <c r="D392" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E392" t="s">
         <v>55</v>
@@ -30722,7 +30719,7 @@
         <v>2026</v>
       </c>
       <c r="R392">
-        <v>17042587</v>
+        <v>16960074</v>
       </c>
       <c r="S392" t="s">
         <v>186</v>
@@ -30731,7 +30728,7 @@
         <v>197</v>
       </c>
       <c r="V392" s="1">
-        <v>46282.36469679398</v>
+        <v>46282.36469869213</v>
       </c>
       <c r="W392">
         <v>4</v>
@@ -30740,7 +30737,7 @@
         <v>199</v>
       </c>
       <c r="Y392" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AB392">
         <v>0</v>
@@ -30749,27 +30746,27 @@
         <v>186</v>
       </c>
       <c r="AH392" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI392" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="393" spans="1:35">
       <c r="A393">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B393" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C393" t="s">
         <v>50</v>
       </c>
       <c r="D393" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E393" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F393" t="s">
         <v>56</v>
@@ -30799,7 +30796,7 @@
         <v>2026</v>
       </c>
       <c r="R393">
-        <v>16960074</v>
+        <v>17941217</v>
       </c>
       <c r="S393" t="s">
         <v>186</v>
@@ -30808,16 +30805,16 @@
         <v>197</v>
       </c>
       <c r="V393" s="1">
-        <v>46282.36469869213</v>
+        <v>46282.36473159722</v>
       </c>
       <c r="W393">
         <v>4</v>
       </c>
       <c r="X393" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="Y393" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AB393">
         <v>0</v>
@@ -30826,24 +30823,24 @@
         <v>186</v>
       </c>
       <c r="AH393" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI393" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="394" spans="1:35">
       <c r="A394">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B394" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C394" t="s">
         <v>50</v>
       </c>
       <c r="D394" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E394" t="s">
         <v>54</v>
@@ -30876,7 +30873,7 @@
         <v>2026</v>
       </c>
       <c r="R394">
-        <v>17941217</v>
+        <v>17952444</v>
       </c>
       <c r="S394" t="s">
         <v>186</v>
@@ -30885,16 +30882,16 @@
         <v>197</v>
       </c>
       <c r="V394" s="1">
-        <v>46282.36473159722</v>
+        <v>46282.36473394676</v>
       </c>
       <c r="W394">
         <v>4</v>
       </c>
       <c r="X394" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="Y394" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AB394">
         <v>0</v>
@@ -30903,24 +30900,24 @@
         <v>186</v>
       </c>
       <c r="AH394" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI394" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="395" spans="1:35">
       <c r="A395">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B395" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C395" t="s">
         <v>50</v>
       </c>
       <c r="D395" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E395" t="s">
         <v>54</v>
@@ -30953,7 +30950,7 @@
         <v>2026</v>
       </c>
       <c r="R395">
-        <v>17952444</v>
+        <v>17952624</v>
       </c>
       <c r="S395" t="s">
         <v>186</v>
@@ -30962,7 +30959,7 @@
         <v>197</v>
       </c>
       <c r="V395" s="1">
-        <v>46282.36473394676</v>
+        <v>46282.36473579861</v>
       </c>
       <c r="W395">
         <v>4</v>
@@ -30971,7 +30968,7 @@
         <v>203</v>
       </c>
       <c r="Y395" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AB395">
         <v>0</v>
@@ -30980,18 +30977,18 @@
         <v>186</v>
       </c>
       <c r="AH395" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI395" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="396" spans="1:35">
       <c r="A396">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B396" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C396" t="s">
         <v>50</v>
@@ -31030,7 +31027,7 @@
         <v>2026</v>
       </c>
       <c r="R396">
-        <v>17952624</v>
+        <v>18056801</v>
       </c>
       <c r="S396" t="s">
         <v>186</v>
@@ -31039,7 +31036,7 @@
         <v>197</v>
       </c>
       <c r="V396" s="1">
-        <v>46282.36473579861</v>
+        <v>46282.36475297454</v>
       </c>
       <c r="W396">
         <v>4</v>
@@ -31048,7 +31045,7 @@
         <v>203</v>
       </c>
       <c r="Y396" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AB396">
         <v>0</v>
@@ -31057,18 +31054,18 @@
         <v>186</v>
       </c>
       <c r="AH396" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI396" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="397" spans="1:35">
       <c r="A397">
-        <v>6779</v>
+        <v>6945</v>
       </c>
       <c r="B397" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C397" t="s">
         <v>50</v>
@@ -31080,7 +31077,7 @@
         <v>54</v>
       </c>
       <c r="F397" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G397">
         <v>9086</v>
@@ -31107,7 +31104,7 @@
         <v>2026</v>
       </c>
       <c r="R397">
-        <v>18056801</v>
+        <v>18164551</v>
       </c>
       <c r="S397" t="s">
         <v>186</v>
@@ -31116,16 +31113,16 @@
         <v>197</v>
       </c>
       <c r="V397" s="1">
-        <v>46282.36475297454</v>
+        <v>46282.36486408565</v>
       </c>
       <c r="W397">
         <v>4</v>
       </c>
       <c r="X397" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="Y397" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AB397">
         <v>0</v>
@@ -31134,24 +31131,24 @@
         <v>186</v>
       </c>
       <c r="AH397" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI397" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="398" spans="1:35">
       <c r="A398">
-        <v>6945</v>
+        <v>6949</v>
       </c>
       <c r="B398" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C398" t="s">
         <v>50</v>
       </c>
       <c r="D398" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E398" t="s">
         <v>54</v>
@@ -31184,7 +31181,7 @@
         <v>2026</v>
       </c>
       <c r="R398">
-        <v>18164551</v>
+        <v>18178187</v>
       </c>
       <c r="S398" t="s">
         <v>186</v>
@@ -31193,13 +31190,13 @@
         <v>197</v>
       </c>
       <c r="V398" s="1">
-        <v>46282.36486408565</v>
+        <v>46282.36487561343</v>
       </c>
       <c r="W398">
         <v>4</v>
       </c>
       <c r="X398" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Y398" t="s">
         <v>357</v>
@@ -31211,24 +31208,24 @@
         <v>186</v>
       </c>
       <c r="AH398" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI398" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="399" spans="1:35">
       <c r="A399">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B399" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C399" t="s">
         <v>50</v>
       </c>
       <c r="D399" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E399" t="s">
         <v>54</v>
@@ -31261,7 +31258,7 @@
         <v>2026</v>
       </c>
       <c r="R399">
-        <v>18178187</v>
+        <v>18188774</v>
       </c>
       <c r="S399" t="s">
         <v>186</v>
@@ -31270,16 +31267,16 @@
         <v>197</v>
       </c>
       <c r="V399" s="1">
-        <v>46282.36487561343</v>
+        <v>46282.36486778935</v>
       </c>
       <c r="W399">
         <v>4</v>
       </c>
       <c r="X399" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Y399" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="AB399">
         <v>0</v>
@@ -31288,18 +31285,18 @@
         <v>186</v>
       </c>
       <c r="AH399" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI399" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="400" spans="1:35">
       <c r="A400">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B400" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C400" t="s">
         <v>50</v>
@@ -31338,7 +31335,7 @@
         <v>2026</v>
       </c>
       <c r="R400">
-        <v>18188774</v>
+        <v>18188680</v>
       </c>
       <c r="S400" t="s">
         <v>186</v>
@@ -31347,7 +31344,7 @@
         <v>197</v>
       </c>
       <c r="V400" s="1">
-        <v>46282.36486778935</v>
+        <v>46282.36486851852</v>
       </c>
       <c r="W400">
         <v>4</v>
@@ -31356,7 +31353,7 @@
         <v>202</v>
       </c>
       <c r="Y400" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AB400">
         <v>0</v>
@@ -31365,33 +31362,33 @@
         <v>186</v>
       </c>
       <c r="AH400" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI400" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="401" spans="1:35">
       <c r="A401">
-        <v>6963</v>
+        <v>5417</v>
       </c>
       <c r="B401" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C401" t="s">
         <v>50</v>
       </c>
       <c r="D401" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E401" t="s">
         <v>54</v>
       </c>
       <c r="F401" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G401">
-        <v>9086</v>
+        <v>940</v>
       </c>
       <c r="H401">
         <v>0</v>
@@ -31400,13 +31397,13 @@
         <v>64</v>
       </c>
       <c r="J401" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="N401" s="1">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="O401" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="P401">
         <v>9</v>
@@ -31415,25 +31412,25 @@
         <v>2026</v>
       </c>
       <c r="R401">
-        <v>18188680</v>
+        <v>17398840</v>
       </c>
       <c r="S401" t="s">
         <v>186</v>
       </c>
       <c r="U401" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="V401" s="1">
-        <v>46282.36486851852</v>
+        <v>46286.45925082176</v>
       </c>
       <c r="W401">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X401" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Y401" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AB401">
         <v>0</v>
@@ -31442,7 +31439,7 @@
         <v>186</v>
       </c>
       <c r="AH401" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI401" t="s">
         <v>383</v>
@@ -31450,16 +31447,16 @@
     </row>
     <row r="402" spans="1:35">
       <c r="A402">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B402" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C402" t="s">
         <v>50</v>
       </c>
       <c r="D402" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E402" t="s">
         <v>54</v>
@@ -31483,7 +31480,7 @@
         <v>46283</v>
       </c>
       <c r="O402" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="P402">
         <v>9</v>
@@ -31492,22 +31489,22 @@
         <v>2026</v>
       </c>
       <c r="R402">
-        <v>17398840</v>
+        <v>16962074</v>
       </c>
       <c r="S402" t="s">
         <v>186</v>
       </c>
       <c r="U402" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="V402" s="1">
-        <v>46286.45925082176</v>
+        <v>46282.79619427084</v>
       </c>
       <c r="W402">
         <v>3</v>
       </c>
       <c r="X402" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="Y402" t="s">
         <v>359</v>
@@ -31519,24 +31516,24 @@
         <v>186</v>
       </c>
       <c r="AH402" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI402" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="403" spans="1:35">
       <c r="A403">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B403" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C403" t="s">
         <v>50</v>
       </c>
       <c r="D403" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E403" t="s">
         <v>54</v>
@@ -31569,7 +31566,7 @@
         <v>2026</v>
       </c>
       <c r="R403">
-        <v>16962074</v>
+        <v>16975871</v>
       </c>
       <c r="S403" t="s">
         <v>186</v>
@@ -31578,16 +31575,16 @@
         <v>196</v>
       </c>
       <c r="V403" s="1">
-        <v>46282.79619427084</v>
+        <v>46282.79620872685</v>
       </c>
       <c r="W403">
         <v>3</v>
       </c>
       <c r="X403" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="Y403" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AB403">
         <v>0</v>
@@ -31596,18 +31593,18 @@
         <v>186</v>
       </c>
       <c r="AH403" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI403" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="404" spans="1:35">
       <c r="A404">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B404" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="C404" t="s">
         <v>50</v>
@@ -31646,7 +31643,7 @@
         <v>2026</v>
       </c>
       <c r="R404">
-        <v>16975871</v>
+        <v>17222366</v>
       </c>
       <c r="S404" t="s">
         <v>186</v>
@@ -31655,16 +31652,16 @@
         <v>196</v>
       </c>
       <c r="V404" s="1">
-        <v>46282.79620872685</v>
+        <v>46282.79623825232</v>
       </c>
       <c r="W404">
         <v>3</v>
       </c>
       <c r="X404" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="Y404" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AB404">
         <v>0</v>
@@ -31673,18 +31670,18 @@
         <v>186</v>
       </c>
       <c r="AH404" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI404" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="405" spans="1:35">
       <c r="A405">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B405" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C405" t="s">
         <v>50</v>
@@ -31693,7 +31690,7 @@
         <v>51</v>
       </c>
       <c r="E405" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F405" t="s">
         <v>56</v>
@@ -31723,7 +31720,7 @@
         <v>2026</v>
       </c>
       <c r="R405">
-        <v>17222366</v>
+        <v>17042221</v>
       </c>
       <c r="S405" t="s">
         <v>186</v>
@@ -31732,16 +31729,16 @@
         <v>196</v>
       </c>
       <c r="V405" s="1">
-        <v>46282.79623825232</v>
+        <v>46282.7962541551</v>
       </c>
       <c r="W405">
         <v>3</v>
       </c>
       <c r="X405" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Y405" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AB405">
         <v>0</v>
@@ -31750,24 +31747,24 @@
         <v>186</v>
       </c>
       <c r="AH405" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI405" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="406" spans="1:35">
       <c r="A406">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B406" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C406" t="s">
         <v>50</v>
       </c>
       <c r="D406" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E406" t="s">
         <v>55</v>
@@ -31800,7 +31797,7 @@
         <v>2026</v>
       </c>
       <c r="R406">
-        <v>17042221</v>
+        <v>16959926</v>
       </c>
       <c r="S406" t="s">
         <v>186</v>
@@ -31809,7 +31806,7 @@
         <v>196</v>
       </c>
       <c r="V406" s="1">
-        <v>46282.7962541551</v>
+        <v>46282.7962703125</v>
       </c>
       <c r="W406">
         <v>3</v>
@@ -31818,7 +31815,7 @@
         <v>199</v>
       </c>
       <c r="Y406" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AB406">
         <v>0</v>
@@ -31827,27 +31824,27 @@
         <v>186</v>
       </c>
       <c r="AH406" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI406" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="407" spans="1:35">
       <c r="A407">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B407" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C407" t="s">
         <v>50</v>
       </c>
       <c r="D407" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E407" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F407" t="s">
         <v>56</v>
@@ -31877,7 +31874,7 @@
         <v>2026</v>
       </c>
       <c r="R407">
-        <v>16959926</v>
+        <v>17941112</v>
       </c>
       <c r="S407" t="s">
         <v>186</v>
@@ -31886,16 +31883,16 @@
         <v>196</v>
       </c>
       <c r="V407" s="1">
-        <v>46282.7962703125</v>
+        <v>46282.79628381944</v>
       </c>
       <c r="W407">
         <v>3</v>
       </c>
       <c r="X407" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="Y407" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AB407">
         <v>0</v>
@@ -31904,24 +31901,24 @@
         <v>186</v>
       </c>
       <c r="AH407" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI407" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="408" spans="1:35">
       <c r="A408">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B408" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C408" t="s">
         <v>50</v>
       </c>
       <c r="D408" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E408" t="s">
         <v>54</v>
@@ -31954,7 +31951,7 @@
         <v>2026</v>
       </c>
       <c r="R408">
-        <v>17941112</v>
+        <v>17952292</v>
       </c>
       <c r="S408" t="s">
         <v>186</v>
@@ -31963,16 +31960,16 @@
         <v>196</v>
       </c>
       <c r="V408" s="1">
-        <v>46282.79628381944</v>
+        <v>46282.79630119213</v>
       </c>
       <c r="W408">
         <v>3</v>
       </c>
       <c r="X408" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="Y408" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AB408">
         <v>0</v>
@@ -31981,24 +31978,24 @@
         <v>186</v>
       </c>
       <c r="AH408" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI408" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="409" spans="1:35">
       <c r="A409">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B409" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C409" t="s">
         <v>50</v>
       </c>
       <c r="D409" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E409" t="s">
         <v>54</v>
@@ -32031,7 +32028,7 @@
         <v>2026</v>
       </c>
       <c r="R409">
-        <v>17952292</v>
+        <v>17952491</v>
       </c>
       <c r="S409" t="s">
         <v>186</v>
@@ -32040,7 +32037,7 @@
         <v>196</v>
       </c>
       <c r="V409" s="1">
-        <v>46282.79630119213</v>
+        <v>46282.79631224537</v>
       </c>
       <c r="W409">
         <v>3</v>
@@ -32049,7 +32046,7 @@
         <v>203</v>
       </c>
       <c r="Y409" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AB409">
         <v>0</v>
@@ -32058,18 +32055,18 @@
         <v>186</v>
       </c>
       <c r="AH409" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI409" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="410" spans="1:35">
       <c r="A410">
-        <v>6705</v>
+        <v>6945</v>
       </c>
       <c r="B410" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="C410" t="s">
         <v>50</v>
@@ -32081,7 +32078,7 @@
         <v>54</v>
       </c>
       <c r="F410" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G410">
         <v>940</v>
@@ -32108,7 +32105,7 @@
         <v>2026</v>
       </c>
       <c r="R410">
-        <v>17952491</v>
+        <v>18164473</v>
       </c>
       <c r="S410" t="s">
         <v>186</v>
@@ -32117,13 +32114,13 @@
         <v>196</v>
       </c>
       <c r="V410" s="1">
-        <v>46282.79631224537</v>
+        <v>46282.79637734954</v>
       </c>
       <c r="W410">
         <v>3</v>
       </c>
       <c r="X410" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="Y410" t="s">
         <v>360</v>
@@ -32135,24 +32132,24 @@
         <v>186</v>
       </c>
       <c r="AH410" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI410" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="411" spans="1:35">
       <c r="A411">
-        <v>6945</v>
+        <v>6949</v>
       </c>
       <c r="B411" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C411" t="s">
         <v>50</v>
       </c>
       <c r="D411" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E411" t="s">
         <v>54</v>
@@ -32185,7 +32182,7 @@
         <v>2026</v>
       </c>
       <c r="R411">
-        <v>18164473</v>
+        <v>18178120</v>
       </c>
       <c r="S411" t="s">
         <v>186</v>
@@ -32194,16 +32191,16 @@
         <v>196</v>
       </c>
       <c r="V411" s="1">
-        <v>46282.79637734954</v>
+        <v>46282.79638922454</v>
       </c>
       <c r="W411">
         <v>3</v>
       </c>
       <c r="X411" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Y411" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AB411">
         <v>0</v>
@@ -32212,18 +32209,18 @@
         <v>186</v>
       </c>
       <c r="AH411" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI411" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="412" spans="1:35">
       <c r="A412">
-        <v>6949</v>
+        <v>5417</v>
       </c>
       <c r="B412" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C412" t="s">
         <v>50</v>
@@ -32235,19 +32232,19 @@
         <v>54</v>
       </c>
       <c r="F412" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G412">
-        <v>940</v>
+        <v>9088</v>
       </c>
       <c r="H412">
         <v>0</v>
       </c>
       <c r="I412" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J412" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N412" s="1">
         <v>46283</v>
@@ -32262,51 +32259,51 @@
         <v>2026</v>
       </c>
       <c r="R412">
-        <v>18178120</v>
+        <v>17399383</v>
       </c>
       <c r="S412" t="s">
-        <v>186</v>
+        <v>54</v>
       </c>
       <c r="U412" t="s">
         <v>196</v>
       </c>
       <c r="V412" s="1">
-        <v>46282.79638922454</v>
+        <v>46282.3651903588</v>
       </c>
       <c r="W412">
         <v>3</v>
       </c>
       <c r="X412" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="Y412" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AB412">
         <v>0</v>
       </c>
       <c r="AC412" t="s">
-        <v>186</v>
+        <v>54</v>
       </c>
       <c r="AH412" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI412" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="413" spans="1:35">
       <c r="A413">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B413" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C413" t="s">
         <v>50</v>
       </c>
       <c r="D413" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E413" t="s">
         <v>54</v>
@@ -32339,7 +32336,7 @@
         <v>2026</v>
       </c>
       <c r="R413">
-        <v>17399383</v>
+        <v>16962400</v>
       </c>
       <c r="S413" t="s">
         <v>54</v>
@@ -32348,16 +32345,16 @@
         <v>196</v>
       </c>
       <c r="V413" s="1">
-        <v>46282.3651903588</v>
+        <v>46282.36525856482</v>
       </c>
       <c r="W413">
         <v>3</v>
       </c>
       <c r="X413" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="Y413" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AB413">
         <v>0</v>
@@ -32366,24 +32363,24 @@
         <v>54</v>
       </c>
       <c r="AH413" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI413" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="414" spans="1:35">
       <c r="A414">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B414" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C414" t="s">
         <v>50</v>
       </c>
       <c r="D414" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E414" t="s">
         <v>54</v>
@@ -32416,7 +32413,7 @@
         <v>2026</v>
       </c>
       <c r="R414">
-        <v>16962400</v>
+        <v>16976290</v>
       </c>
       <c r="S414" t="s">
         <v>54</v>
@@ -32425,16 +32422,16 @@
         <v>196</v>
       </c>
       <c r="V414" s="1">
-        <v>46282.36525856482</v>
+        <v>46282.36526855324</v>
       </c>
       <c r="W414">
         <v>3</v>
       </c>
       <c r="X414" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="Y414" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AB414">
         <v>0</v>
@@ -32443,18 +32440,18 @@
         <v>54</v>
       </c>
       <c r="AH414" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI414" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="415" spans="1:35">
       <c r="A415">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B415" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="C415" t="s">
         <v>50</v>
@@ -32493,7 +32490,7 @@
         <v>2026</v>
       </c>
       <c r="R415">
-        <v>16976290</v>
+        <v>17222899</v>
       </c>
       <c r="S415" t="s">
         <v>54</v>
@@ -32502,16 +32499,16 @@
         <v>196</v>
       </c>
       <c r="V415" s="1">
-        <v>46282.36526855324</v>
+        <v>46282.36527959491</v>
       </c>
       <c r="W415">
         <v>3</v>
       </c>
       <c r="X415" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="Y415" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AB415">
         <v>0</v>
@@ -32520,18 +32517,18 @@
         <v>54</v>
       </c>
       <c r="AH415" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI415" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="416" spans="1:35">
       <c r="A416">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B416" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C416" t="s">
         <v>50</v>
@@ -32540,7 +32537,7 @@
         <v>51</v>
       </c>
       <c r="E416" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F416" t="s">
         <v>56</v>
@@ -32570,51 +32567,51 @@
         <v>2026</v>
       </c>
       <c r="R416">
-        <v>17222899</v>
+        <v>17042627</v>
       </c>
       <c r="S416" t="s">
-        <v>54</v>
+        <v>187</v>
       </c>
       <c r="U416" t="s">
         <v>196</v>
       </c>
       <c r="V416" s="1">
-        <v>46282.36527959491</v>
+        <v>46282.36528526621</v>
       </c>
       <c r="W416">
         <v>3</v>
       </c>
       <c r="X416" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Y416" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AB416">
         <v>0</v>
       </c>
       <c r="AC416" t="s">
-        <v>54</v>
+        <v>187</v>
       </c>
       <c r="AH416" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI416" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="417" spans="1:35">
       <c r="A417">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B417" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C417" t="s">
         <v>50</v>
       </c>
       <c r="D417" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E417" t="s">
         <v>55</v>
@@ -32647,16 +32644,16 @@
         <v>2026</v>
       </c>
       <c r="R417">
-        <v>17042627</v>
+        <v>16960098</v>
       </c>
       <c r="S417" t="s">
-        <v>187</v>
+        <v>55</v>
       </c>
       <c r="U417" t="s">
         <v>196</v>
       </c>
       <c r="V417" s="1">
-        <v>46282.36528526621</v>
+        <v>46282.36528619213</v>
       </c>
       <c r="W417">
         <v>3</v>
@@ -32665,36 +32662,36 @@
         <v>199</v>
       </c>
       <c r="Y417" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AB417">
         <v>0</v>
       </c>
       <c r="AC417" t="s">
-        <v>187</v>
+        <v>55</v>
       </c>
       <c r="AH417" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI417" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="418" spans="1:35">
       <c r="A418">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B418" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C418" t="s">
         <v>50</v>
       </c>
       <c r="D418" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E418" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F418" t="s">
         <v>56</v>
@@ -32724,51 +32721,51 @@
         <v>2026</v>
       </c>
       <c r="R418">
-        <v>16960098</v>
+        <v>17941237</v>
       </c>
       <c r="S418" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="U418" t="s">
         <v>196</v>
       </c>
       <c r="V418" s="1">
-        <v>46282.36528619213</v>
+        <v>46282.36529351852</v>
       </c>
       <c r="W418">
         <v>3</v>
       </c>
       <c r="X418" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="Y418" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AB418">
         <v>0</v>
       </c>
       <c r="AC418" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AH418" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI418" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="419" spans="1:35">
       <c r="A419">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B419" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C419" t="s">
         <v>50</v>
       </c>
       <c r="D419" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E419" t="s">
         <v>54</v>
@@ -32801,7 +32798,7 @@
         <v>2026</v>
       </c>
       <c r="R419">
-        <v>17941237</v>
+        <v>17952466</v>
       </c>
       <c r="S419" t="s">
         <v>54</v>
@@ -32810,16 +32807,16 @@
         <v>196</v>
       </c>
       <c r="V419" s="1">
-        <v>46282.36529351852</v>
+        <v>46282.36529424768</v>
       </c>
       <c r="W419">
         <v>3</v>
       </c>
       <c r="X419" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="Y419" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AB419">
         <v>0</v>
@@ -32828,24 +32825,24 @@
         <v>54</v>
       </c>
       <c r="AH419" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI419" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="420" spans="1:35">
       <c r="A420">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B420" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C420" t="s">
         <v>50</v>
       </c>
       <c r="D420" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E420" t="s">
         <v>54</v>
@@ -32878,7 +32875,7 @@
         <v>2026</v>
       </c>
       <c r="R420">
-        <v>17952466</v>
+        <v>17952646</v>
       </c>
       <c r="S420" t="s">
         <v>54</v>
@@ -32887,7 +32884,7 @@
         <v>196</v>
       </c>
       <c r="V420" s="1">
-        <v>46282.36529424768</v>
+        <v>46282.36529490741</v>
       </c>
       <c r="W420">
         <v>3</v>
@@ -32896,7 +32893,7 @@
         <v>203</v>
       </c>
       <c r="Y420" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AB420">
         <v>0</v>
@@ -32905,18 +32902,18 @@
         <v>54</v>
       </c>
       <c r="AH420" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI420" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="421" spans="1:35">
       <c r="A421">
-        <v>6705</v>
+        <v>6779</v>
       </c>
       <c r="B421" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C421" t="s">
         <v>50</v>
@@ -32955,16 +32952,16 @@
         <v>2026</v>
       </c>
       <c r="R421">
-        <v>17952646</v>
+        <v>18056821</v>
       </c>
       <c r="S421" t="s">
-        <v>54</v>
+        <v>187</v>
       </c>
       <c r="U421" t="s">
         <v>196</v>
       </c>
       <c r="V421" s="1">
-        <v>46282.36529490741</v>
+        <v>46282.36529869213</v>
       </c>
       <c r="W421">
         <v>3</v>
@@ -32973,27 +32970,27 @@
         <v>203</v>
       </c>
       <c r="Y421" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AB421">
         <v>0</v>
       </c>
       <c r="AC421" t="s">
-        <v>54</v>
+        <v>187</v>
       </c>
       <c r="AH421" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI421" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="422" spans="1:35">
       <c r="A422">
-        <v>6779</v>
+        <v>6945</v>
       </c>
       <c r="B422" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C422" t="s">
         <v>50</v>
@@ -33005,7 +33002,7 @@
         <v>54</v>
       </c>
       <c r="F422" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G422">
         <v>9088</v>
@@ -33032,51 +33029,51 @@
         <v>2026</v>
       </c>
       <c r="R422">
-        <v>18056821</v>
+        <v>18164565</v>
       </c>
       <c r="S422" t="s">
-        <v>187</v>
+        <v>54</v>
       </c>
       <c r="U422" t="s">
         <v>196</v>
       </c>
       <c r="V422" s="1">
-        <v>46282.36529869213</v>
+        <v>46282.36531149306</v>
       </c>
       <c r="W422">
         <v>3</v>
       </c>
       <c r="X422" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="Y422" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AB422">
         <v>0</v>
       </c>
       <c r="AC422" t="s">
-        <v>187</v>
+        <v>54</v>
       </c>
       <c r="AH422" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI422" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="423" spans="1:35">
       <c r="A423">
-        <v>6945</v>
+        <v>6949</v>
       </c>
       <c r="B423" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C423" t="s">
         <v>50</v>
       </c>
       <c r="D423" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E423" t="s">
         <v>54</v>
@@ -33109,22 +33106,22 @@
         <v>2026</v>
       </c>
       <c r="R423">
-        <v>18164565</v>
+        <v>18178199</v>
       </c>
       <c r="S423" t="s">
-        <v>54</v>
+        <v>187</v>
       </c>
       <c r="U423" t="s">
         <v>196</v>
       </c>
       <c r="V423" s="1">
-        <v>46282.36531149306</v>
+        <v>46282.36531554398</v>
       </c>
       <c r="W423">
         <v>3</v>
       </c>
       <c r="X423" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Y423" t="s">
         <v>361</v>
@@ -33133,27 +33130,27 @@
         <v>0</v>
       </c>
       <c r="AC423" t="s">
-        <v>54</v>
+        <v>187</v>
       </c>
       <c r="AH423" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI423" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="424" spans="1:35">
       <c r="A424">
-        <v>6949</v>
+        <v>6962</v>
       </c>
       <c r="B424" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C424" t="s">
         <v>50</v>
       </c>
       <c r="D424" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E424" t="s">
         <v>54</v>
@@ -33186,45 +33183,45 @@
         <v>2026</v>
       </c>
       <c r="R424">
-        <v>18178199</v>
+        <v>18188788</v>
       </c>
       <c r="S424" t="s">
-        <v>187</v>
+        <v>54</v>
       </c>
       <c r="U424" t="s">
         <v>196</v>
       </c>
       <c r="V424" s="1">
-        <v>46282.36531554398</v>
+        <v>46282.36531253472</v>
       </c>
       <c r="W424">
         <v>3</v>
       </c>
       <c r="X424" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Y424" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AB424">
         <v>0</v>
       </c>
       <c r="AC424" t="s">
-        <v>187</v>
+        <v>54</v>
       </c>
       <c r="AH424" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI424" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="425" spans="1:35">
       <c r="A425">
-        <v>6962</v>
+        <v>6963</v>
       </c>
       <c r="B425" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C425" t="s">
         <v>50</v>
@@ -33263,7 +33260,7 @@
         <v>2026</v>
       </c>
       <c r="R425">
-        <v>18188788</v>
+        <v>18188694</v>
       </c>
       <c r="S425" t="s">
         <v>54</v>
@@ -33272,7 +33269,7 @@
         <v>196</v>
       </c>
       <c r="V425" s="1">
-        <v>46282.36531253472</v>
+        <v>46282.36531288194</v>
       </c>
       <c r="W425">
         <v>3</v>
@@ -33281,7 +33278,7 @@
         <v>202</v>
       </c>
       <c r="Y425" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AB425">
         <v>0</v>
@@ -33290,33 +33287,33 @@
         <v>54</v>
       </c>
       <c r="AH425" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI425" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="426" spans="1:35">
       <c r="A426">
-        <v>6963</v>
+        <v>5417</v>
       </c>
       <c r="B426" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C426" t="s">
         <v>50</v>
       </c>
       <c r="D426" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E426" t="s">
         <v>54</v>
       </c>
       <c r="F426" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G426">
-        <v>9088</v>
+        <v>6813</v>
       </c>
       <c r="H426">
         <v>0</v>
@@ -33325,13 +33322,13 @@
         <v>65</v>
       </c>
       <c r="J426" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N426" s="1">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="O426" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="P426">
         <v>9</v>
@@ -33340,34 +33337,34 @@
         <v>2026</v>
       </c>
       <c r="R426">
-        <v>18188694</v>
+        <v>17399241</v>
       </c>
       <c r="S426" t="s">
         <v>54</v>
       </c>
       <c r="U426" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="V426" s="1">
-        <v>46282.36531288194</v>
+        <v>46286.45925106481</v>
       </c>
       <c r="W426">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X426" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Y426" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AB426">
         <v>0</v>
       </c>
       <c r="AC426" t="s">
-        <v>54</v>
+        <v>186</v>
       </c>
       <c r="AH426" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI426" t="s">
         <v>383</v>
@@ -33375,16 +33372,16 @@
     </row>
     <row r="427" spans="1:35">
       <c r="A427">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B427" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C427" t="s">
         <v>50</v>
       </c>
       <c r="D427" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E427" t="s">
         <v>54</v>
@@ -33405,10 +33402,10 @@
         <v>154</v>
       </c>
       <c r="N427" s="1">
-        <v>46286</v>
+        <v>46283</v>
       </c>
       <c r="O427" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="P427">
         <v>9</v>
@@ -33417,51 +33414,51 @@
         <v>2026</v>
       </c>
       <c r="R427">
-        <v>17399241</v>
+        <v>16962319</v>
       </c>
       <c r="S427" t="s">
         <v>54</v>
       </c>
       <c r="U427" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="V427" s="1">
-        <v>46286.45925106481</v>
+        <v>46282.79619331018</v>
       </c>
       <c r="W427">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X427" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="Y427" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="AB427">
         <v>0</v>
       </c>
       <c r="AC427" t="s">
-        <v>186</v>
+        <v>54</v>
       </c>
       <c r="AH427" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI427" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="428" spans="1:35">
       <c r="A428">
-        <v>6404</v>
+        <v>6486</v>
       </c>
       <c r="B428" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C428" t="s">
         <v>50</v>
       </c>
       <c r="D428" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E428" t="s">
         <v>54</v>
@@ -33494,7 +33491,7 @@
         <v>2026</v>
       </c>
       <c r="R428">
-        <v>16962319</v>
+        <v>16976198</v>
       </c>
       <c r="S428" t="s">
         <v>54</v>
@@ -33503,16 +33500,16 @@
         <v>196</v>
       </c>
       <c r="V428" s="1">
-        <v>46282.79619331018</v>
+        <v>46282.79620888889</v>
       </c>
       <c r="W428">
         <v>3</v>
       </c>
       <c r="X428" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="Y428" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AB428">
         <v>0</v>
@@ -33521,18 +33518,18 @@
         <v>54</v>
       </c>
       <c r="AH428" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI428" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="429" spans="1:35">
       <c r="A429">
-        <v>6486</v>
+        <v>6548</v>
       </c>
       <c r="B429" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="C429" t="s">
         <v>50</v>
@@ -33571,7 +33568,7 @@
         <v>2026</v>
       </c>
       <c r="R429">
-        <v>16976198</v>
+        <v>17222763</v>
       </c>
       <c r="S429" t="s">
         <v>54</v>
@@ -33580,16 +33577,16 @@
         <v>196</v>
       </c>
       <c r="V429" s="1">
-        <v>46282.79620888889</v>
+        <v>46282.79623803241</v>
       </c>
       <c r="W429">
         <v>3</v>
       </c>
       <c r="X429" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="Y429" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AB429">
         <v>0</v>
@@ -33598,18 +33595,18 @@
         <v>54</v>
       </c>
       <c r="AH429" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI429" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="430" spans="1:35">
       <c r="A430">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B430" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C430" t="s">
         <v>50</v>
@@ -33618,7 +33615,7 @@
         <v>51</v>
       </c>
       <c r="E430" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F430" t="s">
         <v>56</v>
@@ -33648,51 +33645,51 @@
         <v>2026</v>
       </c>
       <c r="R430">
-        <v>17222763</v>
+        <v>17042469</v>
       </c>
       <c r="S430" t="s">
-        <v>54</v>
+        <v>187</v>
       </c>
       <c r="U430" t="s">
         <v>196</v>
       </c>
       <c r="V430" s="1">
-        <v>46282.79623803241</v>
+        <v>46282.79625384259</v>
       </c>
       <c r="W430">
         <v>3</v>
       </c>
       <c r="X430" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Y430" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AB430">
         <v>0</v>
       </c>
       <c r="AC430" t="s">
-        <v>54</v>
+        <v>187</v>
       </c>
       <c r="AH430" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI430" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="431" spans="1:35">
       <c r="A431">
-        <v>6627</v>
+        <v>6628</v>
       </c>
       <c r="B431" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C431" t="s">
         <v>50</v>
       </c>
       <c r="D431" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E431" t="s">
         <v>55</v>
@@ -33725,16 +33722,16 @@
         <v>2026</v>
       </c>
       <c r="R431">
-        <v>17042469</v>
+        <v>16960013</v>
       </c>
       <c r="S431" t="s">
-        <v>187</v>
+        <v>55</v>
       </c>
       <c r="U431" t="s">
         <v>196</v>
       </c>
       <c r="V431" s="1">
-        <v>46282.79625384259</v>
+        <v>46282.79626969907</v>
       </c>
       <c r="W431">
         <v>3</v>
@@ -33743,36 +33740,36 @@
         <v>199</v>
       </c>
       <c r="Y431" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AB431">
         <v>0</v>
       </c>
       <c r="AC431" t="s">
-        <v>187</v>
+        <v>55</v>
       </c>
       <c r="AH431" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI431" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="432" spans="1:35">
       <c r="A432">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B432" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C432" t="s">
         <v>50</v>
       </c>
       <c r="D432" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E432" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F432" t="s">
         <v>56</v>
@@ -33802,51 +33799,51 @@
         <v>2026</v>
       </c>
       <c r="R432">
-        <v>16960013</v>
+        <v>17941197</v>
       </c>
       <c r="S432" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="U432" t="s">
         <v>196</v>
       </c>
       <c r="V432" s="1">
-        <v>46282.79626969907</v>
+        <v>46282.79628394676</v>
       </c>
       <c r="W432">
         <v>3</v>
       </c>
       <c r="X432" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="Y432" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AB432">
         <v>0</v>
       </c>
       <c r="AC432" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AH432" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI432" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="433" spans="1:35">
       <c r="A433">
-        <v>6703</v>
+        <v>6704</v>
       </c>
       <c r="B433" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C433" t="s">
         <v>50</v>
       </c>
       <c r="D433" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E433" t="s">
         <v>54</v>
@@ -33879,7 +33876,7 @@
         <v>2026</v>
       </c>
       <c r="R433">
-        <v>17941197</v>
+        <v>17952411</v>
       </c>
       <c r="S433" t="s">
         <v>54</v>
@@ -33888,16 +33885,16 @@
         <v>196</v>
       </c>
       <c r="V433" s="1">
-        <v>46282.79628394676</v>
+        <v>46282.79630097222</v>
       </c>
       <c r="W433">
         <v>3</v>
       </c>
       <c r="X433" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="Y433" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AB433">
         <v>0</v>
@@ -33906,24 +33903,24 @@
         <v>54</v>
       </c>
       <c r="AH433" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI433" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="434" spans="1:35">
       <c r="A434">
-        <v>6704</v>
+        <v>6705</v>
       </c>
       <c r="B434" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C434" t="s">
         <v>50</v>
       </c>
       <c r="D434" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E434" t="s">
         <v>54</v>
@@ -33956,7 +33953,7 @@
         <v>2026</v>
       </c>
       <c r="R434">
-        <v>17952411</v>
+        <v>17952591</v>
       </c>
       <c r="S434" t="s">
         <v>54</v>
@@ -33965,7 +33962,7 @@
         <v>196</v>
       </c>
       <c r="V434" s="1">
-        <v>46282.79630097222</v>
+        <v>46282.79631204861</v>
       </c>
       <c r="W434">
         <v>3</v>
@@ -33974,7 +33971,7 @@
         <v>203</v>
       </c>
       <c r="Y434" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AB434">
         <v>0</v>
@@ -33983,18 +33980,18 @@
         <v>54</v>
       </c>
       <c r="AH434" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI434" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="435" spans="1:35">
       <c r="A435">
-        <v>6705</v>
+        <v>6945</v>
       </c>
       <c r="B435" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="C435" t="s">
         <v>50</v>
@@ -34006,7 +34003,7 @@
         <v>54</v>
       </c>
       <c r="F435" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G435">
         <v>6813</v>
@@ -34033,7 +34030,7 @@
         <v>2026</v>
       </c>
       <c r="R435">
-        <v>17952591</v>
+        <v>18164530</v>
       </c>
       <c r="S435" t="s">
         <v>54</v>
@@ -34042,13 +34039,13 @@
         <v>196</v>
       </c>
       <c r="V435" s="1">
-        <v>46282.79631204861</v>
+        <v>46282.79637748843</v>
       </c>
       <c r="W435">
         <v>3</v>
       </c>
       <c r="X435" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="Y435" t="s">
         <v>361</v>
@@ -34060,24 +34057,24 @@
         <v>54</v>
       </c>
       <c r="AH435" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI435" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="436" spans="1:35">
       <c r="A436">
-        <v>6945</v>
+        <v>6949</v>
       </c>
       <c r="B436" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C436" t="s">
         <v>50</v>
       </c>
       <c r="D436" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E436" t="s">
         <v>54</v>
@@ -34110,45 +34107,45 @@
         <v>2026</v>
       </c>
       <c r="R436">
-        <v>18164530</v>
+        <v>18178169</v>
       </c>
       <c r="S436" t="s">
-        <v>54</v>
+        <v>187</v>
       </c>
       <c r="U436" t="s">
         <v>196</v>
       </c>
       <c r="V436" s="1">
-        <v>46282.79637748843</v>
+        <v>46282.79638901621</v>
       </c>
       <c r="W436">
         <v>3</v>
       </c>
       <c r="X436" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Y436" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AB436">
         <v>0</v>
       </c>
       <c r="AC436" t="s">
-        <v>54</v>
+        <v>187</v>
       </c>
       <c r="AH436" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AI436" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="437" spans="1:35">
       <c r="A437">
-        <v>6949</v>
+        <v>5417</v>
       </c>
       <c r="B437" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C437" t="s">
         <v>50</v>
@@ -34160,10 +34157,10 @@
         <v>54</v>
       </c>
       <c r="F437" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G437">
-        <v>6813</v>
+        <v>7027</v>
       </c>
       <c r="H437">
         <v>0</v>
@@ -34172,66 +34169,63 @@
         <v>65</v>
       </c>
       <c r="J437" t="s">
-        <v>154</v>
+        <v>119</v>
       </c>
       <c r="N437" s="1">
-        <v>46283</v>
-      </c>
-      <c r="O437" t="s">
-        <v>163</v>
+        <v>46289</v>
       </c>
       <c r="P437">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q437">
         <v>2026</v>
       </c>
       <c r="R437">
-        <v>18178169</v>
+        <v>17399290</v>
       </c>
       <c r="S437" t="s">
-        <v>187</v>
+        <v>54</v>
       </c>
       <c r="U437" t="s">
         <v>196</v>
       </c>
       <c r="V437" s="1">
-        <v>46282.79638901621</v>
+        <v>46283.39832862269</v>
       </c>
       <c r="W437">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="X437" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="Y437" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AB437">
         <v>0</v>
       </c>
       <c r="AC437" t="s">
-        <v>187</v>
+        <v>54</v>
       </c>
       <c r="AH437" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="AI437" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="438" spans="1:35">
       <c r="A438">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B438" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C438" t="s">
         <v>50</v>
       </c>
       <c r="D438" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E438" t="s">
         <v>54</v>
@@ -34261,7 +34255,7 @@
         <v>2026</v>
       </c>
       <c r="R438">
-        <v>17399290</v>
+        <v>16962348</v>
       </c>
       <c r="S438" t="s">
         <v>54</v>
@@ -34270,13 +34264,13 @@
         <v>196</v>
       </c>
       <c r="V438" s="1">
-        <v>46283.39832862269</v>
+        <v>46282.64018086805</v>
       </c>
       <c r="W438">
         <v>-3</v>
       </c>
       <c r="X438" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="Y438" t="s">
         <v>364</v>
@@ -34288,84 +34282,10 @@
         <v>54</v>
       </c>
       <c r="AH438" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AI438" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="439" spans="1:35">
-      <c r="A439">
-        <v>6404</v>
-      </c>
-      <c r="B439" t="s">
-        <v>47</v>
-      </c>
-      <c r="C439" t="s">
-        <v>50</v>
-      </c>
-      <c r="D439" t="s">
-        <v>53</v>
-      </c>
-      <c r="E439" t="s">
-        <v>54</v>
-      </c>
-      <c r="F439" t="s">
-        <v>56</v>
-      </c>
-      <c r="G439">
-        <v>7027</v>
-      </c>
-      <c r="H439">
-        <v>0</v>
-      </c>
-      <c r="I439" t="s">
-        <v>65</v>
-      </c>
-      <c r="J439" t="s">
-        <v>119</v>
-      </c>
-      <c r="N439" s="1">
-        <v>46289</v>
-      </c>
-      <c r="P439">
-        <v>8</v>
-      </c>
-      <c r="Q439">
-        <v>2026</v>
-      </c>
-      <c r="R439">
-        <v>16962348</v>
-      </c>
-      <c r="S439" t="s">
-        <v>54</v>
-      </c>
-      <c r="U439" t="s">
-        <v>196</v>
-      </c>
-      <c r="V439" s="1">
-        <v>46282.64018086805</v>
-      </c>
-      <c r="W439">
-        <v>-3</v>
-      </c>
-      <c r="X439" t="s">
-        <v>208</v>
-      </c>
-      <c r="Y439" t="s">
-        <v>365</v>
-      </c>
-      <c r="AB439">
-        <v>0</v>
-      </c>
-      <c r="AC439" t="s">
-        <v>54</v>
-      </c>
-      <c r="AH439" t="s">
-        <v>378</v>
-      </c>
-      <c r="AI439" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
   </sheetData>

--- a/data/base/goias.xlsx
+++ b/data/base/goias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6345" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6360" uniqueCount="385">
   <si>
     <t>CodCliente</t>
   </si>
@@ -1091,6 +1091,9 @@
   </si>
   <si>
     <t>Tarefa baixada via Rotina SisAnalise x MGC - ExecutarPisCofinsZeradosOuComCredito. - Data Comentário: 18/09/2026 18:03</t>
+  </si>
+  <si>
+    <t>Baixado via API integração MGC x Sistema de Analise Fiscal em 21/09/2026 14:18:48. - Data Comentário: 21/09/2026 14:13</t>
   </si>
   <si>
     <t>Baixado via API integração MGC x Sistema de Analise Fiscal em 17/09/2026 17:55:53. - Data Comentário: 17/09/2026 17:50</t>
@@ -1528,7 +1531,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AI438"/>
+  <dimension ref="A1:AI439"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:35">
@@ -1709,10 +1712,10 @@
         <v>170</v>
       </c>
       <c r="AH2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="3" spans="1:35">
@@ -1786,10 +1789,10 @@
         <v>171</v>
       </c>
       <c r="AH3" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="4" spans="1:35">
@@ -1863,10 +1866,10 @@
         <v>170</v>
       </c>
       <c r="AH4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI4" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="5" spans="1:35">
@@ -1937,10 +1940,10 @@
         <v>170</v>
       </c>
       <c r="AH5" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI5" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="6" spans="1:35">
@@ -2011,10 +2014,10 @@
         <v>171</v>
       </c>
       <c r="AH6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI6" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="7" spans="1:35">
@@ -2085,10 +2088,10 @@
         <v>171</v>
       </c>
       <c r="AH7" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI7" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="8" spans="1:35">
@@ -2159,10 +2162,10 @@
         <v>172</v>
       </c>
       <c r="AH8" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI8" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="9" spans="1:35">
@@ -2233,10 +2236,10 @@
         <v>170</v>
       </c>
       <c r="AH9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI9" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="10" spans="1:35">
@@ -2307,10 +2310,10 @@
         <v>173</v>
       </c>
       <c r="AH10" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI10" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="11" spans="1:35">
@@ -2381,10 +2384,10 @@
         <v>173</v>
       </c>
       <c r="AH11" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI11" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="12" spans="1:35">
@@ -2455,10 +2458,10 @@
         <v>174</v>
       </c>
       <c r="AH12" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI12" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="13" spans="1:35">
@@ -2526,13 +2529,13 @@
         <v>0</v>
       </c>
       <c r="AC13" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AH13" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI13" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="14" spans="1:35">
@@ -2600,13 +2603,13 @@
         <v>0</v>
       </c>
       <c r="AC14" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AH14" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI14" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="15" spans="1:35">
@@ -2674,10 +2677,10 @@
         <v>0</v>
       </c>
       <c r="AH15" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI15" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="16" spans="1:35">
@@ -2739,10 +2742,10 @@
         <v>0</v>
       </c>
       <c r="AH16" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI16" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="17" spans="1:35">
@@ -2810,10 +2813,10 @@
         <v>0</v>
       </c>
       <c r="AH17" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI17" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="18" spans="1:35">
@@ -2887,10 +2890,10 @@
         <v>176</v>
       </c>
       <c r="AH18" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI18" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="19" spans="1:35">
@@ -2964,10 +2967,10 @@
         <v>175</v>
       </c>
       <c r="AH19" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI19" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="20" spans="1:35">
@@ -3041,10 +3044,10 @@
         <v>176</v>
       </c>
       <c r="AH20" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI20" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="21" spans="1:35">
@@ -3118,10 +3121,10 @@
         <v>174</v>
       </c>
       <c r="AH21" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI21" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="22" spans="1:35">
@@ -3192,10 +3195,10 @@
         <v>177</v>
       </c>
       <c r="AH22" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI22" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="23" spans="1:35">
@@ -3266,10 +3269,10 @@
         <v>174</v>
       </c>
       <c r="AH23" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI23" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="24" spans="1:35">
@@ -3340,10 +3343,10 @@
         <v>174</v>
       </c>
       <c r="AH24" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI24" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="25" spans="1:35">
@@ -3414,10 +3417,10 @@
         <v>174</v>
       </c>
       <c r="AH25" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI25" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="26" spans="1:35">
@@ -3488,10 +3491,10 @@
         <v>175</v>
       </c>
       <c r="AH26" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI26" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="27" spans="1:35">
@@ -3562,10 +3565,10 @@
         <v>174</v>
       </c>
       <c r="AH27" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI27" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="28" spans="1:35">
@@ -3636,10 +3639,10 @@
         <v>174</v>
       </c>
       <c r="AH28" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI28" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="29" spans="1:35">
@@ -3710,10 +3713,10 @@
         <v>174</v>
       </c>
       <c r="AH29" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI29" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="30" spans="1:35">
@@ -3784,10 +3787,10 @@
         <v>178</v>
       </c>
       <c r="AH30" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI30" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="31" spans="1:35">
@@ -3864,10 +3867,10 @@
         <v>179</v>
       </c>
       <c r="AH31" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI31" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="32" spans="1:35">
@@ -3938,10 +3941,10 @@
         <v>180</v>
       </c>
       <c r="AH32" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI32" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="33" spans="1:35">
@@ -4018,10 +4021,10 @@
         <v>181</v>
       </c>
       <c r="AH33" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI33" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="34" spans="1:35">
@@ -4095,10 +4098,10 @@
         <v>182</v>
       </c>
       <c r="AH34" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI34" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="35" spans="1:35">
@@ -4172,13 +4175,13 @@
         <v>0</v>
       </c>
       <c r="AC35" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AH35" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI35" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="36" spans="1:35">
@@ -4255,10 +4258,10 @@
         <v>184</v>
       </c>
       <c r="AH36" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI36" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="37" spans="1:35">
@@ -4335,10 +4338,10 @@
         <v>178</v>
       </c>
       <c r="AH37" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI37" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="38" spans="1:35">
@@ -4412,10 +4415,10 @@
         <v>200</v>
       </c>
       <c r="AH38" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI38" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="39" spans="1:35">
@@ -4492,10 +4495,10 @@
         <v>179</v>
       </c>
       <c r="AH39" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI39" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="40" spans="1:35">
@@ -4572,10 +4575,10 @@
         <v>179</v>
       </c>
       <c r="AH40" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI40" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="41" spans="1:35">
@@ -4652,10 +4655,10 @@
         <v>179</v>
       </c>
       <c r="AH41" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI41" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="42" spans="1:35">
@@ -4732,10 +4735,10 @@
         <v>178</v>
       </c>
       <c r="AH42" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI42" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="43" spans="1:35">
@@ -4812,10 +4815,10 @@
         <v>185</v>
       </c>
       <c r="AH43" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI43" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="44" spans="1:35">
@@ -4892,10 +4895,10 @@
         <v>180</v>
       </c>
       <c r="AH44" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI44" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="45" spans="1:35">
@@ -4972,10 +4975,10 @@
         <v>181</v>
       </c>
       <c r="AH45" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI45" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="46" spans="1:35">
@@ -5043,10 +5046,10 @@
         <v>182</v>
       </c>
       <c r="AH46" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI46" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="47" spans="1:35">
@@ -5117,10 +5120,10 @@
         <v>179</v>
       </c>
       <c r="AH47" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI47" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="48" spans="1:35">
@@ -5191,10 +5194,10 @@
         <v>179</v>
       </c>
       <c r="AH48" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI48" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="49" spans="1:35">
@@ -5265,10 +5268,10 @@
         <v>179</v>
       </c>
       <c r="AH49" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI49" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="50" spans="1:35">
@@ -5339,10 +5342,10 @@
         <v>178</v>
       </c>
       <c r="AH50" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI50" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="51" spans="1:35">
@@ -5413,10 +5416,10 @@
         <v>185</v>
       </c>
       <c r="AH51" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI51" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="52" spans="1:35">
@@ -5493,10 +5496,10 @@
         <v>180</v>
       </c>
       <c r="AH52" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI52" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="53" spans="1:35">
@@ -5567,10 +5570,10 @@
         <v>181</v>
       </c>
       <c r="AH53" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI53" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="54" spans="1:35">
@@ -5647,10 +5650,10 @@
         <v>179</v>
       </c>
       <c r="AH54" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI54" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="55" spans="1:35">
@@ -5727,10 +5730,10 @@
         <v>179</v>
       </c>
       <c r="AH55" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI55" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="56" spans="1:35">
@@ -5807,10 +5810,10 @@
         <v>179</v>
       </c>
       <c r="AH56" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI56" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="57" spans="1:35">
@@ -5887,10 +5890,10 @@
         <v>178</v>
       </c>
       <c r="AH57" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI57" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="58" spans="1:35">
@@ -5964,10 +5967,10 @@
         <v>182</v>
       </c>
       <c r="AH58" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI58" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="59" spans="1:35">
@@ -6041,13 +6044,13 @@
         <v>0</v>
       </c>
       <c r="AC59" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AH59" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI59" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="60" spans="1:35">
@@ -6124,10 +6127,10 @@
         <v>179</v>
       </c>
       <c r="AH60" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI60" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="61" spans="1:35">
@@ -6204,10 +6207,10 @@
         <v>179</v>
       </c>
       <c r="AH61" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI61" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="62" spans="1:35">
@@ -6284,10 +6287,10 @@
         <v>179</v>
       </c>
       <c r="AH62" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI62" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="63" spans="1:35">
@@ -6364,10 +6367,10 @@
         <v>178</v>
       </c>
       <c r="AH63" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI63" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="64" spans="1:35">
@@ -6444,10 +6447,10 @@
         <v>185</v>
       </c>
       <c r="AH64" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI64" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="65" spans="1:35">
@@ -6524,10 +6527,10 @@
         <v>180</v>
       </c>
       <c r="AH65" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI65" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="66" spans="1:35">
@@ -6604,10 +6607,10 @@
         <v>181</v>
       </c>
       <c r="AH66" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI66" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="67" spans="1:35">
@@ -6684,10 +6687,10 @@
         <v>179</v>
       </c>
       <c r="AH67" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI67" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="68" spans="1:35">
@@ -6755,10 +6758,10 @@
         <v>182</v>
       </c>
       <c r="AH68" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI68" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="69" spans="1:35">
@@ -6826,13 +6829,13 @@
         <v>0</v>
       </c>
       <c r="AC69" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AH69" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI69" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="70" spans="1:35">
@@ -6903,10 +6906,10 @@
         <v>179</v>
       </c>
       <c r="AH70" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI70" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="71" spans="1:35">
@@ -6977,10 +6980,10 @@
         <v>179</v>
       </c>
       <c r="AH71" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI71" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="72" spans="1:35">
@@ -7051,10 +7054,10 @@
         <v>179</v>
       </c>
       <c r="AH72" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI72" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="73" spans="1:35">
@@ -7125,10 +7128,10 @@
         <v>178</v>
       </c>
       <c r="AH73" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI73" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="74" spans="1:35">
@@ -7199,10 +7202,10 @@
         <v>185</v>
       </c>
       <c r="AH74" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI74" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="75" spans="1:35">
@@ -7273,10 +7276,10 @@
         <v>180</v>
       </c>
       <c r="AH75" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI75" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="76" spans="1:35">
@@ -7347,10 +7350,10 @@
         <v>181</v>
       </c>
       <c r="AH76" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI76" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="77" spans="1:35">
@@ -7421,10 +7424,10 @@
         <v>181</v>
       </c>
       <c r="AH77" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI77" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="78" spans="1:35">
@@ -7495,10 +7498,10 @@
         <v>181</v>
       </c>
       <c r="AH78" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI78" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="79" spans="1:35">
@@ -7569,10 +7572,10 @@
         <v>181</v>
       </c>
       <c r="AH79" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI79" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="80" spans="1:35">
@@ -7643,10 +7646,10 @@
         <v>201</v>
       </c>
       <c r="AH80" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI80" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="81" spans="1:35">
@@ -7714,10 +7717,10 @@
         <v>201</v>
       </c>
       <c r="AH81" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI81" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="82" spans="1:35">
@@ -7788,10 +7791,10 @@
         <v>188</v>
       </c>
       <c r="AH82" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI82" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="83" spans="1:35">
@@ -7862,10 +7865,10 @@
         <v>201</v>
       </c>
       <c r="AH83" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI83" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="84" spans="1:35">
@@ -7933,10 +7936,10 @@
         <v>201</v>
       </c>
       <c r="AH84" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI84" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="85" spans="1:35">
@@ -8007,10 +8010,10 @@
         <v>201</v>
       </c>
       <c r="AH85" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI85" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="86" spans="1:35">
@@ -8075,10 +8078,10 @@
         <v>188</v>
       </c>
       <c r="AH86" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI86" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="87" spans="1:35">
@@ -8149,10 +8152,10 @@
         <v>201</v>
       </c>
       <c r="AH87" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI87" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="88" spans="1:35">
@@ -8220,10 +8223,10 @@
         <v>201</v>
       </c>
       <c r="AH88" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI88" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="89" spans="1:35">
@@ -8294,10 +8297,10 @@
         <v>201</v>
       </c>
       <c r="AH89" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI89" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="90" spans="1:35">
@@ -8362,10 +8365,10 @@
         <v>201</v>
       </c>
       <c r="AH90" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI90" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="91" spans="1:35">
@@ -8430,10 +8433,10 @@
         <v>188</v>
       </c>
       <c r="AH91" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI91" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="92" spans="1:35">
@@ -8504,10 +8507,10 @@
         <v>201</v>
       </c>
       <c r="AH92" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI92" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="93" spans="1:35">
@@ -8575,10 +8578,10 @@
         <v>201</v>
       </c>
       <c r="AH93" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI93" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="94" spans="1:35">
@@ -8649,10 +8652,10 @@
         <v>201</v>
       </c>
       <c r="AH94" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI94" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="95" spans="1:35">
@@ -8717,10 +8720,10 @@
         <v>201</v>
       </c>
       <c r="AH95" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI95" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="96" spans="1:35">
@@ -8785,10 +8788,10 @@
         <v>188</v>
       </c>
       <c r="AH96" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI96" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="97" spans="1:35">
@@ -8859,10 +8862,10 @@
         <v>201</v>
       </c>
       <c r="AH97" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI97" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="98" spans="1:35">
@@ -8930,10 +8933,10 @@
         <v>201</v>
       </c>
       <c r="AH98" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI98" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="99" spans="1:35">
@@ -9004,10 +9007,10 @@
         <v>188</v>
       </c>
       <c r="AH99" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI99" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="100" spans="1:35">
@@ -9084,10 +9087,10 @@
         <v>201</v>
       </c>
       <c r="AH100" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI100" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="101" spans="1:35">
@@ -9155,10 +9158,10 @@
         <v>201</v>
       </c>
       <c r="AH101" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI101" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="102" spans="1:35">
@@ -9229,10 +9232,10 @@
         <v>201</v>
       </c>
       <c r="AH102" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI102" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="103" spans="1:35">
@@ -9300,10 +9303,10 @@
         <v>201</v>
       </c>
       <c r="AH103" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI103" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="104" spans="1:35">
@@ -9374,10 +9377,10 @@
         <v>201</v>
       </c>
       <c r="AH104" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI104" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="105" spans="1:35">
@@ -9442,10 +9445,10 @@
         <v>201</v>
       </c>
       <c r="AH105" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI105" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="106" spans="1:35">
@@ -9510,10 +9513,10 @@
         <v>188</v>
       </c>
       <c r="AH106" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI106" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="107" spans="1:35">
@@ -9584,10 +9587,10 @@
         <v>201</v>
       </c>
       <c r="AH107" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI107" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="108" spans="1:35">
@@ -9658,10 +9661,10 @@
         <v>201</v>
       </c>
       <c r="AH108" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI108" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="109" spans="1:35">
@@ -9729,10 +9732,10 @@
         <v>201</v>
       </c>
       <c r="AH109" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI109" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="110" spans="1:35">
@@ -9803,10 +9806,10 @@
         <v>188</v>
       </c>
       <c r="AH110" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI110" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="111" spans="1:35">
@@ -9874,10 +9877,10 @@
         <v>187</v>
       </c>
       <c r="AH111" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI111" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="112" spans="1:35">
@@ -9948,10 +9951,10 @@
         <v>188</v>
       </c>
       <c r="AH112" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI112" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="113" spans="1:35">
@@ -10022,10 +10025,10 @@
         <v>186</v>
       </c>
       <c r="AH113" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI113" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="114" spans="1:35">
@@ -10093,10 +10096,10 @@
         <v>187</v>
       </c>
       <c r="AH114" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI114" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="115" spans="1:35">
@@ -10167,10 +10170,10 @@
         <v>188</v>
       </c>
       <c r="AH115" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI115" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:35">
@@ -10241,10 +10244,10 @@
         <v>201</v>
       </c>
       <c r="AH116" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI116" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:35">
@@ -10312,10 +10315,10 @@
         <v>201</v>
       </c>
       <c r="AH117" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI117" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="118" spans="1:35">
@@ -10386,10 +10389,10 @@
         <v>201</v>
       </c>
       <c r="AH118" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI118" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="119" spans="1:35">
@@ -10454,10 +10457,10 @@
         <v>201</v>
       </c>
       <c r="AH119" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI119" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="120" spans="1:35">
@@ -10522,10 +10525,10 @@
         <v>188</v>
       </c>
       <c r="AH120" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI120" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="121" spans="1:35">
@@ -10596,10 +10599,10 @@
         <v>201</v>
       </c>
       <c r="AH121" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI121" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="122" spans="1:35">
@@ -10667,10 +10670,10 @@
         <v>201</v>
       </c>
       <c r="AH122" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI122" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="123" spans="1:35">
@@ -10741,10 +10744,10 @@
         <v>201</v>
       </c>
       <c r="AH123" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI123" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="124" spans="1:35">
@@ -10809,10 +10812,10 @@
         <v>201</v>
       </c>
       <c r="AH124" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI124" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="125" spans="1:35">
@@ -10877,10 +10880,10 @@
         <v>188</v>
       </c>
       <c r="AH125" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI125" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="126" spans="1:35">
@@ -10957,10 +10960,10 @@
         <v>188</v>
       </c>
       <c r="AH126" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI126" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="127" spans="1:35">
@@ -11037,10 +11040,10 @@
         <v>188</v>
       </c>
       <c r="AH127" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI127" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="128" spans="1:35">
@@ -11111,10 +11114,10 @@
         <v>191</v>
       </c>
       <c r="AH128" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI128" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="129" spans="1:35">
@@ -11185,10 +11188,10 @@
         <v>191</v>
       </c>
       <c r="AH129" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI129" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="130" spans="1:35">
@@ -11265,10 +11268,10 @@
         <v>191</v>
       </c>
       <c r="AH130" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI130" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="131" spans="1:35">
@@ -11339,10 +11342,10 @@
         <v>191</v>
       </c>
       <c r="AH131" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI131" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="132" spans="1:35">
@@ -11413,10 +11416,10 @@
         <v>191</v>
       </c>
       <c r="AH132" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI132" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="133" spans="1:35">
@@ -11487,10 +11490,10 @@
         <v>191</v>
       </c>
       <c r="AH133" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI133" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="134" spans="1:35">
@@ -11561,10 +11564,10 @@
         <v>191</v>
       </c>
       <c r="AH134" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI134" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="135" spans="1:35">
@@ -11641,10 +11644,10 @@
         <v>191</v>
       </c>
       <c r="AH135" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI135" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="136" spans="1:35">
@@ -11715,10 +11718,10 @@
         <v>191</v>
       </c>
       <c r="AH136" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI136" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="137" spans="1:35">
@@ -11789,10 +11792,10 @@
         <v>191</v>
       </c>
       <c r="AH137" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI137" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="138" spans="1:35">
@@ -11863,10 +11866,10 @@
         <v>191</v>
       </c>
       <c r="AH138" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI138" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="139" spans="1:35">
@@ -11943,10 +11946,10 @@
         <v>191</v>
       </c>
       <c r="AH139" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI139" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="140" spans="1:35">
@@ -12017,10 +12020,10 @@
         <v>191</v>
       </c>
       <c r="AH140" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI140" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="141" spans="1:35">
@@ -12091,10 +12094,10 @@
         <v>191</v>
       </c>
       <c r="AH141" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI141" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="142" spans="1:35">
@@ -12165,10 +12168,10 @@
         <v>191</v>
       </c>
       <c r="AH142" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI142" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="143" spans="1:35">
@@ -12239,10 +12242,10 @@
         <v>191</v>
       </c>
       <c r="AH143" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI143" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="144" spans="1:35">
@@ -12313,10 +12316,10 @@
         <v>191</v>
       </c>
       <c r="AH144" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI144" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="145" spans="1:35">
@@ -12387,10 +12390,10 @@
         <v>191</v>
       </c>
       <c r="AH145" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI145" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="146" spans="1:35">
@@ -12461,10 +12464,10 @@
         <v>191</v>
       </c>
       <c r="AH146" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI146" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="147" spans="1:35">
@@ -12535,10 +12538,10 @@
         <v>191</v>
       </c>
       <c r="AH147" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI147" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="148" spans="1:35">
@@ -12609,10 +12612,10 @@
         <v>191</v>
       </c>
       <c r="AH148" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI148" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="149" spans="1:35">
@@ -12683,10 +12686,10 @@
         <v>191</v>
       </c>
       <c r="AH149" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI149" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="150" spans="1:35">
@@ -12763,10 +12766,10 @@
         <v>191</v>
       </c>
       <c r="AH150" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI150" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="151" spans="1:35">
@@ -12837,10 +12840,10 @@
         <v>191</v>
       </c>
       <c r="AH151" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI151" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="152" spans="1:35">
@@ -12911,10 +12914,10 @@
         <v>191</v>
       </c>
       <c r="AH152" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI152" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="153" spans="1:35">
@@ -12985,10 +12988,10 @@
         <v>191</v>
       </c>
       <c r="AH153" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI153" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="154" spans="1:35">
@@ -13059,10 +13062,10 @@
         <v>192</v>
       </c>
       <c r="AH154" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI154" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="155" spans="1:35">
@@ -13133,10 +13136,10 @@
         <v>192</v>
       </c>
       <c r="AH155" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI155" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="156" spans="1:35">
@@ -13207,10 +13210,10 @@
         <v>192</v>
       </c>
       <c r="AH156" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI156" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="157" spans="1:35">
@@ -13281,10 +13284,10 @@
         <v>192</v>
       </c>
       <c r="AH157" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI157" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="158" spans="1:35">
@@ -13355,10 +13358,10 @@
         <v>192</v>
       </c>
       <c r="AH158" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI158" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="159" spans="1:35">
@@ -13429,10 +13432,10 @@
         <v>192</v>
       </c>
       <c r="AH159" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI159" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="160" spans="1:35">
@@ -13503,10 +13506,10 @@
         <v>192</v>
       </c>
       <c r="AH160" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI160" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="161" spans="1:35">
@@ -13577,10 +13580,10 @@
         <v>192</v>
       </c>
       <c r="AH161" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI161" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="162" spans="1:35">
@@ -13654,10 +13657,10 @@
         <v>192</v>
       </c>
       <c r="AH162" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI162" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="163" spans="1:35">
@@ -13731,10 +13734,10 @@
         <v>192</v>
       </c>
       <c r="AH163" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI163" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="164" spans="1:35">
@@ -13808,10 +13811,10 @@
         <v>192</v>
       </c>
       <c r="AH164" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI164" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="165" spans="1:35">
@@ -13885,10 +13888,10 @@
         <v>192</v>
       </c>
       <c r="AH165" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI165" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="166" spans="1:35">
@@ -13962,10 +13965,10 @@
         <v>192</v>
       </c>
       <c r="AH166" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI166" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="167" spans="1:35">
@@ -14039,10 +14042,10 @@
         <v>192</v>
       </c>
       <c r="AH167" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI167" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="168" spans="1:35">
@@ -14116,10 +14119,10 @@
         <v>192</v>
       </c>
       <c r="AH168" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI168" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="169" spans="1:35">
@@ -14193,10 +14196,10 @@
         <v>192</v>
       </c>
       <c r="AH169" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI169" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="170" spans="1:35">
@@ -14270,10 +14273,10 @@
         <v>192</v>
       </c>
       <c r="AH170" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI170" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="171" spans="1:35">
@@ -14347,10 +14350,10 @@
         <v>192</v>
       </c>
       <c r="AH171" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI171" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="172" spans="1:35">
@@ -14424,10 +14427,10 @@
         <v>192</v>
       </c>
       <c r="AH172" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI172" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="173" spans="1:35">
@@ -14501,10 +14504,10 @@
         <v>192</v>
       </c>
       <c r="AH173" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI173" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="174" spans="1:35">
@@ -14578,10 +14581,10 @@
         <v>192</v>
       </c>
       <c r="AH174" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI174" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="175" spans="1:35">
@@ -14655,10 +14658,10 @@
         <v>192</v>
       </c>
       <c r="AH175" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI175" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="176" spans="1:35">
@@ -14726,10 +14729,10 @@
         <v>192</v>
       </c>
       <c r="AH176" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI176" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="177" spans="1:35">
@@ -14797,10 +14800,10 @@
         <v>192</v>
       </c>
       <c r="AH177" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI177" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="178" spans="1:35">
@@ -14868,10 +14871,10 @@
         <v>192</v>
       </c>
       <c r="AH178" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI178" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="179" spans="1:35">
@@ -14939,10 +14942,10 @@
         <v>192</v>
       </c>
       <c r="AH179" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI179" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="180" spans="1:35">
@@ -15010,10 +15013,10 @@
         <v>192</v>
       </c>
       <c r="AH180" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI180" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="181" spans="1:35">
@@ -15081,10 +15084,10 @@
         <v>192</v>
       </c>
       <c r="AH181" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI181" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="182" spans="1:35">
@@ -15152,10 +15155,10 @@
         <v>54</v>
       </c>
       <c r="AH182" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI182" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="183" spans="1:35">
@@ -15223,10 +15226,10 @@
         <v>54</v>
       </c>
       <c r="AH183" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI183" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="184" spans="1:35">
@@ -15294,10 +15297,10 @@
         <v>54</v>
       </c>
       <c r="AH184" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI184" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="185" spans="1:35">
@@ -15365,10 +15368,10 @@
         <v>54</v>
       </c>
       <c r="AH185" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI185" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="186" spans="1:35">
@@ -15436,10 +15439,10 @@
         <v>193</v>
       </c>
       <c r="AH186" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI186" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="187" spans="1:35">
@@ -15507,10 +15510,10 @@
         <v>55</v>
       </c>
       <c r="AH187" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI187" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="188" spans="1:35">
@@ -15578,10 +15581,10 @@
         <v>54</v>
       </c>
       <c r="AH188" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI188" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="189" spans="1:35">
@@ -15649,10 +15652,10 @@
         <v>54</v>
       </c>
       <c r="AH189" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI189" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="190" spans="1:35">
@@ -15720,10 +15723,10 @@
         <v>54</v>
       </c>
       <c r="AH190" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI190" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="191" spans="1:35">
@@ -15791,10 +15794,10 @@
         <v>193</v>
       </c>
       <c r="AH191" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI191" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="192" spans="1:35">
@@ -15862,10 +15865,10 @@
         <v>54</v>
       </c>
       <c r="AH192" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI192" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="193" spans="1:35">
@@ -15933,10 +15936,10 @@
         <v>193</v>
       </c>
       <c r="AH193" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI193" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="194" spans="1:35">
@@ -16004,10 +16007,10 @@
         <v>54</v>
       </c>
       <c r="AH194" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI194" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="195" spans="1:35">
@@ -16075,10 +16078,10 @@
         <v>54</v>
       </c>
       <c r="AH195" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI195" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="196" spans="1:35">
@@ -16146,10 +16149,10 @@
         <v>54</v>
       </c>
       <c r="AH196" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI196" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="197" spans="1:35">
@@ -16217,10 +16220,10 @@
         <v>54</v>
       </c>
       <c r="AH197" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI197" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="198" spans="1:35">
@@ -16288,10 +16291,10 @@
         <v>54</v>
       </c>
       <c r="AH198" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI198" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="199" spans="1:35">
@@ -16359,10 +16362,10 @@
         <v>54</v>
       </c>
       <c r="AH199" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI199" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="200" spans="1:35">
@@ -16430,10 +16433,10 @@
         <v>193</v>
       </c>
       <c r="AH200" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI200" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="201" spans="1:35">
@@ -16501,10 +16504,10 @@
         <v>55</v>
       </c>
       <c r="AH201" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI201" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="202" spans="1:35">
@@ -16575,10 +16578,10 @@
         <v>54</v>
       </c>
       <c r="AH202" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI202" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="203" spans="1:35">
@@ -16649,10 +16652,10 @@
         <v>54</v>
       </c>
       <c r="AH203" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI203" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="204" spans="1:35">
@@ -16723,10 +16726,10 @@
         <v>54</v>
       </c>
       <c r="AH204" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI204" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="205" spans="1:35">
@@ -16797,10 +16800,10 @@
         <v>54</v>
       </c>
       <c r="AH205" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI205" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="206" spans="1:35">
@@ -16868,10 +16871,10 @@
         <v>54</v>
       </c>
       <c r="AH206" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI206" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="207" spans="1:35">
@@ -16939,10 +16942,10 @@
         <v>54</v>
       </c>
       <c r="AH207" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI207" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="208" spans="1:35">
@@ -17007,10 +17010,10 @@
         <v>0</v>
       </c>
       <c r="AH208" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI208" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="209" spans="1:35">
@@ -17072,10 +17075,10 @@
         <v>0</v>
       </c>
       <c r="AH209" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI209" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="210" spans="1:35">
@@ -17143,13 +17146,13 @@
         <v>0</v>
       </c>
       <c r="AC210" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AH210" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI210" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="211" spans="1:35">
@@ -17220,10 +17223,10 @@
         <v>175</v>
       </c>
       <c r="AH211" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI211" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="212" spans="1:35">
@@ -17300,10 +17303,10 @@
         <v>179</v>
       </c>
       <c r="AH212" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI212" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="213" spans="1:35">
@@ -17380,10 +17383,10 @@
         <v>179</v>
       </c>
       <c r="AH213" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI213" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="214" spans="1:35">
@@ -17460,10 +17463,10 @@
         <v>180</v>
       </c>
       <c r="AH214" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI214" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="215" spans="1:35">
@@ -17540,10 +17543,10 @@
         <v>185</v>
       </c>
       <c r="AH215" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI215" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="216" spans="1:35">
@@ -17620,10 +17623,10 @@
         <v>179</v>
       </c>
       <c r="AH216" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI216" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="217" spans="1:35">
@@ -17700,10 +17703,10 @@
         <v>184</v>
       </c>
       <c r="AH217" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI217" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="218" spans="1:35">
@@ -17780,10 +17783,10 @@
         <v>179</v>
       </c>
       <c r="AH218" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI218" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="219" spans="1:35">
@@ -17860,10 +17863,10 @@
         <v>179</v>
       </c>
       <c r="AH219" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI219" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="220" spans="1:35">
@@ -17934,10 +17937,10 @@
         <v>178</v>
       </c>
       <c r="AH220" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI220" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="221" spans="1:35">
@@ -18008,10 +18011,10 @@
         <v>185</v>
       </c>
       <c r="AH221" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI221" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="222" spans="1:35">
@@ -18088,10 +18091,10 @@
         <v>179</v>
       </c>
       <c r="AH222" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI222" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="223" spans="1:35">
@@ -18168,10 +18171,10 @@
         <v>184</v>
       </c>
       <c r="AH223" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI223" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="224" spans="1:35">
@@ -18248,10 +18251,10 @@
         <v>179</v>
       </c>
       <c r="AH224" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI224" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="225" spans="1:35">
@@ -18328,10 +18331,10 @@
         <v>179</v>
       </c>
       <c r="AH225" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI225" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="226" spans="1:35">
@@ -18402,10 +18405,10 @@
         <v>178</v>
       </c>
       <c r="AH226" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI226" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="227" spans="1:35">
@@ -18476,10 +18479,10 @@
         <v>185</v>
       </c>
       <c r="AH227" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI227" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="228" spans="1:35">
@@ -18550,10 +18553,10 @@
         <v>182</v>
       </c>
       <c r="AH228" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI228" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="229" spans="1:35">
@@ -18627,10 +18630,10 @@
         <v>183</v>
       </c>
       <c r="AH229" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI229" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="230" spans="1:35">
@@ -18704,10 +18707,10 @@
         <v>179</v>
       </c>
       <c r="AH230" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI230" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="231" spans="1:35">
@@ -18781,10 +18784,10 @@
         <v>184</v>
       </c>
       <c r="AH231" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI231" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="232" spans="1:35">
@@ -18858,10 +18861,10 @@
         <v>179</v>
       </c>
       <c r="AH232" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI232" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="233" spans="1:35">
@@ -18935,10 +18938,10 @@
         <v>179</v>
       </c>
       <c r="AH233" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI233" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="234" spans="1:35">
@@ -19015,10 +19018,10 @@
         <v>178</v>
       </c>
       <c r="AH234" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI234" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="235" spans="1:35">
@@ -19092,10 +19095,10 @@
         <v>185</v>
       </c>
       <c r="AH235" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI235" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="236" spans="1:35">
@@ -19169,10 +19172,10 @@
         <v>180</v>
       </c>
       <c r="AH236" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI236" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="237" spans="1:35">
@@ -19246,10 +19249,10 @@
         <v>181</v>
       </c>
       <c r="AH237" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI237" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="238" spans="1:35">
@@ -19323,10 +19326,10 @@
         <v>182</v>
       </c>
       <c r="AH238" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI238" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="239" spans="1:35">
@@ -19403,10 +19406,10 @@
         <v>179</v>
       </c>
       <c r="AH239" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI239" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="240" spans="1:35">
@@ -19483,10 +19486,10 @@
         <v>179</v>
       </c>
       <c r="AH240" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI240" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="241" spans="1:35">
@@ -19563,10 +19566,10 @@
         <v>179</v>
       </c>
       <c r="AH241" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI241" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="242" spans="1:35">
@@ -19643,10 +19646,10 @@
         <v>185</v>
       </c>
       <c r="AH242" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI242" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="243" spans="1:35">
@@ -19723,10 +19726,10 @@
         <v>180</v>
       </c>
       <c r="AH243" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI243" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="244" spans="1:35">
@@ -19797,10 +19800,10 @@
         <v>181</v>
       </c>
       <c r="AH244" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI244" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="245" spans="1:35">
@@ -19871,10 +19874,10 @@
         <v>182</v>
       </c>
       <c r="AH245" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI245" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="246" spans="1:35">
@@ -19951,10 +19954,10 @@
         <v>179</v>
       </c>
       <c r="AH246" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI246" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="247" spans="1:35">
@@ -20028,10 +20031,10 @@
         <v>184</v>
       </c>
       <c r="AH247" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI247" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="248" spans="1:35">
@@ -20108,10 +20111,10 @@
         <v>179</v>
       </c>
       <c r="AH248" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI248" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="249" spans="1:35">
@@ -20188,10 +20191,10 @@
         <v>179</v>
       </c>
       <c r="AH249" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI249" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="250" spans="1:35">
@@ -20265,10 +20268,10 @@
         <v>178</v>
       </c>
       <c r="AH250" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI250" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="251" spans="1:35">
@@ -20342,10 +20345,10 @@
         <v>185</v>
       </c>
       <c r="AH251" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI251" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="252" spans="1:35">
@@ -20419,10 +20422,10 @@
         <v>180</v>
       </c>
       <c r="AH252" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI252" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="253" spans="1:35">
@@ -20496,10 +20499,10 @@
         <v>181</v>
       </c>
       <c r="AH253" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI253" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="254" spans="1:35">
@@ -20576,10 +20579,10 @@
         <v>185</v>
       </c>
       <c r="AH254" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI254" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="255" spans="1:35">
@@ -20650,10 +20653,10 @@
         <v>179</v>
       </c>
       <c r="AH255" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI255" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="256" spans="1:35">
@@ -20724,10 +20727,10 @@
         <v>179</v>
       </c>
       <c r="AH256" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI256" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="257" spans="1:35">
@@ -20798,10 +20801,10 @@
         <v>179</v>
       </c>
       <c r="AH257" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI257" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="258" spans="1:35">
@@ -20878,10 +20881,10 @@
         <v>190</v>
       </c>
       <c r="AH258" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI258" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="259" spans="1:35">
@@ -20958,10 +20961,10 @@
         <v>190</v>
       </c>
       <c r="AH259" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI259" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="260" spans="1:35">
@@ -21038,10 +21041,10 @@
         <v>189</v>
       </c>
       <c r="AH260" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI260" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="261" spans="1:35">
@@ -21109,10 +21112,10 @@
         <v>187</v>
       </c>
       <c r="AH261" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI261" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="262" spans="1:35">
@@ -21189,10 +21192,10 @@
         <v>186</v>
       </c>
       <c r="AH262" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI262" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="263" spans="1:35">
@@ -21260,10 +21263,10 @@
         <v>201</v>
       </c>
       <c r="AH263" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI263" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="264" spans="1:35">
@@ -21340,10 +21343,10 @@
         <v>201</v>
       </c>
       <c r="AH264" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI264" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="265" spans="1:35">
@@ -21417,10 +21420,10 @@
         <v>187</v>
       </c>
       <c r="AH265" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI265" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="266" spans="1:35">
@@ -21497,10 +21500,10 @@
         <v>188</v>
       </c>
       <c r="AH266" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI266" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="267" spans="1:35">
@@ -21574,10 +21577,10 @@
         <v>190</v>
       </c>
       <c r="AH267" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI267" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="268" spans="1:35">
@@ -21654,10 +21657,10 @@
         <v>190</v>
       </c>
       <c r="AH268" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI268" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="269" spans="1:35">
@@ -21731,10 +21734,10 @@
         <v>189</v>
       </c>
       <c r="AH269" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI269" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="270" spans="1:35">
@@ -21805,10 +21808,10 @@
         <v>187</v>
       </c>
       <c r="AH270" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI270" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="271" spans="1:35">
@@ -21882,10 +21885,10 @@
         <v>190</v>
       </c>
       <c r="AH271" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI271" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="272" spans="1:35">
@@ -21959,10 +21962,10 @@
         <v>190</v>
       </c>
       <c r="AH272" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI272" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="273" spans="1:35">
@@ -22039,10 +22042,10 @@
         <v>186</v>
       </c>
       <c r="AH273" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI273" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="274" spans="1:35">
@@ -22110,10 +22113,10 @@
         <v>201</v>
       </c>
       <c r="AH274" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI274" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="275" spans="1:35">
@@ -22187,10 +22190,10 @@
         <v>187</v>
       </c>
       <c r="AH275" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI275" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="276" spans="1:35">
@@ -22261,10 +22264,10 @@
         <v>190</v>
       </c>
       <c r="AH276" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI276" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="277" spans="1:35">
@@ -22335,10 +22338,10 @@
         <v>190</v>
       </c>
       <c r="AH277" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI277" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="278" spans="1:35">
@@ -22409,10 +22412,10 @@
         <v>188</v>
       </c>
       <c r="AH278" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI278" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="279" spans="1:35">
@@ -22486,10 +22489,10 @@
         <v>187</v>
       </c>
       <c r="AH279" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI279" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="280" spans="1:35">
@@ -22563,10 +22566,10 @@
         <v>187</v>
       </c>
       <c r="AH280" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI280" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="281" spans="1:35">
@@ -22643,10 +22646,10 @@
         <v>188</v>
       </c>
       <c r="AH281" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI281" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="282" spans="1:35">
@@ -22723,10 +22726,10 @@
         <v>191</v>
       </c>
       <c r="AH282" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI282" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="283" spans="1:35">
@@ -22800,10 +22803,10 @@
         <v>191</v>
       </c>
       <c r="AH283" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI283" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="284" spans="1:35">
@@ -22880,10 +22883,10 @@
         <v>191</v>
       </c>
       <c r="AH284" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI284" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="285" spans="1:35">
@@ -22954,10 +22957,10 @@
         <v>191</v>
       </c>
       <c r="AH285" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI285" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="286" spans="1:35">
@@ -23028,10 +23031,10 @@
         <v>191</v>
       </c>
       <c r="AH286" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI286" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="287" spans="1:35">
@@ -23102,10 +23105,10 @@
         <v>191</v>
       </c>
       <c r="AH287" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI287" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="288" spans="1:35">
@@ -23176,10 +23179,10 @@
         <v>191</v>
       </c>
       <c r="AH288" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI288" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="289" spans="1:35">
@@ -23250,10 +23253,10 @@
         <v>191</v>
       </c>
       <c r="AH289" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI289" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="290" spans="1:35">
@@ -23330,10 +23333,10 @@
         <v>191</v>
       </c>
       <c r="AH290" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI290" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="291" spans="1:35">
@@ -23404,10 +23407,10 @@
         <v>191</v>
       </c>
       <c r="AH291" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI291" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="292" spans="1:35">
@@ -23484,10 +23487,10 @@
         <v>191</v>
       </c>
       <c r="AH292" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI292" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="293" spans="1:35">
@@ -23558,10 +23561,10 @@
         <v>191</v>
       </c>
       <c r="AH293" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI293" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="294" spans="1:35">
@@ -23632,10 +23635,10 @@
         <v>191</v>
       </c>
       <c r="AH294" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI294" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="295" spans="1:35">
@@ -23706,10 +23709,10 @@
         <v>191</v>
       </c>
       <c r="AH295" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI295" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="296" spans="1:35">
@@ -23786,10 +23789,10 @@
         <v>191</v>
       </c>
       <c r="AH296" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI296" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="297" spans="1:35">
@@ -23860,10 +23863,10 @@
         <v>191</v>
       </c>
       <c r="AH297" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI297" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="298" spans="1:35">
@@ -23934,10 +23937,10 @@
         <v>191</v>
       </c>
       <c r="AH298" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI298" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="299" spans="1:35">
@@ -24008,10 +24011,10 @@
         <v>191</v>
       </c>
       <c r="AH299" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI299" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="300" spans="1:35">
@@ -24082,10 +24085,10 @@
         <v>191</v>
       </c>
       <c r="AH300" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI300" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="301" spans="1:35">
@@ -24156,10 +24159,10 @@
         <v>191</v>
       </c>
       <c r="AH301" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI301" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="302" spans="1:35">
@@ -24230,10 +24233,10 @@
         <v>191</v>
       </c>
       <c r="AH302" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI302" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="303" spans="1:35">
@@ -24310,10 +24313,10 @@
         <v>191</v>
       </c>
       <c r="AH303" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI303" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="304" spans="1:35">
@@ -24390,10 +24393,10 @@
         <v>191</v>
       </c>
       <c r="AH304" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI304" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="305" spans="1:35">
@@ -24470,10 +24473,10 @@
         <v>191</v>
       </c>
       <c r="AH305" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI305" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="306" spans="1:35">
@@ -24547,10 +24550,10 @@
         <v>191</v>
       </c>
       <c r="AH306" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI306" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="307" spans="1:35">
@@ -24624,10 +24627,10 @@
         <v>191</v>
       </c>
       <c r="AH307" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI307" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="308" spans="1:35">
@@ -24701,10 +24704,10 @@
         <v>192</v>
       </c>
       <c r="AH308" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI308" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="309" spans="1:35">
@@ -24778,10 +24781,10 @@
         <v>192</v>
       </c>
       <c r="AH309" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI309" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="310" spans="1:35">
@@ -24852,10 +24855,10 @@
         <v>192</v>
       </c>
       <c r="AH310" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI310" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="311" spans="1:35">
@@ -24926,10 +24929,10 @@
         <v>192</v>
       </c>
       <c r="AH311" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI311" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="312" spans="1:35">
@@ -25000,10 +25003,10 @@
         <v>192</v>
       </c>
       <c r="AH312" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI312" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="313" spans="1:35">
@@ -25074,10 +25077,10 @@
         <v>192</v>
       </c>
       <c r="AH313" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI313" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="314" spans="1:35">
@@ -25145,10 +25148,10 @@
         <v>192</v>
       </c>
       <c r="AH314" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI314" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="315" spans="1:35">
@@ -25222,10 +25225,10 @@
         <v>192</v>
       </c>
       <c r="AH315" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI315" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="316" spans="1:35">
@@ -25299,10 +25302,10 @@
         <v>192</v>
       </c>
       <c r="AH316" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI316" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="317" spans="1:35">
@@ -25376,10 +25379,10 @@
         <v>192</v>
       </c>
       <c r="AH317" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI317" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="318" spans="1:35">
@@ -25453,10 +25456,10 @@
         <v>192</v>
       </c>
       <c r="AH318" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI318" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="319" spans="1:35">
@@ -25530,10 +25533,10 @@
         <v>192</v>
       </c>
       <c r="AH319" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI319" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="320" spans="1:35">
@@ -25604,10 +25607,10 @@
         <v>192</v>
       </c>
       <c r="AH320" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI320" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="321" spans="1:35">
@@ -25678,10 +25681,10 @@
         <v>192</v>
       </c>
       <c r="AH321" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI321" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="322" spans="1:35">
@@ -25752,10 +25755,10 @@
         <v>192</v>
       </c>
       <c r="AH322" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI322" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="323" spans="1:35">
@@ -25823,10 +25826,10 @@
         <v>192</v>
       </c>
       <c r="AH323" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI323" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="324" spans="1:35">
@@ -25894,10 +25897,10 @@
         <v>192</v>
       </c>
       <c r="AH324" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI324" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="325" spans="1:35">
@@ -25965,10 +25968,10 @@
         <v>192</v>
       </c>
       <c r="AH325" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI325" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="326" spans="1:35">
@@ -26036,10 +26039,10 @@
         <v>192</v>
       </c>
       <c r="AH326" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI326" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="327" spans="1:35">
@@ -26107,10 +26110,10 @@
         <v>192</v>
       </c>
       <c r="AH327" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI327" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="328" spans="1:35">
@@ -26178,10 +26181,10 @@
         <v>54</v>
       </c>
       <c r="AH328" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI328" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="329" spans="1:35">
@@ -26249,10 +26252,10 @@
         <v>54</v>
       </c>
       <c r="AH329" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI329" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="330" spans="1:35">
@@ -26320,10 +26323,10 @@
         <v>54</v>
       </c>
       <c r="AH330" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI330" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="331" spans="1:35">
@@ -26391,10 +26394,10 @@
         <v>54</v>
       </c>
       <c r="AH331" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI331" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="332" spans="1:35">
@@ -26462,10 +26465,10 @@
         <v>193</v>
       </c>
       <c r="AH332" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI332" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="333" spans="1:35">
@@ -26533,10 +26536,10 @@
         <v>193</v>
       </c>
       <c r="AH333" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI333" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="334" spans="1:35">
@@ -26604,10 +26607,10 @@
         <v>193</v>
       </c>
       <c r="AH334" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI334" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="335" spans="1:35">
@@ -26675,10 +26678,10 @@
         <v>193</v>
       </c>
       <c r="AH335" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI335" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="336" spans="1:35">
@@ -26746,10 +26749,10 @@
         <v>193</v>
       </c>
       <c r="AH336" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI336" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="337" spans="1:35">
@@ -26817,10 +26820,10 @@
         <v>193</v>
       </c>
       <c r="AH337" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI337" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="338" spans="1:35">
@@ -26888,10 +26891,10 @@
         <v>193</v>
       </c>
       <c r="AH338" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI338" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="339" spans="1:35">
@@ -26959,10 +26962,10 @@
         <v>193</v>
       </c>
       <c r="AH339" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI339" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="340" spans="1:35">
@@ -27030,10 +27033,10 @@
         <v>193</v>
       </c>
       <c r="AH340" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI340" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="341" spans="1:35">
@@ -27104,10 +27107,10 @@
         <v>54</v>
       </c>
       <c r="AH341" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI341" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="342" spans="1:35">
@@ -27178,10 +27181,10 @@
         <v>54</v>
       </c>
       <c r="AH342" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI342" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="343" spans="1:35">
@@ -27249,13 +27252,13 @@
         <v>0</v>
       </c>
       <c r="AC343" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AH343" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI343" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="344" spans="1:35">
@@ -27326,10 +27329,10 @@
         <v>170</v>
       </c>
       <c r="AH344" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI344" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="345" spans="1:35">
@@ -27400,10 +27403,10 @@
         <v>170</v>
       </c>
       <c r="AH345" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI345" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="346" spans="1:35">
@@ -27477,10 +27480,10 @@
         <v>175</v>
       </c>
       <c r="AH346" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI346" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="347" spans="1:35">
@@ -27551,10 +27554,10 @@
         <v>176</v>
       </c>
       <c r="AH347" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI347" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="348" spans="1:35">
@@ -27622,10 +27625,10 @@
         <v>182</v>
       </c>
       <c r="AH348" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI348" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="349" spans="1:35">
@@ -27693,10 +27696,10 @@
         <v>182</v>
       </c>
       <c r="AH349" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI349" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="350" spans="1:35">
@@ -27773,10 +27776,10 @@
         <v>179</v>
       </c>
       <c r="AH350" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI350" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="351" spans="1:35">
@@ -27853,10 +27856,10 @@
         <v>184</v>
       </c>
       <c r="AH351" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI351" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="352" spans="1:35">
@@ -27933,10 +27936,10 @@
         <v>179</v>
       </c>
       <c r="AH352" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI352" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="353" spans="1:35">
@@ -28013,10 +28016,10 @@
         <v>179</v>
       </c>
       <c r="AH353" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI353" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="354" spans="1:35">
@@ -28093,10 +28096,10 @@
         <v>178</v>
       </c>
       <c r="AH354" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI354" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="355" spans="1:35">
@@ -28173,10 +28176,10 @@
         <v>183</v>
       </c>
       <c r="AH355" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI355" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="356" spans="1:35">
@@ -28247,10 +28250,10 @@
         <v>183</v>
       </c>
       <c r="AH356" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI356" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="357" spans="1:35">
@@ -28321,10 +28324,10 @@
         <v>186</v>
       </c>
       <c r="AH357" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI357" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="358" spans="1:35">
@@ -28398,10 +28401,10 @@
         <v>186</v>
       </c>
       <c r="AH358" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI358" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="359" spans="1:35">
@@ -28472,10 +28475,10 @@
         <v>187</v>
       </c>
       <c r="AH359" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI359" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="360" spans="1:35">
@@ -28549,10 +28552,10 @@
         <v>189</v>
       </c>
       <c r="AH360" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI360" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="361" spans="1:35">
@@ -28623,10 +28626,10 @@
         <v>187</v>
       </c>
       <c r="AH361" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI361" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="362" spans="1:35">
@@ -28697,18 +28700,18 @@
         <v>187</v>
       </c>
       <c r="AH362" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI362" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="363" spans="1:35">
       <c r="A363">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B363" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C363" t="s">
         <v>50</v>
@@ -28717,7 +28720,7 @@
         <v>51</v>
       </c>
       <c r="E363" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F363" t="s">
         <v>56</v>
@@ -28744,22 +28747,25 @@
         <v>2026</v>
       </c>
       <c r="R363">
-        <v>18048473</v>
+        <v>18094899</v>
       </c>
       <c r="S363" t="s">
-        <v>187</v>
+        <v>186</v>
+      </c>
+      <c r="T363" t="s">
+        <v>201</v>
       </c>
       <c r="U363" t="s">
         <v>204</v>
       </c>
       <c r="V363" s="1">
-        <v>46282.74485532408</v>
+        <v>46286.59476721065</v>
       </c>
       <c r="W363">
         <v>-2</v>
       </c>
       <c r="X363" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y363" t="s">
         <v>350</v>
@@ -28768,21 +28774,21 @@
         <v>0</v>
       </c>
       <c r="AC363" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AH363" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI363" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="364" spans="1:35">
       <c r="A364">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B364" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C364" t="s">
         <v>50</v>
@@ -28791,25 +28797,25 @@
         <v>51</v>
       </c>
       <c r="E364" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F364" t="s">
         <v>56</v>
       </c>
       <c r="G364">
-        <v>1914</v>
+        <v>7026</v>
       </c>
       <c r="H364">
-        <v>1862</v>
+        <v>0</v>
       </c>
       <c r="I364" t="s">
         <v>62</v>
       </c>
       <c r="J364" t="s">
-        <v>147</v>
+        <v>119</v>
       </c>
       <c r="N364" s="1">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="P364">
         <v>8</v>
@@ -28818,45 +28824,45 @@
         <v>2026</v>
       </c>
       <c r="R364">
-        <v>17988591</v>
+        <v>18048473</v>
       </c>
       <c r="S364" t="s">
-        <v>186</v>
-      </c>
-      <c r="T364" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="U364" t="s">
         <v>204</v>
       </c>
       <c r="V364" s="1">
-        <v>46283.39413969908</v>
+        <v>46282.74485532408</v>
       </c>
       <c r="W364">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="X364" t="s">
-        <v>206</v>
+        <v>207</v>
+      </c>
+      <c r="Y364" t="s">
+        <v>351</v>
       </c>
       <c r="AB364">
         <v>0</v>
       </c>
       <c r="AC364" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AH364" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI364" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="365" spans="1:35">
       <c r="A365">
-        <v>5417</v>
+        <v>6548</v>
       </c>
       <c r="B365" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C365" t="s">
         <v>50</v>
@@ -28871,22 +28877,19 @@
         <v>56</v>
       </c>
       <c r="G365">
-        <v>6759</v>
+        <v>1914</v>
       </c>
       <c r="H365">
-        <v>1788</v>
+        <v>1862</v>
       </c>
       <c r="I365" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J365" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N365" s="1">
-        <v>46289</v>
-      </c>
-      <c r="O365" t="s">
-        <v>168</v>
+        <v>46286</v>
       </c>
       <c r="P365">
         <v>8</v>
@@ -28895,48 +28898,45 @@
         <v>2026</v>
       </c>
       <c r="R365">
-        <v>17399190</v>
+        <v>17988591</v>
       </c>
       <c r="S365" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="T365" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="U365" t="s">
         <v>204</v>
       </c>
       <c r="V365" s="1">
-        <v>46283.54620269676</v>
+        <v>46283.39413969908</v>
       </c>
       <c r="W365">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="X365" t="s">
-        <v>212</v>
-      </c>
-      <c r="Y365" t="s">
-        <v>351</v>
+        <v>206</v>
       </c>
       <c r="AB365">
         <v>0</v>
       </c>
       <c r="AC365" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="AH365" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI365" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="366" spans="1:35">
       <c r="A366">
-        <v>6704</v>
+        <v>5417</v>
       </c>
       <c r="B366" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C366" t="s">
         <v>50</v>
@@ -28951,22 +28951,22 @@
         <v>56</v>
       </c>
       <c r="G366">
-        <v>11874</v>
+        <v>6759</v>
       </c>
       <c r="H366">
-        <v>0</v>
+        <v>1788</v>
       </c>
       <c r="I366" t="s">
         <v>63</v>
       </c>
       <c r="J366" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="N366" s="1">
-        <v>46281</v>
+        <v>46289</v>
       </c>
       <c r="O366" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="P366">
         <v>8</v>
@@ -28975,7 +28975,7 @@
         <v>2026</v>
       </c>
       <c r="R366">
-        <v>18273589</v>
+        <v>17399190</v>
       </c>
       <c r="S366" t="s">
         <v>191</v>
@@ -28984,16 +28984,16 @@
         <v>202</v>
       </c>
       <c r="U366" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="V366" s="1">
-        <v>46282.70138376157</v>
+        <v>46283.54620269676</v>
       </c>
       <c r="W366">
-        <v>5</v>
+        <v>-3</v>
       </c>
       <c r="X366" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Y366" t="s">
         <v>352</v>
@@ -29008,21 +29008,21 @@
         <v>378</v>
       </c>
       <c r="AI366" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="367" spans="1:35">
       <c r="A367">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B367" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C367" t="s">
         <v>50</v>
       </c>
       <c r="D367" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E367" t="s">
         <v>54</v>
@@ -29055,7 +29055,7 @@
         <v>2026</v>
       </c>
       <c r="R367">
-        <v>18239293</v>
+        <v>18273589</v>
       </c>
       <c r="S367" t="s">
         <v>191</v>
@@ -29067,7 +29067,7 @@
         <v>203</v>
       </c>
       <c r="V367" s="1">
-        <v>46282.7013840625</v>
+        <v>46282.70138376157</v>
       </c>
       <c r="W367">
         <v>5</v>
@@ -29076,7 +29076,7 @@
         <v>211</v>
       </c>
       <c r="Y367" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AB367">
         <v>0</v>
@@ -29085,24 +29085,24 @@
         <v>191</v>
       </c>
       <c r="AH367" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI367" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="368" spans="1:35">
       <c r="A368">
-        <v>6703</v>
+        <v>6705</v>
       </c>
       <c r="B368" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C368" t="s">
         <v>50</v>
       </c>
       <c r="D368" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E368" t="s">
         <v>54</v>
@@ -29111,7 +29111,7 @@
         <v>56</v>
       </c>
       <c r="G368">
-        <v>1802</v>
+        <v>11874</v>
       </c>
       <c r="H368">
         <v>0</v>
@@ -29120,10 +29120,13 @@
         <v>63</v>
       </c>
       <c r="J368" t="s">
-        <v>144</v>
+        <v>125</v>
       </c>
       <c r="N368" s="1">
-        <v>46283</v>
+        <v>46281</v>
+      </c>
+      <c r="O368" t="s">
+        <v>164</v>
       </c>
       <c r="P368">
         <v>8</v>
@@ -29132,7 +29135,7 @@
         <v>2026</v>
       </c>
       <c r="R368">
-        <v>17948796</v>
+        <v>18239293</v>
       </c>
       <c r="S368" t="s">
         <v>191</v>
@@ -29141,16 +29144,16 @@
         <v>202</v>
       </c>
       <c r="U368" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="V368" s="1">
-        <v>46283.75077045139</v>
+        <v>46282.7013840625</v>
       </c>
       <c r="W368">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X368" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="Y368" t="s">
         <v>353</v>
@@ -29162,24 +29165,24 @@
         <v>191</v>
       </c>
       <c r="AH368" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI368" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="369" spans="1:35">
       <c r="A369">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B369" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C369" t="s">
         <v>50</v>
       </c>
       <c r="D369" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E369" t="s">
         <v>54</v>
@@ -29202,9 +29205,6 @@
       <c r="N369" s="1">
         <v>46283</v>
       </c>
-      <c r="O369" t="s">
-        <v>169</v>
-      </c>
       <c r="P369">
         <v>8</v>
       </c>
@@ -29212,7 +29212,7 @@
         <v>2026</v>
       </c>
       <c r="R369">
-        <v>18085198</v>
+        <v>17948796</v>
       </c>
       <c r="S369" t="s">
         <v>191</v>
@@ -29221,16 +29221,16 @@
         <v>202</v>
       </c>
       <c r="U369" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="V369" s="1">
-        <v>46286.36164050926</v>
+        <v>46283.75077045139</v>
       </c>
       <c r="W369">
         <v>3</v>
       </c>
       <c r="X369" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="Y369" t="s">
         <v>354</v>
@@ -29242,7 +29242,7 @@
         <v>191</v>
       </c>
       <c r="AH369" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI369" t="s">
         <v>383</v>
@@ -29250,10 +29250,10 @@
     </row>
     <row r="370" spans="1:35">
       <c r="A370">
-        <v>5417</v>
+        <v>6704</v>
       </c>
       <c r="B370" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C370" t="s">
         <v>50</v>
@@ -29268,7 +29268,7 @@
         <v>56</v>
       </c>
       <c r="G370">
-        <v>11286</v>
+        <v>1802</v>
       </c>
       <c r="H370">
         <v>0</v>
@@ -29277,7 +29277,7 @@
         <v>63</v>
       </c>
       <c r="J370" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="N370" s="1">
         <v>46283</v>
@@ -29292,7 +29292,7 @@
         <v>2026</v>
       </c>
       <c r="R370">
-        <v>17399434</v>
+        <v>18085198</v>
       </c>
       <c r="S370" t="s">
         <v>191</v>
@@ -29304,16 +29304,16 @@
         <v>203</v>
       </c>
       <c r="V370" s="1">
-        <v>46286.36164494213</v>
+        <v>46286.36164050926</v>
       </c>
       <c r="W370">
         <v>3</v>
       </c>
       <c r="X370" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Y370" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AB370">
         <v>0</v>
@@ -29322,24 +29322,24 @@
         <v>191</v>
       </c>
       <c r="AH370" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI370" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="371" spans="1:35">
       <c r="A371">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B371" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C371" t="s">
         <v>50</v>
       </c>
       <c r="D371" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E371" t="s">
         <v>54</v>
@@ -29372,7 +29372,7 @@
         <v>2026</v>
       </c>
       <c r="R371">
-        <v>16962464</v>
+        <v>17399434</v>
       </c>
       <c r="S371" t="s">
         <v>191</v>
@@ -29384,16 +29384,16 @@
         <v>203</v>
       </c>
       <c r="V371" s="1">
-        <v>46286.36164826389</v>
+        <v>46286.36164494213</v>
       </c>
       <c r="W371">
         <v>3</v>
       </c>
       <c r="X371" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="Y371" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AB371">
         <v>0</v>
@@ -29402,24 +29402,24 @@
         <v>191</v>
       </c>
       <c r="AH371" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI371" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="372" spans="1:35">
       <c r="A372">
-        <v>6705</v>
+        <v>6404</v>
       </c>
       <c r="B372" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C372" t="s">
         <v>50</v>
       </c>
       <c r="D372" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E372" t="s">
         <v>54</v>
@@ -29428,7 +29428,7 @@
         <v>56</v>
       </c>
       <c r="G372">
-        <v>1805</v>
+        <v>11286</v>
       </c>
       <c r="H372">
         <v>0</v>
@@ -29437,11 +29437,14 @@
         <v>63</v>
       </c>
       <c r="J372" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="N372" s="1">
         <v>46283</v>
       </c>
+      <c r="O372" t="s">
+        <v>169</v>
+      </c>
       <c r="P372">
         <v>8</v>
       </c>
@@ -29449,7 +29452,7 @@
         <v>2026</v>
       </c>
       <c r="R372">
-        <v>17948948</v>
+        <v>16962464</v>
       </c>
       <c r="S372" t="s">
         <v>191</v>
@@ -29458,16 +29461,16 @@
         <v>202</v>
       </c>
       <c r="U372" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="V372" s="1">
-        <v>46283.35452896991</v>
+        <v>46286.36164826389</v>
       </c>
       <c r="W372">
         <v>3</v>
       </c>
       <c r="X372" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="Y372" t="s">
         <v>355</v>
@@ -29479,18 +29482,18 @@
         <v>191</v>
       </c>
       <c r="AH372" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI372" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="373" spans="1:35">
       <c r="A373">
-        <v>6779</v>
+        <v>6705</v>
       </c>
       <c r="B373" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C373" t="s">
         <v>50</v>
@@ -29526,7 +29529,7 @@
         <v>2026</v>
       </c>
       <c r="R373">
-        <v>18084966</v>
+        <v>17948948</v>
       </c>
       <c r="S373" t="s">
         <v>191</v>
@@ -29538,7 +29541,7 @@
         <v>205</v>
       </c>
       <c r="V373" s="1">
-        <v>46283.35453171296</v>
+        <v>46283.35452896991</v>
       </c>
       <c r="W373">
         <v>3</v>
@@ -29547,7 +29550,7 @@
         <v>211</v>
       </c>
       <c r="Y373" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AB373">
         <v>0</v>
@@ -29556,24 +29559,24 @@
         <v>191</v>
       </c>
       <c r="AH373" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI373" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="374" spans="1:35">
       <c r="A374">
-        <v>5417</v>
+        <v>6779</v>
       </c>
       <c r="B374" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C374" t="s">
         <v>50</v>
       </c>
       <c r="D374" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E374" t="s">
         <v>54</v>
@@ -29582,7 +29585,7 @@
         <v>56</v>
       </c>
       <c r="G374">
-        <v>7025</v>
+        <v>1805</v>
       </c>
       <c r="H374">
         <v>0</v>
@@ -29591,10 +29594,10 @@
         <v>63</v>
       </c>
       <c r="J374" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="N374" s="1">
-        <v>46288</v>
+        <v>46283</v>
       </c>
       <c r="P374">
         <v>8</v>
@@ -29603,7 +29606,7 @@
         <v>2026</v>
       </c>
       <c r="R374">
-        <v>17399280</v>
+        <v>18084966</v>
       </c>
       <c r="S374" t="s">
         <v>191</v>
@@ -29612,16 +29615,16 @@
         <v>202</v>
       </c>
       <c r="U374" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="V374" s="1">
-        <v>46283.38367943287</v>
+        <v>46283.35453171296</v>
       </c>
       <c r="W374">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="X374" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Y374" t="s">
         <v>356</v>
@@ -29633,24 +29636,24 @@
         <v>191</v>
       </c>
       <c r="AH374" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AI374" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="375" spans="1:35">
       <c r="A375">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B375" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C375" t="s">
         <v>50</v>
       </c>
       <c r="D375" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E375" t="s">
         <v>54</v>
@@ -29680,7 +29683,7 @@
         <v>2026</v>
       </c>
       <c r="R375">
-        <v>16962338</v>
+        <v>17399280</v>
       </c>
       <c r="S375" t="s">
         <v>191</v>
@@ -29692,13 +29695,13 @@
         <v>204</v>
       </c>
       <c r="V375" s="1">
-        <v>46282.54038741898</v>
+        <v>46283.38367943287</v>
       </c>
       <c r="W375">
         <v>-2</v>
       </c>
       <c r="X375" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="Y375" t="s">
         <v>357</v>
@@ -29710,48 +29713,45 @@
         <v>191</v>
       </c>
       <c r="AH375" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI375" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="376" spans="1:35">
       <c r="A376">
-        <v>6628</v>
+        <v>6404</v>
       </c>
       <c r="B376" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C376" t="s">
         <v>50</v>
       </c>
       <c r="D376" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E376" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F376" t="s">
         <v>56</v>
       </c>
       <c r="G376">
-        <v>945</v>
+        <v>7025</v>
       </c>
       <c r="H376">
         <v>0</v>
       </c>
       <c r="I376" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J376" t="s">
-        <v>149</v>
+        <v>119</v>
       </c>
       <c r="N376" s="1">
-        <v>46283</v>
-      </c>
-      <c r="O376" t="s">
-        <v>163</v>
+        <v>46288</v>
       </c>
       <c r="P376">
         <v>8</v>
@@ -29760,22 +29760,25 @@
         <v>2026</v>
       </c>
       <c r="R376">
-        <v>16959938</v>
+        <v>16962338</v>
       </c>
       <c r="S376" t="s">
-        <v>192</v>
+        <v>191</v>
+      </c>
+      <c r="T376" t="s">
+        <v>202</v>
       </c>
       <c r="U376" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="V376" s="1">
-        <v>46283.64213659722</v>
+        <v>46282.54038741898</v>
       </c>
       <c r="W376">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="X376" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="Y376" t="s">
         <v>358</v>
@@ -29784,21 +29787,21 @@
         <v>0</v>
       </c>
       <c r="AC376" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AH376" t="s">
         <v>378</v>
       </c>
       <c r="AI376" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="377" spans="1:35">
       <c r="A377">
-        <v>6705</v>
+        <v>6628</v>
       </c>
       <c r="B377" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C377" t="s">
         <v>50</v>
@@ -29807,7 +29810,7 @@
         <v>52</v>
       </c>
       <c r="E377" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F377" t="s">
         <v>56</v>
@@ -29837,7 +29840,7 @@
         <v>2026</v>
       </c>
       <c r="R377">
-        <v>17952524</v>
+        <v>16959938</v>
       </c>
       <c r="S377" t="s">
         <v>192</v>
@@ -29846,13 +29849,13 @@
         <v>205</v>
       </c>
       <c r="V377" s="1">
-        <v>46283.65291121528</v>
+        <v>46283.64213659722</v>
       </c>
       <c r="W377">
         <v>3</v>
       </c>
       <c r="X377" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="Y377" t="s">
         <v>359</v>
@@ -29864,18 +29867,18 @@
         <v>192</v>
       </c>
       <c r="AH377" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI377" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="378" spans="1:35">
       <c r="A378">
-        <v>6779</v>
+        <v>6705</v>
       </c>
       <c r="B378" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C378" t="s">
         <v>50</v>
@@ -29914,7 +29917,7 @@
         <v>2026</v>
       </c>
       <c r="R378">
-        <v>18056695</v>
+        <v>17952524</v>
       </c>
       <c r="S378" t="s">
         <v>192</v>
@@ -29923,7 +29926,7 @@
         <v>205</v>
       </c>
       <c r="V378" s="1">
-        <v>46283.65291194445</v>
+        <v>46283.65291121528</v>
       </c>
       <c r="W378">
         <v>3</v>
@@ -29932,7 +29935,7 @@
         <v>211</v>
       </c>
       <c r="Y378" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AB378">
         <v>0</v>
@@ -29941,18 +29944,18 @@
         <v>192</v>
       </c>
       <c r="AH378" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI378" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="379" spans="1:35">
       <c r="A379">
-        <v>6945</v>
+        <v>6779</v>
       </c>
       <c r="B379" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C379" t="s">
         <v>50</v>
@@ -29964,7 +29967,7 @@
         <v>54</v>
       </c>
       <c r="F379" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G379">
         <v>945</v>
@@ -29982,7 +29985,7 @@
         <v>46283</v>
       </c>
       <c r="O379" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="P379">
         <v>8</v>
@@ -29991,22 +29994,22 @@
         <v>2026</v>
       </c>
       <c r="R379">
-        <v>18164487</v>
+        <v>18056695</v>
       </c>
       <c r="S379" t="s">
         <v>192</v>
       </c>
       <c r="U379" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="V379" s="1">
-        <v>46286.39955256944</v>
+        <v>46283.65291194445</v>
       </c>
       <c r="W379">
         <v>3</v>
       </c>
       <c r="X379" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Y379" t="s">
         <v>360</v>
@@ -30018,7 +30021,7 @@
         <v>192</v>
       </c>
       <c r="AH379" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI379" t="s">
         <v>383</v>
@@ -30026,25 +30029,25 @@
     </row>
     <row r="380" spans="1:35">
       <c r="A380">
-        <v>5417</v>
+        <v>6945</v>
       </c>
       <c r="B380" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C380" t="s">
         <v>50</v>
       </c>
       <c r="D380" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E380" t="s">
         <v>54</v>
       </c>
       <c r="F380" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G380">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H380">
         <v>0</v>
@@ -30053,11 +30056,14 @@
         <v>64</v>
       </c>
       <c r="J380" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N380" s="1">
         <v>46283</v>
       </c>
+      <c r="O380" t="s">
+        <v>169</v>
+      </c>
       <c r="P380">
         <v>8</v>
       </c>
@@ -30065,7 +30071,7 @@
         <v>2026</v>
       </c>
       <c r="R380">
-        <v>17398869</v>
+        <v>18164487</v>
       </c>
       <c r="S380" t="s">
         <v>192</v>
@@ -30074,13 +30080,13 @@
         <v>203</v>
       </c>
       <c r="V380" s="1">
-        <v>46286.42397924769</v>
+        <v>46286.39955256944</v>
       </c>
       <c r="W380">
         <v>3</v>
       </c>
       <c r="X380" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="Y380" t="s">
         <v>361</v>
@@ -30092,24 +30098,24 @@
         <v>192</v>
       </c>
       <c r="AH380" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI380" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="381" spans="1:35">
       <c r="A381">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B381" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C381" t="s">
         <v>50</v>
       </c>
       <c r="D381" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E381" t="s">
         <v>54</v>
@@ -30139,7 +30145,7 @@
         <v>2026</v>
       </c>
       <c r="R381">
-        <v>16962093</v>
+        <v>17398869</v>
       </c>
       <c r="S381" t="s">
         <v>192</v>
@@ -30148,16 +30154,16 @@
         <v>203</v>
       </c>
       <c r="V381" s="1">
-        <v>46286.42389136574</v>
+        <v>46286.42397924769</v>
       </c>
       <c r="W381">
         <v>3</v>
       </c>
       <c r="X381" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="Y381" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AB381">
         <v>0</v>
@@ -30166,27 +30172,27 @@
         <v>192</v>
       </c>
       <c r="AH381" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI381" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="382" spans="1:35">
       <c r="A382">
-        <v>6627</v>
+        <v>6404</v>
       </c>
       <c r="B382" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="C382" t="s">
         <v>50</v>
       </c>
       <c r="D382" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E382" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F382" t="s">
         <v>56</v>
@@ -30206,9 +30212,6 @@
       <c r="N382" s="1">
         <v>46283</v>
       </c>
-      <c r="O382" t="s">
-        <v>163</v>
-      </c>
       <c r="P382">
         <v>8</v>
       </c>
@@ -30216,25 +30219,25 @@
         <v>2026</v>
       </c>
       <c r="R382">
-        <v>17042272</v>
+        <v>16962093</v>
       </c>
       <c r="S382" t="s">
         <v>192</v>
       </c>
       <c r="U382" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="V382" s="1">
-        <v>46283.67999300926</v>
+        <v>46286.42389136574</v>
       </c>
       <c r="W382">
         <v>3</v>
       </c>
       <c r="X382" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="Y382" t="s">
-        <v>318</v>
+        <v>362</v>
       </c>
       <c r="AB382">
         <v>0</v>
@@ -30243,27 +30246,27 @@
         <v>192</v>
       </c>
       <c r="AH382" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI382" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="383" spans="1:35">
       <c r="A383">
-        <v>6703</v>
+        <v>6627</v>
       </c>
       <c r="B383" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C383" t="s">
         <v>50</v>
       </c>
       <c r="D383" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E383" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F383" t="s">
         <v>56</v>
@@ -30284,7 +30287,7 @@
         <v>46283</v>
       </c>
       <c r="O383" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="P383">
         <v>8</v>
@@ -30293,25 +30296,25 @@
         <v>2026</v>
       </c>
       <c r="R383">
-        <v>17941132</v>
+        <v>17042272</v>
       </c>
       <c r="S383" t="s">
         <v>192</v>
       </c>
       <c r="U383" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="V383" s="1">
-        <v>46286.42398471065</v>
+        <v>46283.67999300926</v>
       </c>
       <c r="W383">
         <v>3</v>
       </c>
       <c r="X383" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="Y383" t="s">
-        <v>362</v>
+        <v>318</v>
       </c>
       <c r="AB383">
         <v>0</v>
@@ -30320,7 +30323,7 @@
         <v>192</v>
       </c>
       <c r="AH383" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI383" t="s">
         <v>383</v>
@@ -30328,16 +30331,16 @@
     </row>
     <row r="384" spans="1:35">
       <c r="A384">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B384" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C384" t="s">
         <v>50</v>
       </c>
       <c r="D384" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E384" t="s">
         <v>54</v>
@@ -30360,6 +30363,9 @@
       <c r="N384" s="1">
         <v>46283</v>
       </c>
+      <c r="O384" t="s">
+        <v>169</v>
+      </c>
       <c r="P384">
         <v>8</v>
       </c>
@@ -30367,7 +30373,7 @@
         <v>2026</v>
       </c>
       <c r="R384">
-        <v>17952325</v>
+        <v>17941132</v>
       </c>
       <c r="S384" t="s">
         <v>192</v>
@@ -30376,13 +30382,13 @@
         <v>203</v>
       </c>
       <c r="V384" s="1">
-        <v>46286.42398568287</v>
+        <v>46286.42398471065</v>
       </c>
       <c r="W384">
         <v>3</v>
       </c>
       <c r="X384" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="Y384" t="s">
         <v>363</v>
@@ -30394,30 +30400,30 @@
         <v>192</v>
       </c>
       <c r="AH384" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI384" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="385" spans="1:35">
       <c r="A385">
-        <v>6945</v>
+        <v>6704</v>
       </c>
       <c r="B385" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C385" t="s">
         <v>50</v>
       </c>
       <c r="D385" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E385" t="s">
         <v>54</v>
       </c>
       <c r="F385" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G385">
         <v>946</v>
@@ -30434,9 +30440,6 @@
       <c r="N385" s="1">
         <v>46283</v>
       </c>
-      <c r="O385" t="s">
-        <v>163</v>
-      </c>
       <c r="P385">
         <v>8</v>
       </c>
@@ -30444,25 +30447,25 @@
         <v>2026</v>
       </c>
       <c r="R385">
-        <v>18164494</v>
+        <v>17952325</v>
       </c>
       <c r="S385" t="s">
         <v>192</v>
       </c>
       <c r="U385" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="V385" s="1">
-        <v>46283.67625043981</v>
+        <v>46286.42398568287</v>
       </c>
       <c r="W385">
         <v>3</v>
       </c>
       <c r="X385" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Y385" t="s">
-        <v>318</v>
+        <v>364</v>
       </c>
       <c r="AB385">
         <v>0</v>
@@ -30471,18 +30474,18 @@
         <v>192</v>
       </c>
       <c r="AH385" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI385" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="386" spans="1:35">
       <c r="A386">
-        <v>6705</v>
+        <v>6945</v>
       </c>
       <c r="B386" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="C386" t="s">
         <v>50</v>
@@ -30494,10 +30497,10 @@
         <v>54</v>
       </c>
       <c r="F386" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G386">
-        <v>7022</v>
+        <v>946</v>
       </c>
       <c r="H386">
         <v>0</v>
@@ -30506,7 +30509,7 @@
         <v>64</v>
       </c>
       <c r="J386" t="s">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="N386" s="1">
         <v>46283</v>
@@ -30521,7 +30524,7 @@
         <v>2026</v>
       </c>
       <c r="R386">
-        <v>17952601</v>
+        <v>18164494</v>
       </c>
       <c r="S386" t="s">
         <v>192</v>
@@ -30530,13 +30533,13 @@
         <v>205</v>
       </c>
       <c r="V386" s="1">
-        <v>46283.38329579861</v>
+        <v>46283.67625043981</v>
       </c>
       <c r="W386">
         <v>3</v>
       </c>
       <c r="X386" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="Y386" t="s">
         <v>318</v>
@@ -30548,24 +30551,24 @@
         <v>192</v>
       </c>
       <c r="AH386" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AI386" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="387" spans="1:35">
       <c r="A387">
-        <v>5417</v>
+        <v>6705</v>
       </c>
       <c r="B387" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C387" t="s">
         <v>50</v>
       </c>
       <c r="D387" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E387" t="s">
         <v>54</v>
@@ -30574,7 +30577,7 @@
         <v>56</v>
       </c>
       <c r="G387">
-        <v>9086</v>
+        <v>7022</v>
       </c>
       <c r="H387">
         <v>0</v>
@@ -30583,22 +30586,22 @@
         <v>64</v>
       </c>
       <c r="J387" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="N387" s="1">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="O387" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="P387">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q387">
         <v>2026</v>
       </c>
       <c r="R387">
-        <v>17399363</v>
+        <v>17952601</v>
       </c>
       <c r="S387" t="s">
         <v>192</v>
@@ -30607,16 +30610,16 @@
         <v>205</v>
       </c>
       <c r="V387" s="1">
-        <v>46282.36440621527</v>
+        <v>46283.38329579861</v>
       </c>
       <c r="W387">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X387" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Y387" t="s">
-        <v>364</v>
+        <v>318</v>
       </c>
       <c r="AB387">
         <v>0</v>
@@ -30628,21 +30631,21 @@
         <v>379</v>
       </c>
       <c r="AI387" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="388" spans="1:35">
       <c r="A388">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B388" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C388" t="s">
         <v>50</v>
       </c>
       <c r="D388" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E388" t="s">
         <v>54</v>
@@ -30675,7 +30678,7 @@
         <v>2026</v>
       </c>
       <c r="R388">
-        <v>16962380</v>
+        <v>17399363</v>
       </c>
       <c r="S388" t="s">
         <v>192</v>
@@ -30684,16 +30687,16 @@
         <v>205</v>
       </c>
       <c r="V388" s="1">
-        <v>46282.36462596065</v>
+        <v>46282.36440621527</v>
       </c>
       <c r="W388">
         <v>4</v>
       </c>
       <c r="X388" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="Y388" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AB388">
         <v>0</v>
@@ -30702,24 +30705,24 @@
         <v>192</v>
       </c>
       <c r="AH388" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI388" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="389" spans="1:35">
       <c r="A389">
-        <v>6486</v>
+        <v>6404</v>
       </c>
       <c r="B389" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C389" t="s">
         <v>50</v>
       </c>
       <c r="D389" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E389" t="s">
         <v>54</v>
@@ -30752,7 +30755,7 @@
         <v>2026</v>
       </c>
       <c r="R389">
-        <v>16976270</v>
+        <v>16962380</v>
       </c>
       <c r="S389" t="s">
         <v>192</v>
@@ -30761,16 +30764,16 @@
         <v>205</v>
       </c>
       <c r="V389" s="1">
-        <v>46282.36464421296</v>
+        <v>46282.36462596065</v>
       </c>
       <c r="W389">
         <v>4</v>
       </c>
       <c r="X389" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Y389" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AB389">
         <v>0</v>
@@ -30779,18 +30782,18 @@
         <v>192</v>
       </c>
       <c r="AH389" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI389" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="390" spans="1:35">
       <c r="A390">
-        <v>6548</v>
+        <v>6486</v>
       </c>
       <c r="B390" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C390" t="s">
         <v>50</v>
@@ -30829,7 +30832,7 @@
         <v>2026</v>
       </c>
       <c r="R390">
-        <v>17222865</v>
+        <v>16976270</v>
       </c>
       <c r="S390" t="s">
         <v>192</v>
@@ -30838,16 +30841,16 @@
         <v>205</v>
       </c>
       <c r="V390" s="1">
-        <v>46282.36467337963</v>
+        <v>46282.36464421296</v>
       </c>
       <c r="W390">
         <v>4</v>
       </c>
       <c r="X390" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="Y390" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AB390">
         <v>0</v>
@@ -30856,18 +30859,18 @@
         <v>192</v>
       </c>
       <c r="AH390" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI390" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="391" spans="1:35">
       <c r="A391">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B391" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C391" t="s">
         <v>50</v>
@@ -30876,7 +30879,7 @@
         <v>51</v>
       </c>
       <c r="E391" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F391" t="s">
         <v>56</v>
@@ -30906,7 +30909,7 @@
         <v>2026</v>
       </c>
       <c r="R391">
-        <v>17042587</v>
+        <v>17222865</v>
       </c>
       <c r="S391" t="s">
         <v>192</v>
@@ -30915,16 +30918,16 @@
         <v>205</v>
       </c>
       <c r="V391" s="1">
-        <v>46282.36469679398</v>
+        <v>46282.36467337963</v>
       </c>
       <c r="W391">
         <v>4</v>
       </c>
       <c r="X391" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y391" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AB391">
         <v>0</v>
@@ -30933,24 +30936,24 @@
         <v>192</v>
       </c>
       <c r="AH391" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI391" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="392" spans="1:35">
       <c r="A392">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B392" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C392" t="s">
         <v>50</v>
       </c>
       <c r="D392" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E392" t="s">
         <v>55</v>
@@ -30983,7 +30986,7 @@
         <v>2026</v>
       </c>
       <c r="R392">
-        <v>16960074</v>
+        <v>17042587</v>
       </c>
       <c r="S392" t="s">
         <v>192</v>
@@ -30992,7 +30995,7 @@
         <v>205</v>
       </c>
       <c r="V392" s="1">
-        <v>46282.36469869213</v>
+        <v>46282.36469679398</v>
       </c>
       <c r="W392">
         <v>4</v>
@@ -31001,7 +31004,7 @@
         <v>207</v>
       </c>
       <c r="Y392" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AB392">
         <v>0</v>
@@ -31010,27 +31013,27 @@
         <v>192</v>
       </c>
       <c r="AH392" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI392" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="393" spans="1:35">
       <c r="A393">
-        <v>6703</v>
+        <v>6628</v>
       </c>
       <c r="B393" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C393" t="s">
         <v>50</v>
       </c>
       <c r="D393" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E393" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F393" t="s">
         <v>56</v>
@@ -31060,7 +31063,7 @@
         <v>2026</v>
       </c>
       <c r="R393">
-        <v>17941217</v>
+        <v>16960074</v>
       </c>
       <c r="S393" t="s">
         <v>192</v>
@@ -31069,16 +31072,16 @@
         <v>205</v>
       </c>
       <c r="V393" s="1">
-        <v>46282.36473159722</v>
+        <v>46282.36469869213</v>
       </c>
       <c r="W393">
         <v>4</v>
       </c>
       <c r="X393" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="Y393" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AB393">
         <v>0</v>
@@ -31087,24 +31090,24 @@
         <v>192</v>
       </c>
       <c r="AH393" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI393" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="394" spans="1:35">
       <c r="A394">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B394" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C394" t="s">
         <v>50</v>
       </c>
       <c r="D394" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E394" t="s">
         <v>54</v>
@@ -31137,7 +31140,7 @@
         <v>2026</v>
       </c>
       <c r="R394">
-        <v>17952444</v>
+        <v>17941217</v>
       </c>
       <c r="S394" t="s">
         <v>192</v>
@@ -31146,16 +31149,16 @@
         <v>205</v>
       </c>
       <c r="V394" s="1">
-        <v>46282.36473394676</v>
+        <v>46282.36473159722</v>
       </c>
       <c r="W394">
         <v>4</v>
       </c>
       <c r="X394" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="Y394" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AB394">
         <v>0</v>
@@ -31164,24 +31167,24 @@
         <v>192</v>
       </c>
       <c r="AH394" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI394" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="395" spans="1:35">
       <c r="A395">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B395" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C395" t="s">
         <v>50</v>
       </c>
       <c r="D395" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E395" t="s">
         <v>54</v>
@@ -31214,7 +31217,7 @@
         <v>2026</v>
       </c>
       <c r="R395">
-        <v>17952624</v>
+        <v>17952444</v>
       </c>
       <c r="S395" t="s">
         <v>192</v>
@@ -31223,7 +31226,7 @@
         <v>205</v>
       </c>
       <c r="V395" s="1">
-        <v>46282.36473579861</v>
+        <v>46282.36473394676</v>
       </c>
       <c r="W395">
         <v>4</v>
@@ -31232,7 +31235,7 @@
         <v>211</v>
       </c>
       <c r="Y395" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AB395">
         <v>0</v>
@@ -31241,18 +31244,18 @@
         <v>192</v>
       </c>
       <c r="AH395" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI395" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="396" spans="1:35">
       <c r="A396">
-        <v>6779</v>
+        <v>6705</v>
       </c>
       <c r="B396" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C396" t="s">
         <v>50</v>
@@ -31291,7 +31294,7 @@
         <v>2026</v>
       </c>
       <c r="R396">
-        <v>18056801</v>
+        <v>17952624</v>
       </c>
       <c r="S396" t="s">
         <v>192</v>
@@ -31300,7 +31303,7 @@
         <v>205</v>
       </c>
       <c r="V396" s="1">
-        <v>46282.36475297454</v>
+        <v>46282.36473579861</v>
       </c>
       <c r="W396">
         <v>4</v>
@@ -31309,7 +31312,7 @@
         <v>211</v>
       </c>
       <c r="Y396" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AB396">
         <v>0</v>
@@ -31318,18 +31321,18 @@
         <v>192</v>
       </c>
       <c r="AH396" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI396" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="397" spans="1:35">
       <c r="A397">
-        <v>6945</v>
+        <v>6779</v>
       </c>
       <c r="B397" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C397" t="s">
         <v>50</v>
@@ -31341,7 +31344,7 @@
         <v>54</v>
       </c>
       <c r="F397" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G397">
         <v>9086</v>
@@ -31368,7 +31371,7 @@
         <v>2026</v>
       </c>
       <c r="R397">
-        <v>18164551</v>
+        <v>18056801</v>
       </c>
       <c r="S397" t="s">
         <v>192</v>
@@ -31377,16 +31380,16 @@
         <v>205</v>
       </c>
       <c r="V397" s="1">
-        <v>46282.36486408565</v>
+        <v>46282.36475297454</v>
       </c>
       <c r="W397">
         <v>4</v>
       </c>
       <c r="X397" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Y397" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AB397">
         <v>0</v>
@@ -31395,24 +31398,24 @@
         <v>192</v>
       </c>
       <c r="AH397" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI397" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="398" spans="1:35">
       <c r="A398">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B398" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C398" t="s">
         <v>50</v>
       </c>
       <c r="D398" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E398" t="s">
         <v>54</v>
@@ -31445,7 +31448,7 @@
         <v>2026</v>
       </c>
       <c r="R398">
-        <v>18178187</v>
+        <v>18164551</v>
       </c>
       <c r="S398" t="s">
         <v>192</v>
@@ -31454,13 +31457,13 @@
         <v>205</v>
       </c>
       <c r="V398" s="1">
-        <v>46282.36487561343</v>
+        <v>46282.36486408565</v>
       </c>
       <c r="W398">
         <v>4</v>
       </c>
       <c r="X398" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Y398" t="s">
         <v>365</v>
@@ -31472,24 +31475,24 @@
         <v>192</v>
       </c>
       <c r="AH398" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI398" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="399" spans="1:35">
       <c r="A399">
-        <v>6962</v>
+        <v>6949</v>
       </c>
       <c r="B399" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C399" t="s">
         <v>50</v>
       </c>
       <c r="D399" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E399" t="s">
         <v>54</v>
@@ -31522,7 +31525,7 @@
         <v>2026</v>
       </c>
       <c r="R399">
-        <v>18188774</v>
+        <v>18178187</v>
       </c>
       <c r="S399" t="s">
         <v>192</v>
@@ -31531,16 +31534,16 @@
         <v>205</v>
       </c>
       <c r="V399" s="1">
-        <v>46282.36486778935</v>
+        <v>46282.36487561343</v>
       </c>
       <c r="W399">
         <v>4</v>
       </c>
       <c r="X399" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="Y399" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AB399">
         <v>0</v>
@@ -31549,18 +31552,18 @@
         <v>192</v>
       </c>
       <c r="AH399" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI399" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="400" spans="1:35">
       <c r="A400">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B400" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C400" t="s">
         <v>50</v>
@@ -31599,7 +31602,7 @@
         <v>2026</v>
       </c>
       <c r="R400">
-        <v>18188680</v>
+        <v>18188774</v>
       </c>
       <c r="S400" t="s">
         <v>192</v>
@@ -31608,7 +31611,7 @@
         <v>205</v>
       </c>
       <c r="V400" s="1">
-        <v>46282.36486851852</v>
+        <v>46282.36486778935</v>
       </c>
       <c r="W400">
         <v>4</v>
@@ -31617,7 +31620,7 @@
         <v>210</v>
       </c>
       <c r="Y400" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AB400">
         <v>0</v>
@@ -31626,33 +31629,33 @@
         <v>192</v>
       </c>
       <c r="AH400" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI400" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="401" spans="1:35">
       <c r="A401">
-        <v>5417</v>
+        <v>6963</v>
       </c>
       <c r="B401" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C401" t="s">
         <v>50</v>
       </c>
       <c r="D401" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E401" t="s">
         <v>54</v>
       </c>
       <c r="F401" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G401">
-        <v>940</v>
+        <v>9086</v>
       </c>
       <c r="H401">
         <v>0</v>
@@ -31661,13 +31664,13 @@
         <v>64</v>
       </c>
       <c r="J401" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N401" s="1">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="O401" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="P401">
         <v>9</v>
@@ -31676,25 +31679,25 @@
         <v>2026</v>
       </c>
       <c r="R401">
-        <v>17398840</v>
+        <v>18188680</v>
       </c>
       <c r="S401" t="s">
         <v>192</v>
       </c>
       <c r="U401" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="V401" s="1">
-        <v>46286.45925082176</v>
+        <v>46282.36486851852</v>
       </c>
       <c r="W401">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X401" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="Y401" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AB401">
         <v>0</v>
@@ -31703,7 +31706,7 @@
         <v>192</v>
       </c>
       <c r="AH401" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI401" t="s">
         <v>383</v>
@@ -31711,16 +31714,16 @@
     </row>
     <row r="402" spans="1:35">
       <c r="A402">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B402" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C402" t="s">
         <v>50</v>
       </c>
       <c r="D402" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E402" t="s">
         <v>54</v>
@@ -31744,7 +31747,7 @@
         <v>46283</v>
       </c>
       <c r="O402" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="P402">
         <v>9</v>
@@ -31753,22 +31756,22 @@
         <v>2026</v>
       </c>
       <c r="R402">
-        <v>16962074</v>
+        <v>17398840</v>
       </c>
       <c r="S402" t="s">
         <v>192</v>
       </c>
       <c r="U402" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="V402" s="1">
-        <v>46282.79619427084</v>
+        <v>46286.45925082176</v>
       </c>
       <c r="W402">
         <v>3</v>
       </c>
       <c r="X402" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="Y402" t="s">
         <v>367</v>
@@ -31780,24 +31783,24 @@
         <v>192</v>
       </c>
       <c r="AH402" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI402" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="403" spans="1:35">
       <c r="A403">
-        <v>6486</v>
+        <v>6404</v>
       </c>
       <c r="B403" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C403" t="s">
         <v>50</v>
       </c>
       <c r="D403" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E403" t="s">
         <v>54</v>
@@ -31830,7 +31833,7 @@
         <v>2026</v>
       </c>
       <c r="R403">
-        <v>16975871</v>
+        <v>16962074</v>
       </c>
       <c r="S403" t="s">
         <v>192</v>
@@ -31839,16 +31842,16 @@
         <v>204</v>
       </c>
       <c r="V403" s="1">
-        <v>46282.79620872685</v>
+        <v>46282.79619427084</v>
       </c>
       <c r="W403">
         <v>3</v>
       </c>
       <c r="X403" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Y403" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AB403">
         <v>0</v>
@@ -31857,18 +31860,18 @@
         <v>192</v>
       </c>
       <c r="AH403" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI403" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="404" spans="1:35">
       <c r="A404">
-        <v>6548</v>
+        <v>6486</v>
       </c>
       <c r="B404" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C404" t="s">
         <v>50</v>
@@ -31907,7 +31910,7 @@
         <v>2026</v>
       </c>
       <c r="R404">
-        <v>17222366</v>
+        <v>16975871</v>
       </c>
       <c r="S404" t="s">
         <v>192</v>
@@ -31916,16 +31919,16 @@
         <v>204</v>
       </c>
       <c r="V404" s="1">
-        <v>46282.79623825232</v>
+        <v>46282.79620872685</v>
       </c>
       <c r="W404">
         <v>3</v>
       </c>
       <c r="X404" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="Y404" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AB404">
         <v>0</v>
@@ -31934,18 +31937,18 @@
         <v>192</v>
       </c>
       <c r="AH404" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI404" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="405" spans="1:35">
       <c r="A405">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B405" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C405" t="s">
         <v>50</v>
@@ -31954,7 +31957,7 @@
         <v>51</v>
       </c>
       <c r="E405" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F405" t="s">
         <v>56</v>
@@ -31984,7 +31987,7 @@
         <v>2026</v>
       </c>
       <c r="R405">
-        <v>17042221</v>
+        <v>17222366</v>
       </c>
       <c r="S405" t="s">
         <v>192</v>
@@ -31993,16 +31996,16 @@
         <v>204</v>
       </c>
       <c r="V405" s="1">
-        <v>46282.7962541551</v>
+        <v>46282.79623825232</v>
       </c>
       <c r="W405">
         <v>3</v>
       </c>
       <c r="X405" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y405" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AB405">
         <v>0</v>
@@ -32011,24 +32014,24 @@
         <v>192</v>
       </c>
       <c r="AH405" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI405" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="406" spans="1:35">
       <c r="A406">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B406" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C406" t="s">
         <v>50</v>
       </c>
       <c r="D406" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E406" t="s">
         <v>55</v>
@@ -32061,7 +32064,7 @@
         <v>2026</v>
       </c>
       <c r="R406">
-        <v>16959926</v>
+        <v>17042221</v>
       </c>
       <c r="S406" t="s">
         <v>192</v>
@@ -32070,7 +32073,7 @@
         <v>204</v>
       </c>
       <c r="V406" s="1">
-        <v>46282.7962703125</v>
+        <v>46282.7962541551</v>
       </c>
       <c r="W406">
         <v>3</v>
@@ -32079,7 +32082,7 @@
         <v>207</v>
       </c>
       <c r="Y406" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AB406">
         <v>0</v>
@@ -32088,27 +32091,27 @@
         <v>192</v>
       </c>
       <c r="AH406" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI406" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="407" spans="1:35">
       <c r="A407">
-        <v>6703</v>
+        <v>6628</v>
       </c>
       <c r="B407" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C407" t="s">
         <v>50</v>
       </c>
       <c r="D407" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E407" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F407" t="s">
         <v>56</v>
@@ -32138,7 +32141,7 @@
         <v>2026</v>
       </c>
       <c r="R407">
-        <v>17941112</v>
+        <v>16959926</v>
       </c>
       <c r="S407" t="s">
         <v>192</v>
@@ -32147,16 +32150,16 @@
         <v>204</v>
       </c>
       <c r="V407" s="1">
-        <v>46282.79628381944</v>
+        <v>46282.7962703125</v>
       </c>
       <c r="W407">
         <v>3</v>
       </c>
       <c r="X407" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="Y407" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AB407">
         <v>0</v>
@@ -32165,24 +32168,24 @@
         <v>192</v>
       </c>
       <c r="AH407" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI407" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="408" spans="1:35">
       <c r="A408">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B408" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C408" t="s">
         <v>50</v>
       </c>
       <c r="D408" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E408" t="s">
         <v>54</v>
@@ -32215,7 +32218,7 @@
         <v>2026</v>
       </c>
       <c r="R408">
-        <v>17952292</v>
+        <v>17941112</v>
       </c>
       <c r="S408" t="s">
         <v>192</v>
@@ -32224,16 +32227,16 @@
         <v>204</v>
       </c>
       <c r="V408" s="1">
-        <v>46282.79630119213</v>
+        <v>46282.79628381944</v>
       </c>
       <c r="W408">
         <v>3</v>
       </c>
       <c r="X408" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="Y408" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AB408">
         <v>0</v>
@@ -32242,24 +32245,24 @@
         <v>192</v>
       </c>
       <c r="AH408" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI408" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="409" spans="1:35">
       <c r="A409">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B409" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C409" t="s">
         <v>50</v>
       </c>
       <c r="D409" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E409" t="s">
         <v>54</v>
@@ -32292,7 +32295,7 @@
         <v>2026</v>
       </c>
       <c r="R409">
-        <v>17952491</v>
+        <v>17952292</v>
       </c>
       <c r="S409" t="s">
         <v>192</v>
@@ -32301,7 +32304,7 @@
         <v>204</v>
       </c>
       <c r="V409" s="1">
-        <v>46282.79631224537</v>
+        <v>46282.79630119213</v>
       </c>
       <c r="W409">
         <v>3</v>
@@ -32310,7 +32313,7 @@
         <v>211</v>
       </c>
       <c r="Y409" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AB409">
         <v>0</v>
@@ -32319,18 +32322,18 @@
         <v>192</v>
       </c>
       <c r="AH409" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI409" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="410" spans="1:35">
       <c r="A410">
-        <v>6945</v>
+        <v>6705</v>
       </c>
       <c r="B410" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C410" t="s">
         <v>50</v>
@@ -32342,7 +32345,7 @@
         <v>54</v>
       </c>
       <c r="F410" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G410">
         <v>940</v>
@@ -32369,7 +32372,7 @@
         <v>2026</v>
       </c>
       <c r="R410">
-        <v>18164473</v>
+        <v>17952491</v>
       </c>
       <c r="S410" t="s">
         <v>192</v>
@@ -32378,13 +32381,13 @@
         <v>204</v>
       </c>
       <c r="V410" s="1">
-        <v>46282.79637734954</v>
+        <v>46282.79631224537</v>
       </c>
       <c r="W410">
         <v>3</v>
       </c>
       <c r="X410" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Y410" t="s">
         <v>368</v>
@@ -32396,24 +32399,24 @@
         <v>192</v>
       </c>
       <c r="AH410" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI410" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="411" spans="1:35">
       <c r="A411">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B411" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C411" t="s">
         <v>50</v>
       </c>
       <c r="D411" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E411" t="s">
         <v>54</v>
@@ -32446,7 +32449,7 @@
         <v>2026</v>
       </c>
       <c r="R411">
-        <v>18178120</v>
+        <v>18164473</v>
       </c>
       <c r="S411" t="s">
         <v>192</v>
@@ -32455,16 +32458,16 @@
         <v>204</v>
       </c>
       <c r="V411" s="1">
-        <v>46282.79638922454</v>
+        <v>46282.79637734954</v>
       </c>
       <c r="W411">
         <v>3</v>
       </c>
       <c r="X411" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Y411" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AB411">
         <v>0</v>
@@ -32473,18 +32476,18 @@
         <v>192</v>
       </c>
       <c r="AH411" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI411" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="412" spans="1:35">
       <c r="A412">
-        <v>5417</v>
+        <v>6949</v>
       </c>
       <c r="B412" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C412" t="s">
         <v>50</v>
@@ -32496,19 +32499,19 @@
         <v>54</v>
       </c>
       <c r="F412" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G412">
-        <v>9088</v>
+        <v>940</v>
       </c>
       <c r="H412">
         <v>0</v>
       </c>
       <c r="I412" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J412" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N412" s="1">
         <v>46283</v>
@@ -32523,51 +32526,51 @@
         <v>2026</v>
       </c>
       <c r="R412">
-        <v>17399383</v>
+        <v>18178120</v>
       </c>
       <c r="S412" t="s">
-        <v>54</v>
+        <v>192</v>
       </c>
       <c r="U412" t="s">
         <v>204</v>
       </c>
       <c r="V412" s="1">
-        <v>46282.3651903588</v>
+        <v>46282.79638922454</v>
       </c>
       <c r="W412">
         <v>3</v>
       </c>
       <c r="X412" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="Y412" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AB412">
         <v>0</v>
       </c>
       <c r="AC412" t="s">
-        <v>54</v>
+        <v>192</v>
       </c>
       <c r="AH412" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI412" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="413" spans="1:35">
       <c r="A413">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B413" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C413" t="s">
         <v>50</v>
       </c>
       <c r="D413" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E413" t="s">
         <v>54</v>
@@ -32600,7 +32603,7 @@
         <v>2026</v>
       </c>
       <c r="R413">
-        <v>16962400</v>
+        <v>17399383</v>
       </c>
       <c r="S413" t="s">
         <v>54</v>
@@ -32609,16 +32612,16 @@
         <v>204</v>
       </c>
       <c r="V413" s="1">
-        <v>46282.36525856482</v>
+        <v>46282.3651903588</v>
       </c>
       <c r="W413">
         <v>3</v>
       </c>
       <c r="X413" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="Y413" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AB413">
         <v>0</v>
@@ -32627,24 +32630,24 @@
         <v>54</v>
       </c>
       <c r="AH413" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI413" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="414" spans="1:35">
       <c r="A414">
-        <v>6486</v>
+        <v>6404</v>
       </c>
       <c r="B414" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C414" t="s">
         <v>50</v>
       </c>
       <c r="D414" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E414" t="s">
         <v>54</v>
@@ -32677,7 +32680,7 @@
         <v>2026</v>
       </c>
       <c r="R414">
-        <v>16976290</v>
+        <v>16962400</v>
       </c>
       <c r="S414" t="s">
         <v>54</v>
@@ -32686,16 +32689,16 @@
         <v>204</v>
       </c>
       <c r="V414" s="1">
-        <v>46282.36526855324</v>
+        <v>46282.36525856482</v>
       </c>
       <c r="W414">
         <v>3</v>
       </c>
       <c r="X414" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Y414" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AB414">
         <v>0</v>
@@ -32704,18 +32707,18 @@
         <v>54</v>
       </c>
       <c r="AH414" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI414" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="415" spans="1:35">
       <c r="A415">
-        <v>6548</v>
+        <v>6486</v>
       </c>
       <c r="B415" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C415" t="s">
         <v>50</v>
@@ -32754,7 +32757,7 @@
         <v>2026</v>
       </c>
       <c r="R415">
-        <v>17222899</v>
+        <v>16976290</v>
       </c>
       <c r="S415" t="s">
         <v>54</v>
@@ -32763,16 +32766,16 @@
         <v>204</v>
       </c>
       <c r="V415" s="1">
-        <v>46282.36527959491</v>
+        <v>46282.36526855324</v>
       </c>
       <c r="W415">
         <v>3</v>
       </c>
       <c r="X415" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="Y415" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AB415">
         <v>0</v>
@@ -32781,18 +32784,18 @@
         <v>54</v>
       </c>
       <c r="AH415" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI415" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="416" spans="1:35">
       <c r="A416">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B416" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C416" t="s">
         <v>50</v>
@@ -32801,7 +32804,7 @@
         <v>51</v>
       </c>
       <c r="E416" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F416" t="s">
         <v>56</v>
@@ -32831,51 +32834,51 @@
         <v>2026</v>
       </c>
       <c r="R416">
-        <v>17042627</v>
+        <v>17222899</v>
       </c>
       <c r="S416" t="s">
-        <v>193</v>
+        <v>54</v>
       </c>
       <c r="U416" t="s">
         <v>204</v>
       </c>
       <c r="V416" s="1">
-        <v>46282.36528526621</v>
+        <v>46282.36527959491</v>
       </c>
       <c r="W416">
         <v>3</v>
       </c>
       <c r="X416" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y416" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AB416">
         <v>0</v>
       </c>
       <c r="AC416" t="s">
-        <v>193</v>
+        <v>54</v>
       </c>
       <c r="AH416" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI416" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="417" spans="1:35">
       <c r="A417">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B417" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C417" t="s">
         <v>50</v>
       </c>
       <c r="D417" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E417" t="s">
         <v>55</v>
@@ -32908,16 +32911,16 @@
         <v>2026</v>
       </c>
       <c r="R417">
-        <v>16960098</v>
+        <v>17042627</v>
       </c>
       <c r="S417" t="s">
-        <v>55</v>
+        <v>193</v>
       </c>
       <c r="U417" t="s">
         <v>204</v>
       </c>
       <c r="V417" s="1">
-        <v>46282.36528619213</v>
+        <v>46282.36528526621</v>
       </c>
       <c r="W417">
         <v>3</v>
@@ -32926,36 +32929,36 @@
         <v>207</v>
       </c>
       <c r="Y417" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AB417">
         <v>0</v>
       </c>
       <c r="AC417" t="s">
-        <v>55</v>
+        <v>193</v>
       </c>
       <c r="AH417" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI417" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="418" spans="1:35">
       <c r="A418">
-        <v>6703</v>
+        <v>6628</v>
       </c>
       <c r="B418" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C418" t="s">
         <v>50</v>
       </c>
       <c r="D418" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E418" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F418" t="s">
         <v>56</v>
@@ -32985,51 +32988,51 @@
         <v>2026</v>
       </c>
       <c r="R418">
-        <v>17941237</v>
+        <v>16960098</v>
       </c>
       <c r="S418" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="U418" t="s">
         <v>204</v>
       </c>
       <c r="V418" s="1">
-        <v>46282.36529351852</v>
+        <v>46282.36528619213</v>
       </c>
       <c r="W418">
         <v>3</v>
       </c>
       <c r="X418" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="Y418" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AB418">
         <v>0</v>
       </c>
       <c r="AC418" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AH418" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI418" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="419" spans="1:35">
       <c r="A419">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B419" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C419" t="s">
         <v>50</v>
       </c>
       <c r="D419" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E419" t="s">
         <v>54</v>
@@ -33062,7 +33065,7 @@
         <v>2026</v>
       </c>
       <c r="R419">
-        <v>17952466</v>
+        <v>17941237</v>
       </c>
       <c r="S419" t="s">
         <v>54</v>
@@ -33071,16 +33074,16 @@
         <v>204</v>
       </c>
       <c r="V419" s="1">
-        <v>46282.36529424768</v>
+        <v>46282.36529351852</v>
       </c>
       <c r="W419">
         <v>3</v>
       </c>
       <c r="X419" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="Y419" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AB419">
         <v>0</v>
@@ -33089,24 +33092,24 @@
         <v>54</v>
       </c>
       <c r="AH419" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI419" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="420" spans="1:35">
       <c r="A420">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B420" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C420" t="s">
         <v>50</v>
       </c>
       <c r="D420" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E420" t="s">
         <v>54</v>
@@ -33139,7 +33142,7 @@
         <v>2026</v>
       </c>
       <c r="R420">
-        <v>17952646</v>
+        <v>17952466</v>
       </c>
       <c r="S420" t="s">
         <v>54</v>
@@ -33148,7 +33151,7 @@
         <v>204</v>
       </c>
       <c r="V420" s="1">
-        <v>46282.36529490741</v>
+        <v>46282.36529424768</v>
       </c>
       <c r="W420">
         <v>3</v>
@@ -33157,7 +33160,7 @@
         <v>211</v>
       </c>
       <c r="Y420" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AB420">
         <v>0</v>
@@ -33166,18 +33169,18 @@
         <v>54</v>
       </c>
       <c r="AH420" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI420" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="421" spans="1:35">
       <c r="A421">
-        <v>6779</v>
+        <v>6705</v>
       </c>
       <c r="B421" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C421" t="s">
         <v>50</v>
@@ -33216,16 +33219,16 @@
         <v>2026</v>
       </c>
       <c r="R421">
-        <v>18056821</v>
+        <v>17952646</v>
       </c>
       <c r="S421" t="s">
-        <v>193</v>
+        <v>54</v>
       </c>
       <c r="U421" t="s">
         <v>204</v>
       </c>
       <c r="V421" s="1">
-        <v>46282.36529869213</v>
+        <v>46282.36529490741</v>
       </c>
       <c r="W421">
         <v>3</v>
@@ -33234,27 +33237,27 @@
         <v>211</v>
       </c>
       <c r="Y421" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AB421">
         <v>0</v>
       </c>
       <c r="AC421" t="s">
-        <v>193</v>
+        <v>54</v>
       </c>
       <c r="AH421" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI421" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="422" spans="1:35">
       <c r="A422">
-        <v>6945</v>
+        <v>6779</v>
       </c>
       <c r="B422" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C422" t="s">
         <v>50</v>
@@ -33266,7 +33269,7 @@
         <v>54</v>
       </c>
       <c r="F422" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G422">
         <v>9088</v>
@@ -33293,51 +33296,51 @@
         <v>2026</v>
       </c>
       <c r="R422">
-        <v>18164565</v>
+        <v>18056821</v>
       </c>
       <c r="S422" t="s">
-        <v>54</v>
+        <v>193</v>
       </c>
       <c r="U422" t="s">
         <v>204</v>
       </c>
       <c r="V422" s="1">
-        <v>46282.36531149306</v>
+        <v>46282.36529869213</v>
       </c>
       <c r="W422">
         <v>3</v>
       </c>
       <c r="X422" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Y422" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AB422">
         <v>0</v>
       </c>
       <c r="AC422" t="s">
-        <v>54</v>
+        <v>193</v>
       </c>
       <c r="AH422" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI422" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="423" spans="1:35">
       <c r="A423">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B423" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C423" t="s">
         <v>50</v>
       </c>
       <c r="D423" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E423" t="s">
         <v>54</v>
@@ -33370,22 +33373,22 @@
         <v>2026</v>
       </c>
       <c r="R423">
-        <v>18178199</v>
+        <v>18164565</v>
       </c>
       <c r="S423" t="s">
-        <v>193</v>
+        <v>54</v>
       </c>
       <c r="U423" t="s">
         <v>204</v>
       </c>
       <c r="V423" s="1">
-        <v>46282.36531554398</v>
+        <v>46282.36531149306</v>
       </c>
       <c r="W423">
         <v>3</v>
       </c>
       <c r="X423" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Y423" t="s">
         <v>369</v>
@@ -33394,27 +33397,27 @@
         <v>0</v>
       </c>
       <c r="AC423" t="s">
-        <v>193</v>
+        <v>54</v>
       </c>
       <c r="AH423" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI423" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="424" spans="1:35">
       <c r="A424">
-        <v>6962</v>
+        <v>6949</v>
       </c>
       <c r="B424" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C424" t="s">
         <v>50</v>
       </c>
       <c r="D424" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E424" t="s">
         <v>54</v>
@@ -33447,45 +33450,45 @@
         <v>2026</v>
       </c>
       <c r="R424">
-        <v>18188788</v>
+        <v>18178199</v>
       </c>
       <c r="S424" t="s">
-        <v>54</v>
+        <v>193</v>
       </c>
       <c r="U424" t="s">
         <v>204</v>
       </c>
       <c r="V424" s="1">
-        <v>46282.36531253472</v>
+        <v>46282.36531554398</v>
       </c>
       <c r="W424">
         <v>3</v>
       </c>
       <c r="X424" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="Y424" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AB424">
         <v>0</v>
       </c>
       <c r="AC424" t="s">
-        <v>54</v>
+        <v>193</v>
       </c>
       <c r="AH424" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI424" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="425" spans="1:35">
       <c r="A425">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B425" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C425" t="s">
         <v>50</v>
@@ -33524,7 +33527,7 @@
         <v>2026</v>
       </c>
       <c r="R425">
-        <v>18188694</v>
+        <v>18188788</v>
       </c>
       <c r="S425" t="s">
         <v>54</v>
@@ -33533,7 +33536,7 @@
         <v>204</v>
       </c>
       <c r="V425" s="1">
-        <v>46282.36531288194</v>
+        <v>46282.36531253472</v>
       </c>
       <c r="W425">
         <v>3</v>
@@ -33542,7 +33545,7 @@
         <v>210</v>
       </c>
       <c r="Y425" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AB425">
         <v>0</v>
@@ -33551,33 +33554,33 @@
         <v>54</v>
       </c>
       <c r="AH425" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI425" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="426" spans="1:35">
       <c r="A426">
-        <v>5417</v>
+        <v>6963</v>
       </c>
       <c r="B426" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C426" t="s">
         <v>50</v>
       </c>
       <c r="D426" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E426" t="s">
         <v>54</v>
       </c>
       <c r="F426" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G426">
-        <v>6813</v>
+        <v>9088</v>
       </c>
       <c r="H426">
         <v>0</v>
@@ -33586,13 +33589,13 @@
         <v>65</v>
       </c>
       <c r="J426" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="N426" s="1">
-        <v>46286</v>
+        <v>46283</v>
       </c>
       <c r="O426" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="P426">
         <v>9</v>
@@ -33601,34 +33604,34 @@
         <v>2026</v>
       </c>
       <c r="R426">
-        <v>17399241</v>
+        <v>18188694</v>
       </c>
       <c r="S426" t="s">
         <v>54</v>
       </c>
       <c r="U426" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="V426" s="1">
-        <v>46286.45925106481</v>
+        <v>46282.36531288194</v>
       </c>
       <c r="W426">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X426" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="Y426" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AB426">
         <v>0</v>
       </c>
       <c r="AC426" t="s">
-        <v>192</v>
+        <v>54</v>
       </c>
       <c r="AH426" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI426" t="s">
         <v>383</v>
@@ -33636,16 +33639,16 @@
     </row>
     <row r="427" spans="1:35">
       <c r="A427">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B427" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C427" t="s">
         <v>50</v>
       </c>
       <c r="D427" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E427" t="s">
         <v>54</v>
@@ -33666,10 +33669,10 @@
         <v>154</v>
       </c>
       <c r="N427" s="1">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="O427" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="P427">
         <v>9</v>
@@ -33678,51 +33681,51 @@
         <v>2026</v>
       </c>
       <c r="R427">
-        <v>16962319</v>
+        <v>17399241</v>
       </c>
       <c r="S427" t="s">
         <v>54</v>
       </c>
       <c r="U427" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="V427" s="1">
-        <v>46282.79619331018</v>
+        <v>46286.45925106481</v>
       </c>
       <c r="W427">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X427" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="Y427" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="AB427">
         <v>0</v>
       </c>
       <c r="AC427" t="s">
-        <v>54</v>
+        <v>192</v>
       </c>
       <c r="AH427" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI427" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="428" spans="1:35">
       <c r="A428">
-        <v>6486</v>
+        <v>6404</v>
       </c>
       <c r="B428" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C428" t="s">
         <v>50</v>
       </c>
       <c r="D428" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E428" t="s">
         <v>54</v>
@@ -33755,7 +33758,7 @@
         <v>2026</v>
       </c>
       <c r="R428">
-        <v>16976198</v>
+        <v>16962319</v>
       </c>
       <c r="S428" t="s">
         <v>54</v>
@@ -33764,16 +33767,16 @@
         <v>204</v>
       </c>
       <c r="V428" s="1">
-        <v>46282.79620888889</v>
+        <v>46282.79619331018</v>
       </c>
       <c r="W428">
         <v>3</v>
       </c>
       <c r="X428" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Y428" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AB428">
         <v>0</v>
@@ -33782,18 +33785,18 @@
         <v>54</v>
       </c>
       <c r="AH428" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI428" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="429" spans="1:35">
       <c r="A429">
-        <v>6548</v>
+        <v>6486</v>
       </c>
       <c r="B429" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C429" t="s">
         <v>50</v>
@@ -33832,7 +33835,7 @@
         <v>2026</v>
       </c>
       <c r="R429">
-        <v>17222763</v>
+        <v>16976198</v>
       </c>
       <c r="S429" t="s">
         <v>54</v>
@@ -33841,16 +33844,16 @@
         <v>204</v>
       </c>
       <c r="V429" s="1">
-        <v>46282.79623803241</v>
+        <v>46282.79620888889</v>
       </c>
       <c r="W429">
         <v>3</v>
       </c>
       <c r="X429" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="Y429" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AB429">
         <v>0</v>
@@ -33859,18 +33862,18 @@
         <v>54</v>
       </c>
       <c r="AH429" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI429" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="430" spans="1:35">
       <c r="A430">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B430" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C430" t="s">
         <v>50</v>
@@ -33879,7 +33882,7 @@
         <v>51</v>
       </c>
       <c r="E430" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F430" t="s">
         <v>56</v>
@@ -33909,51 +33912,51 @@
         <v>2026</v>
       </c>
       <c r="R430">
-        <v>17042469</v>
+        <v>17222763</v>
       </c>
       <c r="S430" t="s">
-        <v>193</v>
+        <v>54</v>
       </c>
       <c r="U430" t="s">
         <v>204</v>
       </c>
       <c r="V430" s="1">
-        <v>46282.79625384259</v>
+        <v>46282.79623803241</v>
       </c>
       <c r="W430">
         <v>3</v>
       </c>
       <c r="X430" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Y430" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AB430">
         <v>0</v>
       </c>
       <c r="AC430" t="s">
-        <v>193</v>
+        <v>54</v>
       </c>
       <c r="AH430" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI430" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="431" spans="1:35">
       <c r="A431">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B431" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C431" t="s">
         <v>50</v>
       </c>
       <c r="D431" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E431" t="s">
         <v>55</v>
@@ -33986,16 +33989,16 @@
         <v>2026</v>
       </c>
       <c r="R431">
-        <v>16960013</v>
+        <v>17042469</v>
       </c>
       <c r="S431" t="s">
-        <v>55</v>
+        <v>193</v>
       </c>
       <c r="U431" t="s">
         <v>204</v>
       </c>
       <c r="V431" s="1">
-        <v>46282.79626969907</v>
+        <v>46282.79625384259</v>
       </c>
       <c r="W431">
         <v>3</v>
@@ -34004,36 +34007,36 @@
         <v>207</v>
       </c>
       <c r="Y431" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AB431">
         <v>0</v>
       </c>
       <c r="AC431" t="s">
-        <v>55</v>
+        <v>193</v>
       </c>
       <c r="AH431" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI431" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="432" spans="1:35">
       <c r="A432">
-        <v>6703</v>
+        <v>6628</v>
       </c>
       <c r="B432" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C432" t="s">
         <v>50</v>
       </c>
       <c r="D432" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E432" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F432" t="s">
         <v>56</v>
@@ -34063,51 +34066,51 @@
         <v>2026</v>
       </c>
       <c r="R432">
-        <v>17941197</v>
+        <v>16960013</v>
       </c>
       <c r="S432" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="U432" t="s">
         <v>204</v>
       </c>
       <c r="V432" s="1">
-        <v>46282.79628394676</v>
+        <v>46282.79626969907</v>
       </c>
       <c r="W432">
         <v>3</v>
       </c>
       <c r="X432" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="Y432" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AB432">
         <v>0</v>
       </c>
       <c r="AC432" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AH432" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI432" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="433" spans="1:35">
       <c r="A433">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B433" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C433" t="s">
         <v>50</v>
       </c>
       <c r="D433" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E433" t="s">
         <v>54</v>
@@ -34140,7 +34143,7 @@
         <v>2026</v>
       </c>
       <c r="R433">
-        <v>17952411</v>
+        <v>17941197</v>
       </c>
       <c r="S433" t="s">
         <v>54</v>
@@ -34149,16 +34152,16 @@
         <v>204</v>
       </c>
       <c r="V433" s="1">
-        <v>46282.79630097222</v>
+        <v>46282.79628394676</v>
       </c>
       <c r="W433">
         <v>3</v>
       </c>
       <c r="X433" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="Y433" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AB433">
         <v>0</v>
@@ -34167,24 +34170,24 @@
         <v>54</v>
       </c>
       <c r="AH433" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI433" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="434" spans="1:35">
       <c r="A434">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B434" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C434" t="s">
         <v>50</v>
       </c>
       <c r="D434" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E434" t="s">
         <v>54</v>
@@ -34217,7 +34220,7 @@
         <v>2026</v>
       </c>
       <c r="R434">
-        <v>17952591</v>
+        <v>17952411</v>
       </c>
       <c r="S434" t="s">
         <v>54</v>
@@ -34226,7 +34229,7 @@
         <v>204</v>
       </c>
       <c r="V434" s="1">
-        <v>46282.79631204861</v>
+        <v>46282.79630097222</v>
       </c>
       <c r="W434">
         <v>3</v>
@@ -34235,7 +34238,7 @@
         <v>211</v>
       </c>
       <c r="Y434" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AB434">
         <v>0</v>
@@ -34244,18 +34247,18 @@
         <v>54</v>
       </c>
       <c r="AH434" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI434" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="435" spans="1:35">
       <c r="A435">
-        <v>6945</v>
+        <v>6705</v>
       </c>
       <c r="B435" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C435" t="s">
         <v>50</v>
@@ -34267,7 +34270,7 @@
         <v>54</v>
       </c>
       <c r="F435" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G435">
         <v>6813</v>
@@ -34294,7 +34297,7 @@
         <v>2026</v>
       </c>
       <c r="R435">
-        <v>18164530</v>
+        <v>17952591</v>
       </c>
       <c r="S435" t="s">
         <v>54</v>
@@ -34303,13 +34306,13 @@
         <v>204</v>
       </c>
       <c r="V435" s="1">
-        <v>46282.79637748843</v>
+        <v>46282.79631204861</v>
       </c>
       <c r="W435">
         <v>3</v>
       </c>
       <c r="X435" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Y435" t="s">
         <v>369</v>
@@ -34321,24 +34324,24 @@
         <v>54</v>
       </c>
       <c r="AH435" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI435" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="436" spans="1:35">
       <c r="A436">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B436" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C436" t="s">
         <v>50</v>
       </c>
       <c r="D436" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E436" t="s">
         <v>54</v>
@@ -34371,45 +34374,45 @@
         <v>2026</v>
       </c>
       <c r="R436">
-        <v>18178169</v>
+        <v>18164530</v>
       </c>
       <c r="S436" t="s">
-        <v>193</v>
+        <v>54</v>
       </c>
       <c r="U436" t="s">
         <v>204</v>
       </c>
       <c r="V436" s="1">
-        <v>46282.79638901621</v>
+        <v>46282.79637748843</v>
       </c>
       <c r="W436">
         <v>3</v>
       </c>
       <c r="X436" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Y436" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AB436">
         <v>0</v>
       </c>
       <c r="AC436" t="s">
-        <v>193</v>
+        <v>54</v>
       </c>
       <c r="AH436" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AI436" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="437" spans="1:35">
       <c r="A437">
-        <v>5417</v>
+        <v>6949</v>
       </c>
       <c r="B437" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C437" t="s">
         <v>50</v>
@@ -34421,10 +34424,10 @@
         <v>54</v>
       </c>
       <c r="F437" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G437">
-        <v>7027</v>
+        <v>6813</v>
       </c>
       <c r="H437">
         <v>0</v>
@@ -34433,63 +34436,66 @@
         <v>65</v>
       </c>
       <c r="J437" t="s">
-        <v>119</v>
+        <v>154</v>
       </c>
       <c r="N437" s="1">
-        <v>46289</v>
+        <v>46283</v>
+      </c>
+      <c r="O437" t="s">
+        <v>163</v>
       </c>
       <c r="P437">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q437">
         <v>2026</v>
       </c>
       <c r="R437">
-        <v>17399290</v>
+        <v>18178169</v>
       </c>
       <c r="S437" t="s">
-        <v>54</v>
+        <v>193</v>
       </c>
       <c r="U437" t="s">
         <v>204</v>
       </c>
       <c r="V437" s="1">
-        <v>46283.39832862269</v>
+        <v>46282.79638901621</v>
       </c>
       <c r="W437">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="X437" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="Y437" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AB437">
         <v>0</v>
       </c>
       <c r="AC437" t="s">
-        <v>54</v>
+        <v>193</v>
       </c>
       <c r="AH437" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="AI437" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="438" spans="1:35">
       <c r="A438">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B438" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C438" t="s">
         <v>50</v>
       </c>
       <c r="D438" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E438" t="s">
         <v>54</v>
@@ -34519,7 +34525,7 @@
         <v>2026</v>
       </c>
       <c r="R438">
-        <v>16962348</v>
+        <v>17399290</v>
       </c>
       <c r="S438" t="s">
         <v>54</v>
@@ -34528,13 +34534,13 @@
         <v>204</v>
       </c>
       <c r="V438" s="1">
-        <v>46282.64018086805</v>
+        <v>46283.39832862269</v>
       </c>
       <c r="W438">
         <v>-3</v>
       </c>
       <c r="X438" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="Y438" t="s">
         <v>372</v>
@@ -34546,10 +34552,84 @@
         <v>54</v>
       </c>
       <c r="AH438" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AI438" t="s">
-        <v>382</v>
+        <v>383</v>
+      </c>
+    </row>
+    <row r="439" spans="1:35">
+      <c r="A439">
+        <v>6404</v>
+      </c>
+      <c r="B439" t="s">
+        <v>47</v>
+      </c>
+      <c r="C439" t="s">
+        <v>50</v>
+      </c>
+      <c r="D439" t="s">
+        <v>53</v>
+      </c>
+      <c r="E439" t="s">
+        <v>54</v>
+      </c>
+      <c r="F439" t="s">
+        <v>56</v>
+      </c>
+      <c r="G439">
+        <v>7027</v>
+      </c>
+      <c r="H439">
+        <v>0</v>
+      </c>
+      <c r="I439" t="s">
+        <v>65</v>
+      </c>
+      <c r="J439" t="s">
+        <v>119</v>
+      </c>
+      <c r="N439" s="1">
+        <v>46289</v>
+      </c>
+      <c r="P439">
+        <v>8</v>
+      </c>
+      <c r="Q439">
+        <v>2026</v>
+      </c>
+      <c r="R439">
+        <v>16962348</v>
+      </c>
+      <c r="S439" t="s">
+        <v>54</v>
+      </c>
+      <c r="U439" t="s">
+        <v>204</v>
+      </c>
+      <c r="V439" s="1">
+        <v>46282.64018086805</v>
+      </c>
+      <c r="W439">
+        <v>-3</v>
+      </c>
+      <c r="X439" t="s">
+        <v>216</v>
+      </c>
+      <c r="Y439" t="s">
+        <v>373</v>
+      </c>
+      <c r="AB439">
+        <v>0</v>
+      </c>
+      <c r="AC439" t="s">
+        <v>54</v>
+      </c>
+      <c r="AH439" t="s">
+        <v>378</v>
+      </c>
+      <c r="AI439" t="s">
+        <v>383</v>
       </c>
     </row>
   </sheetData>

--- a/data/base/goias.xlsx
+++ b/data/base/goias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6800" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6851" uniqueCount="420">
   <si>
     <t>CodCliente</t>
   </si>
@@ -643,7 +643,7 @@
     <t>Fernanda Araujo</t>
   </si>
   <si>
-    <t>Karina Santos</t>
+    <t>Karina Fonseca</t>
   </si>
   <si>
     <t>David Bragança</t>
@@ -658,7 +658,7 @@
     <t>Nayara Oliveira</t>
   </si>
   <si>
-    <t>Ricardo Fischer</t>
+    <t>Larice Souza</t>
   </si>
   <si>
     <t>Baixada em atraso</t>
@@ -1092,6 +1092,9 @@
 Reunião confirmada pelo cliente - Data Comentário: 11/09/2026 09:55</t>
   </si>
   <si>
+    <t>Baixado via API integração MGC x Analise Balanço em 23/09/2026 10:25:30. - Data Comentário: 23/09/2026 10:20</t>
+  </si>
+  <si>
     <t>Comentário Colaborador + Previsão de Conclusão. Previsto para: 21/09/2026 - Data Comentário: 18/09/2026 15:23</t>
   </si>
   <si>
@@ -1272,9 +1275,6 @@
   </si>
   <si>
     <t>Karen Ribeiro</t>
-  </si>
-  <si>
-    <t>Karina Fonseca</t>
   </si>
   <si>
     <t>Santos Karina</t>
@@ -1643,7 +1643,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AI467"/>
+  <dimension ref="A1:AI468"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:35">
@@ -2641,7 +2641,7 @@
         <v>0</v>
       </c>
       <c r="AC13" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AH13" t="s">
         <v>413</v>
@@ -2715,7 +2715,7 @@
         <v>0</v>
       </c>
       <c r="AC14" t="s">
-        <v>408</v>
+        <v>209</v>
       </c>
       <c r="AH14" t="s">
         <v>413</v>
@@ -4188,6 +4188,9 @@
       <c r="S34" t="s">
         <v>194</v>
       </c>
+      <c r="T34" t="s">
+        <v>212</v>
+      </c>
       <c r="U34" t="s">
         <v>215</v>
       </c>
@@ -4505,6 +4508,9 @@
       <c r="S38" t="s">
         <v>194</v>
       </c>
+      <c r="T38" t="s">
+        <v>212</v>
+      </c>
       <c r="U38" t="s">
         <v>216</v>
       </c>
@@ -5139,6 +5145,9 @@
       <c r="S46" t="s">
         <v>194</v>
       </c>
+      <c r="T46" t="s">
+        <v>212</v>
+      </c>
       <c r="U46" t="s">
         <v>217</v>
       </c>
@@ -6057,6 +6066,9 @@
       <c r="S58" t="s">
         <v>194</v>
       </c>
+      <c r="T58" t="s">
+        <v>212</v>
+      </c>
       <c r="U58" t="s">
         <v>217</v>
       </c>
@@ -6851,6 +6863,9 @@
       <c r="S68" t="s">
         <v>194</v>
       </c>
+      <c r="T68" t="s">
+        <v>212</v>
+      </c>
       <c r="U68" t="s">
         <v>216</v>
       </c>
@@ -7810,6 +7825,9 @@
       <c r="S81" t="s">
         <v>199</v>
       </c>
+      <c r="T81" t="s">
+        <v>213</v>
+      </c>
       <c r="U81" t="s">
         <v>216</v>
       </c>
@@ -8029,6 +8047,9 @@
       <c r="S84" t="s">
         <v>199</v>
       </c>
+      <c r="T84" t="s">
+        <v>213</v>
+      </c>
       <c r="U84" t="s">
         <v>216</v>
       </c>
@@ -8316,6 +8337,9 @@
       <c r="S88" t="s">
         <v>199</v>
       </c>
+      <c r="T88" t="s">
+        <v>213</v>
+      </c>
       <c r="U88" t="s">
         <v>216</v>
       </c>
@@ -8671,6 +8695,9 @@
       <c r="S93" t="s">
         <v>199</v>
       </c>
+      <c r="T93" t="s">
+        <v>213</v>
+      </c>
       <c r="U93" t="s">
         <v>216</v>
       </c>
@@ -9026,6 +9053,9 @@
       <c r="S98" t="s">
         <v>199</v>
       </c>
+      <c r="T98" t="s">
+        <v>213</v>
+      </c>
       <c r="U98" t="s">
         <v>216</v>
       </c>
@@ -9251,6 +9281,9 @@
       <c r="S101" t="s">
         <v>199</v>
       </c>
+      <c r="T101" t="s">
+        <v>213</v>
+      </c>
       <c r="U101" t="s">
         <v>216</v>
       </c>
@@ -9396,6 +9429,9 @@
       <c r="S103" t="s">
         <v>199</v>
       </c>
+      <c r="T103" t="s">
+        <v>213</v>
+      </c>
       <c r="U103" t="s">
         <v>216</v>
       </c>
@@ -9825,6 +9861,9 @@
       <c r="S109" t="s">
         <v>199</v>
       </c>
+      <c r="T109" t="s">
+        <v>213</v>
+      </c>
       <c r="U109" t="s">
         <v>216</v>
       </c>
@@ -9970,6 +10009,9 @@
       <c r="S111" t="s">
         <v>199</v>
       </c>
+      <c r="T111" t="s">
+        <v>213</v>
+      </c>
       <c r="U111" t="s">
         <v>216</v>
       </c>
@@ -10189,6 +10231,9 @@
       <c r="S114" t="s">
         <v>199</v>
       </c>
+      <c r="T114" t="s">
+        <v>213</v>
+      </c>
       <c r="U114" t="s">
         <v>216</v>
       </c>
@@ -10408,6 +10453,9 @@
       <c r="S117" t="s">
         <v>199</v>
       </c>
+      <c r="T117" t="s">
+        <v>213</v>
+      </c>
       <c r="U117" t="s">
         <v>216</v>
       </c>
@@ -10763,6 +10811,9 @@
       <c r="S122" t="s">
         <v>199</v>
       </c>
+      <c r="T122" t="s">
+        <v>213</v>
+      </c>
       <c r="U122" t="s">
         <v>216</v>
       </c>
@@ -18495,6 +18546,9 @@
       <c r="S226" t="s">
         <v>194</v>
       </c>
+      <c r="T226" t="s">
+        <v>212</v>
+      </c>
       <c r="U226" t="s">
         <v>216</v>
       </c>
@@ -19268,6 +19322,9 @@
       <c r="S236" t="s">
         <v>194</v>
       </c>
+      <c r="T236" t="s">
+        <v>212</v>
+      </c>
       <c r="U236" t="s">
         <v>216</v>
       </c>
@@ -19816,6 +19873,9 @@
       <c r="S243" t="s">
         <v>194</v>
       </c>
+      <c r="T243" t="s">
+        <v>212</v>
+      </c>
       <c r="U243" t="s">
         <v>216</v>
       </c>
@@ -21057,6 +21117,9 @@
       <c r="S259" t="s">
         <v>199</v>
       </c>
+      <c r="T259" t="s">
+        <v>213</v>
+      </c>
       <c r="U259" t="s">
         <v>216</v>
       </c>
@@ -21208,6 +21271,9 @@
       <c r="S261" t="s">
         <v>199</v>
       </c>
+      <c r="T261" t="s">
+        <v>213</v>
+      </c>
       <c r="U261" t="s">
         <v>217</v>
       </c>
@@ -21362,6 +21428,9 @@
       <c r="S263" t="s">
         <v>199</v>
       </c>
+      <c r="T263" t="s">
+        <v>213</v>
+      </c>
       <c r="U263" t="s">
         <v>217</v>
       </c>
@@ -21750,6 +21819,9 @@
       <c r="S268" t="s">
         <v>199</v>
       </c>
+      <c r="T268" t="s">
+        <v>213</v>
+      </c>
       <c r="U268" t="s">
         <v>217</v>
       </c>
@@ -22058,6 +22130,9 @@
       <c r="S272" t="s">
         <v>199</v>
       </c>
+      <c r="T272" t="s">
+        <v>213</v>
+      </c>
       <c r="U272" t="s">
         <v>217</v>
       </c>
@@ -22132,6 +22207,9 @@
       <c r="S273" t="s">
         <v>199</v>
       </c>
+      <c r="T273" t="s">
+        <v>213</v>
+      </c>
       <c r="U273" t="s">
         <v>215</v>
       </c>
@@ -22431,6 +22509,9 @@
       <c r="S277" t="s">
         <v>199</v>
       </c>
+      <c r="T277" t="s">
+        <v>213</v>
+      </c>
       <c r="U277" t="s">
         <v>217</v>
       </c>
@@ -22508,6 +22589,9 @@
       <c r="S278" t="s">
         <v>199</v>
       </c>
+      <c r="T278" t="s">
+        <v>213</v>
+      </c>
       <c r="U278" t="s">
         <v>217</v>
       </c>
@@ -27227,37 +27311,37 @@
     </row>
     <row r="342" spans="1:35">
       <c r="A342">
-        <v>6548</v>
+        <v>6945</v>
       </c>
       <c r="B342" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C342" t="s">
         <v>50</v>
       </c>
       <c r="D342" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E342" t="s">
         <v>54</v>
       </c>
       <c r="F342" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G342">
-        <v>1697</v>
+        <v>9764</v>
       </c>
       <c r="H342">
-        <v>1650</v>
+        <v>0</v>
       </c>
       <c r="I342" t="s">
         <v>59</v>
       </c>
       <c r="J342" t="s">
-        <v>75</v>
+        <v>118</v>
       </c>
       <c r="N342" s="1">
-        <v>46286</v>
+        <v>46295</v>
       </c>
       <c r="P342">
         <v>8</v>
@@ -27266,45 +27350,48 @@
         <v>2026</v>
       </c>
       <c r="R342">
-        <v>17968001</v>
+        <v>18200045</v>
       </c>
       <c r="S342" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="T342" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="U342" t="s">
         <v>216</v>
       </c>
       <c r="V342" s="1">
-        <v>46282.62254486111</v>
+        <v>46288.43167056713</v>
       </c>
       <c r="W342">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="X342" t="s">
-        <v>218</v>
+        <v>221</v>
+      </c>
+      <c r="Y342" t="s">
+        <v>350</v>
       </c>
       <c r="AB342">
         <v>0</v>
       </c>
       <c r="AC342" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AH342" t="s">
         <v>413</v>
       </c>
       <c r="AI342" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="343" spans="1:35">
       <c r="A343">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B343" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C343" t="s">
         <v>50</v>
@@ -27313,7 +27400,7 @@
         <v>51</v>
       </c>
       <c r="E343" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F343" t="s">
         <v>56</v>
@@ -27333,9 +27420,6 @@
       <c r="N343" s="1">
         <v>46286</v>
       </c>
-      <c r="O343" t="s">
-        <v>175</v>
-      </c>
       <c r="P343">
         <v>8</v>
       </c>
@@ -27343,48 +27427,45 @@
         <v>2026</v>
       </c>
       <c r="R343">
-        <v>17042403</v>
+        <v>17968001</v>
       </c>
       <c r="S343" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="T343" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="U343" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="V343" s="1">
-        <v>46286.64173940972</v>
+        <v>46282.62254486111</v>
       </c>
       <c r="W343">
         <v>2</v>
       </c>
       <c r="X343" t="s">
-        <v>219</v>
-      </c>
-      <c r="Y343" t="s">
-        <v>350</v>
+        <v>218</v>
       </c>
       <c r="AB343">
         <v>0</v>
       </c>
       <c r="AC343" t="s">
-        <v>412</v>
+        <v>182</v>
       </c>
       <c r="AH343" t="s">
         <v>413</v>
       </c>
       <c r="AI343" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="344" spans="1:35">
       <c r="A344">
-        <v>6949</v>
+        <v>6627</v>
       </c>
       <c r="B344" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C344" t="s">
         <v>50</v>
@@ -27393,10 +27474,10 @@
         <v>51</v>
       </c>
       <c r="E344" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F344" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G344">
         <v>1697</v>
@@ -27413,6 +27494,9 @@
       <c r="N344" s="1">
         <v>46286</v>
       </c>
+      <c r="O344" t="s">
+        <v>175</v>
+      </c>
       <c r="P344">
         <v>8</v>
       </c>
@@ -27420,45 +27504,48 @@
         <v>2026</v>
       </c>
       <c r="R344">
-        <v>18178280</v>
+        <v>17042403</v>
       </c>
       <c r="S344" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="T344" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="U344" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="V344" s="1">
-        <v>46283.44840582176</v>
+        <v>46286.64173940972</v>
       </c>
       <c r="W344">
         <v>2</v>
       </c>
       <c r="X344" t="s">
-        <v>220</v>
+        <v>219</v>
+      </c>
+      <c r="Y344" t="s">
+        <v>351</v>
       </c>
       <c r="AB344">
         <v>0</v>
       </c>
       <c r="AC344" t="s">
-        <v>182</v>
+        <v>412</v>
       </c>
       <c r="AH344" t="s">
         <v>413</v>
       </c>
       <c r="AI344" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="345" spans="1:35">
       <c r="A345">
-        <v>5417</v>
+        <v>6949</v>
       </c>
       <c r="B345" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C345" t="s">
         <v>50</v>
@@ -27470,25 +27557,22 @@
         <v>54</v>
       </c>
       <c r="F345" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G345">
-        <v>6890</v>
+        <v>1697</v>
       </c>
       <c r="H345">
-        <v>0</v>
+        <v>1650</v>
       </c>
       <c r="I345" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J345" t="s">
-        <v>140</v>
+        <v>75</v>
       </c>
       <c r="N345" s="1">
-        <v>46290</v>
-      </c>
-      <c r="O345" t="s">
-        <v>176</v>
+        <v>46286</v>
       </c>
       <c r="P345">
         <v>8</v>
@@ -27497,40 +27581,37 @@
         <v>2026</v>
       </c>
       <c r="R345">
-        <v>17399260</v>
+        <v>18178280</v>
       </c>
       <c r="S345" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="T345" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="U345" t="s">
         <v>216</v>
       </c>
       <c r="V345" s="1">
-        <v>46287.48052434028</v>
+        <v>46283.44840582176</v>
       </c>
       <c r="W345">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="X345" t="s">
-        <v>224</v>
-      </c>
-      <c r="Y345" t="s">
-        <v>351</v>
+        <v>220</v>
       </c>
       <c r="AB345">
         <v>0</v>
       </c>
       <c r="AC345" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="AH345" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="AI345" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="346" spans="1:35">
@@ -27553,7 +27634,7 @@
         <v>56</v>
       </c>
       <c r="G346">
-        <v>11514</v>
+        <v>6890</v>
       </c>
       <c r="H346">
         <v>0</v>
@@ -27562,7 +27643,7 @@
         <v>60</v>
       </c>
       <c r="J346" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="N346" s="1">
         <v>46290</v>
@@ -27577,7 +27658,7 @@
         <v>2026</v>
       </c>
       <c r="R346">
-        <v>17399465</v>
+        <v>17399260</v>
       </c>
       <c r="S346" t="s">
         <v>187</v>
@@ -27589,7 +27670,7 @@
         <v>216</v>
       </c>
       <c r="V346" s="1">
-        <v>46287.48083141204</v>
+        <v>46287.48052434028</v>
       </c>
       <c r="W346">
         <v>-2</v>
@@ -27598,7 +27679,7 @@
         <v>224</v>
       </c>
       <c r="Y346" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AB346">
         <v>0</v>
@@ -27633,7 +27714,7 @@
         <v>56</v>
       </c>
       <c r="G347">
-        <v>7874</v>
+        <v>11514</v>
       </c>
       <c r="H347">
         <v>0</v>
@@ -27642,10 +27723,13 @@
         <v>60</v>
       </c>
       <c r="J347" t="s">
-        <v>67</v>
+        <v>141</v>
       </c>
       <c r="N347" s="1">
-        <v>46295</v>
+        <v>46290</v>
+      </c>
+      <c r="O347" t="s">
+        <v>176</v>
       </c>
       <c r="P347">
         <v>8</v>
@@ -27654,7 +27738,7 @@
         <v>2026</v>
       </c>
       <c r="R347">
-        <v>17399320</v>
+        <v>17399465</v>
       </c>
       <c r="S347" t="s">
         <v>187</v>
@@ -27666,10 +27750,10 @@
         <v>216</v>
       </c>
       <c r="V347" s="1">
-        <v>46283.6781059838</v>
+        <v>46287.48083141204</v>
       </c>
       <c r="W347">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="X347" t="s">
         <v>224</v>
@@ -27684,24 +27768,24 @@
         <v>187</v>
       </c>
       <c r="AH347" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AI347" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="348" spans="1:35">
       <c r="A348">
-        <v>6703</v>
+        <v>5417</v>
       </c>
       <c r="B348" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C348" t="s">
         <v>50</v>
       </c>
       <c r="D348" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E348" t="s">
         <v>54</v>
@@ -27710,19 +27794,19 @@
         <v>56</v>
       </c>
       <c r="G348">
-        <v>1628</v>
+        <v>7874</v>
       </c>
       <c r="H348">
-        <v>1581</v>
+        <v>0</v>
       </c>
       <c r="I348" t="s">
         <v>60</v>
       </c>
       <c r="J348" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="N348" s="1">
-        <v>46286</v>
+        <v>46295</v>
       </c>
       <c r="P348">
         <v>8</v>
@@ -27731,10 +27815,10 @@
         <v>2026</v>
       </c>
       <c r="R348">
-        <v>17955176</v>
+        <v>17399320</v>
       </c>
       <c r="S348" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="T348" t="s">
         <v>209</v>
@@ -27743,19 +27827,22 @@
         <v>216</v>
       </c>
       <c r="V348" s="1">
-        <v>46282.42251184028</v>
+        <v>46283.6781059838</v>
       </c>
       <c r="W348">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="X348" t="s">
-        <v>227</v>
+        <v>224</v>
+      </c>
+      <c r="Y348" t="s">
+        <v>353</v>
       </c>
       <c r="AB348">
         <v>0</v>
       </c>
       <c r="AC348" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AH348" t="s">
         <v>413</v>
@@ -27766,16 +27853,16 @@
     </row>
     <row r="349" spans="1:35">
       <c r="A349">
-        <v>5417</v>
+        <v>6703</v>
       </c>
       <c r="B349" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C349" t="s">
         <v>50</v>
       </c>
       <c r="D349" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E349" t="s">
         <v>54</v>
@@ -27784,49 +27871,52 @@
         <v>56</v>
       </c>
       <c r="G349">
-        <v>5883</v>
+        <v>1628</v>
       </c>
       <c r="H349">
-        <v>5792</v>
+        <v>1581</v>
       </c>
       <c r="I349" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J349" t="s">
-        <v>123</v>
+        <v>75</v>
       </c>
       <c r="N349" s="1">
         <v>46286</v>
       </c>
       <c r="P349">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q349">
         <v>2026</v>
       </c>
       <c r="R349">
-        <v>17399067</v>
+        <v>17955176</v>
       </c>
       <c r="S349" t="s">
-        <v>194</v>
+        <v>188</v>
+      </c>
+      <c r="T349" t="s">
+        <v>209</v>
       </c>
       <c r="U349" t="s">
         <v>216</v>
       </c>
       <c r="V349" s="1">
-        <v>46282.47420876157</v>
+        <v>46282.42251184028</v>
       </c>
       <c r="W349">
         <v>2</v>
       </c>
       <c r="X349" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="AB349">
         <v>0</v>
       </c>
       <c r="AC349" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="AH349" t="s">
         <v>413</v>
@@ -27837,22 +27927,22 @@
     </row>
     <row r="350" spans="1:35">
       <c r="A350">
-        <v>6945</v>
+        <v>5417</v>
       </c>
       <c r="B350" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C350" t="s">
         <v>50</v>
       </c>
       <c r="D350" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E350" t="s">
         <v>54</v>
       </c>
       <c r="F350" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G350">
         <v>5883</v>
@@ -27869,9 +27959,6 @@
       <c r="N350" s="1">
         <v>46286</v>
       </c>
-      <c r="O350" t="s">
-        <v>177</v>
-      </c>
       <c r="P350">
         <v>9</v>
       </c>
@@ -27879,63 +27966,60 @@
         <v>2026</v>
       </c>
       <c r="R350">
-        <v>18179111</v>
+        <v>17399067</v>
       </c>
       <c r="S350" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="T350" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="U350" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="V350" s="1">
-        <v>46286.7220354051</v>
+        <v>46282.47420876157</v>
       </c>
       <c r="W350">
         <v>2</v>
       </c>
       <c r="X350" t="s">
-        <v>221</v>
-      </c>
-      <c r="Y350" t="s">
-        <v>353</v>
+        <v>224</v>
       </c>
       <c r="AB350">
         <v>0</v>
       </c>
       <c r="AC350" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AH350" t="s">
         <v>413</v>
       </c>
       <c r="AI350" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="351" spans="1:35">
       <c r="A351">
-        <v>5417</v>
+        <v>6945</v>
       </c>
       <c r="B351" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C351" t="s">
         <v>50</v>
       </c>
       <c r="D351" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E351" t="s">
         <v>54</v>
       </c>
       <c r="F351" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G351">
-        <v>5884</v>
+        <v>5883</v>
       </c>
       <c r="H351">
         <v>5792</v>
@@ -27944,11 +28028,14 @@
         <v>61</v>
       </c>
       <c r="J351" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="N351" s="1">
         <v>46286</v>
       </c>
+      <c r="O351" t="s">
+        <v>177</v>
+      </c>
       <c r="P351">
         <v>9</v>
       </c>
@@ -27956,54 +28043,60 @@
         <v>2026</v>
       </c>
       <c r="R351">
-        <v>17399077</v>
+        <v>18179111</v>
       </c>
       <c r="S351" t="s">
-        <v>194</v>
+        <v>192</v>
+      </c>
+      <c r="T351" t="s">
+        <v>210</v>
       </c>
       <c r="U351" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="V351" s="1">
-        <v>46282.47437324074</v>
+        <v>46286.7220354051</v>
       </c>
       <c r="W351">
         <v>2</v>
       </c>
       <c r="X351" t="s">
-        <v>224</v>
+        <v>221</v>
+      </c>
+      <c r="Y351" t="s">
+        <v>354</v>
       </c>
       <c r="AB351">
         <v>0</v>
       </c>
       <c r="AC351" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AH351" t="s">
         <v>413</v>
       </c>
       <c r="AI351" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="352" spans="1:35">
       <c r="A352">
-        <v>6945</v>
+        <v>5417</v>
       </c>
       <c r="B352" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C352" t="s">
         <v>50</v>
       </c>
       <c r="D352" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E352" t="s">
         <v>54</v>
       </c>
       <c r="F352" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G352">
         <v>5884</v>
@@ -28020,9 +28113,6 @@
       <c r="N352" s="1">
         <v>46286</v>
       </c>
-      <c r="O352" t="s">
-        <v>177</v>
-      </c>
       <c r="P352">
         <v>9</v>
       </c>
@@ -28030,105 +28120,102 @@
         <v>2026</v>
       </c>
       <c r="R352">
-        <v>18179118</v>
+        <v>17399077</v>
       </c>
       <c r="S352" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="T352" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="U352" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="V352" s="1">
-        <v>46286.7221544213</v>
+        <v>46282.47437324074</v>
       </c>
       <c r="W352">
         <v>2</v>
       </c>
       <c r="X352" t="s">
-        <v>221</v>
-      </c>
-      <c r="Y352" t="s">
-        <v>354</v>
+        <v>224</v>
       </c>
       <c r="AB352">
         <v>0</v>
       </c>
       <c r="AC352" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AH352" t="s">
         <v>413</v>
       </c>
       <c r="AI352" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="353" spans="1:35">
       <c r="A353">
-        <v>6486</v>
+        <v>6945</v>
       </c>
       <c r="B353" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C353" t="s">
         <v>50</v>
       </c>
       <c r="D353" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E353" t="s">
         <v>54</v>
       </c>
       <c r="F353" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G353">
-        <v>11542</v>
+        <v>5884</v>
       </c>
       <c r="H353">
-        <v>0</v>
+        <v>5792</v>
       </c>
       <c r="I353" t="s">
         <v>61</v>
       </c>
       <c r="J353" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="N353" s="1">
-        <v>46296</v>
+        <v>46286</v>
       </c>
       <c r="O353" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P353">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q353">
         <v>2026</v>
       </c>
       <c r="R353">
-        <v>16976373</v>
+        <v>18179118</v>
       </c>
       <c r="S353" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="T353" t="s">
         <v>210</v>
       </c>
       <c r="U353" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="V353" s="1">
-        <v>46287.66751398148</v>
+        <v>46286.7221544213</v>
       </c>
       <c r="W353">
-        <v>-8</v>
+        <v>2</v>
       </c>
       <c r="X353" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="Y353" t="s">
         <v>355</v>
@@ -28137,10 +28224,10 @@
         <v>0</v>
       </c>
       <c r="AC353" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AH353" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="AI353" t="s">
         <v>419</v>
@@ -28148,16 +28235,16 @@
     </row>
     <row r="354" spans="1:35">
       <c r="A354">
-        <v>6703</v>
+        <v>6486</v>
       </c>
       <c r="B354" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C354" t="s">
         <v>50</v>
       </c>
       <c r="D354" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E354" t="s">
         <v>54</v>
@@ -28181,7 +28268,7 @@
         <v>46296</v>
       </c>
       <c r="O354" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P354">
         <v>10</v>
@@ -28190,10 +28277,10 @@
         <v>2026</v>
       </c>
       <c r="R354">
-        <v>18077186</v>
+        <v>16976373</v>
       </c>
       <c r="S354" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="T354" t="s">
         <v>210</v>
@@ -28202,13 +28289,13 @@
         <v>216</v>
       </c>
       <c r="V354" s="1">
-        <v>46287.46969533565</v>
+        <v>46287.66751398148</v>
       </c>
       <c r="W354">
         <v>-8</v>
       </c>
       <c r="X354" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="Y354" t="s">
         <v>356</v>
@@ -28217,7 +28304,7 @@
         <v>0</v>
       </c>
       <c r="AC354" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AH354" t="s">
         <v>415</v>
@@ -28228,16 +28315,16 @@
     </row>
     <row r="355" spans="1:35">
       <c r="A355">
-        <v>5417</v>
+        <v>6703</v>
       </c>
       <c r="B355" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C355" t="s">
         <v>50</v>
       </c>
       <c r="D355" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E355" t="s">
         <v>54</v>
@@ -28246,46 +28333,49 @@
         <v>56</v>
       </c>
       <c r="G355">
-        <v>5836</v>
+        <v>11542</v>
       </c>
       <c r="H355">
-        <v>5784</v>
+        <v>0</v>
       </c>
       <c r="I355" t="s">
         <v>61</v>
       </c>
       <c r="J355" t="s">
-        <v>142</v>
+        <v>79</v>
       </c>
       <c r="N355" s="1">
-        <v>46286</v>
+        <v>46296</v>
       </c>
       <c r="O355" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="P355">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q355">
         <v>2026</v>
       </c>
       <c r="R355">
-        <v>17399027</v>
+        <v>18077186</v>
       </c>
       <c r="S355" t="s">
-        <v>194</v>
+        <v>190</v>
+      </c>
+      <c r="T355" t="s">
+        <v>210</v>
       </c>
       <c r="U355" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="V355" s="1">
-        <v>46286.71510853009</v>
+        <v>46287.46969533565</v>
       </c>
       <c r="W355">
-        <v>2</v>
+        <v>-8</v>
       </c>
       <c r="X355" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Y355" t="s">
         <v>357</v>
@@ -28294,10 +28384,10 @@
         <v>0</v>
       </c>
       <c r="AC355" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="AH355" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AI355" t="s">
         <v>419</v>
@@ -28305,10 +28395,10 @@
     </row>
     <row r="356" spans="1:35">
       <c r="A356">
-        <v>6486</v>
+        <v>5417</v>
       </c>
       <c r="B356" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C356" t="s">
         <v>50</v>
@@ -28338,7 +28428,7 @@
         <v>46286</v>
       </c>
       <c r="O356" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="P356">
         <v>9</v>
@@ -28347,25 +28437,25 @@
         <v>2026</v>
       </c>
       <c r="R356">
-        <v>16976037</v>
+        <v>17399027</v>
       </c>
       <c r="S356" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="T356" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="U356" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="V356" s="1">
-        <v>46283.59424842593</v>
+        <v>46286.71510853009</v>
       </c>
       <c r="W356">
         <v>2</v>
       </c>
       <c r="X356" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Y356" t="s">
         <v>358</v>
@@ -28374,21 +28464,21 @@
         <v>0</v>
       </c>
       <c r="AC356" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="AH356" t="s">
         <v>413</v>
       </c>
       <c r="AI356" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="357" spans="1:35">
       <c r="A357">
-        <v>6548</v>
+        <v>6486</v>
       </c>
       <c r="B357" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C357" t="s">
         <v>50</v>
@@ -28427,10 +28517,10 @@
         <v>2026</v>
       </c>
       <c r="R357">
-        <v>17222579</v>
+        <v>16976037</v>
       </c>
       <c r="S357" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="T357" t="s">
         <v>210</v>
@@ -28439,13 +28529,13 @@
         <v>216</v>
       </c>
       <c r="V357" s="1">
-        <v>46283.68435655093</v>
+        <v>46283.59424842593</v>
       </c>
       <c r="W357">
         <v>2</v>
       </c>
       <c r="X357" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="Y357" t="s">
         <v>359</v>
@@ -28454,7 +28544,7 @@
         <v>0</v>
       </c>
       <c r="AC357" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="AH357" t="s">
         <v>413</v>
@@ -28465,10 +28555,10 @@
     </row>
     <row r="358" spans="1:35">
       <c r="A358">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B358" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C358" t="s">
         <v>50</v>
@@ -28477,7 +28567,7 @@
         <v>51</v>
       </c>
       <c r="E358" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F358" t="s">
         <v>56</v>
@@ -28507,10 +28597,10 @@
         <v>2026</v>
       </c>
       <c r="R358">
-        <v>18068500</v>
+        <v>17222579</v>
       </c>
       <c r="S358" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="T358" t="s">
         <v>210</v>
@@ -28519,22 +28609,22 @@
         <v>216</v>
       </c>
       <c r="V358" s="1">
-        <v>46283.5942487037</v>
+        <v>46283.68435655093</v>
       </c>
       <c r="W358">
         <v>2</v>
       </c>
       <c r="X358" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Y358" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AB358">
         <v>0</v>
       </c>
       <c r="AC358" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="AH358" t="s">
         <v>413</v>
@@ -28545,16 +28635,16 @@
     </row>
     <row r="359" spans="1:35">
       <c r="A359">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B359" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C359" t="s">
         <v>50</v>
       </c>
       <c r="D359" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E359" t="s">
         <v>55</v>
@@ -28587,7 +28677,7 @@
         <v>2026</v>
       </c>
       <c r="R359">
-        <v>18052419</v>
+        <v>18068500</v>
       </c>
       <c r="S359" t="s">
         <v>191</v>
@@ -28599,7 +28689,7 @@
         <v>216</v>
       </c>
       <c r="V359" s="1">
-        <v>46283.59424924768</v>
+        <v>46283.5942487037</v>
       </c>
       <c r="W359">
         <v>2</v>
@@ -28608,7 +28698,7 @@
         <v>219</v>
       </c>
       <c r="Y359" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AB359">
         <v>0</v>
@@ -28625,19 +28715,19 @@
     </row>
     <row r="360" spans="1:35">
       <c r="A360">
-        <v>6703</v>
+        <v>6628</v>
       </c>
       <c r="B360" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C360" t="s">
         <v>50</v>
       </c>
       <c r="D360" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E360" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F360" t="s">
         <v>56</v>
@@ -28667,10 +28757,10 @@
         <v>2026</v>
       </c>
       <c r="R360">
-        <v>18077082</v>
+        <v>18052419</v>
       </c>
       <c r="S360" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="T360" t="s">
         <v>210</v>
@@ -28679,22 +28769,22 @@
         <v>216</v>
       </c>
       <c r="V360" s="1">
-        <v>46283.68161918982</v>
+        <v>46283.59424924768</v>
       </c>
       <c r="W360">
         <v>2</v>
       </c>
       <c r="X360" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="Y360" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AB360">
         <v>0</v>
       </c>
       <c r="AC360" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AH360" t="s">
         <v>413</v>
@@ -28705,16 +28795,16 @@
     </row>
     <row r="361" spans="1:35">
       <c r="A361">
-        <v>6779</v>
+        <v>6703</v>
       </c>
       <c r="B361" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C361" t="s">
         <v>50</v>
       </c>
       <c r="D361" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E361" t="s">
         <v>54</v>
@@ -28738,7 +28828,7 @@
         <v>46286</v>
       </c>
       <c r="O361" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="P361">
         <v>9</v>
@@ -28747,25 +28837,25 @@
         <v>2026</v>
       </c>
       <c r="R361">
-        <v>18090149</v>
+        <v>18077082</v>
       </c>
       <c r="S361" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="T361" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="U361" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="V361" s="1">
-        <v>46286.6489187037</v>
+        <v>46283.68161918982</v>
       </c>
       <c r="W361">
         <v>2</v>
       </c>
       <c r="X361" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Y361" t="s">
         <v>361</v>
@@ -28774,21 +28864,21 @@
         <v>0</v>
       </c>
       <c r="AC361" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="AH361" t="s">
         <v>413</v>
       </c>
       <c r="AI361" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="362" spans="1:35">
       <c r="A362">
-        <v>6945</v>
+        <v>6779</v>
       </c>
       <c r="B362" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C362" t="s">
         <v>50</v>
@@ -28800,7 +28890,7 @@
         <v>54</v>
       </c>
       <c r="F362" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G362">
         <v>5836</v>
@@ -28818,7 +28908,7 @@
         <v>46286</v>
       </c>
       <c r="O362" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="P362">
         <v>9</v>
@@ -28827,25 +28917,25 @@
         <v>2026</v>
       </c>
       <c r="R362">
-        <v>18179083</v>
+        <v>18090149</v>
       </c>
       <c r="S362" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="T362" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="U362" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="V362" s="1">
-        <v>46288.38004474537</v>
+        <v>46286.6489187037</v>
       </c>
       <c r="W362">
         <v>2</v>
       </c>
       <c r="X362" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Y362" t="s">
         <v>362</v>
@@ -28854,7 +28944,7 @@
         <v>0</v>
       </c>
       <c r="AC362" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="AH362" t="s">
         <v>413</v>
@@ -28865,40 +28955,40 @@
     </row>
     <row r="363" spans="1:35">
       <c r="A363">
-        <v>6404</v>
+        <v>6945</v>
       </c>
       <c r="B363" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C363" t="s">
         <v>50</v>
       </c>
       <c r="D363" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E363" t="s">
         <v>54</v>
       </c>
       <c r="F363" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G363">
-        <v>5903</v>
+        <v>5836</v>
       </c>
       <c r="H363">
-        <v>5830</v>
+        <v>5784</v>
       </c>
       <c r="I363" t="s">
         <v>61</v>
       </c>
       <c r="J363" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="N363" s="1">
         <v>46286</v>
       </c>
       <c r="O363" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="P363">
         <v>9</v>
@@ -28907,25 +28997,25 @@
         <v>2026</v>
       </c>
       <c r="R363">
-        <v>16962221</v>
+        <v>18179083</v>
       </c>
       <c r="S363" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="T363" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="U363" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="V363" s="1">
-        <v>46282.42048836806</v>
+        <v>46288.38004474537</v>
       </c>
       <c r="W363">
         <v>2</v>
       </c>
       <c r="X363" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="Y363" t="s">
         <v>363</v>
@@ -28934,13 +29024,13 @@
         <v>0</v>
       </c>
       <c r="AC363" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="AH363" t="s">
         <v>413</v>
       </c>
       <c r="AI363" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="364" spans="1:35">
@@ -28963,20 +29053,23 @@
         <v>56</v>
       </c>
       <c r="G364">
+        <v>5903</v>
+      </c>
+      <c r="H364">
         <v>5830</v>
-      </c>
-      <c r="H364">
-        <v>5784</v>
       </c>
       <c r="I364" t="s">
         <v>61</v>
       </c>
       <c r="J364" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N364" s="1">
         <v>46286</v>
       </c>
+      <c r="O364" t="s">
+        <v>170</v>
+      </c>
       <c r="P364">
         <v>9</v>
       </c>
@@ -28984,7 +29077,7 @@
         <v>2026</v>
       </c>
       <c r="R364">
-        <v>16962211</v>
+        <v>16962221</v>
       </c>
       <c r="S364" t="s">
         <v>195</v>
@@ -28996,7 +29089,7 @@
         <v>216</v>
       </c>
       <c r="V364" s="1">
-        <v>46282.42138976852</v>
+        <v>46282.42048836806</v>
       </c>
       <c r="W364">
         <v>2</v>
@@ -29004,6 +29097,9 @@
       <c r="X364" t="s">
         <v>228</v>
       </c>
+      <c r="Y364" t="s">
+        <v>364</v>
+      </c>
       <c r="AB364">
         <v>0</v>
       </c>
@@ -29019,16 +29115,16 @@
     </row>
     <row r="365" spans="1:35">
       <c r="A365">
-        <v>6486</v>
+        <v>6404</v>
       </c>
       <c r="B365" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C365" t="s">
         <v>50</v>
       </c>
       <c r="D365" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E365" t="s">
         <v>54</v>
@@ -29037,78 +29133,72 @@
         <v>56</v>
       </c>
       <c r="G365">
-        <v>11541</v>
+        <v>5830</v>
       </c>
       <c r="H365">
-        <v>0</v>
+        <v>5784</v>
       </c>
       <c r="I365" t="s">
         <v>61</v>
       </c>
       <c r="J365" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N365" s="1">
-        <v>46296</v>
-      </c>
-      <c r="O365" t="s">
-        <v>178</v>
+        <v>46286</v>
       </c>
       <c r="P365">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q365">
         <v>2026</v>
       </c>
       <c r="R365">
-        <v>16976363</v>
+        <v>16962211</v>
       </c>
       <c r="S365" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="T365" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="U365" t="s">
         <v>216</v>
       </c>
       <c r="V365" s="1">
-        <v>46287.66967658565</v>
+        <v>46282.42138976852</v>
       </c>
       <c r="W365">
-        <v>-8</v>
+        <v>2</v>
       </c>
       <c r="X365" t="s">
-        <v>225</v>
-      </c>
-      <c r="Y365" t="s">
-        <v>355</v>
+        <v>228</v>
       </c>
       <c r="AB365">
         <v>0</v>
       </c>
       <c r="AC365" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AH365" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="AI365" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="366" spans="1:35">
       <c r="A366">
-        <v>6703</v>
+        <v>6486</v>
       </c>
       <c r="B366" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C366" t="s">
         <v>50</v>
       </c>
       <c r="D366" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E366" t="s">
         <v>54</v>
@@ -29132,7 +29222,7 @@
         <v>46296</v>
       </c>
       <c r="O366" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P366">
         <v>10</v>
@@ -29141,10 +29231,10 @@
         <v>2026</v>
       </c>
       <c r="R366">
-        <v>18077176</v>
+        <v>16976363</v>
       </c>
       <c r="S366" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="T366" t="s">
         <v>210</v>
@@ -29153,22 +29243,22 @@
         <v>216</v>
       </c>
       <c r="V366" s="1">
-        <v>46287.47257043982</v>
+        <v>46287.66967658565</v>
       </c>
       <c r="W366">
         <v>-8</v>
       </c>
       <c r="X366" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="Y366" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="AB366">
         <v>0</v>
       </c>
       <c r="AC366" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AH366" t="s">
         <v>415</v>
@@ -29179,25 +29269,25 @@
     </row>
     <row r="367" spans="1:35">
       <c r="A367">
-        <v>6628</v>
+        <v>6703</v>
       </c>
       <c r="B367" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C367" t="s">
         <v>50</v>
       </c>
       <c r="D367" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E367" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F367" t="s">
         <v>56</v>
       </c>
       <c r="G367">
-        <v>11810</v>
+        <v>11541</v>
       </c>
       <c r="H367">
         <v>0</v>
@@ -29206,34 +29296,40 @@
         <v>61</v>
       </c>
       <c r="J367" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N367" s="1">
-        <v>46286</v>
+        <v>46296</v>
       </c>
       <c r="O367" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="P367">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q367">
         <v>2026</v>
       </c>
       <c r="R367">
-        <v>18278512</v>
+        <v>18077176</v>
+      </c>
+      <c r="S367" t="s">
+        <v>190</v>
+      </c>
+      <c r="T367" t="s">
+        <v>210</v>
       </c>
       <c r="U367" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="V367" s="1">
-        <v>46286.6987844213</v>
+        <v>46287.47257043982</v>
       </c>
       <c r="W367">
-        <v>2</v>
+        <v>-8</v>
       </c>
       <c r="X367" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="Y367" t="s">
         <v>365</v>
@@ -29242,10 +29338,10 @@
         <v>0</v>
       </c>
       <c r="AC367" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AH367" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AI367" t="s">
         <v>419</v>
@@ -29253,25 +29349,25 @@
     </row>
     <row r="368" spans="1:35">
       <c r="A368">
-        <v>5417</v>
+        <v>6628</v>
       </c>
       <c r="B368" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C368" t="s">
         <v>50</v>
       </c>
       <c r="D368" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E368" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F368" t="s">
         <v>56</v>
       </c>
       <c r="G368">
-        <v>6348</v>
+        <v>11810</v>
       </c>
       <c r="H368">
         <v>0</v>
@@ -29280,13 +29376,13 @@
         <v>61</v>
       </c>
       <c r="J368" t="s">
-        <v>87</v>
+        <v>146</v>
       </c>
       <c r="N368" s="1">
-        <v>46288</v>
+        <v>46286</v>
       </c>
       <c r="O368" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="P368">
         <v>9</v>
@@ -29295,19 +29391,19 @@
         <v>2026</v>
       </c>
       <c r="R368">
-        <v>18274307</v>
+        <v>18278512</v>
       </c>
       <c r="U368" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="V368" s="1">
-        <v>46287.45807677083</v>
+        <v>46286.6987844213</v>
       </c>
       <c r="W368">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X368" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="Y368" t="s">
         <v>366</v>
@@ -29316,10 +29412,10 @@
         <v>0</v>
       </c>
       <c r="AC368" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="AH368" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AI368" t="s">
         <v>419</v>
@@ -29327,10 +29423,10 @@
     </row>
     <row r="369" spans="1:35">
       <c r="A369">
-        <v>6949</v>
+        <v>5417</v>
       </c>
       <c r="B369" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C369" t="s">
         <v>50</v>
@@ -29342,7 +29438,7 @@
         <v>54</v>
       </c>
       <c r="F369" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G369">
         <v>6348</v>
@@ -29360,7 +29456,7 @@
         <v>46288</v>
       </c>
       <c r="O369" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="P369">
         <v>9</v>
@@ -29369,25 +29465,19 @@
         <v>2026</v>
       </c>
       <c r="R369">
-        <v>18275979</v>
-      </c>
-      <c r="S369" t="s">
-        <v>193</v>
-      </c>
-      <c r="T369" t="s">
-        <v>211</v>
+        <v>18274307</v>
       </c>
       <c r="U369" t="s">
         <v>216</v>
       </c>
       <c r="V369" s="1">
-        <v>46286.74096042824</v>
+        <v>46287.45807677083</v>
       </c>
       <c r="W369">
         <v>0</v>
       </c>
       <c r="X369" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="Y369" t="s">
         <v>367</v>
@@ -29396,7 +29486,7 @@
         <v>0</v>
       </c>
       <c r="AC369" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AH369" t="s">
         <v>414</v>
@@ -29407,10 +29497,10 @@
     </row>
     <row r="370" spans="1:35">
       <c r="A370">
-        <v>6548</v>
+        <v>6949</v>
       </c>
       <c r="B370" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C370" t="s">
         <v>50</v>
@@ -29422,69 +29512,75 @@
         <v>54</v>
       </c>
       <c r="F370" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G370">
-        <v>1913</v>
+        <v>6348</v>
       </c>
       <c r="H370">
-        <v>1862</v>
+        <v>0</v>
       </c>
       <c r="I370" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J370" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="N370" s="1">
-        <v>46286</v>
+        <v>46288</v>
+      </c>
+      <c r="O370" t="s">
+        <v>179</v>
       </c>
       <c r="P370">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q370">
         <v>2026</v>
       </c>
       <c r="R370">
-        <v>17988579</v>
+        <v>18275979</v>
       </c>
       <c r="S370" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="T370" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="U370" t="s">
         <v>216</v>
       </c>
       <c r="V370" s="1">
-        <v>46283.3939177662</v>
+        <v>46286.74096042824</v>
       </c>
       <c r="W370">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X370" t="s">
-        <v>218</v>
+        <v>220</v>
+      </c>
+      <c r="Y370" t="s">
+        <v>368</v>
       </c>
       <c r="AB370">
         <v>0</v>
       </c>
       <c r="AC370" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="AH370" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI370" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="371" spans="1:35">
       <c r="A371">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B371" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C371" t="s">
         <v>50</v>
@@ -29493,7 +29589,7 @@
         <v>51</v>
       </c>
       <c r="E371" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F371" t="s">
         <v>56</v>
@@ -29513,9 +29609,6 @@
       <c r="N371" s="1">
         <v>46286</v>
       </c>
-      <c r="O371" t="s">
-        <v>175</v>
-      </c>
       <c r="P371">
         <v>8</v>
       </c>
@@ -29523,45 +29616,45 @@
         <v>2026</v>
       </c>
       <c r="R371">
-        <v>18048433</v>
+        <v>17988579</v>
       </c>
       <c r="S371" t="s">
-        <v>199</v>
+        <v>198</v>
+      </c>
+      <c r="T371" t="s">
+        <v>213</v>
       </c>
       <c r="U371" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="V371" s="1">
-        <v>46286.64017539352</v>
+        <v>46283.3939177662</v>
       </c>
       <c r="W371">
         <v>2</v>
       </c>
       <c r="X371" t="s">
-        <v>219</v>
-      </c>
-      <c r="Y371" t="s">
-        <v>350</v>
+        <v>218</v>
       </c>
       <c r="AB371">
         <v>0</v>
       </c>
       <c r="AC371" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AH371" t="s">
         <v>413</v>
       </c>
       <c r="AI371" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="372" spans="1:35">
       <c r="A372">
-        <v>6949</v>
+        <v>6627</v>
       </c>
       <c r="B372" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C372" t="s">
         <v>50</v>
@@ -29570,10 +29663,10 @@
         <v>51</v>
       </c>
       <c r="E372" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F372" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G372">
         <v>1913</v>
@@ -29600,10 +29693,10 @@
         <v>2026</v>
       </c>
       <c r="R372">
-        <v>18214877</v>
+        <v>18048433</v>
       </c>
       <c r="S372" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="T372" t="s">
         <v>213</v>
@@ -29612,22 +29705,22 @@
         <v>217</v>
       </c>
       <c r="V372" s="1">
-        <v>46286.7204416551</v>
+        <v>46286.64017539352</v>
       </c>
       <c r="W372">
         <v>2</v>
       </c>
       <c r="X372" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Y372" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AB372">
         <v>0</v>
       </c>
       <c r="AC372" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="AH372" t="s">
         <v>413</v>
@@ -29638,10 +29731,10 @@
     </row>
     <row r="373" spans="1:35">
       <c r="A373">
-        <v>6548</v>
+        <v>6949</v>
       </c>
       <c r="B373" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C373" t="s">
         <v>50</v>
@@ -29653,22 +29746,25 @@
         <v>54</v>
       </c>
       <c r="F373" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G373">
-        <v>1876</v>
+        <v>1913</v>
       </c>
       <c r="H373">
-        <v>0</v>
+        <v>1862</v>
       </c>
       <c r="I373" t="s">
         <v>62</v>
       </c>
       <c r="J373" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N373" s="1">
-        <v>46283</v>
+        <v>46286</v>
+      </c>
+      <c r="O373" t="s">
+        <v>175</v>
       </c>
       <c r="P373">
         <v>8</v>
@@ -29677,10 +29773,10 @@
         <v>2026</v>
       </c>
       <c r="R373">
-        <v>17988555</v>
+        <v>18214877</v>
       </c>
       <c r="S373" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="T373" t="s">
         <v>213</v>
@@ -29689,36 +29785,36 @@
         <v>217</v>
       </c>
       <c r="V373" s="1">
-        <v>46283.66538607639</v>
+        <v>46286.7204416551</v>
       </c>
       <c r="W373">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="X373" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Y373" t="s">
-        <v>368</v>
+        <v>351</v>
       </c>
       <c r="AB373">
         <v>0</v>
       </c>
       <c r="AC373" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="AH373" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AI373" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="374" spans="1:35">
       <c r="A374">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B374" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C374" t="s">
         <v>50</v>
@@ -29727,13 +29823,13 @@
         <v>51</v>
       </c>
       <c r="E374" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F374" t="s">
         <v>56</v>
       </c>
       <c r="G374">
-        <v>11411</v>
+        <v>1876</v>
       </c>
       <c r="H374">
         <v>0</v>
@@ -29742,7 +29838,7 @@
         <v>62</v>
       </c>
       <c r="J374" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="N374" s="1">
         <v>46283</v>
@@ -29754,22 +29850,25 @@
         <v>2026</v>
       </c>
       <c r="R374">
-        <v>18048483</v>
+        <v>17988555</v>
       </c>
       <c r="S374" t="s">
-        <v>199</v>
+        <v>198</v>
+      </c>
+      <c r="T374" t="s">
+        <v>213</v>
       </c>
       <c r="U374" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="V374" s="1">
-        <v>46286.43482986111</v>
+        <v>46283.66538607639</v>
       </c>
       <c r="W374">
         <v>5</v>
       </c>
       <c r="X374" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Y374" t="s">
         <v>369</v>
@@ -29778,21 +29877,21 @@
         <v>0</v>
       </c>
       <c r="AC374" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AH374" t="s">
         <v>414</v>
       </c>
       <c r="AI374" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="375" spans="1:35">
       <c r="A375">
-        <v>6949</v>
+        <v>6627</v>
       </c>
       <c r="B375" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C375" t="s">
         <v>50</v>
@@ -29801,10 +29900,10 @@
         <v>51</v>
       </c>
       <c r="E375" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F375" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G375">
         <v>11411</v>
@@ -29828,10 +29927,10 @@
         <v>2026</v>
       </c>
       <c r="R375">
-        <v>18214925</v>
+        <v>18048483</v>
       </c>
       <c r="S375" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="T375" t="s">
         <v>213</v>
@@ -29840,13 +29939,13 @@
         <v>215</v>
       </c>
       <c r="V375" s="1">
-        <v>46286.74368133102</v>
+        <v>46286.43482986111</v>
       </c>
       <c r="W375">
         <v>5</v>
       </c>
       <c r="X375" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Y375" t="s">
         <v>370</v>
@@ -29855,7 +29954,7 @@
         <v>0</v>
       </c>
       <c r="AC375" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AH375" t="s">
         <v>414</v>
@@ -29866,25 +29965,25 @@
     </row>
     <row r="376" spans="1:35">
       <c r="A376">
-        <v>6628</v>
+        <v>6949</v>
       </c>
       <c r="B376" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C376" t="s">
         <v>50</v>
       </c>
       <c r="D376" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E376" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F376" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G376">
-        <v>1879</v>
+        <v>11411</v>
       </c>
       <c r="H376">
         <v>0</v>
@@ -29893,7 +29992,7 @@
         <v>62</v>
       </c>
       <c r="J376" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="N376" s="1">
         <v>46283</v>
@@ -29905,25 +30004,25 @@
         <v>2026</v>
       </c>
       <c r="R376">
-        <v>17988684</v>
+        <v>18214925</v>
       </c>
       <c r="S376" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="T376" t="s">
         <v>213</v>
       </c>
       <c r="U376" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="V376" s="1">
-        <v>46283.41459880787</v>
+        <v>46286.74368133102</v>
       </c>
       <c r="W376">
         <v>5</v>
       </c>
       <c r="X376" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Y376" t="s">
         <v>371</v>
@@ -29932,21 +30031,21 @@
         <v>0</v>
       </c>
       <c r="AC376" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AH376" t="s">
         <v>414</v>
       </c>
       <c r="AI376" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="377" spans="1:35">
       <c r="A377">
-        <v>6945</v>
+        <v>6628</v>
       </c>
       <c r="B377" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C377" t="s">
         <v>50</v>
@@ -29955,10 +30054,10 @@
         <v>52</v>
       </c>
       <c r="E377" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F377" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G377">
         <v>1879</v>
@@ -29982,22 +30081,25 @@
         <v>2026</v>
       </c>
       <c r="R377">
-        <v>18220194</v>
+        <v>17988684</v>
       </c>
       <c r="S377" t="s">
-        <v>199</v>
+        <v>201</v>
+      </c>
+      <c r="T377" t="s">
+        <v>213</v>
       </c>
       <c r="U377" t="s">
         <v>217</v>
       </c>
       <c r="V377" s="1">
-        <v>46283.73838344908</v>
+        <v>46283.41459880787</v>
       </c>
       <c r="W377">
         <v>5</v>
       </c>
       <c r="X377" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="Y377" t="s">
         <v>372</v>
@@ -30006,7 +30108,7 @@
         <v>0</v>
       </c>
       <c r="AC377" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AH377" t="s">
         <v>414</v>
@@ -30017,16 +30119,16 @@
     </row>
     <row r="378" spans="1:35">
       <c r="A378">
-        <v>6962</v>
+        <v>6945</v>
       </c>
       <c r="B378" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C378" t="s">
         <v>50</v>
       </c>
       <c r="D378" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E378" t="s">
         <v>54</v>
@@ -30035,7 +30137,7 @@
         <v>57</v>
       </c>
       <c r="G378">
-        <v>1881</v>
+        <v>1879</v>
       </c>
       <c r="H378">
         <v>0</v>
@@ -30044,10 +30146,10 @@
         <v>62</v>
       </c>
       <c r="J378" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N378" s="1">
-        <v>46287</v>
+        <v>46283</v>
       </c>
       <c r="P378">
         <v>8</v>
@@ -30056,25 +30158,25 @@
         <v>2026</v>
       </c>
       <c r="R378">
-        <v>18260044</v>
+        <v>18220194</v>
       </c>
       <c r="S378" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="T378" t="s">
         <v>213</v>
       </c>
       <c r="U378" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="V378" s="1">
-        <v>46286.76327152778</v>
+        <v>46283.73838344908</v>
       </c>
       <c r="W378">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="X378" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Y378" t="s">
         <v>373</v>
@@ -30083,21 +30185,21 @@
         <v>0</v>
       </c>
       <c r="AC378" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="AH378" t="s">
         <v>414</v>
       </c>
       <c r="AI378" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="379" spans="1:35">
       <c r="A379">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B379" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C379" t="s">
         <v>50</v>
@@ -30133,7 +30235,7 @@
         <v>2026</v>
       </c>
       <c r="R379">
-        <v>18260177</v>
+        <v>18260044</v>
       </c>
       <c r="S379" t="s">
         <v>202</v>
@@ -30145,7 +30247,7 @@
         <v>216</v>
       </c>
       <c r="V379" s="1">
-        <v>46286.76330447917</v>
+        <v>46286.76327152778</v>
       </c>
       <c r="W379">
         <v>1</v>
@@ -30154,7 +30256,7 @@
         <v>222</v>
       </c>
       <c r="Y379" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AB379">
         <v>0</v>
@@ -30171,25 +30273,25 @@
     </row>
     <row r="380" spans="1:35">
       <c r="A380">
-        <v>6548</v>
+        <v>6963</v>
       </c>
       <c r="B380" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C380" t="s">
         <v>50</v>
       </c>
       <c r="D380" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E380" t="s">
         <v>54</v>
       </c>
       <c r="F380" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G380">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="H380">
         <v>0</v>
@@ -30198,14 +30300,11 @@
         <v>62</v>
       </c>
       <c r="J380" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="N380" s="1">
         <v>46287</v>
       </c>
-      <c r="O380" t="s">
-        <v>177</v>
-      </c>
       <c r="P380">
         <v>8</v>
       </c>
@@ -30213,25 +30312,25 @@
         <v>2026</v>
       </c>
       <c r="R380">
-        <v>17988567</v>
+        <v>18260177</v>
       </c>
       <c r="S380" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="T380" t="s">
         <v>213</v>
       </c>
       <c r="U380" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="V380" s="1">
-        <v>46287.42040790509</v>
+        <v>46286.76330447917</v>
       </c>
       <c r="W380">
         <v>1</v>
       </c>
       <c r="X380" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="Y380" t="s">
         <v>374</v>
@@ -30240,7 +30339,7 @@
         <v>0</v>
       </c>
       <c r="AC380" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="AH380" t="s">
         <v>414</v>
@@ -30251,10 +30350,10 @@
     </row>
     <row r="381" spans="1:35">
       <c r="A381">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B381" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C381" t="s">
         <v>50</v>
@@ -30263,7 +30362,7 @@
         <v>51</v>
       </c>
       <c r="E381" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F381" t="s">
         <v>56</v>
@@ -30283,6 +30382,9 @@
       <c r="N381" s="1">
         <v>46287</v>
       </c>
+      <c r="O381" t="s">
+        <v>177</v>
+      </c>
       <c r="P381">
         <v>8</v>
       </c>
@@ -30290,22 +30392,25 @@
         <v>2026</v>
       </c>
       <c r="R381">
-        <v>17968390</v>
+        <v>17988567</v>
       </c>
       <c r="S381" t="s">
-        <v>199</v>
+        <v>198</v>
+      </c>
+      <c r="T381" t="s">
+        <v>213</v>
       </c>
       <c r="U381" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="V381" s="1">
-        <v>46283.75381304398</v>
+        <v>46287.42040790509</v>
       </c>
       <c r="W381">
         <v>1</v>
       </c>
       <c r="X381" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Y381" t="s">
         <v>375</v>
@@ -30314,21 +30419,21 @@
         <v>0</v>
       </c>
       <c r="AC381" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AH381" t="s">
         <v>414</v>
       </c>
       <c r="AI381" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="382" spans="1:35">
       <c r="A382">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B382" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C382" t="s">
         <v>50</v>
@@ -30337,13 +30442,13 @@
         <v>51</v>
       </c>
       <c r="E382" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F382" t="s">
         <v>56</v>
       </c>
       <c r="G382">
-        <v>7026</v>
+        <v>1882</v>
       </c>
       <c r="H382">
         <v>0</v>
@@ -30352,13 +30457,10 @@
         <v>62</v>
       </c>
       <c r="J382" t="s">
-        <v>119</v>
+        <v>151</v>
       </c>
       <c r="N382" s="1">
-        <v>46288</v>
-      </c>
-      <c r="O382" t="s">
-        <v>179</v>
+        <v>46287</v>
       </c>
       <c r="P382">
         <v>8</v>
@@ -30367,10 +30469,10 @@
         <v>2026</v>
       </c>
       <c r="R382">
-        <v>18094899</v>
+        <v>17968390</v>
       </c>
       <c r="S382" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="T382" t="s">
         <v>213</v>
@@ -30379,13 +30481,13 @@
         <v>216</v>
       </c>
       <c r="V382" s="1">
-        <v>46287.67534456019</v>
+        <v>46283.75381304398</v>
       </c>
       <c r="W382">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X382" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Y382" t="s">
         <v>376</v>
@@ -30394,21 +30496,21 @@
         <v>0</v>
       </c>
       <c r="AC382" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AH382" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI382" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="383" spans="1:35">
       <c r="A383">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B383" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C383" t="s">
         <v>50</v>
@@ -30417,7 +30519,7 @@
         <v>51</v>
       </c>
       <c r="E383" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F383" t="s">
         <v>56</v>
@@ -30437,6 +30539,9 @@
       <c r="N383" s="1">
         <v>46288</v>
       </c>
+      <c r="O383" t="s">
+        <v>179</v>
+      </c>
       <c r="P383">
         <v>8</v>
       </c>
@@ -30444,22 +30549,25 @@
         <v>2026</v>
       </c>
       <c r="R383">
-        <v>18048473</v>
+        <v>18094899</v>
       </c>
       <c r="S383" t="s">
-        <v>199</v>
+        <v>198</v>
+      </c>
+      <c r="T383" t="s">
+        <v>213</v>
       </c>
       <c r="U383" t="s">
         <v>216</v>
       </c>
       <c r="V383" s="1">
-        <v>46282.74485532408</v>
+        <v>46287.67534456019</v>
       </c>
       <c r="W383">
         <v>0</v>
       </c>
       <c r="X383" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Y383" t="s">
         <v>377</v>
@@ -30468,21 +30576,21 @@
         <v>0</v>
       </c>
       <c r="AC383" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AH383" t="s">
         <v>413</v>
       </c>
       <c r="AI383" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="384" spans="1:35">
       <c r="A384">
-        <v>6548</v>
+        <v>6627</v>
       </c>
       <c r="B384" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C384" t="s">
         <v>50</v>
@@ -30491,25 +30599,25 @@
         <v>51</v>
       </c>
       <c r="E384" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F384" t="s">
         <v>56</v>
       </c>
       <c r="G384">
-        <v>1914</v>
+        <v>7026</v>
       </c>
       <c r="H384">
-        <v>1862</v>
+        <v>0</v>
       </c>
       <c r="I384" t="s">
         <v>62</v>
       </c>
       <c r="J384" t="s">
-        <v>152</v>
+        <v>119</v>
       </c>
       <c r="N384" s="1">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="P384">
         <v>8</v>
@@ -30518,10 +30626,10 @@
         <v>2026</v>
       </c>
       <c r="R384">
-        <v>17988591</v>
+        <v>18048473</v>
       </c>
       <c r="S384" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="T384" t="s">
         <v>213</v>
@@ -30530,19 +30638,22 @@
         <v>216</v>
       </c>
       <c r="V384" s="1">
-        <v>46283.39413969908</v>
+        <v>46282.74485532408</v>
       </c>
       <c r="W384">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X384" t="s">
-        <v>218</v>
+        <v>219</v>
+      </c>
+      <c r="Y384" t="s">
+        <v>378</v>
       </c>
       <c r="AB384">
         <v>0</v>
       </c>
       <c r="AC384" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AH384" t="s">
         <v>413</v>
@@ -30553,10 +30664,10 @@
     </row>
     <row r="385" spans="1:35">
       <c r="A385">
-        <v>6949</v>
+        <v>6548</v>
       </c>
       <c r="B385" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C385" t="s">
         <v>50</v>
@@ -30568,7 +30679,7 @@
         <v>54</v>
       </c>
       <c r="F385" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G385">
         <v>1914</v>
@@ -30585,9 +30696,6 @@
       <c r="N385" s="1">
         <v>46286</v>
       </c>
-      <c r="O385" t="s">
-        <v>175</v>
-      </c>
       <c r="P385">
         <v>8</v>
       </c>
@@ -30595,48 +30703,45 @@
         <v>2026</v>
       </c>
       <c r="R385">
-        <v>18214883</v>
+        <v>17988591</v>
       </c>
       <c r="S385" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="T385" t="s">
         <v>213</v>
       </c>
       <c r="U385" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="V385" s="1">
-        <v>46286.72051887732</v>
+        <v>46283.39413969908</v>
       </c>
       <c r="W385">
         <v>2</v>
       </c>
       <c r="X385" t="s">
-        <v>220</v>
-      </c>
-      <c r="Y385" t="s">
-        <v>350</v>
+        <v>218</v>
       </c>
       <c r="AB385">
         <v>0</v>
       </c>
       <c r="AC385" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="AH385" t="s">
         <v>413</v>
       </c>
       <c r="AI385" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="386" spans="1:35">
       <c r="A386">
-        <v>5417</v>
+        <v>6949</v>
       </c>
       <c r="B386" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C386" t="s">
         <v>50</v>
@@ -30648,25 +30753,25 @@
         <v>54</v>
       </c>
       <c r="F386" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G386">
-        <v>6759</v>
+        <v>1914</v>
       </c>
       <c r="H386">
-        <v>1788</v>
+        <v>1862</v>
       </c>
       <c r="I386" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J386" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N386" s="1">
-        <v>46289</v>
+        <v>46286</v>
       </c>
       <c r="O386" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="P386">
         <v>8</v>
@@ -30675,40 +30780,40 @@
         <v>2026</v>
       </c>
       <c r="R386">
-        <v>17399190</v>
+        <v>18214883</v>
       </c>
       <c r="S386" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="T386" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="U386" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="V386" s="1">
-        <v>46283.54620269676</v>
+        <v>46286.72051887732</v>
       </c>
       <c r="W386">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="X386" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="Y386" t="s">
-        <v>378</v>
+        <v>351</v>
       </c>
       <c r="AB386">
         <v>0</v>
       </c>
       <c r="AC386" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="AH386" t="s">
         <v>413</v>
       </c>
       <c r="AI386" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="387" spans="1:35">
@@ -30731,22 +30836,22 @@
         <v>56</v>
       </c>
       <c r="G387">
-        <v>11678</v>
+        <v>6759</v>
       </c>
       <c r="H387">
-        <v>0</v>
+        <v>1788</v>
       </c>
       <c r="I387" t="s">
         <v>63</v>
       </c>
       <c r="J387" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="N387" s="1">
-        <v>46281</v>
+        <v>46289</v>
       </c>
       <c r="O387" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="P387">
         <v>8</v>
@@ -30755,7 +30860,7 @@
         <v>2026</v>
       </c>
       <c r="R387">
-        <v>16948688</v>
+        <v>17399190</v>
       </c>
       <c r="S387" t="s">
         <v>203</v>
@@ -30764,13 +30869,13 @@
         <v>214</v>
       </c>
       <c r="U387" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="V387" s="1">
-        <v>46287.46001957176</v>
+        <v>46283.54620269676</v>
       </c>
       <c r="W387">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="X387" t="s">
         <v>224</v>
@@ -30788,21 +30893,21 @@
         <v>413</v>
       </c>
       <c r="AI387" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="388" spans="1:35">
       <c r="A388">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B388" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C388" t="s">
         <v>50</v>
       </c>
       <c r="D388" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E388" t="s">
         <v>54</v>
@@ -30835,7 +30940,7 @@
         <v>2026</v>
       </c>
       <c r="R388">
-        <v>16962484</v>
+        <v>16948688</v>
       </c>
       <c r="S388" t="s">
         <v>203</v>
@@ -30847,16 +30952,16 @@
         <v>215</v>
       </c>
       <c r="V388" s="1">
-        <v>46287.46001266204</v>
+        <v>46287.46001957176</v>
       </c>
       <c r="W388">
         <v>7</v>
       </c>
       <c r="X388" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="Y388" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AB388">
         <v>0</v>
@@ -30873,16 +30978,16 @@
     </row>
     <row r="389" spans="1:35">
       <c r="A389">
-        <v>6486</v>
+        <v>6404</v>
       </c>
       <c r="B389" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C389" t="s">
         <v>50</v>
       </c>
       <c r="D389" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E389" t="s">
         <v>54</v>
@@ -30906,7 +31011,7 @@
         <v>46281</v>
       </c>
       <c r="O389" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="P389">
         <v>8</v>
@@ -30915,7 +31020,7 @@
         <v>2026</v>
       </c>
       <c r="R389">
-        <v>16976381</v>
+        <v>16962484</v>
       </c>
       <c r="S389" t="s">
         <v>203</v>
@@ -30927,13 +31032,13 @@
         <v>215</v>
       </c>
       <c r="V389" s="1">
-        <v>46286.72594498843</v>
+        <v>46287.46001266204</v>
       </c>
       <c r="W389">
         <v>7</v>
       </c>
       <c r="X389" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Y389" t="s">
         <v>380</v>
@@ -30953,10 +31058,10 @@
     </row>
     <row r="390" spans="1:35">
       <c r="A390">
-        <v>6704</v>
+        <v>6486</v>
       </c>
       <c r="B390" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C390" t="s">
         <v>50</v>
@@ -30971,7 +31076,7 @@
         <v>56</v>
       </c>
       <c r="G390">
-        <v>11874</v>
+        <v>11678</v>
       </c>
       <c r="H390">
         <v>0</v>
@@ -30980,13 +31085,13 @@
         <v>63</v>
       </c>
       <c r="J390" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="N390" s="1">
         <v>46281</v>
       </c>
       <c r="O390" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="P390">
         <v>8</v>
@@ -30995,7 +31100,7 @@
         <v>2026</v>
       </c>
       <c r="R390">
-        <v>18273589</v>
+        <v>16976381</v>
       </c>
       <c r="S390" t="s">
         <v>203</v>
@@ -31007,13 +31112,13 @@
         <v>215</v>
       </c>
       <c r="V390" s="1">
-        <v>46282.70138376157</v>
+        <v>46286.72594498843</v>
       </c>
       <c r="W390">
         <v>7</v>
       </c>
       <c r="X390" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Y390" t="s">
         <v>381</v>
@@ -31025,24 +31130,24 @@
         <v>203</v>
       </c>
       <c r="AH390" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AI390" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="391" spans="1:35">
       <c r="A391">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B391" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C391" t="s">
         <v>50</v>
       </c>
       <c r="D391" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E391" t="s">
         <v>54</v>
@@ -31075,7 +31180,7 @@
         <v>2026</v>
       </c>
       <c r="R391">
-        <v>18239293</v>
+        <v>18273589</v>
       </c>
       <c r="S391" t="s">
         <v>203</v>
@@ -31087,7 +31192,7 @@
         <v>215</v>
       </c>
       <c r="V391" s="1">
-        <v>46282.7013840625</v>
+        <v>46282.70138376157</v>
       </c>
       <c r="W391">
         <v>7</v>
@@ -31096,7 +31201,7 @@
         <v>223</v>
       </c>
       <c r="Y391" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AB391">
         <v>0</v>
@@ -31113,16 +31218,16 @@
     </row>
     <row r="392" spans="1:35">
       <c r="A392">
-        <v>6703</v>
+        <v>6705</v>
       </c>
       <c r="B392" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C392" t="s">
         <v>50</v>
       </c>
       <c r="D392" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E392" t="s">
         <v>54</v>
@@ -31131,7 +31236,7 @@
         <v>56</v>
       </c>
       <c r="G392">
-        <v>1802</v>
+        <v>11874</v>
       </c>
       <c r="H392">
         <v>0</v>
@@ -31140,10 +31245,13 @@
         <v>63</v>
       </c>
       <c r="J392" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="N392" s="1">
-        <v>46283</v>
+        <v>46281</v>
+      </c>
+      <c r="O392" t="s">
+        <v>171</v>
       </c>
       <c r="P392">
         <v>8</v>
@@ -31152,7 +31260,7 @@
         <v>2026</v>
       </c>
       <c r="R392">
-        <v>17948796</v>
+        <v>18239293</v>
       </c>
       <c r="S392" t="s">
         <v>203</v>
@@ -31161,16 +31269,16 @@
         <v>214</v>
       </c>
       <c r="U392" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="V392" s="1">
-        <v>46283.75077045139</v>
+        <v>46282.7013840625</v>
       </c>
       <c r="W392">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X392" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="Y392" t="s">
         <v>382</v>
@@ -31190,16 +31298,16 @@
     </row>
     <row r="393" spans="1:35">
       <c r="A393">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B393" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C393" t="s">
         <v>50</v>
       </c>
       <c r="D393" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E393" t="s">
         <v>54</v>
@@ -31222,9 +31330,6 @@
       <c r="N393" s="1">
         <v>46283</v>
       </c>
-      <c r="O393" t="s">
-        <v>175</v>
-      </c>
       <c r="P393">
         <v>8</v>
       </c>
@@ -31232,7 +31337,7 @@
         <v>2026</v>
       </c>
       <c r="R393">
-        <v>18085198</v>
+        <v>17948796</v>
       </c>
       <c r="S393" t="s">
         <v>203</v>
@@ -31241,16 +31346,16 @@
         <v>214</v>
       </c>
       <c r="U393" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="V393" s="1">
-        <v>46286.36164050926</v>
+        <v>46283.75077045139</v>
       </c>
       <c r="W393">
         <v>5</v>
       </c>
       <c r="X393" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Y393" t="s">
         <v>383</v>
@@ -31265,15 +31370,15 @@
         <v>414</v>
       </c>
       <c r="AI393" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="394" spans="1:35">
       <c r="A394">
-        <v>5417</v>
+        <v>6704</v>
       </c>
       <c r="B394" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C394" t="s">
         <v>50</v>
@@ -31288,7 +31393,7 @@
         <v>56</v>
       </c>
       <c r="G394">
-        <v>11286</v>
+        <v>1802</v>
       </c>
       <c r="H394">
         <v>0</v>
@@ -31297,7 +31402,7 @@
         <v>63</v>
       </c>
       <c r="J394" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="N394" s="1">
         <v>46283</v>
@@ -31312,7 +31417,7 @@
         <v>2026</v>
       </c>
       <c r="R394">
-        <v>17399434</v>
+        <v>18085198</v>
       </c>
       <c r="S394" t="s">
         <v>203</v>
@@ -31324,16 +31429,16 @@
         <v>215</v>
       </c>
       <c r="V394" s="1">
-        <v>46286.36164494213</v>
+        <v>46286.36164050926</v>
       </c>
       <c r="W394">
         <v>5</v>
       </c>
       <c r="X394" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="Y394" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AB394">
         <v>0</v>
@@ -31350,16 +31455,16 @@
     </row>
     <row r="395" spans="1:35">
       <c r="A395">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B395" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C395" t="s">
         <v>50</v>
       </c>
       <c r="D395" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E395" t="s">
         <v>54</v>
@@ -31392,7 +31497,7 @@
         <v>2026</v>
       </c>
       <c r="R395">
-        <v>16962464</v>
+        <v>17399434</v>
       </c>
       <c r="S395" t="s">
         <v>203</v>
@@ -31404,16 +31509,16 @@
         <v>215</v>
       </c>
       <c r="V395" s="1">
-        <v>46286.36164826389</v>
+        <v>46286.36164494213</v>
       </c>
       <c r="W395">
         <v>5</v>
       </c>
       <c r="X395" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="Y395" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AB395">
         <v>0</v>
@@ -31430,16 +31535,16 @@
     </row>
     <row r="396" spans="1:35">
       <c r="A396">
-        <v>6705</v>
+        <v>6404</v>
       </c>
       <c r="B396" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C396" t="s">
         <v>50</v>
       </c>
       <c r="D396" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E396" t="s">
         <v>54</v>
@@ -31448,7 +31553,7 @@
         <v>56</v>
       </c>
       <c r="G396">
-        <v>1805</v>
+        <v>11286</v>
       </c>
       <c r="H396">
         <v>0</v>
@@ -31457,11 +31562,14 @@
         <v>63</v>
       </c>
       <c r="J396" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="N396" s="1">
         <v>46283</v>
       </c>
+      <c r="O396" t="s">
+        <v>175</v>
+      </c>
       <c r="P396">
         <v>8</v>
       </c>
@@ -31469,7 +31577,7 @@
         <v>2026</v>
       </c>
       <c r="R396">
-        <v>17948948</v>
+        <v>16962464</v>
       </c>
       <c r="S396" t="s">
         <v>203</v>
@@ -31478,16 +31586,16 @@
         <v>214</v>
       </c>
       <c r="U396" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="V396" s="1">
-        <v>46283.35452896991</v>
+        <v>46286.36164826389</v>
       </c>
       <c r="W396">
         <v>5</v>
       </c>
       <c r="X396" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="Y396" t="s">
         <v>384</v>
@@ -31502,15 +31610,15 @@
         <v>414</v>
       </c>
       <c r="AI396" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="397" spans="1:35">
       <c r="A397">
-        <v>6779</v>
+        <v>6705</v>
       </c>
       <c r="B397" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C397" t="s">
         <v>50</v>
@@ -31546,7 +31654,7 @@
         <v>2026</v>
       </c>
       <c r="R397">
-        <v>18084966</v>
+        <v>17948948</v>
       </c>
       <c r="S397" t="s">
         <v>203</v>
@@ -31558,7 +31666,7 @@
         <v>217</v>
       </c>
       <c r="V397" s="1">
-        <v>46283.35453171296</v>
+        <v>46283.35452896991</v>
       </c>
       <c r="W397">
         <v>5</v>
@@ -31567,7 +31675,7 @@
         <v>223</v>
       </c>
       <c r="Y397" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AB397">
         <v>0</v>
@@ -31584,16 +31692,16 @@
     </row>
     <row r="398" spans="1:35">
       <c r="A398">
-        <v>6703</v>
+        <v>6779</v>
       </c>
       <c r="B398" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C398" t="s">
         <v>50</v>
       </c>
       <c r="D398" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E398" t="s">
         <v>54</v>
@@ -31602,7 +31710,7 @@
         <v>56</v>
       </c>
       <c r="G398">
-        <v>1811</v>
+        <v>1805</v>
       </c>
       <c r="H398">
         <v>0</v>
@@ -31611,22 +31719,19 @@
         <v>63</v>
       </c>
       <c r="J398" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="N398" s="1">
-        <v>46290</v>
-      </c>
-      <c r="O398" t="s">
-        <v>176</v>
+        <v>46283</v>
       </c>
       <c r="P398">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q398">
         <v>2026</v>
       </c>
       <c r="R398">
-        <v>17948816</v>
+        <v>18084966</v>
       </c>
       <c r="S398" t="s">
         <v>203</v>
@@ -31635,16 +31740,16 @@
         <v>214</v>
       </c>
       <c r="U398" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="V398" s="1">
-        <v>46287.36782538195</v>
+        <v>46283.35453171296</v>
       </c>
       <c r="W398">
-        <v>-2</v>
+        <v>5</v>
       </c>
       <c r="X398" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="Y398" t="s">
         <v>385</v>
@@ -31659,15 +31764,15 @@
         <v>414</v>
       </c>
       <c r="AI398" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="399" spans="1:35">
       <c r="A399">
-        <v>6404</v>
+        <v>6703</v>
       </c>
       <c r="B399" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C399" t="s">
         <v>50</v>
@@ -31682,7 +31787,7 @@
         <v>56</v>
       </c>
       <c r="G399">
-        <v>1807</v>
+        <v>1811</v>
       </c>
       <c r="H399">
         <v>0</v>
@@ -31691,22 +31796,22 @@
         <v>63</v>
       </c>
       <c r="J399" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="N399" s="1">
-        <v>46287</v>
+        <v>46290</v>
       </c>
       <c r="O399" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P399">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q399">
         <v>2026</v>
       </c>
       <c r="R399">
-        <v>16962171</v>
+        <v>17948816</v>
       </c>
       <c r="S399" t="s">
         <v>203</v>
@@ -31715,16 +31820,16 @@
         <v>214</v>
       </c>
       <c r="U399" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="V399" s="1">
-        <v>46287.42044105324</v>
+        <v>46287.36782538195</v>
       </c>
       <c r="W399">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="X399" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Y399" t="s">
         <v>386</v>
@@ -31744,16 +31849,16 @@
     </row>
     <row r="400" spans="1:35">
       <c r="A400">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B400" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C400" t="s">
         <v>50</v>
       </c>
       <c r="D400" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E400" t="s">
         <v>54</v>
@@ -31762,7 +31867,7 @@
         <v>56</v>
       </c>
       <c r="G400">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="H400">
         <v>0</v>
@@ -31771,7 +31876,7 @@
         <v>63</v>
       </c>
       <c r="J400" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="N400" s="1">
         <v>46287</v>
@@ -31786,7 +31891,7 @@
         <v>2026</v>
       </c>
       <c r="R400">
-        <v>17398965</v>
+        <v>16962171</v>
       </c>
       <c r="S400" t="s">
         <v>203</v>
@@ -31798,13 +31903,13 @@
         <v>217</v>
       </c>
       <c r="V400" s="1">
-        <v>46287.75597989583</v>
+        <v>46287.42044105324</v>
       </c>
       <c r="W400">
         <v>1</v>
       </c>
       <c r="X400" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Y400" t="s">
         <v>387</v>
@@ -31842,7 +31947,7 @@
         <v>56</v>
       </c>
       <c r="G401">
-        <v>7025</v>
+        <v>1808</v>
       </c>
       <c r="H401">
         <v>0</v>
@@ -31851,10 +31956,13 @@
         <v>63</v>
       </c>
       <c r="J401" t="s">
-        <v>119</v>
+        <v>151</v>
       </c>
       <c r="N401" s="1">
-        <v>46288</v>
+        <v>46287</v>
+      </c>
+      <c r="O401" t="s">
+        <v>177</v>
       </c>
       <c r="P401">
         <v>8</v>
@@ -31863,7 +31971,7 @@
         <v>2026</v>
       </c>
       <c r="R401">
-        <v>17399280</v>
+        <v>17398965</v>
       </c>
       <c r="S401" t="s">
         <v>203</v>
@@ -31872,13 +31980,13 @@
         <v>214</v>
       </c>
       <c r="U401" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="V401" s="1">
-        <v>46283.38367943287</v>
+        <v>46287.75597989583</v>
       </c>
       <c r="W401">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X401" t="s">
         <v>224</v>
@@ -31893,24 +32001,24 @@
         <v>203</v>
       </c>
       <c r="AH401" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI401" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="402" spans="1:35">
       <c r="A402">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B402" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C402" t="s">
         <v>50</v>
       </c>
       <c r="D402" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E402" t="s">
         <v>54</v>
@@ -31940,7 +32048,7 @@
         <v>2026</v>
       </c>
       <c r="R402">
-        <v>16962338</v>
+        <v>17399280</v>
       </c>
       <c r="S402" t="s">
         <v>203</v>
@@ -31952,13 +32060,13 @@
         <v>216</v>
       </c>
       <c r="V402" s="1">
-        <v>46282.54038741898</v>
+        <v>46283.38367943287</v>
       </c>
       <c r="W402">
         <v>0</v>
       </c>
       <c r="X402" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="Y402" t="s">
         <v>389</v>
@@ -31978,40 +32086,37 @@
     </row>
     <row r="403" spans="1:35">
       <c r="A403">
-        <v>6628</v>
+        <v>6404</v>
       </c>
       <c r="B403" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C403" t="s">
         <v>50</v>
       </c>
       <c r="D403" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E403" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F403" t="s">
         <v>56</v>
       </c>
       <c r="G403">
-        <v>945</v>
+        <v>7025</v>
       </c>
       <c r="H403">
         <v>0</v>
       </c>
       <c r="I403" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J403" t="s">
-        <v>156</v>
+        <v>119</v>
       </c>
       <c r="N403" s="1">
-        <v>46283</v>
-      </c>
-      <c r="O403" t="s">
-        <v>170</v>
+        <v>46288</v>
       </c>
       <c r="P403">
         <v>8</v>
@@ -32020,22 +32125,25 @@
         <v>2026</v>
       </c>
       <c r="R403">
-        <v>16959938</v>
+        <v>16962338</v>
       </c>
       <c r="S403" t="s">
-        <v>204</v>
+        <v>203</v>
+      </c>
+      <c r="T403" t="s">
+        <v>214</v>
       </c>
       <c r="U403" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="V403" s="1">
-        <v>46283.64213659722</v>
+        <v>46282.54038741898</v>
       </c>
       <c r="W403">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="X403" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="Y403" t="s">
         <v>390</v>
@@ -32044,10 +32152,10 @@
         <v>0</v>
       </c>
       <c r="AC403" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AH403" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AI403" t="s">
         <v>418</v>
@@ -32055,10 +32163,10 @@
     </row>
     <row r="404" spans="1:35">
       <c r="A404">
-        <v>6705</v>
+        <v>6628</v>
       </c>
       <c r="B404" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C404" t="s">
         <v>50</v>
@@ -32067,7 +32175,7 @@
         <v>52</v>
       </c>
       <c r="E404" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F404" t="s">
         <v>56</v>
@@ -32097,7 +32205,7 @@
         <v>2026</v>
       </c>
       <c r="R404">
-        <v>17952524</v>
+        <v>16959938</v>
       </c>
       <c r="S404" t="s">
         <v>204</v>
@@ -32106,13 +32214,13 @@
         <v>217</v>
       </c>
       <c r="V404" s="1">
-        <v>46283.65291121528</v>
+        <v>46283.64213659722</v>
       </c>
       <c r="W404">
         <v>5</v>
       </c>
       <c r="X404" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="Y404" t="s">
         <v>391</v>
@@ -32132,10 +32240,10 @@
     </row>
     <row r="405" spans="1:35">
       <c r="A405">
-        <v>6779</v>
+        <v>6705</v>
       </c>
       <c r="B405" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C405" t="s">
         <v>50</v>
@@ -32174,7 +32282,7 @@
         <v>2026</v>
       </c>
       <c r="R405">
-        <v>18056695</v>
+        <v>17952524</v>
       </c>
       <c r="S405" t="s">
         <v>204</v>
@@ -32183,7 +32291,7 @@
         <v>217</v>
       </c>
       <c r="V405" s="1">
-        <v>46283.65291194445</v>
+        <v>46283.65291121528</v>
       </c>
       <c r="W405">
         <v>5</v>
@@ -32192,7 +32300,7 @@
         <v>223</v>
       </c>
       <c r="Y405" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AB405">
         <v>0</v>
@@ -32209,10 +32317,10 @@
     </row>
     <row r="406" spans="1:35">
       <c r="A406">
-        <v>6945</v>
+        <v>6779</v>
       </c>
       <c r="B406" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C406" t="s">
         <v>50</v>
@@ -32224,7 +32332,7 @@
         <v>54</v>
       </c>
       <c r="F406" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G406">
         <v>945</v>
@@ -32242,7 +32350,7 @@
         <v>46283</v>
       </c>
       <c r="O406" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="P406">
         <v>8</v>
@@ -32251,22 +32359,22 @@
         <v>2026</v>
       </c>
       <c r="R406">
-        <v>18164487</v>
+        <v>18056695</v>
       </c>
       <c r="S406" t="s">
         <v>204</v>
       </c>
       <c r="U406" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="V406" s="1">
-        <v>46286.39955256944</v>
+        <v>46283.65291194445</v>
       </c>
       <c r="W406">
         <v>5</v>
       </c>
       <c r="X406" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Y406" t="s">
         <v>392</v>
@@ -32281,30 +32389,30 @@
         <v>414</v>
       </c>
       <c r="AI406" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="407" spans="1:35">
       <c r="A407">
-        <v>5417</v>
+        <v>6945</v>
       </c>
       <c r="B407" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C407" t="s">
         <v>50</v>
       </c>
       <c r="D407" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E407" t="s">
         <v>54</v>
       </c>
       <c r="F407" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G407">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H407">
         <v>0</v>
@@ -32313,11 +32421,14 @@
         <v>64</v>
       </c>
       <c r="J407" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="N407" s="1">
         <v>46283</v>
       </c>
+      <c r="O407" t="s">
+        <v>175</v>
+      </c>
       <c r="P407">
         <v>8</v>
       </c>
@@ -32325,7 +32436,7 @@
         <v>2026</v>
       </c>
       <c r="R407">
-        <v>17398869</v>
+        <v>18164487</v>
       </c>
       <c r="S407" t="s">
         <v>204</v>
@@ -32334,13 +32445,13 @@
         <v>215</v>
       </c>
       <c r="V407" s="1">
-        <v>46286.42397924769</v>
+        <v>46286.39955256944</v>
       </c>
       <c r="W407">
         <v>5</v>
       </c>
       <c r="X407" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="Y407" t="s">
         <v>393</v>
@@ -32360,16 +32471,16 @@
     </row>
     <row r="408" spans="1:35">
       <c r="A408">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B408" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C408" t="s">
         <v>50</v>
       </c>
       <c r="D408" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E408" t="s">
         <v>54</v>
@@ -32399,7 +32510,7 @@
         <v>2026</v>
       </c>
       <c r="R408">
-        <v>16962093</v>
+        <v>17398869</v>
       </c>
       <c r="S408" t="s">
         <v>204</v>
@@ -32408,16 +32519,16 @@
         <v>215</v>
       </c>
       <c r="V408" s="1">
-        <v>46286.42389136574</v>
+        <v>46286.42397924769</v>
       </c>
       <c r="W408">
         <v>5</v>
       </c>
       <c r="X408" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="Y408" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AB408">
         <v>0</v>
@@ -32434,19 +32545,19 @@
     </row>
     <row r="409" spans="1:35">
       <c r="A409">
-        <v>6627</v>
+        <v>6404</v>
       </c>
       <c r="B409" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="C409" t="s">
         <v>50</v>
       </c>
       <c r="D409" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E409" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F409" t="s">
         <v>56</v>
@@ -32466,9 +32577,6 @@
       <c r="N409" s="1">
         <v>46283</v>
       </c>
-      <c r="O409" t="s">
-        <v>170</v>
-      </c>
       <c r="P409">
         <v>8</v>
       </c>
@@ -32476,25 +32584,25 @@
         <v>2026</v>
       </c>
       <c r="R409">
-        <v>17042272</v>
+        <v>16962093</v>
       </c>
       <c r="S409" t="s">
         <v>204</v>
       </c>
       <c r="U409" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="V409" s="1">
-        <v>46283.67999300926</v>
+        <v>46286.42389136574</v>
       </c>
       <c r="W409">
         <v>5</v>
       </c>
       <c r="X409" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="Y409" t="s">
-        <v>328</v>
+        <v>394</v>
       </c>
       <c r="AB409">
         <v>0</v>
@@ -32506,24 +32614,24 @@
         <v>414</v>
       </c>
       <c r="AI409" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="410" spans="1:35">
       <c r="A410">
-        <v>6703</v>
+        <v>6627</v>
       </c>
       <c r="B410" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C410" t="s">
         <v>50</v>
       </c>
       <c r="D410" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E410" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F410" t="s">
         <v>56</v>
@@ -32544,7 +32652,7 @@
         <v>46283</v>
       </c>
       <c r="O410" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="P410">
         <v>8</v>
@@ -32553,25 +32661,25 @@
         <v>2026</v>
       </c>
       <c r="R410">
-        <v>17941132</v>
+        <v>17042272</v>
       </c>
       <c r="S410" t="s">
         <v>204</v>
       </c>
       <c r="U410" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="V410" s="1">
-        <v>46286.42398471065</v>
+        <v>46283.67999300926</v>
       </c>
       <c r="W410">
         <v>5</v>
       </c>
       <c r="X410" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="Y410" t="s">
-        <v>394</v>
+        <v>328</v>
       </c>
       <c r="AB410">
         <v>0</v>
@@ -32583,21 +32691,21 @@
         <v>414</v>
       </c>
       <c r="AI410" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="411" spans="1:35">
       <c r="A411">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B411" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C411" t="s">
         <v>50</v>
       </c>
       <c r="D411" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E411" t="s">
         <v>54</v>
@@ -32620,6 +32728,9 @@
       <c r="N411" s="1">
         <v>46283</v>
       </c>
+      <c r="O411" t="s">
+        <v>175</v>
+      </c>
       <c r="P411">
         <v>8</v>
       </c>
@@ -32627,7 +32738,7 @@
         <v>2026</v>
       </c>
       <c r="R411">
-        <v>17952325</v>
+        <v>17941132</v>
       </c>
       <c r="S411" t="s">
         <v>204</v>
@@ -32636,13 +32747,13 @@
         <v>215</v>
       </c>
       <c r="V411" s="1">
-        <v>46286.42398568287</v>
+        <v>46286.42398471065</v>
       </c>
       <c r="W411">
         <v>5</v>
       </c>
       <c r="X411" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Y411" t="s">
         <v>395</v>
@@ -32662,22 +32773,22 @@
     </row>
     <row r="412" spans="1:35">
       <c r="A412">
-        <v>6945</v>
+        <v>6704</v>
       </c>
       <c r="B412" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C412" t="s">
         <v>50</v>
       </c>
       <c r="D412" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E412" t="s">
         <v>54</v>
       </c>
       <c r="F412" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G412">
         <v>946</v>
@@ -32694,9 +32805,6 @@
       <c r="N412" s="1">
         <v>46283</v>
       </c>
-      <c r="O412" t="s">
-        <v>170</v>
-      </c>
       <c r="P412">
         <v>8</v>
       </c>
@@ -32704,25 +32812,25 @@
         <v>2026</v>
       </c>
       <c r="R412">
-        <v>18164494</v>
+        <v>17952325</v>
       </c>
       <c r="S412" t="s">
         <v>204</v>
       </c>
       <c r="U412" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="V412" s="1">
-        <v>46283.67625043981</v>
+        <v>46286.42398568287</v>
       </c>
       <c r="W412">
         <v>5</v>
       </c>
       <c r="X412" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Y412" t="s">
-        <v>328</v>
+        <v>396</v>
       </c>
       <c r="AB412">
         <v>0</v>
@@ -32734,15 +32842,15 @@
         <v>414</v>
       </c>
       <c r="AI412" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="413" spans="1:35">
       <c r="A413">
-        <v>6705</v>
+        <v>6945</v>
       </c>
       <c r="B413" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="C413" t="s">
         <v>50</v>
@@ -32754,10 +32862,10 @@
         <v>54</v>
       </c>
       <c r="F413" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G413">
-        <v>7022</v>
+        <v>946</v>
       </c>
       <c r="H413">
         <v>0</v>
@@ -32766,7 +32874,7 @@
         <v>64</v>
       </c>
       <c r="J413" t="s">
-        <v>113</v>
+        <v>157</v>
       </c>
       <c r="N413" s="1">
         <v>46283</v>
@@ -32781,7 +32889,7 @@
         <v>2026</v>
       </c>
       <c r="R413">
-        <v>17952601</v>
+        <v>18164494</v>
       </c>
       <c r="S413" t="s">
         <v>204</v>
@@ -32790,13 +32898,13 @@
         <v>217</v>
       </c>
       <c r="V413" s="1">
-        <v>46283.38329579861</v>
+        <v>46283.67625043981</v>
       </c>
       <c r="W413">
         <v>5</v>
       </c>
       <c r="X413" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="Y413" t="s">
         <v>328</v>
@@ -32816,16 +32924,16 @@
     </row>
     <row r="414" spans="1:35">
       <c r="A414">
-        <v>5417</v>
+        <v>6705</v>
       </c>
       <c r="B414" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C414" t="s">
         <v>50</v>
       </c>
       <c r="D414" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E414" t="s">
         <v>54</v>
@@ -32834,7 +32942,7 @@
         <v>56</v>
       </c>
       <c r="G414">
-        <v>9086</v>
+        <v>7022</v>
       </c>
       <c r="H414">
         <v>0</v>
@@ -32843,22 +32951,22 @@
         <v>64</v>
       </c>
       <c r="J414" t="s">
-        <v>158</v>
+        <v>113</v>
       </c>
       <c r="N414" s="1">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="O414" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P414">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q414">
         <v>2026</v>
       </c>
       <c r="R414">
-        <v>17399363</v>
+        <v>17952601</v>
       </c>
       <c r="S414" t="s">
         <v>204</v>
@@ -32867,16 +32975,16 @@
         <v>217</v>
       </c>
       <c r="V414" s="1">
-        <v>46282.36440621527</v>
+        <v>46283.38329579861</v>
       </c>
       <c r="W414">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X414" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="Y414" t="s">
-        <v>396</v>
+        <v>328</v>
       </c>
       <c r="AB414">
         <v>0</v>
@@ -32885,7 +32993,7 @@
         <v>204</v>
       </c>
       <c r="AH414" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AI414" t="s">
         <v>418</v>
@@ -32893,16 +33001,16 @@
     </row>
     <row r="415" spans="1:35">
       <c r="A415">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B415" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C415" t="s">
         <v>50</v>
       </c>
       <c r="D415" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E415" t="s">
         <v>54</v>
@@ -32935,7 +33043,7 @@
         <v>2026</v>
       </c>
       <c r="R415">
-        <v>16962380</v>
+        <v>17399363</v>
       </c>
       <c r="S415" t="s">
         <v>204</v>
@@ -32944,16 +33052,16 @@
         <v>217</v>
       </c>
       <c r="V415" s="1">
-        <v>46282.36462596065</v>
+        <v>46282.36440621527</v>
       </c>
       <c r="W415">
         <v>6</v>
       </c>
       <c r="X415" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="Y415" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AB415">
         <v>0</v>
@@ -32970,16 +33078,16 @@
     </row>
     <row r="416" spans="1:35">
       <c r="A416">
-        <v>6486</v>
+        <v>6404</v>
       </c>
       <c r="B416" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C416" t="s">
         <v>50</v>
       </c>
       <c r="D416" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E416" t="s">
         <v>54</v>
@@ -33012,7 +33120,7 @@
         <v>2026</v>
       </c>
       <c r="R416">
-        <v>16976270</v>
+        <v>16962380</v>
       </c>
       <c r="S416" t="s">
         <v>204</v>
@@ -33021,16 +33129,16 @@
         <v>217</v>
       </c>
       <c r="V416" s="1">
-        <v>46282.36464421296</v>
+        <v>46282.36462596065</v>
       </c>
       <c r="W416">
         <v>6</v>
       </c>
       <c r="X416" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Y416" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AB416">
         <v>0</v>
@@ -33047,10 +33155,10 @@
     </row>
     <row r="417" spans="1:35">
       <c r="A417">
-        <v>6548</v>
+        <v>6486</v>
       </c>
       <c r="B417" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C417" t="s">
         <v>50</v>
@@ -33089,7 +33197,7 @@
         <v>2026</v>
       </c>
       <c r="R417">
-        <v>17222865</v>
+        <v>16976270</v>
       </c>
       <c r="S417" t="s">
         <v>204</v>
@@ -33098,16 +33206,16 @@
         <v>217</v>
       </c>
       <c r="V417" s="1">
-        <v>46282.36467337963</v>
+        <v>46282.36464421296</v>
       </c>
       <c r="W417">
         <v>6</v>
       </c>
       <c r="X417" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="Y417" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AB417">
         <v>0</v>
@@ -33124,10 +33232,10 @@
     </row>
     <row r="418" spans="1:35">
       <c r="A418">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B418" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C418" t="s">
         <v>50</v>
@@ -33136,7 +33244,7 @@
         <v>51</v>
       </c>
       <c r="E418" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F418" t="s">
         <v>56</v>
@@ -33166,7 +33274,7 @@
         <v>2026</v>
       </c>
       <c r="R418">
-        <v>17042587</v>
+        <v>17222865</v>
       </c>
       <c r="S418" t="s">
         <v>204</v>
@@ -33175,16 +33283,16 @@
         <v>217</v>
       </c>
       <c r="V418" s="1">
-        <v>46282.36469679398</v>
+        <v>46282.36467337963</v>
       </c>
       <c r="W418">
         <v>6</v>
       </c>
       <c r="X418" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Y418" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AB418">
         <v>0</v>
@@ -33201,16 +33309,16 @@
     </row>
     <row r="419" spans="1:35">
       <c r="A419">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B419" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C419" t="s">
         <v>50</v>
       </c>
       <c r="D419" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E419" t="s">
         <v>55</v>
@@ -33243,7 +33351,7 @@
         <v>2026</v>
       </c>
       <c r="R419">
-        <v>16960074</v>
+        <v>17042587</v>
       </c>
       <c r="S419" t="s">
         <v>204</v>
@@ -33252,7 +33360,7 @@
         <v>217</v>
       </c>
       <c r="V419" s="1">
-        <v>46282.36469869213</v>
+        <v>46282.36469679398</v>
       </c>
       <c r="W419">
         <v>6</v>
@@ -33261,7 +33369,7 @@
         <v>219</v>
       </c>
       <c r="Y419" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AB419">
         <v>0</v>
@@ -33278,19 +33386,19 @@
     </row>
     <row r="420" spans="1:35">
       <c r="A420">
-        <v>6703</v>
+        <v>6628</v>
       </c>
       <c r="B420" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C420" t="s">
         <v>50</v>
       </c>
       <c r="D420" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E420" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F420" t="s">
         <v>56</v>
@@ -33320,7 +33428,7 @@
         <v>2026</v>
       </c>
       <c r="R420">
-        <v>17941217</v>
+        <v>16960074</v>
       </c>
       <c r="S420" t="s">
         <v>204</v>
@@ -33329,16 +33437,16 @@
         <v>217</v>
       </c>
       <c r="V420" s="1">
-        <v>46282.36473159722</v>
+        <v>46282.36469869213</v>
       </c>
       <c r="W420">
         <v>6</v>
       </c>
       <c r="X420" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="Y420" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AB420">
         <v>0</v>
@@ -33355,16 +33463,16 @@
     </row>
     <row r="421" spans="1:35">
       <c r="A421">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B421" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C421" t="s">
         <v>50</v>
       </c>
       <c r="D421" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E421" t="s">
         <v>54</v>
@@ -33397,7 +33505,7 @@
         <v>2026</v>
       </c>
       <c r="R421">
-        <v>17952444</v>
+        <v>17941217</v>
       </c>
       <c r="S421" t="s">
         <v>204</v>
@@ -33406,16 +33514,16 @@
         <v>217</v>
       </c>
       <c r="V421" s="1">
-        <v>46282.36473394676</v>
+        <v>46282.36473159722</v>
       </c>
       <c r="W421">
         <v>6</v>
       </c>
       <c r="X421" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Y421" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AB421">
         <v>0</v>
@@ -33432,16 +33540,16 @@
     </row>
     <row r="422" spans="1:35">
       <c r="A422">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B422" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C422" t="s">
         <v>50</v>
       </c>
       <c r="D422" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E422" t="s">
         <v>54</v>
@@ -33474,7 +33582,7 @@
         <v>2026</v>
       </c>
       <c r="R422">
-        <v>17952624</v>
+        <v>17952444</v>
       </c>
       <c r="S422" t="s">
         <v>204</v>
@@ -33483,7 +33591,7 @@
         <v>217</v>
       </c>
       <c r="V422" s="1">
-        <v>46282.36473579861</v>
+        <v>46282.36473394676</v>
       </c>
       <c r="W422">
         <v>6</v>
@@ -33492,7 +33600,7 @@
         <v>223</v>
       </c>
       <c r="Y422" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AB422">
         <v>0</v>
@@ -33509,10 +33617,10 @@
     </row>
     <row r="423" spans="1:35">
       <c r="A423">
-        <v>6779</v>
+        <v>6705</v>
       </c>
       <c r="B423" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C423" t="s">
         <v>50</v>
@@ -33551,7 +33659,7 @@
         <v>2026</v>
       </c>
       <c r="R423">
-        <v>18056801</v>
+        <v>17952624</v>
       </c>
       <c r="S423" t="s">
         <v>204</v>
@@ -33560,7 +33668,7 @@
         <v>217</v>
       </c>
       <c r="V423" s="1">
-        <v>46282.36475297454</v>
+        <v>46282.36473579861</v>
       </c>
       <c r="W423">
         <v>6</v>
@@ -33569,7 +33677,7 @@
         <v>223</v>
       </c>
       <c r="Y423" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AB423">
         <v>0</v>
@@ -33586,10 +33694,10 @@
     </row>
     <row r="424" spans="1:35">
       <c r="A424">
-        <v>6945</v>
+        <v>6779</v>
       </c>
       <c r="B424" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C424" t="s">
         <v>50</v>
@@ -33601,7 +33709,7 @@
         <v>54</v>
       </c>
       <c r="F424" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G424">
         <v>9086</v>
@@ -33628,7 +33736,7 @@
         <v>2026</v>
       </c>
       <c r="R424">
-        <v>18164551</v>
+        <v>18056801</v>
       </c>
       <c r="S424" t="s">
         <v>204</v>
@@ -33637,16 +33745,16 @@
         <v>217</v>
       </c>
       <c r="V424" s="1">
-        <v>46282.36486408565</v>
+        <v>46282.36475297454</v>
       </c>
       <c r="W424">
         <v>6</v>
       </c>
       <c r="X424" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Y424" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AB424">
         <v>0</v>
@@ -33663,16 +33771,16 @@
     </row>
     <row r="425" spans="1:35">
       <c r="A425">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B425" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C425" t="s">
         <v>50</v>
       </c>
       <c r="D425" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E425" t="s">
         <v>54</v>
@@ -33705,7 +33813,7 @@
         <v>2026</v>
       </c>
       <c r="R425">
-        <v>18178187</v>
+        <v>18164551</v>
       </c>
       <c r="S425" t="s">
         <v>204</v>
@@ -33714,13 +33822,13 @@
         <v>217</v>
       </c>
       <c r="V425" s="1">
-        <v>46282.36487561343</v>
+        <v>46282.36486408565</v>
       </c>
       <c r="W425">
         <v>6</v>
       </c>
       <c r="X425" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Y425" t="s">
         <v>397</v>
@@ -33740,16 +33848,16 @@
     </row>
     <row r="426" spans="1:35">
       <c r="A426">
-        <v>6962</v>
+        <v>6949</v>
       </c>
       <c r="B426" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C426" t="s">
         <v>50</v>
       </c>
       <c r="D426" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E426" t="s">
         <v>54</v>
@@ -33782,7 +33890,7 @@
         <v>2026</v>
       </c>
       <c r="R426">
-        <v>18188774</v>
+        <v>18178187</v>
       </c>
       <c r="S426" t="s">
         <v>204</v>
@@ -33791,16 +33899,16 @@
         <v>217</v>
       </c>
       <c r="V426" s="1">
-        <v>46282.36486778935</v>
+        <v>46282.36487561343</v>
       </c>
       <c r="W426">
         <v>6</v>
       </c>
       <c r="X426" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="Y426" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AB426">
         <v>0</v>
@@ -33817,10 +33925,10 @@
     </row>
     <row r="427" spans="1:35">
       <c r="A427">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B427" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C427" t="s">
         <v>50</v>
@@ -33859,7 +33967,7 @@
         <v>2026</v>
       </c>
       <c r="R427">
-        <v>18188680</v>
+        <v>18188774</v>
       </c>
       <c r="S427" t="s">
         <v>204</v>
@@ -33868,7 +33976,7 @@
         <v>217</v>
       </c>
       <c r="V427" s="1">
-        <v>46282.36486851852</v>
+        <v>46282.36486778935</v>
       </c>
       <c r="W427">
         <v>6</v>
@@ -33877,7 +33985,7 @@
         <v>222</v>
       </c>
       <c r="Y427" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AB427">
         <v>0</v>
@@ -33894,25 +34002,25 @@
     </row>
     <row r="428" spans="1:35">
       <c r="A428">
-        <v>5417</v>
+        <v>6963</v>
       </c>
       <c r="B428" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C428" t="s">
         <v>50</v>
       </c>
       <c r="D428" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E428" t="s">
         <v>54</v>
       </c>
       <c r="F428" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G428">
-        <v>940</v>
+        <v>9086</v>
       </c>
       <c r="H428">
         <v>0</v>
@@ -33921,13 +34029,13 @@
         <v>64</v>
       </c>
       <c r="J428" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N428" s="1">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="O428" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="P428">
         <v>9</v>
@@ -33936,25 +34044,25 @@
         <v>2026</v>
       </c>
       <c r="R428">
-        <v>17398840</v>
+        <v>18188680</v>
       </c>
       <c r="S428" t="s">
         <v>204</v>
       </c>
       <c r="U428" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="V428" s="1">
-        <v>46286.45925082176</v>
+        <v>46282.36486851852</v>
       </c>
       <c r="W428">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X428" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="Y428" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AB428">
         <v>0</v>
@@ -33966,21 +34074,21 @@
         <v>415</v>
       </c>
       <c r="AI428" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="429" spans="1:35">
       <c r="A429">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B429" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C429" t="s">
         <v>50</v>
       </c>
       <c r="D429" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E429" t="s">
         <v>54</v>
@@ -34004,7 +34112,7 @@
         <v>46283</v>
       </c>
       <c r="O429" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="P429">
         <v>9</v>
@@ -34013,22 +34121,22 @@
         <v>2026</v>
       </c>
       <c r="R429">
-        <v>16962074</v>
+        <v>17398840</v>
       </c>
       <c r="S429" t="s">
         <v>204</v>
       </c>
       <c r="U429" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="V429" s="1">
-        <v>46282.79619427084</v>
+        <v>46286.45925082176</v>
       </c>
       <c r="W429">
         <v>5</v>
       </c>
       <c r="X429" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="Y429" t="s">
         <v>399</v>
@@ -34043,21 +34151,21 @@
         <v>415</v>
       </c>
       <c r="AI429" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="430" spans="1:35">
       <c r="A430">
-        <v>6486</v>
+        <v>6404</v>
       </c>
       <c r="B430" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C430" t="s">
         <v>50</v>
       </c>
       <c r="D430" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E430" t="s">
         <v>54</v>
@@ -34090,7 +34198,7 @@
         <v>2026</v>
       </c>
       <c r="R430">
-        <v>16975871</v>
+        <v>16962074</v>
       </c>
       <c r="S430" t="s">
         <v>204</v>
@@ -34099,16 +34207,16 @@
         <v>216</v>
       </c>
       <c r="V430" s="1">
-        <v>46282.79620872685</v>
+        <v>46282.79619427084</v>
       </c>
       <c r="W430">
         <v>5</v>
       </c>
       <c r="X430" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Y430" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AB430">
         <v>0</v>
@@ -34125,10 +34233,10 @@
     </row>
     <row r="431" spans="1:35">
       <c r="A431">
-        <v>6548</v>
+        <v>6486</v>
       </c>
       <c r="B431" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C431" t="s">
         <v>50</v>
@@ -34167,7 +34275,7 @@
         <v>2026</v>
       </c>
       <c r="R431">
-        <v>17222366</v>
+        <v>16975871</v>
       </c>
       <c r="S431" t="s">
         <v>204</v>
@@ -34176,16 +34284,16 @@
         <v>216</v>
       </c>
       <c r="V431" s="1">
-        <v>46282.79623825232</v>
+        <v>46282.79620872685</v>
       </c>
       <c r="W431">
         <v>5</v>
       </c>
       <c r="X431" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="Y431" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AB431">
         <v>0</v>
@@ -34202,10 +34310,10 @@
     </row>
     <row r="432" spans="1:35">
       <c r="A432">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B432" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C432" t="s">
         <v>50</v>
@@ -34214,7 +34322,7 @@
         <v>51</v>
       </c>
       <c r="E432" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F432" t="s">
         <v>56</v>
@@ -34244,7 +34352,7 @@
         <v>2026</v>
       </c>
       <c r="R432">
-        <v>17042221</v>
+        <v>17222366</v>
       </c>
       <c r="S432" t="s">
         <v>204</v>
@@ -34253,16 +34361,16 @@
         <v>216</v>
       </c>
       <c r="V432" s="1">
-        <v>46282.7962541551</v>
+        <v>46282.79623825232</v>
       </c>
       <c r="W432">
         <v>5</v>
       </c>
       <c r="X432" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Y432" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AB432">
         <v>0</v>
@@ -34279,16 +34387,16 @@
     </row>
     <row r="433" spans="1:35">
       <c r="A433">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B433" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C433" t="s">
         <v>50</v>
       </c>
       <c r="D433" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E433" t="s">
         <v>55</v>
@@ -34321,7 +34429,7 @@
         <v>2026</v>
       </c>
       <c r="R433">
-        <v>16959926</v>
+        <v>17042221</v>
       </c>
       <c r="S433" t="s">
         <v>204</v>
@@ -34330,7 +34438,7 @@
         <v>216</v>
       </c>
       <c r="V433" s="1">
-        <v>46282.7962703125</v>
+        <v>46282.7962541551</v>
       </c>
       <c r="W433">
         <v>5</v>
@@ -34339,7 +34447,7 @@
         <v>219</v>
       </c>
       <c r="Y433" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AB433">
         <v>0</v>
@@ -34356,19 +34464,19 @@
     </row>
     <row r="434" spans="1:35">
       <c r="A434">
-        <v>6703</v>
+        <v>6628</v>
       </c>
       <c r="B434" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C434" t="s">
         <v>50</v>
       </c>
       <c r="D434" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E434" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F434" t="s">
         <v>56</v>
@@ -34398,7 +34506,7 @@
         <v>2026</v>
       </c>
       <c r="R434">
-        <v>17941112</v>
+        <v>16959926</v>
       </c>
       <c r="S434" t="s">
         <v>204</v>
@@ -34407,16 +34515,16 @@
         <v>216</v>
       </c>
       <c r="V434" s="1">
-        <v>46282.79628381944</v>
+        <v>46282.7962703125</v>
       </c>
       <c r="W434">
         <v>5</v>
       </c>
       <c r="X434" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="Y434" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AB434">
         <v>0</v>
@@ -34433,16 +34541,16 @@
     </row>
     <row r="435" spans="1:35">
       <c r="A435">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B435" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C435" t="s">
         <v>50</v>
       </c>
       <c r="D435" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E435" t="s">
         <v>54</v>
@@ -34475,7 +34583,7 @@
         <v>2026</v>
       </c>
       <c r="R435">
-        <v>17952292</v>
+        <v>17941112</v>
       </c>
       <c r="S435" t="s">
         <v>204</v>
@@ -34484,16 +34592,16 @@
         <v>216</v>
       </c>
       <c r="V435" s="1">
-        <v>46282.79630119213</v>
+        <v>46282.79628381944</v>
       </c>
       <c r="W435">
         <v>5</v>
       </c>
       <c r="X435" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Y435" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AB435">
         <v>0</v>
@@ -34510,16 +34618,16 @@
     </row>
     <row r="436" spans="1:35">
       <c r="A436">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B436" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C436" t="s">
         <v>50</v>
       </c>
       <c r="D436" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E436" t="s">
         <v>54</v>
@@ -34552,7 +34660,7 @@
         <v>2026</v>
       </c>
       <c r="R436">
-        <v>17952491</v>
+        <v>17952292</v>
       </c>
       <c r="S436" t="s">
         <v>204</v>
@@ -34561,7 +34669,7 @@
         <v>216</v>
       </c>
       <c r="V436" s="1">
-        <v>46282.79631224537</v>
+        <v>46282.79630119213</v>
       </c>
       <c r="W436">
         <v>5</v>
@@ -34570,7 +34678,7 @@
         <v>223</v>
       </c>
       <c r="Y436" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AB436">
         <v>0</v>
@@ -34587,10 +34695,10 @@
     </row>
     <row r="437" spans="1:35">
       <c r="A437">
-        <v>6945</v>
+        <v>6705</v>
       </c>
       <c r="B437" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C437" t="s">
         <v>50</v>
@@ -34602,7 +34710,7 @@
         <v>54</v>
       </c>
       <c r="F437" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G437">
         <v>940</v>
@@ -34629,7 +34737,7 @@
         <v>2026</v>
       </c>
       <c r="R437">
-        <v>18164473</v>
+        <v>17952491</v>
       </c>
       <c r="S437" t="s">
         <v>204</v>
@@ -34638,13 +34746,13 @@
         <v>216</v>
       </c>
       <c r="V437" s="1">
-        <v>46282.79637734954</v>
+        <v>46282.79631224537</v>
       </c>
       <c r="W437">
         <v>5</v>
       </c>
       <c r="X437" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Y437" t="s">
         <v>400</v>
@@ -34664,16 +34772,16 @@
     </row>
     <row r="438" spans="1:35">
       <c r="A438">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B438" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C438" t="s">
         <v>50</v>
       </c>
       <c r="D438" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E438" t="s">
         <v>54</v>
@@ -34706,7 +34814,7 @@
         <v>2026</v>
       </c>
       <c r="R438">
-        <v>18178120</v>
+        <v>18164473</v>
       </c>
       <c r="S438" t="s">
         <v>204</v>
@@ -34715,16 +34823,16 @@
         <v>216</v>
       </c>
       <c r="V438" s="1">
-        <v>46282.79638922454</v>
+        <v>46282.79637734954</v>
       </c>
       <c r="W438">
         <v>5</v>
       </c>
       <c r="X438" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Y438" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AB438">
         <v>0</v>
@@ -34741,10 +34849,10 @@
     </row>
     <row r="439" spans="1:35">
       <c r="A439">
-        <v>5417</v>
+        <v>6949</v>
       </c>
       <c r="B439" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C439" t="s">
         <v>50</v>
@@ -34756,19 +34864,19 @@
         <v>54</v>
       </c>
       <c r="F439" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G439">
-        <v>9088</v>
+        <v>940</v>
       </c>
       <c r="H439">
         <v>0</v>
       </c>
       <c r="I439" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J439" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N439" s="1">
         <v>46283</v>
@@ -34783,31 +34891,31 @@
         <v>2026</v>
       </c>
       <c r="R439">
-        <v>17399383</v>
+        <v>18178120</v>
       </c>
       <c r="S439" t="s">
-        <v>54</v>
+        <v>204</v>
       </c>
       <c r="U439" t="s">
         <v>216</v>
       </c>
       <c r="V439" s="1">
-        <v>46282.3651903588</v>
+        <v>46282.79638922454</v>
       </c>
       <c r="W439">
         <v>5</v>
       </c>
       <c r="X439" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="Y439" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AB439">
         <v>0</v>
       </c>
       <c r="AC439" t="s">
-        <v>54</v>
+        <v>204</v>
       </c>
       <c r="AH439" t="s">
         <v>415</v>
@@ -34818,16 +34926,16 @@
     </row>
     <row r="440" spans="1:35">
       <c r="A440">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B440" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C440" t="s">
         <v>50</v>
       </c>
       <c r="D440" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E440" t="s">
         <v>54</v>
@@ -34860,7 +34968,7 @@
         <v>2026</v>
       </c>
       <c r="R440">
-        <v>16962400</v>
+        <v>17399383</v>
       </c>
       <c r="S440" t="s">
         <v>54</v>
@@ -34869,16 +34977,16 @@
         <v>216</v>
       </c>
       <c r="V440" s="1">
-        <v>46282.36525856482</v>
+        <v>46282.3651903588</v>
       </c>
       <c r="W440">
         <v>5</v>
       </c>
       <c r="X440" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="Y440" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AB440">
         <v>0</v>
@@ -34895,16 +35003,16 @@
     </row>
     <row r="441" spans="1:35">
       <c r="A441">
-        <v>6486</v>
+        <v>6404</v>
       </c>
       <c r="B441" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C441" t="s">
         <v>50</v>
       </c>
       <c r="D441" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E441" t="s">
         <v>54</v>
@@ -34937,7 +35045,7 @@
         <v>2026</v>
       </c>
       <c r="R441">
-        <v>16976290</v>
+        <v>16962400</v>
       </c>
       <c r="S441" t="s">
         <v>54</v>
@@ -34946,16 +35054,16 @@
         <v>216</v>
       </c>
       <c r="V441" s="1">
-        <v>46282.36526855324</v>
+        <v>46282.36525856482</v>
       </c>
       <c r="W441">
         <v>5</v>
       </c>
       <c r="X441" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Y441" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AB441">
         <v>0</v>
@@ -34972,10 +35080,10 @@
     </row>
     <row r="442" spans="1:35">
       <c r="A442">
-        <v>6548</v>
+        <v>6486</v>
       </c>
       <c r="B442" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C442" t="s">
         <v>50</v>
@@ -35014,7 +35122,7 @@
         <v>2026</v>
       </c>
       <c r="R442">
-        <v>17222899</v>
+        <v>16976290</v>
       </c>
       <c r="S442" t="s">
         <v>54</v>
@@ -35023,16 +35131,16 @@
         <v>216</v>
       </c>
       <c r="V442" s="1">
-        <v>46282.36527959491</v>
+        <v>46282.36526855324</v>
       </c>
       <c r="W442">
         <v>5</v>
       </c>
       <c r="X442" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="Y442" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AB442">
         <v>0</v>
@@ -35049,10 +35157,10 @@
     </row>
     <row r="443" spans="1:35">
       <c r="A443">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B443" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C443" t="s">
         <v>50</v>
@@ -35061,7 +35169,7 @@
         <v>51</v>
       </c>
       <c r="E443" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F443" t="s">
         <v>56</v>
@@ -35091,31 +35199,31 @@
         <v>2026</v>
       </c>
       <c r="R443">
-        <v>17042627</v>
+        <v>17222899</v>
       </c>
       <c r="S443" t="s">
-        <v>205</v>
+        <v>54</v>
       </c>
       <c r="U443" t="s">
         <v>216</v>
       </c>
       <c r="V443" s="1">
-        <v>46282.36528526621</v>
+        <v>46282.36527959491</v>
       </c>
       <c r="W443">
         <v>5</v>
       </c>
       <c r="X443" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Y443" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AB443">
         <v>0</v>
       </c>
       <c r="AC443" t="s">
-        <v>205</v>
+        <v>54</v>
       </c>
       <c r="AH443" t="s">
         <v>415</v>
@@ -35126,16 +35234,16 @@
     </row>
     <row r="444" spans="1:35">
       <c r="A444">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B444" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C444" t="s">
         <v>50</v>
       </c>
       <c r="D444" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E444" t="s">
         <v>55</v>
@@ -35168,16 +35276,16 @@
         <v>2026</v>
       </c>
       <c r="R444">
-        <v>16960098</v>
+        <v>17042627</v>
       </c>
       <c r="S444" t="s">
-        <v>55</v>
+        <v>205</v>
       </c>
       <c r="U444" t="s">
         <v>216</v>
       </c>
       <c r="V444" s="1">
-        <v>46282.36528619213</v>
+        <v>46282.36528526621</v>
       </c>
       <c r="W444">
         <v>5</v>
@@ -35186,13 +35294,13 @@
         <v>219</v>
       </c>
       <c r="Y444" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AB444">
         <v>0</v>
       </c>
       <c r="AC444" t="s">
-        <v>55</v>
+        <v>205</v>
       </c>
       <c r="AH444" t="s">
         <v>415</v>
@@ -35203,19 +35311,19 @@
     </row>
     <row r="445" spans="1:35">
       <c r="A445">
-        <v>6703</v>
+        <v>6628</v>
       </c>
       <c r="B445" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C445" t="s">
         <v>50</v>
       </c>
       <c r="D445" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E445" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F445" t="s">
         <v>56</v>
@@ -35245,31 +35353,31 @@
         <v>2026</v>
       </c>
       <c r="R445">
-        <v>17941237</v>
+        <v>16960098</v>
       </c>
       <c r="S445" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="U445" t="s">
         <v>216</v>
       </c>
       <c r="V445" s="1">
-        <v>46282.36529351852</v>
+        <v>46282.36528619213</v>
       </c>
       <c r="W445">
         <v>5</v>
       </c>
       <c r="X445" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="Y445" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AB445">
         <v>0</v>
       </c>
       <c r="AC445" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AH445" t="s">
         <v>415</v>
@@ -35280,16 +35388,16 @@
     </row>
     <row r="446" spans="1:35">
       <c r="A446">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B446" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C446" t="s">
         <v>50</v>
       </c>
       <c r="D446" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E446" t="s">
         <v>54</v>
@@ -35322,7 +35430,7 @@
         <v>2026</v>
       </c>
       <c r="R446">
-        <v>17952466</v>
+        <v>17941237</v>
       </c>
       <c r="S446" t="s">
         <v>54</v>
@@ -35331,16 +35439,16 @@
         <v>216</v>
       </c>
       <c r="V446" s="1">
-        <v>46282.36529424768</v>
+        <v>46282.36529351852</v>
       </c>
       <c r="W446">
         <v>5</v>
       </c>
       <c r="X446" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Y446" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AB446">
         <v>0</v>
@@ -35357,16 +35465,16 @@
     </row>
     <row r="447" spans="1:35">
       <c r="A447">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B447" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C447" t="s">
         <v>50</v>
       </c>
       <c r="D447" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E447" t="s">
         <v>54</v>
@@ -35399,7 +35507,7 @@
         <v>2026</v>
       </c>
       <c r="R447">
-        <v>17952646</v>
+        <v>17952466</v>
       </c>
       <c r="S447" t="s">
         <v>54</v>
@@ -35408,7 +35516,7 @@
         <v>216</v>
       </c>
       <c r="V447" s="1">
-        <v>46282.36529490741</v>
+        <v>46282.36529424768</v>
       </c>
       <c r="W447">
         <v>5</v>
@@ -35417,7 +35525,7 @@
         <v>223</v>
       </c>
       <c r="Y447" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AB447">
         <v>0</v>
@@ -35434,10 +35542,10 @@
     </row>
     <row r="448" spans="1:35">
       <c r="A448">
-        <v>6779</v>
+        <v>6705</v>
       </c>
       <c r="B448" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C448" t="s">
         <v>50</v>
@@ -35476,16 +35584,16 @@
         <v>2026</v>
       </c>
       <c r="R448">
-        <v>18056821</v>
+        <v>17952646</v>
       </c>
       <c r="S448" t="s">
-        <v>205</v>
+        <v>54</v>
       </c>
       <c r="U448" t="s">
         <v>216</v>
       </c>
       <c r="V448" s="1">
-        <v>46282.36529869213</v>
+        <v>46282.36529490741</v>
       </c>
       <c r="W448">
         <v>5</v>
@@ -35494,13 +35602,13 @@
         <v>223</v>
       </c>
       <c r="Y448" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AB448">
         <v>0</v>
       </c>
       <c r="AC448" t="s">
-        <v>205</v>
+        <v>54</v>
       </c>
       <c r="AH448" t="s">
         <v>415</v>
@@ -35511,10 +35619,10 @@
     </row>
     <row r="449" spans="1:35">
       <c r="A449">
-        <v>6945</v>
+        <v>6779</v>
       </c>
       <c r="B449" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C449" t="s">
         <v>50</v>
@@ -35526,7 +35634,7 @@
         <v>54</v>
       </c>
       <c r="F449" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G449">
         <v>9088</v>
@@ -35553,31 +35661,31 @@
         <v>2026</v>
       </c>
       <c r="R449">
-        <v>18164565</v>
+        <v>18056821</v>
       </c>
       <c r="S449" t="s">
-        <v>54</v>
+        <v>205</v>
       </c>
       <c r="U449" t="s">
         <v>216</v>
       </c>
       <c r="V449" s="1">
-        <v>46282.36531149306</v>
+        <v>46282.36529869213</v>
       </c>
       <c r="W449">
         <v>5</v>
       </c>
       <c r="X449" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Y449" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AB449">
         <v>0</v>
       </c>
       <c r="AC449" t="s">
-        <v>54</v>
+        <v>205</v>
       </c>
       <c r="AH449" t="s">
         <v>415</v>
@@ -35588,16 +35696,16 @@
     </row>
     <row r="450" spans="1:35">
       <c r="A450">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B450" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C450" t="s">
         <v>50</v>
       </c>
       <c r="D450" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E450" t="s">
         <v>54</v>
@@ -35630,22 +35738,22 @@
         <v>2026</v>
       </c>
       <c r="R450">
-        <v>18178199</v>
+        <v>18164565</v>
       </c>
       <c r="S450" t="s">
-        <v>205</v>
+        <v>54</v>
       </c>
       <c r="U450" t="s">
         <v>216</v>
       </c>
       <c r="V450" s="1">
-        <v>46282.36531554398</v>
+        <v>46282.36531149306</v>
       </c>
       <c r="W450">
         <v>5</v>
       </c>
       <c r="X450" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Y450" t="s">
         <v>401</v>
@@ -35654,7 +35762,7 @@
         <v>0</v>
       </c>
       <c r="AC450" t="s">
-        <v>205</v>
+        <v>54</v>
       </c>
       <c r="AH450" t="s">
         <v>415</v>
@@ -35665,16 +35773,16 @@
     </row>
     <row r="451" spans="1:35">
       <c r="A451">
-        <v>6962</v>
+        <v>6949</v>
       </c>
       <c r="B451" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C451" t="s">
         <v>50</v>
       </c>
       <c r="D451" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E451" t="s">
         <v>54</v>
@@ -35707,31 +35815,31 @@
         <v>2026</v>
       </c>
       <c r="R451">
-        <v>18188788</v>
+        <v>18178199</v>
       </c>
       <c r="S451" t="s">
-        <v>54</v>
+        <v>205</v>
       </c>
       <c r="U451" t="s">
         <v>216</v>
       </c>
       <c r="V451" s="1">
-        <v>46282.36531253472</v>
+        <v>46282.36531554398</v>
       </c>
       <c r="W451">
         <v>5</v>
       </c>
       <c r="X451" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="Y451" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AB451">
         <v>0</v>
       </c>
       <c r="AC451" t="s">
-        <v>54</v>
+        <v>205</v>
       </c>
       <c r="AH451" t="s">
         <v>415</v>
@@ -35742,10 +35850,10 @@
     </row>
     <row r="452" spans="1:35">
       <c r="A452">
-        <v>6963</v>
+        <v>6962</v>
       </c>
       <c r="B452" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C452" t="s">
         <v>50</v>
@@ -35784,7 +35892,7 @@
         <v>2026</v>
       </c>
       <c r="R452">
-        <v>18188694</v>
+        <v>18188788</v>
       </c>
       <c r="S452" t="s">
         <v>54</v>
@@ -35793,7 +35901,7 @@
         <v>216</v>
       </c>
       <c r="V452" s="1">
-        <v>46282.36531288194</v>
+        <v>46282.36531253472</v>
       </c>
       <c r="W452">
         <v>5</v>
@@ -35802,7 +35910,7 @@
         <v>222</v>
       </c>
       <c r="Y452" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AB452">
         <v>0</v>
@@ -35819,25 +35927,25 @@
     </row>
     <row r="453" spans="1:35">
       <c r="A453">
-        <v>5417</v>
+        <v>6963</v>
       </c>
       <c r="B453" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C453" t="s">
         <v>50</v>
       </c>
       <c r="D453" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E453" t="s">
         <v>54</v>
       </c>
       <c r="F453" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G453">
-        <v>6813</v>
+        <v>9088</v>
       </c>
       <c r="H453">
         <v>0</v>
@@ -35846,13 +35954,13 @@
         <v>65</v>
       </c>
       <c r="J453" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="N453" s="1">
-        <v>46286</v>
+        <v>46283</v>
       </c>
       <c r="O453" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="P453">
         <v>9</v>
@@ -35861,51 +35969,51 @@
         <v>2026</v>
       </c>
       <c r="R453">
-        <v>17399241</v>
+        <v>18188694</v>
       </c>
       <c r="S453" t="s">
         <v>54</v>
       </c>
       <c r="U453" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="V453" s="1">
-        <v>46286.45925106481</v>
+        <v>46282.36531288194</v>
       </c>
       <c r="W453">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="X453" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="Y453" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AB453">
         <v>0</v>
       </c>
       <c r="AC453" t="s">
-        <v>204</v>
+        <v>54</v>
       </c>
       <c r="AH453" t="s">
         <v>415</v>
       </c>
       <c r="AI453" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="454" spans="1:35">
       <c r="A454">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B454" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C454" t="s">
         <v>50</v>
       </c>
       <c r="D454" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E454" t="s">
         <v>54</v>
@@ -35926,10 +36034,10 @@
         <v>161</v>
       </c>
       <c r="N454" s="1">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="O454" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="P454">
         <v>9</v>
@@ -35938,51 +36046,51 @@
         <v>2026</v>
       </c>
       <c r="R454">
-        <v>16962319</v>
+        <v>17399241</v>
       </c>
       <c r="S454" t="s">
         <v>54</v>
       </c>
       <c r="U454" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="V454" s="1">
-        <v>46282.79619331018</v>
+        <v>46286.45925106481</v>
       </c>
       <c r="W454">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="X454" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="Y454" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="AB454">
         <v>0</v>
       </c>
       <c r="AC454" t="s">
-        <v>54</v>
+        <v>204</v>
       </c>
       <c r="AH454" t="s">
         <v>415</v>
       </c>
       <c r="AI454" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="455" spans="1:35">
       <c r="A455">
-        <v>6486</v>
+        <v>6404</v>
       </c>
       <c r="B455" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C455" t="s">
         <v>50</v>
       </c>
       <c r="D455" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E455" t="s">
         <v>54</v>
@@ -36015,7 +36123,7 @@
         <v>2026</v>
       </c>
       <c r="R455">
-        <v>16976198</v>
+        <v>16962319</v>
       </c>
       <c r="S455" t="s">
         <v>54</v>
@@ -36024,16 +36132,16 @@
         <v>216</v>
       </c>
       <c r="V455" s="1">
-        <v>46282.79620888889</v>
+        <v>46282.79619331018</v>
       </c>
       <c r="W455">
         <v>5</v>
       </c>
       <c r="X455" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Y455" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AB455">
         <v>0</v>
@@ -36050,10 +36158,10 @@
     </row>
     <row r="456" spans="1:35">
       <c r="A456">
-        <v>6548</v>
+        <v>6486</v>
       </c>
       <c r="B456" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C456" t="s">
         <v>50</v>
@@ -36092,7 +36200,7 @@
         <v>2026</v>
       </c>
       <c r="R456">
-        <v>17222763</v>
+        <v>16976198</v>
       </c>
       <c r="S456" t="s">
         <v>54</v>
@@ -36101,16 +36209,16 @@
         <v>216</v>
       </c>
       <c r="V456" s="1">
-        <v>46282.79623803241</v>
+        <v>46282.79620888889</v>
       </c>
       <c r="W456">
         <v>5</v>
       </c>
       <c r="X456" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="Y456" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AB456">
         <v>0</v>
@@ -36127,10 +36235,10 @@
     </row>
     <row r="457" spans="1:35">
       <c r="A457">
-        <v>6627</v>
+        <v>6548</v>
       </c>
       <c r="B457" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C457" t="s">
         <v>50</v>
@@ -36139,7 +36247,7 @@
         <v>51</v>
       </c>
       <c r="E457" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F457" t="s">
         <v>56</v>
@@ -36169,31 +36277,31 @@
         <v>2026</v>
       </c>
       <c r="R457">
-        <v>17042469</v>
+        <v>17222763</v>
       </c>
       <c r="S457" t="s">
-        <v>205</v>
+        <v>54</v>
       </c>
       <c r="U457" t="s">
         <v>216</v>
       </c>
       <c r="V457" s="1">
-        <v>46282.79625384259</v>
+        <v>46282.79623803241</v>
       </c>
       <c r="W457">
         <v>5</v>
       </c>
       <c r="X457" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Y457" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AB457">
         <v>0</v>
       </c>
       <c r="AC457" t="s">
-        <v>205</v>
+        <v>54</v>
       </c>
       <c r="AH457" t="s">
         <v>415</v>
@@ -36204,16 +36312,16 @@
     </row>
     <row r="458" spans="1:35">
       <c r="A458">
-        <v>6628</v>
+        <v>6627</v>
       </c>
       <c r="B458" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C458" t="s">
         <v>50</v>
       </c>
       <c r="D458" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E458" t="s">
         <v>55</v>
@@ -36246,16 +36354,16 @@
         <v>2026</v>
       </c>
       <c r="R458">
-        <v>16960013</v>
+        <v>17042469</v>
       </c>
       <c r="S458" t="s">
-        <v>55</v>
+        <v>205</v>
       </c>
       <c r="U458" t="s">
         <v>216</v>
       </c>
       <c r="V458" s="1">
-        <v>46282.79626969907</v>
+        <v>46282.79625384259</v>
       </c>
       <c r="W458">
         <v>5</v>
@@ -36264,13 +36372,13 @@
         <v>219</v>
       </c>
       <c r="Y458" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AB458">
         <v>0</v>
       </c>
       <c r="AC458" t="s">
-        <v>55</v>
+        <v>205</v>
       </c>
       <c r="AH458" t="s">
         <v>415</v>
@@ -36281,19 +36389,19 @@
     </row>
     <row r="459" spans="1:35">
       <c r="A459">
-        <v>6703</v>
+        <v>6628</v>
       </c>
       <c r="B459" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C459" t="s">
         <v>50</v>
       </c>
       <c r="D459" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E459" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F459" t="s">
         <v>56</v>
@@ -36323,31 +36431,31 @@
         <v>2026</v>
       </c>
       <c r="R459">
-        <v>17941197</v>
+        <v>16960013</v>
       </c>
       <c r="S459" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="U459" t="s">
         <v>216</v>
       </c>
       <c r="V459" s="1">
-        <v>46282.79628394676</v>
+        <v>46282.79626969907</v>
       </c>
       <c r="W459">
         <v>5</v>
       </c>
       <c r="X459" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="Y459" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AB459">
         <v>0</v>
       </c>
       <c r="AC459" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AH459" t="s">
         <v>415</v>
@@ -36358,16 +36466,16 @@
     </row>
     <row r="460" spans="1:35">
       <c r="A460">
-        <v>6704</v>
+        <v>6703</v>
       </c>
       <c r="B460" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C460" t="s">
         <v>50</v>
       </c>
       <c r="D460" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E460" t="s">
         <v>54</v>
@@ -36400,7 +36508,7 @@
         <v>2026</v>
       </c>
       <c r="R460">
-        <v>17952411</v>
+        <v>17941197</v>
       </c>
       <c r="S460" t="s">
         <v>54</v>
@@ -36409,16 +36517,16 @@
         <v>216</v>
       </c>
       <c r="V460" s="1">
-        <v>46282.79630097222</v>
+        <v>46282.79628394676</v>
       </c>
       <c r="W460">
         <v>5</v>
       </c>
       <c r="X460" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Y460" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AB460">
         <v>0</v>
@@ -36435,16 +36543,16 @@
     </row>
     <row r="461" spans="1:35">
       <c r="A461">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="B461" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C461" t="s">
         <v>50</v>
       </c>
       <c r="D461" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E461" t="s">
         <v>54</v>
@@ -36477,7 +36585,7 @@
         <v>2026</v>
       </c>
       <c r="R461">
-        <v>17952591</v>
+        <v>17952411</v>
       </c>
       <c r="S461" t="s">
         <v>54</v>
@@ -36486,7 +36594,7 @@
         <v>216</v>
       </c>
       <c r="V461" s="1">
-        <v>46282.79631204861</v>
+        <v>46282.79630097222</v>
       </c>
       <c r="W461">
         <v>5</v>
@@ -36495,7 +36603,7 @@
         <v>223</v>
       </c>
       <c r="Y461" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AB461">
         <v>0</v>
@@ -36512,10 +36620,10 @@
     </row>
     <row r="462" spans="1:35">
       <c r="A462">
-        <v>6945</v>
+        <v>6705</v>
       </c>
       <c r="B462" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C462" t="s">
         <v>50</v>
@@ -36527,7 +36635,7 @@
         <v>54</v>
       </c>
       <c r="F462" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G462">
         <v>6813</v>
@@ -36554,7 +36662,7 @@
         <v>2026</v>
       </c>
       <c r="R462">
-        <v>18164530</v>
+        <v>17952591</v>
       </c>
       <c r="S462" t="s">
         <v>54</v>
@@ -36563,13 +36671,13 @@
         <v>216</v>
       </c>
       <c r="V462" s="1">
-        <v>46282.79637748843</v>
+        <v>46282.79631204861</v>
       </c>
       <c r="W462">
         <v>5</v>
       </c>
       <c r="X462" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Y462" t="s">
         <v>401</v>
@@ -36589,16 +36697,16 @@
     </row>
     <row r="463" spans="1:35">
       <c r="A463">
-        <v>6949</v>
+        <v>6945</v>
       </c>
       <c r="B463" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C463" t="s">
         <v>50</v>
       </c>
       <c r="D463" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E463" t="s">
         <v>54</v>
@@ -36631,31 +36739,31 @@
         <v>2026</v>
       </c>
       <c r="R463">
-        <v>18178169</v>
+        <v>18164530</v>
       </c>
       <c r="S463" t="s">
-        <v>205</v>
+        <v>54</v>
       </c>
       <c r="U463" t="s">
         <v>216</v>
       </c>
       <c r="V463" s="1">
-        <v>46282.79638901621</v>
+        <v>46282.79637748843</v>
       </c>
       <c r="W463">
         <v>5</v>
       </c>
       <c r="X463" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Y463" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AB463">
         <v>0</v>
       </c>
       <c r="AC463" t="s">
-        <v>205</v>
+        <v>54</v>
       </c>
       <c r="AH463" t="s">
         <v>415</v>
@@ -36666,10 +36774,10 @@
     </row>
     <row r="464" spans="1:35">
       <c r="A464">
-        <v>5417</v>
+        <v>6949</v>
       </c>
       <c r="B464" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C464" t="s">
         <v>50</v>
@@ -36681,10 +36789,10 @@
         <v>54</v>
       </c>
       <c r="F464" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G464">
-        <v>7027</v>
+        <v>6813</v>
       </c>
       <c r="H464">
         <v>0</v>
@@ -36693,46 +36801,49 @@
         <v>65</v>
       </c>
       <c r="J464" t="s">
-        <v>119</v>
+        <v>161</v>
       </c>
       <c r="N464" s="1">
-        <v>46289</v>
+        <v>46283</v>
+      </c>
+      <c r="O464" t="s">
+        <v>170</v>
       </c>
       <c r="P464">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q464">
         <v>2026</v>
       </c>
       <c r="R464">
-        <v>17399290</v>
+        <v>18178169</v>
       </c>
       <c r="S464" t="s">
-        <v>54</v>
+        <v>205</v>
       </c>
       <c r="U464" t="s">
         <v>216</v>
       </c>
       <c r="V464" s="1">
-        <v>46283.39832862269</v>
+        <v>46282.79638901621</v>
       </c>
       <c r="W464">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X464" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="Y464" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AB464">
         <v>0</v>
       </c>
       <c r="AC464" t="s">
-        <v>54</v>
+        <v>205</v>
       </c>
       <c r="AH464" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AI464" t="s">
         <v>418</v>
@@ -36740,16 +36851,16 @@
     </row>
     <row r="465" spans="1:35">
       <c r="A465">
-        <v>6404</v>
+        <v>5417</v>
       </c>
       <c r="B465" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C465" t="s">
         <v>50</v>
       </c>
       <c r="D465" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E465" t="s">
         <v>54</v>
@@ -36779,7 +36890,7 @@
         <v>2026</v>
       </c>
       <c r="R465">
-        <v>16962348</v>
+        <v>17399290</v>
       </c>
       <c r="S465" t="s">
         <v>54</v>
@@ -36788,13 +36899,13 @@
         <v>216</v>
       </c>
       <c r="V465" s="1">
-        <v>46282.64018086805</v>
+        <v>46283.39832862269</v>
       </c>
       <c r="W465">
         <v>-1</v>
       </c>
       <c r="X465" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="Y465" t="s">
         <v>404</v>
@@ -36814,16 +36925,16 @@
     </row>
     <row r="466" spans="1:35">
       <c r="A466">
-        <v>5417</v>
+        <v>6404</v>
       </c>
       <c r="B466" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C466" t="s">
         <v>50</v>
       </c>
       <c r="D466" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E466" t="s">
         <v>54</v>
@@ -36832,22 +36943,19 @@
         <v>56</v>
       </c>
       <c r="G466">
-        <v>11056</v>
+        <v>7027</v>
       </c>
       <c r="H466">
         <v>0</v>
       </c>
       <c r="I466" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J466" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="N466" s="1">
-        <v>46287</v>
-      </c>
-      <c r="O466" t="s">
-        <v>181</v>
+        <v>46289</v>
       </c>
       <c r="P466">
         <v>8</v>
@@ -36856,19 +36964,22 @@
         <v>2026</v>
       </c>
       <c r="R466">
-        <v>18275526</v>
+        <v>16962348</v>
+      </c>
+      <c r="S466" t="s">
+        <v>54</v>
       </c>
       <c r="U466" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="V466" s="1">
-        <v>46287.492834375</v>
+        <v>46282.64018086805</v>
       </c>
       <c r="W466">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="X466" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Y466" t="s">
         <v>405</v>
@@ -36877,33 +36988,33 @@
         <v>0</v>
       </c>
       <c r="AC466" t="s">
-        <v>411</v>
+        <v>54</v>
       </c>
       <c r="AH466" t="s">
         <v>413</v>
       </c>
       <c r="AI466" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="467" spans="1:35">
       <c r="A467">
-        <v>6962</v>
+        <v>5417</v>
       </c>
       <c r="B467" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C467" t="s">
         <v>50</v>
       </c>
       <c r="D467" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E467" t="s">
         <v>54</v>
       </c>
       <c r="F467" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G467">
         <v>11056</v>
@@ -36921,7 +37032,7 @@
         <v>46287</v>
       </c>
       <c r="O467" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="P467">
         <v>8</v>
@@ -36930,19 +37041,19 @@
         <v>2026</v>
       </c>
       <c r="R467">
-        <v>18274091</v>
+        <v>18275526</v>
       </c>
       <c r="U467" t="s">
         <v>217</v>
       </c>
       <c r="V467" s="1">
-        <v>46287.49337789352</v>
+        <v>46287.492834375</v>
       </c>
       <c r="W467">
         <v>1</v>
       </c>
       <c r="X467" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Y467" t="s">
         <v>406</v>
@@ -36957,6 +37068,80 @@
         <v>413</v>
       </c>
       <c r="AI467" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="468" spans="1:35">
+      <c r="A468">
+        <v>6962</v>
+      </c>
+      <c r="B468" t="s">
+        <v>40</v>
+      </c>
+      <c r="C468" t="s">
+        <v>50</v>
+      </c>
+      <c r="D468" t="s">
+        <v>53</v>
+      </c>
+      <c r="E468" t="s">
+        <v>54</v>
+      </c>
+      <c r="F468" t="s">
+        <v>57</v>
+      </c>
+      <c r="G468">
+        <v>11056</v>
+      </c>
+      <c r="H468">
+        <v>0</v>
+      </c>
+      <c r="I468" t="s">
+        <v>66</v>
+      </c>
+      <c r="J468" t="s">
+        <v>120</v>
+      </c>
+      <c r="N468" s="1">
+        <v>46287</v>
+      </c>
+      <c r="O468" t="s">
+        <v>177</v>
+      </c>
+      <c r="P468">
+        <v>8</v>
+      </c>
+      <c r="Q468">
+        <v>2026</v>
+      </c>
+      <c r="R468">
+        <v>18274091</v>
+      </c>
+      <c r="U468" t="s">
+        <v>217</v>
+      </c>
+      <c r="V468" s="1">
+        <v>46287.49337789352</v>
+      </c>
+      <c r="W468">
+        <v>1</v>
+      </c>
+      <c r="X468" t="s">
+        <v>222</v>
+      </c>
+      <c r="Y468" t="s">
+        <v>407</v>
+      </c>
+      <c r="AB468">
+        <v>0</v>
+      </c>
+      <c r="AC468" t="s">
+        <v>411</v>
+      </c>
+      <c r="AH468" t="s">
+        <v>413</v>
+      </c>
+      <c r="AI468" t="s">
         <v>419</v>
       </c>
     </row>

--- a/data/base/goias.xlsx
+++ b/data/base/goias.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6851" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6815" uniqueCount="421">
   <si>
     <t>CodCliente</t>
   </si>
@@ -643,7 +643,7 @@
     <t>Fernanda Araujo</t>
   </si>
   <si>
-    <t>Karina Fonseca</t>
+    <t>Karina Santos</t>
   </si>
   <si>
     <t>David Bragança</t>
@@ -658,7 +658,7 @@
     <t>Nayara Oliveira</t>
   </si>
   <si>
-    <t>Larice Souza</t>
+    <t>Ricardo Fischer</t>
   </si>
   <si>
     <t>Baixada em atraso</t>
@@ -1275,6 +1275,9 @@
   </si>
   <si>
     <t>Karen Ribeiro</t>
+  </si>
+  <si>
+    <t>Karina Fonseca</t>
   </si>
   <si>
     <t>Santos Karina</t>
@@ -1824,10 +1827,10 @@
         <v>182</v>
       </c>
       <c r="AH2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="3" spans="1:35">
@@ -1901,10 +1904,10 @@
         <v>183</v>
       </c>
       <c r="AH3" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="4" spans="1:35">
@@ -1978,10 +1981,10 @@
         <v>182</v>
       </c>
       <c r="AH4" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI4" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="5" spans="1:35">
@@ -2052,10 +2055,10 @@
         <v>182</v>
       </c>
       <c r="AH5" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI5" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="6" spans="1:35">
@@ -2126,10 +2129,10 @@
         <v>183</v>
       </c>
       <c r="AH6" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI6" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="7" spans="1:35">
@@ -2200,10 +2203,10 @@
         <v>183</v>
       </c>
       <c r="AH7" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI7" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="8" spans="1:35">
@@ -2274,10 +2277,10 @@
         <v>184</v>
       </c>
       <c r="AH8" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI8" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="9" spans="1:35">
@@ -2348,10 +2351,10 @@
         <v>182</v>
       </c>
       <c r="AH9" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI9" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="10" spans="1:35">
@@ -2422,10 +2425,10 @@
         <v>185</v>
       </c>
       <c r="AH10" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI10" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="11" spans="1:35">
@@ -2496,10 +2499,10 @@
         <v>185</v>
       </c>
       <c r="AH11" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="12" spans="1:35">
@@ -2570,10 +2573,10 @@
         <v>186</v>
       </c>
       <c r="AH12" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI12" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="13" spans="1:35">
@@ -2644,10 +2647,10 @@
         <v>408</v>
       </c>
       <c r="AH13" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI13" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="14" spans="1:35">
@@ -2715,13 +2718,13 @@
         <v>0</v>
       </c>
       <c r="AC14" t="s">
-        <v>209</v>
+        <v>409</v>
       </c>
       <c r="AH14" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI14" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="15" spans="1:35">
@@ -2789,10 +2792,10 @@
         <v>0</v>
       </c>
       <c r="AH15" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI15" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="16" spans="1:35">
@@ -2854,10 +2857,10 @@
         <v>0</v>
       </c>
       <c r="AH16" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI16" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="17" spans="1:35">
@@ -2925,10 +2928,10 @@
         <v>0</v>
       </c>
       <c r="AH17" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI17" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="18" spans="1:35">
@@ -3002,10 +3005,10 @@
         <v>188</v>
       </c>
       <c r="AH18" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI18" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="19" spans="1:35">
@@ -3079,10 +3082,10 @@
         <v>187</v>
       </c>
       <c r="AH19" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI19" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="20" spans="1:35">
@@ -3156,10 +3159,10 @@
         <v>188</v>
       </c>
       <c r="AH20" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI20" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="21" spans="1:35">
@@ -3233,10 +3236,10 @@
         <v>186</v>
       </c>
       <c r="AH21" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI21" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="22" spans="1:35">
@@ -3307,10 +3310,10 @@
         <v>189</v>
       </c>
       <c r="AH22" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI22" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="23" spans="1:35">
@@ -3381,10 +3384,10 @@
         <v>186</v>
       </c>
       <c r="AH23" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI23" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="24" spans="1:35">
@@ -3455,10 +3458,10 @@
         <v>186</v>
       </c>
       <c r="AH24" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI24" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="25" spans="1:35">
@@ -3529,10 +3532,10 @@
         <v>186</v>
       </c>
       <c r="AH25" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI25" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="26" spans="1:35">
@@ -3603,10 +3606,10 @@
         <v>187</v>
       </c>
       <c r="AH26" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI26" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="27" spans="1:35">
@@ -3677,10 +3680,10 @@
         <v>186</v>
       </c>
       <c r="AH27" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI27" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="28" spans="1:35">
@@ -3751,10 +3754,10 @@
         <v>186</v>
       </c>
       <c r="AH28" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI28" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="29" spans="1:35">
@@ -3825,10 +3828,10 @@
         <v>186</v>
       </c>
       <c r="AH29" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI29" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="30" spans="1:35">
@@ -3899,10 +3902,10 @@
         <v>190</v>
       </c>
       <c r="AH30" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI30" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="31" spans="1:35">
@@ -3979,10 +3982,10 @@
         <v>191</v>
       </c>
       <c r="AH31" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI31" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="32" spans="1:35">
@@ -4050,13 +4053,13 @@
         <v>0</v>
       </c>
       <c r="AC32" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AH32" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI32" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="33" spans="1:35">
@@ -4133,10 +4136,10 @@
         <v>193</v>
       </c>
       <c r="AH33" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI33" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="34" spans="1:35">
@@ -4188,9 +4191,6 @@
       <c r="S34" t="s">
         <v>194</v>
       </c>
-      <c r="T34" t="s">
-        <v>212</v>
-      </c>
       <c r="U34" t="s">
         <v>215</v>
       </c>
@@ -4213,10 +4213,10 @@
         <v>194</v>
       </c>
       <c r="AH34" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI34" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="35" spans="1:35">
@@ -4290,13 +4290,13 @@
         <v>0</v>
       </c>
       <c r="AC35" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AH35" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI35" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="36" spans="1:35">
@@ -4373,10 +4373,10 @@
         <v>196</v>
       </c>
       <c r="AH36" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI36" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="37" spans="1:35">
@@ -4453,10 +4453,10 @@
         <v>190</v>
       </c>
       <c r="AH37" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI37" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="38" spans="1:35">
@@ -4508,9 +4508,6 @@
       <c r="S38" t="s">
         <v>194</v>
       </c>
-      <c r="T38" t="s">
-        <v>212</v>
-      </c>
       <c r="U38" t="s">
         <v>216</v>
       </c>
@@ -4533,10 +4530,10 @@
         <v>212</v>
       </c>
       <c r="AH38" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI38" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="39" spans="1:35">
@@ -4613,10 +4610,10 @@
         <v>191</v>
       </c>
       <c r="AH39" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI39" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="40" spans="1:35">
@@ -4693,10 +4690,10 @@
         <v>191</v>
       </c>
       <c r="AH40" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI40" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="41" spans="1:35">
@@ -4773,10 +4770,10 @@
         <v>191</v>
       </c>
       <c r="AH41" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI41" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="42" spans="1:35">
@@ -4853,10 +4850,10 @@
         <v>190</v>
       </c>
       <c r="AH42" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI42" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="43" spans="1:35">
@@ -4933,10 +4930,10 @@
         <v>197</v>
       </c>
       <c r="AH43" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI43" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="44" spans="1:35">
@@ -5010,13 +5007,13 @@
         <v>0</v>
       </c>
       <c r="AC44" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AH44" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI44" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="45" spans="1:35">
@@ -5093,10 +5090,10 @@
         <v>193</v>
       </c>
       <c r="AH45" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI45" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="46" spans="1:35">
@@ -5145,9 +5142,6 @@
       <c r="S46" t="s">
         <v>194</v>
       </c>
-      <c r="T46" t="s">
-        <v>212</v>
-      </c>
       <c r="U46" t="s">
         <v>217</v>
       </c>
@@ -5167,10 +5161,10 @@
         <v>194</v>
       </c>
       <c r="AH46" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI46" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="47" spans="1:35">
@@ -5241,10 +5235,10 @@
         <v>191</v>
       </c>
       <c r="AH47" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI47" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="48" spans="1:35">
@@ -5315,10 +5309,10 @@
         <v>191</v>
       </c>
       <c r="AH48" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI48" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="49" spans="1:35">
@@ -5389,10 +5383,10 @@
         <v>191</v>
       </c>
       <c r="AH49" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI49" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="50" spans="1:35">
@@ -5463,10 +5457,10 @@
         <v>190</v>
       </c>
       <c r="AH50" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI50" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="51" spans="1:35">
@@ -5537,10 +5531,10 @@
         <v>197</v>
       </c>
       <c r="AH51" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI51" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="52" spans="1:35">
@@ -5614,13 +5608,13 @@
         <v>0</v>
       </c>
       <c r="AC52" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AH52" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI52" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="53" spans="1:35">
@@ -5691,10 +5685,10 @@
         <v>193</v>
       </c>
       <c r="AH53" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI53" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="54" spans="1:35">
@@ -5771,10 +5765,10 @@
         <v>191</v>
       </c>
       <c r="AH54" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI54" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="55" spans="1:35">
@@ -5851,10 +5845,10 @@
         <v>191</v>
       </c>
       <c r="AH55" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI55" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="56" spans="1:35">
@@ -5931,10 +5925,10 @@
         <v>191</v>
       </c>
       <c r="AH56" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI56" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="57" spans="1:35">
@@ -6011,10 +6005,10 @@
         <v>190</v>
       </c>
       <c r="AH57" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI57" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="58" spans="1:35">
@@ -6066,9 +6060,6 @@
       <c r="S58" t="s">
         <v>194</v>
       </c>
-      <c r="T58" t="s">
-        <v>212</v>
-      </c>
       <c r="U58" t="s">
         <v>217</v>
       </c>
@@ -6091,10 +6082,10 @@
         <v>194</v>
       </c>
       <c r="AH58" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI58" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="59" spans="1:35">
@@ -6168,13 +6159,13 @@
         <v>0</v>
       </c>
       <c r="AC59" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AH59" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI59" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="60" spans="1:35">
@@ -6251,10 +6242,10 @@
         <v>191</v>
       </c>
       <c r="AH60" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI60" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="61" spans="1:35">
@@ -6331,10 +6322,10 @@
         <v>191</v>
       </c>
       <c r="AH61" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI61" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="62" spans="1:35">
@@ -6411,10 +6402,10 @@
         <v>191</v>
       </c>
       <c r="AH62" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI62" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="63" spans="1:35">
@@ -6491,10 +6482,10 @@
         <v>190</v>
       </c>
       <c r="AH63" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI63" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="64" spans="1:35">
@@ -6571,10 +6562,10 @@
         <v>197</v>
       </c>
       <c r="AH64" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI64" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="65" spans="1:35">
@@ -6648,13 +6639,13 @@
         <v>0</v>
       </c>
       <c r="AC65" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AH65" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI65" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="66" spans="1:35">
@@ -6731,10 +6722,10 @@
         <v>193</v>
       </c>
       <c r="AH66" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI66" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="67" spans="1:35">
@@ -6811,10 +6802,10 @@
         <v>191</v>
       </c>
       <c r="AH67" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI67" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="68" spans="1:35">
@@ -6863,9 +6854,6 @@
       <c r="S68" t="s">
         <v>194</v>
       </c>
-      <c r="T68" t="s">
-        <v>212</v>
-      </c>
       <c r="U68" t="s">
         <v>216</v>
       </c>
@@ -6885,10 +6873,10 @@
         <v>194</v>
       </c>
       <c r="AH68" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI68" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="69" spans="1:35">
@@ -6956,13 +6944,13 @@
         <v>0</v>
       </c>
       <c r="AC69" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AH69" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI69" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="70" spans="1:35">
@@ -7033,10 +7021,10 @@
         <v>191</v>
       </c>
       <c r="AH70" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI70" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="71" spans="1:35">
@@ -7107,10 +7095,10 @@
         <v>191</v>
       </c>
       <c r="AH71" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI71" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="72" spans="1:35">
@@ -7181,10 +7169,10 @@
         <v>191</v>
       </c>
       <c r="AH72" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI72" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="73" spans="1:35">
@@ -7255,10 +7243,10 @@
         <v>190</v>
       </c>
       <c r="AH73" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI73" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="74" spans="1:35">
@@ -7329,10 +7317,10 @@
         <v>197</v>
       </c>
       <c r="AH74" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI74" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="75" spans="1:35">
@@ -7400,13 +7388,13 @@
         <v>0</v>
       </c>
       <c r="AC75" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AH75" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI75" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="76" spans="1:35">
@@ -7477,10 +7465,10 @@
         <v>193</v>
       </c>
       <c r="AH76" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI76" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="77" spans="1:35">
@@ -7551,10 +7539,10 @@
         <v>193</v>
       </c>
       <c r="AH77" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI77" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="78" spans="1:35">
@@ -7625,10 +7613,10 @@
         <v>193</v>
       </c>
       <c r="AH78" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI78" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="79" spans="1:35">
@@ -7699,10 +7687,10 @@
         <v>193</v>
       </c>
       <c r="AH79" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI79" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="80" spans="1:35">
@@ -7773,10 +7761,10 @@
         <v>213</v>
       </c>
       <c r="AH80" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI80" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="81" spans="1:35">
@@ -7825,9 +7813,6 @@
       <c r="S81" t="s">
         <v>199</v>
       </c>
-      <c r="T81" t="s">
-        <v>213</v>
-      </c>
       <c r="U81" t="s">
         <v>216</v>
       </c>
@@ -7847,10 +7832,10 @@
         <v>213</v>
       </c>
       <c r="AH81" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI81" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="82" spans="1:35">
@@ -7921,10 +7906,10 @@
         <v>200</v>
       </c>
       <c r="AH82" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI82" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="83" spans="1:35">
@@ -7995,10 +7980,10 @@
         <v>213</v>
       </c>
       <c r="AH83" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI83" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="84" spans="1:35">
@@ -8047,9 +8032,6 @@
       <c r="S84" t="s">
         <v>199</v>
       </c>
-      <c r="T84" t="s">
-        <v>213</v>
-      </c>
       <c r="U84" t="s">
         <v>216</v>
       </c>
@@ -8069,10 +8051,10 @@
         <v>213</v>
       </c>
       <c r="AH84" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI84" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="85" spans="1:35">
@@ -8143,10 +8125,10 @@
         <v>213</v>
       </c>
       <c r="AH85" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI85" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="86" spans="1:35">
@@ -8211,10 +8193,10 @@
         <v>200</v>
       </c>
       <c r="AH86" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI86" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="87" spans="1:35">
@@ -8285,10 +8267,10 @@
         <v>213</v>
       </c>
       <c r="AH87" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI87" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="88" spans="1:35">
@@ -8337,9 +8319,6 @@
       <c r="S88" t="s">
         <v>199</v>
       </c>
-      <c r="T88" t="s">
-        <v>213</v>
-      </c>
       <c r="U88" t="s">
         <v>216</v>
       </c>
@@ -8359,10 +8338,10 @@
         <v>213</v>
       </c>
       <c r="AH88" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI88" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="89" spans="1:35">
@@ -8433,10 +8412,10 @@
         <v>213</v>
       </c>
       <c r="AH89" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI89" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="90" spans="1:35">
@@ -8501,10 +8480,10 @@
         <v>213</v>
       </c>
       <c r="AH90" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI90" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="91" spans="1:35">
@@ -8569,10 +8548,10 @@
         <v>200</v>
       </c>
       <c r="AH91" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI91" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="92" spans="1:35">
@@ -8643,10 +8622,10 @@
         <v>213</v>
       </c>
       <c r="AH92" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI92" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="93" spans="1:35">
@@ -8695,9 +8674,6 @@
       <c r="S93" t="s">
         <v>199</v>
       </c>
-      <c r="T93" t="s">
-        <v>213</v>
-      </c>
       <c r="U93" t="s">
         <v>216</v>
       </c>
@@ -8717,10 +8693,10 @@
         <v>213</v>
       </c>
       <c r="AH93" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI93" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="94" spans="1:35">
@@ -8791,10 +8767,10 @@
         <v>213</v>
       </c>
       <c r="AH94" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI94" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="95" spans="1:35">
@@ -8859,10 +8835,10 @@
         <v>213</v>
       </c>
       <c r="AH95" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI95" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="96" spans="1:35">
@@ -8927,10 +8903,10 @@
         <v>200</v>
       </c>
       <c r="AH96" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI96" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="97" spans="1:35">
@@ -9001,10 +8977,10 @@
         <v>213</v>
       </c>
       <c r="AH97" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI97" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="98" spans="1:35">
@@ -9053,9 +9029,6 @@
       <c r="S98" t="s">
         <v>199</v>
       </c>
-      <c r="T98" t="s">
-        <v>213</v>
-      </c>
       <c r="U98" t="s">
         <v>216</v>
       </c>
@@ -9075,10 +9048,10 @@
         <v>213</v>
       </c>
       <c r="AH98" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI98" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="99" spans="1:35">
@@ -9149,10 +9122,10 @@
         <v>200</v>
       </c>
       <c r="AH99" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI99" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="100" spans="1:35">
@@ -9229,10 +9202,10 @@
         <v>213</v>
       </c>
       <c r="AH100" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI100" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="101" spans="1:35">
@@ -9281,9 +9254,6 @@
       <c r="S101" t="s">
         <v>199</v>
       </c>
-      <c r="T101" t="s">
-        <v>213</v>
-      </c>
       <c r="U101" t="s">
         <v>216</v>
       </c>
@@ -9303,10 +9273,10 @@
         <v>213</v>
       </c>
       <c r="AH101" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI101" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="102" spans="1:35">
@@ -9377,10 +9347,10 @@
         <v>213</v>
       </c>
       <c r="AH102" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI102" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="103" spans="1:35">
@@ -9429,9 +9399,6 @@
       <c r="S103" t="s">
         <v>199</v>
       </c>
-      <c r="T103" t="s">
-        <v>213</v>
-      </c>
       <c r="U103" t="s">
         <v>216</v>
       </c>
@@ -9451,10 +9418,10 @@
         <v>213</v>
       </c>
       <c r="AH103" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI103" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="104" spans="1:35">
@@ -9525,10 +9492,10 @@
         <v>213</v>
       </c>
       <c r="AH104" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI104" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="105" spans="1:35">
@@ -9593,10 +9560,10 @@
         <v>213</v>
       </c>
       <c r="AH105" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI105" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="106" spans="1:35">
@@ -9661,10 +9628,10 @@
         <v>200</v>
       </c>
       <c r="AH106" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI106" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="107" spans="1:35">
@@ -9735,10 +9702,10 @@
         <v>213</v>
       </c>
       <c r="AH107" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI107" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="108" spans="1:35">
@@ -9809,10 +9776,10 @@
         <v>213</v>
       </c>
       <c r="AH108" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI108" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="109" spans="1:35">
@@ -9861,9 +9828,6 @@
       <c r="S109" t="s">
         <v>199</v>
       </c>
-      <c r="T109" t="s">
-        <v>213</v>
-      </c>
       <c r="U109" t="s">
         <v>216</v>
       </c>
@@ -9883,10 +9847,10 @@
         <v>213</v>
       </c>
       <c r="AH109" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI109" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="110" spans="1:35">
@@ -9957,10 +9921,10 @@
         <v>200</v>
       </c>
       <c r="AH110" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI110" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="111" spans="1:35">
@@ -10009,9 +9973,6 @@
       <c r="S111" t="s">
         <v>199</v>
       </c>
-      <c r="T111" t="s">
-        <v>213</v>
-      </c>
       <c r="U111" t="s">
         <v>216</v>
       </c>
@@ -10031,10 +9992,10 @@
         <v>199</v>
       </c>
       <c r="AH111" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI111" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="112" spans="1:35">
@@ -10105,10 +10066,10 @@
         <v>200</v>
       </c>
       <c r="AH112" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI112" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="113" spans="1:35">
@@ -10179,10 +10140,10 @@
         <v>198</v>
       </c>
       <c r="AH113" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI113" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="114" spans="1:35">
@@ -10231,9 +10192,6 @@
       <c r="S114" t="s">
         <v>199</v>
       </c>
-      <c r="T114" t="s">
-        <v>213</v>
-      </c>
       <c r="U114" t="s">
         <v>216</v>
       </c>
@@ -10253,10 +10211,10 @@
         <v>199</v>
       </c>
       <c r="AH114" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI114" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="115" spans="1:35">
@@ -10327,10 +10285,10 @@
         <v>200</v>
       </c>
       <c r="AH115" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI115" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="116" spans="1:35">
@@ -10401,10 +10359,10 @@
         <v>213</v>
       </c>
       <c r="AH116" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI116" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="117" spans="1:35">
@@ -10453,9 +10411,6 @@
       <c r="S117" t="s">
         <v>199</v>
       </c>
-      <c r="T117" t="s">
-        <v>213</v>
-      </c>
       <c r="U117" t="s">
         <v>216</v>
       </c>
@@ -10475,10 +10430,10 @@
         <v>213</v>
       </c>
       <c r="AH117" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI117" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="118" spans="1:35">
@@ -10549,10 +10504,10 @@
         <v>213</v>
       </c>
       <c r="AH118" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI118" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="119" spans="1:35">
@@ -10617,10 +10572,10 @@
         <v>213</v>
       </c>
       <c r="AH119" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI119" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="120" spans="1:35">
@@ -10685,10 +10640,10 @@
         <v>200</v>
       </c>
       <c r="AH120" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI120" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="121" spans="1:35">
@@ -10759,10 +10714,10 @@
         <v>213</v>
       </c>
       <c r="AH121" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI121" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="122" spans="1:35">
@@ -10811,9 +10766,6 @@
       <c r="S122" t="s">
         <v>199</v>
       </c>
-      <c r="T122" t="s">
-        <v>213</v>
-      </c>
       <c r="U122" t="s">
         <v>216</v>
       </c>
@@ -10833,10 +10785,10 @@
         <v>213</v>
       </c>
       <c r="AH122" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI122" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="123" spans="1:35">
@@ -10907,10 +10859,10 @@
         <v>213</v>
       </c>
       <c r="AH123" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI123" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="124" spans="1:35">
@@ -10975,10 +10927,10 @@
         <v>213</v>
       </c>
       <c r="AH124" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI124" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="125" spans="1:35">
@@ -11043,10 +10995,10 @@
         <v>200</v>
       </c>
       <c r="AH125" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI125" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="126" spans="1:35">
@@ -11123,10 +11075,10 @@
         <v>200</v>
       </c>
       <c r="AH126" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI126" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="127" spans="1:35">
@@ -11203,10 +11155,10 @@
         <v>200</v>
       </c>
       <c r="AH127" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI127" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="128" spans="1:35">
@@ -11277,10 +11229,10 @@
         <v>203</v>
       </c>
       <c r="AH128" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI128" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="129" spans="1:35">
@@ -11351,10 +11303,10 @@
         <v>203</v>
       </c>
       <c r="AH129" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI129" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="130" spans="1:35">
@@ -11431,10 +11383,10 @@
         <v>203</v>
       </c>
       <c r="AH130" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI130" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="131" spans="1:35">
@@ -11505,10 +11457,10 @@
         <v>203</v>
       </c>
       <c r="AH131" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI131" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="132" spans="1:35">
@@ -11579,10 +11531,10 @@
         <v>203</v>
       </c>
       <c r="AH132" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI132" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="133" spans="1:35">
@@ -11653,10 +11605,10 @@
         <v>203</v>
       </c>
       <c r="AH133" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI133" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="134" spans="1:35">
@@ -11727,10 +11679,10 @@
         <v>203</v>
       </c>
       <c r="AH134" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI134" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="135" spans="1:35">
@@ -11807,10 +11759,10 @@
         <v>203</v>
       </c>
       <c r="AH135" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI135" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="136" spans="1:35">
@@ -11881,10 +11833,10 @@
         <v>203</v>
       </c>
       <c r="AH136" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI136" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="137" spans="1:35">
@@ -11955,10 +11907,10 @@
         <v>203</v>
       </c>
       <c r="AH137" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI137" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="138" spans="1:35">
@@ -12029,10 +11981,10 @@
         <v>203</v>
       </c>
       <c r="AH138" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI138" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="139" spans="1:35">
@@ -12109,10 +12061,10 @@
         <v>203</v>
       </c>
       <c r="AH139" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI139" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="140" spans="1:35">
@@ -12183,10 +12135,10 @@
         <v>203</v>
       </c>
       <c r="AH140" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI140" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="141" spans="1:35">
@@ -12257,10 +12209,10 @@
         <v>203</v>
       </c>
       <c r="AH141" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI141" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="142" spans="1:35">
@@ -12331,10 +12283,10 @@
         <v>203</v>
       </c>
       <c r="AH142" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI142" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="143" spans="1:35">
@@ -12405,10 +12357,10 @@
         <v>203</v>
       </c>
       <c r="AH143" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI143" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="144" spans="1:35">
@@ -12479,10 +12431,10 @@
         <v>203</v>
       </c>
       <c r="AH144" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI144" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="145" spans="1:35">
@@ -12553,10 +12505,10 @@
         <v>203</v>
       </c>
       <c r="AH145" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI145" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="146" spans="1:35">
@@ -12627,10 +12579,10 @@
         <v>203</v>
       </c>
       <c r="AH146" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI146" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="147" spans="1:35">
@@ -12701,10 +12653,10 @@
         <v>203</v>
       </c>
       <c r="AH147" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI147" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="148" spans="1:35">
@@ -12775,10 +12727,10 @@
         <v>203</v>
       </c>
       <c r="AH148" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI148" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="149" spans="1:35">
@@ -12849,10 +12801,10 @@
         <v>203</v>
       </c>
       <c r="AH149" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI149" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="150" spans="1:35">
@@ -12929,10 +12881,10 @@
         <v>203</v>
       </c>
       <c r="AH150" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI150" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="151" spans="1:35">
@@ -13003,10 +12955,10 @@
         <v>203</v>
       </c>
       <c r="AH151" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI151" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:35">
@@ -13077,10 +13029,10 @@
         <v>203</v>
       </c>
       <c r="AH152" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI152" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:35">
@@ -13151,10 +13103,10 @@
         <v>203</v>
       </c>
       <c r="AH153" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI153" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="154" spans="1:35">
@@ -13225,10 +13177,10 @@
         <v>204</v>
       </c>
       <c r="AH154" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI154" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="155" spans="1:35">
@@ -13299,10 +13251,10 @@
         <v>204</v>
       </c>
       <c r="AH155" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI155" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="156" spans="1:35">
@@ -13373,10 +13325,10 @@
         <v>204</v>
       </c>
       <c r="AH156" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI156" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="157" spans="1:35">
@@ -13447,10 +13399,10 @@
         <v>204</v>
       </c>
       <c r="AH157" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI157" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="158" spans="1:35">
@@ -13521,10 +13473,10 @@
         <v>204</v>
       </c>
       <c r="AH158" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI158" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="159" spans="1:35">
@@ -13595,10 +13547,10 @@
         <v>204</v>
       </c>
       <c r="AH159" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI159" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="160" spans="1:35">
@@ -13672,10 +13624,10 @@
         <v>204</v>
       </c>
       <c r="AH160" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI160" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="161" spans="1:35">
@@ -13749,10 +13701,10 @@
         <v>204</v>
       </c>
       <c r="AH161" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI161" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="162" spans="1:35">
@@ -13826,10 +13778,10 @@
         <v>204</v>
       </c>
       <c r="AH162" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI162" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="163" spans="1:35">
@@ -13903,10 +13855,10 @@
         <v>204</v>
       </c>
       <c r="AH163" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI163" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="164" spans="1:35">
@@ -13980,10 +13932,10 @@
         <v>204</v>
       </c>
       <c r="AH164" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI164" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="165" spans="1:35">
@@ -14057,10 +14009,10 @@
         <v>204</v>
       </c>
       <c r="AH165" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI165" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="166" spans="1:35">
@@ -14134,10 +14086,10 @@
         <v>204</v>
       </c>
       <c r="AH166" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI166" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="167" spans="1:35">
@@ -14211,10 +14163,10 @@
         <v>204</v>
       </c>
       <c r="AH167" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI167" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="168" spans="1:35">
@@ -14288,10 +14240,10 @@
         <v>204</v>
       </c>
       <c r="AH168" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI168" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="169" spans="1:35">
@@ -14365,10 +14317,10 @@
         <v>204</v>
       </c>
       <c r="AH169" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI169" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="170" spans="1:35">
@@ -14442,10 +14394,10 @@
         <v>204</v>
       </c>
       <c r="AH170" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI170" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="171" spans="1:35">
@@ -14519,10 +14471,10 @@
         <v>204</v>
       </c>
       <c r="AH171" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI171" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="172" spans="1:35">
@@ -14596,10 +14548,10 @@
         <v>204</v>
       </c>
       <c r="AH172" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI172" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="173" spans="1:35">
@@ -14673,10 +14625,10 @@
         <v>204</v>
       </c>
       <c r="AH173" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI173" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="174" spans="1:35">
@@ -14744,10 +14696,10 @@
         <v>204</v>
       </c>
       <c r="AH174" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI174" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="175" spans="1:35">
@@ -14815,10 +14767,10 @@
         <v>204</v>
       </c>
       <c r="AH175" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI175" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="176" spans="1:35">
@@ -14886,10 +14838,10 @@
         <v>204</v>
       </c>
       <c r="AH176" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI176" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="177" spans="1:35">
@@ -14957,10 +14909,10 @@
         <v>204</v>
       </c>
       <c r="AH177" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI177" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="178" spans="1:35">
@@ -15028,10 +14980,10 @@
         <v>204</v>
       </c>
       <c r="AH178" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI178" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="179" spans="1:35">
@@ -15099,10 +15051,10 @@
         <v>204</v>
       </c>
       <c r="AH179" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI179" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="180" spans="1:35">
@@ -15170,10 +15122,10 @@
         <v>54</v>
       </c>
       <c r="AH180" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI180" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="181" spans="1:35">
@@ -15241,10 +15193,10 @@
         <v>54</v>
       </c>
       <c r="AH181" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI181" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="182" spans="1:35">
@@ -15312,10 +15264,10 @@
         <v>54</v>
       </c>
       <c r="AH182" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI182" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="183" spans="1:35">
@@ -15383,10 +15335,10 @@
         <v>54</v>
       </c>
       <c r="AH183" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI183" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="184" spans="1:35">
@@ -15454,10 +15406,10 @@
         <v>205</v>
       </c>
       <c r="AH184" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI184" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="185" spans="1:35">
@@ -15525,10 +15477,10 @@
         <v>55</v>
       </c>
       <c r="AH185" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI185" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="186" spans="1:35">
@@ -15596,10 +15548,10 @@
         <v>54</v>
       </c>
       <c r="AH186" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI186" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="187" spans="1:35">
@@ -15667,10 +15619,10 @@
         <v>54</v>
       </c>
       <c r="AH187" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI187" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="188" spans="1:35">
@@ -15738,10 +15690,10 @@
         <v>54</v>
       </c>
       <c r="AH188" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI188" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="189" spans="1:35">
@@ -15809,10 +15761,10 @@
         <v>205</v>
       </c>
       <c r="AH189" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI189" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="190" spans="1:35">
@@ -15880,10 +15832,10 @@
         <v>54</v>
       </c>
       <c r="AH190" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI190" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="191" spans="1:35">
@@ -15951,10 +15903,10 @@
         <v>205</v>
       </c>
       <c r="AH191" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI191" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="192" spans="1:35">
@@ -16022,10 +15974,10 @@
         <v>54</v>
       </c>
       <c r="AH192" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI192" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="193" spans="1:35">
@@ -16093,10 +16045,10 @@
         <v>54</v>
       </c>
       <c r="AH193" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI193" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="194" spans="1:35">
@@ -16164,10 +16116,10 @@
         <v>54</v>
       </c>
       <c r="AH194" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI194" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="195" spans="1:35">
@@ -16235,10 +16187,10 @@
         <v>54</v>
       </c>
       <c r="AH195" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI195" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="196" spans="1:35">
@@ -16306,10 +16258,10 @@
         <v>54</v>
       </c>
       <c r="AH196" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI196" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="197" spans="1:35">
@@ -16377,10 +16329,10 @@
         <v>54</v>
       </c>
       <c r="AH197" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI197" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="198" spans="1:35">
@@ -16448,10 +16400,10 @@
         <v>205</v>
       </c>
       <c r="AH198" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI198" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="199" spans="1:35">
@@ -16519,10 +16471,10 @@
         <v>55</v>
       </c>
       <c r="AH199" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI199" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="200" spans="1:35">
@@ -16593,10 +16545,10 @@
         <v>54</v>
       </c>
       <c r="AH200" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI200" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="201" spans="1:35">
@@ -16667,10 +16619,10 @@
         <v>54</v>
       </c>
       <c r="AH201" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI201" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="202" spans="1:35">
@@ -16741,10 +16693,10 @@
         <v>54</v>
       </c>
       <c r="AH202" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI202" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="203" spans="1:35">
@@ -16815,10 +16767,10 @@
         <v>54</v>
       </c>
       <c r="AH203" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI203" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="204" spans="1:35">
@@ -16886,10 +16838,10 @@
         <v>54</v>
       </c>
       <c r="AH204" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI204" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="205" spans="1:35">
@@ -16957,10 +16909,10 @@
         <v>54</v>
       </c>
       <c r="AH205" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI205" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="206" spans="1:35">
@@ -17025,10 +16977,10 @@
         <v>0</v>
       </c>
       <c r="AH206" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI206" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="207" spans="1:35">
@@ -17090,10 +17042,10 @@
         <v>0</v>
       </c>
       <c r="AH207" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI207" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="208" spans="1:35">
@@ -17161,13 +17113,13 @@
         <v>0</v>
       </c>
       <c r="AC208" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AH208" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI208" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="209" spans="1:35">
@@ -17238,10 +17190,10 @@
         <v>187</v>
       </c>
       <c r="AH209" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI209" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="210" spans="1:35">
@@ -17318,10 +17270,10 @@
         <v>191</v>
       </c>
       <c r="AH210" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI210" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="211" spans="1:35">
@@ -17398,10 +17350,10 @@
         <v>191</v>
       </c>
       <c r="AH211" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI211" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="212" spans="1:35">
@@ -17475,13 +17427,13 @@
         <v>0</v>
       </c>
       <c r="AC212" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AH212" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI212" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="213" spans="1:35">
@@ -17558,10 +17510,10 @@
         <v>197</v>
       </c>
       <c r="AH213" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI213" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="214" spans="1:35">
@@ -17638,10 +17590,10 @@
         <v>191</v>
       </c>
       <c r="AH214" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI214" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="215" spans="1:35">
@@ -17718,10 +17670,10 @@
         <v>196</v>
       </c>
       <c r="AH215" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI215" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="216" spans="1:35">
@@ -17798,10 +17750,10 @@
         <v>191</v>
       </c>
       <c r="AH216" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI216" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="217" spans="1:35">
@@ -17878,10 +17830,10 @@
         <v>191</v>
       </c>
       <c r="AH217" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI217" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="218" spans="1:35">
@@ -17952,10 +17904,10 @@
         <v>190</v>
       </c>
       <c r="AH218" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI218" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="219" spans="1:35">
@@ -18026,10 +17978,10 @@
         <v>197</v>
       </c>
       <c r="AH219" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI219" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="220" spans="1:35">
@@ -18106,10 +18058,10 @@
         <v>191</v>
       </c>
       <c r="AH220" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI220" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="221" spans="1:35">
@@ -18186,10 +18138,10 @@
         <v>196</v>
       </c>
       <c r="AH221" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI221" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="222" spans="1:35">
@@ -18266,10 +18218,10 @@
         <v>191</v>
       </c>
       <c r="AH222" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI222" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="223" spans="1:35">
@@ -18346,10 +18298,10 @@
         <v>191</v>
       </c>
       <c r="AH223" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI223" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="224" spans="1:35">
@@ -18420,10 +18372,10 @@
         <v>190</v>
       </c>
       <c r="AH224" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI224" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="225" spans="1:35">
@@ -18494,10 +18446,10 @@
         <v>197</v>
       </c>
       <c r="AH225" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI225" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="226" spans="1:35">
@@ -18546,9 +18498,6 @@
       <c r="S226" t="s">
         <v>194</v>
       </c>
-      <c r="T226" t="s">
-        <v>212</v>
-      </c>
       <c r="U226" t="s">
         <v>216</v>
       </c>
@@ -18571,10 +18520,10 @@
         <v>194</v>
       </c>
       <c r="AH226" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI226" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="227" spans="1:35">
@@ -18648,10 +18597,10 @@
         <v>195</v>
       </c>
       <c r="AH227" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI227" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="228" spans="1:35">
@@ -18725,10 +18674,10 @@
         <v>191</v>
       </c>
       <c r="AH228" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI228" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="229" spans="1:35">
@@ -18802,10 +18751,10 @@
         <v>196</v>
       </c>
       <c r="AH229" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI229" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="230" spans="1:35">
@@ -18879,10 +18828,10 @@
         <v>191</v>
       </c>
       <c r="AH230" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI230" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="231" spans="1:35">
@@ -18956,10 +18905,10 @@
         <v>191</v>
       </c>
       <c r="AH231" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI231" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="232" spans="1:35">
@@ -19036,10 +18985,10 @@
         <v>190</v>
       </c>
       <c r="AH232" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI232" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="233" spans="1:35">
@@ -19113,10 +19062,10 @@
         <v>197</v>
       </c>
       <c r="AH233" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI233" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="234" spans="1:35">
@@ -19190,10 +19139,10 @@
         <v>192</v>
       </c>
       <c r="AH234" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI234" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="235" spans="1:35">
@@ -19267,10 +19216,10 @@
         <v>193</v>
       </c>
       <c r="AH235" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI235" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="236" spans="1:35">
@@ -19322,9 +19271,6 @@
       <c r="S236" t="s">
         <v>194</v>
       </c>
-      <c r="T236" t="s">
-        <v>212</v>
-      </c>
       <c r="U236" t="s">
         <v>216</v>
       </c>
@@ -19347,10 +19293,10 @@
         <v>194</v>
       </c>
       <c r="AH236" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI236" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="237" spans="1:35">
@@ -19427,10 +19373,10 @@
         <v>191</v>
       </c>
       <c r="AH237" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI237" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="238" spans="1:35">
@@ -19507,10 +19453,10 @@
         <v>191</v>
       </c>
       <c r="AH238" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI238" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="239" spans="1:35">
@@ -19587,10 +19533,10 @@
         <v>191</v>
       </c>
       <c r="AH239" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI239" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="240" spans="1:35">
@@ -19667,10 +19613,10 @@
         <v>197</v>
       </c>
       <c r="AH240" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI240" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="241" spans="1:35">
@@ -19744,13 +19690,13 @@
         <v>0</v>
       </c>
       <c r="AC241" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AH241" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI241" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="242" spans="1:35">
@@ -19821,10 +19767,10 @@
         <v>193</v>
       </c>
       <c r="AH242" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI242" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="243" spans="1:35">
@@ -19873,9 +19819,6 @@
       <c r="S243" t="s">
         <v>194</v>
       </c>
-      <c r="T243" t="s">
-        <v>212</v>
-      </c>
       <c r="U243" t="s">
         <v>216</v>
       </c>
@@ -19898,10 +19841,10 @@
         <v>194</v>
       </c>
       <c r="AH243" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI243" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="244" spans="1:35">
@@ -19978,10 +19921,10 @@
         <v>191</v>
       </c>
       <c r="AH244" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI244" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="245" spans="1:35">
@@ -20055,10 +19998,10 @@
         <v>196</v>
       </c>
       <c r="AH245" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI245" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="246" spans="1:35">
@@ -20135,10 +20078,10 @@
         <v>191</v>
       </c>
       <c r="AH246" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI246" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="247" spans="1:35">
@@ -20215,10 +20158,10 @@
         <v>191</v>
       </c>
       <c r="AH247" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI247" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="248" spans="1:35">
@@ -20292,10 +20235,10 @@
         <v>190</v>
       </c>
       <c r="AH248" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI248" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="249" spans="1:35">
@@ -20369,10 +20312,10 @@
         <v>197</v>
       </c>
       <c r="AH249" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI249" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="250" spans="1:35">
@@ -20446,10 +20389,10 @@
         <v>192</v>
       </c>
       <c r="AH250" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI250" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="251" spans="1:35">
@@ -20523,10 +20466,10 @@
         <v>193</v>
       </c>
       <c r="AH251" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI251" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="252" spans="1:35">
@@ -20603,10 +20546,10 @@
         <v>197</v>
       </c>
       <c r="AH252" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI252" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="253" spans="1:35">
@@ -20677,10 +20620,10 @@
         <v>191</v>
       </c>
       <c r="AH253" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI253" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="254" spans="1:35">
@@ -20751,10 +20694,10 @@
         <v>191</v>
       </c>
       <c r="AH254" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI254" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="255" spans="1:35">
@@ -20825,10 +20768,10 @@
         <v>191</v>
       </c>
       <c r="AH255" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI255" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="256" spans="1:35">
@@ -20905,10 +20848,10 @@
         <v>202</v>
       </c>
       <c r="AH256" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI256" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="257" spans="1:35">
@@ -20985,10 +20928,10 @@
         <v>202</v>
       </c>
       <c r="AH257" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI257" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="258" spans="1:35">
@@ -21065,10 +21008,10 @@
         <v>201</v>
       </c>
       <c r="AH258" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI258" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="259" spans="1:35">
@@ -21117,9 +21060,6 @@
       <c r="S259" t="s">
         <v>199</v>
       </c>
-      <c r="T259" t="s">
-        <v>213</v>
-      </c>
       <c r="U259" t="s">
         <v>216</v>
       </c>
@@ -21139,10 +21079,10 @@
         <v>199</v>
       </c>
       <c r="AH259" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI259" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="260" spans="1:35">
@@ -21219,10 +21159,10 @@
         <v>198</v>
       </c>
       <c r="AH260" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI260" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="261" spans="1:35">
@@ -21271,9 +21211,6 @@
       <c r="S261" t="s">
         <v>199</v>
       </c>
-      <c r="T261" t="s">
-        <v>213</v>
-      </c>
       <c r="U261" t="s">
         <v>217</v>
       </c>
@@ -21293,10 +21230,10 @@
         <v>213</v>
       </c>
       <c r="AH261" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI261" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="262" spans="1:35">
@@ -21373,10 +21310,10 @@
         <v>213</v>
       </c>
       <c r="AH262" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI262" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="263" spans="1:35">
@@ -21428,9 +21365,6 @@
       <c r="S263" t="s">
         <v>199</v>
       </c>
-      <c r="T263" t="s">
-        <v>213</v>
-      </c>
       <c r="U263" t="s">
         <v>217</v>
       </c>
@@ -21453,10 +21387,10 @@
         <v>199</v>
       </c>
       <c r="AH263" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI263" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="264" spans="1:35">
@@ -21533,10 +21467,10 @@
         <v>200</v>
       </c>
       <c r="AH264" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI264" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="265" spans="1:35">
@@ -21610,10 +21544,10 @@
         <v>202</v>
       </c>
       <c r="AH265" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI265" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="266" spans="1:35">
@@ -21690,10 +21624,10 @@
         <v>202</v>
       </c>
       <c r="AH266" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI266" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="267" spans="1:35">
@@ -21767,10 +21701,10 @@
         <v>201</v>
       </c>
       <c r="AH267" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI267" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="268" spans="1:35">
@@ -21819,9 +21753,6 @@
       <c r="S268" t="s">
         <v>199</v>
       </c>
-      <c r="T268" t="s">
-        <v>213</v>
-      </c>
       <c r="U268" t="s">
         <v>217</v>
       </c>
@@ -21844,10 +21775,10 @@
         <v>199</v>
       </c>
       <c r="AH268" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI268" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="269" spans="1:35">
@@ -21921,10 +21852,10 @@
         <v>202</v>
       </c>
       <c r="AH269" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI269" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="270" spans="1:35">
@@ -21998,10 +21929,10 @@
         <v>202</v>
       </c>
       <c r="AH270" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI270" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="271" spans="1:35">
@@ -22078,10 +22009,10 @@
         <v>198</v>
       </c>
       <c r="AH271" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI271" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="272" spans="1:35">
@@ -22130,9 +22061,6 @@
       <c r="S272" t="s">
         <v>199</v>
       </c>
-      <c r="T272" t="s">
-        <v>213</v>
-      </c>
       <c r="U272" t="s">
         <v>217</v>
       </c>
@@ -22152,10 +22080,10 @@
         <v>213</v>
       </c>
       <c r="AH272" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI272" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="273" spans="1:35">
@@ -22207,9 +22135,6 @@
       <c r="S273" t="s">
         <v>199</v>
       </c>
-      <c r="T273" t="s">
-        <v>213</v>
-      </c>
       <c r="U273" t="s">
         <v>215</v>
       </c>
@@ -22232,10 +22157,10 @@
         <v>199</v>
       </c>
       <c r="AH273" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI273" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="274" spans="1:35">
@@ -22306,10 +22231,10 @@
         <v>202</v>
       </c>
       <c r="AH274" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI274" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="275" spans="1:35">
@@ -22380,10 +22305,10 @@
         <v>202</v>
       </c>
       <c r="AH275" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI275" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="276" spans="1:35">
@@ -22454,10 +22379,10 @@
         <v>200</v>
       </c>
       <c r="AH276" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI276" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="277" spans="1:35">
@@ -22509,9 +22434,6 @@
       <c r="S277" t="s">
         <v>199</v>
       </c>
-      <c r="T277" t="s">
-        <v>213</v>
-      </c>
       <c r="U277" t="s">
         <v>217</v>
       </c>
@@ -22534,10 +22456,10 @@
         <v>199</v>
       </c>
       <c r="AH277" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI277" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="278" spans="1:35">
@@ -22589,9 +22511,6 @@
       <c r="S278" t="s">
         <v>199</v>
       </c>
-      <c r="T278" t="s">
-        <v>213</v>
-      </c>
       <c r="U278" t="s">
         <v>217</v>
       </c>
@@ -22614,10 +22533,10 @@
         <v>199</v>
       </c>
       <c r="AH278" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI278" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="279" spans="1:35">
@@ -22694,10 +22613,10 @@
         <v>200</v>
       </c>
       <c r="AH279" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI279" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="280" spans="1:35">
@@ -22774,10 +22693,10 @@
         <v>203</v>
       </c>
       <c r="AH280" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI280" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="281" spans="1:35">
@@ -22851,10 +22770,10 @@
         <v>203</v>
       </c>
       <c r="AH281" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI281" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="282" spans="1:35">
@@ -22931,10 +22850,10 @@
         <v>203</v>
       </c>
       <c r="AH282" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI282" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="283" spans="1:35">
@@ -23005,10 +22924,10 @@
         <v>203</v>
       </c>
       <c r="AH283" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI283" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="284" spans="1:35">
@@ -23079,10 +22998,10 @@
         <v>203</v>
       </c>
       <c r="AH284" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI284" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="285" spans="1:35">
@@ -23153,10 +23072,10 @@
         <v>203</v>
       </c>
       <c r="AH285" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI285" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="286" spans="1:35">
@@ -23227,10 +23146,10 @@
         <v>203</v>
       </c>
       <c r="AH286" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI286" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="287" spans="1:35">
@@ -23301,10 +23220,10 @@
         <v>203</v>
       </c>
       <c r="AH287" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI287" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="288" spans="1:35">
@@ -23381,10 +23300,10 @@
         <v>203</v>
       </c>
       <c r="AH288" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI288" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="289" spans="1:35">
@@ -23455,10 +23374,10 @@
         <v>203</v>
       </c>
       <c r="AH289" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI289" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="290" spans="1:35">
@@ -23535,10 +23454,10 @@
         <v>203</v>
       </c>
       <c r="AH290" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI290" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="291" spans="1:35">
@@ -23609,10 +23528,10 @@
         <v>203</v>
       </c>
       <c r="AH291" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI291" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="292" spans="1:35">
@@ -23683,10 +23602,10 @@
         <v>203</v>
       </c>
       <c r="AH292" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI292" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="293" spans="1:35">
@@ -23757,10 +23676,10 @@
         <v>203</v>
       </c>
       <c r="AH293" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI293" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="294" spans="1:35">
@@ -23837,10 +23756,10 @@
         <v>203</v>
       </c>
       <c r="AH294" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI294" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="295" spans="1:35">
@@ -23911,10 +23830,10 @@
         <v>203</v>
       </c>
       <c r="AH295" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI295" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="296" spans="1:35">
@@ -23985,10 +23904,10 @@
         <v>203</v>
       </c>
       <c r="AH296" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI296" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="297" spans="1:35">
@@ -24059,10 +23978,10 @@
         <v>203</v>
       </c>
       <c r="AH297" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI297" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="298" spans="1:35">
@@ -24133,10 +24052,10 @@
         <v>203</v>
       </c>
       <c r="AH298" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI298" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="299" spans="1:35">
@@ -24207,10 +24126,10 @@
         <v>203</v>
       </c>
       <c r="AH299" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI299" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="300" spans="1:35">
@@ -24281,10 +24200,10 @@
         <v>203</v>
       </c>
       <c r="AH300" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI300" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="301" spans="1:35">
@@ -24361,10 +24280,10 @@
         <v>203</v>
       </c>
       <c r="AH301" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI301" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="302" spans="1:35">
@@ -24441,10 +24360,10 @@
         <v>203</v>
       </c>
       <c r="AH302" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI302" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="303" spans="1:35">
@@ -24521,10 +24440,10 @@
         <v>203</v>
       </c>
       <c r="AH303" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI303" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="304" spans="1:35">
@@ -24598,10 +24517,10 @@
         <v>203</v>
       </c>
       <c r="AH304" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI304" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="305" spans="1:35">
@@ -24675,10 +24594,10 @@
         <v>203</v>
       </c>
       <c r="AH305" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI305" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="306" spans="1:35">
@@ -24752,10 +24671,10 @@
         <v>204</v>
       </c>
       <c r="AH306" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI306" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="307" spans="1:35">
@@ -24829,10 +24748,10 @@
         <v>204</v>
       </c>
       <c r="AH307" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI307" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="308" spans="1:35">
@@ -24903,10 +24822,10 @@
         <v>204</v>
       </c>
       <c r="AH308" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI308" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="309" spans="1:35">
@@ -24977,10 +24896,10 @@
         <v>204</v>
       </c>
       <c r="AH309" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI309" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="310" spans="1:35">
@@ -25051,10 +24970,10 @@
         <v>204</v>
       </c>
       <c r="AH310" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI310" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="311" spans="1:35">
@@ -25125,10 +25044,10 @@
         <v>204</v>
       </c>
       <c r="AH311" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI311" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="312" spans="1:35">
@@ -25196,10 +25115,10 @@
         <v>204</v>
       </c>
       <c r="AH312" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI312" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="313" spans="1:35">
@@ -25273,10 +25192,10 @@
         <v>204</v>
       </c>
       <c r="AH313" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI313" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="314" spans="1:35">
@@ -25350,10 +25269,10 @@
         <v>204</v>
       </c>
       <c r="AH314" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI314" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="315" spans="1:35">
@@ -25427,10 +25346,10 @@
         <v>204</v>
       </c>
       <c r="AH315" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI315" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="316" spans="1:35">
@@ -25504,10 +25423,10 @@
         <v>204</v>
       </c>
       <c r="AH316" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI316" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="317" spans="1:35">
@@ -25581,10 +25500,10 @@
         <v>204</v>
       </c>
       <c r="AH317" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI317" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="318" spans="1:35">
@@ -25655,10 +25574,10 @@
         <v>204</v>
       </c>
       <c r="AH318" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI318" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="319" spans="1:35">
@@ -25729,10 +25648,10 @@
         <v>204</v>
       </c>
       <c r="AH319" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI319" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="320" spans="1:35">
@@ -25803,10 +25722,10 @@
         <v>204</v>
       </c>
       <c r="AH320" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI320" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="321" spans="1:35">
@@ -25874,10 +25793,10 @@
         <v>204</v>
       </c>
       <c r="AH321" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI321" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="322" spans="1:35">
@@ -25945,10 +25864,10 @@
         <v>204</v>
       </c>
       <c r="AH322" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI322" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="323" spans="1:35">
@@ -26016,10 +25935,10 @@
         <v>204</v>
       </c>
       <c r="AH323" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI323" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="324" spans="1:35">
@@ -26087,10 +26006,10 @@
         <v>204</v>
       </c>
       <c r="AH324" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI324" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="325" spans="1:35">
@@ -26158,10 +26077,10 @@
         <v>204</v>
       </c>
       <c r="AH325" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI325" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="326" spans="1:35">
@@ -26229,10 +26148,10 @@
         <v>54</v>
       </c>
       <c r="AH326" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI326" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="327" spans="1:35">
@@ -26300,10 +26219,10 @@
         <v>54</v>
       </c>
       <c r="AH327" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI327" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="328" spans="1:35">
@@ -26371,10 +26290,10 @@
         <v>54</v>
       </c>
       <c r="AH328" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI328" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="329" spans="1:35">
@@ -26442,10 +26361,10 @@
         <v>54</v>
       </c>
       <c r="AH329" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI329" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="330" spans="1:35">
@@ -26513,10 +26432,10 @@
         <v>205</v>
       </c>
       <c r="AH330" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI330" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="331" spans="1:35">
@@ -26584,10 +26503,10 @@
         <v>205</v>
       </c>
       <c r="AH331" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI331" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="332" spans="1:35">
@@ -26655,10 +26574,10 @@
         <v>205</v>
       </c>
       <c r="AH332" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI332" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="333" spans="1:35">
@@ -26726,10 +26645,10 @@
         <v>205</v>
       </c>
       <c r="AH333" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI333" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="334" spans="1:35">
@@ -26797,10 +26716,10 @@
         <v>205</v>
       </c>
       <c r="AH334" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI334" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="335" spans="1:35">
@@ -26868,10 +26787,10 @@
         <v>205</v>
       </c>
       <c r="AH335" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI335" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="336" spans="1:35">
@@ -26939,10 +26858,10 @@
         <v>205</v>
       </c>
       <c r="AH336" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI336" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="337" spans="1:35">
@@ -27010,10 +26929,10 @@
         <v>205</v>
       </c>
       <c r="AH337" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI337" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="338" spans="1:35">
@@ -27081,10 +27000,10 @@
         <v>205</v>
       </c>
       <c r="AH338" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI338" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="339" spans="1:35">
@@ -27155,10 +27074,10 @@
         <v>54</v>
       </c>
       <c r="AH339" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI339" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="340" spans="1:35">
@@ -27229,10 +27148,10 @@
         <v>54</v>
       </c>
       <c r="AH340" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI340" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="341" spans="1:35">
@@ -27300,13 +27219,13 @@
         <v>0</v>
       </c>
       <c r="AC341" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AH341" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI341" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="342" spans="1:35">
@@ -27380,10 +27299,10 @@
         <v>184</v>
       </c>
       <c r="AH342" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI342" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="343" spans="1:35">
@@ -27454,10 +27373,10 @@
         <v>182</v>
       </c>
       <c r="AH343" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI343" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="344" spans="1:35">
@@ -27531,13 +27450,13 @@
         <v>0</v>
       </c>
       <c r="AC344" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AH344" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI344" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="345" spans="1:35">
@@ -27608,10 +27527,10 @@
         <v>182</v>
       </c>
       <c r="AH345" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI345" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="346" spans="1:35">
@@ -27688,10 +27607,10 @@
         <v>187</v>
       </c>
       <c r="AH346" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI346" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="347" spans="1:35">
@@ -27768,10 +27687,10 @@
         <v>187</v>
       </c>
       <c r="AH347" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI347" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="348" spans="1:35">
@@ -27845,10 +27764,10 @@
         <v>187</v>
       </c>
       <c r="AH348" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI348" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="349" spans="1:35">
@@ -27919,10 +27838,10 @@
         <v>188</v>
       </c>
       <c r="AH349" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI349" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="350" spans="1:35">
@@ -27971,9 +27890,6 @@
       <c r="S350" t="s">
         <v>194</v>
       </c>
-      <c r="T350" t="s">
-        <v>212</v>
-      </c>
       <c r="U350" t="s">
         <v>216</v>
       </c>
@@ -27993,10 +27909,10 @@
         <v>194</v>
       </c>
       <c r="AH350" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI350" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="351" spans="1:35">
@@ -28073,10 +27989,10 @@
         <v>192</v>
       </c>
       <c r="AH351" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI351" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="352" spans="1:35">
@@ -28125,9 +28041,6 @@
       <c r="S352" t="s">
         <v>194</v>
       </c>
-      <c r="T352" t="s">
-        <v>212</v>
-      </c>
       <c r="U352" t="s">
         <v>216</v>
       </c>
@@ -28147,10 +28060,10 @@
         <v>194</v>
       </c>
       <c r="AH352" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI352" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="353" spans="1:35">
@@ -28227,10 +28140,10 @@
         <v>192</v>
       </c>
       <c r="AH353" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI353" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="354" spans="1:35">
@@ -28307,10 +28220,10 @@
         <v>191</v>
       </c>
       <c r="AH354" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI354" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="355" spans="1:35">
@@ -28387,10 +28300,10 @@
         <v>190</v>
       </c>
       <c r="AH355" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI355" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="356" spans="1:35">
@@ -28442,9 +28355,6 @@
       <c r="S356" t="s">
         <v>194</v>
       </c>
-      <c r="T356" t="s">
-        <v>212</v>
-      </c>
       <c r="U356" t="s">
         <v>217</v>
       </c>
@@ -28467,10 +28377,10 @@
         <v>194</v>
       </c>
       <c r="AH356" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI356" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="357" spans="1:35">
@@ -28547,10 +28457,10 @@
         <v>191</v>
       </c>
       <c r="AH357" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI357" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="358" spans="1:35">
@@ -28627,10 +28537,10 @@
         <v>196</v>
       </c>
       <c r="AH358" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI358" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="359" spans="1:35">
@@ -28707,10 +28617,10 @@
         <v>191</v>
       </c>
       <c r="AH359" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI359" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="360" spans="1:35">
@@ -28787,10 +28697,10 @@
         <v>191</v>
       </c>
       <c r="AH360" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI360" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="361" spans="1:35">
@@ -28867,10 +28777,10 @@
         <v>190</v>
       </c>
       <c r="AH361" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI361" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="362" spans="1:35">
@@ -28947,10 +28857,10 @@
         <v>197</v>
       </c>
       <c r="AH362" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI362" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="363" spans="1:35">
@@ -29027,10 +28937,10 @@
         <v>192</v>
       </c>
       <c r="AH363" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI363" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="364" spans="1:35">
@@ -29107,10 +29017,10 @@
         <v>195</v>
       </c>
       <c r="AH364" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI364" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="365" spans="1:35">
@@ -29181,10 +29091,10 @@
         <v>195</v>
       </c>
       <c r="AH365" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI365" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="366" spans="1:35">
@@ -29261,10 +29171,10 @@
         <v>191</v>
       </c>
       <c r="AH366" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI366" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="367" spans="1:35">
@@ -29341,10 +29251,10 @@
         <v>190</v>
       </c>
       <c r="AH367" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI367" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="368" spans="1:35">
@@ -29415,10 +29325,10 @@
         <v>191</v>
       </c>
       <c r="AH368" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI368" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="369" spans="1:35">
@@ -29489,10 +29399,10 @@
         <v>194</v>
       </c>
       <c r="AH369" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI369" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="370" spans="1:35">
@@ -29569,10 +29479,10 @@
         <v>193</v>
       </c>
       <c r="AH370" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI370" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="371" spans="1:35">
@@ -29643,10 +29553,10 @@
         <v>198</v>
       </c>
       <c r="AH371" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI371" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="372" spans="1:35">
@@ -29698,9 +29608,6 @@
       <c r="S372" t="s">
         <v>199</v>
       </c>
-      <c r="T372" t="s">
-        <v>213</v>
-      </c>
       <c r="U372" t="s">
         <v>217</v>
       </c>
@@ -29723,10 +29630,10 @@
         <v>199</v>
       </c>
       <c r="AH372" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI372" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="373" spans="1:35">
@@ -29803,10 +29710,10 @@
         <v>213</v>
       </c>
       <c r="AH373" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI373" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="374" spans="1:35">
@@ -29880,10 +29787,10 @@
         <v>198</v>
       </c>
       <c r="AH374" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI374" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="375" spans="1:35">
@@ -29932,9 +29839,6 @@
       <c r="S375" t="s">
         <v>199</v>
       </c>
-      <c r="T375" t="s">
-        <v>213</v>
-      </c>
       <c r="U375" t="s">
         <v>215</v>
       </c>
@@ -29957,10 +29861,10 @@
         <v>199</v>
       </c>
       <c r="AH375" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI375" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="376" spans="1:35">
@@ -30034,10 +29938,10 @@
         <v>200</v>
       </c>
       <c r="AH376" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI376" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="377" spans="1:35">
@@ -30111,10 +30015,10 @@
         <v>201</v>
       </c>
       <c r="AH377" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI377" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="378" spans="1:35">
@@ -30163,9 +30067,6 @@
       <c r="S378" t="s">
         <v>199</v>
       </c>
-      <c r="T378" t="s">
-        <v>213</v>
-      </c>
       <c r="U378" t="s">
         <v>217</v>
       </c>
@@ -30188,10 +30089,10 @@
         <v>199</v>
       </c>
       <c r="AH378" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI378" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="379" spans="1:35">
@@ -30265,10 +30166,10 @@
         <v>202</v>
       </c>
       <c r="AH379" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI379" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="380" spans="1:35">
@@ -30342,10 +30243,10 @@
         <v>202</v>
       </c>
       <c r="AH380" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI380" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="381" spans="1:35">
@@ -30422,10 +30323,10 @@
         <v>198</v>
       </c>
       <c r="AH381" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI381" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="382" spans="1:35">
@@ -30474,9 +30375,6 @@
       <c r="S382" t="s">
         <v>199</v>
       </c>
-      <c r="T382" t="s">
-        <v>213</v>
-      </c>
       <c r="U382" t="s">
         <v>216</v>
       </c>
@@ -30499,10 +30397,10 @@
         <v>199</v>
       </c>
       <c r="AH382" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI382" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="383" spans="1:35">
@@ -30579,10 +30477,10 @@
         <v>198</v>
       </c>
       <c r="AH383" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI383" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="384" spans="1:35">
@@ -30631,9 +30529,6 @@
       <c r="S384" t="s">
         <v>199</v>
       </c>
-      <c r="T384" t="s">
-        <v>213</v>
-      </c>
       <c r="U384" t="s">
         <v>216</v>
       </c>
@@ -30656,10 +30551,10 @@
         <v>199</v>
       </c>
       <c r="AH384" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI384" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="385" spans="1:35">
@@ -30730,10 +30625,10 @@
         <v>198</v>
       </c>
       <c r="AH385" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI385" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="386" spans="1:35">
@@ -30810,10 +30705,10 @@
         <v>213</v>
       </c>
       <c r="AH386" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI386" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="387" spans="1:35">
@@ -30890,10 +30785,10 @@
         <v>203</v>
       </c>
       <c r="AH387" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI387" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="388" spans="1:35">
@@ -30970,10 +30865,10 @@
         <v>203</v>
       </c>
       <c r="AH388" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI388" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="389" spans="1:35">
@@ -31050,10 +30945,10 @@
         <v>203</v>
       </c>
       <c r="AH389" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI389" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="390" spans="1:35">
@@ -31130,10 +31025,10 @@
         <v>203</v>
       </c>
       <c r="AH390" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI390" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="391" spans="1:35">
@@ -31210,10 +31105,10 @@
         <v>203</v>
       </c>
       <c r="AH391" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI391" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="392" spans="1:35">
@@ -31290,10 +31185,10 @@
         <v>203</v>
       </c>
       <c r="AH392" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI392" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="393" spans="1:35">
@@ -31367,10 +31262,10 @@
         <v>203</v>
       </c>
       <c r="AH393" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI393" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="394" spans="1:35">
@@ -31447,10 +31342,10 @@
         <v>203</v>
       </c>
       <c r="AH394" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI394" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="395" spans="1:35">
@@ -31527,10 +31422,10 @@
         <v>203</v>
       </c>
       <c r="AH395" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI395" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="396" spans="1:35">
@@ -31607,10 +31502,10 @@
         <v>203</v>
       </c>
       <c r="AH396" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI396" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="397" spans="1:35">
@@ -31684,10 +31579,10 @@
         <v>203</v>
       </c>
       <c r="AH397" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI397" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="398" spans="1:35">
@@ -31761,10 +31656,10 @@
         <v>203</v>
       </c>
       <c r="AH398" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI398" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="399" spans="1:35">
@@ -31841,10 +31736,10 @@
         <v>203</v>
       </c>
       <c r="AH399" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI399" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="400" spans="1:35">
@@ -31921,10 +31816,10 @@
         <v>203</v>
       </c>
       <c r="AH400" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI400" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="401" spans="1:35">
@@ -32001,10 +31896,10 @@
         <v>203</v>
       </c>
       <c r="AH401" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI401" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="402" spans="1:35">
@@ -32078,10 +31973,10 @@
         <v>203</v>
       </c>
       <c r="AH402" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI402" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="403" spans="1:35">
@@ -32155,10 +32050,10 @@
         <v>203</v>
       </c>
       <c r="AH403" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AI403" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="404" spans="1:35">
@@ -32232,10 +32127,10 @@
         <v>204</v>
       </c>
       <c r="AH404" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI404" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="405" spans="1:35">
@@ -32309,10 +32204,10 @@
         <v>204</v>
       </c>
       <c r="AH405" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI405" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="406" spans="1:35">
@@ -32386,10 +32281,10 @@
         <v>204</v>
       </c>
       <c r="AH406" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI406" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="407" spans="1:35">
@@ -32463,10 +32358,10 @@
         <v>204</v>
       </c>
       <c r="AH407" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI407" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="408" spans="1:35">
@@ -32537,10 +32432,10 @@
         <v>204</v>
       </c>
       <c r="AH408" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI408" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="409" spans="1:35">
@@ -32611,10 +32506,10 @@
         <v>204</v>
       </c>
       <c r="AH409" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI409" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="410" spans="1:35">
@@ -32688,10 +32583,10 @@
         <v>204</v>
       </c>
       <c r="AH410" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI410" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="411" spans="1:35">
@@ -32765,10 +32660,10 @@
         <v>204</v>
       </c>
       <c r="AH411" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI411" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="412" spans="1:35">
@@ -32839,10 +32734,10 @@
         <v>204</v>
       </c>
       <c r="AH412" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI412" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="413" spans="1:35">
@@ -32916,10 +32811,10 @@
         <v>204</v>
       </c>
       <c r="AH413" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI413" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="414" spans="1:35">
@@ -32993,10 +32888,10 @@
         <v>204</v>
       </c>
       <c r="AH414" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AI414" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="415" spans="1:35">
@@ -33070,10 +32965,10 @@
         <v>204</v>
       </c>
       <c r="AH415" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI415" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="416" spans="1:35">
@@ -33147,10 +33042,10 @@
         <v>204</v>
       </c>
       <c r="AH416" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI416" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="417" spans="1:35">
@@ -33224,10 +33119,10 @@
         <v>204</v>
       </c>
       <c r="AH417" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI417" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="418" spans="1:35">
@@ -33301,10 +33196,10 @@
         <v>204</v>
       </c>
       <c r="AH418" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI418" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="419" spans="1:35">
@@ -33378,10 +33273,10 @@
         <v>204</v>
       </c>
       <c r="AH419" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI419" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="420" spans="1:35">
@@ -33455,10 +33350,10 @@
         <v>204</v>
       </c>
       <c r="AH420" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI420" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="421" spans="1:35">
@@ -33532,10 +33427,10 @@
         <v>204</v>
       </c>
       <c r="AH421" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI421" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="422" spans="1:35">
@@ -33609,10 +33504,10 @@
         <v>204</v>
       </c>
       <c r="AH422" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI422" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="423" spans="1:35">
@@ -33686,10 +33581,10 @@
         <v>204</v>
       </c>
       <c r="AH423" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI423" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="424" spans="1:35">
@@ -33763,10 +33658,10 @@
         <v>204</v>
       </c>
       <c r="AH424" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI424" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="425" spans="1:35">
@@ -33840,10 +33735,10 @@
         <v>204</v>
       </c>
       <c r="AH425" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI425" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="426" spans="1:35">
@@ -33917,10 +33812,10 @@
         <v>204</v>
       </c>
       <c r="AH426" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI426" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="427" spans="1:35">
@@ -33994,10 +33889,10 @@
         <v>204</v>
       </c>
       <c r="AH427" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI427" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="428" spans="1:35">
@@ -34071,10 +33966,10 @@
         <v>204</v>
       </c>
       <c r="AH428" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI428" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="429" spans="1:35">
@@ -34148,10 +34043,10 @@
         <v>204</v>
       </c>
       <c r="AH429" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI429" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="430" spans="1:35">
@@ -34225,10 +34120,10 @@
         <v>204</v>
       </c>
       <c r="AH430" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI430" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="431" spans="1:35">
@@ -34302,10 +34197,10 @@
         <v>204</v>
       </c>
       <c r="AH431" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI431" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="432" spans="1:35">
@@ -34379,10 +34274,10 @@
         <v>204</v>
       </c>
       <c r="AH432" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI432" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="433" spans="1:35">
@@ -34456,10 +34351,10 @@
         <v>204</v>
       </c>
       <c r="AH433" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI433" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="434" spans="1:35">
@@ -34533,10 +34428,10 @@
         <v>204</v>
       </c>
       <c r="AH434" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI434" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="435" spans="1:35">
@@ -34610,10 +34505,10 @@
         <v>204</v>
       </c>
       <c r="AH435" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI435" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="436" spans="1:35">
@@ -34687,10 +34582,10 @@
         <v>204</v>
       </c>
       <c r="AH436" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI436" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="437" spans="1:35">
@@ -34764,10 +34659,10 @@
         <v>204</v>
       </c>
       <c r="AH437" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI437" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="438" spans="1:35">
@@ -34841,10 +34736,10 @@
         <v>204</v>
       </c>
       <c r="AH438" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI438" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="439" spans="1:35">
@@ -34918,10 +34813,10 @@
         <v>204</v>
       </c>
       <c r="AH439" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI439" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="440" spans="1:35">
@@ -34995,10 +34890,10 @@
         <v>54</v>
       </c>
       <c r="AH440" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI440" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="441" spans="1:35">
@@ -35072,10 +34967,10 @@
         <v>54</v>
       </c>
       <c r="AH441" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI441" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="442" spans="1:35">
@@ -35149,10 +35044,10 @@
         <v>54</v>
       </c>
       <c r="AH442" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI442" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="443" spans="1:35">
@@ -35226,10 +35121,10 @@
         <v>54</v>
       </c>
       <c r="AH443" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI443" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="444" spans="1:35">
@@ -35303,10 +35198,10 @@
         <v>205</v>
       </c>
       <c r="AH444" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI444" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="445" spans="1:35">
@@ -35380,10 +35275,10 @@
         <v>55</v>
       </c>
       <c r="AH445" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI445" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="446" spans="1:35">
@@ -35457,10 +35352,10 @@
         <v>54</v>
       </c>
       <c r="AH446" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI446" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="447" spans="1:35">
@@ -35534,10 +35429,10 @@
         <v>54</v>
       </c>
       <c r="AH447" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI447" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="448" spans="1:35">
@@ -35611,10 +35506,10 @@
         <v>54</v>
       </c>
       <c r="AH448" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI448" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="449" spans="1:35">
@@ -35688,10 +35583,10 @@
         <v>205</v>
       </c>
       <c r="AH449" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI449" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="450" spans="1:35">
@@ -35765,10 +35660,10 @@
         <v>54</v>
       </c>
       <c r="AH450" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI450" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="451" spans="1:35">
@@ -35842,10 +35737,10 @@
         <v>205</v>
       </c>
       <c r="AH451" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI451" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="452" spans="1:35">
@@ -35919,10 +35814,10 @@
         <v>54</v>
       </c>
       <c r="AH452" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AI452" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="453" spans="1:35">
@@ -35996,10 +35891,10 @@
         <v>54</v>
       </c>
       <c r="AH453" t="s">
-        <v>415</v>
+        <v>416</v>
      